--- a/tools/static-site/ISE_Data_Entry.xlsx
+++ b/tools/static-site/ISE_Data_Entry.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="how to use" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pages" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="edges" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="how to use" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="pages" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="edges" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'pages'!$A$1:$T$262</definedName>
@@ -10682,6 +10682,11 @@
           <t>imp-senators-stock-purchases-barring-members</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>etype: observational</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -10719,6 +10724,11 @@
           <t>imp-trades-placed-before-barring-members</t>
         </is>
       </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>etype: observational | erq: 2 | erp: 50</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -10756,6 +10766,11 @@
           <t>imp-78-members-117th-barring-members</t>
         </is>
       </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>etype: statistics</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -10793,6 +10808,11 @@
           <t>imp-131-federal-judges-barring-members</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>etype: statistics</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -10835,6 +10855,11 @@
           <t>uniq-federal-reserve-officials-federal-reserve</t>
         </is>
       </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>etype: record</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -10872,6 +10897,11 @@
           <t>imp-congressional-portfolios-underperformed-barring-members</t>
         </is>
       </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>etype: observational</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -10909,6 +10939,11 @@
           <t>imp-no-evidence-members-barring-members</t>
         </is>
       </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>etype: observational | erq: 2 | erp: 50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -12866,6 +12901,11 @@
           <t>Office of Legal Counsel opinion, January 20, 2017</t>
         </is>
       </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>etype: record</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -12893,6 +12933,11 @@
           <t>Congressional nomination records and contemporaneous reporting, 2025 to 2026</t>
         </is>
       </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>etype: record</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -12920,6 +12965,11 @@
           <t>Office of Government Ethics filings reported July 2017</t>
         </is>
       </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>etype: record</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -12947,6 +12997,11 @@
           <t>OpenSecrets analysis, June 2020</t>
         </is>
       </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>etype: statistics</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -14147,6 +14202,11 @@
           <t>House Ways and Means Committee report and release of tax years 2015 to 2020, December 2022</t>
         </is>
       </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>etype: record</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
@@ -14174,6 +14234,11 @@
           <t>Joint Committee on Taxation review, April 1974</t>
         </is>
       </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>etype: record</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
@@ -14201,6 +14266,11 @@
           <t>Office of Government Ethics, Public Financial Disclosure Guide (2024)</t>
         </is>
       </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>etype: record</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
@@ -14228,6 +14298,11 @@
           <t>Patterson v. Padilla, California Supreme Court, November 21, 2019</t>
         </is>
       </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>etype: record</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
@@ -15421,6 +15496,11 @@
           <t>Economist and YouGov poll, December 2025</t>
         </is>
       </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>etype: survey</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
@@ -15448,6 +15528,11 @@
           <t>Opinion of Chief Judge Beryl Howell, unsealed December 1, 2020</t>
         </is>
       </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>etype: record</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
@@ -15475,6 +15560,11 @@
           <t>Collateral Consequences Resource Center fifty-state survey, 2024 to 2025</t>
         </is>
       </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>etype: statistics</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
@@ -15502,6 +15592,11 @@
           <t>Ex parte Garland, 71 U.S. 333 (1866)</t>
         </is>
       </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>etype: record</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
@@ -15532,6 +15627,11 @@
       <c r="G206" s="4" t="inlineStr">
         <is>
           <t>evid-proposals-let-congress-letting-congress</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>etype: record</t>
         </is>
       </c>
     </row>

--- a/tools/static-site/ISE_Data_Entry.xlsx
+++ b/tools/static-site/ISE_Data_Entry.xlsx
@@ -12,7 +12,7 @@
     <sheet name="edges" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'pages'!$A$1:$T$262</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'pages'!$A$1:$W$262</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'edges'!$A$1:$R$885</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -230,35 +230,50 @@
     </comment>
     <comment ref="N1" authorId="0" shapeId="0">
       <text>
-        <t>interest: what the measure shows if the belief is true.</t>
+        <t>What this claim rests on, if it is an observed finding: statistics, record, rct, meta, observational, historical, expert_data, expert_claim, anecdote, logic, analogy, norm, intuition, news, survey, eyewitness, visual, artifact. Blank means nothing observed, and the claim starts at a coin flip. Classify what the sentence asserts, not the instrument: "58 percent told a pollster X" is statistics; "Americans believe X" is survey.</t>
       </text>
     </comment>
     <comment ref="O1" authorId="0" shapeId="0">
       <text>
-        <t>interest: what it shows if the belief is false.</t>
+        <t>Independent replications of this finding. Blank counts as one, the finding itself.</t>
       </text>
     </comment>
     <comment ref="P1" authorId="0" shapeId="0">
       <text>
-        <t>interest: the latest reading, with source.</t>
+        <t>Percent of those replications that agreed. Blank counts as 100. At 50 the claim starts at a coin flip whatever its source type, because a contested literature has established nothing.</t>
       </text>
     </comment>
     <comment ref="Q1" authorId="0" shapeId="0">
       <text>
-        <t>The one-sentence answer in the check table.</t>
+        <t>interest: what the measure shows if the belief is true.</t>
       </text>
     </comment>
     <comment ref="R1" authorId="0" shapeId="0">
       <text>
-        <t>The one typed line in the scorecard.</t>
+        <t>interest: what it shows if the belief is false.</t>
       </text>
     </comment>
     <comment ref="S1" authorId="0" shapeId="0">
       <text>
+        <t>interest: the latest reading, with source.</t>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0" shapeId="0">
+      <text>
+        <t>The one-sentence answer in the check table.</t>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0" shapeId="0">
+      <text>
+        <t>The one typed line in the scorecard.</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0">
+      <text>
         <t>belief: -100 to +100 on the topic page.</t>
       </text>
     </comment>
-    <comment ref="T1" authorId="0" shapeId="0">
+    <comment ref="W1" authorId="0" shapeId="0">
       <text>
         <t>belief: the logical form of the claim.</t>
       </text>
@@ -755,7 +770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T262"/>
+  <dimension ref="A1:W262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -771,9 +786,9 @@
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="50" customWidth="1" min="12" max="12"/>
     <col width="40" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
-    <col width="50" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="60" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
@@ -848,35 +863,50 @@
       </c>
       <c r="N1" s="3" t="inlineStr">
         <is>
+          <t>etype</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>erq</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>erp</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
           <t>if_true</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>if_false</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>bridge</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>bottom_line</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>positivity</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>form</t>
         </is>
@@ -906,15 +936,15 @@
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="R2" s="4" t="inlineStr">
+      <c r="U2" s="4" t="inlineStr">
         <is>
           <t>The conflict is documented and the disclosure regime demonstrably fails. Whether a ban removes the conflict or relocates it into spouses, partnerships and the revolving door is the open question, and it is the component that holds this page's truth score down.</t>
         </is>
       </c>
-      <c r="S2" s="5" t="n">
+      <c r="V2" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="T2" s="4" t="inlineStr">
+      <c r="W2" s="4" t="inlineStr">
         <is>
           <t>(Officials' holdings currently influence official decisions) AND (removing the holdings removes the influence rather than relocating it) AND (a ban can be enacted and enforced). The normative component, that reducing conflicts is worth a narrower candidate pool, is separable.</t>
         </is>
@@ -944,15 +974,15 @@
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>The legal gap is documented and the supervision problem is real. The page turns on whether a bar removes the conflict or converts a disclosed adviser into an undisclosed one. Two load-bearing components are tied at the cap, so the truth score other pages read sits below what the arguments alone support.</t>
         </is>
       </c>
-      <c r="S3" s="5" t="n">
+      <c r="V3" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>(Relatives in official roles produce conflicts that ordinary supervision cannot check) AND (a bar removes those conflicts rather than driving them out of view) AND (Congress can impose the bar on the White House). The third component is where the legal fight is.</t>
         </is>
@@ -982,15 +1012,15 @@
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="R4" s="4" t="inlineStr">
+      <c r="U4" s="4" t="inlineStr">
         <is>
           <t>The documentary claim is the strongest part: returns do carry conflict-relevant facts the disclosure form omits. What nobody can show is that publishing them changes anything. All three load-bearing components sit at the same argued level, so what caps this page is the whole anatomy rather than any one part of it.</t>
         </is>
       </c>
-      <c r="S4" s="5" t="n">
+      <c r="V4" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="T4" s="4" t="inlineStr">
+      <c r="W4" s="4" t="inlineStr">
         <is>
           <t>(Returns contain conflict-relevant information the disclosure form lacks) AND (publishing it changes behavior or enables a check) AND (a publication requirement can be imposed). The first is documentary, the second is contested, the third is narrower than the usual objection assumes.</t>
         </is>
@@ -1020,15 +1050,15 @@
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="R5" s="4" t="inlineStr">
+      <c r="U5" s="4" t="inlineStr">
         <is>
           <t>The gap is real: clemency is the only federal power with no check, and grants to the president's own circle are documented in both parties. The component that caps this page is not the constitutional objection, which scores higher here than its citation rate suggests. It is whether an override could ever be exercised at a two-thirds threshold against a president whose own party holds a third of either chamber.</t>
         </is>
       </c>
-      <c r="S5" s="5" t="n">
+      <c r="V5" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="T5" s="4" t="inlineStr">
+      <c r="W5" s="4" t="inlineStr">
         <is>
           <t>(Some pardons are granted for the president's private benefit) AND (a congressional override would deter or reverse those grants) AND (an override can be enacted). The third component is legal rather than empirical, and it is the one that holds this page down.</t>
         </is>
@@ -1053,12 +1083,12 @@
           <t>Public office should not be usable for private gain.</t>
         </is>
       </c>
-      <c r="R6" s="4" t="inlineStr">
+      <c r="U6" s="4" t="inlineStr">
         <is>
           <t>Held nearly universally at this level of generality, which is why the argument always moves to the specific rules below it.</t>
         </is>
       </c>
-      <c r="S6" s="5" t="n">
+      <c r="V6" s="5" t="n">
         <v>80</v>
       </c>
     </row>
@@ -1086,7 +1116,7 @@
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="R7" s="4" t="inlineStr">
+      <c r="U7" s="4" t="inlineStr">
         <is>
           <t>True as legal history; that is a weaker claim than the principle itself.</t>
         </is>
@@ -1116,7 +1146,7 @@
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="R8" s="4" t="inlineStr">
+      <c r="U8" s="4" t="inlineStr">
         <is>
           <t>The mechanism is right in the extreme case; the size of the effect at low levels of self-dealing is not established here.</t>
         </is>
@@ -1146,7 +1176,7 @@
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="R9" s="4" t="inlineStr">
+      <c r="U9" s="4" t="inlineStr">
         <is>
           <t>Well measured for the stock trading case; it says what people want, not what is right.</t>
         </is>
@@ -1176,7 +1206,7 @@
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="R10" s="4" t="inlineStr">
+      <c r="U10" s="4" t="inlineStr">
         <is>
           <t>A real objection to using the principle as a decision rule, not to holding it.</t>
         </is>
@@ -1206,7 +1236,7 @@
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="R11" s="4" t="inlineStr">
+      <c r="U11" s="4" t="inlineStr">
         <is>
           <t>A reductio that the drafted versions of these rules already avoid.</t>
         </is>
@@ -1236,7 +1266,7 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R12" s="4" t="inlineStr">
+      <c r="U12" s="4" t="inlineStr">
         <is>
           <t>The overlap is documented; what it causes is the contested part.</t>
         </is>
@@ -1266,7 +1296,7 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R13" s="4" t="inlineStr">
+      <c r="U13" s="4" t="inlineStr">
         <is>
           <t>The enforcement record is strong evidence; it shows the reporting regime is unenforced, not that trades were corrupt.</t>
         </is>
@@ -1296,7 +1326,7 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R14" s="4" t="inlineStr">
+      <c r="U14" s="4" t="inlineStr">
         <is>
           <t>The strongest structural argument on the page: it changes what has to be proven.</t>
         </is>
@@ -1326,7 +1356,7 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R15" s="4" t="inlineStr">
+      <c r="U15" s="4" t="inlineStr">
         <is>
           <t>A live natural experiment in a nearby institution, with a real scope objection.</t>
         </is>
@@ -1356,7 +1386,7 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R16" s="4" t="inlineStr">
+      <c r="U16" s="4" t="inlineStr">
         <is>
           <t>The enforcement asymmetry is real; it is evidence about provability, not about guilt.</t>
         </is>
@@ -1386,7 +1416,7 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R17" s="4" t="inlineStr">
+      <c r="U17" s="4" t="inlineStr">
         <is>
           <t>The aggregate finding is solid and the rebuttal is that aggregates are the wrong place to look.</t>
         </is>
@@ -1416,7 +1446,7 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R18" s="4" t="inlineStr">
+      <c r="U18" s="4" t="inlineStr">
         <is>
           <t>A real drafting objection that the Fed template already answers in part.</t>
         </is>
@@ -1446,7 +1476,7 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R19" s="4" t="inlineStr">
+      <c r="U19" s="4" t="inlineStr">
         <is>
           <t>The cost is real and largely fixable in drafting; the rebuttal is stronger than the argument.</t>
         </is>
@@ -1476,7 +1506,7 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R20" s="4" t="inlineStr">
+      <c r="U20" s="4" t="inlineStr">
         <is>
           <t>Weakest of the four: the restriction is common elsewhere in government and the office is voluntary.</t>
         </is>
@@ -1506,7 +1536,7 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R21" s="4" t="inlineStr">
+      <c r="U21" s="4" t="inlineStr">
         <is>
           <t>The best argument against: it predicts the failure mode from the closest precedent.</t>
         </is>
@@ -1536,7 +1566,12 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R22" s="4" t="inlineStr">
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observational</t>
+        </is>
+      </c>
+      <c r="U22" s="4" t="inlineStr">
         <is>
           <t>Methodologically solid for its period; its period is the problem.</t>
         </is>
@@ -1566,7 +1601,22 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R23" s="4" t="inlineStr">
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observational</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="U23" s="4" t="inlineStr">
         <is>
           <t>The most direct answer to the underperformance studies, and the newest, which cuts both ways.</t>
         </is>
@@ -1596,7 +1646,12 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R24" s="4" t="inlineStr">
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>statistics</t>
+        </is>
+      </c>
+      <c r="U24" s="4" t="inlineStr">
         <is>
           <t>Accurate as a count of filing failures; frequently oversold as a count of misconduct.</t>
         </is>
@@ -1626,7 +1681,12 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R25" s="4" t="inlineStr">
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>statistics</t>
+        </is>
+      </c>
+      <c r="U25" s="4" t="inlineStr">
         <is>
           <t>Strong evidence about disclosure regimes generally; one institution removed from the belief.</t>
         </is>
@@ -1656,7 +1716,12 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R26" s="4" t="inlineStr">
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="U26" s="4" t="inlineStr">
         <is>
           <t>Establishes that the rule is workable; says little yet about its long-run costs.</t>
         </is>
@@ -1686,7 +1751,12 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R27" s="4" t="inlineStr">
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observational</t>
+        </is>
+      </c>
+      <c r="U27" s="4" t="inlineStr">
         <is>
           <t>The strongest single piece of evidence against, and its known weakness is that averages hide tails.</t>
         </is>
@@ -1716,7 +1786,22 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R28" s="4" t="inlineStr">
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observational</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="U28" s="4" t="inlineStr">
         <is>
           <t>Directly on point for the trading-advantage claim; silent on the voting-conflict claim.</t>
         </is>
@@ -1746,7 +1831,7 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R29" s="4" t="inlineStr">
+      <c r="U29" s="4" t="inlineStr">
         <is>
           <t>Pending, and the metric is gameable in a way the prediction should name.</t>
         </is>
@@ -1776,7 +1861,7 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R30" s="4" t="inlineStr">
+      <c r="U30" s="4" t="inlineStr">
         <is>
           <t>Weakly diagnostic: a lot of noise for one signal.</t>
         </is>
@@ -1806,7 +1891,7 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R31" s="4" t="inlineStr">
+      <c r="U31" s="4" t="inlineStr">
         <is>
           <t>The single most informative study nobody has run.</t>
         </is>
@@ -1836,7 +1921,7 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R32" s="4" t="inlineStr">
+      <c r="U32" s="4" t="inlineStr">
         <is>
           <t>The most likely way the belief fails, and the one the drafting can answer.</t>
         </is>
@@ -1866,7 +1951,7 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R33" s="4" t="inlineStr">
+      <c r="U33" s="4" t="inlineStr">
         <is>
           <t>Testable from existing data, and the base rate makes a large move unlikely.</t>
         </is>
@@ -1896,7 +1981,7 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R34" s="4" t="inlineStr">
+      <c r="U34" s="4" t="inlineStr">
         <is>
           <t>Would weaken one branch of the tree and leave the other standing.</t>
         </is>
@@ -1926,7 +2011,7 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R35" s="4" t="inlineStr">
+      <c r="U35" s="4" t="inlineStr">
         <is>
           <t>Mechanically near-certain in direction, contested in size.</t>
         </is>
@@ -1956,7 +2041,7 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R36" s="4" t="inlineStr">
+      <c r="U36" s="4" t="inlineStr">
         <is>
           <t>Direction certain, magnitude resting on a contested base rate.</t>
         </is>
@@ -1986,7 +2071,7 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R37" s="4" t="inlineStr">
+      <c r="U37" s="4" t="inlineStr">
         <is>
           <t>The benefit most often claimed and the least supported by the record.</t>
         </is>
@@ -2016,7 +2101,7 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R38" s="4" t="inlineStr">
+      <c r="U38" s="4" t="inlineStr">
         <is>
           <t>Plausible and small; the Fed rule suggests the saving is partly offset.</t>
         </is>
@@ -2046,7 +2131,7 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R39" s="4" t="inlineStr">
+      <c r="U39" s="4" t="inlineStr">
         <is>
           <t>Real and largely solvable in drafting.</t>
         </is>
@@ -2076,7 +2161,7 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R40" s="4" t="inlineStr">
+      <c r="U40" s="4" t="inlineStr">
         <is>
           <t>The mechanism is real; the affected group is narrower than the argument implies.</t>
         </is>
@@ -2106,7 +2191,7 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R41" s="4" t="inlineStr">
+      <c r="U41" s="4" t="inlineStr">
         <is>
           <t>A cost that only exists to the extent the belief's own premise is true, and it falls on an interest almost nobody defends.</t>
         </is>
@@ -2236,7 +2321,7 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R46" s="4" t="inlineStr">
+      <c r="U46" s="4" t="inlineStr">
         <is>
           <t>Documented as correlation, not established as influence. This is the load-bearing claim the whole belief rests on.</t>
         </is>
@@ -2266,7 +2351,7 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R47" s="4" t="inlineStr">
+      <c r="U47" s="4" t="inlineStr">
         <is>
           <t>The weakest load-bearing part, and the one that caps the page.</t>
         </is>
@@ -2296,7 +2381,7 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R48" s="4" t="inlineStr">
+      <c r="U48" s="4" t="inlineStr">
         <is>
           <t>Much stronger than it was two years ago, and still unfinished.</t>
         </is>
@@ -2326,7 +2411,7 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R49" s="4" t="inlineStr">
+      <c r="U49" s="4" t="inlineStr">
         <is>
           <t>A value judgment that the cost-benefit table prices rather than settles.</t>
         </is>
@@ -2431,7 +2516,7 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R53" s="4" t="inlineStr">
+      <c r="U53" s="4" t="inlineStr">
         <is>
           <t>The most defensible version on offer; its weakness is political, not analytical.</t>
         </is>
@@ -2661,7 +2746,7 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R62" s="4" t="inlineStr">
+      <c r="U62" s="4" t="inlineStr">
         <is>
           <t>Listed on the weakening side because it is cited that way; the linkage page is where that gets tested.</t>
         </is>
@@ -2866,7 +2951,7 @@
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="R70" s="4" t="inlineStr">
+      <c r="U70" s="4" t="inlineStr">
         <is>
           <t>Accurate as a quotation, misleading as a summary of her final position.</t>
         </is>
@@ -2896,7 +2981,7 @@
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="R71" s="4" t="inlineStr">
+      <c r="U71" s="4" t="inlineStr">
         <is>
           <t>The legal gap is real and was formally relied upon; whether a court would agree has never been tested.</t>
         </is>
@@ -2926,7 +3011,7 @@
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="R72" s="4" t="inlineStr">
+      <c r="U72" s="4" t="inlineStr">
         <is>
           <t>The strongest argument on the page: it names a mechanism that does not depend on anyone's motives.</t>
         </is>
@@ -2956,7 +3041,7 @@
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="R73" s="4" t="inlineStr">
+      <c r="U73" s="4" t="inlineStr">
         <is>
           <t>Concrete and current; the rebuttal points at a narrower remedy.</t>
         </is>
@@ -2986,7 +3071,7 @@
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="R74" s="4" t="inlineStr">
+      <c r="U74" s="4" t="inlineStr">
         <is>
           <t>True, and the rebuttal reframes the whole proposal as an enforcement question.</t>
         </is>
@@ -3016,7 +3101,7 @@
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="R75" s="4" t="inlineStr">
+      <c r="U75" s="4" t="inlineStr">
         <is>
           <t>The best argument against, and it is answered only if the rule is drafted around function rather than title.</t>
         </is>
@@ -3046,7 +3131,7 @@
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="R76" s="4" t="inlineStr">
+      <c r="U76" s="4" t="inlineStr">
         <is>
           <t>A genuine scope objection: the proposal is aimed at a smaller target than the grievance that motivates it.</t>
         </is>
@@ -3076,7 +3161,7 @@
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="R77" s="4" t="inlineStr">
+      <c r="U77" s="4" t="inlineStr">
         <is>
           <t>Strong for White House staff, weak for Senate-confirmed posts.</t>
         </is>
@@ -3106,7 +3191,7 @@
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="R78" s="4" t="inlineStr">
+      <c r="U78" s="4" t="inlineStr">
         <is>
           <t>Answers an argument the proposal does not make.</t>
         </is>
@@ -3136,7 +3221,12 @@
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="R79" s="4" t="inlineStr">
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="U79" s="4" t="inlineStr">
         <is>
           <t>Authoritative in practice, untested in court.</t>
         </is>
@@ -3166,7 +3256,12 @@
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="R80" s="4" t="inlineStr">
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="U80" s="4" t="inlineStr">
         <is>
           <t>Current and verifiable; the confirmation point cuts against reading it as an unchecked practice.</t>
         </is>
@@ -3196,7 +3291,12 @@
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="R81" s="4" t="inlineStr">
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="U81" s="4" t="inlineStr">
         <is>
           <t>The concrete form of the "inside the rules" argument.</t>
         </is>
@@ -3226,7 +3326,12 @@
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="R82" s="4" t="inlineStr">
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>statistics</t>
+        </is>
+      </c>
+      <c r="U82" s="4" t="inlineStr">
         <is>
           <t>Shows where the money actually moves, which is not where the proposal points.</t>
         </is>
@@ -3256,7 +3361,7 @@
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="R83" s="4" t="inlineStr">
+      <c r="U83" s="4" t="inlineStr">
         <is>
           <t>Easy to measure and easy to satisfy without changing anything, which is the objection in one line.</t>
         </is>
@@ -3286,7 +3391,7 @@
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="R84" s="4" t="inlineStr">
+      <c r="U84" s="4" t="inlineStr">
         <is>
           <t>The right thing to measure, measured by a proxy that moves for other reasons.</t>
         </is>
@@ -3316,7 +3421,7 @@
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="R85" s="4" t="inlineStr">
+      <c r="U85" s="4" t="inlineStr">
         <is>
           <t>The way this belief most plausibly fails.</t>
         </is>
@@ -3496,7 +3601,7 @@
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="R92" s="4" t="inlineStr">
+      <c r="U92" s="4" t="inlineStr">
         <is>
           <t>Contested, and the disagreement is the mirror image of the "inside the rules" argument.</t>
         </is>
@@ -3526,7 +3631,7 @@
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="R93" s="4" t="inlineStr">
+      <c r="U93" s="4" t="inlineStr">
         <is>
           <t>Tied for weakest load-bearing component on this page, which is why the cap bites.</t>
         </is>
@@ -3556,7 +3661,7 @@
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="R94" s="4" t="inlineStr">
+      <c r="U94" s="4" t="inlineStr">
         <is>
           <t>More defensible than the pardon case and less settled than the stock case.</t>
         </is>
@@ -3661,7 +3766,7 @@
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="R98" s="4" t="inlineStr">
+      <c r="U98" s="4" t="inlineStr">
         <is>
           <t>The factual claim about what each document contains is correct; whether the extra content is what screens conflicts is the argument.</t>
         </is>
@@ -3691,7 +3796,7 @@
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="R99" s="4" t="inlineStr">
+      <c r="U99" s="4" t="inlineStr">
         <is>
           <t>The strongest evidence on the page, and it is about the audit rather than about publication.</t>
         </is>
@@ -3721,7 +3826,7 @@
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="R100" s="4" t="inlineStr">
+      <c r="U100" s="4" t="inlineStr">
         <is>
           <t>Accurate history; the step from norm to statute is the contested part.</t>
         </is>
@@ -3751,7 +3856,7 @@
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="R101" s="4" t="inlineStr">
+      <c r="U101" s="4" t="inlineStr">
         <is>
           <t>The structural argument, and the one least dependent on any particular administration.</t>
         </is>
@@ -3781,7 +3886,7 @@
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="R102" s="4" t="inlineStr">
+      <c r="U102" s="4" t="inlineStr">
         <is>
           <t>The best argument against, and the rebuttal is specific enough to test.</t>
         </is>
@@ -3811,7 +3916,7 @@
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="R103" s="4" t="inlineStr">
+      <c r="U103" s="4" t="inlineStr">
         <is>
           <t>A real privacy cost with a partial drafting answer.</t>
         </is>
@@ -3841,7 +3946,7 @@
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="R104" s="4" t="inlineStr">
+      <c r="U104" s="4" t="inlineStr">
         <is>
           <t>The precedent is real and much narrower than the argument treats it.</t>
         </is>
@@ -3871,7 +3976,7 @@
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="R105" s="4" t="inlineStr">
+      <c r="U105" s="4" t="inlineStr">
         <is>
           <t>The most technically substantive objection on the page.</t>
         </is>
@@ -3901,7 +4006,12 @@
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="R106" s="4" t="inlineStr">
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="U106" s="4" t="inlineStr">
         <is>
           <t>The dates are documentary and the characterization is the committee's.</t>
         </is>
@@ -3931,7 +4041,12 @@
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="R107" s="4" t="inlineStr">
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="U107" s="4" t="inlineStr">
         <is>
           <t>The founding case of the norm, and it cuts slightly against compulsion.</t>
         </is>
@@ -3961,7 +4076,12 @@
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="R108" s="4" t="inlineStr">
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="U108" s="4" t="inlineStr">
         <is>
           <t>Accurate, and the range structure is exactly what the other side points at.</t>
         </is>
@@ -3991,7 +4111,12 @@
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="R109" s="4" t="inlineStr">
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="U109" s="4" t="inlineStr">
         <is>
           <t>Frequently cited for more than it holds, which is what its linkage page is for.</t>
         </is>
@@ -4021,7 +4146,7 @@
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="R110" s="4" t="inlineStr">
+      <c r="U110" s="4" t="inlineStr">
         <is>
           <t>Diagnostic, and its failure would be ambiguous between deterrence and nothing to find.</t>
         </is>
@@ -4051,7 +4176,7 @@
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="R111" s="4" t="inlineStr">
+      <c r="U111" s="4" t="inlineStr">
         <is>
           <t>Directly testable against the one case where both documents exist.</t>
         </is>
@@ -4231,7 +4356,7 @@
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="R118" s="4" t="inlineStr">
+      <c r="U118" s="4" t="inlineStr">
         <is>
           <t>The most checkable component on any of these four pages.</t>
         </is>
@@ -4261,7 +4386,7 @@
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="R119" s="4" t="inlineStr">
+      <c r="U119" s="4" t="inlineStr">
         <is>
           <t>The weak link in substance, and it scores level with the other two rather than below them.</t>
         </is>
@@ -4291,7 +4416,7 @@
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="R120" s="4" t="inlineStr">
+      <c r="U120" s="4" t="inlineStr">
         <is>
           <t>Stronger than the pardon case: the disclosure precedent is well established.</t>
         </is>
@@ -4396,7 +4521,7 @@
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="R124" s="4" t="inlineStr">
+      <c r="U124" s="4" t="inlineStr">
         <is>
           <t>Structurally accurate. Whether the absence of a check is a defect or the point is the whole argument.</t>
         </is>
@@ -4426,7 +4551,7 @@
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="R125" s="4" t="inlineStr">
+      <c r="U125" s="4" t="inlineStr">
         <is>
           <t>The pattern is documented across parties, which is what makes it a structural argument rather than a partisan one.</t>
         </is>
@@ -4456,7 +4581,7 @@
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="R126" s="4" t="inlineStr">
+      <c r="U126" s="4" t="inlineStr">
         <is>
           <t>The threshold argument cuts both ways, and the page should show that rather than resolve it.</t>
         </is>
@@ -4486,7 +4611,7 @@
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="R127" s="4" t="inlineStr">
+      <c r="U127" s="4" t="inlineStr">
         <is>
           <t>The best evidence that a check is workable, and the rebuttal correctly identifies that it is not this check.</t>
         </is>
@@ -4516,7 +4641,7 @@
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="R128" s="4" t="inlineStr">
+      <c r="U128" s="4" t="inlineStr">
         <is>
           <t>Decisive against a statute and not against the belief as written, which is why it is a component question rather than a refutation.</t>
         </is>
@@ -4546,7 +4671,7 @@
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="R129" s="4" t="inlineStr">
+      <c r="U129" s="4" t="inlineStr">
         <is>
           <t>The strongest argument on the page in principle, and the two-thirds threshold is a real answer to it.</t>
         </is>
@@ -4576,7 +4701,7 @@
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="R130" s="4" t="inlineStr">
+      <c r="U130" s="4" t="inlineStr">
         <is>
           <t>A serious design objection with an obvious drafting answer that no proposal has adopted.</t>
         </is>
@@ -4606,7 +4731,7 @@
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="R131" s="4" t="inlineStr">
+      <c r="U131" s="4" t="inlineStr">
         <is>
           <t>The most practical alternative, and the response is that it has never actually been used.</t>
         </is>
@@ -4636,7 +4761,12 @@
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="R132" s="4" t="inlineStr">
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>statistics</t>
+        </is>
+      </c>
+      <c r="U132" s="4" t="inlineStr">
         <is>
           <t>Real support, and the crosstabs are the reason to doubt the amendment path.</t>
         </is>
@@ -4666,7 +4796,12 @@
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="R133" s="4" t="inlineStr">
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="U133" s="4" t="inlineStr">
         <is>
           <t>Enough to show the risk is not hypothetical; not enough to show it materialized.</t>
         </is>
@@ -4696,7 +4831,12 @@
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="R134" s="4" t="inlineStr">
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>statistics</t>
+        </is>
+      </c>
+      <c r="U134" s="4" t="inlineStr">
         <is>
           <t>Strong precedent for a check; weak precedent for this particular check.</t>
         </is>
@@ -4726,7 +4866,12 @@
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="R135" s="4" t="inlineStr">
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="U135" s="4" t="inlineStr">
         <is>
           <t>Decisive on the mechanism and silent on the belief as stated.</t>
         </is>
@@ -4756,7 +4901,12 @@
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="R136" s="4" t="inlineStr">
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="U136" s="4" t="inlineStr">
         <is>
           <t>Listed on the weakening side because it is argued that way, and its linkage page is where the relevance fails.</t>
         </is>
@@ -4786,7 +4936,7 @@
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="R137" s="4" t="inlineStr">
+      <c r="U137" s="4" t="inlineStr">
         <is>
           <t>The best-measured prediction on the page.</t>
         </is>
@@ -4816,7 +4966,7 @@
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="R138" s="4" t="inlineStr">
+      <c r="U138" s="4" t="inlineStr">
         <is>
           <t>The most likely outcome, and the deterrence rebuttal is real but unmeasurable.</t>
         </is>
@@ -4846,7 +4996,7 @@
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="R139" s="4" t="inlineStr">
+      <c r="U139" s="4" t="inlineStr">
         <is>
           <t>Predicts the adaptation, and names the drafting fix in its own rebuttal.</t>
         </is>
@@ -5026,7 +5176,7 @@
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="R146" s="4" t="inlineStr">
+      <c r="U146" s="4" t="inlineStr">
         <is>
           <t>The pattern is documented and the characterization is inference. It is the firmest of the three components.</t>
         </is>
@@ -5056,7 +5206,7 @@
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="R147" s="4" t="inlineStr">
+      <c r="U147" s="4" t="inlineStr">
         <is>
           <t>The weakest load-bearing component on this page, and the one that caps it. The prediction table says why.</t>
         </is>
@@ -5086,7 +5236,7 @@
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="R148" s="4" t="inlineStr">
+      <c r="U148" s="4" t="inlineStr">
         <is>
           <t>Argued down more effectively than the constitutional objection is usually argued, and not the component that caps this page.</t>
         </is>
@@ -5231,22 +5381,22 @@
           <t>Share of official decisions made by an official holding a personal financial stake in the outcome</t>
         </is>
       </c>
-      <c r="N153" s="4" t="inlineStr">
+      <c r="Q153" s="4" t="inlineStr">
         <is>
           <t>Falls after the rule takes effect</t>
         </is>
       </c>
-      <c r="O153" s="4" t="inlineStr">
+      <c r="R153" s="4" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="P153" s="4" t="inlineStr">
+      <c r="S153" s="4" t="inlineStr">
         <is>
           <t>Not measured systematically; 78 members of one Congress filed late transaction reports (Insider, 2023)</t>
         </is>
       </c>
-      <c r="R153" s="4" t="inlineStr">
+      <c r="U153" s="4" t="inlineStr">
         <is>
           <t>Near the top of any hierarchy of public needs, and contested only at the edges of its application.</t>
         </is>
@@ -5291,22 +5441,22 @@
           <t>Abnormal returns on officials' trades placed before government announcements</t>
         </is>
       </c>
-      <c r="N154" s="4" t="inlineStr">
+      <c r="Q154" s="4" t="inlineStr">
         <is>
           <t>Fall to zero</t>
         </is>
       </c>
-      <c r="O154" s="4" t="inlineStr">
+      <c r="R154" s="4" t="inlineStr">
         <is>
           <t>Persist at their current level</t>
         </is>
       </c>
-      <c r="P154" s="4" t="inlineStr">
+      <c r="S154" s="4" t="inlineStr">
         <is>
           <t>Mixed: 85 basis points a month for senators over 1993 to 1998 (Ziobrowski 2004); no advantage found over 2012 to 2020 (Belmont 2022); 3 to 5 percent before legislative events over 2014 to 2021 (Zhou 2025)</t>
         </is>
       </c>
-      <c r="R154" s="4" t="inlineStr">
+      <c r="U154" s="4" t="inlineStr">
         <is>
           <t>Valid and recognized; the disputed part is how much is actually at stake.</t>
         </is>
@@ -5351,22 +5501,22 @@
           <t>Share of an official's income sources, debts and foreign ties visible in public filings</t>
         </is>
       </c>
-      <c r="N155" s="4" t="inlineStr">
+      <c r="Q155" s="4" t="inlineStr">
         <is>
           <t>Rises to near complete</t>
         </is>
       </c>
-      <c r="O155" s="4" t="inlineStr">
+      <c r="R155" s="4" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="P155" s="4" t="inlineStr">
+      <c r="S155" s="4" t="inlineStr">
         <is>
           <t>Assets and income are disclosed in broad ranges; foreign income, lender identity and effective tax rate are not (OGE Public Financial Disclosure Guide, 2024)</t>
         </is>
       </c>
-      <c r="R155" s="4" t="inlineStr">
+      <c r="U155" s="4" t="inlineStr">
         <is>
           <t>Strong as a need, contested in how far into a family it reaches.</t>
         </is>
@@ -5411,22 +5561,22 @@
           <t>Share of clemency grants that went through the Justice Department review process</t>
         </is>
       </c>
-      <c r="N156" s="4" t="inlineStr">
+      <c r="Q156" s="4" t="inlineStr">
         <is>
           <t>Rises toward the historical norm</t>
         </is>
       </c>
-      <c r="O156" s="4" t="inlineStr">
+      <c r="R156" s="4" t="inlineStr">
         <is>
           <t>Stays at recent lows</t>
         </is>
       </c>
-      <c r="P156" s="4" t="inlineStr">
+      <c r="S156" s="4" t="inlineStr">
         <is>
           <t>About 93 percent of one administration's first-term grants bypassed the Pardon Attorney (Goldsmith and Gluck, 2020)</t>
         </is>
       </c>
-      <c r="R156" s="4" t="inlineStr">
+      <c r="U156" s="4" t="inlineStr">
         <is>
           <t>A real need with an unusually direct constitutional obstacle, which is argued on the belief page rather than here.</t>
         </is>
@@ -5471,22 +5621,22 @@
           <t>Number of inadvertent reporting violations per year</t>
         </is>
       </c>
-      <c r="N157" s="4" t="inlineStr">
+      <c r="Q157" s="4" t="inlineStr">
         <is>
           <t>Falls toward zero</t>
         </is>
       </c>
-      <c r="O157" s="4" t="inlineStr">
+      <c r="R157" s="4" t="inlineStr">
         <is>
           <t>Stays at current levels</t>
         </is>
       </c>
-      <c r="P157" s="4" t="inlineStr">
+      <c r="S157" s="4" t="inlineStr">
         <is>
           <t>78 members of the 117th Congress filed late under the STOCK Act (Insider, 2023)</t>
         </is>
       </c>
-      <c r="R157" s="4" t="inlineStr">
+      <c r="U157" s="4" t="inlineStr">
         <is>
           <t>Valid and usually ignored, and it is the interest a bright-line ban serves best.</t>
         </is>
@@ -5531,22 +5681,22 @@
           <t>Whether a restriction reaches only the official or also family members who hold no office</t>
         </is>
       </c>
-      <c r="N158" s="4" t="inlineStr">
+      <c r="Q158" s="4" t="inlineStr">
         <is>
           <t>Restrictions stay narrow and are compensated</t>
         </is>
       </c>
-      <c r="O158" s="4" t="inlineStr">
+      <c r="R158" s="4" t="inlineStr">
         <is>
           <t>Restrictions extend to family and are not</t>
         </is>
       </c>
-      <c r="P158" s="4" t="inlineStr">
+      <c r="S158" s="4" t="inlineStr">
         <is>
           <t>Proposals vary: most reach the spouse and dependent children, and the Federal Reserve rule reaches immediate family</t>
         </is>
       </c>
-      <c r="R158" s="4" t="inlineStr">
+      <c r="U158" s="4" t="inlineStr">
         <is>
           <t>Valid in general, weakest exactly where it is invoked most: a voluntary office with known conditions.</t>
         </is>
@@ -5591,22 +5741,22 @@
           <t>Net worth distribution of candidates and of incoming members</t>
         </is>
       </c>
-      <c r="N159" s="4" t="inlineStr">
+      <c r="Q159" s="4" t="inlineStr">
         <is>
           <t>Unchanged or more representative after the rule</t>
         </is>
       </c>
-      <c r="O159" s="4" t="inlineStr">
+      <c r="R159" s="4" t="inlineStr">
         <is>
           <t>Shifts toward the already-wealthy</t>
         </is>
       </c>
-      <c r="P159" s="4" t="inlineStr">
+      <c r="S159" s="4" t="inlineStr">
         <is>
           <t>Congress is already far wealthier than the population it represents</t>
         </is>
       </c>
-      <c r="R159" s="4" t="inlineStr">
+      <c r="U159" s="4" t="inlineStr">
         <is>
           <t>A real need, and the evidence runs against the version of it used in this debate.</t>
         </is>
@@ -5651,22 +5801,22 @@
           <t>Whether unpopular but just clemency grants continue to be made</t>
         </is>
       </c>
-      <c r="N160" s="4" t="inlineStr">
+      <c r="Q160" s="4" t="inlineStr">
         <is>
           <t>They continue</t>
         </is>
       </c>
-      <c r="O160" s="4" t="inlineStr">
+      <c r="R160" s="4" t="inlineStr">
         <is>
           <t>They stop</t>
         </is>
       </c>
-      <c r="P160" s="4" t="inlineStr">
+      <c r="S160" s="4" t="inlineStr">
         <is>
           <t>Mass commutations of drug sentences were unpopular when granted and are now widely defended</t>
         </is>
       </c>
-      <c r="R160" s="4" t="inlineStr">
+      <c r="U160" s="4" t="inlineStr">
         <is>
           <t>Strong on the constitutional text, weaker as a claim that the current design is working.</t>
         </is>
@@ -5711,22 +5861,22 @@
           <t>Income officials and their relatives earn from activities that depend on the office</t>
         </is>
       </c>
-      <c r="N161" s="4" t="inlineStr">
+      <c r="Q161" s="4" t="inlineStr">
         <is>
           <t>Falls</t>
         </is>
       </c>
-      <c r="O161" s="4" t="inlineStr">
+      <c r="R161" s="4" t="inlineStr">
         <is>
           <t>Continues</t>
         </is>
       </c>
-      <c r="P161" s="4" t="inlineStr">
+      <c r="S161" s="4" t="inlineStr">
         <is>
           <t>Not measured directly; campaign committees paid $1.3 million in wages to candidates' relatives in one cycle (OpenSecrets, 2020)</t>
         </is>
       </c>
-      <c r="R161" s="4" t="inlineStr">
+      <c r="U161" s="4" t="inlineStr">
         <is>
           <t>Held by some and valid by almost no standard. It is on the page so that the scoring of a bad interest is visible rather than assumed.</t>
         </is>
@@ -5766,12 +5916,12 @@
           <t>Support</t>
         </is>
       </c>
-      <c r="Q162" s="4" t="inlineStr">
+      <c r="T162" s="4" t="inlineStr">
         <is>
           <t>Support that tracked partisan control rather than institutional distrust would point to a different driver.</t>
         </is>
       </c>
-      <c r="R162" s="4" t="inlineStr">
+      <c r="U162" s="4" t="inlineStr">
         <is>
           <t>Drives the position as strongly as any interest on the page, and the alternative explanation is hard to separate from it.</t>
         </is>
@@ -5811,12 +5961,12 @@
           <t>Support</t>
         </is>
       </c>
-      <c r="Q163" s="4" t="inlineStr">
+      <c r="T163" s="4" t="inlineStr">
         <is>
           <t>A coalition that kept its size with the market-integrity argument removed would show this interest is decorative.</t>
         </is>
       </c>
-      <c r="R163" s="4" t="inlineStr">
+      <c r="U163" s="4" t="inlineStr">
         <is>
           <t>Valid but largely decorative here: real interest, small share of what drives the position.</t>
         </is>
@@ -5856,12 +6006,12 @@
           <t>Support</t>
         </is>
       </c>
-      <c r="Q164" s="4" t="inlineStr">
+      <c r="T164" s="4" t="inlineStr">
         <is>
           <t>Whether transparency advocates would accept enforced disclosure instead of a ban is the test, and most say they would not.</t>
         </is>
       </c>
-      <c r="R164" s="4" t="inlineStr">
+      <c r="U164" s="4" t="inlineStr">
         <is>
           <t>A strong driver, and partly the same driver as the first interest on the page.</t>
         </is>
@@ -5901,12 +6051,12 @@
           <t>Support</t>
         </is>
       </c>
-      <c r="Q165" s="4" t="inlineStr">
+      <c r="T165" s="4" t="inlineStr">
         <is>
           <t>If officials who support a ban stopped doing so when preclearance was added, this interest would be shown to drive them.</t>
         </is>
       </c>
-      <c r="R165" s="4" t="inlineStr">
+      <c r="U165" s="4" t="inlineStr">
         <is>
           <t>A minor driver of the public position and a major one inside the institution.</t>
         </is>
@@ -5946,12 +6096,12 @@
           <t>Opposition</t>
         </is>
       </c>
-      <c r="Q166" s="4" t="inlineStr">
+      <c r="T166" s="4" t="inlineStr">
         <is>
           <t>Opposition as strong among members with no individual holdings would point to principle rather than interest.</t>
         </is>
       </c>
-      <c r="R166" s="4" t="inlineStr">
+      <c r="U166" s="4" t="inlineStr">
         <is>
           <t>Stated first and predicts the position well, which is what a real driver looks like even when the stated principle is inconsistently applied.</t>
         </is>
@@ -5991,12 +6141,12 @@
           <t>Opposition</t>
         </is>
       </c>
-      <c r="Q167" s="4" t="inlineStr">
+      <c r="T167" s="4" t="inlineStr">
         <is>
           <t>Evidence that candidate recruitment fell in a jurisdiction after a holdings rule would show this interest drives the position.</t>
         </is>
       </c>
-      <c r="R167" s="4" t="inlineStr">
+      <c r="U167" s="4" t="inlineStr">
         <is>
           <t>Weak as a driver: asserted often, never demonstrated.</t>
         </is>
@@ -6036,12 +6186,12 @@
           <t>Opposition</t>
         </is>
       </c>
-      <c r="Q168" s="4" t="inlineStr">
+      <c r="T168" s="4" t="inlineStr">
         <is>
           <t>Opposition that was uncorrelated with trading volume would show this interest is not the driver.</t>
         </is>
       </c>
-      <c r="R168" s="4" t="inlineStr">
+      <c r="U168" s="4" t="inlineStr">
         <is>
           <t>Drives a small number of positions strongly, which is the shape the evidence supports and no more than that.</t>
         </is>
@@ -6081,12 +6231,12 @@
           <t>Support</t>
         </is>
       </c>
-      <c r="Q169" s="4" t="inlineStr">
+      <c r="T169" s="4" t="inlineStr">
         <is>
           <t>Support that stayed constant across changes of administration would show a stable interest rather than a partisan one.</t>
         </is>
       </c>
-      <c r="R169" s="4" t="inlineStr">
+      <c r="U169" s="4" t="inlineStr">
         <is>
           <t>Real, and the partisan tracking is strong enough that the driver page scores lower than the interest page does.</t>
         </is>
@@ -6126,12 +6276,12 @@
           <t>Opposition</t>
         </is>
       </c>
-      <c r="Q170" s="4" t="inlineStr">
+      <c r="T170" s="4" t="inlineStr">
         <is>
           <t>Whether the same officials took this position under the other party's president is the test, and mostly they did not.</t>
         </is>
       </c>
-      <c r="R170" s="4" t="inlineStr">
+      <c r="U170" s="4" t="inlineStr">
         <is>
           <t>Genuinely principled among scholars and almost perfectly partisan among officials, which is why it scores where it does.</t>
         </is>
@@ -6176,12 +6326,12 @@
           <t>Supports</t>
         </is>
       </c>
-      <c r="Q171" s="4" t="inlineStr">
+      <c r="T171" s="4" t="inlineStr">
         <is>
           <t>The overlap is the conflict the ban targets, so if it exists the ban has something to remove.</t>
         </is>
       </c>
-      <c r="R171" s="4" t="inlineStr">
+      <c r="U171" s="4" t="inlineStr">
         <is>
           <t>High linkage: the row and the belief are about the same thing.</t>
         </is>
@@ -6226,12 +6376,12 @@
           <t>Supports</t>
         </is>
       </c>
-      <c r="Q172" s="4" t="inlineStr">
+      <c r="T172" s="4" t="inlineStr">
         <is>
           <t>A ban is only better than disclosure if disclosure is failing, which this row establishes and the rest of the tree has to complete.</t>
         </is>
       </c>
-      <c r="R172" s="4" t="inlineStr">
+      <c r="U172" s="4" t="inlineStr">
         <is>
           <t>Good linkage with a real gap: it rules out the alternative without establishing the proposal.</t>
         </is>
@@ -6276,12 +6426,12 @@
           <t>Supports</t>
         </is>
       </c>
-      <c r="Q173" s="4" t="inlineStr">
+      <c r="T173" s="4" t="inlineStr">
         <is>
           <t>If the conflict is structural, a structural remedy reaches it and an intent-based one does not.</t>
         </is>
       </c>
-      <c r="R173" s="4" t="inlineStr">
+      <c r="U173" s="4" t="inlineStr">
         <is>
           <t>The most direct linkage on the page.</t>
         </is>
@@ -6326,12 +6476,12 @@
           <t>Supports</t>
         </is>
       </c>
-      <c r="Q174" s="4" t="inlineStr">
+      <c r="T174" s="4" t="inlineStr">
         <is>
           <t>A comparable institution operating under the rule shows the rule is administrable, which is one of the belief's components.</t>
         </is>
       </c>
-      <c r="R174" s="4" t="inlineStr">
+      <c r="U174" s="4" t="inlineStr">
         <is>
           <t>Bears on feasibility rather than on effect, which is a real but narrower contribution.</t>
         </is>
@@ -6376,12 +6526,12 @@
           <t>Supports</t>
         </is>
       </c>
-      <c r="Q175" s="4" t="inlineStr">
+      <c r="T175" s="4" t="inlineStr">
         <is>
           <t>If the conduct cannot be prosecuted even when it occurs, the choice is between a status rule and nothing.</t>
         </is>
       </c>
-      <c r="R175" s="4" t="inlineStr">
+      <c r="U175" s="4" t="inlineStr">
         <is>
           <t>Strong linkage, and the rebuttal is the most important sentence on this page.</t>
         </is>
@@ -6426,12 +6576,12 @@
           <t>Weakens</t>
         </is>
       </c>
-      <c r="Q176" s="4" t="inlineStr">
+      <c r="T176" s="4" t="inlineStr">
         <is>
           <t>Underperformance would weaken the trading-advantage branch of the tree and leave the voting-conflict branch untouched.</t>
         </is>
       </c>
-      <c r="R176" s="4" t="inlineStr">
+      <c r="U176" s="4" t="inlineStr">
         <is>
           <t>This is the page where the belief's two branches come apart, and the linkage score should show it.</t>
         </is>
@@ -6476,12 +6626,12 @@
           <t>Weakens</t>
         </is>
       </c>
-      <c r="Q177" s="4" t="inlineStr">
+      <c r="T177" s="4" t="inlineStr">
         <is>
           <t>A ban only reduces conflicts if what it covers is not simply replaced by what it does not.</t>
         </is>
       </c>
-      <c r="R177" s="4" t="inlineStr">
+      <c r="U177" s="4" t="inlineStr">
         <is>
           <t>The highest-linkage argument on the disagree side: it strikes the load-bearing component directly.</t>
         </is>
@@ -6526,12 +6676,12 @@
           <t>Weakens</t>
         </is>
       </c>
-      <c r="Q178" s="4" t="inlineStr">
+      <c r="T178" s="4" t="inlineStr">
         <is>
           <t>Divestiture costs would weaken the belief only if they defeated the rule politically or changed who holds office.</t>
         </is>
       </c>
-      <c r="R178" s="4" t="inlineStr">
+      <c r="U178" s="4" t="inlineStr">
         <is>
           <t>Low linkage: a real cost aimed at the wrong question, and it counts fully in the cost-benefit table instead.</t>
         </is>
@@ -6576,12 +6726,12 @@
           <t>Weakens</t>
         </is>
       </c>
-      <c r="Q179" s="4" t="inlineStr">
+      <c r="T179" s="4" t="inlineStr">
         <is>
           <t>If Congress will not enforce it, the rule changes filings rather than conduct.</t>
         </is>
       </c>
-      <c r="R179" s="4" t="inlineStr">
+      <c r="U179" s="4" t="inlineStr">
         <is>
           <t>High linkage and the rebuttal is specific: the enforcement mechanism is not the same one that failed.</t>
         </is>
@@ -6626,12 +6776,12 @@
           <t>Supports</t>
         </is>
       </c>
-      <c r="Q180" s="4" t="inlineStr">
+      <c r="T180" s="4" t="inlineStr">
         <is>
           <t>If senators earned abnormal returns, there was an advantage for a rule to remove, at least then.</t>
         </is>
       </c>
-      <c r="R180" s="4" t="inlineStr">
+      <c r="U180" s="4" t="inlineStr">
         <is>
           <t>Moderate linkage: right quantity, wrong era.</t>
         </is>
@@ -6676,12 +6826,12 @@
           <t>Supports</t>
         </is>
       </c>
-      <c r="Q181" s="4" t="inlineStr">
+      <c r="T181" s="4" t="inlineStr">
         <is>
           <t>Abnormal returns around legislative events is the conflict operating, measured in the current regime.</t>
         </is>
       </c>
-      <c r="R181" s="4" t="inlineStr">
+      <c r="U181" s="4" t="inlineStr">
         <is>
           <t>The highest-linkage evidence on the page, and the least replicated.</t>
         </is>
@@ -6726,12 +6876,12 @@
           <t>Supports</t>
         </is>
       </c>
-      <c r="Q182" s="4" t="inlineStr">
+      <c r="T182" s="4" t="inlineStr">
         <is>
           <t>Non-compliance bears on the belief only through the comparison between a ban and the disclosure regime it would replace.</t>
         </is>
       </c>
-      <c r="R182" s="4" t="inlineStr">
+      <c r="U182" s="4" t="inlineStr">
         <is>
           <t>Low linkage, cited constantly, and this page is where that gets priced.</t>
         </is>
@@ -6776,12 +6926,12 @@
           <t>Supports</t>
         </is>
       </c>
-      <c r="Q183" s="4" t="inlineStr">
+      <c r="T183" s="4" t="inlineStr">
         <is>
           <t>If disclosure fails where a recusal duty backs it, it is unlikely to succeed where nothing does.</t>
         </is>
       </c>
-      <c r="R183" s="4" t="inlineStr">
+      <c r="U183" s="4" t="inlineStr">
         <is>
           <t>Moderate linkage through an analogy that has to carry real weight.</t>
         </is>
@@ -6826,12 +6976,12 @@
           <t>Supports</t>
         </is>
       </c>
-      <c r="Q184" s="4" t="inlineStr">
+      <c r="T184" s="4" t="inlineStr">
         <is>
           <t>A working example of the rule bears on whether the rule is workable, which is one component of the belief.</t>
         </is>
       </c>
-      <c r="R184" s="4" t="inlineStr">
+      <c r="U184" s="4" t="inlineStr">
         <is>
           <t>Bears on feasibility, and it substantially repeats the Fed argument above, which is what its uniqueness page is about.</t>
         </is>
@@ -6876,12 +7026,12 @@
           <t>Weakens</t>
         </is>
       </c>
-      <c r="Q185" s="4" t="inlineStr">
+      <c r="T185" s="4" t="inlineStr">
         <is>
           <t>Underperformance weakens the trading branch of the belief and is silent on the voting branch.</t>
         </is>
       </c>
-      <c r="R185" s="4" t="inlineStr">
+      <c r="U185" s="4" t="inlineStr">
         <is>
           <t>Strong on its own branch, and the tree has two.</t>
         </is>
@@ -6926,12 +7076,12 @@
           <t>Weakens</t>
         </is>
       </c>
-      <c r="Q186" s="4" t="inlineStr">
+      <c r="T186" s="4" t="inlineStr">
         <is>
           <t>No post-reform advantage would mean the trading channel is already closed by the current rule.</t>
         </is>
       </c>
-      <c r="R186" s="4" t="inlineStr">
+      <c r="U186" s="4" t="inlineStr">
         <is>
           <t>The most relevant weakening evidence, and it reaches only one of the two branches.</t>
         </is>
@@ -6976,12 +7126,12 @@
           <t>Supports</t>
         </is>
       </c>
-      <c r="Q187" s="4" t="inlineStr">
+      <c r="T187" s="4" t="inlineStr">
         <is>
           <t>Would this observation tell the two sides apart, or do both expect it?</t>
         </is>
       </c>
-      <c r="R187" s="4" t="inlineStr">
+      <c r="U187" s="4" t="inlineStr">
         <is>
           <t>Half diagnostic: the compliance half is expected by everyone, the scandal half is not.</t>
         </is>
@@ -7026,12 +7176,12 @@
           <t>Supports</t>
         </is>
       </c>
-      <c r="Q188" s="4" t="inlineStr">
+      <c r="T188" s="4" t="inlineStr">
         <is>
           <t>Would this observation tell the two sides apart, or do both expect it?</t>
         </is>
       </c>
-      <c r="R188" s="4" t="inlineStr">
+      <c r="U188" s="4" t="inlineStr">
         <is>
           <t>Weakly diagnostic, and this page is why its contribution to the belief is small.</t>
         </is>
@@ -7076,12 +7226,12 @@
           <t>Supports</t>
         </is>
       </c>
-      <c r="Q189" s="4" t="inlineStr">
+      <c r="T189" s="4" t="inlineStr">
         <is>
           <t>Would this observation tell the two sides apart, or do both expect it?</t>
         </is>
       </c>
-      <c r="R189" s="4" t="inlineStr">
+      <c r="U189" s="4" t="inlineStr">
         <is>
           <t>The most diagnostic prediction on the page and the only one nobody has attempted.</t>
         </is>
@@ -7126,12 +7276,12 @@
           <t>Weakens</t>
         </is>
       </c>
-      <c r="Q190" s="4" t="inlineStr">
+      <c r="T190" s="4" t="inlineStr">
         <is>
           <t>Would this observation tell the two sides apart, or do both expect it?</t>
         </is>
       </c>
-      <c r="R190" s="4" t="inlineStr">
+      <c r="U190" s="4" t="inlineStr">
         <is>
           <t>High diagnosticity through a noisy instrument.</t>
         </is>
@@ -7176,12 +7326,12 @@
           <t>Weakens</t>
         </is>
       </c>
-      <c r="Q191" s="4" t="inlineStr">
+      <c r="T191" s="4" t="inlineStr">
         <is>
           <t>Would this observation tell the two sides apart, or do both expect it?</t>
         </is>
       </c>
-      <c r="R191" s="4" t="inlineStr">
+      <c r="U191" s="4" t="inlineStr">
         <is>
           <t>Low linkage to the belief and high relevance to the cost-benefit table, which is where it belongs.</t>
         </is>
@@ -7226,12 +7376,12 @@
           <t>Weakens</t>
         </is>
       </c>
-      <c r="Q192" s="4" t="inlineStr">
+      <c r="T192" s="4" t="inlineStr">
         <is>
           <t>Would this observation tell the two sides apart, or do both expect it?</t>
         </is>
       </c>
-      <c r="R192" s="4" t="inlineStr">
+      <c r="U192" s="4" t="inlineStr">
         <is>
           <t>Diagnostic for half the belief, which is what its score should reflect.</t>
         </is>
@@ -7276,12 +7426,12 @@
           <t>Weakens</t>
         </is>
       </c>
-      <c r="Q193" s="4" t="inlineStr">
+      <c r="T193" s="4" t="inlineStr">
         <is>
           <t>A bar that converts a disclosed adviser into an undisclosed one would make things worse rather than better.</t>
         </is>
       </c>
-      <c r="R193" s="4" t="inlineStr">
+      <c r="U193" s="4" t="inlineStr">
         <is>
           <t>The highest-linkage argument on that page.</t>
         </is>
@@ -7326,12 +7476,12 @@
           <t>Weakens</t>
         </is>
       </c>
-      <c r="Q194" s="4" t="inlineStr">
+      <c r="T194" s="4" t="inlineStr">
         <is>
           <t>A gap in coverage bears on the size of the effect, not on its direction.</t>
         </is>
       </c>
-      <c r="R194" s="4" t="inlineStr">
+      <c r="U194" s="4" t="inlineStr">
         <is>
           <t>Moderate linkage: a scope argument doing duty as a refutation.</t>
         </is>
@@ -7376,12 +7526,12 @@
           <t>Weakens</t>
         </is>
       </c>
-      <c r="Q195" s="4" t="inlineStr">
+      <c r="T195" s="4" t="inlineStr">
         <is>
           <t>If the existing form shows what a return would show, publication adds nothing.</t>
         </is>
       </c>
-      <c r="R195" s="4" t="inlineStr">
+      <c r="U195" s="4" t="inlineStr">
         <is>
           <t>High linkage and directly checkable, which is unusual and good.</t>
         </is>
@@ -7426,12 +7576,12 @@
           <t>Weakens</t>
         </is>
       </c>
-      <c r="Q196" s="4" t="inlineStr">
+      <c r="T196" s="4" t="inlineStr">
         <is>
           <t>A precedent about ballot access bears on a disclosure duty only if the two are the same kind of rule, and they are not.</t>
         </is>
       </c>
-      <c r="R196" s="4" t="inlineStr">
+      <c r="U196" s="4" t="inlineStr">
         <is>
           <t>Low linkage: the precedent is cited far beyond what it holds, and this page is where that is priced.</t>
         </is>
@@ -7476,12 +7626,12 @@
           <t>Weakens</t>
         </is>
       </c>
-      <c r="Q197" s="4" t="inlineStr">
+      <c r="T197" s="4" t="inlineStr">
         <is>
           <t>The cases foreclose a statute; the belief as written does not require one.</t>
         </is>
       </c>
-      <c r="R197" s="4" t="inlineStr">
+      <c r="U197" s="4" t="inlineStr">
         <is>
           <t>The most-cited argument on that page, and its linkage is lower than its citation rate implies.</t>
         </is>
@@ -7526,12 +7676,12 @@
           <t>Weakens</t>
         </is>
       </c>
-      <c r="Q198" s="4" t="inlineStr">
+      <c r="T198" s="4" t="inlineStr">
         <is>
           <t>Failure to advance bears on feasibility, and the belief is about effect.</t>
         </is>
       </c>
-      <c r="R198" s="4" t="inlineStr">
+      <c r="U198" s="4" t="inlineStr">
         <is>
           <t>Very low linkage, and it is the clearest example in this workbook of a true fact aimed at the wrong claim.</t>
         </is>
@@ -7576,12 +7726,12 @@
           <t>Supports</t>
         </is>
       </c>
-      <c r="Q199" s="4" t="inlineStr">
+      <c r="T199" s="4" t="inlineStr">
         <is>
           <t>State practice shows a check is compatible with a functioning clemency power, but not this check.</t>
         </is>
       </c>
-      <c r="R199" s="4" t="inlineStr">
+      <c r="U199" s="4" t="inlineStr">
         <is>
           <t>Real evidence for the general proposition and weak evidence for the specific proposal.</t>
         </is>
@@ -7626,12 +7776,12 @@
           <t>Supports</t>
         </is>
       </c>
-      <c r="Q200" s="4" t="inlineStr">
+      <c r="T200" s="4" t="inlineStr">
         <is>
           <t>The filing deadline exists for the market-integrity interest, but a violation of it does not show that interest was harmed.</t>
         </is>
       </c>
-      <c r="R200" s="4" t="inlineStr">
+      <c r="U200" s="4" t="inlineStr">
         <is>
           <t>Bearing: how far the row is really about this interest.</t>
         </is>
@@ -7676,12 +7826,12 @@
           <t>Supports</t>
         </is>
       </c>
-      <c r="Q201" s="4" t="inlineStr">
+      <c r="T201" s="4" t="inlineStr">
         <is>
           <t>Cost to sitting officials and deterrence of future candidates are related but not the same quantity.</t>
         </is>
       </c>
-      <c r="R201" s="4" t="inlineStr">
+      <c r="U201" s="4" t="inlineStr">
         <is>
           <t>Bearing: how far the row is really about this interest.</t>
         </is>
@@ -7721,7 +7871,7 @@
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="Q202" s="4" t="inlineStr">
+      <c r="T202" s="4" t="inlineStr">
         <is>
           <t>Citizens whose decisions are made by someone holding a stake, and investors on the other side of the trades.</t>
         </is>
@@ -7761,7 +7911,7 @@
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="Q203" s="4" t="inlineStr">
+      <c r="T203" s="4" t="inlineStr">
         <is>
           <t>Voters, who cannot tell a compromised official from a clean one, and officials living under a rule nobody enforces.</t>
         </is>
@@ -7801,7 +7951,7 @@
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="Q204" s="4" t="inlineStr">
+      <c r="T204" s="4" t="inlineStr">
         <is>
           <t>Everyone who needs decisions made on the merits, and officials who want a rule they can actually follow.</t>
         </is>
@@ -7841,7 +7991,7 @@
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="Q205" s="4" t="inlineStr">
+      <c r="T205" s="4" t="inlineStr">
         <is>
           <t>Officials, who would live under the rule, and anyone worried it makes service impossible.</t>
         </is>
@@ -7881,7 +8031,7 @@
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="Q206" s="4" t="inlineStr">
+      <c r="T206" s="4" t="inlineStr">
         <is>
           <t>Citizens and investors, who currently rely on a rule that cannot be enforced.</t>
         </is>
@@ -7921,7 +8071,7 @@
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="Q207" s="4" t="inlineStr">
+      <c r="T207" s="4" t="inlineStr">
         <is>
           <t>Investors, if there turns out to be no advantage being taken.</t>
         </is>
@@ -7961,7 +8111,7 @@
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="Q208" s="4" t="inlineStr">
+      <c r="T208" s="4" t="inlineStr">
         <is>
           <t>Citizens, if the conflict moves instead of ending, and voters, who would see less of it.</t>
         </is>
@@ -8001,7 +8151,7 @@
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="Q209" s="4" t="inlineStr">
+      <c r="T209" s="4" t="inlineStr">
         <is>
           <t>People of ordinary means considering office, and officials asked to sell on someone else's schedule.</t>
         </is>
@@ -8041,7 +8191,7 @@
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="Q210" s="4" t="inlineStr">
+      <c r="T210" s="4" t="inlineStr">
         <is>
           <t>Officials and their families, whose ordinary rights the rule restricts.</t>
         </is>
@@ -8081,7 +8231,7 @@
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="Q211" s="4" t="inlineStr">
+      <c r="T211" s="4" t="inlineStr">
         <is>
           <t>Citizens, if the rule is a symbol, and officials, who would carry its burden for nothing.</t>
         </is>
@@ -8121,7 +8271,7 @@
           <t>supporting finding</t>
         </is>
       </c>
-      <c r="Q212" s="4" t="inlineStr">
+      <c r="T212" s="4" t="inlineStr">
         <is>
           <t>Investors trading against officials during the period studied.</t>
         </is>
@@ -8161,7 +8311,7 @@
           <t>supporting finding</t>
         </is>
       </c>
-      <c r="Q213" s="4" t="inlineStr">
+      <c r="T213" s="4" t="inlineStr">
         <is>
           <t>Investors on the other side of trades placed before legislative events.</t>
         </is>
@@ -8201,7 +8351,7 @@
           <t>supporting finding</t>
         </is>
       </c>
-      <c r="Q214" s="4" t="inlineStr">
+      <c r="T214" s="4" t="inlineStr">
         <is>
           <t>Investors relying on a disclosure regime, and officials living under a rule that is widely missed.</t>
         </is>
@@ -8241,7 +8391,7 @@
           <t>supporting finding</t>
         </is>
       </c>
-      <c r="Q215" s="4" t="inlineStr">
+      <c r="T215" s="4" t="inlineStr">
         <is>
           <t>Litigants and voters relying on disclosure to reveal a decision-maker's stake.</t>
         </is>
@@ -8281,7 +8431,7 @@
           <t>supporting finding</t>
         </is>
       </c>
-      <c r="Q216" s="4" t="inlineStr">
+      <c r="T216" s="4" t="inlineStr">
         <is>
           <t>Officials under the rule, and anyone concerned it deters qualified people.</t>
         </is>
@@ -8321,7 +8471,7 @@
           <t>weakening finding</t>
         </is>
       </c>
-      <c r="Q217" s="4" t="inlineStr">
+      <c r="T217" s="4" t="inlineStr">
         <is>
           <t>Investors, if there is no advantage to remove.</t>
         </is>
@@ -8361,7 +8511,7 @@
           <t>weakening finding</t>
         </is>
       </c>
-      <c r="Q218" s="4" t="inlineStr">
+      <c r="T218" s="4" t="inlineStr">
         <is>
           <t>Investors in the post-reform period.</t>
         </is>
@@ -8401,7 +8551,7 @@
           <t>prediction if the belief is true</t>
         </is>
       </c>
-      <c r="Q219" s="4" t="inlineStr">
+      <c r="T219" s="4" t="inlineStr">
         <is>
           <t>Citizens, whose officials would no longer hold the stakes.</t>
         </is>
@@ -8441,7 +8591,7 @@
           <t>prediction if the belief is true</t>
         </is>
       </c>
-      <c r="Q220" s="4" t="inlineStr">
+      <c r="T220" s="4" t="inlineStr">
         <is>
           <t>Voters, whose confidence is the thing being measured.</t>
         </is>
@@ -8481,7 +8631,7 @@
           <t>prediction if the belief is true</t>
         </is>
       </c>
-      <c r="Q221" s="4" t="inlineStr">
+      <c r="T221" s="4" t="inlineStr">
         <is>
           <t>Citizens, whose votes would be cast without the stake.</t>
         </is>
@@ -8521,7 +8671,7 @@
           <t>prediction if the belief is false</t>
         </is>
       </c>
-      <c r="Q222" s="4" t="inlineStr">
+      <c r="T222" s="4" t="inlineStr">
         <is>
           <t>Citizens, if the conflict persists out of view.</t>
         </is>
@@ -8561,7 +8711,7 @@
           <t>prediction if the belief is false</t>
         </is>
       </c>
-      <c r="Q223" s="4" t="inlineStr">
+      <c r="T223" s="4" t="inlineStr">
         <is>
           <t>People of ordinary means who might otherwise run.</t>
         </is>
@@ -8601,7 +8751,7 @@
           <t>prediction if the belief is false</t>
         </is>
       </c>
-      <c r="Q224" s="4" t="inlineStr">
+      <c r="T224" s="4" t="inlineStr">
         <is>
           <t>Investors, if the advantage was already gone.</t>
         </is>
@@ -8641,7 +8791,7 @@
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="Q225" s="4" t="inlineStr">
+      <c r="T225" s="4" t="inlineStr">
         <is>
           <t>Citizens, whose decisions are made by someone outside the rule that covers everyone else.</t>
         </is>
@@ -8681,7 +8831,7 @@
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="Q226" s="4" t="inlineStr">
+      <c r="T226" s="4" t="inlineStr">
         <is>
           <t>Citizens relying on an ordinary chain of command to check official conduct.</t>
         </is>
@@ -8721,7 +8871,7 @@
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="Q227" s="4" t="inlineStr">
+      <c r="T227" s="4" t="inlineStr">
         <is>
           <t>Citizens, and voters who cannot see what the channel carries.</t>
         </is>
@@ -8761,7 +8911,7 @@
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="Q228" s="4" t="inlineStr">
+      <c r="T228" s="4" t="inlineStr">
         <is>
           <t>Officials, who would face one rule instead of two.</t>
         </is>
@@ -8801,7 +8951,7 @@
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="Q229" s="4" t="inlineStr">
+      <c r="T229" s="4" t="inlineStr">
         <is>
           <t>Voters, who would lose the disclosure that appointment triggers.</t>
         </is>
@@ -8841,7 +8991,7 @@
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="Q230" s="4" t="inlineStr">
+      <c r="T230" s="4" t="inlineStr">
         <is>
           <t>Relatives making money from the name, which the rule does not reach.</t>
         </is>
@@ -8881,7 +9031,7 @@
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="Q231" s="4" t="inlineStr">
+      <c r="T231" s="4" t="inlineStr">
         <is>
           <t>A president restricted in whom he may consult.</t>
         </is>
@@ -8921,7 +9071,7 @@
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="Q232" s="4" t="inlineStr">
+      <c r="T232" s="4" t="inlineStr">
         <is>
           <t>Qualified people excluded for a relationship.</t>
         </is>
@@ -8961,7 +9111,7 @@
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="Q233" s="4" t="inlineStr">
+      <c r="T233" s="4" t="inlineStr">
         <is>
           <t>Voters, who currently see ranges instead of figures.</t>
         </is>
@@ -9001,7 +9151,7 @@
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="Q234" s="4" t="inlineStr">
+      <c r="T234" s="4" t="inlineStr">
         <is>
           <t>Citizens relying on an audit that did not happen.</t>
         </is>
@@ -9041,7 +9191,7 @@
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="Q235" s="4" t="inlineStr">
+      <c r="T235" s="4" t="inlineStr">
         <is>
           <t>Voters, who had the information for forty years and then did not.</t>
         </is>
@@ -9081,7 +9231,7 @@
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="Q236" s="4" t="inlineStr">
+      <c r="T236" s="4" t="inlineStr">
         <is>
           <t>Voters, who can check a published document without waiting for an agency.</t>
         </is>
@@ -9121,7 +9271,7 @@
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="Q237" s="4" t="inlineStr">
+      <c r="T237" s="4" t="inlineStr">
         <is>
           <t>Voters, if the existing form already tells them what they need.</t>
         </is>
@@ -9161,7 +9311,7 @@
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="Q238" s="4" t="inlineStr">
+      <c r="T238" s="4" t="inlineStr">
         <is>
           <t>Spouses, children and partners who hold no office.</t>
         </is>
@@ -9201,7 +9351,7 @@
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="Q239" s="4" t="inlineStr">
+      <c r="T239" s="4" t="inlineStr">
         <is>
           <t>Officials facing a rule that would be litigated rather than obeyed.</t>
         </is>
@@ -9241,7 +9391,7 @@
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="Q240" s="4" t="inlineStr">
+      <c r="T240" s="4" t="inlineStr">
         <is>
           <t>Voters, who would see a document that shows little.</t>
         </is>
@@ -9281,7 +9431,7 @@
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="Q241" s="4" t="inlineStr">
+      <c r="T241" s="4" t="inlineStr">
         <is>
           <t>Victims and the public, for whom nothing reviews a grant.</t>
         </is>
@@ -9321,7 +9471,7 @@
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="Q242" s="4" t="inlineStr">
+      <c r="T242" s="4" t="inlineStr">
         <is>
           <t>Victims of the underlying offenses, and citizens watching the power used on the president's circle.</t>
         </is>
@@ -9361,7 +9511,7 @@
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="Q243" s="4" t="inlineStr">
+      <c r="T243" s="4" t="inlineStr">
         <is>
           <t>A president whose unpopular but just grants would survive a two-thirds test.</t>
         </is>
@@ -9401,7 +9551,7 @@
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="Q244" s="4" t="inlineStr">
+      <c r="T244" s="4" t="inlineStr">
         <is>
           <t>The public in states where clemency already carries a check.</t>
         </is>
@@ -9441,7 +9591,7 @@
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="Q245" s="4" t="inlineStr">
+      <c r="T245" s="4" t="inlineStr">
         <is>
           <t>A president whose constitutional power would be narrowed.</t>
         </is>
@@ -9481,7 +9631,7 @@
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="Q246" s="4" t="inlineStr">
+      <c r="T246" s="4" t="inlineStr">
         <is>
           <t>People whom only an unpopular act of mercy can reach.</t>
         </is>
@@ -9521,7 +9671,7 @@
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="Q247" s="4" t="inlineStr">
+      <c r="T247" s="4" t="inlineStr">
         <is>
           <t>Recipients who could not rely on a grant.</t>
         </is>
@@ -9561,7 +9711,7 @@
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="Q248" s="4" t="inlineStr">
+      <c r="T248" s="4" t="inlineStr">
         <is>
           <t>The same public interest, served by a smaller change.</t>
         </is>
@@ -9596,12 +9746,12 @@
           <t>federal-reserve-barred-its</t>
         </is>
       </c>
-      <c r="Q249" s="4" t="inlineStr">
+      <c r="T249" s="4" t="inlineStr">
         <is>
           <t>The finding adds the rule's scope and dates; the argument adds the claim that the institution kept working.</t>
         </is>
       </c>
-      <c r="R249" s="4" t="inlineStr">
+      <c r="U249" s="4" t="inlineStr">
         <is>
           <t>Largely redundant: the finding keeps a minority of its weight, which is the discount working as intended.</t>
         </is>
@@ -9636,12 +9786,12 @@
           <t>ban-official-leaves-conflict</t>
         </is>
       </c>
-      <c r="Q250" s="4" t="inlineStr">
+      <c r="T250" s="4" t="inlineStr">
         <is>
           <t>Substitution is about what the rule covers; non-enforcement is about whether what it covers is policed.</t>
         </is>
       </c>
-      <c r="R250" s="4" t="inlineStr">
+      <c r="U250" s="4" t="inlineStr">
         <is>
           <t>Distinct: they fail in different ways and would be refuted by different evidence.</t>
         </is>
@@ -9676,12 +9826,12 @@
           <t>members-congress-barred-owning</t>
         </is>
       </c>
-      <c r="Q251" s="4" t="inlineStr">
+      <c r="T251" s="4" t="inlineStr">
         <is>
           <t>The broader version reaches every asset class rather than publicly traded shares.</t>
         </is>
       </c>
-      <c r="R251" s="4" t="inlineStr">
+      <c r="U251" s="4" t="inlineStr">
         <is>
           <t>Same direction, different policy. Keep both pages and cross-link them.</t>
         </is>
@@ -9716,12 +9866,12 @@
           <t>members-congress-required-place</t>
         </is>
       </c>
-      <c r="Q252" s="4" t="inlineStr">
+      <c r="T252" s="4" t="inlineStr">
         <is>
           <t>A blind trust removes control and keeps ownership; a ban removes ownership.</t>
         </is>
       </c>
-      <c r="R252" s="4" t="inlineStr">
+      <c r="U252" s="4" t="inlineStr">
         <is>
           <t>Overlapping rather than equivalent: keep both pages and name the difference on each.</t>
         </is>
@@ -9756,12 +9906,12 @@
           <t>president-barred-pardoning-relatives</t>
         </is>
       </c>
-      <c r="Q253" s="4" t="inlineStr">
+      <c r="T253" s="4" t="inlineStr">
         <is>
           <t>One restricts who may be pardoned; the other lets Congress undo any grant.</t>
         </is>
       </c>
-      <c r="R253" s="4" t="inlineStr">
+      <c r="U253" s="4" t="inlineStr">
         <is>
           <t>Distinct mechanisms aimed at overlapping cases. Both need an amendment.</t>
         </is>
@@ -9806,12 +9956,12 @@
           <t>Journal of Financial and Quantitative Analysis 39(4), 661 to 676</t>
         </is>
       </c>
-      <c r="Q254" s="4" t="inlineStr">
+      <c r="T254" s="4" t="inlineStr">
         <is>
           <t>Senators earned abnormal returns on their stock purchases in the 1990s.</t>
         </is>
       </c>
-      <c r="R254" s="4" t="inlineStr">
+      <c r="U254" s="4" t="inlineStr">
         <is>
           <t>The foundational study for the trading-advantage argument, and its period is now a generation old.</t>
         </is>
@@ -9856,12 +10006,12 @@
           <t>Insider investigative series, tally updated January 2023</t>
         </is>
       </c>
-      <c r="Q255" s="4" t="inlineStr">
+      <c r="T255" s="4" t="inlineStr">
         <is>
           <t>Members of Congress violate the existing disclosure rule routinely and without consequence.</t>
         </is>
       </c>
-      <c r="R255" s="4" t="inlineStr">
+      <c r="U255" s="4" t="inlineStr">
         <is>
           <t>Accurate as a count and routinely oversold as a measure of misconduct.</t>
         </is>
@@ -9906,12 +10056,12 @@
           <t>Journal of Politics 75(2)</t>
         </is>
       </c>
-      <c r="Q256" s="4" t="inlineStr">
+      <c r="T256" s="4" t="inlineStr">
         <is>
           <t>Congressional portfolios did not beat the market.</t>
         </is>
       </c>
-      <c r="R256" s="4" t="inlineStr">
+      <c r="U256" s="4" t="inlineStr">
         <is>
           <t>The most careful study on the skeptical side, and the tail-versus-average objection is unresolved.</t>
         </is>
@@ -9956,12 +10106,12 @@
           <t>Supports</t>
         </is>
       </c>
-      <c r="Q257" s="4" t="inlineStr">
+      <c r="T257" s="4" t="inlineStr">
         <is>
           <t>The work speaks to the trading branch of the belief and not to the voting branch.</t>
         </is>
       </c>
-      <c r="R257" s="4" t="inlineStr">
+      <c r="U257" s="4" t="inlineStr">
         <is>
           <t>Bears on one of the belief's two branches.</t>
         </is>
@@ -10006,12 +10156,12 @@
           <t>Supports</t>
         </is>
       </c>
-      <c r="Q258" s="4" t="inlineStr">
+      <c r="T258" s="4" t="inlineStr">
         <is>
           <t>The work speaks to the trading branch of the belief and not to the voting branch.</t>
         </is>
       </c>
-      <c r="R258" s="4" t="inlineStr">
+      <c r="U258" s="4" t="inlineStr">
         <is>
           <t>Bears on one of the belief's two branches.</t>
         </is>
@@ -10056,12 +10206,12 @@
           <t>Weakens</t>
         </is>
       </c>
-      <c r="Q259" s="4" t="inlineStr">
+      <c r="T259" s="4" t="inlineStr">
         <is>
           <t>The work speaks to the trading branch of the belief and not to the voting branch.</t>
         </is>
       </c>
-      <c r="R259" s="4" t="inlineStr">
+      <c r="U259" s="4" t="inlineStr">
         <is>
           <t>Bears on one of the belief's two branches.</t>
         </is>
@@ -10101,7 +10251,7 @@
           <t>work</t>
         </is>
       </c>
-      <c r="Q260" s="4" t="inlineStr">
+      <c r="T260" s="4" t="inlineStr">
         <is>
           <t>Investors on the other side of the trades the study measures.</t>
         </is>
@@ -10141,7 +10291,7 @@
           <t>work</t>
         </is>
       </c>
-      <c r="Q261" s="4" t="inlineStr">
+      <c r="T261" s="4" t="inlineStr">
         <is>
           <t>Voters relying on disclosure, and officials living under the rule being violated.</t>
         </is>
@@ -10181,15 +10331,15 @@
           <t>work</t>
         </is>
       </c>
-      <c r="Q262" s="4" t="inlineStr">
+      <c r="T262" s="4" t="inlineStr">
         <is>
           <t>Investors, if the advantage the belief assumes is not there.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T262"/>
-  <dataValidations count="3">
+  <autoFilter ref="A1:W262"/>
+  <dataValidations count="4">
     <dataValidation sqref="C2:C5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"belief,claim,linkage,importance,interest,uniqueness,equivalence,driver,media"</formula1>
     </dataValidation>
@@ -10198,6 +10348,9 @@
     </dataValidation>
     <dataValidation sqref="I2:I5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Supports,Weakens,Support,Opposition"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"analogy,anecdote,artifact,expert_claim,expert_data,eyewitness,historical,intuition,logic,meta,news,norm,observational,rct,record,statistics,survey,visual"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10682,11 +10835,6 @@
           <t>imp-senators-stock-purchases-barring-members</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>etype: observational</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -10724,11 +10872,6 @@
           <t>imp-trades-placed-before-barring-members</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>etype: observational | erq: 2 | erp: 50</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -10766,11 +10909,6 @@
           <t>imp-78-members-117th-barring-members</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>etype: statistics</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -10808,11 +10946,6 @@
           <t>imp-131-federal-judges-barring-members</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>etype: statistics</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -10855,11 +10988,6 @@
           <t>uniq-federal-reserve-officials-federal-reserve</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>etype: record</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -10897,11 +11025,6 @@
           <t>imp-congressional-portfolios-underperformed-barring-members</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>etype: observational</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -10939,11 +11062,6 @@
           <t>imp-no-evidence-members-barring-members</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>etype: observational | erq: 2 | erp: 50</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -12901,11 +13019,6 @@
           <t>Office of Legal Counsel opinion, January 20, 2017</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr">
-        <is>
-          <t>etype: record</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -12933,11 +13046,6 @@
           <t>Congressional nomination records and contemporaneous reporting, 2025 to 2026</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr">
-        <is>
-          <t>etype: record</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -12965,11 +13073,6 @@
           <t>Office of Government Ethics filings reported July 2017</t>
         </is>
       </c>
-      <c r="R98" t="inlineStr">
-        <is>
-          <t>etype: record</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -12997,11 +13100,6 @@
           <t>OpenSecrets analysis, June 2020</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr">
-        <is>
-          <t>etype: statistics</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -14202,11 +14300,6 @@
           <t>House Ways and Means Committee report and release of tax years 2015 to 2020, December 2022</t>
         </is>
       </c>
-      <c r="R149" t="inlineStr">
-        <is>
-          <t>etype: record</t>
-        </is>
-      </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
@@ -14234,11 +14327,6 @@
           <t>Joint Committee on Taxation review, April 1974</t>
         </is>
       </c>
-      <c r="R150" t="inlineStr">
-        <is>
-          <t>etype: record</t>
-        </is>
-      </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
@@ -14266,11 +14354,6 @@
           <t>Office of Government Ethics, Public Financial Disclosure Guide (2024)</t>
         </is>
       </c>
-      <c r="R151" t="inlineStr">
-        <is>
-          <t>etype: record</t>
-        </is>
-      </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
@@ -14298,11 +14381,6 @@
           <t>Patterson v. Padilla, California Supreme Court, November 21, 2019</t>
         </is>
       </c>
-      <c r="R152" t="inlineStr">
-        <is>
-          <t>etype: record</t>
-        </is>
-      </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
@@ -15496,11 +15574,6 @@
           <t>Economist and YouGov poll, December 2025</t>
         </is>
       </c>
-      <c r="R202" t="inlineStr">
-        <is>
-          <t>etype: survey</t>
-        </is>
-      </c>
     </row>
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
@@ -15528,11 +15601,6 @@
           <t>Opinion of Chief Judge Beryl Howell, unsealed December 1, 2020</t>
         </is>
       </c>
-      <c r="R203" t="inlineStr">
-        <is>
-          <t>etype: record</t>
-        </is>
-      </c>
     </row>
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
@@ -15560,11 +15628,6 @@
           <t>Collateral Consequences Resource Center fifty-state survey, 2024 to 2025</t>
         </is>
       </c>
-      <c r="R204" t="inlineStr">
-        <is>
-          <t>etype: statistics</t>
-        </is>
-      </c>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
@@ -15592,11 +15655,6 @@
           <t>Ex parte Garland, 71 U.S. 333 (1866)</t>
         </is>
       </c>
-      <c r="R205" t="inlineStr">
-        <is>
-          <t>etype: record</t>
-        </is>
-      </c>
     </row>
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
@@ -15627,11 +15685,6 @@
       <c r="G206" s="4" t="inlineStr">
         <is>
           <t>evid-proposals-let-congress-letting-congress</t>
-        </is>
-      </c>
-      <c r="R206" t="inlineStr">
-        <is>
-          <t>etype: record</t>
         </is>
       </c>
     </row>

--- a/tools/static-site/ISE_Data_Entry.xlsx
+++ b/tools/static-site/ISE_Data_Entry.xlsx
@@ -938,7 +938,7 @@
       </c>
       <c r="U2" s="4" t="inlineStr">
         <is>
-          <t>The conflict is documented and the disclosure regime demonstrably fails. Whether a ban removes the conflict or relocates it into spouses, partnerships and the revolving door is the open question, and it is the component that holds this page's truth score down.</t>
+          <t>The conflict is documented and the disclosure regime demonstrably fails. Whether a ban removes the conflict or relocates it into spouses, partnerships and the revolving door is the open question. It is one of three load-bearing components all sitting at the neutral start, and while they sit there any one of them caps what this page can read, however far the evidence carries the argument.</t>
         </is>
       </c>
       <c r="V2" s="5" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="U3" s="4" t="inlineStr">
         <is>
-          <t>The legal gap is documented and the supervision problem is real. The page turns on whether a bar removes the conflict or converts a disclosed adviser into an undisclosed one. Two load-bearing components are tied at the cap, so the truth score other pages read sits below what the arguments alone support.</t>
+          <t>The legal gap is documented and the supervision problem is real. The page turns on whether a bar removes the conflict or converts a disclosed adviser into an undisclosed one. All three load-bearing components sit at the neutral start, so nothing has been established here yet and nothing is capping anything: the work is to argue them.</t>
         </is>
       </c>
       <c r="V3" s="5" t="n">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="U4" s="4" t="inlineStr">
         <is>
-          <t>The documentary claim is the strongest part: returns do carry conflict-relevant facts the disclosure form omits. What nobody can show is that publishing them changes anything. All three load-bearing components sit at the same argued level, so what caps this page is the whole anatomy rather than any one part of it.</t>
+          <t>The documentary claim is the strongest part: returns do carry conflict-relevant facts the disclosure form omits. What nobody can show is that publishing them changes anything. All three load-bearing components sit at the neutral start, so what this page needs is not more evidence for the conclusion but an argument for each of its parts.</t>
         </is>
       </c>
       <c r="V4" s="5" t="n">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="U5" s="4" t="inlineStr">
         <is>
-          <t>The gap is real: clemency is the only federal power with no check, and grants to the president's own circle are documented in both parties. The component that caps this page is not the constitutional objection, which scores higher here than its citation rate suggests. It is whether an override could ever be exercised at a two-thirds threshold against a president whose own party holds a third of either chamber.</t>
+          <t>The gap is real: clemency is the only federal power with no check, and grants to the president's own circle are documented in both parties. All three load-bearing components sit at the neutral start, so any one of them caps the page. The one to argue first is not the constitutional objection but whether an override could ever be exercised at a two-thirds threshold against a president whose own party holds a third of either chamber.</t>
         </is>
       </c>
       <c r="V5" s="5" t="n">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="W5" s="4" t="inlineStr">
         <is>
-          <t>(Some pardons are granted for the president's private benefit) AND (a congressional override would deter or reverse those grants) AND (an override can be enacted). The third component is legal rather than empirical, and it is the one that holds this page down.</t>
+          <t>(Some pardons are granted for the president's private benefit) AND (a congressional override would deter or reverse those grants) AND (an override can be enacted). The third component is legal rather than empirical, and it is the one most likely to hold this page down once all three have been argued.</t>
         </is>
       </c>
     </row>
@@ -7633,7 +7633,7 @@
       </c>
       <c r="U197" s="4" t="inlineStr">
         <is>
-          <t>The most-cited argument on that page, and its linkage is lower than its citation rate implies.</t>
+          <t>The most-cited argument on that page, and nobody has opened this linkage page to argue it either way, so it still reads the presumption that a reason placed under a conclusion is relevant.</t>
         </is>
       </c>
     </row>
@@ -12485,7 +12485,7 @@
       </c>
       <c r="R73" s="4" t="inlineStr">
         <is>
-          <t>term: Use of public office for private gain | definition: Defined on the principle page (tab 5) and used here without restatement.</t>
+          <t>term: Use of public office for private gain | definition: Defined on the principle page this one sits under and used here without restatement.</t>
         </is>
       </c>
     </row>

--- a/tools/static-site/ISE_Data_Entry.xlsx
+++ b/tools/static-site/ISE_Data_Entry.xlsx
@@ -1606,15 +1606,11 @@
           <t>observational</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="O23" t="n">
+        <v>2</v>
+      </c>
+      <c r="P23" t="n">
+        <v>50</v>
       </c>
       <c r="U23" s="4" t="inlineStr">
         <is>
@@ -1791,15 +1787,11 @@
           <t>observational</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="O28" t="n">
+        <v>2</v>
+      </c>
+      <c r="P28" t="n">
+        <v>50</v>
       </c>
       <c r="U28" s="4" t="inlineStr">
         <is>

--- a/tools/static-site/ISE_Data_Entry.xlsx
+++ b/tools/static-site/ISE_Data_Entry.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'pages'!$A$1:$W$262</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'edges'!$A$1:$R$885</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'edges'!$A$1:$T$885</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -370,10 +370,20 @@
     </comment>
     <comment ref="Q1" authorId="0" shapeId="0">
       <text>
+        <t>cost and benefit rows: the low end of the estimate, in the same units. Blank means nobody has stated a range, which the page reports as a deficiency rather than treating the central estimate as exact.</t>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0" shapeId="0">
+      <text>
+        <t>cost and benefit rows: the high end of the estimate, in the same units.</t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0" shapeId="0">
+      <text>
         <t>prediction rows: when and how it gets settled.</t>
       </text>
     </comment>
-    <comment ref="R1" authorId="0" shapeId="0">
+    <comment ref="T1" authorId="0" shapeId="0">
       <text>
         <t>Anything else the row carries, as "name: value | name: value".</t>
       </text>
@@ -10356,7 +10366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R885"/>
+  <dimension ref="A1:T885"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -10375,8 +10385,8 @@
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="40" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="40" customWidth="1" min="17" max="17"/>
-    <col width="60" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10462,10 +10472,20 @@
       </c>
       <c r="Q1" s="3" t="inlineStr">
         <is>
+          <t>mag_low</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>mag_high</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
           <t>deadline</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>extra</t>
         </is>
@@ -11086,7 +11106,7 @@
           <t>imp-five-years-after-barring-members</t>
         </is>
       </c>
-      <c r="Q19" s="4" t="inlineStr">
+      <c r="S19" s="4" t="inlineStr">
         <is>
           <t>By 2032; annual review of Form 278e filings and periodic transaction reports</t>
         </is>
@@ -11123,7 +11143,7 @@
           <t>imp-public-trust-congress-barring-members</t>
         </is>
       </c>
-      <c r="Q20" s="4" t="inlineStr">
+      <c r="S20" s="4" t="inlineStr">
         <is>
           <t>By 2032; Gallup confidence-in-institutions series against its own pre-ban trend</t>
         </is>
@@ -11160,7 +11180,7 @@
           <t>imp-jurisdiction-adopts-holdings-barring-members</t>
         </is>
       </c>
-      <c r="Q21" s="4" t="inlineStr">
+      <c r="S21" s="4" t="inlineStr">
         <is>
           <t>By 2031; difference-in-differences on roll-call votes matched to member holdings</t>
         </is>
@@ -11197,7 +11217,7 @@
           <t>imp-reported-conflicts-migrate-barring-members</t>
         </is>
       </c>
-      <c r="Q22" s="4" t="inlineStr">
+      <c r="S22" s="4" t="inlineStr">
         <is>
           <t>By 2032; count of ethics complaints by category before and after</t>
         </is>
@@ -11234,7 +11254,7 @@
           <t>imp-share-incoming-members-barring-members</t>
         </is>
       </c>
-      <c r="Q23" s="4" t="inlineStr">
+      <c r="S23" s="4" t="inlineStr">
         <is>
           <t>By 2032; personal financial disclosure data for each incoming class</t>
         </is>
@@ -11271,7 +11291,7 @@
           <t>imp-post-reform-studies-barring-members</t>
         </is>
       </c>
-      <c r="Q24" s="4" t="inlineStr">
+      <c r="S24" s="4" t="inlineStr">
         <is>
           <t>By 2030; replication of the 2022 and 2025 studies on 2021 to 2029 data</t>
         </is>
@@ -11606,7 +11626,7 @@
           <t>officials-financial-holdings-currently</t>
         </is>
       </c>
-      <c r="R36" s="4" t="inlineStr">
+      <c r="T36" s="4" t="inlineStr">
         <is>
           <t>type: Empirical | stated: N | lb: Y | assumes: Assumes the observed overlap between holdings and committee jurisdiction reflects influence rather than coincidence</t>
         </is>
@@ -11628,7 +11648,7 @@
           <t>removing-holding-removes-influence</t>
         </is>
       </c>
-      <c r="R37" s="4" t="inlineStr">
+      <c r="T37" s="4" t="inlineStr">
         <is>
           <t>type: Causal | stated: Y | lb: Y | assumes: Assumes substitution into uncovered vehicles is partial rather than complete</t>
         </is>
@@ -11650,7 +11670,7 @@
           <t>holdings-ban-can-enacted</t>
         </is>
       </c>
-      <c r="R38" s="4" t="inlineStr">
+      <c r="T38" s="4" t="inlineStr">
         <is>
           <t>type: Empirical | stated: N | lb: Y | assumes: Assumes a Congress will bind itself and a future Congress will not quietly unwind it</t>
         </is>
@@ -11672,7 +11692,7 @@
           <t>reducing-conflicts-worth-narrower</t>
         </is>
       </c>
-      <c r="R39" s="4" t="inlineStr">
+      <c r="T39" s="4" t="inlineStr">
         <is>
           <t>type: Normative | stated: N | lb: N | assumes: Assumes trust in the institution outranks the convenience of the people in it</t>
         </is>
@@ -11883,7 +11903,7 @@
           <t>both-sides-want-officials</t>
         </is>
       </c>
-      <c r="R47" s="4" t="inlineStr">
+      <c r="T47" s="4" t="inlineStr">
         <is>
           <t>direction: Ban individual holdings, keep diversified funds legal, and let officials defer the tax on forced sales.</t>
         </is>
@@ -11905,7 +11925,7 @@
           <t>bar-individual-stocks-sector</t>
         </is>
       </c>
-      <c r="R48" s="4" t="inlineStr">
+      <c r="T48" s="4" t="inlineStr">
         <is>
           <t>premise: Both sides accept that the current $200 fee is not a penalty. | difficult: Every element is drafted, and the Senate has not scheduled a vote.</t>
         </is>
@@ -11932,7 +11952,7 @@
           <t>advertised-reason-what-actually</t>
         </is>
       </c>
-      <c r="R49" s="4" t="inlineStr">
+      <c r="T49" s="4" t="inlineStr">
         <is>
           <t>advertised: Stop officials from trading on what they learn in office. | actual: For some sponsors, a popular vote that substitutes for harder ethics reform. Evidence: bills advance in election years and stall afterward.</t>
         </is>
@@ -11959,7 +11979,7 @@
           <t>advertised-reason-what-actually-2</t>
         </is>
       </c>
-      <c r="R50" s="4" t="inlineStr">
+      <c r="T50" s="4" t="inlineStr">
         <is>
           <t>advertised: Protect ordinary property rights. | actual: Protecting a specific income stream. Evidence: the loudest objections came from members with the largest active portfolios.</t>
         </is>
@@ -12390,7 +12410,7 @@
           <t>value</t>
         </is>
       </c>
-      <c r="R68" s="4" t="inlineStr">
+      <c r="T68" s="4" t="inlineStr">
         <is>
           <t>value: Honest government | srank: 1 | orank: 2 | why: Supporters rank it above the cost to officials; opponents agree it matters but rank property rights first.</t>
         </is>
@@ -12407,7 +12427,7 @@
           <t>value</t>
         </is>
       </c>
-      <c r="R69" s="4" t="inlineStr">
+      <c r="T69" s="4" t="inlineStr">
         <is>
           <t>value: Property rights | srank: 3 | orank: 1 | why: Opponents treat the holding as an ordinary right; supporters treat it as a condition of a voluntary office.</t>
         </is>
@@ -12424,7 +12444,7 @@
           <t>value</t>
         </is>
       </c>
-      <c r="R70" s="4" t="inlineStr">
+      <c r="T70" s="4" t="inlineStr">
         <is>
           <t>value: Open service to people of ordinary means | srank: 2 | orank: 3 | why: Both sides claim it: supporters say conflicts favor the wealthy, opponents say divestiture costs do.</t>
         </is>
@@ -12441,7 +12461,7 @@
           <t>definition</t>
         </is>
       </c>
-      <c r="R71" s="4" t="inlineStr">
+      <c r="T71" s="4" t="inlineStr">
         <is>
           <t>term: Individual stock | definition: A holding in a single company, as opposed to a diversified fund holding many. Every serious proposal permits diversified funds and Treasuries.</t>
         </is>
@@ -12458,7 +12478,7 @@
           <t>definition</t>
         </is>
       </c>
-      <c r="R72" s="4" t="inlineStr">
+      <c r="T72" s="4" t="inlineStr">
         <is>
           <t>term: Conflict of interest | definition: A financial stake in the outcome of a decision the official participates in. It exists on ownership and does not require proof that the decision was changed.</t>
         </is>
@@ -12475,7 +12495,7 @@
           <t>definition</t>
         </is>
       </c>
-      <c r="R73" s="4" t="inlineStr">
+      <c r="T73" s="4" t="inlineStr">
         <is>
           <t>term: Use of public office for private gain | definition: Defined on the principle page this one sits under and used here without restatement.</t>
         </is>
@@ -12497,7 +12517,7 @@
           <t>Empirical</t>
         </is>
       </c>
-      <c r="R74" s="4" t="inlineStr">
+      <c r="T74" s="4" t="inlineStr">
         <is>
           <t>what: Whether holdings actually change votes, and whether any trading advantage survived the STOCK Act. | move: A matched study of holdings against roll-call votes, which does not yet exist.</t>
         </is>
@@ -12519,7 +12539,7 @@
           <t>Definitional</t>
         </is>
       </c>
-      <c r="R75" s="4" t="inlineStr">
+      <c r="T75" s="4" t="inlineStr">
         <is>
           <t>what: Whether "conflict of interest" means a proven influence or an unresolvable appearance. | move: Score the two readings separately; they have different evidence.</t>
         </is>
@@ -12541,7 +12561,7 @@
           <t>Values</t>
         </is>
       </c>
-      <c r="R76" s="4" t="inlineStr">
+      <c r="T76" s="4" t="inlineStr">
         <is>
           <t>what: Whether the property rights of officeholders outrank public confidence in the institution. | move: A values ranking, not more data.</t>
         </is>
@@ -12563,7 +12583,7 @@
           <t>Linkage</t>
         </is>
       </c>
-      <c r="R77" s="4" t="inlineStr">
+      <c r="T77" s="4" t="inlineStr">
         <is>
           <t>what: Whether underperforming portfolios bear on whether ownership creates a voting conflict. | move: The linkage page for the returns argument.</t>
         </is>
@@ -13114,7 +13134,7 @@
           <t>after-bar-takes-effect</t>
         </is>
       </c>
-      <c r="Q100" s="4" t="inlineStr">
+      <c r="S100" s="4" t="inlineStr">
         <is>
           <t>By 2030; nomination records and White House staff lists</t>
         </is>
@@ -13141,7 +13161,7 @@
           <t>documented-contacts-which-foreign</t>
         </is>
       </c>
-      <c r="Q101" s="4" t="inlineStr">
+      <c r="S101" s="4" t="inlineStr">
         <is>
           <t>By 2032; inspector general and congressional oversight records</t>
         </is>
@@ -13168,7 +13188,7 @@
           <t>relatives-continue-shape-policy</t>
         </is>
       </c>
-      <c r="Q102" s="4" t="inlineStr">
+      <c r="S102" s="4" t="inlineStr">
         <is>
           <t>By 2032; same oversight records, counted the same way</t>
         </is>
@@ -13397,7 +13417,7 @@
           <t>relative-official-role-creates</t>
         </is>
       </c>
-      <c r="R109" s="4" t="inlineStr">
+      <c r="T109" s="4" t="inlineStr">
         <is>
           <t>type: Empirical | stated: N | lb: Y | assumes: Assumes the supervision problem is not solved by disclosure and recusal</t>
         </is>
@@ -13419,7 +13439,7 @@
           <t>bar-removes-influence-rather</t>
         </is>
       </c>
-      <c r="R110" s="4" t="inlineStr">
+      <c r="T110" s="4" t="inlineStr">
         <is>
           <t>type: Causal | stated: Y | lb: Y | assumes: Assumes the rule is written around function rather than job title</t>
         </is>
@@ -13441,7 +13461,7 @@
           <t>congress-can-impose-bar</t>
         </is>
       </c>
-      <c r="R111" s="4" t="inlineStr">
+      <c r="T111" s="4" t="inlineStr">
         <is>
           <t>type: Definitional | stated: N | lb: Y | assumes: Assumes Congress can narrow the staffing latitude it granted in 1978</t>
         </is>
@@ -13595,7 +13615,7 @@
           <t>both-sides-want-relatives</t>
         </is>
       </c>
-      <c r="R118" s="4" t="inlineStr">
+      <c r="T118" s="4" t="inlineStr">
         <is>
           <t>direction: Reach anyone performing official functions, related or not, with disclosure and recusal rules.</t>
         </is>
@@ -13617,7 +13637,7 @@
           <t>bar-relatives-senate-confirmed</t>
         </is>
       </c>
-      <c r="R119" s="4" t="inlineStr">
+      <c r="T119" s="4" t="inlineStr">
         <is>
           <t>premise: Both sides agree that an unrecorded adviser with real authority is the worst outcome. | difficult: Defining "official function" tightly enough to enforce and loosely enough to catch the informal adviser.</t>
         </is>
@@ -13766,7 +13786,7 @@
           <t>value</t>
         </is>
       </c>
-      <c r="R126" s="4" t="inlineStr">
+      <c r="T126" s="4" t="inlineStr">
         <is>
           <t>value: Accountable government | srank: 1 | orank: 2 | why: Supporters rank a supervisable chain of command first; opponents rank the president's choice of advisers first.</t>
         </is>
@@ -13783,7 +13803,7 @@
           <t>value</t>
         </is>
       </c>
-      <c r="R127" s="4" t="inlineStr">
+      <c r="T127" s="4" t="inlineStr">
         <is>
           <t>value: Presidential discretion | srank: 3 | orank: 1 | why: Opponents treat it as constitutional; supporters treat it as a statutory grant Congress can narrow.</t>
         </is>
@@ -13800,7 +13820,7 @@
           <t>definition</t>
         </is>
       </c>
-      <c r="R128" s="4" t="inlineStr">
+      <c r="T128" s="4" t="inlineStr">
         <is>
           <t>term: Family member | definition: The twenty-five relations enumerated in 5 U.S.C. 3110, which includes in-laws, plus any person sharing a household with the official.</t>
         </is>
@@ -13817,7 +13837,7 @@
           <t>definition</t>
         </is>
       </c>
-      <c r="R129" s="4" t="inlineStr">
+      <c r="T129" s="4" t="inlineStr">
         <is>
           <t>term: Official government function | definition: Exercising authority delegated by the office: negotiating on behalf of the United States, directing staff, or making or approving a government decision. Giving private advice is not.</t>
         </is>
@@ -13839,7 +13859,7 @@
           <t>Empirical</t>
         </is>
       </c>
-      <c r="R130" s="4" t="inlineStr">
+      <c r="T130" s="4" t="inlineStr">
         <is>
           <t>what: Whether formal roles or informal ones produce more unchecked influence. | move: A count of documented family-channel decisions under each arrangement.</t>
         </is>
@@ -13861,7 +13881,7 @@
           <t>Definitional</t>
         </is>
       </c>
-      <c r="R131" s="4" t="inlineStr">
+      <c r="T131" s="4" t="inlineStr">
         <is>
           <t>what: What counts as an "official government function" when the adviser holds no office. | move: Draft the function test and see whether it can be applied to real cases.</t>
         </is>
@@ -13883,7 +13903,7 @@
           <t>Values</t>
         </is>
       </c>
-      <c r="R132" s="4" t="inlineStr">
+      <c r="T132" s="4" t="inlineStr">
         <is>
           <t>what: Whether a president's trust in an adviser outranks the public's claim to a supervisable one. | move: A values ranking.</t>
         </is>
@@ -13905,7 +13925,7 @@
           <t>Linkage</t>
         </is>
       </c>
-      <c r="R133" s="4" t="inlineStr">
+      <c r="T133" s="4" t="inlineStr">
         <is>
           <t>what: Whether campaign payments and private ventures bear on a rule about official duties. | move: The linkage page for the private-business argument.</t>
         </is>
@@ -14395,7 +14415,7 @@
           <t>within-two-election-cycles</t>
         </is>
       </c>
-      <c r="Q153" s="4" t="inlineStr">
+      <c r="S153" s="4" t="inlineStr">
         <is>
           <t>By 2032; published returns compared against the same officials' disclosure filings</t>
         </is>
@@ -14422,7 +14442,7 @@
           <t>published-returns-add-nothing</t>
         </is>
       </c>
-      <c r="Q154" s="4" t="inlineStr">
+      <c r="S154" s="4" t="inlineStr">
         <is>
           <t>By 2032; independent review of both documents for the same officials</t>
         </is>
@@ -14654,7 +14674,7 @@
           <t>tax-returns-contain-conflict</t>
         </is>
       </c>
-      <c r="R161" s="4" t="inlineStr">
+      <c r="T161" s="4" t="inlineStr">
         <is>
           <t>type: Empirical | stated: Y | lb: Y | assumes: Assumes foreign income, lender identity and income character are conflict-relevant</t>
         </is>
@@ -14676,7 +14696,7 @@
           <t>publication-changes-what-officials</t>
         </is>
       </c>
-      <c r="R162" s="4" t="inlineStr">
+      <c r="T162" s="4" t="inlineStr">
         <is>
           <t>type: Causal | stated: N | lb: Y | assumes: Assumes someone with the power to act reads and responds to the disclosure</t>
         </is>
@@ -14698,7 +14718,7 @@
           <t>federal-publication-requirement-officeholders</t>
         </is>
       </c>
-      <c r="R163" s="4" t="inlineStr">
+      <c r="T163" s="4" t="inlineStr">
         <is>
           <t>type: Definitional | stated: N | lb: Y | assumes: Assumes a duty on officeholders differs from a condition on ballot access</t>
         </is>
@@ -14852,7 +14872,7 @@
           <t>both-sides-want-conflicts</t>
         </is>
       </c>
-      <c r="R170" s="4" t="inlineStr">
+      <c r="T170" s="4" t="inlineStr">
         <is>
           <t>direction: Strengthen the disclosure form to require exact values, foreign income and lender identity, rather than publishing the return itself.</t>
         </is>
@@ -14874,7 +14894,7 @@
           <t>require-exact-values-rather</t>
         </is>
       </c>
-      <c r="R171" s="4" t="inlineStr">
+      <c r="T171" s="4" t="inlineStr">
         <is>
           <t>premise: Both sides agree the current ranges are too coarse to screen conflicts. | difficult: Officials would have to agree to disclose exact figures, which is the thing the ranges were designed to avoid.</t>
         </is>
@@ -15023,7 +15043,7 @@
           <t>value</t>
         </is>
       </c>
-      <c r="R178" s="4" t="inlineStr">
+      <c r="T178" s="4" t="inlineStr">
         <is>
           <t>value: Transparency | srank: 1 | orank: 3 | why: Supporters treat publication as the default for public power; opponents treat it as a burden requiring justification.</t>
         </is>
@@ -15040,7 +15060,7 @@
           <t>value</t>
         </is>
       </c>
-      <c r="R179" s="4" t="inlineStr">
+      <c r="T179" s="4" t="inlineStr">
         <is>
           <t>value: Privacy | srank: 3 | orank: 1 | why: Opponents extend it to the official's family; supporters confine it to people who did not take the office.</t>
         </is>
@@ -15057,7 +15077,7 @@
           <t>definition</t>
         </is>
       </c>
-      <c r="R180" s="4" t="inlineStr">
+      <c r="T180" s="4" t="inlineStr">
         <is>
           <t>term: Tax return | definition: The complete federal return as filed, including schedules, and the returns of entities the filer controls where the proposal reaches them.</t>
         </is>
@@ -15074,7 +15094,7 @@
           <t>definition</t>
         </is>
       </c>
-      <c r="R181" s="4" t="inlineStr">
+      <c r="T181" s="4" t="inlineStr">
         <is>
           <t>term: Financial disclosure form | definition: OGE Form 278e, filed annually, reporting assets, income sources, liabilities, positions, agreements and gifts in value ranges.</t>
         </is>
@@ -15096,7 +15116,7 @@
           <t>Empirical</t>
         </is>
       </c>
-      <c r="R182" s="4" t="inlineStr">
+      <c r="T182" s="4" t="inlineStr">
         <is>
           <t>what: Whether returns contain conflict-relevant facts the disclosure form lacks. | move: A line-by-line comparison of both documents for the same official, which the 2022 release makes possible.</t>
         </is>
@@ -15118,7 +15138,7 @@
           <t>Definitional</t>
         </is>
       </c>
-      <c r="R183" s="4" t="inlineStr">
+      <c r="T183" s="4" t="inlineStr">
         <is>
           <t>what: Whether "conflict" means an asset that could be affected or an income stream that was. | move: Score the two readings separately.</t>
         </is>
@@ -15140,7 +15160,7 @@
           <t>Values</t>
         </is>
       </c>
-      <c r="R184" s="4" t="inlineStr">
+      <c r="T184" s="4" t="inlineStr">
         <is>
           <t>what: Whether an officeholder's family keeps ordinary financial privacy. | move: A values ranking, not more data.</t>
         </is>
@@ -15162,7 +15182,7 @@
           <t>Linkage</t>
         </is>
       </c>
-      <c r="R185" s="4" t="inlineStr">
+      <c r="T185" s="4" t="inlineStr">
         <is>
           <t>what: Whether a state ballot-access ruling bears on a federal duty imposed on officeholders. | move: The linkage page for the constitutional argument.</t>
         </is>
@@ -15701,7 +15721,7 @@
           <t>decade-after-override-mechanism</t>
         </is>
       </c>
-      <c r="Q207" s="4" t="inlineStr">
+      <c r="S207" s="4" t="inlineStr">
         <is>
           <t>By 2040; Office of the Pardon Attorney records against the clemency grant list</t>
         </is>
@@ -15728,7 +15748,7 @@
           <t>override-never-used-because</t>
         </is>
       </c>
-      <c r="Q208" s="4" t="inlineStr">
+      <c r="S208" s="4" t="inlineStr">
         <is>
           <t>By 2040; count of override votes attempted and succeeded</t>
         </is>
@@ -15755,7 +15775,7 @@
           <t>presidents-shift-pre-emptive</t>
         </is>
       </c>
-      <c r="Q209" s="4" t="inlineStr">
+      <c r="S209" s="4" t="inlineStr">
         <is>
           <t>By 2040; share of grants issued in the final week of a term</t>
         </is>
@@ -15987,7 +16007,7 @@
           <t>some-pardons-granted-president</t>
         </is>
       </c>
-      <c r="R216" s="4" t="inlineStr">
+      <c r="T216" s="4" t="inlineStr">
         <is>
           <t>type: Empirical | stated: Y | lb: Y | assumes: Assumes a grant to a relative or associate is for private benefit rather than an ordinary exercise of mercy</t>
         </is>
@@ -16009,7 +16029,7 @@
           <t>congressional-override-deter-reverse</t>
         </is>
       </c>
-      <c r="R217" s="4" t="inlineStr">
+      <c r="T217" s="4" t="inlineStr">
         <is>
           <t>type: Causal | stated: N | lb: Y | assumes: Assumes two thirds of both chambers could be assembled against a president of either party</t>
         </is>
@@ -16031,7 +16051,7 @@
           <t>override-mechanism-can-enacted</t>
         </is>
       </c>
-      <c r="R218" s="4" t="inlineStr">
+      <c r="T218" s="4" t="inlineStr">
         <is>
           <t>type: Definitional | stated: N | lb: Y | assumes: Assumes a constitutional amendment, since the Supreme Court has foreclosed the statutory route</t>
         </is>
@@ -16195,7 +16215,7 @@
           <t>both-sides-agree-selling</t>
         </is>
       </c>
-      <c r="R225" s="4" t="inlineStr">
+      <c r="T225" s="4" t="inlineStr">
         <is>
           <t>direction: Publish the review file for every grant and prosecute pardon bribery, which needs no amendment.</t>
         </is>
@@ -16217,7 +16237,7 @@
           <t>require-pardon-attorney-s</t>
         </is>
       </c>
-      <c r="R226" s="4" t="inlineStr">
+      <c r="T226" s="4" t="inlineStr">
         <is>
           <t>premise: Both sides accept that a pardon sold for money is indefensible. | difficult: It needs three quarters of the states, and support currently splits 76 to 34 by party.</t>
         </is>
@@ -16437,7 +16457,7 @@
           <t>value</t>
         </is>
       </c>
-      <c r="R236" s="4" t="inlineStr">
+      <c r="T236" s="4" t="inlineStr">
         <is>
           <t>value: Accountability for every public power | srank: 1 | orank: 3 | why: Supporters treat an unchecked power as an anomaly; opponents treat this one as deliberate.</t>
         </is>
@@ -16454,7 +16474,7 @@
           <t>value</t>
         </is>
       </c>
-      <c r="R237" s="4" t="inlineStr">
+      <c r="T237" s="4" t="inlineStr">
         <is>
           <t>value: Mercy that does not need permission | srank: 3 | orank: 1 | why: Opponents rank the unpopular pardon first; supporters say a two-thirds bar protects it.</t>
         </is>
@@ -16471,7 +16491,7 @@
           <t>value</t>
         </is>
       </c>
-      <c r="R238" s="4" t="inlineStr">
+      <c r="T238" s="4" t="inlineStr">
         <is>
           <t>value: Separation of powers | srank: 2 | orank: 1 | why: Both claim it: supporters as a check, opponents as a boundary.</t>
         </is>
@@ -16488,7 +16508,7 @@
           <t>definition</t>
         </is>
       </c>
-      <c r="R239" s="4" t="inlineStr">
+      <c r="T239" s="4" t="inlineStr">
         <is>
           <t>term: Pardon | definition: An executive act relieving a person of the legal consequences of a federal offense. It reaches federal offenses only and cannot be used in cases of impeachment.</t>
         </is>
@@ -16505,7 +16525,7 @@
           <t>definition</t>
         </is>
       </c>
-      <c r="R240" s="4" t="inlineStr">
+      <c r="T240" s="4" t="inlineStr">
         <is>
           <t>term: Override | definition: A vote of two thirds of both chambers nullifying a grant of clemency, which on the analysis of this page requires a constitutional amendment.</t>
         </is>
@@ -16527,7 +16547,7 @@
           <t>Empirical</t>
         </is>
       </c>
-      <c r="R241" s="4" t="inlineStr">
+      <c r="T241" s="4" t="inlineStr">
         <is>
           <t>what: Whether an override could ever actually be exercised at a two-thirds threshold. | move: Count the votes in past Congresses against actual controversial grants.</t>
         </is>
@@ -16549,7 +16569,7 @@
           <t>Definitional</t>
         </is>
       </c>
-      <c r="R242" s="4" t="inlineStr">
+      <c r="T242" s="4" t="inlineStr">
         <is>
           <t>what: Whether a pardon to a relative is "private gain" or an exercise of mercy the relationship does not disqualify. | move: Score the two readings separately.</t>
         </is>
@@ -16571,7 +16591,7 @@
           <t>Values</t>
         </is>
       </c>
-      <c r="R243" s="4" t="inlineStr">
+      <c r="T243" s="4" t="inlineStr">
         <is>
           <t>what: Whether unchecked mercy is a defect in the design or its purpose. | move: A values ranking, not more data.</t>
         </is>
@@ -16593,7 +16613,7 @@
           <t>Linkage</t>
         </is>
       </c>
-      <c r="R244" s="4" t="inlineStr">
+      <c r="T244" s="4" t="inlineStr">
         <is>
           <t>what: Whether the failure of the introduced amendments bears on whether the mechanism would work. | move: The linkage page for the stalled-proposals evidence.</t>
         </is>
@@ -17086,7 +17106,7 @@
           <t>definition</t>
         </is>
       </c>
-      <c r="R268" s="4" t="inlineStr">
+      <c r="T268" s="4" t="inlineStr">
         <is>
           <t>term: Private gain | definition: A financial or positional benefit that flows to the official, the official's family, or a business they hold an interest in, and that would not have flowed to them had they not held the office.</t>
         </is>
@@ -17103,7 +17123,7 @@
           <t>definition</t>
         </is>
       </c>
-      <c r="R269" s="4" t="inlineStr">
+      <c r="T269" s="4" t="inlineStr">
         <is>
           <t>term: Use of office | definition: Any exercise of the powers, information or access that the office confers, including appointments, votes, clemency and the ability to be in the room.</t>
         </is>
@@ -31302,7 +31322,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R885"/>
+  <autoFilter ref="A1:T885"/>
   <dataValidations count="2">
     <dataValidation sqref="B2:B5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"argument,assumption,bias,category,cba,component,compromise,definition,dispute,downstream,evidence,impact,interest,interest_listing,law,long_term,media,motive,obstacle,person,prediction,related,shared_interest,short_term,similar,upstream,value"</formula1>

--- a/tools/static-site/ISE_Data_Entry.xlsx
+++ b/tools/static-site/ISE_Data_Entry.xlsx
@@ -12,7 +12,7 @@
     <sheet name="edges" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'pages'!$A$1:$W$262</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'pages'!$A$1:$X$262</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'edges'!$A$1:$T$885</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -180,100 +180,105 @@
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>The claim, in one complete sentence. Blank for the kinds whose question is written by formula.</t>
+        <t>The claim as it reads in the table of the page it sits under, where that page supplies the context. Blank for the kinds whose question is written by formula.</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>The page this one is used on.</t>
+        <t>The same claim with its context written back in, as a complete proposition that can headline its own page. Fill it whenever the short wording only means what it means underneath its parent; leave it blank when the short wording already stands alone.</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>For a formula-built page: the row it is about.</t>
+        <t>The page this one is used on.</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
-        <t>For a formula-built page: the page that row is under.</t>
+        <t>For a formula-built page: the row it is about.</t>
       </text>
     </comment>
     <comment ref="H1" authorId="0" shapeId="0">
       <text>
-        <t>linkage: Argument, Evidence, Prediction, Interest or Media. media: Book, Study, Article, Report, Film, Podcast, Video.</t>
+        <t>For a formula-built page: the page that row is under.</t>
       </text>
     </comment>
     <comment ref="I1" authorId="0" shapeId="0">
       <text>
-        <t>linkage: Supports or Weakens. driver: Support or Opposition.</t>
+        <t>linkage: Argument, Evidence, Prediction, Interest or Media. media: Book, Study, Article, Report, Film, Podcast, Video.</t>
       </text>
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
-        <t>importance: what kind of row this page scores.</t>
+        <t>linkage: Supports or Weakens. driver: Support or Opposition.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>interest: the value it appeals to.</t>
+        <t>importance: what kind of row this page scores.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
       <text>
-        <t>interest: what a reading of it looks like.</t>
+        <t>interest: the value it appeals to.</t>
       </text>
     </comment>
     <comment ref="M1" authorId="0" shapeId="0">
       <text>
-        <t>media: where to find the work.</t>
+        <t>interest: what a reading of it looks like.</t>
       </text>
     </comment>
     <comment ref="N1" authorId="0" shapeId="0">
       <text>
-        <t>What this claim rests on, if it is an observed finding: statistics, record, rct, meta, observational, historical, expert_data, expert_claim, anecdote, logic, analogy, norm, intuition, news, survey, eyewitness, visual, artifact. Blank means nothing observed, and the claim starts at a coin flip. Classify what the sentence asserts, not the instrument: "58 percent told a pollster X" is statistics; "Americans believe X" is survey.</t>
+        <t>media: where to find the work.</t>
       </text>
     </comment>
     <comment ref="O1" authorId="0" shapeId="0">
       <text>
-        <t>Independent replications of this finding. Blank counts as one, the finding itself.</t>
+        <t>What this claim rests on, if it is an observed finding: statistics, record, rct, meta, observational, historical, expert_data, expert_claim, anecdote, logic, analogy, norm, intuition, news, survey, eyewitness, visual, artifact. Blank means nothing observed, and the claim starts at a coin flip. Classify what the sentence asserts, not the instrument: "58 percent told a pollster X" is statistics; "Americans believe X" is survey.</t>
       </text>
     </comment>
     <comment ref="P1" authorId="0" shapeId="0">
       <text>
-        <t>Percent of those replications that agreed. Blank counts as 100. At 50 the claim starts at a coin flip whatever its source type, because a contested literature has established nothing.</t>
+        <t>Independent replications of this finding. Blank counts as one, the finding itself.</t>
       </text>
     </comment>
     <comment ref="Q1" authorId="0" shapeId="0">
       <text>
-        <t>interest: what the measure shows if the belief is true.</t>
+        <t>Percent of those replications that agreed. Blank counts as 100. At 50 the claim starts at a coin flip whatever its source type, because a contested literature has established nothing.</t>
       </text>
     </comment>
     <comment ref="R1" authorId="0" shapeId="0">
       <text>
-        <t>interest: what it shows if the belief is false.</t>
+        <t>interest: what the measure shows if the belief is true.</t>
       </text>
     </comment>
     <comment ref="S1" authorId="0" shapeId="0">
       <text>
-        <t>interest: the latest reading, with source.</t>
+        <t>interest: what it shows if the belief is false.</t>
       </text>
     </comment>
     <comment ref="T1" authorId="0" shapeId="0">
       <text>
-        <t>The one-sentence answer in the check table.</t>
+        <t>interest: the latest reading, with source.</t>
       </text>
     </comment>
     <comment ref="U1" authorId="0" shapeId="0">
       <text>
-        <t>The one typed line in the scorecard.</t>
+        <t>The one-sentence answer in the check table.</t>
       </text>
     </comment>
     <comment ref="V1" authorId="0" shapeId="0">
       <text>
+        <t>The one typed line in the scorecard.</t>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0" shapeId="0">
+      <text>
         <t>belief: -100 to +100 on the topic page.</t>
       </text>
     </comment>
-    <comment ref="W1" authorId="0" shapeId="0">
+    <comment ref="X1" authorId="0" shapeId="0">
       <text>
         <t>belief: the logical form of the claim.</t>
       </text>
@@ -310,7 +315,7 @@
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>The claim, in one complete sentence. Blank for the kinds whose question is written by formula.</t>
+        <t>The claim as it reads in the table of the page it sits under, where that page supplies the context. Blank for the kinds whose question is written by formula.</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
@@ -365,7 +370,7 @@
     </comment>
     <comment ref="P1" authorId="0" shapeId="0">
       <text>
-        <t>cost and benefit rows: the estimate, in those units. The one typed number in the system.</t>
+        <t>cost and benefit rows: the central estimate, in those units. The one typed number in the system.</t>
       </text>
     </comment>
     <comment ref="Q1" authorId="0" shapeId="0">
@@ -780,29 +785,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W262"/>
+  <dimension ref="A1:X262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="90" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="90" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="50" customWidth="1" min="12" max="12"/>
-    <col width="40" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="60" customWidth="1" min="17" max="17"/>
-    <col width="60" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="60" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
+    <col width="40" customWidth="1" min="19" max="19"/>
+    <col width="50" customWidth="1" min="20" max="20"/>
+    <col width="60" customWidth="1" min="21" max="21"/>
+    <col width="60" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="60" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -828,95 +837,100 @@
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
           <t>parent</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>y</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>direction</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>rowkind</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>measured_by</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>where_found</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>etype</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>erq</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>erp</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>if_true</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>if_false</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>bridge</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>bottom_line</t>
         </is>
       </c>
-      <c r="V1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>positivity</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>form</t>
         </is>
@@ -941,20 +955,20 @@
           <t>Barring members of Congress and the president from owning or trading individual stocks would reduce the use of public office for private gain.</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="U2" s="4" t="inlineStr">
+      <c r="V2" s="4" t="inlineStr">
         <is>
           <t>The conflict is documented and the disclosure regime demonstrably fails. Whether a ban removes the conflict or relocates it into spouses, partnerships and the revolving door is the open question. It is one of three load-bearing components all sitting at the neutral start, and while they sit there any one of them caps what this page can read, however far the evidence carries the argument.</t>
         </is>
       </c>
-      <c r="V2" s="5" t="n">
+      <c r="W2" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="W2" s="4" t="inlineStr">
+      <c r="X2" s="4" t="inlineStr">
         <is>
           <t>(Officials' holdings currently influence official decisions) AND (removing the holdings removes the influence rather than relocating it) AND (a ban can be enacted and enforced). The normative component, that reducing conflicts is worth a narrower candidate pool, is separable.</t>
         </is>
@@ -979,20 +993,20 @@
           <t>Barring the president and members of Congress from giving any official government function to a family member would reduce the use of public office for private gain.</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>The legal gap is documented and the supervision problem is real. The page turns on whether a bar removes the conflict or converts a disclosed adviser into an undisclosed one. All three load-bearing components sit at the neutral start, so nothing has been established here yet and nothing is capping anything: the work is to argue them.</t>
         </is>
       </c>
-      <c r="V3" s="5" t="n">
+      <c r="W3" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="W3" s="4" t="inlineStr">
+      <c r="X3" s="4" t="inlineStr">
         <is>
           <t>(Relatives in official roles produce conflicts that ordinary supervision cannot check) AND (a bar removes those conflicts rather than driving them out of view) AND (Congress can impose the bar on the White House). The third component is where the legal fight is.</t>
         </is>
@@ -1017,20 +1031,20 @@
           <t>Requiring the president and members of Congress to publish their tax returns would reduce the use of public office for private gain.</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr">
+      <c r="V4" s="4" t="inlineStr">
         <is>
           <t>The documentary claim is the strongest part: returns do carry conflict-relevant facts the disclosure form omits. What nobody can show is that publishing them changes anything. All three load-bearing components sit at the neutral start, so what this page needs is not more evidence for the conclusion but an argument for each of its parts.</t>
         </is>
       </c>
-      <c r="V4" s="5" t="n">
+      <c r="W4" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="X4" s="4" t="inlineStr">
         <is>
           <t>(Returns contain conflict-relevant information the disclosure form lacks) AND (publishing it changes behavior or enables a check) AND (a publication requirement can be imposed). The first is documentary, the second is contested, the third is narrower than the usual objection assumes.</t>
         </is>
@@ -1055,20 +1069,20 @@
           <t>Letting Congress overturn a presidential pardon by a two-thirds vote of both chambers would reduce the use of the pardon power for private gain.</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="U5" s="4" t="inlineStr">
+      <c r="V5" s="4" t="inlineStr">
         <is>
           <t>The gap is real: clemency is the only federal power with no check, and grants to the president's own circle are documented in both parties. All three load-bearing components sit at the neutral start, so any one of them caps the page. The one to argue first is not the constitutional objection but whether an override could ever be exercised at a two-thirds threshold against a president whose own party holds a third of either chamber.</t>
         </is>
       </c>
-      <c r="V5" s="5" t="n">
+      <c r="W5" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="W5" s="4" t="inlineStr">
+      <c r="X5" s="4" t="inlineStr">
         <is>
           <t>(Some pardons are granted for the president's private benefit) AND (a congressional override would deter or reverse those grants) AND (an override can be enacted). The third component is legal rather than empirical, and it is the one most likely to hold this page down once all three have been argued.</t>
         </is>
@@ -1093,12 +1107,12 @@
           <t>Public office should not be usable for private gain.</t>
         </is>
       </c>
-      <c r="U6" s="4" t="inlineStr">
+      <c r="V6" s="4" t="inlineStr">
         <is>
           <t>Held nearly universally at this level of generality, which is why the argument always moves to the specific rules below it.</t>
         </is>
       </c>
-      <c r="V6" s="5" t="n">
+      <c r="W6" s="5" t="n">
         <v>80</v>
       </c>
     </row>
@@ -1121,12 +1135,12 @@
           <t>Every federal ethics statute since the 1962 conflict-of-interest reforms rests on this principle, so rejecting it would unsettle the whole body of law rather than one rule.</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="U7" s="4" t="inlineStr">
+      <c r="V7" s="4" t="inlineStr">
         <is>
           <t>True as legal history; that is a weaker claim than the principle itself.</t>
         </is>
@@ -1151,12 +1165,12 @@
           <t>If office can be used for private gain, decisions go to whoever pays the most rather than to whoever is right, which is the definition of a government that does not work.</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="U8" s="4" t="inlineStr">
+      <c r="V8" s="4" t="inlineStr">
         <is>
           <t>The mechanism is right in the extreme case; the size of the effect at low levels of self-dealing is not established here.</t>
         </is>
@@ -1181,12 +1195,12 @@
           <t>It is the rare principle with supermajority agreement across parties: 86 percent of registered voters backed a congressional stock trading ban, including 87 percent of Republicans and 88 percent of Democrats.</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="U9" s="4" t="inlineStr">
+      <c r="V9" s="4" t="inlineStr">
         <is>
           <t>Well measured for the stock trading case; it says what people want, not what is right.</t>
         </is>
@@ -1211,12 +1225,12 @@
           <t>Stated at this level the principle decides nothing, because every real dispute is about what counts as "gain" and what counts as "using" the office.</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="U10" s="4" t="inlineStr">
+      <c r="V10" s="4" t="inlineStr">
         <is>
           <t>A real objection to using the principle as a decision rule, not to holding it.</t>
         </is>
@@ -1241,12 +1255,12 @@
           <t>Taken literally it would bar anyone who owns anything from serving, which would leave office to people with no stake in the country they govern.</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="U11" s="4" t="inlineStr">
+      <c r="V11" s="4" t="inlineStr">
         <is>
           <t>A reductio that the drafted versions of these rules already avoid.</t>
         </is>
@@ -1271,12 +1285,12 @@
           <t>Members regularly trade in the industries their own committees oversee, which puts a private financial stake on both sides of decisions they control.</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="U12" s="4" t="inlineStr">
+      <c r="V12" s="4" t="inlineStr">
         <is>
           <t>The overlap is documented; what it causes is the contested part.</t>
         </is>
@@ -1301,12 +1315,12 @@
           <t>Disclosure has failed as a check: 78 members of one Congress filed late under the STOCK Act, the standard penalty is a $200 fee that is routinely waived, and no member has faced a serious sanction.</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="U13" s="4" t="inlineStr">
+      <c r="V13" s="4" t="inlineStr">
         <is>
           <t>The enforcement record is strong evidence; it shows the reporting regime is unenforced, not that trades were corrupt.</t>
         </is>
@@ -1331,12 +1345,12 @@
           <t>A holdings ban removes the conflict itself instead of asking the public to police thousands of individual trades after the fact.</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="U14" s="4" t="inlineStr">
+      <c r="V14" s="4" t="inlineStr">
         <is>
           <t>The strongest structural argument on the page: it changes what has to be proven.</t>
         </is>
@@ -1361,12 +1375,12 @@
           <t>The Federal Reserve barred its own policymakers from holding individual stocks in 2022 and kept functioning and kept hiring, which shows a comparable institution can operate under the rule.</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="U15" s="4" t="inlineStr">
+      <c r="V15" s="4" t="inlineStr">
         <is>
           <t>A live natural experiment in a nearby institution, with a real scope objection.</t>
         </is>
@@ -1391,12 +1405,12 @@
           <t>Trading on a closed briefing is almost impossible to prosecute, so the only rule that can actually be enforced is one that does not require proving what an official knew.</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="U16" s="4" t="inlineStr">
+      <c r="V16" s="4" t="inlineStr">
         <is>
           <t>The enforcement asymmetry is real; it is evidence about provability, not about guilt.</t>
         </is>
@@ -1421,12 +1435,12 @@
           <t>The best-identified studies of actual returns find congressional portfolios underperform the market, which is hard to square with a systematic insider advantage.</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="U17" s="4" t="inlineStr">
+      <c r="V17" s="4" t="inlineStr">
         <is>
           <t>The aggregate finding is solid and the rebuttal is that aggregates are the wrong place to look.</t>
         </is>
@@ -1451,12 +1465,12 @@
           <t>A ban on the official leaves the conflict in place through spouses, dependent children, private partnerships, real estate and crypto, none of which most proposals reach.</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="U18" s="4" t="inlineStr">
+      <c r="V18" s="4" t="inlineStr">
         <is>
           <t>A real drafting objection that the Fed template already answers in part.</t>
         </is>
@@ -1481,12 +1495,12 @@
           <t>Forced divestiture imposes real costs on officials of ordinary means and narrows who can afford to serve.</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="U19" s="4" t="inlineStr">
+      <c r="V19" s="4" t="inlineStr">
         <is>
           <t>The cost is real and largely fixable in drafting; the rebuttal is stronger than the argument.</t>
         </is>
@@ -1511,12 +1525,12 @@
           <t>Members keep the property rights of other citizens, and a ban restricts a lawful activity because of the job someone holds.</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="U20" s="4" t="inlineStr">
+      <c r="V20" s="4" t="inlineStr">
         <is>
           <t>Weakest of the four: the restriction is common elsewhere in government and the office is voluntary.</t>
         </is>
@@ -1541,12 +1555,12 @@
           <t>Congress will not enforce a ban on itself, so the statute would put a symbol in place of the enforcement reform that could work.</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="U21" s="4" t="inlineStr">
+      <c r="V21" s="4" t="inlineStr">
         <is>
           <t>The best argument against: it predicts the failure mode from the closest precedent.</t>
         </is>
@@ -1571,17 +1585,17 @@
           <t>Senators' stock purchases beat the market by about 85 basis points a month, roughly 10 percent a year, over 1993 to 1998.</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" s="5" t="inlineStr">
         <is>
           <t>observational</t>
         </is>
       </c>
-      <c r="U22" s="4" t="inlineStr">
+      <c r="V22" s="4" t="inlineStr">
         <is>
           <t>Methodologically solid for its period; its period is the problem.</t>
         </is>
@@ -1606,23 +1620,23 @@
           <t>Trades placed before legislative events earned abnormal returns of about 3 to 5 percent over 2014 to 2021.</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" s="5" t="inlineStr">
         <is>
           <t>observational</t>
         </is>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="U23" s="4" t="inlineStr">
+      <c r="V23" s="4" t="inlineStr">
         <is>
           <t>The most direct answer to the underperformance studies, and the newest, which cuts both ways.</t>
         </is>
@@ -1647,17 +1661,17 @@
           <t>78 members of the 117th Congress violated the STOCK Act's disclosure deadlines.</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" s="5" t="inlineStr">
         <is>
           <t>statistics</t>
         </is>
       </c>
-      <c r="U24" s="4" t="inlineStr">
+      <c r="V24" s="4" t="inlineStr">
         <is>
           <t>Accurate as a count of filing failures; frequently oversold as a count of misconduct.</t>
         </is>
@@ -1682,17 +1696,17 @@
           <t>131 federal judges heard 685 cases involving companies in which they or their families held stock, over 2010 to 2018.</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" s="5" t="inlineStr">
         <is>
           <t>statistics</t>
         </is>
       </c>
-      <c r="U25" s="4" t="inlineStr">
+      <c r="V25" s="4" t="inlineStr">
         <is>
           <t>Strong evidence about disclosure regimes generally; one institution removed from the belief.</t>
         </is>
@@ -1717,17 +1731,17 @@
           <t>Federal Reserve officials have been barred from holding individual stocks, sector funds, individual bonds, crypto and derivatives since May 2022, with preclearance and a one-year holding period.</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" s="5" t="inlineStr">
         <is>
           <t>record</t>
         </is>
       </c>
-      <c r="U26" s="4" t="inlineStr">
+      <c r="V26" s="4" t="inlineStr">
         <is>
           <t>Establishes that the rule is workable; says little yet about its long-run costs.</t>
         </is>
@@ -1752,17 +1766,17 @@
           <t>Congressional portfolios underperformed market benchmarks by roughly 2 to 3 percent a year over 2004 to 2008.</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" s="5" t="inlineStr">
         <is>
           <t>observational</t>
         </is>
       </c>
-      <c r="U27" s="4" t="inlineStr">
+      <c r="V27" s="4" t="inlineStr">
         <is>
           <t>The strongest single piece of evidence against, and its known weakness is that averages hide tails.</t>
         </is>
@@ -1787,23 +1801,23 @@
           <t>No evidence that members of Congress outperformed the market over 2012 to 2020, the period after the STOCK Act.</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" s="5" t="inlineStr">
         <is>
           <t>observational</t>
         </is>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="U28" s="4" t="inlineStr">
+      <c r="V28" s="4" t="inlineStr">
         <is>
           <t>Directly on point for the trading-advantage claim; silent on the voting-conflict claim.</t>
         </is>
@@ -1828,12 +1842,12 @@
           <t>Five years after a ban takes effect, individual equity holdings reported by members fall to near zero and no trading scandal originates in Congress.</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="U29" s="4" t="inlineStr">
+      <c r="V29" s="4" t="inlineStr">
         <is>
           <t>Pending, and the metric is gameable in a way the prediction should name.</t>
         </is>
@@ -1858,12 +1872,12 @@
           <t>Public trust in Congress five years after a ban is higher than the pre-ban trend predicted.</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="U30" s="4" t="inlineStr">
+      <c r="V30" s="4" t="inlineStr">
         <is>
           <t>Weakly diagnostic: a lot of noise for one signal.</t>
         </is>
@@ -1888,12 +1902,12 @@
           <t>A jurisdiction that adopts a holdings ban shows conflicted votes falling relative to comparable bodies that did not.</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="U31" s="4" t="inlineStr">
+      <c r="V31" s="4" t="inlineStr">
         <is>
           <t>The single most informative study nobody has run.</t>
         </is>
@@ -1918,12 +1932,12 @@
           <t>Reported conflicts migrate to spouse accounts and private partnerships, leaving the total number of conflict complaints unchanged.</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="U32" s="4" t="inlineStr">
+      <c r="V32" s="4" t="inlineStr">
         <is>
           <t>The most likely way the belief fails, and the one the drafting can answer.</t>
         </is>
@@ -1948,12 +1962,12 @@
           <t>The share of incoming members whose wealth is in the top 1 percent rises after a ban.</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="U33" s="4" t="inlineStr">
+      <c r="V33" s="4" t="inlineStr">
         <is>
           <t>Testable from existing data, and the base rate makes a large move unlikely.</t>
         </is>
@@ -1978,12 +1992,12 @@
           <t>Post-reform studies continue to find no abnormal returns, so there is no trading advantage for a ban to remove.</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="U34" s="4" t="inlineStr">
+      <c r="V34" s="4" t="inlineStr">
         <is>
           <t>Would weaken one branch of the tree and leave the other standing.</t>
         </is>
@@ -2008,12 +2022,12 @@
           <t>Members stop voting on industries in which they hold a personal stake.</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="U35" s="4" t="inlineStr">
+      <c r="V35" s="4" t="inlineStr">
         <is>
           <t>Mechanically near-certain in direction, contested in size.</t>
         </is>
@@ -2038,12 +2052,12 @@
           <t>Officials stop placing trades ahead of government announcements.</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="U36" s="4" t="inlineStr">
+      <c r="V36" s="4" t="inlineStr">
         <is>
           <t>Direction certain, magnitude resting on a contested base rate.</t>
         </is>
@@ -2068,12 +2082,12 @@
           <t>Voters can tell a compromised official from a clean one without an investigation.</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="U37" s="4" t="inlineStr">
+      <c r="V37" s="4" t="inlineStr">
         <is>
           <t>The benefit most often claimed and the least supported by the record.</t>
         </is>
@@ -2098,12 +2112,12 @@
           <t>Officials get one rule they can follow without a lawyer instead of a reporting regime they violate by accident.</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="U38" s="4" t="inlineStr">
+      <c r="V38" s="4" t="inlineStr">
         <is>
           <t>Plausible and small; the Fed rule suggests the saving is partly offset.</t>
         </is>
@@ -2128,12 +2142,12 @@
           <t>Officials sell holdings on a schedule they did not choose and pay tax on the gains.</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="U39" s="4" t="inlineStr">
+      <c r="V39" s="4" t="inlineStr">
         <is>
           <t>Real and largely solvable in drafting.</t>
         </is>
@@ -2158,12 +2172,12 @@
           <t>Mid-career professionals with savings in individual equities decline to run.</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="U40" s="4" t="inlineStr">
+      <c r="V40" s="4" t="inlineStr">
         <is>
           <t>The mechanism is real; the affected group is narrower than the argument implies.</t>
         </is>
@@ -2188,12 +2202,12 @@
           <t>Officeholders lose income they currently earn from trading on their position.</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="U41" s="4" t="inlineStr">
+      <c r="V41" s="4" t="inlineStr">
         <is>
           <t>A cost that only exists to the extent the belief's own premise is true, and it falls on an interest almost nobody defends.</t>
         </is>
@@ -2218,7 +2232,7 @@
           <t>Members divest or move holdings into diversified funds within the compliance window.</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2243,7 +2257,7 @@
           <t>Filing volume falls because there are fewer transactions to report.</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2268,7 +2282,7 @@
           <t>Conflict complaints shift from trading to family and outside business interests.</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="F44" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2293,7 +2307,7 @@
           <t>The rule becomes unremarkable, as judicial and executive branch holding rules did.</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
+      <c r="F45" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2318,12 +2332,12 @@
           <t>Officials' financial holdings currently influence how they vote and what they say.</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="F46" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="U46" s="4" t="inlineStr">
+      <c r="V46" s="4" t="inlineStr">
         <is>
           <t>Documented as correlation, not established as influence. This is the load-bearing claim the whole belief rests on.</t>
         </is>
@@ -2348,12 +2362,12 @@
           <t>Removing the holding removes the influence rather than relocating it to a spouse, a partnership or a post-office job.</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
+      <c r="F47" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="U47" s="4" t="inlineStr">
+      <c r="V47" s="4" t="inlineStr">
         <is>
           <t>The weakest load-bearing part, and the one that caps the page.</t>
         </is>
@@ -2378,12 +2392,12 @@
           <t>A holdings ban can be enacted and enforced against sitting members.</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="F48" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="U48" s="4" t="inlineStr">
+      <c r="V48" s="4" t="inlineStr">
         <is>
           <t>Much stronger than it was two years ago, and still unfinished.</t>
         </is>
@@ -2408,12 +2422,12 @@
           <t>Reducing conflicts is worth a narrower candidate pool and a real compliance burden.</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="F49" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="U49" s="4" t="inlineStr">
+      <c r="V49" s="4" t="inlineStr">
         <is>
           <t>A value judgment that the cost-benefit table prices rather than settles.</t>
         </is>
@@ -2438,7 +2452,7 @@
           <t>Officials respond to financial incentives the way other people do.</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="F50" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2463,7 +2477,7 @@
           <t>Disclosure alone is sufficient when it is actually enforced.</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="F51" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2488,7 +2502,7 @@
           <t>Both sides want officials who are not, and do not appear to be, for sale.</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="F52" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2513,12 +2527,12 @@
           <t>Bar individual stocks, sector funds and derivatives for the official, spouse and dependent children; keep diversified funds and Treasuries legal; allow deferral of capital gains on forced divestiture; and set the penalty at a share of the transaction rather than a flat fee.</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
+      <c r="F53" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="U53" s="4" t="inlineStr">
+      <c r="V53" s="4" t="inlineStr">
         <is>
           <t>The most defensible version on offer; its weakness is political, not analytical.</t>
         </is>
@@ -2543,7 +2557,7 @@
           <t>The advertised reason is not what actually drives the position: Stop officials from trading on what they learn in office.</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="F54" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2568,7 +2582,7 @@
           <t>The advertised reason is not what actually drives the position: Protect ordinary property rights.</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
+      <c r="F55" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2593,7 +2607,7 @@
           <t>The people who would be bound are the people who must vote for it.</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="F56" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2618,7 +2632,7 @@
           <t>Opponents cannot point to a benefit of officials owning individual stocks that a diversified fund does not provide.</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="F57" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2643,7 +2657,7 @@
           <t>Scandal salience: a handful of vivid cases stands in for a rate nobody has measured.</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="F58" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2668,7 +2682,7 @@
           <t>Self-interest and status quo bias among the officials who would be bound.</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="F59" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2693,7 +2707,7 @@
           <t>The STOCK Act of 2012 made insider trading law explicitly applicable to Congress and required transaction reports within 45 days.</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="F60" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2718,7 +2732,7 @@
           <t>The Courthouse Ethics and Transparency Act of 2022 applied the same transaction reporting to federal judges and created a searchable database.</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2743,12 +2757,12 @@
           <t>The criminal conflict-of-interest statute does not apply to the president, the vice president, members of Congress or federal judges.</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="F62" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="U62" s="4" t="inlineStr">
+      <c r="V62" s="4" t="inlineStr">
         <is>
           <t>Listed on the weakening side because it is cited that way; the linkage page is where that gets tested.</t>
         </is>
@@ -2773,7 +2787,7 @@
           <t>Citizens keep their ordinary rights when they take public office.</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
+      <c r="F63" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2798,7 +2812,7 @@
           <t>Senior executive branch officials and their spouses should be barred from holding individual stocks.</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
+      <c r="F64" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2823,7 +2837,7 @@
           <t>Congressional staff with access to nonpublic information should face the same ban.</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="F65" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2848,7 +2862,7 @@
           <t>Members of Congress should be barred from owning any asset other than Treasury securities and diversified funds while in office.</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
+      <c r="F66" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2873,7 +2887,7 @@
           <t>Members of Congress should be required to place individual stocks in a qualified blind trust.</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
+      <c r="F67" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2898,7 +2912,7 @@
           <t>Senators Jeff Merkley, Josh Hawley and Jon Ossoff have sponsored or cosponsored legislation to ban congressional stock trading.</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="F68" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2923,7 +2937,7 @@
           <t>Representatives Chip Roy and Seth Magaziner have sponsored the leading House bills in the 119th Congress.</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
+      <c r="F69" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2948,12 +2962,12 @@
           <t>Speaker Nancy Pelosi said in December 2021 that members should be able to participate in the free-market economy, before later supporting floor consideration of a ban.</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="F70" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="U70" s="4" t="inlineStr">
+      <c r="V70" s="4" t="inlineStr">
         <is>
           <t>Accurate as a quotation, misleading as a summary of her final position.</t>
         </is>
@@ -2978,12 +2992,12 @@
           <t>The anti-nepotism statute stops at the White House door, so the rule does not reach the place where the stakes are highest.</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
+      <c r="F71" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="U71" s="4" t="inlineStr">
+      <c r="V71" s="4" t="inlineStr">
         <is>
           <t>The legal gap is real and was formally relied upon; whether a court would agree has never been tested.</t>
         </is>
@@ -3008,12 +3022,12 @@
           <t>A relative cannot be supervised, disciplined or fired the way another official can, so the ordinary checks on an official's conduct do not operate.</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
+      <c r="F72" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="U72" s="4" t="inlineStr">
+      <c r="V72" s="4" t="inlineStr">
         <is>
           <t>The strongest argument on the page: it names a mechanism that does not depend on anyone's motives.</t>
         </is>
@@ -3038,12 +3052,12 @@
           <t>An official role gives a family member a channel that foreign governments and business partners can use, with the family's private interests attached to it.</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
+      <c r="F73" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="U73" s="4" t="inlineStr">
+      <c r="V73" s="4" t="inlineStr">
         <is>
           <t>Concrete and current; the rebuttal points at a narrower remedy.</t>
         </is>
@@ -3068,12 +3082,12 @@
           <t>The rule already applies to every other federal agency, so extending it closes a gap rather than inventing a restriction.</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
+      <c r="F74" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="U74" s="4" t="inlineStr">
+      <c r="V74" s="4" t="inlineStr">
         <is>
           <t>True, and the rebuttal reframes the whole proposal as an enforcement question.</t>
         </is>
@@ -3098,12 +3112,12 @@
           <t>Formal appointment is what brings a relative inside the ethics rules; a bar pushes the same influence outside them, where nothing applies.</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
+      <c r="F75" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="U75" s="4" t="inlineStr">
+      <c r="V75" s="4" t="inlineStr">
         <is>
           <t>The best argument against, and it is answered only if the rule is drafted around function rather than title.</t>
         </is>
@@ -3128,12 +3142,12 @@
           <t>The problem people actually point to is relatives trading on the family name in private business, which this proposal does not touch.</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
+      <c r="F76" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="U76" s="4" t="inlineStr">
+      <c r="V76" s="4" t="inlineStr">
         <is>
           <t>A genuine scope objection: the proposal is aimed at a smaller target than the grievance that motivates it.</t>
         </is>
@@ -3158,12 +3172,12 @@
           <t>A president is entitled to advisers he trusts, and Congress's power to tell him whom he may consult is constitutionally contested.</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
+      <c r="F77" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="U77" s="4" t="inlineStr">
+      <c r="V77" s="4" t="inlineStr">
         <is>
           <t>Strong for White House staff, weak for Senate-confirmed posts.</t>
         </is>
@@ -3188,12 +3202,12 @@
           <t>Competence is neither inherited nor disqualified by relation, and a blanket bar excludes people for a relationship rather than for a conflict.</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
+      <c r="F78" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="U78" s="4" t="inlineStr">
+      <c r="V78" s="4" t="inlineStr">
         <is>
           <t>Answers an argument the proposal does not make.</t>
         </is>
@@ -3218,17 +3232,17 @@
           <t>The Justice Department concluded that the federal anti-nepotism statute does not bar a presidential relative's appointment to the White House Office.</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
+      <c r="F79" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
+      <c r="O79" s="5" t="inlineStr">
         <is>
           <t>record</t>
         </is>
       </c>
-      <c r="U79" s="4" t="inlineStr">
+      <c r="V79" s="4" t="inlineStr">
         <is>
           <t>Authoritative in practice, untested in court.</t>
         </is>
@@ -3253,17 +3267,17 @@
           <t>Relatives by marriage have held Senate-confirmed and envoy positions outside the White House Office, including an ambassadorship in 2025 and a special envoy designation in February 2026.</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
+      <c r="F80" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="O80" s="5" t="inlineStr">
         <is>
           <t>record</t>
         </is>
       </c>
-      <c r="U80" s="4" t="inlineStr">
+      <c r="V80" s="4" t="inlineStr">
         <is>
           <t>Current and verifiable; the confirmation point cuts against reading it as an unchecked practice.</t>
         </is>
@@ -3288,17 +3302,17 @@
           <t>Relatives who became federal employees filed public financial disclosures reporting assets of up to roughly $762 million, with multiple amendments adding previously omitted holdings.</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
+      <c r="F81" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
+      <c r="O81" s="5" t="inlineStr">
         <is>
           <t>record</t>
         </is>
       </c>
-      <c r="U81" s="4" t="inlineStr">
+      <c r="V81" s="4" t="inlineStr">
         <is>
           <t>The concrete form of the "inside the rules" argument.</t>
         </is>
@@ -3323,17 +3337,17 @@
           <t>Federal candidates paid a combined $1.3 million in wages to people sharing their surname in one election cycle, entirely through campaign committees that no official-duty rule reaches.</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
+      <c r="F82" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
+      <c r="O82" s="5" t="inlineStr">
         <is>
           <t>statistics</t>
         </is>
       </c>
-      <c r="U82" s="4" t="inlineStr">
+      <c r="V82" s="4" t="inlineStr">
         <is>
           <t>Shows where the money actually moves, which is not where the proposal points.</t>
         </is>
@@ -3358,12 +3372,12 @@
           <t>After a bar takes effect, no relative of a president or a member holds a White House, envoy or ambassadorial post.</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
+      <c r="F83" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="U83" s="4" t="inlineStr">
+      <c r="V83" s="4" t="inlineStr">
         <is>
           <t>Easy to measure and easy to satisfy without changing anything, which is the objection in one line.</t>
         </is>
@@ -3388,12 +3402,12 @@
           <t>Documented contacts in which a foreign government routes business through a presidential relative fall relative to the preceding decade.</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
+      <c r="F84" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="U84" s="4" t="inlineStr">
+      <c r="V84" s="4" t="inlineStr">
         <is>
           <t>The right thing to measure, measured by a proxy that moves for other reasons.</t>
         </is>
@@ -3418,12 +3432,12 @@
           <t>Relatives continue to shape policy as private citizens and unpaid informal advisers, and the number of documented family-channel contacts is unchanged.</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
+      <c r="F85" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="U85" s="4" t="inlineStr">
+      <c r="V85" s="4" t="inlineStr">
         <is>
           <t>The way this belief most plausibly fails.</t>
         </is>
@@ -3448,7 +3462,7 @@
           <t>Official decisions stop being made by people the president cannot supervise or remove in the ordinary way.</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
+      <c r="F86" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
@@ -3473,7 +3487,7 @@
           <t>Foreign governments lose a contact point that carries private family interests with it.</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
+      <c r="F87" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
@@ -3498,7 +3512,7 @@
           <t>Career staff can raise objections to a senior adviser without raising them to the president about his own family.</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
+      <c r="F88" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
@@ -3523,7 +3537,7 @@
           <t>A president loses advisers he trusts most, at some cost to the quality of advice he acts on.</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
+      <c r="F89" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
@@ -3548,7 +3562,7 @@
           <t>Qualified people are excluded from public service for a family relationship they did not choose.</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
+      <c r="F90" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
@@ -3573,7 +3587,7 @@
           <t>Influence moves to informal channels that file nothing and leave no record.</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
+      <c r="F91" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
@@ -3598,12 +3612,12 @@
           <t>A relative in an official role creates conflicts that ordinary supervision and ethics rules cannot check.</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
+      <c r="F92" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="U92" s="4" t="inlineStr">
+      <c r="V92" s="4" t="inlineStr">
         <is>
           <t>Contested, and the disagreement is the mirror image of the "inside the rules" argument.</t>
         </is>
@@ -3628,12 +3642,12 @@
           <t>A bar removes the influence rather than pushing it into informal channels.</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
+      <c r="F93" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="U93" s="4" t="inlineStr">
+      <c r="V93" s="4" t="inlineStr">
         <is>
           <t>Tied for weakest load-bearing component on this page, which is why the cap bites.</t>
         </is>
@@ -3658,12 +3672,12 @@
           <t>Congress can impose the bar on White House appointments.</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
+      <c r="F94" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="U94" s="4" t="inlineStr">
+      <c r="V94" s="4" t="inlineStr">
         <is>
           <t>More defensible than the pardon case and less settled than the stock case.</t>
         </is>
@@ -3688,7 +3702,7 @@
           <t>Both sides want relatives' financial interests visible rather than hidden.</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
+      <c r="F95" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
@@ -3713,7 +3727,7 @@
           <t>Bar relatives from Senate-confirmed and envoy positions, and require anyone performing official functions, whatever their title, to file the same disclosures and follow the same conflict rules as an employee.</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
+      <c r="F96" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
@@ -3738,7 +3752,7 @@
           <t>Relatives of the president should be barred from Senate-confirmed positions but permitted to serve as unpaid advisers subject to full disclosure.</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
+      <c r="F97" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
@@ -3765,10 +3779,15 @@
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
+          <t>A published tax return shows what the federal financial disclosure form does not: exact income and its character, foreign income and foreign tax credits, business losses carried forward, charitable giving, and the rate actually paid.</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="U98" s="4" t="inlineStr">
+      <c r="V98" s="4" t="inlineStr">
         <is>
           <t>The factual claim about what each document contains is correct; whether the extra content is what screens conflicts is the argument.</t>
         </is>
@@ -3795,10 +3814,15 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
+          <t>The internal check on a president’s tax compliance failed in the one case that tested it: the mandatory presidential audit was dormant, and the audit of the first two years opened the day Congress asked for the returns.</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="U99" s="4" t="inlineStr">
+      <c r="V99" s="4" t="inlineStr">
         <is>
           <t>The strongest evidence on the page, and it is about the audit rather than about publication.</t>
         </is>
@@ -3825,10 +3849,15 @@
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
+          <t>Every president from Carter through Obama released tax returns voluntarily, so a publication requirement restores a forty-year norm rather than inventing an obligation.</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="U100" s="4" t="inlineStr">
+      <c r="V100" s="4" t="inlineStr">
         <is>
           <t>Accurate history; the step from norm to statute is the contested part.</t>
         </is>
@@ -3855,10 +3884,15 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
+          <t>A published tax return can be checked by anyone, which is the only enforcement of an officeholder’s tax compliance that does not depend on an agency the officeholder appoints.</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="U101" s="4" t="inlineStr">
+      <c r="V101" s="4" t="inlineStr">
         <is>
           <t>The structural argument, and the one least dependent on any particular administration.</t>
         </is>
@@ -3885,10 +3919,15 @@
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
+          <t>A tax return shows tax positions, not conflicts, and the federal financial disclosure form already lists assets, income sources, liabilities and positions in categories built for conflict screening.</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="U102" s="4" t="inlineStr">
+      <c r="V102" s="4" t="inlineStr">
         <is>
           <t>The best argument against, and the rebuttal is specific enough to test.</t>
         </is>
@@ -3915,10 +3954,15 @@
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
+          <t>Requiring the president and members of Congress to publish their tax returns would publish the finances of spouses, children and business partners who never ran for office.</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="U103" s="4" t="inlineStr">
+      <c r="V103" s="4" t="inlineStr">
         <is>
           <t>A real privacy cost with a partial drafting answer.</t>
         </is>
@@ -3945,10 +3989,15 @@
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
+          <t>The constitutional route to a tax-return publication requirement is narrow: a disclosure condition on ballot access was already struck down once, and a badly drafted rule would be litigated rather than obeyed.</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="U104" s="4" t="inlineStr">
+      <c r="V104" s="4" t="inlineStr">
         <is>
           <t>The precedent is real and much narrower than the argument treats it.</t>
         </is>
@@ -3973,12 +4022,12 @@
           <t>Sophisticated wealth sits in pass-through entities and trusts that file their own returns, so a personal return can be published and show very little.</t>
         </is>
       </c>
-      <c r="E105" s="4" t="inlineStr">
+      <c r="F105" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="U105" s="4" t="inlineStr">
+      <c r="V105" s="4" t="inlineStr">
         <is>
           <t>The most technically substantive objection on the page.</t>
         </is>
@@ -4003,17 +4052,17 @@
           <t>The mandatory IRS audit of presidential returns was "dormant, at best," and the audit of the 2015 and 2016 returns opened on April 3, 2019, the day the committee requested them; only 2016 was completed in office.</t>
         </is>
       </c>
-      <c r="E106" s="4" t="inlineStr">
+      <c r="F106" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr">
+      <c r="O106" s="5" t="inlineStr">
         <is>
           <t>record</t>
         </is>
       </c>
-      <c r="U106" s="4" t="inlineStr">
+      <c r="V106" s="4" t="inlineStr">
         <is>
           <t>The dates are documentary and the characterization is the committee's.</t>
         </is>
@@ -4038,17 +4087,17 @@
           <t>Nixon released his returns in December 1973 and asked the Joint Committee on Taxation to review them; the review found roughly $465,000 in back taxes owed.</t>
         </is>
       </c>
-      <c r="E107" s="4" t="inlineStr">
+      <c r="F107" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr">
+      <c r="O107" s="5" t="inlineStr">
         <is>
           <t>record</t>
         </is>
       </c>
-      <c r="U107" s="4" t="inlineStr">
+      <c r="V107" s="4" t="inlineStr">
         <is>
           <t>The founding case of the norm, and it cuts slightly against compulsion.</t>
         </is>
@@ -4073,17 +4122,17 @@
           <t>The public financial disclosure form already requires assets, income sources, liabilities, positions, agreements and gifts, reported in value ranges.</t>
         </is>
       </c>
-      <c r="E108" s="4" t="inlineStr">
+      <c r="F108" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="N108" t="inlineStr">
+      <c r="O108" s="5" t="inlineStr">
         <is>
           <t>record</t>
         </is>
       </c>
-      <c r="U108" s="4" t="inlineStr">
+      <c r="V108" s="4" t="inlineStr">
         <is>
           <t>Accurate, and the range structure is exactly what the other side points at.</t>
         </is>
@@ -4108,17 +4157,17 @@
           <t>A state law requiring five years of returns from presidential primary candidates was struck down unanimously on state constitutional grounds.</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
+      <c r="F109" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="N109" t="inlineStr">
+      <c r="O109" s="5" t="inlineStr">
         <is>
           <t>record</t>
         </is>
       </c>
-      <c r="U109" s="4" t="inlineStr">
+      <c r="V109" s="4" t="inlineStr">
         <is>
           <t>Frequently cited for more than it holds, which is what its linkage page is for.</t>
         </is>
@@ -4143,12 +4192,12 @@
           <t>Within two election cycles of a publication requirement, at least one significant undisclosed foreign income source or lender relationship is found in a published return.</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
+      <c r="F110" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="U110" s="4" t="inlineStr">
+      <c r="V110" s="4" t="inlineStr">
         <is>
           <t>Diagnostic, and its failure would be ambiguous between deterrence and nothing to find.</t>
         </is>
@@ -4173,12 +4222,12 @@
           <t>Published returns add nothing to what the disclosure form already showed, and no conflict is identified from a return that the form had not already flagged.</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
+      <c r="F111" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="U111" s="4" t="inlineStr">
+      <c r="V111" s="4" t="inlineStr">
         <is>
           <t>Directly testable against the one case where both documents exist.</t>
         </is>
@@ -4205,6 +4254,11 @@
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
+          <t>If the president and members of Congress published their tax returns, foreign income and lender relationships would become visible without a subpoena.</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
@@ -4230,6 +4284,11 @@
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
+          <t>If the president and members of Congress published their tax returns, voters could judge an official’s financial entanglements before voting rather than after an investigation.</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
@@ -4255,6 +4314,11 @@
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
+          <t>If the president published their tax returns, the audit of the president would stop depending on an agency the president appoints.</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
@@ -4280,6 +4344,11 @@
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
+          <t>Under a tax-return publication requirement, spouses, children and business partners have their finances published without holding office.</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
@@ -4305,6 +4374,11 @@
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
+          <t>Under a tax-return publication requirement, officials structure their finances to look unremarkable rather than to be efficient.</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
@@ -4330,6 +4404,11 @@
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
+          <t>Published tax returns are read as scandal rather than as data, and complex but lawful items are litigated in public.</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
@@ -4353,12 +4432,12 @@
           <t>Tax returns contain conflict-relevant information that the financial disclosure form does not.</t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr">
+      <c r="F118" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="U118" s="4" t="inlineStr">
+      <c r="V118" s="4" t="inlineStr">
         <is>
           <t>The most checkable component on any of these four pages.</t>
         </is>
@@ -4385,10 +4464,15 @@
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
+          <t>Publishing the tax returns of the president and members of Congress changes what officials do, or lets someone act on what it shows.</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="U119" s="4" t="inlineStr">
+      <c r="V119" s="4" t="inlineStr">
         <is>
           <t>The weak link in substance, and it scores level with the other two rather than below them.</t>
         </is>
@@ -4413,12 +4497,12 @@
           <t>A federal publication requirement for officeholders can be enacted and would survive review.</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
+      <c r="F120" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="U120" s="4" t="inlineStr">
+      <c r="V120" s="4" t="inlineStr">
         <is>
           <t>Stronger than the pardon case: the disclosure precedent is well established.</t>
         </is>
@@ -4443,7 +4527,7 @@
           <t>Both sides want conflicts visible; they disagree about which document shows them.</t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
+      <c r="F121" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
@@ -4468,7 +4552,7 @@
           <t>Require exact values rather than ranges on the disclosure form, add foreign income and lender identity, and require the president to publish returns while leaving members under the enhanced form.</t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr">
+      <c r="F122" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
@@ -4493,7 +4577,7 @@
           <t>All senior federal officials, including agency heads and judges, should publish their tax returns annually.</t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr">
+      <c r="F123" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
@@ -4518,12 +4602,12 @@
           <t>Clemency is the only executive power with no check at all: impeachment reaches the officer, not the act, and the act is final the moment it is signed.</t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr">
+      <c r="F124" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="U124" s="4" t="inlineStr">
+      <c r="V124" s="4" t="inlineStr">
         <is>
           <t>Structurally accurate. Whether the absence of a check is a defect or the point is the whole argument.</t>
         </is>
@@ -4548,12 +4632,12 @@
           <t>Pardons granted to the president's relatives, donors, business partners and co-defendants are the clearest case of office used for private benefit, and nothing reviews them.</t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr">
+      <c r="F125" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="U125" s="4" t="inlineStr">
+      <c r="V125" s="4" t="inlineStr">
         <is>
           <t>The pattern is documented across parties, which is what makes it a structural argument rather than a partisan one.</t>
         </is>
@@ -4578,12 +4662,12 @@
           <t>A two-thirds threshold means only the pardons that both parties find indefensible would ever be reversed.</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
+      <c r="F126" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="U126" s="4" t="inlineStr">
+      <c r="V126" s="4" t="inlineStr">
         <is>
           <t>The threshold argument cuts both ways, and the page should show that rather than resolve it.</t>
         </is>
@@ -4608,12 +4692,12 @@
           <t>Most states already put a structural check on clemency and those systems function.</t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr">
+      <c r="F127" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="U127" s="4" t="inlineStr">
+      <c r="V127" s="4" t="inlineStr">
         <is>
           <t>The best evidence that a check is workable, and the rebuttal correctly identifies that it is not this check.</t>
         </is>
@@ -4638,12 +4722,12 @@
           <t>Article II grants the power without a congressional role, and the Supreme Court has held it is not subject to legislative control, so this requires a constitutional amendment rather than a statute.</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
+      <c r="F128" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="U128" s="4" t="inlineStr">
+      <c r="V128" s="4" t="inlineStr">
         <is>
           <t>Decisive against a statute and not against the belief as written, which is why it is a component question rather than a refutation.</t>
         </is>
@@ -4668,12 +4752,12 @@
           <t>Clemency exists to correct injustices the political branches will not, so a legislative veto would remove precisely the unpopular mercy the power is for.</t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr">
+      <c r="F129" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="U129" s="4" t="inlineStr">
+      <c r="V129" s="4" t="inlineStr">
         <is>
           <t>The strongest argument on the page in principle, and the two-thirds threshold is a real answer to it.</t>
         </is>
@@ -4698,12 +4782,12 @@
           <t>A reversible pardon is not a pardon: nobody could rely on it, and the power to settle whole classes of cases through amnesties would end.</t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr">
+      <c r="F130" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="U130" s="4" t="inlineStr">
+      <c r="V130" s="4" t="inlineStr">
         <is>
           <t>A serious design objection with an obvious drafting answer that no proposal has adopted.</t>
         </is>
@@ -4728,12 +4812,12 @@
           <t>A narrower fix reaches the actual abuse without touching the power: prosecute bribes paid for pardons, and require the review file to be published.</t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr">
+      <c r="F131" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="U131" s="4" t="inlineStr">
+      <c r="V131" s="4" t="inlineStr">
         <is>
           <t>The most practical alternative, and the response is that it has never actually been used.</t>
         </is>
@@ -4758,17 +4842,17 @@
           <t>58 percent of Americans said the president grants too many pardons and 56 percent supported a constitutional amendment limiting the power, with Democrats at 76 percent and Republicans at 34 percent.</t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr">
+      <c r="F132" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="N132" t="inlineStr">
+      <c r="O132" s="5" t="inlineStr">
         <is>
           <t>statistics</t>
         </is>
       </c>
-      <c r="U132" s="4" t="inlineStr">
+      <c r="V132" s="4" t="inlineStr">
         <is>
           <t>Real support, and the crosstabs are the reason to doubt the amendment path.</t>
         </is>
@@ -4793,17 +4877,17 @@
           <t>A federal judge unsealed a redacted opinion describing a Justice Department investigation into an alleged bribery-for-pardon scheme; no names were released and nobody was charged.</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
+      <c r="F133" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="N133" t="inlineStr">
+      <c r="O133" s="5" t="inlineStr">
         <is>
           <t>record</t>
         </is>
       </c>
-      <c r="U133" s="4" t="inlineStr">
+      <c r="V133" s="4" t="inlineStr">
         <is>
           <t>Enough to show the risk is not hypothetical; not enough to show it materialized.</t>
         </is>
@@ -4828,17 +4912,17 @@
           <t>Independent boards hold or gate the clemency power in more than a dozen states, and those systems operate continuously.</t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr">
+      <c r="F134" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="N134" t="inlineStr">
+      <c r="O134" s="5" t="inlineStr">
         <is>
           <t>statistics</t>
         </is>
       </c>
-      <c r="U134" s="4" t="inlineStr">
+      <c r="V134" s="4" t="inlineStr">
         <is>
           <t>Strong precedent for a check; weak precedent for this particular check.</t>
         </is>
@@ -4863,17 +4947,17 @@
           <t>The Supreme Court held that the pardon power is not subject to legislative control and that Congress can neither limit the effect of a pardon nor exclude any class of offenders from it.</t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr">
+      <c r="F135" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="N135" t="inlineStr">
+      <c r="O135" s="5" t="inlineStr">
         <is>
           <t>record</t>
         </is>
       </c>
-      <c r="U135" s="4" t="inlineStr">
+      <c r="V135" s="4" t="inlineStr">
         <is>
           <t>Decisive on the mechanism and silent on the belief as stated.</t>
         </is>
@@ -4898,17 +4982,17 @@
           <t>Proposals to let Congress nullify pardons by two-thirds vote have been introduced with bipartisan sponsorship and have not moved out of committee.</t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr">
+      <c r="F136" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="N136" t="inlineStr">
+      <c r="O136" s="5" t="inlineStr">
         <is>
           <t>record</t>
         </is>
       </c>
-      <c r="U136" s="4" t="inlineStr">
+      <c r="V136" s="4" t="inlineStr">
         <is>
           <t>Listed on the weakening side because it is argued that way, and its linkage page is where the relevance fails.</t>
         </is>
@@ -4933,12 +5017,12 @@
           <t>In the decade after an override mechanism exists, the share of clemency grants that bypass the Justice Department review process falls.</t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr">
+      <c r="F137" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="U137" s="4" t="inlineStr">
+      <c r="V137" s="4" t="inlineStr">
         <is>
           <t>The best-measured prediction on the page.</t>
         </is>
@@ -4963,12 +5047,12 @@
           <t>The override is never used, because two thirds of both chambers cannot be assembled against a president whose party holds a third of either one.</t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr">
+      <c r="F138" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="U138" s="4" t="inlineStr">
+      <c r="V138" s="4" t="inlineStr">
         <is>
           <t>The most likely outcome, and the deterrence rebuttal is real but unmeasurable.</t>
         </is>
@@ -4993,12 +5077,12 @@
           <t>Presidents shift to pre-emptive and blanket pardons issued on the last day, where an override vote arrives after the recipients have scattered.</t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
+      <c r="F139" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="U139" s="4" t="inlineStr">
+      <c r="V139" s="4" t="inlineStr">
         <is>
           <t>Predicts the adaptation, and names the drafting fix in its own rebuttal.</t>
         </is>
@@ -5023,7 +5107,7 @@
           <t>Pardons granted to the president's own circle become reviewable rather than final.</t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr">
+      <c r="F140" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
@@ -5048,7 +5132,7 @@
           <t>The prospect of a vote deters the grants that could not survive one.</t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr">
+      <c r="F141" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
@@ -5073,7 +5157,7 @@
           <t>Clemency decisions return to the Justice Department review process that screens petitions on the merits.</t>
         </is>
       </c>
-      <c r="E142" s="4" t="inlineStr">
+      <c r="F142" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
@@ -5098,7 +5182,7 @@
           <t>Unpopular but just clemency becomes harder, which is the case the power exists for.</t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr">
+      <c r="F143" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
@@ -5123,7 +5207,7 @@
           <t>Recipients cannot rely on a pardon, so it settles nothing until the override window closes.</t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr">
+      <c r="F144" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
@@ -5148,7 +5232,7 @@
           <t>Every controversial clemency decision becomes another partisan floor fight.</t>
         </is>
       </c>
-      <c r="E145" s="4" t="inlineStr">
+      <c r="F145" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
@@ -5173,12 +5257,12 @@
           <t>Some pardons are granted for the president's private benefit.</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
+      <c r="F146" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="U146" s="4" t="inlineStr">
+      <c r="V146" s="4" t="inlineStr">
         <is>
           <t>The pattern is documented and the characterization is inference. It is the firmest of the three components.</t>
         </is>
@@ -5203,12 +5287,12 @@
           <t>A congressional override would deter or reverse the grants at issue.</t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr">
+      <c r="F147" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="U147" s="4" t="inlineStr">
+      <c r="V147" s="4" t="inlineStr">
         <is>
           <t>The weakest load-bearing component on this page, and the one that caps it. The prediction table says why.</t>
         </is>
@@ -5233,12 +5317,12 @@
           <t>An override mechanism can be enacted.</t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr">
+      <c r="F148" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="U148" s="4" t="inlineStr">
+      <c r="V148" s="4" t="inlineStr">
         <is>
           <t>Argued down more effectively than the constitutional objection is usually argued, and not the component that caps this page.</t>
         </is>
@@ -5263,7 +5347,7 @@
           <t>Both sides agree that selling a pardon is a crime and that nobody currently checks whether one was sold.</t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr">
+      <c r="F149" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
@@ -5288,7 +5372,7 @@
           <t>Require the Pardon Attorney's file and the president's stated reasons to be published for every grant, and let Congress reverse a grant within sixty days by two-thirds vote, adopted as a constitutional amendment.</t>
         </is>
       </c>
-      <c r="E150" s="4" t="inlineStr">
+      <c r="F150" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
@@ -5313,7 +5397,7 @@
           <t>The pardon power should be abolished and replaced with a clemency commission whose decisions the president may only ratify.</t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr">
+      <c r="F151" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
@@ -5338,7 +5422,7 @@
           <t>A president should be barred from pardoning relatives, donors and co-defendants, with no general override.</t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr">
+      <c r="F152" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
@@ -5363,42 +5447,42 @@
           <t>Citizens need government decisions made on the merits rather than on what enriches the decider.</t>
         </is>
       </c>
-      <c r="E153" s="4" t="inlineStr">
+      <c r="F153" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="G153" s="4" t="inlineStr">
+      <c r="H153" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="K153" s="5" t="inlineStr">
+      <c r="L153" s="5" t="inlineStr">
         <is>
           <t>Fairness</t>
         </is>
       </c>
-      <c r="L153" s="4" t="inlineStr">
+      <c r="M153" s="4" t="inlineStr">
         <is>
           <t>Share of official decisions made by an official holding a personal financial stake in the outcome</t>
         </is>
       </c>
-      <c r="Q153" s="4" t="inlineStr">
+      <c r="R153" s="4" t="inlineStr">
         <is>
           <t>Falls after the rule takes effect</t>
         </is>
       </c>
-      <c r="R153" s="4" t="inlineStr">
+      <c r="S153" s="4" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="S153" s="4" t="inlineStr">
+      <c r="T153" s="4" t="inlineStr">
         <is>
           <t>Not measured systematically; 78 members of one Congress filed late transaction reports (Insider, 2023)</t>
         </is>
       </c>
-      <c r="U153" s="4" t="inlineStr">
+      <c r="V153" s="4" t="inlineStr">
         <is>
           <t>Near the top of any hierarchy of public needs, and contested only at the edges of its application.</t>
         </is>
@@ -5423,42 +5507,42 @@
           <t>Investors need markets where nobody trades on information the government has not released.</t>
         </is>
       </c>
-      <c r="E154" s="4" t="inlineStr">
+      <c r="F154" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="G154" s="4" t="inlineStr">
+      <c r="H154" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="K154" s="5" t="inlineStr">
+      <c r="L154" s="5" t="inlineStr">
         <is>
           <t>Free enterprise</t>
         </is>
       </c>
-      <c r="L154" s="4" t="inlineStr">
+      <c r="M154" s="4" t="inlineStr">
         <is>
           <t>Abnormal returns on officials' trades placed before government announcements</t>
         </is>
       </c>
-      <c r="Q154" s="4" t="inlineStr">
+      <c r="R154" s="4" t="inlineStr">
         <is>
           <t>Fall to zero</t>
         </is>
       </c>
-      <c r="R154" s="4" t="inlineStr">
+      <c r="S154" s="4" t="inlineStr">
         <is>
           <t>Persist at their current level</t>
         </is>
       </c>
-      <c r="S154" s="4" t="inlineStr">
+      <c r="T154" s="4" t="inlineStr">
         <is>
           <t>Mixed: 85 basis points a month for senators over 1993 to 1998 (Ziobrowski 2004); no advantage found over 2012 to 2020 (Belmont 2022); 3 to 5 percent before legislative events over 2014 to 2021 (Zhou 2025)</t>
         </is>
       </c>
-      <c r="U154" s="4" t="inlineStr">
+      <c r="V154" s="4" t="inlineStr">
         <is>
           <t>Valid and recognized; the disputed part is how much is actually at stake.</t>
         </is>
@@ -5483,42 +5567,42 @@
           <t>Voters need enough information to judge whether an official is compromised.</t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr">
+      <c r="F155" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="G155" s="4" t="inlineStr">
+      <c r="H155" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="K155" s="5" t="inlineStr">
+      <c r="L155" s="5" t="inlineStr">
         <is>
           <t>Accountability</t>
         </is>
       </c>
-      <c r="L155" s="4" t="inlineStr">
+      <c r="M155" s="4" t="inlineStr">
         <is>
           <t>Share of an official's income sources, debts and foreign ties visible in public filings</t>
         </is>
       </c>
-      <c r="Q155" s="4" t="inlineStr">
+      <c r="R155" s="4" t="inlineStr">
         <is>
           <t>Rises to near complete</t>
         </is>
       </c>
-      <c r="R155" s="4" t="inlineStr">
+      <c r="S155" s="4" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="S155" s="4" t="inlineStr">
+      <c r="T155" s="4" t="inlineStr">
         <is>
           <t>Assets and income are disclosed in broad ranges; foreign income, lender identity and effective tax rate are not (OGE Public Financial Disclosure Guide, 2024)</t>
         </is>
       </c>
-      <c r="U155" s="4" t="inlineStr">
+      <c r="V155" s="4" t="inlineStr">
         <is>
           <t>Strong as a need, contested in how far into a family it reaches.</t>
         </is>
@@ -5543,42 +5627,42 @@
           <t>Crime victims and the public need clemency decisions that can be reviewed rather than traded.</t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr">
+      <c r="F156" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="G156" s="4" t="inlineStr">
+      <c r="H156" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="K156" s="5" t="inlineStr">
+      <c r="L156" s="5" t="inlineStr">
         <is>
           <t>Rule of law</t>
         </is>
       </c>
-      <c r="L156" s="4" t="inlineStr">
+      <c r="M156" s="4" t="inlineStr">
         <is>
           <t>Share of clemency grants that went through the Justice Department review process</t>
         </is>
       </c>
-      <c r="Q156" s="4" t="inlineStr">
+      <c r="R156" s="4" t="inlineStr">
         <is>
           <t>Rises toward the historical norm</t>
         </is>
       </c>
-      <c r="R156" s="4" t="inlineStr">
+      <c r="S156" s="4" t="inlineStr">
         <is>
           <t>Stays at recent lows</t>
         </is>
       </c>
-      <c r="S156" s="4" t="inlineStr">
+      <c r="T156" s="4" t="inlineStr">
         <is>
           <t>About 93 percent of one administration's first-term grants bypassed the Pardon Attorney (Goldsmith and Gluck, 2020)</t>
         </is>
       </c>
-      <c r="U156" s="4" t="inlineStr">
+      <c r="V156" s="4" t="inlineStr">
         <is>
           <t>A real need with an unusually direct constitutional obstacle, which is argued on the belief page rather than here.</t>
         </is>
@@ -5603,42 +5687,42 @@
           <t>Officials need rules they can follow without a lawyer and without violating them by accident.</t>
         </is>
       </c>
-      <c r="E157" s="4" t="inlineStr">
+      <c r="F157" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="G157" s="4" t="inlineStr">
+      <c r="H157" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="K157" s="5" t="inlineStr">
+      <c r="L157" s="5" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="L157" s="4" t="inlineStr">
+      <c r="M157" s="4" t="inlineStr">
         <is>
           <t>Number of inadvertent reporting violations per year</t>
         </is>
       </c>
-      <c r="Q157" s="4" t="inlineStr">
+      <c r="R157" s="4" t="inlineStr">
         <is>
           <t>Falls toward zero</t>
         </is>
       </c>
-      <c r="R157" s="4" t="inlineStr">
+      <c r="S157" s="4" t="inlineStr">
         <is>
           <t>Stays at current levels</t>
         </is>
       </c>
-      <c r="S157" s="4" t="inlineStr">
+      <c r="T157" s="4" t="inlineStr">
         <is>
           <t>78 members of the 117th Congress filed late under the STOCK Act (Insider, 2023)</t>
         </is>
       </c>
-      <c r="U157" s="4" t="inlineStr">
+      <c r="V157" s="4" t="inlineStr">
         <is>
           <t>Valid and usually ignored, and it is the interest a bright-line ban serves best.</t>
         </is>
@@ -5663,42 +5747,42 @@
           <t>Officials and their families need the same property rights and privacy as other citizens.</t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr">
+      <c r="F158" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="G158" s="4" t="inlineStr">
+      <c r="H158" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="K158" s="5" t="inlineStr">
+      <c r="L158" s="5" t="inlineStr">
         <is>
           <t>Liberty</t>
         </is>
       </c>
-      <c r="L158" s="4" t="inlineStr">
+      <c r="M158" s="4" t="inlineStr">
         <is>
           <t>Whether a restriction reaches only the official or also family members who hold no office</t>
         </is>
       </c>
-      <c r="Q158" s="4" t="inlineStr">
+      <c r="R158" s="4" t="inlineStr">
         <is>
           <t>Restrictions stay narrow and are compensated</t>
         </is>
       </c>
-      <c r="R158" s="4" t="inlineStr">
+      <c r="S158" s="4" t="inlineStr">
         <is>
           <t>Restrictions extend to family and are not</t>
         </is>
       </c>
-      <c r="S158" s="4" t="inlineStr">
+      <c r="T158" s="4" t="inlineStr">
         <is>
           <t>Proposals vary: most reach the spouse and dependent children, and the Federal Reserve rule reaches immediate family</t>
         </is>
       </c>
-      <c r="U158" s="4" t="inlineStr">
+      <c r="V158" s="4" t="inlineStr">
         <is>
           <t>Valid in general, weakest exactly where it is invoked most: a voluntary office with known conditions.</t>
         </is>
@@ -5723,42 +5807,42 @@
           <t>The country needs capable people of ordinary means willing to serve, not only the wealthy and the indifferent.</t>
         </is>
       </c>
-      <c r="E159" s="4" t="inlineStr">
+      <c r="F159" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="G159" s="4" t="inlineStr">
+      <c r="H159" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="K159" s="5" t="inlineStr">
+      <c r="L159" s="5" t="inlineStr">
         <is>
           <t>Opportunity</t>
         </is>
       </c>
-      <c r="L159" s="4" t="inlineStr">
+      <c r="M159" s="4" t="inlineStr">
         <is>
           <t>Net worth distribution of candidates and of incoming members</t>
         </is>
       </c>
-      <c r="Q159" s="4" t="inlineStr">
+      <c r="R159" s="4" t="inlineStr">
         <is>
           <t>Unchanged or more representative after the rule</t>
         </is>
       </c>
-      <c r="R159" s="4" t="inlineStr">
+      <c r="S159" s="4" t="inlineStr">
         <is>
           <t>Shifts toward the already-wealthy</t>
         </is>
       </c>
-      <c r="S159" s="4" t="inlineStr">
+      <c r="T159" s="4" t="inlineStr">
         <is>
           <t>Congress is already far wealthier than the population it represents</t>
         </is>
       </c>
-      <c r="U159" s="4" t="inlineStr">
+      <c r="V159" s="4" t="inlineStr">
         <is>
           <t>A real need, and the evidence runs against the version of it used in this debate.</t>
         </is>
@@ -5783,42 +5867,42 @@
           <t>The president needs a clemency power the legislature cannot veto.</t>
         </is>
       </c>
-      <c r="E160" s="4" t="inlineStr">
+      <c r="F160" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="G160" s="4" t="inlineStr">
+      <c r="H160" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="K160" s="5" t="inlineStr">
+      <c r="L160" s="5" t="inlineStr">
         <is>
           <t>Rule of law</t>
         </is>
       </c>
-      <c r="L160" s="4" t="inlineStr">
+      <c r="M160" s="4" t="inlineStr">
         <is>
           <t>Whether unpopular but just clemency grants continue to be made</t>
         </is>
       </c>
-      <c r="Q160" s="4" t="inlineStr">
+      <c r="R160" s="4" t="inlineStr">
         <is>
           <t>They continue</t>
         </is>
       </c>
-      <c r="R160" s="4" t="inlineStr">
+      <c r="S160" s="4" t="inlineStr">
         <is>
           <t>They stop</t>
         </is>
       </c>
-      <c r="S160" s="4" t="inlineStr">
+      <c r="T160" s="4" t="inlineStr">
         <is>
           <t>Mass commutations of drug sentences were unpopular when granted and are now widely defended</t>
         </is>
       </c>
-      <c r="U160" s="4" t="inlineStr">
+      <c r="V160" s="4" t="inlineStr">
         <is>
           <t>Strong on the constitutional text, weaker as a claim that the current design is working.</t>
         </is>
@@ -5843,42 +5927,42 @@
           <t>Some officeholders want to keep using their position and their families to make money.</t>
         </is>
       </c>
-      <c r="E161" s="4" t="inlineStr">
+      <c r="F161" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="G161" s="4" t="inlineStr">
+      <c r="H161" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="K161" s="5" t="inlineStr">
+      <c r="L161" s="5" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="L161" s="4" t="inlineStr">
+      <c r="M161" s="4" t="inlineStr">
         <is>
           <t>Income officials and their relatives earn from activities that depend on the office</t>
         </is>
       </c>
-      <c r="Q161" s="4" t="inlineStr">
+      <c r="R161" s="4" t="inlineStr">
         <is>
           <t>Falls</t>
         </is>
       </c>
-      <c r="R161" s="4" t="inlineStr">
+      <c r="S161" s="4" t="inlineStr">
         <is>
           <t>Continues</t>
         </is>
       </c>
-      <c r="S161" s="4" t="inlineStr">
+      <c r="T161" s="4" t="inlineStr">
         <is>
           <t>Not measured directly; campaign committees paid $1.3 million in wages to candidates' relatives in one cycle (OpenSecrets, 2020)</t>
         </is>
       </c>
-      <c r="U161" s="4" t="inlineStr">
+      <c r="V161" s="4" t="inlineStr">
         <is>
           <t>Held by some and valid by almost no standard. It is on the page so that the scoring of a bad interest is visible rather than assumed.</t>
         </is>
@@ -5898,32 +5982,32 @@
           <t>driver</t>
         </is>
       </c>
-      <c r="E162" s="4" t="inlineStr">
+      <c r="F162" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F162" s="4" t="inlineStr">
+      <c r="G162" s="4" t="inlineStr">
         <is>
           <t>citizens-need-government-decisions</t>
         </is>
       </c>
-      <c r="G162" s="4" t="inlineStr">
+      <c r="H162" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I162" s="5" t="inlineStr">
+      <c r="J162" s="5" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="T162" s="4" t="inlineStr">
+      <c r="U162" s="4" t="inlineStr">
         <is>
           <t>Support that tracked partisan control rather than institutional distrust would point to a different driver.</t>
         </is>
       </c>
-      <c r="U162" s="4" t="inlineStr">
+      <c r="V162" s="4" t="inlineStr">
         <is>
           <t>Drives the position as strongly as any interest on the page, and the alternative explanation is hard to separate from it.</t>
         </is>
@@ -5943,32 +6027,32 @@
           <t>driver</t>
         </is>
       </c>
-      <c r="E163" s="4" t="inlineStr">
+      <c r="F163" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F163" s="4" t="inlineStr">
+      <c r="G163" s="4" t="inlineStr">
         <is>
           <t>investors-need-markets-where</t>
         </is>
       </c>
-      <c r="G163" s="4" t="inlineStr">
+      <c r="H163" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I163" s="5" t="inlineStr">
+      <c r="J163" s="5" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="T163" s="4" t="inlineStr">
+      <c r="U163" s="4" t="inlineStr">
         <is>
           <t>A coalition that kept its size with the market-integrity argument removed would show this interest is decorative.</t>
         </is>
       </c>
-      <c r="U163" s="4" t="inlineStr">
+      <c r="V163" s="4" t="inlineStr">
         <is>
           <t>Valid but largely decorative here: real interest, small share of what drives the position.</t>
         </is>
@@ -5988,32 +6072,32 @@
           <t>driver</t>
         </is>
       </c>
-      <c r="E164" s="4" t="inlineStr">
+      <c r="F164" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F164" s="4" t="inlineStr">
+      <c r="G164" s="4" t="inlineStr">
         <is>
           <t>voters-need-enough-information</t>
         </is>
       </c>
-      <c r="G164" s="4" t="inlineStr">
+      <c r="H164" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I164" s="5" t="inlineStr">
+      <c r="J164" s="5" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="T164" s="4" t="inlineStr">
+      <c r="U164" s="4" t="inlineStr">
         <is>
           <t>Whether transparency advocates would accept enforced disclosure instead of a ban is the test, and most say they would not.</t>
         </is>
       </c>
-      <c r="U164" s="4" t="inlineStr">
+      <c r="V164" s="4" t="inlineStr">
         <is>
           <t>A strong driver, and partly the same driver as the first interest on the page.</t>
         </is>
@@ -6033,32 +6117,32 @@
           <t>driver</t>
         </is>
       </c>
-      <c r="E165" s="4" t="inlineStr">
+      <c r="F165" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F165" s="4" t="inlineStr">
+      <c r="G165" s="4" t="inlineStr">
         <is>
           <t>officials-need-rules-can</t>
         </is>
       </c>
-      <c r="G165" s="4" t="inlineStr">
+      <c r="H165" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I165" s="5" t="inlineStr">
+      <c r="J165" s="5" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="T165" s="4" t="inlineStr">
+      <c r="U165" s="4" t="inlineStr">
         <is>
           <t>If officials who support a ban stopped doing so when preclearance was added, this interest would be shown to drive them.</t>
         </is>
       </c>
-      <c r="U165" s="4" t="inlineStr">
+      <c r="V165" s="4" t="inlineStr">
         <is>
           <t>A minor driver of the public position and a major one inside the institution.</t>
         </is>
@@ -6078,32 +6162,32 @@
           <t>driver</t>
         </is>
       </c>
-      <c r="E166" s="4" t="inlineStr">
+      <c r="F166" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F166" s="4" t="inlineStr">
+      <c r="G166" s="4" t="inlineStr">
         <is>
           <t>officials-families-need-same</t>
         </is>
       </c>
-      <c r="G166" s="4" t="inlineStr">
+      <c r="H166" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I166" s="5" t="inlineStr">
+      <c r="J166" s="5" t="inlineStr">
         <is>
           <t>Opposition</t>
         </is>
       </c>
-      <c r="T166" s="4" t="inlineStr">
+      <c r="U166" s="4" t="inlineStr">
         <is>
           <t>Opposition as strong among members with no individual holdings would point to principle rather than interest.</t>
         </is>
       </c>
-      <c r="U166" s="4" t="inlineStr">
+      <c r="V166" s="4" t="inlineStr">
         <is>
           <t>Stated first and predicts the position well, which is what a real driver looks like even when the stated principle is inconsistently applied.</t>
         </is>
@@ -6123,32 +6207,32 @@
           <t>driver</t>
         </is>
       </c>
-      <c r="E167" s="4" t="inlineStr">
+      <c r="F167" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F167" s="4" t="inlineStr">
+      <c r="G167" s="4" t="inlineStr">
         <is>
           <t>country-needs-capable-people</t>
         </is>
       </c>
-      <c r="G167" s="4" t="inlineStr">
+      <c r="H167" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I167" s="5" t="inlineStr">
+      <c r="J167" s="5" t="inlineStr">
         <is>
           <t>Opposition</t>
         </is>
       </c>
-      <c r="T167" s="4" t="inlineStr">
+      <c r="U167" s="4" t="inlineStr">
         <is>
           <t>Evidence that candidate recruitment fell in a jurisdiction after a holdings rule would show this interest drives the position.</t>
         </is>
       </c>
-      <c r="U167" s="4" t="inlineStr">
+      <c r="V167" s="4" t="inlineStr">
         <is>
           <t>Weak as a driver: asserted often, never demonstrated.</t>
         </is>
@@ -6168,32 +6252,32 @@
           <t>driver</t>
         </is>
       </c>
-      <c r="E168" s="4" t="inlineStr">
+      <c r="F168" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F168" s="4" t="inlineStr">
+      <c r="G168" s="4" t="inlineStr">
         <is>
           <t>some-officeholders-want-keep</t>
         </is>
       </c>
-      <c r="G168" s="4" t="inlineStr">
+      <c r="H168" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I168" s="5" t="inlineStr">
+      <c r="J168" s="5" t="inlineStr">
         <is>
           <t>Opposition</t>
         </is>
       </c>
-      <c r="T168" s="4" t="inlineStr">
+      <c r="U168" s="4" t="inlineStr">
         <is>
           <t>Opposition that was uncorrelated with trading volume would show this interest is not the driver.</t>
         </is>
       </c>
-      <c r="U168" s="4" t="inlineStr">
+      <c r="V168" s="4" t="inlineStr">
         <is>
           <t>Drives a small number of positions strongly, which is the shape the evidence supports and no more than that.</t>
         </is>
@@ -6213,32 +6297,32 @@
           <t>driver</t>
         </is>
       </c>
-      <c r="E169" s="4" t="inlineStr">
+      <c r="F169" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="F169" s="4" t="inlineStr">
+      <c r="G169" s="4" t="inlineStr">
         <is>
           <t>crime-victims-public-need</t>
         </is>
       </c>
-      <c r="G169" s="4" t="inlineStr">
+      <c r="H169" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="I169" s="5" t="inlineStr">
+      <c r="J169" s="5" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="T169" s="4" t="inlineStr">
+      <c r="U169" s="4" t="inlineStr">
         <is>
           <t>Support that stayed constant across changes of administration would show a stable interest rather than a partisan one.</t>
         </is>
       </c>
-      <c r="U169" s="4" t="inlineStr">
+      <c r="V169" s="4" t="inlineStr">
         <is>
           <t>Real, and the partisan tracking is strong enough that the driver page scores lower than the interest page does.</t>
         </is>
@@ -6258,32 +6342,32 @@
           <t>driver</t>
         </is>
       </c>
-      <c r="E170" s="4" t="inlineStr">
+      <c r="F170" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="F170" s="4" t="inlineStr">
+      <c r="G170" s="4" t="inlineStr">
         <is>
           <t>president-needs-clemency-power</t>
         </is>
       </c>
-      <c r="G170" s="4" t="inlineStr">
+      <c r="H170" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="I170" s="5" t="inlineStr">
+      <c r="J170" s="5" t="inlineStr">
         <is>
           <t>Opposition</t>
         </is>
       </c>
-      <c r="T170" s="4" t="inlineStr">
+      <c r="U170" s="4" t="inlineStr">
         <is>
           <t>Whether the same officials took this position under the other party's president is the test, and mostly they did not.</t>
         </is>
       </c>
-      <c r="U170" s="4" t="inlineStr">
+      <c r="V170" s="4" t="inlineStr">
         <is>
           <t>Genuinely principled among scholars and almost perfectly partisan among officials, which is why it scores where it does.</t>
         </is>
@@ -6303,37 +6387,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E171" s="4" t="inlineStr">
+      <c r="F171" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F171" s="4" t="inlineStr">
+      <c r="G171" s="4" t="inlineStr">
         <is>
           <t>members-regularly-trade-industries</t>
         </is>
       </c>
-      <c r="G171" s="4" t="inlineStr">
+      <c r="H171" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H171" s="5" t="inlineStr">
+      <c r="I171" s="5" t="inlineStr">
         <is>
           <t>Argument</t>
         </is>
       </c>
-      <c r="I171" s="5" t="inlineStr">
+      <c r="J171" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="T171" s="4" t="inlineStr">
+      <c r="U171" s="4" t="inlineStr">
         <is>
           <t>The overlap is the conflict the ban targets, so if it exists the ban has something to remove.</t>
         </is>
       </c>
-      <c r="U171" s="4" t="inlineStr">
+      <c r="V171" s="4" t="inlineStr">
         <is>
           <t>High linkage: the row and the belief are about the same thing.</t>
         </is>
@@ -6353,37 +6437,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E172" s="4" t="inlineStr">
+      <c r="F172" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F172" s="4" t="inlineStr">
+      <c r="G172" s="4" t="inlineStr">
         <is>
           <t>disclosure-has-failed-check</t>
         </is>
       </c>
-      <c r="G172" s="4" t="inlineStr">
+      <c r="H172" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H172" s="5" t="inlineStr">
+      <c r="I172" s="5" t="inlineStr">
         <is>
           <t>Argument</t>
         </is>
       </c>
-      <c r="I172" s="5" t="inlineStr">
+      <c r="J172" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="T172" s="4" t="inlineStr">
+      <c r="U172" s="4" t="inlineStr">
         <is>
           <t>A ban is only better than disclosure if disclosure is failing, which this row establishes and the rest of the tree has to complete.</t>
         </is>
       </c>
-      <c r="U172" s="4" t="inlineStr">
+      <c r="V172" s="4" t="inlineStr">
         <is>
           <t>Good linkage with a real gap: it rules out the alternative without establishing the proposal.</t>
         </is>
@@ -6403,37 +6487,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E173" s="4" t="inlineStr">
+      <c r="F173" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F173" s="4" t="inlineStr">
+      <c r="G173" s="4" t="inlineStr">
         <is>
           <t>holdings-ban-removes-conflict</t>
         </is>
       </c>
-      <c r="G173" s="4" t="inlineStr">
+      <c r="H173" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H173" s="5" t="inlineStr">
+      <c r="I173" s="5" t="inlineStr">
         <is>
           <t>Argument</t>
         </is>
       </c>
-      <c r="I173" s="5" t="inlineStr">
+      <c r="J173" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="T173" s="4" t="inlineStr">
+      <c r="U173" s="4" t="inlineStr">
         <is>
           <t>If the conflict is structural, a structural remedy reaches it and an intent-based one does not.</t>
         </is>
       </c>
-      <c r="U173" s="4" t="inlineStr">
+      <c r="V173" s="4" t="inlineStr">
         <is>
           <t>The most direct linkage on the page.</t>
         </is>
@@ -6453,37 +6537,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E174" s="4" t="inlineStr">
+      <c r="F174" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F174" s="4" t="inlineStr">
+      <c r="G174" s="4" t="inlineStr">
         <is>
           <t>federal-reserve-barred-its</t>
         </is>
       </c>
-      <c r="G174" s="4" t="inlineStr">
+      <c r="H174" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H174" s="5" t="inlineStr">
+      <c r="I174" s="5" t="inlineStr">
         <is>
           <t>Argument</t>
         </is>
       </c>
-      <c r="I174" s="5" t="inlineStr">
+      <c r="J174" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="T174" s="4" t="inlineStr">
+      <c r="U174" s="4" t="inlineStr">
         <is>
           <t>A comparable institution operating under the rule shows the rule is administrable, which is one of the belief's components.</t>
         </is>
       </c>
-      <c r="U174" s="4" t="inlineStr">
+      <c r="V174" s="4" t="inlineStr">
         <is>
           <t>Bears on feasibility rather than on effect, which is a real but narrower contribution.</t>
         </is>
@@ -6503,37 +6587,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E175" s="4" t="inlineStr">
+      <c r="F175" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F175" s="4" t="inlineStr">
+      <c r="G175" s="4" t="inlineStr">
         <is>
           <t>trading-closed-briefing-almost</t>
         </is>
       </c>
-      <c r="G175" s="4" t="inlineStr">
+      <c r="H175" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H175" s="5" t="inlineStr">
+      <c r="I175" s="5" t="inlineStr">
         <is>
           <t>Argument</t>
         </is>
       </c>
-      <c r="I175" s="5" t="inlineStr">
+      <c r="J175" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="T175" s="4" t="inlineStr">
+      <c r="U175" s="4" t="inlineStr">
         <is>
           <t>If the conduct cannot be prosecuted even when it occurs, the choice is between a status rule and nothing.</t>
         </is>
       </c>
-      <c r="U175" s="4" t="inlineStr">
+      <c r="V175" s="4" t="inlineStr">
         <is>
           <t>Strong linkage, and the rebuttal is the most important sentence on this page.</t>
         </is>
@@ -6553,37 +6637,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E176" s="4" t="inlineStr">
+      <c r="F176" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F176" s="4" t="inlineStr">
+      <c r="G176" s="4" t="inlineStr">
         <is>
           <t>best-identified-studies-actual</t>
         </is>
       </c>
-      <c r="G176" s="4" t="inlineStr">
+      <c r="H176" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H176" s="5" t="inlineStr">
+      <c r="I176" s="5" t="inlineStr">
         <is>
           <t>Argument</t>
         </is>
       </c>
-      <c r="I176" s="5" t="inlineStr">
+      <c r="J176" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="T176" s="4" t="inlineStr">
+      <c r="U176" s="4" t="inlineStr">
         <is>
           <t>Underperformance would weaken the trading-advantage branch of the tree and leave the voting-conflict branch untouched.</t>
         </is>
       </c>
-      <c r="U176" s="4" t="inlineStr">
+      <c r="V176" s="4" t="inlineStr">
         <is>
           <t>This is the page where the belief's two branches come apart, and the linkage score should show it.</t>
         </is>
@@ -6603,37 +6687,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E177" s="4" t="inlineStr">
+      <c r="F177" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F177" s="4" t="inlineStr">
+      <c r="G177" s="4" t="inlineStr">
         <is>
           <t>ban-official-leaves-conflict</t>
         </is>
       </c>
-      <c r="G177" s="4" t="inlineStr">
+      <c r="H177" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H177" s="5" t="inlineStr">
+      <c r="I177" s="5" t="inlineStr">
         <is>
           <t>Argument</t>
         </is>
       </c>
-      <c r="I177" s="5" t="inlineStr">
+      <c r="J177" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="T177" s="4" t="inlineStr">
+      <c r="U177" s="4" t="inlineStr">
         <is>
           <t>A ban only reduces conflicts if what it covers is not simply replaced by what it does not.</t>
         </is>
       </c>
-      <c r="U177" s="4" t="inlineStr">
+      <c r="V177" s="4" t="inlineStr">
         <is>
           <t>The highest-linkage argument on the disagree side: it strikes the load-bearing component directly.</t>
         </is>
@@ -6653,37 +6737,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E178" s="4" t="inlineStr">
+      <c r="F178" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F178" s="4" t="inlineStr">
+      <c r="G178" s="4" t="inlineStr">
         <is>
           <t>forced-divestiture-imposes-real</t>
         </is>
       </c>
-      <c r="G178" s="4" t="inlineStr">
+      <c r="H178" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H178" s="5" t="inlineStr">
+      <c r="I178" s="5" t="inlineStr">
         <is>
           <t>Argument</t>
         </is>
       </c>
-      <c r="I178" s="5" t="inlineStr">
+      <c r="J178" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="T178" s="4" t="inlineStr">
+      <c r="U178" s="4" t="inlineStr">
         <is>
           <t>Divestiture costs would weaken the belief only if they defeated the rule politically or changed who holds office.</t>
         </is>
       </c>
-      <c r="U178" s="4" t="inlineStr">
+      <c r="V178" s="4" t="inlineStr">
         <is>
           <t>Low linkage: a real cost aimed at the wrong question, and it counts fully in the cost-benefit table instead.</t>
         </is>
@@ -6703,37 +6787,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E179" s="4" t="inlineStr">
+      <c r="F179" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F179" s="4" t="inlineStr">
+      <c r="G179" s="4" t="inlineStr">
         <is>
           <t>congress-will-enforce-ban</t>
         </is>
       </c>
-      <c r="G179" s="4" t="inlineStr">
+      <c r="H179" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H179" s="5" t="inlineStr">
+      <c r="I179" s="5" t="inlineStr">
         <is>
           <t>Argument</t>
         </is>
       </c>
-      <c r="I179" s="5" t="inlineStr">
+      <c r="J179" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="T179" s="4" t="inlineStr">
+      <c r="U179" s="4" t="inlineStr">
         <is>
           <t>If Congress will not enforce it, the rule changes filings rather than conduct.</t>
         </is>
       </c>
-      <c r="U179" s="4" t="inlineStr">
+      <c r="V179" s="4" t="inlineStr">
         <is>
           <t>High linkage and the rebuttal is specific: the enforcement mechanism is not the same one that failed.</t>
         </is>
@@ -6753,37 +6837,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E180" s="4" t="inlineStr">
+      <c r="F180" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F180" s="4" t="inlineStr">
+      <c r="G180" s="4" t="inlineStr">
         <is>
           <t>senators-stock-purchases-beat</t>
         </is>
       </c>
-      <c r="G180" s="4" t="inlineStr">
+      <c r="H180" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H180" s="5" t="inlineStr">
+      <c r="I180" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="I180" s="5" t="inlineStr">
+      <c r="J180" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="T180" s="4" t="inlineStr">
+      <c r="U180" s="4" t="inlineStr">
         <is>
           <t>If senators earned abnormal returns, there was an advantage for a rule to remove, at least then.</t>
         </is>
       </c>
-      <c r="U180" s="4" t="inlineStr">
+      <c r="V180" s="4" t="inlineStr">
         <is>
           <t>Moderate linkage: right quantity, wrong era.</t>
         </is>
@@ -6803,37 +6887,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E181" s="4" t="inlineStr">
+      <c r="F181" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F181" s="4" t="inlineStr">
+      <c r="G181" s="4" t="inlineStr">
         <is>
           <t>trades-placed-before-legislative</t>
         </is>
       </c>
-      <c r="G181" s="4" t="inlineStr">
+      <c r="H181" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H181" s="5" t="inlineStr">
+      <c r="I181" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="I181" s="5" t="inlineStr">
+      <c r="J181" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="T181" s="4" t="inlineStr">
+      <c r="U181" s="4" t="inlineStr">
         <is>
           <t>Abnormal returns around legislative events is the conflict operating, measured in the current regime.</t>
         </is>
       </c>
-      <c r="U181" s="4" t="inlineStr">
+      <c r="V181" s="4" t="inlineStr">
         <is>
           <t>The highest-linkage evidence on the page, and the least replicated.</t>
         </is>
@@ -6853,37 +6937,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E182" s="4" t="inlineStr">
+      <c r="F182" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F182" s="4" t="inlineStr">
+      <c r="G182" s="4" t="inlineStr">
         <is>
           <t>78-members-117th-congress</t>
         </is>
       </c>
-      <c r="G182" s="4" t="inlineStr">
+      <c r="H182" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H182" s="5" t="inlineStr">
+      <c r="I182" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="I182" s="5" t="inlineStr">
+      <c r="J182" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="T182" s="4" t="inlineStr">
+      <c r="U182" s="4" t="inlineStr">
         <is>
           <t>Non-compliance bears on the belief only through the comparison between a ban and the disclosure regime it would replace.</t>
         </is>
       </c>
-      <c r="U182" s="4" t="inlineStr">
+      <c r="V182" s="4" t="inlineStr">
         <is>
           <t>Low linkage, cited constantly, and this page is where that gets priced.</t>
         </is>
@@ -6903,37 +6987,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E183" s="4" t="inlineStr">
+      <c r="F183" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F183" s="4" t="inlineStr">
+      <c r="G183" s="4" t="inlineStr">
         <is>
           <t>131-federal-judges-heard</t>
         </is>
       </c>
-      <c r="G183" s="4" t="inlineStr">
+      <c r="H183" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H183" s="5" t="inlineStr">
+      <c r="I183" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="I183" s="5" t="inlineStr">
+      <c r="J183" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="T183" s="4" t="inlineStr">
+      <c r="U183" s="4" t="inlineStr">
         <is>
           <t>If disclosure fails where a recusal duty backs it, it is unlikely to succeed where nothing does.</t>
         </is>
       </c>
-      <c r="U183" s="4" t="inlineStr">
+      <c r="V183" s="4" t="inlineStr">
         <is>
           <t>Moderate linkage through an analogy that has to carry real weight.</t>
         </is>
@@ -6953,37 +7037,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E184" s="4" t="inlineStr">
+      <c r="F184" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F184" s="4" t="inlineStr">
+      <c r="G184" s="4" t="inlineStr">
         <is>
           <t>federal-reserve-officials-have</t>
         </is>
       </c>
-      <c r="G184" s="4" t="inlineStr">
+      <c r="H184" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H184" s="5" t="inlineStr">
+      <c r="I184" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="I184" s="5" t="inlineStr">
+      <c r="J184" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="T184" s="4" t="inlineStr">
+      <c r="U184" s="4" t="inlineStr">
         <is>
           <t>A working example of the rule bears on whether the rule is workable, which is one component of the belief.</t>
         </is>
       </c>
-      <c r="U184" s="4" t="inlineStr">
+      <c r="V184" s="4" t="inlineStr">
         <is>
           <t>Bears on feasibility, and it substantially repeats the Fed argument above, which is what its uniqueness page is about.</t>
         </is>
@@ -7003,37 +7087,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E185" s="4" t="inlineStr">
+      <c r="F185" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F185" s="4" t="inlineStr">
+      <c r="G185" s="4" t="inlineStr">
         <is>
           <t>congressional-portfolios-underperformed-market</t>
         </is>
       </c>
-      <c r="G185" s="4" t="inlineStr">
+      <c r="H185" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H185" s="5" t="inlineStr">
+      <c r="I185" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="I185" s="5" t="inlineStr">
+      <c r="J185" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="T185" s="4" t="inlineStr">
+      <c r="U185" s="4" t="inlineStr">
         <is>
           <t>Underperformance weakens the trading branch of the belief and is silent on the voting branch.</t>
         </is>
       </c>
-      <c r="U185" s="4" t="inlineStr">
+      <c r="V185" s="4" t="inlineStr">
         <is>
           <t>Strong on its own branch, and the tree has two.</t>
         </is>
@@ -7053,37 +7137,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E186" s="4" t="inlineStr">
+      <c r="F186" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F186" s="4" t="inlineStr">
+      <c r="G186" s="4" t="inlineStr">
         <is>
           <t>no-evidence-members-congress</t>
         </is>
       </c>
-      <c r="G186" s="4" t="inlineStr">
+      <c r="H186" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H186" s="5" t="inlineStr">
+      <c r="I186" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="I186" s="5" t="inlineStr">
+      <c r="J186" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="T186" s="4" t="inlineStr">
+      <c r="U186" s="4" t="inlineStr">
         <is>
           <t>No post-reform advantage would mean the trading channel is already closed by the current rule.</t>
         </is>
       </c>
-      <c r="U186" s="4" t="inlineStr">
+      <c r="V186" s="4" t="inlineStr">
         <is>
           <t>The most relevant weakening evidence, and it reaches only one of the two branches.</t>
         </is>
@@ -7103,37 +7187,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E187" s="4" t="inlineStr">
+      <c r="F187" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F187" s="4" t="inlineStr">
+      <c r="G187" s="4" t="inlineStr">
         <is>
           <t>five-years-after-ban</t>
         </is>
       </c>
-      <c r="G187" s="4" t="inlineStr">
+      <c r="H187" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H187" s="5" t="inlineStr">
+      <c r="I187" s="5" t="inlineStr">
         <is>
           <t>Prediction</t>
         </is>
       </c>
-      <c r="I187" s="5" t="inlineStr">
+      <c r="J187" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="T187" s="4" t="inlineStr">
+      <c r="U187" s="4" t="inlineStr">
         <is>
           <t>Would this observation tell the two sides apart, or do both expect it?</t>
         </is>
       </c>
-      <c r="U187" s="4" t="inlineStr">
+      <c r="V187" s="4" t="inlineStr">
         <is>
           <t>Half diagnostic: the compliance half is expected by everyone, the scandal half is not.</t>
         </is>
@@ -7153,37 +7237,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E188" s="4" t="inlineStr">
+      <c r="F188" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F188" s="4" t="inlineStr">
+      <c r="G188" s="4" t="inlineStr">
         <is>
           <t>public-trust-congress-five</t>
         </is>
       </c>
-      <c r="G188" s="4" t="inlineStr">
+      <c r="H188" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H188" s="5" t="inlineStr">
+      <c r="I188" s="5" t="inlineStr">
         <is>
           <t>Prediction</t>
         </is>
       </c>
-      <c r="I188" s="5" t="inlineStr">
+      <c r="J188" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="T188" s="4" t="inlineStr">
+      <c r="U188" s="4" t="inlineStr">
         <is>
           <t>Would this observation tell the two sides apart, or do both expect it?</t>
         </is>
       </c>
-      <c r="U188" s="4" t="inlineStr">
+      <c r="V188" s="4" t="inlineStr">
         <is>
           <t>Weakly diagnostic, and this page is why its contribution to the belief is small.</t>
         </is>
@@ -7203,37 +7287,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E189" s="4" t="inlineStr">
+      <c r="F189" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F189" s="4" t="inlineStr">
+      <c r="G189" s="4" t="inlineStr">
         <is>
           <t>jurisdiction-adopts-holdings-ban</t>
         </is>
       </c>
-      <c r="G189" s="4" t="inlineStr">
+      <c r="H189" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H189" s="5" t="inlineStr">
+      <c r="I189" s="5" t="inlineStr">
         <is>
           <t>Prediction</t>
         </is>
       </c>
-      <c r="I189" s="5" t="inlineStr">
+      <c r="J189" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="T189" s="4" t="inlineStr">
+      <c r="U189" s="4" t="inlineStr">
         <is>
           <t>Would this observation tell the two sides apart, or do both expect it?</t>
         </is>
       </c>
-      <c r="U189" s="4" t="inlineStr">
+      <c r="V189" s="4" t="inlineStr">
         <is>
           <t>The most diagnostic prediction on the page and the only one nobody has attempted.</t>
         </is>
@@ -7253,37 +7337,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E190" s="4" t="inlineStr">
+      <c r="F190" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F190" s="4" t="inlineStr">
+      <c r="G190" s="4" t="inlineStr">
         <is>
           <t>reported-conflicts-migrate-spouse</t>
         </is>
       </c>
-      <c r="G190" s="4" t="inlineStr">
+      <c r="H190" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H190" s="5" t="inlineStr">
+      <c r="I190" s="5" t="inlineStr">
         <is>
           <t>Prediction</t>
         </is>
       </c>
-      <c r="I190" s="5" t="inlineStr">
+      <c r="J190" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="T190" s="4" t="inlineStr">
+      <c r="U190" s="4" t="inlineStr">
         <is>
           <t>Would this observation tell the two sides apart, or do both expect it?</t>
         </is>
       </c>
-      <c r="U190" s="4" t="inlineStr">
+      <c r="V190" s="4" t="inlineStr">
         <is>
           <t>High diagnosticity through a noisy instrument.</t>
         </is>
@@ -7303,37 +7387,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E191" s="4" t="inlineStr">
+      <c r="F191" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F191" s="4" t="inlineStr">
+      <c r="G191" s="4" t="inlineStr">
         <is>
           <t>share-incoming-members-whose</t>
         </is>
       </c>
-      <c r="G191" s="4" t="inlineStr">
+      <c r="H191" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H191" s="5" t="inlineStr">
+      <c r="I191" s="5" t="inlineStr">
         <is>
           <t>Prediction</t>
         </is>
       </c>
-      <c r="I191" s="5" t="inlineStr">
+      <c r="J191" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="T191" s="4" t="inlineStr">
+      <c r="U191" s="4" t="inlineStr">
         <is>
           <t>Would this observation tell the two sides apart, or do both expect it?</t>
         </is>
       </c>
-      <c r="U191" s="4" t="inlineStr">
+      <c r="V191" s="4" t="inlineStr">
         <is>
           <t>Low linkage to the belief and high relevance to the cost-benefit table, which is where it belongs.</t>
         </is>
@@ -7353,37 +7437,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E192" s="4" t="inlineStr">
+      <c r="F192" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F192" s="4" t="inlineStr">
+      <c r="G192" s="4" t="inlineStr">
         <is>
           <t>post-reform-studies-continue</t>
         </is>
       </c>
-      <c r="G192" s="4" t="inlineStr">
+      <c r="H192" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H192" s="5" t="inlineStr">
+      <c r="I192" s="5" t="inlineStr">
         <is>
           <t>Prediction</t>
         </is>
       </c>
-      <c r="I192" s="5" t="inlineStr">
+      <c r="J192" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="T192" s="4" t="inlineStr">
+      <c r="U192" s="4" t="inlineStr">
         <is>
           <t>Would this observation tell the two sides apart, or do both expect it?</t>
         </is>
       </c>
-      <c r="U192" s="4" t="inlineStr">
+      <c r="V192" s="4" t="inlineStr">
         <is>
           <t>Diagnostic for half the belief, which is what its score should reflect.</t>
         </is>
@@ -7403,37 +7487,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E193" s="4" t="inlineStr">
+      <c r="F193" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="F193" s="4" t="inlineStr">
+      <c r="G193" s="4" t="inlineStr">
         <is>
           <t>formal-appointment-what-brings</t>
         </is>
       </c>
-      <c r="G193" s="4" t="inlineStr">
+      <c r="H193" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="H193" s="5" t="inlineStr">
+      <c r="I193" s="5" t="inlineStr">
         <is>
           <t>Argument</t>
         </is>
       </c>
-      <c r="I193" s="5" t="inlineStr">
+      <c r="J193" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="T193" s="4" t="inlineStr">
+      <c r="U193" s="4" t="inlineStr">
         <is>
           <t>A bar that converts a disclosed adviser into an undisclosed one would make things worse rather than better.</t>
         </is>
       </c>
-      <c r="U193" s="4" t="inlineStr">
+      <c r="V193" s="4" t="inlineStr">
         <is>
           <t>The highest-linkage argument on that page.</t>
         </is>
@@ -7453,37 +7537,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E194" s="4" t="inlineStr">
+      <c r="F194" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="F194" s="4" t="inlineStr">
+      <c r="G194" s="4" t="inlineStr">
         <is>
           <t>problem-people-actually-point</t>
         </is>
       </c>
-      <c r="G194" s="4" t="inlineStr">
+      <c r="H194" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="H194" s="5" t="inlineStr">
+      <c r="I194" s="5" t="inlineStr">
         <is>
           <t>Argument</t>
         </is>
       </c>
-      <c r="I194" s="5" t="inlineStr">
+      <c r="J194" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="T194" s="4" t="inlineStr">
+      <c r="U194" s="4" t="inlineStr">
         <is>
           <t>A gap in coverage bears on the size of the effect, not on its direction.</t>
         </is>
       </c>
-      <c r="U194" s="4" t="inlineStr">
+      <c r="V194" s="4" t="inlineStr">
         <is>
           <t>Moderate linkage: a scope argument doing duty as a refutation.</t>
         </is>
@@ -7503,37 +7587,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E195" s="4" t="inlineStr">
+      <c r="F195" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="F195" s="4" t="inlineStr">
+      <c r="G195" s="4" t="inlineStr">
         <is>
           <t>return-shows-tax-positions</t>
         </is>
       </c>
-      <c r="G195" s="4" t="inlineStr">
+      <c r="H195" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="H195" s="5" t="inlineStr">
+      <c r="I195" s="5" t="inlineStr">
         <is>
           <t>Argument</t>
         </is>
       </c>
-      <c r="I195" s="5" t="inlineStr">
+      <c r="J195" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="T195" s="4" t="inlineStr">
+      <c r="U195" s="4" t="inlineStr">
         <is>
           <t>If the existing form shows what a return would show, publication adds nothing.</t>
         </is>
       </c>
-      <c r="U195" s="4" t="inlineStr">
+      <c r="V195" s="4" t="inlineStr">
         <is>
           <t>High linkage and directly checkable, which is unusual and good.</t>
         </is>
@@ -7553,37 +7637,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E196" s="4" t="inlineStr">
+      <c r="F196" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="F196" s="4" t="inlineStr">
+      <c r="G196" s="4" t="inlineStr">
         <is>
           <t>route-constitutionally-narrow-disclosure</t>
         </is>
       </c>
-      <c r="G196" s="4" t="inlineStr">
+      <c r="H196" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="H196" s="5" t="inlineStr">
+      <c r="I196" s="5" t="inlineStr">
         <is>
           <t>Argument</t>
         </is>
       </c>
-      <c r="I196" s="5" t="inlineStr">
+      <c r="J196" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="T196" s="4" t="inlineStr">
+      <c r="U196" s="4" t="inlineStr">
         <is>
           <t>A precedent about ballot access bears on a disclosure duty only if the two are the same kind of rule, and they are not.</t>
         </is>
       </c>
-      <c r="U196" s="4" t="inlineStr">
+      <c r="V196" s="4" t="inlineStr">
         <is>
           <t>Low linkage: the precedent is cited far beyond what it holds, and this page is where that is priced.</t>
         </is>
@@ -7603,37 +7687,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E197" s="4" t="inlineStr">
+      <c r="F197" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="F197" s="4" t="inlineStr">
+      <c r="G197" s="4" t="inlineStr">
         <is>
           <t>article-ii-grants-power</t>
         </is>
       </c>
-      <c r="G197" s="4" t="inlineStr">
+      <c r="H197" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="H197" s="5" t="inlineStr">
+      <c r="I197" s="5" t="inlineStr">
         <is>
           <t>Argument</t>
         </is>
       </c>
-      <c r="I197" s="5" t="inlineStr">
+      <c r="J197" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="T197" s="4" t="inlineStr">
+      <c r="U197" s="4" t="inlineStr">
         <is>
           <t>The cases foreclose a statute; the belief as written does not require one.</t>
         </is>
       </c>
-      <c r="U197" s="4" t="inlineStr">
+      <c r="V197" s="4" t="inlineStr">
         <is>
           <t>The most-cited argument on that page, and nobody has opened this linkage page to argue it either way, so it still reads the presumption that a reason placed under a conclusion is relevant.</t>
         </is>
@@ -7653,37 +7737,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E198" s="4" t="inlineStr">
+      <c r="F198" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="F198" s="4" t="inlineStr">
+      <c r="G198" s="4" t="inlineStr">
         <is>
           <t>proposals-let-congress-nullify</t>
         </is>
       </c>
-      <c r="G198" s="4" t="inlineStr">
+      <c r="H198" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="H198" s="5" t="inlineStr">
+      <c r="I198" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="I198" s="5" t="inlineStr">
+      <c r="J198" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="T198" s="4" t="inlineStr">
+      <c r="U198" s="4" t="inlineStr">
         <is>
           <t>Failure to advance bears on feasibility, and the belief is about effect.</t>
         </is>
       </c>
-      <c r="U198" s="4" t="inlineStr">
+      <c r="V198" s="4" t="inlineStr">
         <is>
           <t>Very low linkage, and it is the clearest example in this workbook of a true fact aimed at the wrong claim.</t>
         </is>
@@ -7703,37 +7787,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E199" s="4" t="inlineStr">
+      <c r="F199" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="F199" s="4" t="inlineStr">
+      <c r="G199" s="4" t="inlineStr">
         <is>
           <t>most-states-already-put</t>
         </is>
       </c>
-      <c r="G199" s="4" t="inlineStr">
+      <c r="H199" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="H199" s="5" t="inlineStr">
+      <c r="I199" s="5" t="inlineStr">
         <is>
           <t>Argument</t>
         </is>
       </c>
-      <c r="I199" s="5" t="inlineStr">
+      <c r="J199" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="T199" s="4" t="inlineStr">
+      <c r="U199" s="4" t="inlineStr">
         <is>
           <t>State practice shows a check is compatible with a functioning clemency power, but not this check.</t>
         </is>
       </c>
-      <c r="U199" s="4" t="inlineStr">
+      <c r="V199" s="4" t="inlineStr">
         <is>
           <t>Real evidence for the general proposition and weak evidence for the specific proposal.</t>
         </is>
@@ -7753,37 +7837,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E200" s="4" t="inlineStr">
+      <c r="F200" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F200" s="4" t="inlineStr">
+      <c r="G200" s="4" t="inlineStr">
         <is>
           <t>78-members-117th-congress</t>
         </is>
       </c>
-      <c r="G200" s="4" t="inlineStr">
+      <c r="H200" s="4" t="inlineStr">
         <is>
           <t>investors-need-markets-where</t>
         </is>
       </c>
-      <c r="H200" s="5" t="inlineStr">
+      <c r="I200" s="5" t="inlineStr">
         <is>
           <t>Interest</t>
         </is>
       </c>
-      <c r="I200" s="5" t="inlineStr">
+      <c r="J200" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="T200" s="4" t="inlineStr">
+      <c r="U200" s="4" t="inlineStr">
         <is>
           <t>The filing deadline exists for the market-integrity interest, but a violation of it does not show that interest was harmed.</t>
         </is>
       </c>
-      <c r="U200" s="4" t="inlineStr">
+      <c r="V200" s="4" t="inlineStr">
         <is>
           <t>Bearing: how far the row is really about this interest.</t>
         </is>
@@ -7803,37 +7887,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E201" s="4" t="inlineStr">
+      <c r="F201" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F201" s="4" t="inlineStr">
+      <c r="G201" s="4" t="inlineStr">
         <is>
           <t>forced-divestiture-imposes-real</t>
         </is>
       </c>
-      <c r="G201" s="4" t="inlineStr">
+      <c r="H201" s="4" t="inlineStr">
         <is>
           <t>country-needs-capable-people</t>
         </is>
       </c>
-      <c r="H201" s="5" t="inlineStr">
+      <c r="I201" s="5" t="inlineStr">
         <is>
           <t>Interest</t>
         </is>
       </c>
-      <c r="I201" s="5" t="inlineStr">
+      <c r="J201" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="T201" s="4" t="inlineStr">
+      <c r="U201" s="4" t="inlineStr">
         <is>
           <t>Cost to sitting officials and deterrence of future candidates are related but not the same quantity.</t>
         </is>
       </c>
-      <c r="U201" s="4" t="inlineStr">
+      <c r="V201" s="4" t="inlineStr">
         <is>
           <t>Bearing: how far the row is really about this interest.</t>
         </is>
@@ -7853,27 +7937,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E202" s="4" t="inlineStr">
+      <c r="F202" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F202" s="4" t="inlineStr">
+      <c r="G202" s="4" t="inlineStr">
         <is>
           <t>members-regularly-trade-industries</t>
         </is>
       </c>
-      <c r="G202" s="4" t="inlineStr">
+      <c r="H202" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J202" s="4" t="inlineStr">
+      <c r="K202" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="T202" s="4" t="inlineStr">
+      <c r="U202" s="4" t="inlineStr">
         <is>
           <t>Citizens whose decisions are made by someone holding a stake, and investors on the other side of the trades.</t>
         </is>
@@ -7893,27 +7977,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E203" s="4" t="inlineStr">
+      <c r="F203" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F203" s="4" t="inlineStr">
+      <c r="G203" s="4" t="inlineStr">
         <is>
           <t>disclosure-has-failed-check</t>
         </is>
       </c>
-      <c r="G203" s="4" t="inlineStr">
+      <c r="H203" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J203" s="4" t="inlineStr">
+      <c r="K203" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="T203" s="4" t="inlineStr">
+      <c r="U203" s="4" t="inlineStr">
         <is>
           <t>Voters, who cannot tell a compromised official from a clean one, and officials living under a rule nobody enforces.</t>
         </is>
@@ -7933,27 +8017,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E204" s="4" t="inlineStr">
+      <c r="F204" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F204" s="4" t="inlineStr">
+      <c r="G204" s="4" t="inlineStr">
         <is>
           <t>holdings-ban-removes-conflict</t>
         </is>
       </c>
-      <c r="G204" s="4" t="inlineStr">
+      <c r="H204" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J204" s="4" t="inlineStr">
+      <c r="K204" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="T204" s="4" t="inlineStr">
+      <c r="U204" s="4" t="inlineStr">
         <is>
           <t>Everyone who needs decisions made on the merits, and officials who want a rule they can actually follow.</t>
         </is>
@@ -7973,27 +8057,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E205" s="4" t="inlineStr">
+      <c r="F205" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F205" s="4" t="inlineStr">
+      <c r="G205" s="4" t="inlineStr">
         <is>
           <t>federal-reserve-barred-its</t>
         </is>
       </c>
-      <c r="G205" s="4" t="inlineStr">
+      <c r="H205" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J205" s="4" t="inlineStr">
+      <c r="K205" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="T205" s="4" t="inlineStr">
+      <c r="U205" s="4" t="inlineStr">
         <is>
           <t>Officials, who would live under the rule, and anyone worried it makes service impossible.</t>
         </is>
@@ -8013,27 +8097,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E206" s="4" t="inlineStr">
+      <c r="F206" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F206" s="4" t="inlineStr">
+      <c r="G206" s="4" t="inlineStr">
         <is>
           <t>trading-closed-briefing-almost</t>
         </is>
       </c>
-      <c r="G206" s="4" t="inlineStr">
+      <c r="H206" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J206" s="4" t="inlineStr">
+      <c r="K206" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="T206" s="4" t="inlineStr">
+      <c r="U206" s="4" t="inlineStr">
         <is>
           <t>Citizens and investors, who currently rely on a rule that cannot be enforced.</t>
         </is>
@@ -8053,27 +8137,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E207" s="4" t="inlineStr">
+      <c r="F207" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F207" s="4" t="inlineStr">
+      <c r="G207" s="4" t="inlineStr">
         <is>
           <t>best-identified-studies-actual</t>
         </is>
       </c>
-      <c r="G207" s="4" t="inlineStr">
+      <c r="H207" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J207" s="4" t="inlineStr">
+      <c r="K207" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="T207" s="4" t="inlineStr">
+      <c r="U207" s="4" t="inlineStr">
         <is>
           <t>Investors, if there turns out to be no advantage being taken.</t>
         </is>
@@ -8093,27 +8177,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E208" s="4" t="inlineStr">
+      <c r="F208" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F208" s="4" t="inlineStr">
+      <c r="G208" s="4" t="inlineStr">
         <is>
           <t>ban-official-leaves-conflict</t>
         </is>
       </c>
-      <c r="G208" s="4" t="inlineStr">
+      <c r="H208" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J208" s="4" t="inlineStr">
+      <c r="K208" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="T208" s="4" t="inlineStr">
+      <c r="U208" s="4" t="inlineStr">
         <is>
           <t>Citizens, if the conflict moves instead of ending, and voters, who would see less of it.</t>
         </is>
@@ -8133,27 +8217,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E209" s="4" t="inlineStr">
+      <c r="F209" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F209" s="4" t="inlineStr">
+      <c r="G209" s="4" t="inlineStr">
         <is>
           <t>forced-divestiture-imposes-real</t>
         </is>
       </c>
-      <c r="G209" s="4" t="inlineStr">
+      <c r="H209" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J209" s="4" t="inlineStr">
+      <c r="K209" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="T209" s="4" t="inlineStr">
+      <c r="U209" s="4" t="inlineStr">
         <is>
           <t>People of ordinary means considering office, and officials asked to sell on someone else's schedule.</t>
         </is>
@@ -8173,27 +8257,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E210" s="4" t="inlineStr">
+      <c r="F210" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F210" s="4" t="inlineStr">
+      <c r="G210" s="4" t="inlineStr">
         <is>
           <t>members-keep-property-rights</t>
         </is>
       </c>
-      <c r="G210" s="4" t="inlineStr">
+      <c r="H210" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J210" s="4" t="inlineStr">
+      <c r="K210" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="T210" s="4" t="inlineStr">
+      <c r="U210" s="4" t="inlineStr">
         <is>
           <t>Officials and their families, whose ordinary rights the rule restricts.</t>
         </is>
@@ -8213,27 +8297,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E211" s="4" t="inlineStr">
+      <c r="F211" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F211" s="4" t="inlineStr">
+      <c r="G211" s="4" t="inlineStr">
         <is>
           <t>congress-will-enforce-ban</t>
         </is>
       </c>
-      <c r="G211" s="4" t="inlineStr">
+      <c r="H211" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J211" s="4" t="inlineStr">
+      <c r="K211" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="T211" s="4" t="inlineStr">
+      <c r="U211" s="4" t="inlineStr">
         <is>
           <t>Citizens, if the rule is a symbol, and officials, who would carry its burden for nothing.</t>
         </is>
@@ -8253,27 +8337,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E212" s="4" t="inlineStr">
+      <c r="F212" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F212" s="4" t="inlineStr">
+      <c r="G212" s="4" t="inlineStr">
         <is>
           <t>senators-stock-purchases-beat</t>
         </is>
       </c>
-      <c r="G212" s="4" t="inlineStr">
+      <c r="H212" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J212" s="4" t="inlineStr">
+      <c r="K212" s="4" t="inlineStr">
         <is>
           <t>supporting finding</t>
         </is>
       </c>
-      <c r="T212" s="4" t="inlineStr">
+      <c r="U212" s="4" t="inlineStr">
         <is>
           <t>Investors trading against officials during the period studied.</t>
         </is>
@@ -8293,27 +8377,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E213" s="4" t="inlineStr">
+      <c r="F213" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F213" s="4" t="inlineStr">
+      <c r="G213" s="4" t="inlineStr">
         <is>
           <t>trades-placed-before-legislative</t>
         </is>
       </c>
-      <c r="G213" s="4" t="inlineStr">
+      <c r="H213" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J213" s="4" t="inlineStr">
+      <c r="K213" s="4" t="inlineStr">
         <is>
           <t>supporting finding</t>
         </is>
       </c>
-      <c r="T213" s="4" t="inlineStr">
+      <c r="U213" s="4" t="inlineStr">
         <is>
           <t>Investors on the other side of trades placed before legislative events.</t>
         </is>
@@ -8333,27 +8417,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E214" s="4" t="inlineStr">
+      <c r="F214" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F214" s="4" t="inlineStr">
+      <c r="G214" s="4" t="inlineStr">
         <is>
           <t>78-members-117th-congress</t>
         </is>
       </c>
-      <c r="G214" s="4" t="inlineStr">
+      <c r="H214" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J214" s="4" t="inlineStr">
+      <c r="K214" s="4" t="inlineStr">
         <is>
           <t>supporting finding</t>
         </is>
       </c>
-      <c r="T214" s="4" t="inlineStr">
+      <c r="U214" s="4" t="inlineStr">
         <is>
           <t>Investors relying on a disclosure regime, and officials living under a rule that is widely missed.</t>
         </is>
@@ -8373,27 +8457,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E215" s="4" t="inlineStr">
+      <c r="F215" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F215" s="4" t="inlineStr">
+      <c r="G215" s="4" t="inlineStr">
         <is>
           <t>131-federal-judges-heard</t>
         </is>
       </c>
-      <c r="G215" s="4" t="inlineStr">
+      <c r="H215" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J215" s="4" t="inlineStr">
+      <c r="K215" s="4" t="inlineStr">
         <is>
           <t>supporting finding</t>
         </is>
       </c>
-      <c r="T215" s="4" t="inlineStr">
+      <c r="U215" s="4" t="inlineStr">
         <is>
           <t>Litigants and voters relying on disclosure to reveal a decision-maker's stake.</t>
         </is>
@@ -8413,27 +8497,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E216" s="4" t="inlineStr">
+      <c r="F216" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F216" s="4" t="inlineStr">
+      <c r="G216" s="4" t="inlineStr">
         <is>
           <t>federal-reserve-officials-have</t>
         </is>
       </c>
-      <c r="G216" s="4" t="inlineStr">
+      <c r="H216" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J216" s="4" t="inlineStr">
+      <c r="K216" s="4" t="inlineStr">
         <is>
           <t>supporting finding</t>
         </is>
       </c>
-      <c r="T216" s="4" t="inlineStr">
+      <c r="U216" s="4" t="inlineStr">
         <is>
           <t>Officials under the rule, and anyone concerned it deters qualified people.</t>
         </is>
@@ -8453,27 +8537,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E217" s="4" t="inlineStr">
+      <c r="F217" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F217" s="4" t="inlineStr">
+      <c r="G217" s="4" t="inlineStr">
         <is>
           <t>congressional-portfolios-underperformed-market</t>
         </is>
       </c>
-      <c r="G217" s="4" t="inlineStr">
+      <c r="H217" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J217" s="4" t="inlineStr">
+      <c r="K217" s="4" t="inlineStr">
         <is>
           <t>weakening finding</t>
         </is>
       </c>
-      <c r="T217" s="4" t="inlineStr">
+      <c r="U217" s="4" t="inlineStr">
         <is>
           <t>Investors, if there is no advantage to remove.</t>
         </is>
@@ -8493,27 +8577,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E218" s="4" t="inlineStr">
+      <c r="F218" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F218" s="4" t="inlineStr">
+      <c r="G218" s="4" t="inlineStr">
         <is>
           <t>no-evidence-members-congress</t>
         </is>
       </c>
-      <c r="G218" s="4" t="inlineStr">
+      <c r="H218" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J218" s="4" t="inlineStr">
+      <c r="K218" s="4" t="inlineStr">
         <is>
           <t>weakening finding</t>
         </is>
       </c>
-      <c r="T218" s="4" t="inlineStr">
+      <c r="U218" s="4" t="inlineStr">
         <is>
           <t>Investors in the post-reform period.</t>
         </is>
@@ -8533,27 +8617,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E219" s="4" t="inlineStr">
+      <c r="F219" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F219" s="4" t="inlineStr">
+      <c r="G219" s="4" t="inlineStr">
         <is>
           <t>five-years-after-ban</t>
         </is>
       </c>
-      <c r="G219" s="4" t="inlineStr">
+      <c r="H219" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J219" s="4" t="inlineStr">
+      <c r="K219" s="4" t="inlineStr">
         <is>
           <t>prediction if the belief is true</t>
         </is>
       </c>
-      <c r="T219" s="4" t="inlineStr">
+      <c r="U219" s="4" t="inlineStr">
         <is>
           <t>Citizens, whose officials would no longer hold the stakes.</t>
         </is>
@@ -8573,27 +8657,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E220" s="4" t="inlineStr">
+      <c r="F220" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F220" s="4" t="inlineStr">
+      <c r="G220" s="4" t="inlineStr">
         <is>
           <t>public-trust-congress-five</t>
         </is>
       </c>
-      <c r="G220" s="4" t="inlineStr">
+      <c r="H220" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J220" s="4" t="inlineStr">
+      <c r="K220" s="4" t="inlineStr">
         <is>
           <t>prediction if the belief is true</t>
         </is>
       </c>
-      <c r="T220" s="4" t="inlineStr">
+      <c r="U220" s="4" t="inlineStr">
         <is>
           <t>Voters, whose confidence is the thing being measured.</t>
         </is>
@@ -8613,27 +8697,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E221" s="4" t="inlineStr">
+      <c r="F221" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F221" s="4" t="inlineStr">
+      <c r="G221" s="4" t="inlineStr">
         <is>
           <t>jurisdiction-adopts-holdings-ban</t>
         </is>
       </c>
-      <c r="G221" s="4" t="inlineStr">
+      <c r="H221" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J221" s="4" t="inlineStr">
+      <c r="K221" s="4" t="inlineStr">
         <is>
           <t>prediction if the belief is true</t>
         </is>
       </c>
-      <c r="T221" s="4" t="inlineStr">
+      <c r="U221" s="4" t="inlineStr">
         <is>
           <t>Citizens, whose votes would be cast without the stake.</t>
         </is>
@@ -8653,27 +8737,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E222" s="4" t="inlineStr">
+      <c r="F222" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F222" s="4" t="inlineStr">
+      <c r="G222" s="4" t="inlineStr">
         <is>
           <t>reported-conflicts-migrate-spouse</t>
         </is>
       </c>
-      <c r="G222" s="4" t="inlineStr">
+      <c r="H222" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J222" s="4" t="inlineStr">
+      <c r="K222" s="4" t="inlineStr">
         <is>
           <t>prediction if the belief is false</t>
         </is>
       </c>
-      <c r="T222" s="4" t="inlineStr">
+      <c r="U222" s="4" t="inlineStr">
         <is>
           <t>Citizens, if the conflict persists out of view.</t>
         </is>
@@ -8693,27 +8777,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E223" s="4" t="inlineStr">
+      <c r="F223" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F223" s="4" t="inlineStr">
+      <c r="G223" s="4" t="inlineStr">
         <is>
           <t>share-incoming-members-whose</t>
         </is>
       </c>
-      <c r="G223" s="4" t="inlineStr">
+      <c r="H223" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J223" s="4" t="inlineStr">
+      <c r="K223" s="4" t="inlineStr">
         <is>
           <t>prediction if the belief is false</t>
         </is>
       </c>
-      <c r="T223" s="4" t="inlineStr">
+      <c r="U223" s="4" t="inlineStr">
         <is>
           <t>People of ordinary means who might otherwise run.</t>
         </is>
@@ -8733,27 +8817,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E224" s="4" t="inlineStr">
+      <c r="F224" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F224" s="4" t="inlineStr">
+      <c r="G224" s="4" t="inlineStr">
         <is>
           <t>post-reform-studies-continue</t>
         </is>
       </c>
-      <c r="G224" s="4" t="inlineStr">
+      <c r="H224" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J224" s="4" t="inlineStr">
+      <c r="K224" s="4" t="inlineStr">
         <is>
           <t>prediction if the belief is false</t>
         </is>
       </c>
-      <c r="T224" s="4" t="inlineStr">
+      <c r="U224" s="4" t="inlineStr">
         <is>
           <t>Investors, if the advantage was already gone.</t>
         </is>
@@ -8773,27 +8857,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E225" s="4" t="inlineStr">
+      <c r="F225" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="F225" s="4" t="inlineStr">
+      <c r="G225" s="4" t="inlineStr">
         <is>
           <t>anti-nepotism-statute-stops</t>
         </is>
       </c>
-      <c r="G225" s="4" t="inlineStr">
+      <c r="H225" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="J225" s="4" t="inlineStr">
+      <c r="K225" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="T225" s="4" t="inlineStr">
+      <c r="U225" s="4" t="inlineStr">
         <is>
           <t>Citizens, whose decisions are made by someone outside the rule that covers everyone else.</t>
         </is>
@@ -8813,27 +8897,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E226" s="4" t="inlineStr">
+      <c r="F226" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="F226" s="4" t="inlineStr">
+      <c r="G226" s="4" t="inlineStr">
         <is>
           <t>relative-cannot-supervised-disciplined</t>
         </is>
       </c>
-      <c r="G226" s="4" t="inlineStr">
+      <c r="H226" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="J226" s="4" t="inlineStr">
+      <c r="K226" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="T226" s="4" t="inlineStr">
+      <c r="U226" s="4" t="inlineStr">
         <is>
           <t>Citizens relying on an ordinary chain of command to check official conduct.</t>
         </is>
@@ -8853,27 +8937,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E227" s="4" t="inlineStr">
+      <c r="F227" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="F227" s="4" t="inlineStr">
+      <c r="G227" s="4" t="inlineStr">
         <is>
           <t>official-role-gives-family</t>
         </is>
       </c>
-      <c r="G227" s="4" t="inlineStr">
+      <c r="H227" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="J227" s="4" t="inlineStr">
+      <c r="K227" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="T227" s="4" t="inlineStr">
+      <c r="U227" s="4" t="inlineStr">
         <is>
           <t>Citizens, and voters who cannot see what the channel carries.</t>
         </is>
@@ -8893,27 +8977,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E228" s="4" t="inlineStr">
+      <c r="F228" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="F228" s="4" t="inlineStr">
+      <c r="G228" s="4" t="inlineStr">
         <is>
           <t>rule-already-applies-every</t>
         </is>
       </c>
-      <c r="G228" s="4" t="inlineStr">
+      <c r="H228" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="J228" s="4" t="inlineStr">
+      <c r="K228" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="T228" s="4" t="inlineStr">
+      <c r="U228" s="4" t="inlineStr">
         <is>
           <t>Officials, who would face one rule instead of two.</t>
         </is>
@@ -8933,27 +9017,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E229" s="4" t="inlineStr">
+      <c r="F229" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="F229" s="4" t="inlineStr">
+      <c r="G229" s="4" t="inlineStr">
         <is>
           <t>formal-appointment-what-brings</t>
         </is>
       </c>
-      <c r="G229" s="4" t="inlineStr">
+      <c r="H229" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="J229" s="4" t="inlineStr">
+      <c r="K229" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="T229" s="4" t="inlineStr">
+      <c r="U229" s="4" t="inlineStr">
         <is>
           <t>Voters, who would lose the disclosure that appointment triggers.</t>
         </is>
@@ -8973,27 +9057,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E230" s="4" t="inlineStr">
+      <c r="F230" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="F230" s="4" t="inlineStr">
+      <c r="G230" s="4" t="inlineStr">
         <is>
           <t>problem-people-actually-point</t>
         </is>
       </c>
-      <c r="G230" s="4" t="inlineStr">
+      <c r="H230" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="J230" s="4" t="inlineStr">
+      <c r="K230" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="T230" s="4" t="inlineStr">
+      <c r="U230" s="4" t="inlineStr">
         <is>
           <t>Relatives making money from the name, which the rule does not reach.</t>
         </is>
@@ -9013,27 +9097,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E231" s="4" t="inlineStr">
+      <c r="F231" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="F231" s="4" t="inlineStr">
+      <c r="G231" s="4" t="inlineStr">
         <is>
           <t>president-entitled-advisers-he</t>
         </is>
       </c>
-      <c r="G231" s="4" t="inlineStr">
+      <c r="H231" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="J231" s="4" t="inlineStr">
+      <c r="K231" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="T231" s="4" t="inlineStr">
+      <c r="U231" s="4" t="inlineStr">
         <is>
           <t>A president restricted in whom he may consult.</t>
         </is>
@@ -9053,27 +9137,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E232" s="4" t="inlineStr">
+      <c r="F232" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="F232" s="4" t="inlineStr">
+      <c r="G232" s="4" t="inlineStr">
         <is>
           <t>competence-neither-inherited-nor</t>
         </is>
       </c>
-      <c r="G232" s="4" t="inlineStr">
+      <c r="H232" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="J232" s="4" t="inlineStr">
+      <c r="K232" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="T232" s="4" t="inlineStr">
+      <c r="U232" s="4" t="inlineStr">
         <is>
           <t>Qualified people excluded for a relationship.</t>
         </is>
@@ -9093,27 +9177,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E233" s="4" t="inlineStr">
+      <c r="F233" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="F233" s="4" t="inlineStr">
+      <c r="G233" s="4" t="inlineStr">
         <is>
           <t>return-shows-what-financial</t>
         </is>
       </c>
-      <c r="G233" s="4" t="inlineStr">
+      <c r="H233" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="J233" s="4" t="inlineStr">
+      <c r="K233" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="T233" s="4" t="inlineStr">
+      <c r="U233" s="4" t="inlineStr">
         <is>
           <t>Voters, who currently see ranges instead of figures.</t>
         </is>
@@ -9133,27 +9217,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E234" s="4" t="inlineStr">
+      <c r="F234" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="F234" s="4" t="inlineStr">
+      <c r="G234" s="4" t="inlineStr">
         <is>
           <t>internal-check-failed-one</t>
         </is>
       </c>
-      <c r="G234" s="4" t="inlineStr">
+      <c r="H234" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="J234" s="4" t="inlineStr">
+      <c r="K234" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="T234" s="4" t="inlineStr">
+      <c r="U234" s="4" t="inlineStr">
         <is>
           <t>Citizens relying on an audit that did not happen.</t>
         </is>
@@ -9173,27 +9257,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E235" s="4" t="inlineStr">
+      <c r="F235" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="F235" s="4" t="inlineStr">
+      <c r="G235" s="4" t="inlineStr">
         <is>
           <t>every-president-carter-through</t>
         </is>
       </c>
-      <c r="G235" s="4" t="inlineStr">
+      <c r="H235" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="J235" s="4" t="inlineStr">
+      <c r="K235" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="T235" s="4" t="inlineStr">
+      <c r="U235" s="4" t="inlineStr">
         <is>
           <t>Voters, who had the information for forty years and then did not.</t>
         </is>
@@ -9213,27 +9297,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E236" s="4" t="inlineStr">
+      <c r="F236" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="F236" s="4" t="inlineStr">
+      <c r="G236" s="4" t="inlineStr">
         <is>
           <t>published-return-can-checked</t>
         </is>
       </c>
-      <c r="G236" s="4" t="inlineStr">
+      <c r="H236" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="J236" s="4" t="inlineStr">
+      <c r="K236" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="T236" s="4" t="inlineStr">
+      <c r="U236" s="4" t="inlineStr">
         <is>
           <t>Voters, who can check a published document without waiting for an agency.</t>
         </is>
@@ -9253,27 +9337,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E237" s="4" t="inlineStr">
+      <c r="F237" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="F237" s="4" t="inlineStr">
+      <c r="G237" s="4" t="inlineStr">
         <is>
           <t>return-shows-tax-positions</t>
         </is>
       </c>
-      <c r="G237" s="4" t="inlineStr">
+      <c r="H237" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="J237" s="4" t="inlineStr">
+      <c r="K237" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="T237" s="4" t="inlineStr">
+      <c r="U237" s="4" t="inlineStr">
         <is>
           <t>Voters, if the existing form already tells them what they need.</t>
         </is>
@@ -9293,27 +9377,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E238" s="4" t="inlineStr">
+      <c r="F238" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="F238" s="4" t="inlineStr">
+      <c r="G238" s="4" t="inlineStr">
         <is>
           <t>publication-exposes-spouses-children</t>
         </is>
       </c>
-      <c r="G238" s="4" t="inlineStr">
+      <c r="H238" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="J238" s="4" t="inlineStr">
+      <c r="K238" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="T238" s="4" t="inlineStr">
+      <c r="U238" s="4" t="inlineStr">
         <is>
           <t>Spouses, children and partners who hold no office.</t>
         </is>
@@ -9333,27 +9417,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E239" s="4" t="inlineStr">
+      <c r="F239" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="F239" s="4" t="inlineStr">
+      <c r="G239" s="4" t="inlineStr">
         <is>
           <t>route-constitutionally-narrow-disclosure</t>
         </is>
       </c>
-      <c r="G239" s="4" t="inlineStr">
+      <c r="H239" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="J239" s="4" t="inlineStr">
+      <c r="K239" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="T239" s="4" t="inlineStr">
+      <c r="U239" s="4" t="inlineStr">
         <is>
           <t>Officials facing a rule that would be litigated rather than obeyed.</t>
         </is>
@@ -9373,27 +9457,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E240" s="4" t="inlineStr">
+      <c r="F240" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="F240" s="4" t="inlineStr">
+      <c r="G240" s="4" t="inlineStr">
         <is>
           <t>sophisticated-wealth-sits-pass</t>
         </is>
       </c>
-      <c r="G240" s="4" t="inlineStr">
+      <c r="H240" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="J240" s="4" t="inlineStr">
+      <c r="K240" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="T240" s="4" t="inlineStr">
+      <c r="U240" s="4" t="inlineStr">
         <is>
           <t>Voters, who would see a document that shows little.</t>
         </is>
@@ -9413,27 +9497,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E241" s="4" t="inlineStr">
+      <c r="F241" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="F241" s="4" t="inlineStr">
+      <c r="G241" s="4" t="inlineStr">
         <is>
           <t>clemency-only-executive-power</t>
         </is>
       </c>
-      <c r="G241" s="4" t="inlineStr">
+      <c r="H241" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="J241" s="4" t="inlineStr">
+      <c r="K241" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="T241" s="4" t="inlineStr">
+      <c r="U241" s="4" t="inlineStr">
         <is>
           <t>Victims and the public, for whom nothing reviews a grant.</t>
         </is>
@@ -9453,27 +9537,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E242" s="4" t="inlineStr">
+      <c r="F242" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="F242" s="4" t="inlineStr">
+      <c r="G242" s="4" t="inlineStr">
         <is>
           <t>pardons-granted-president-s</t>
         </is>
       </c>
-      <c r="G242" s="4" t="inlineStr">
+      <c r="H242" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="J242" s="4" t="inlineStr">
+      <c r="K242" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="T242" s="4" t="inlineStr">
+      <c r="U242" s="4" t="inlineStr">
         <is>
           <t>Victims of the underlying offenses, and citizens watching the power used on the president's circle.</t>
         </is>
@@ -9493,27 +9577,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E243" s="4" t="inlineStr">
+      <c r="F243" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="F243" s="4" t="inlineStr">
+      <c r="G243" s="4" t="inlineStr">
         <is>
           <t>two-thirds-threshold-means</t>
         </is>
       </c>
-      <c r="G243" s="4" t="inlineStr">
+      <c r="H243" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="J243" s="4" t="inlineStr">
+      <c r="K243" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="T243" s="4" t="inlineStr">
+      <c r="U243" s="4" t="inlineStr">
         <is>
           <t>A president whose unpopular but just grants would survive a two-thirds test.</t>
         </is>
@@ -9533,27 +9617,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E244" s="4" t="inlineStr">
+      <c r="F244" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="F244" s="4" t="inlineStr">
+      <c r="G244" s="4" t="inlineStr">
         <is>
           <t>most-states-already-put</t>
         </is>
       </c>
-      <c r="G244" s="4" t="inlineStr">
+      <c r="H244" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="J244" s="4" t="inlineStr">
+      <c r="K244" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="T244" s="4" t="inlineStr">
+      <c r="U244" s="4" t="inlineStr">
         <is>
           <t>The public in states where clemency already carries a check.</t>
         </is>
@@ -9573,27 +9657,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E245" s="4" t="inlineStr">
+      <c r="F245" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="F245" s="4" t="inlineStr">
+      <c r="G245" s="4" t="inlineStr">
         <is>
           <t>article-ii-grants-power</t>
         </is>
       </c>
-      <c r="G245" s="4" t="inlineStr">
+      <c r="H245" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="J245" s="4" t="inlineStr">
+      <c r="K245" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="T245" s="4" t="inlineStr">
+      <c r="U245" s="4" t="inlineStr">
         <is>
           <t>A president whose constitutional power would be narrowed.</t>
         </is>
@@ -9613,27 +9697,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E246" s="4" t="inlineStr">
+      <c r="F246" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="F246" s="4" t="inlineStr">
+      <c r="G246" s="4" t="inlineStr">
         <is>
           <t>clemency-exists-correct-injustices</t>
         </is>
       </c>
-      <c r="G246" s="4" t="inlineStr">
+      <c r="H246" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="J246" s="4" t="inlineStr">
+      <c r="K246" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="T246" s="4" t="inlineStr">
+      <c r="U246" s="4" t="inlineStr">
         <is>
           <t>People whom only an unpopular act of mercy can reach.</t>
         </is>
@@ -9653,27 +9737,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E247" s="4" t="inlineStr">
+      <c r="F247" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="F247" s="4" t="inlineStr">
+      <c r="G247" s="4" t="inlineStr">
         <is>
           <t>reversible-pardon-pardon-nobody</t>
         </is>
       </c>
-      <c r="G247" s="4" t="inlineStr">
+      <c r="H247" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="J247" s="4" t="inlineStr">
+      <c r="K247" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="T247" s="4" t="inlineStr">
+      <c r="U247" s="4" t="inlineStr">
         <is>
           <t>Recipients who could not rely on a grant.</t>
         </is>
@@ -9693,27 +9777,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E248" s="4" t="inlineStr">
+      <c r="F248" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="F248" s="4" t="inlineStr">
+      <c r="G248" s="4" t="inlineStr">
         <is>
           <t>narrower-fix-reaches-actual</t>
         </is>
       </c>
-      <c r="G248" s="4" t="inlineStr">
+      <c r="H248" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="J248" s="4" t="inlineStr">
+      <c r="K248" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="T248" s="4" t="inlineStr">
+      <c r="U248" s="4" t="inlineStr">
         <is>
           <t>The same public interest, served by a smaller change.</t>
         </is>
@@ -9733,27 +9817,27 @@
           <t>uniqueness</t>
         </is>
       </c>
-      <c r="E249" s="4" t="inlineStr">
+      <c r="F249" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F249" s="4" t="inlineStr">
+      <c r="G249" s="4" t="inlineStr">
         <is>
           <t>federal-reserve-officials-have</t>
         </is>
       </c>
-      <c r="G249" s="4" t="inlineStr">
+      <c r="H249" s="4" t="inlineStr">
         <is>
           <t>federal-reserve-barred-its</t>
         </is>
       </c>
-      <c r="T249" s="4" t="inlineStr">
+      <c r="U249" s="4" t="inlineStr">
         <is>
           <t>The finding adds the rule's scope and dates; the argument adds the claim that the institution kept working.</t>
         </is>
       </c>
-      <c r="U249" s="4" t="inlineStr">
+      <c r="V249" s="4" t="inlineStr">
         <is>
           <t>Largely redundant: the finding keeps a minority of its weight, which is the discount working as intended.</t>
         </is>
@@ -9773,27 +9857,27 @@
           <t>uniqueness</t>
         </is>
       </c>
-      <c r="E250" s="4" t="inlineStr">
+      <c r="F250" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F250" s="4" t="inlineStr">
+      <c r="G250" s="4" t="inlineStr">
         <is>
           <t>congress-will-enforce-ban</t>
         </is>
       </c>
-      <c r="G250" s="4" t="inlineStr">
+      <c r="H250" s="4" t="inlineStr">
         <is>
           <t>ban-official-leaves-conflict</t>
         </is>
       </c>
-      <c r="T250" s="4" t="inlineStr">
+      <c r="U250" s="4" t="inlineStr">
         <is>
           <t>Substitution is about what the rule covers; non-enforcement is about whether what it covers is policed.</t>
         </is>
       </c>
-      <c r="U250" s="4" t="inlineStr">
+      <c r="V250" s="4" t="inlineStr">
         <is>
           <t>Distinct: they fail in different ways and would be refuted by different evidence.</t>
         </is>
@@ -9813,27 +9897,27 @@
           <t>equivalence</t>
         </is>
       </c>
-      <c r="E251" s="4" t="inlineStr">
+      <c r="F251" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F251" s="4" t="inlineStr">
+      <c r="G251" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G251" s="4" t="inlineStr">
+      <c r="H251" s="4" t="inlineStr">
         <is>
           <t>members-congress-barred-owning</t>
         </is>
       </c>
-      <c r="T251" s="4" t="inlineStr">
+      <c r="U251" s="4" t="inlineStr">
         <is>
           <t>The broader version reaches every asset class rather than publicly traded shares.</t>
         </is>
       </c>
-      <c r="U251" s="4" t="inlineStr">
+      <c r="V251" s="4" t="inlineStr">
         <is>
           <t>Same direction, different policy. Keep both pages and cross-link them.</t>
         </is>
@@ -9853,27 +9937,27 @@
           <t>equivalence</t>
         </is>
       </c>
-      <c r="E252" s="4" t="inlineStr">
+      <c r="F252" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F252" s="4" t="inlineStr">
+      <c r="G252" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G252" s="4" t="inlineStr">
+      <c r="H252" s="4" t="inlineStr">
         <is>
           <t>members-congress-required-place</t>
         </is>
       </c>
-      <c r="T252" s="4" t="inlineStr">
+      <c r="U252" s="4" t="inlineStr">
         <is>
           <t>A blind trust removes control and keeps ownership; a ban removes ownership.</t>
         </is>
       </c>
-      <c r="U252" s="4" t="inlineStr">
+      <c r="V252" s="4" t="inlineStr">
         <is>
           <t>Overlapping rather than equivalent: keep both pages and name the difference on each.</t>
         </is>
@@ -9893,27 +9977,27 @@
           <t>equivalence</t>
         </is>
       </c>
-      <c r="E253" s="4" t="inlineStr">
+      <c r="F253" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="F253" s="4" t="inlineStr">
+      <c r="G253" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="G253" s="4" t="inlineStr">
+      <c r="H253" s="4" t="inlineStr">
         <is>
           <t>president-barred-pardoning-relatives</t>
         </is>
       </c>
-      <c r="T253" s="4" t="inlineStr">
+      <c r="U253" s="4" t="inlineStr">
         <is>
           <t>One restricts who may be pardoned; the other lets Congress undo any grant.</t>
         </is>
       </c>
-      <c r="U253" s="4" t="inlineStr">
+      <c r="V253" s="4" t="inlineStr">
         <is>
           <t>Distinct mechanisms aimed at overlapping cases. Both need an amendment.</t>
         </is>
@@ -9938,32 +10022,32 @@
           <t>Ziobrowski, Cheng, Boyd and Ziobrowski, Abnormal Returns from the Common Stock Investments of the U.S. Senate (2004)</t>
         </is>
       </c>
-      <c r="E254" s="4" t="inlineStr">
+      <c r="F254" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G254" s="4" t="inlineStr">
+      <c r="H254" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H254" s="5" t="inlineStr">
+      <c r="I254" s="5" t="inlineStr">
         <is>
           <t>Study</t>
         </is>
       </c>
-      <c r="M254" s="4" t="inlineStr">
+      <c r="N254" s="4" t="inlineStr">
         <is>
           <t>Journal of Financial and Quantitative Analysis 39(4), 661 to 676</t>
         </is>
       </c>
-      <c r="T254" s="4" t="inlineStr">
+      <c r="U254" s="4" t="inlineStr">
         <is>
           <t>Senators earned abnormal returns on their stock purchases in the 1990s.</t>
         </is>
       </c>
-      <c r="U254" s="4" t="inlineStr">
+      <c r="V254" s="4" t="inlineStr">
         <is>
           <t>The foundational study for the trading-advantage argument, and its period is now a generation old.</t>
         </is>
@@ -9988,32 +10072,32 @@
           <t>Insider, Conflicted Congress (2021 to 2023)</t>
         </is>
       </c>
-      <c r="E255" s="4" t="inlineStr">
+      <c r="F255" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G255" s="4" t="inlineStr">
+      <c r="H255" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H255" s="5" t="inlineStr">
+      <c r="I255" s="5" t="inlineStr">
         <is>
           <t>Report</t>
         </is>
       </c>
-      <c r="M255" s="4" t="inlineStr">
+      <c r="N255" s="4" t="inlineStr">
         <is>
           <t>Insider investigative series, tally updated January 2023</t>
         </is>
       </c>
-      <c r="T255" s="4" t="inlineStr">
+      <c r="U255" s="4" t="inlineStr">
         <is>
           <t>Members of Congress violate the existing disclosure rule routinely and without consequence.</t>
         </is>
       </c>
-      <c r="U255" s="4" t="inlineStr">
+      <c r="V255" s="4" t="inlineStr">
         <is>
           <t>Accurate as a count and routinely oversold as a measure of misconduct.</t>
         </is>
@@ -10038,32 +10122,32 @@
           <t>Eggers and Hainmueller, Capitol Losses: The Mediocre Performance of Congressional Stock Portfolios (2013)</t>
         </is>
       </c>
-      <c r="E256" s="4" t="inlineStr">
+      <c r="F256" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G256" s="4" t="inlineStr">
+      <c r="H256" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H256" s="5" t="inlineStr">
+      <c r="I256" s="5" t="inlineStr">
         <is>
           <t>Study</t>
         </is>
       </c>
-      <c r="M256" s="4" t="inlineStr">
+      <c r="N256" s="4" t="inlineStr">
         <is>
           <t>Journal of Politics 75(2)</t>
         </is>
       </c>
-      <c r="T256" s="4" t="inlineStr">
+      <c r="U256" s="4" t="inlineStr">
         <is>
           <t>Congressional portfolios did not beat the market.</t>
         </is>
       </c>
-      <c r="U256" s="4" t="inlineStr">
+      <c r="V256" s="4" t="inlineStr">
         <is>
           <t>The most careful study on the skeptical side, and the tail-versus-average objection is unresolved.</t>
         </is>
@@ -10083,37 +10167,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E257" s="4" t="inlineStr">
+      <c r="F257" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F257" s="4" t="inlineStr">
+      <c r="G257" s="4" t="inlineStr">
         <is>
           <t>ziobrowski-cheng-boyd-ziobrowski</t>
         </is>
       </c>
-      <c r="G257" s="4" t="inlineStr">
+      <c r="H257" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H257" s="5" t="inlineStr">
+      <c r="I257" s="5" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="I257" s="5" t="inlineStr">
+      <c r="J257" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="T257" s="4" t="inlineStr">
+      <c r="U257" s="4" t="inlineStr">
         <is>
           <t>The work speaks to the trading branch of the belief and not to the voting branch.</t>
         </is>
       </c>
-      <c r="U257" s="4" t="inlineStr">
+      <c r="V257" s="4" t="inlineStr">
         <is>
           <t>Bears on one of the belief's two branches.</t>
         </is>
@@ -10133,37 +10217,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E258" s="4" t="inlineStr">
+      <c r="F258" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F258" s="4" t="inlineStr">
+      <c r="G258" s="4" t="inlineStr">
         <is>
           <t>insider-conflicted-congress-2021</t>
         </is>
       </c>
-      <c r="G258" s="4" t="inlineStr">
+      <c r="H258" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H258" s="5" t="inlineStr">
+      <c r="I258" s="5" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="I258" s="5" t="inlineStr">
+      <c r="J258" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="T258" s="4" t="inlineStr">
+      <c r="U258" s="4" t="inlineStr">
         <is>
           <t>The work speaks to the trading branch of the belief and not to the voting branch.</t>
         </is>
       </c>
-      <c r="U258" s="4" t="inlineStr">
+      <c r="V258" s="4" t="inlineStr">
         <is>
           <t>Bears on one of the belief's two branches.</t>
         </is>
@@ -10183,37 +10267,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="E259" s="4" t="inlineStr">
+      <c r="F259" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F259" s="4" t="inlineStr">
+      <c r="G259" s="4" t="inlineStr">
         <is>
           <t>eggers-hainmueller-capitol-losses</t>
         </is>
       </c>
-      <c r="G259" s="4" t="inlineStr">
+      <c r="H259" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H259" s="5" t="inlineStr">
+      <c r="I259" s="5" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="I259" s="5" t="inlineStr">
+      <c r="J259" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="T259" s="4" t="inlineStr">
+      <c r="U259" s="4" t="inlineStr">
         <is>
           <t>The work speaks to the trading branch of the belief and not to the voting branch.</t>
         </is>
       </c>
-      <c r="U259" s="4" t="inlineStr">
+      <c r="V259" s="4" t="inlineStr">
         <is>
           <t>Bears on one of the belief's two branches.</t>
         </is>
@@ -10233,27 +10317,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E260" s="4" t="inlineStr">
+      <c r="F260" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F260" s="4" t="inlineStr">
+      <c r="G260" s="4" t="inlineStr">
         <is>
           <t>ziobrowski-cheng-boyd-ziobrowski</t>
         </is>
       </c>
-      <c r="G260" s="4" t="inlineStr">
+      <c r="H260" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J260" s="4" t="inlineStr">
+      <c r="K260" s="4" t="inlineStr">
         <is>
           <t>work</t>
         </is>
       </c>
-      <c r="T260" s="4" t="inlineStr">
+      <c r="U260" s="4" t="inlineStr">
         <is>
           <t>Investors on the other side of the trades the study measures.</t>
         </is>
@@ -10273,27 +10357,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E261" s="4" t="inlineStr">
+      <c r="F261" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F261" s="4" t="inlineStr">
+      <c r="G261" s="4" t="inlineStr">
         <is>
           <t>insider-conflicted-congress-2021</t>
         </is>
       </c>
-      <c r="G261" s="4" t="inlineStr">
+      <c r="H261" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J261" s="4" t="inlineStr">
+      <c r="K261" s="4" t="inlineStr">
         <is>
           <t>work</t>
         </is>
       </c>
-      <c r="T261" s="4" t="inlineStr">
+      <c r="U261" s="4" t="inlineStr">
         <is>
           <t>Voters relying on disclosure, and officials living under the rule being violated.</t>
         </is>
@@ -10313,45 +10397,45 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="E262" s="4" t="inlineStr">
+      <c r="F262" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="F262" s="4" t="inlineStr">
+      <c r="G262" s="4" t="inlineStr">
         <is>
           <t>eggers-hainmueller-capitol-losses</t>
         </is>
       </c>
-      <c r="G262" s="4" t="inlineStr">
+      <c r="H262" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J262" s="4" t="inlineStr">
+      <c r="K262" s="4" t="inlineStr">
         <is>
           <t>work</t>
         </is>
       </c>
-      <c r="T262" s="4" t="inlineStr">
+      <c r="U262" s="4" t="inlineStr">
         <is>
           <t>Investors, if the advantage the belief assumes is not there.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W262"/>
+  <autoFilter ref="A1:X262"/>
   <dataValidations count="4">
     <dataValidation sqref="C2:C5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"belief,claim,linkage,importance,interest,uniqueness,equivalence,driver,media"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Argument,Evidence,Prediction,Interest,Media,Book,Study,Article,Report,Film,Podcast,Video"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Supports,Weakens,Support,Opposition"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"analogy,anecdote,artifact,expert_claim,expert_data,eyewitness,historical,intuition,logic,meta,news,norm,observational,rct,record,statistics,survey,visual"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10387,6 +10471,8 @@
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="40" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/tools/static-site/ISE_Data_Entry.xlsx
+++ b/tools/static-site/ISE_Data_Entry.xlsx
@@ -10,10 +10,12 @@
     <sheet name="how to use" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="pages" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="edges" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="topics" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'pages'!$A$1:$X$262</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'pages'!$A$1:$Z$262</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'edges'!$A$1:$T$885</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'topics'!$A$1:$E$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -190,95 +192,105 @@
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>The page this one is used on.</t>
+        <t>belief: the key of the topic page this belief is filed under (a row in the topics sheet). Pages beneath the belief inherit it.</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
-        <t>For a formula-built page: the row it is about.</t>
+        <t>The page this one is used on.</t>
       </text>
     </comment>
     <comment ref="H1" authorId="0" shapeId="0">
       <text>
-        <t>For a formula-built page: the page that row is under.</t>
+        <t>For a formula-built page: the row it is about.</t>
       </text>
     </comment>
     <comment ref="I1" authorId="0" shapeId="0">
       <text>
-        <t>linkage: Argument, Evidence, Prediction, Interest or Media. media: Book, Study, Article, Report, Film, Podcast, Video.</t>
+        <t>For a formula-built page: the page that row is under.</t>
       </text>
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
-        <t>linkage: Supports or Weakens. driver: Support or Opposition.</t>
+        <t>linkage: Argument, Evidence, Prediction, Interest or Media. media: Book, Study, Article, Report, Film, Podcast, Video.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>importance: what kind of row this page scores.</t>
+        <t>linkage: Supports or Weakens. driver: Support or Opposition.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
       <text>
-        <t>interest: the value it appeals to.</t>
+        <t>importance: what kind of row this page scores.</t>
       </text>
     </comment>
     <comment ref="M1" authorId="0" shapeId="0">
       <text>
-        <t>interest: what a reading of it looks like.</t>
+        <t>interest: the value it appeals to.</t>
       </text>
     </comment>
     <comment ref="N1" authorId="0" shapeId="0">
       <text>
-        <t>media: where to find the work.</t>
+        <t>interest: what a reading of it looks like.</t>
       </text>
     </comment>
     <comment ref="O1" authorId="0" shapeId="0">
       <text>
-        <t>What this claim rests on, if it is an observed finding: statistics, record, rct, meta, observational, historical, expert_data, expert_claim, anecdote, logic, analogy, norm, intuition, news, survey, eyewitness, visual, artifact. Blank means nothing observed, and the claim starts at a coin flip. Classify what the sentence asserts, not the instrument: "58 percent told a pollster X" is statistics; "Americans believe X" is survey.</t>
+        <t>media: where to find the work.</t>
       </text>
     </comment>
     <comment ref="P1" authorId="0" shapeId="0">
       <text>
-        <t>Independent replications of this finding. Blank counts as one, the finding itself.</t>
+        <t>What this claim rests on, if it is an observed finding: statistics, record, rct, meta, observational, historical, expert_data, expert_claim, anecdote, logic, analogy, norm, intuition, news, survey, eyewitness, visual, artifact. Blank means nothing observed, and the claim starts at a coin flip. Classify what the sentence asserts, not the instrument: "58 percent told a pollster X" is statistics; "Americans believe X" is survey.</t>
       </text>
     </comment>
     <comment ref="Q1" authorId="0" shapeId="0">
       <text>
-        <t>Percent of those replications that agreed. Blank counts as 100. At 50 the claim starts at a coin flip whatever its source type, because a contested literature has established nothing.</t>
+        <t>Independent replications of this finding. Blank counts as one, the finding itself.</t>
       </text>
     </comment>
     <comment ref="R1" authorId="0" shapeId="0">
       <text>
-        <t>interest: what the measure shows if the belief is true.</t>
+        <t>Percent of those replications that agreed. Blank counts as 100. At 50 the claim starts at a coin flip whatever its source type, because a contested literature has established nothing.</t>
       </text>
     </comment>
     <comment ref="S1" authorId="0" shapeId="0">
       <text>
-        <t>interest: what it shows if the belief is false.</t>
+        <t>interest: what the measure shows if the belief is true.</t>
       </text>
     </comment>
     <comment ref="T1" authorId="0" shapeId="0">
       <text>
-        <t>interest: the latest reading, with source.</t>
+        <t>interest: what it shows if the belief is false.</t>
       </text>
     </comment>
     <comment ref="U1" authorId="0" shapeId="0">
       <text>
-        <t>The one-sentence answer in the check table.</t>
+        <t>interest: the latest reading, with source.</t>
       </text>
     </comment>
     <comment ref="V1" authorId="0" shapeId="0">
       <text>
-        <t>The one typed line in the scorecard.</t>
+        <t>The one-sentence answer in the check table.</t>
       </text>
     </comment>
     <comment ref="W1" authorId="0" shapeId="0">
       <text>
+        <t>The one typed line in the scorecard.</t>
+      </text>
+    </comment>
+    <comment ref="X1" authorId="0" shapeId="0">
+      <text>
         <t>belief: -100 to +100 on the topic page.</t>
       </text>
     </comment>
-    <comment ref="X1" authorId="0" shapeId="0">
+    <comment ref="Y1" authorId="0" shapeId="0">
+      <text>
+        <t>belief: how absolute the claim is, as a label. Modest (hedged), Moderate (definite but bounded), Strong (near-universal) or Total (no exceptions). Typed, never scored: it places the belief on the topic page and nothing reads it as a number.</t>
+      </text>
+    </comment>
+    <comment ref="Z1" authorId="0" shapeId="0">
       <text>
         <t>belief: the logical form of the claim.</t>
       </text>
@@ -391,6 +403,41 @@
     <comment ref="T1" authorId="0" shapeId="0">
       <text>
         <t>Anything else the row carries, as "name: value | name: value".</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ISE</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Short name for this page. Other rows point at it by this name, so tab numbers never have to be typed.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>topic: the name a reader sees. A noun phrase, not a claim: "Public office and private gain", not "Public office should not be usable for private gain".</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>The page this one is used on.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>topic: one sentence naming what the topic covers, written so a reader can tell whether a given belief belongs here.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>topic: what sits inside this page and what belongs to a neighbouring topic with its own page.</t>
       </text>
     </comment>
   </commentList>
@@ -686,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -705,70 +752,77 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Two sheets. One row in "pages" per page. One row in "edges" per row of every table on every page.</t>
+          <t>Three sheets. One row in "pages" per page. One row in "edges" per row of every table on every page.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>One row in "topics" per topic page; a belief names its topic in the "topic" column of "pages".</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
           <t>Pages point at each other by key, never by tab number, so nothing has to be renumbered when content is added.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
-    </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>To add a reason to a belief: add a row to "pages" (kind = claim, key, text), then a row to "edges" with</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>page = the belief's key, section = argument, side = agree or disagree, claim = the new key.</t>
+          <t>To add a reason to a belief: add a row to "pages" (kind = claim, key, text), then a row to "edges" with</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>To argue that reason's relevance: add a linkage page (kind = linkage, x = the reason, y = the belief,</t>
+          <t>page = the belief's key, section = argument, side = agree or disagree, claim = the new key.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>To argue that reason's relevance: add a linkage page (kind = linkage, x = the reason, y = the belief,</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t>type = Argument, direction = Supports) and put its key in the reason's row under "link".</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
-    </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Nothing here is a score. Every number in the built workbook is computed from these two sheets.</t>
-        </is>
-      </c>
+      <c r="A11" s="1" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>Nothing here is a score. Every number in the built workbook is computed from these two sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>The only typed number in the system is "magnitude" on a cost or benefit row.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-    </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Build: python3 build_example.py ISE_Data_Entry.xlsx</t>
         </is>
@@ -785,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X262"/>
+  <dimension ref="A1:Z262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -793,25 +847,27 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="90" customWidth="1" min="4" max="4"/>
     <col width="90" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="50" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="40" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
     <col width="40" customWidth="1" min="19" max="19"/>
-    <col width="50" customWidth="1" min="20" max="20"/>
-    <col width="60" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="20" max="20"/>
+    <col width="50" customWidth="1" min="21" max="21"/>
     <col width="60" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="60" customWidth="1" min="24" max="24"/>
+    <col width="60" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="60" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -842,95 +898,105 @@
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
           <t>parent</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>y</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>direction</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>rowkind</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>measured_by</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>where_found</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>etype</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>erq</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>erp</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>if_true</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>if_false</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>bridge</t>
         </is>
       </c>
-      <c r="V1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>bottom_line</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>positivity</t>
         </is>
       </c>
-      <c r="X1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
+        <is>
+          <t>strength</t>
+        </is>
+      </c>
+      <c r="Z1" s="3" t="inlineStr">
         <is>
           <t>form</t>
         </is>
@@ -955,20 +1021,30 @@
           <t>Barring members of Congress and the president from owning or trading individual stocks would reduce the use of public office for private gain.</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="V2" s="4" t="inlineStr">
+      <c r="W2" s="4" t="inlineStr">
         <is>
           <t>The conflict is documented and the disclosure regime demonstrably fails. Whether a ban removes the conflict or relocates it into spouses, partnerships and the revolving door is the open question. It is one of three load-bearing components all sitting at the neutral start, and while they sit there any one of them caps what this page can read, however far the evidence carries the argument.</t>
         </is>
       </c>
-      <c r="W2" s="5" t="n">
+      <c r="X2" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="X2" s="4" t="inlineStr">
+      <c r="Y2" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="Z2" s="4" t="inlineStr">
         <is>
           <t>(Officials' holdings currently influence official decisions) AND (removing the holdings removes the influence rather than relocating it) AND (a ban can be enacted and enforced). The normative component, that reducing conflicts is worth a narrower candidate pool, is separable.</t>
         </is>
@@ -993,20 +1069,30 @@
           <t>Barring the president and members of Congress from giving any official government function to a family member would reduce the use of public office for private gain.</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>The legal gap is documented and the supervision problem is real. The page turns on whether a bar removes the conflict or converts a disclosed adviser into an undisclosed one. All three load-bearing components sit at the neutral start, so nothing has been established here yet and nothing is capping anything: the work is to argue them.</t>
         </is>
       </c>
-      <c r="W3" s="5" t="n">
+      <c r="X3" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="X3" s="4" t="inlineStr">
+      <c r="Y3" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="Z3" s="4" t="inlineStr">
         <is>
           <t>(Relatives in official roles produce conflicts that ordinary supervision cannot check) AND (a bar removes those conflicts rather than driving them out of view) AND (Congress can impose the bar on the White House). The third component is where the legal fight is.</t>
         </is>
@@ -1031,20 +1117,30 @@
           <t>Requiring the president and members of Congress to publish their tax returns would reduce the use of public office for private gain.</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="V4" s="4" t="inlineStr">
+      <c r="W4" s="4" t="inlineStr">
         <is>
           <t>The documentary claim is the strongest part: returns do carry conflict-relevant facts the disclosure form omits. What nobody can show is that publishing them changes anything. All three load-bearing components sit at the neutral start, so what this page needs is not more evidence for the conclusion but an argument for each of its parts.</t>
         </is>
       </c>
-      <c r="W4" s="5" t="n">
+      <c r="X4" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="X4" s="4" t="inlineStr">
+      <c r="Y4" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="Z4" s="4" t="inlineStr">
         <is>
           <t>(Returns contain conflict-relevant information the disclosure form lacks) AND (publishing it changes behavior or enables a check) AND (a publication requirement can be imposed). The first is documentary, the second is contested, the third is narrower than the usual objection assumes.</t>
         </is>
@@ -1069,20 +1165,30 @@
           <t>Letting Congress overturn a presidential pardon by a two-thirds vote of both chambers would reduce the use of the pardon power for private gain.</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="V5" s="4" t="inlineStr">
+      <c r="W5" s="4" t="inlineStr">
         <is>
           <t>The gap is real: clemency is the only federal power with no check, and grants to the president's own circle are documented in both parties. All three load-bearing components sit at the neutral start, so any one of them caps the page. The one to argue first is not the constitutional objection but whether an override could ever be exercised at a two-thirds threshold against a president whose own party holds a third of either chamber.</t>
         </is>
       </c>
-      <c r="W5" s="5" t="n">
+      <c r="X5" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="X5" s="4" t="inlineStr">
+      <c r="Y5" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="Z5" s="4" t="inlineStr">
         <is>
           <t>(Some pardons are granted for the president's private benefit) AND (a congressional override would deter or reverse those grants) AND (an override can be enacted). The third component is legal rather than empirical, and it is the one most likely to hold this page down once all three have been argued.</t>
         </is>
@@ -1107,13 +1213,23 @@
           <t>Public office should not be usable for private gain.</t>
         </is>
       </c>
-      <c r="V6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="inlineStr">
         <is>
           <t>Held nearly universally at this level of generality, which is why the argument always moves to the specific rules below it.</t>
         </is>
       </c>
-      <c r="W6" s="5" t="n">
+      <c r="X6" s="5" t="n">
         <v>80</v>
+      </c>
+      <c r="Y6" s="5" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1135,12 +1251,12 @@
           <t>Every federal ethics statute since the 1962 conflict-of-interest reforms rests on this principle, so rejecting it would unsettle the whole body of law rather than one rule.</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="V7" s="4" t="inlineStr">
+      <c r="W7" s="4" t="inlineStr">
         <is>
           <t>True as legal history; that is a weaker claim than the principle itself.</t>
         </is>
@@ -1165,12 +1281,12 @@
           <t>If office can be used for private gain, decisions go to whoever pays the most rather than to whoever is right, which is the definition of a government that does not work.</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="V8" s="4" t="inlineStr">
+      <c r="W8" s="4" t="inlineStr">
         <is>
           <t>The mechanism is right in the extreme case; the size of the effect at low levels of self-dealing is not established here.</t>
         </is>
@@ -1195,12 +1311,12 @@
           <t>It is the rare principle with supermajority agreement across parties: 86 percent of registered voters backed a congressional stock trading ban, including 87 percent of Republicans and 88 percent of Democrats.</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="V9" s="4" t="inlineStr">
+      <c r="W9" s="4" t="inlineStr">
         <is>
           <t>Well measured for the stock trading case; it says what people want, not what is right.</t>
         </is>
@@ -1225,12 +1341,12 @@
           <t>Stated at this level the principle decides nothing, because every real dispute is about what counts as "gain" and what counts as "using" the office.</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="V10" s="4" t="inlineStr">
+      <c r="W10" s="4" t="inlineStr">
         <is>
           <t>A real objection to using the principle as a decision rule, not to holding it.</t>
         </is>
@@ -1255,12 +1371,12 @@
           <t>Taken literally it would bar anyone who owns anything from serving, which would leave office to people with no stake in the country they govern.</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="V11" s="4" t="inlineStr">
+      <c r="W11" s="4" t="inlineStr">
         <is>
           <t>A reductio that the drafted versions of these rules already avoid.</t>
         </is>
@@ -1285,12 +1401,12 @@
           <t>Members regularly trade in the industries their own committees oversee, which puts a private financial stake on both sides of decisions they control.</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="V12" s="4" t="inlineStr">
+      <c r="W12" s="4" t="inlineStr">
         <is>
           <t>The overlap is documented; what it causes is the contested part.</t>
         </is>
@@ -1315,12 +1431,12 @@
           <t>Disclosure has failed as a check: 78 members of one Congress filed late under the STOCK Act, the standard penalty is a $200 fee that is routinely waived, and no member has faced a serious sanction.</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="V13" s="4" t="inlineStr">
+      <c r="W13" s="4" t="inlineStr">
         <is>
           <t>The enforcement record is strong evidence; it shows the reporting regime is unenforced, not that trades were corrupt.</t>
         </is>
@@ -1345,12 +1461,12 @@
           <t>A holdings ban removes the conflict itself instead of asking the public to police thousands of individual trades after the fact.</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="V14" s="4" t="inlineStr">
+      <c r="W14" s="4" t="inlineStr">
         <is>
           <t>The strongest structural argument on the page: it changes what has to be proven.</t>
         </is>
@@ -1375,12 +1491,12 @@
           <t>The Federal Reserve barred its own policymakers from holding individual stocks in 2022 and kept functioning and kept hiring, which shows a comparable institution can operate under the rule.</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="V15" s="4" t="inlineStr">
+      <c r="W15" s="4" t="inlineStr">
         <is>
           <t>A live natural experiment in a nearby institution, with a real scope objection.</t>
         </is>
@@ -1405,12 +1521,12 @@
           <t>Trading on a closed briefing is almost impossible to prosecute, so the only rule that can actually be enforced is one that does not require proving what an official knew.</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="V16" s="4" t="inlineStr">
+      <c r="W16" s="4" t="inlineStr">
         <is>
           <t>The enforcement asymmetry is real; it is evidence about provability, not about guilt.</t>
         </is>
@@ -1435,12 +1551,12 @@
           <t>The best-identified studies of actual returns find congressional portfolios underperform the market, which is hard to square with a systematic insider advantage.</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="V17" s="4" t="inlineStr">
+      <c r="W17" s="4" t="inlineStr">
         <is>
           <t>The aggregate finding is solid and the rebuttal is that aggregates are the wrong place to look.</t>
         </is>
@@ -1465,12 +1581,12 @@
           <t>A ban on the official leaves the conflict in place through spouses, dependent children, private partnerships, real estate and crypto, none of which most proposals reach.</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="V18" s="4" t="inlineStr">
+      <c r="W18" s="4" t="inlineStr">
         <is>
           <t>A real drafting objection that the Fed template already answers in part.</t>
         </is>
@@ -1495,12 +1611,12 @@
           <t>Forced divestiture imposes real costs on officials of ordinary means and narrows who can afford to serve.</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="V19" s="4" t="inlineStr">
+      <c r="W19" s="4" t="inlineStr">
         <is>
           <t>The cost is real and largely fixable in drafting; the rebuttal is stronger than the argument.</t>
         </is>
@@ -1525,12 +1641,12 @@
           <t>Members keep the property rights of other citizens, and a ban restricts a lawful activity because of the job someone holds.</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="V20" s="4" t="inlineStr">
+      <c r="W20" s="4" t="inlineStr">
         <is>
           <t>Weakest of the four: the restriction is common elsewhere in government and the office is voluntary.</t>
         </is>
@@ -1555,12 +1671,12 @@
           <t>Congress will not enforce a ban on itself, so the statute would put a symbol in place of the enforcement reform that could work.</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="V21" s="4" t="inlineStr">
+      <c r="W21" s="4" t="inlineStr">
         <is>
           <t>The best argument against: it predicts the failure mode from the closest precedent.</t>
         </is>
@@ -1585,17 +1701,17 @@
           <t>Senators' stock purchases beat the market by about 85 basis points a month, roughly 10 percent a year, over 1993 to 1998.</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="O22" s="5" t="inlineStr">
+      <c r="P22" s="5" t="inlineStr">
         <is>
           <t>observational</t>
         </is>
       </c>
-      <c r="V22" s="4" t="inlineStr">
+      <c r="W22" s="4" t="inlineStr">
         <is>
           <t>Methodologically solid for its period; its period is the problem.</t>
         </is>
@@ -1620,23 +1736,23 @@
           <t>Trades placed before legislative events earned abnormal returns of about 3 to 5 percent over 2014 to 2021.</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="O23" s="5" t="inlineStr">
+      <c r="P23" s="5" t="inlineStr">
         <is>
           <t>observational</t>
         </is>
       </c>
-      <c r="P23" s="5" t="n">
+      <c r="Q23" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="Q23" s="5" t="n">
+      <c r="R23" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="V23" s="4" t="inlineStr">
+      <c r="W23" s="4" t="inlineStr">
         <is>
           <t>The most direct answer to the underperformance studies, and the newest, which cuts both ways.</t>
         </is>
@@ -1661,17 +1777,17 @@
           <t>78 members of the 117th Congress violated the STOCK Act's disclosure deadlines.</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="O24" s="5" t="inlineStr">
+      <c r="P24" s="5" t="inlineStr">
         <is>
           <t>statistics</t>
         </is>
       </c>
-      <c r="V24" s="4" t="inlineStr">
+      <c r="W24" s="4" t="inlineStr">
         <is>
           <t>Accurate as a count of filing failures; frequently oversold as a count of misconduct.</t>
         </is>
@@ -1696,17 +1812,17 @@
           <t>131 federal judges heard 685 cases involving companies in which they or their families held stock, over 2010 to 2018.</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="O25" s="5" t="inlineStr">
+      <c r="P25" s="5" t="inlineStr">
         <is>
           <t>statistics</t>
         </is>
       </c>
-      <c r="V25" s="4" t="inlineStr">
+      <c r="W25" s="4" t="inlineStr">
         <is>
           <t>Strong evidence about disclosure regimes generally; one institution removed from the belief.</t>
         </is>
@@ -1731,17 +1847,17 @@
           <t>Federal Reserve officials have been barred from holding individual stocks, sector funds, individual bonds, crypto and derivatives since May 2022, with preclearance and a one-year holding period.</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="O26" s="5" t="inlineStr">
+      <c r="P26" s="5" t="inlineStr">
         <is>
           <t>record</t>
         </is>
       </c>
-      <c r="V26" s="4" t="inlineStr">
+      <c r="W26" s="4" t="inlineStr">
         <is>
           <t>Establishes that the rule is workable; says little yet about its long-run costs.</t>
         </is>
@@ -1766,17 +1882,17 @@
           <t>Congressional portfolios underperformed market benchmarks by roughly 2 to 3 percent a year over 2004 to 2008.</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="O27" s="5" t="inlineStr">
+      <c r="P27" s="5" t="inlineStr">
         <is>
           <t>observational</t>
         </is>
       </c>
-      <c r="V27" s="4" t="inlineStr">
+      <c r="W27" s="4" t="inlineStr">
         <is>
           <t>The strongest single piece of evidence against, and its known weakness is that averages hide tails.</t>
         </is>
@@ -1801,23 +1917,23 @@
           <t>No evidence that members of Congress outperformed the market over 2012 to 2020, the period after the STOCK Act.</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="O28" s="5" t="inlineStr">
+      <c r="P28" s="5" t="inlineStr">
         <is>
           <t>observational</t>
         </is>
       </c>
-      <c r="P28" s="5" t="n">
+      <c r="Q28" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="Q28" s="5" t="n">
+      <c r="R28" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="V28" s="4" t="inlineStr">
+      <c r="W28" s="4" t="inlineStr">
         <is>
           <t>Directly on point for the trading-advantage claim; silent on the voting-conflict claim.</t>
         </is>
@@ -1842,12 +1958,12 @@
           <t>Five years after a ban takes effect, individual equity holdings reported by members fall to near zero and no trading scandal originates in Congress.</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="V29" s="4" t="inlineStr">
+      <c r="W29" s="4" t="inlineStr">
         <is>
           <t>Pending, and the metric is gameable in a way the prediction should name.</t>
         </is>
@@ -1872,12 +1988,12 @@
           <t>Public trust in Congress five years after a ban is higher than the pre-ban trend predicted.</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="V30" s="4" t="inlineStr">
+      <c r="W30" s="4" t="inlineStr">
         <is>
           <t>Weakly diagnostic: a lot of noise for one signal.</t>
         </is>
@@ -1902,12 +2018,12 @@
           <t>A jurisdiction that adopts a holdings ban shows conflicted votes falling relative to comparable bodies that did not.</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="V31" s="4" t="inlineStr">
+      <c r="W31" s="4" t="inlineStr">
         <is>
           <t>The single most informative study nobody has run.</t>
         </is>
@@ -1932,12 +2048,12 @@
           <t>Reported conflicts migrate to spouse accounts and private partnerships, leaving the total number of conflict complaints unchanged.</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="V32" s="4" t="inlineStr">
+      <c r="W32" s="4" t="inlineStr">
         <is>
           <t>The most likely way the belief fails, and the one the drafting can answer.</t>
         </is>
@@ -1962,12 +2078,12 @@
           <t>The share of incoming members whose wealth is in the top 1 percent rises after a ban.</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="V33" s="4" t="inlineStr">
+      <c r="W33" s="4" t="inlineStr">
         <is>
           <t>Testable from existing data, and the base rate makes a large move unlikely.</t>
         </is>
@@ -1992,12 +2108,12 @@
           <t>Post-reform studies continue to find no abnormal returns, so there is no trading advantage for a ban to remove.</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="V34" s="4" t="inlineStr">
+      <c r="W34" s="4" t="inlineStr">
         <is>
           <t>Would weaken one branch of the tree and leave the other standing.</t>
         </is>
@@ -2022,12 +2138,12 @@
           <t>Members stop voting on industries in which they hold a personal stake.</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="V35" s="4" t="inlineStr">
+      <c r="W35" s="4" t="inlineStr">
         <is>
           <t>Mechanically near-certain in direction, contested in size.</t>
         </is>
@@ -2052,12 +2168,12 @@
           <t>Officials stop placing trades ahead of government announcements.</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="V36" s="4" t="inlineStr">
+      <c r="W36" s="4" t="inlineStr">
         <is>
           <t>Direction certain, magnitude resting on a contested base rate.</t>
         </is>
@@ -2082,12 +2198,12 @@
           <t>Voters can tell a compromised official from a clean one without an investigation.</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="V37" s="4" t="inlineStr">
+      <c r="W37" s="4" t="inlineStr">
         <is>
           <t>The benefit most often claimed and the least supported by the record.</t>
         </is>
@@ -2112,12 +2228,12 @@
           <t>Officials get one rule they can follow without a lawyer instead of a reporting regime they violate by accident.</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="V38" s="4" t="inlineStr">
+      <c r="W38" s="4" t="inlineStr">
         <is>
           <t>Plausible and small; the Fed rule suggests the saving is partly offset.</t>
         </is>
@@ -2142,12 +2258,12 @@
           <t>Officials sell holdings on a schedule they did not choose and pay tax on the gains.</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="V39" s="4" t="inlineStr">
+      <c r="W39" s="4" t="inlineStr">
         <is>
           <t>Real and largely solvable in drafting.</t>
         </is>
@@ -2172,12 +2288,12 @@
           <t>Mid-career professionals with savings in individual equities decline to run.</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="V40" s="4" t="inlineStr">
+      <c r="W40" s="4" t="inlineStr">
         <is>
           <t>The mechanism is real; the affected group is narrower than the argument implies.</t>
         </is>
@@ -2202,12 +2318,12 @@
           <t>Officeholders lose income they currently earn from trading on their position.</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="V41" s="4" t="inlineStr">
+      <c r="W41" s="4" t="inlineStr">
         <is>
           <t>A cost that only exists to the extent the belief's own premise is true, and it falls on an interest almost nobody defends.</t>
         </is>
@@ -2232,7 +2348,7 @@
           <t>Members divest or move holdings into diversified funds within the compliance window.</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="G42" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2257,7 +2373,7 @@
           <t>Filing volume falls because there are fewer transactions to report.</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="G43" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2282,7 +2398,7 @@
           <t>Conflict complaints shift from trading to family and outside business interests.</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="G44" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2307,7 +2423,7 @@
           <t>The rule becomes unremarkable, as judicial and executive branch holding rules did.</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="G45" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2332,12 +2448,12 @@
           <t>Officials' financial holdings currently influence how they vote and what they say.</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="G46" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="V46" s="4" t="inlineStr">
+      <c r="W46" s="4" t="inlineStr">
         <is>
           <t>Documented as correlation, not established as influence. This is the load-bearing claim the whole belief rests on.</t>
         </is>
@@ -2362,12 +2478,12 @@
           <t>Removing the holding removes the influence rather than relocating it to a spouse, a partnership or a post-office job.</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="V47" s="4" t="inlineStr">
+      <c r="W47" s="4" t="inlineStr">
         <is>
           <t>The weakest load-bearing part, and the one that caps the page.</t>
         </is>
@@ -2392,12 +2508,12 @@
           <t>A holdings ban can be enacted and enforced against sitting members.</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="G48" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="V48" s="4" t="inlineStr">
+      <c r="W48" s="4" t="inlineStr">
         <is>
           <t>Much stronger than it was two years ago, and still unfinished.</t>
         </is>
@@ -2422,12 +2538,12 @@
           <t>Reducing conflicts is worth a narrower candidate pool and a real compliance burden.</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="G49" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="V49" s="4" t="inlineStr">
+      <c r="W49" s="4" t="inlineStr">
         <is>
           <t>A value judgment that the cost-benefit table prices rather than settles.</t>
         </is>
@@ -2452,7 +2568,7 @@
           <t>Officials respond to financial incentives the way other people do.</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="G50" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2477,7 +2593,7 @@
           <t>Disclosure alone is sufficient when it is actually enforced.</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="G51" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2502,7 +2618,7 @@
           <t>Both sides want officials who are not, and do not appear to be, for sale.</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="G52" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2527,12 +2643,12 @@
           <t>Bar individual stocks, sector funds and derivatives for the official, spouse and dependent children; keep diversified funds and Treasuries legal; allow deferral of capital gains on forced divestiture; and set the penalty at a share of the transaction rather than a flat fee.</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="G53" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="V53" s="4" t="inlineStr">
+      <c r="W53" s="4" t="inlineStr">
         <is>
           <t>The most defensible version on offer; its weakness is political, not analytical.</t>
         </is>
@@ -2557,7 +2673,7 @@
           <t>The advertised reason is not what actually drives the position: Stop officials from trading on what they learn in office.</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr">
+      <c r="G54" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2582,7 +2698,7 @@
           <t>The advertised reason is not what actually drives the position: Protect ordinary property rights.</t>
         </is>
       </c>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="G55" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2607,7 +2723,7 @@
           <t>The people who would be bound are the people who must vote for it.</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr">
+      <c r="G56" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2632,7 +2748,7 @@
           <t>Opponents cannot point to a benefit of officials owning individual stocks that a diversified fund does not provide.</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="G57" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2657,7 +2773,7 @@
           <t>Scandal salience: a handful of vivid cases stands in for a rate nobody has measured.</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr">
+      <c r="G58" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2682,7 +2798,7 @@
           <t>Self-interest and status quo bias among the officials who would be bound.</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="G59" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2707,7 +2823,7 @@
           <t>The STOCK Act of 2012 made insider trading law explicitly applicable to Congress and required transaction reports within 45 days.</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr">
+      <c r="G60" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2732,7 +2848,7 @@
           <t>The Courthouse Ethics and Transparency Act of 2022 applied the same transaction reporting to federal judges and created a searchable database.</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="G61" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2757,12 +2873,12 @@
           <t>The criminal conflict-of-interest statute does not apply to the president, the vice president, members of Congress or federal judges.</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr">
+      <c r="G62" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="V62" s="4" t="inlineStr">
+      <c r="W62" s="4" t="inlineStr">
         <is>
           <t>Listed on the weakening side because it is cited that way; the linkage page is where that gets tested.</t>
         </is>
@@ -2787,7 +2903,7 @@
           <t>Citizens keep their ordinary rights when they take public office.</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr">
+      <c r="G63" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2812,7 +2928,7 @@
           <t>Senior executive branch officials and their spouses should be barred from holding individual stocks.</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr">
+      <c r="G64" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2837,7 +2953,7 @@
           <t>Congressional staff with access to nonpublic information should face the same ban.</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="G65" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2862,7 +2978,7 @@
           <t>Members of Congress should be barred from owning any asset other than Treasury securities and diversified funds while in office.</t>
         </is>
       </c>
-      <c r="F66" s="4" t="inlineStr">
+      <c r="G66" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2887,7 +3003,7 @@
           <t>Members of Congress should be required to place individual stocks in a qualified blind trust.</t>
         </is>
       </c>
-      <c r="F67" s="4" t="inlineStr">
+      <c r="G67" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2912,7 +3028,7 @@
           <t>Senators Jeff Merkley, Josh Hawley and Jon Ossoff have sponsored or cosponsored legislation to ban congressional stock trading.</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
+      <c r="G68" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2937,7 +3053,7 @@
           <t>Representatives Chip Roy and Seth Magaziner have sponsored the leading House bills in the 119th Congress.</t>
         </is>
       </c>
-      <c r="F69" s="4" t="inlineStr">
+      <c r="G69" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
@@ -2962,12 +3078,12 @@
           <t>Speaker Nancy Pelosi said in December 2021 that members should be able to participate in the free-market economy, before later supporting floor consideration of a ban.</t>
         </is>
       </c>
-      <c r="F70" s="4" t="inlineStr">
+      <c r="G70" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="V70" s="4" t="inlineStr">
+      <c r="W70" s="4" t="inlineStr">
         <is>
           <t>Accurate as a quotation, misleading as a summary of her final position.</t>
         </is>
@@ -2992,12 +3108,12 @@
           <t>The anti-nepotism statute stops at the White House door, so the rule does not reach the place where the stakes are highest.</t>
         </is>
       </c>
-      <c r="F71" s="4" t="inlineStr">
+      <c r="G71" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="V71" s="4" t="inlineStr">
+      <c r="W71" s="4" t="inlineStr">
         <is>
           <t>The legal gap is real and was formally relied upon; whether a court would agree has never been tested.</t>
         </is>
@@ -3022,12 +3138,12 @@
           <t>A relative cannot be supervised, disciplined or fired the way another official can, so the ordinary checks on an official's conduct do not operate.</t>
         </is>
       </c>
-      <c r="F72" s="4" t="inlineStr">
+      <c r="G72" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="V72" s="4" t="inlineStr">
+      <c r="W72" s="4" t="inlineStr">
         <is>
           <t>The strongest argument on the page: it names a mechanism that does not depend on anyone's motives.</t>
         </is>
@@ -3052,12 +3168,12 @@
           <t>An official role gives a family member a channel that foreign governments and business partners can use, with the family's private interests attached to it.</t>
         </is>
       </c>
-      <c r="F73" s="4" t="inlineStr">
+      <c r="G73" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="V73" s="4" t="inlineStr">
+      <c r="W73" s="4" t="inlineStr">
         <is>
           <t>Concrete and current; the rebuttal points at a narrower remedy.</t>
         </is>
@@ -3082,12 +3198,12 @@
           <t>The rule already applies to every other federal agency, so extending it closes a gap rather than inventing a restriction.</t>
         </is>
       </c>
-      <c r="F74" s="4" t="inlineStr">
+      <c r="G74" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="V74" s="4" t="inlineStr">
+      <c r="W74" s="4" t="inlineStr">
         <is>
           <t>True, and the rebuttal reframes the whole proposal as an enforcement question.</t>
         </is>
@@ -3112,12 +3228,12 @@
           <t>Formal appointment is what brings a relative inside the ethics rules; a bar pushes the same influence outside them, where nothing applies.</t>
         </is>
       </c>
-      <c r="F75" s="4" t="inlineStr">
+      <c r="G75" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="V75" s="4" t="inlineStr">
+      <c r="W75" s="4" t="inlineStr">
         <is>
           <t>The best argument against, and it is answered only if the rule is drafted around function rather than title.</t>
         </is>
@@ -3142,12 +3258,12 @@
           <t>The problem people actually point to is relatives trading on the family name in private business, which this proposal does not touch.</t>
         </is>
       </c>
-      <c r="F76" s="4" t="inlineStr">
+      <c r="G76" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="V76" s="4" t="inlineStr">
+      <c r="W76" s="4" t="inlineStr">
         <is>
           <t>A genuine scope objection: the proposal is aimed at a smaller target than the grievance that motivates it.</t>
         </is>
@@ -3172,12 +3288,12 @@
           <t>A president is entitled to advisers he trusts, and Congress's power to tell him whom he may consult is constitutionally contested.</t>
         </is>
       </c>
-      <c r="F77" s="4" t="inlineStr">
+      <c r="G77" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="V77" s="4" t="inlineStr">
+      <c r="W77" s="4" t="inlineStr">
         <is>
           <t>Strong for White House staff, weak for Senate-confirmed posts.</t>
         </is>
@@ -3202,12 +3318,12 @@
           <t>Competence is neither inherited nor disqualified by relation, and a blanket bar excludes people for a relationship rather than for a conflict.</t>
         </is>
       </c>
-      <c r="F78" s="4" t="inlineStr">
+      <c r="G78" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="V78" s="4" t="inlineStr">
+      <c r="W78" s="4" t="inlineStr">
         <is>
           <t>Answers an argument the proposal does not make.</t>
         </is>
@@ -3232,17 +3348,17 @@
           <t>The Justice Department concluded that the federal anti-nepotism statute does not bar a presidential relative's appointment to the White House Office.</t>
         </is>
       </c>
-      <c r="F79" s="4" t="inlineStr">
+      <c r="G79" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="O79" s="5" t="inlineStr">
+      <c r="P79" s="5" t="inlineStr">
         <is>
           <t>record</t>
         </is>
       </c>
-      <c r="V79" s="4" t="inlineStr">
+      <c r="W79" s="4" t="inlineStr">
         <is>
           <t>Authoritative in practice, untested in court.</t>
         </is>
@@ -3267,17 +3383,17 @@
           <t>Relatives by marriage have held Senate-confirmed and envoy positions outside the White House Office, including an ambassadorship in 2025 and a special envoy designation in February 2026.</t>
         </is>
       </c>
-      <c r="F80" s="4" t="inlineStr">
+      <c r="G80" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="O80" s="5" t="inlineStr">
+      <c r="P80" s="5" t="inlineStr">
         <is>
           <t>record</t>
         </is>
       </c>
-      <c r="V80" s="4" t="inlineStr">
+      <c r="W80" s="4" t="inlineStr">
         <is>
           <t>Current and verifiable; the confirmation point cuts against reading it as an unchecked practice.</t>
         </is>
@@ -3302,17 +3418,17 @@
           <t>Relatives who became federal employees filed public financial disclosures reporting assets of up to roughly $762 million, with multiple amendments adding previously omitted holdings.</t>
         </is>
       </c>
-      <c r="F81" s="4" t="inlineStr">
+      <c r="G81" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="O81" s="5" t="inlineStr">
+      <c r="P81" s="5" t="inlineStr">
         <is>
           <t>record</t>
         </is>
       </c>
-      <c r="V81" s="4" t="inlineStr">
+      <c r="W81" s="4" t="inlineStr">
         <is>
           <t>The concrete form of the "inside the rules" argument.</t>
         </is>
@@ -3337,17 +3453,17 @@
           <t>Federal candidates paid a combined $1.3 million in wages to people sharing their surname in one election cycle, entirely through campaign committees that no official-duty rule reaches.</t>
         </is>
       </c>
-      <c r="F82" s="4" t="inlineStr">
+      <c r="G82" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="O82" s="5" t="inlineStr">
+      <c r="P82" s="5" t="inlineStr">
         <is>
           <t>statistics</t>
         </is>
       </c>
-      <c r="V82" s="4" t="inlineStr">
+      <c r="W82" s="4" t="inlineStr">
         <is>
           <t>Shows where the money actually moves, which is not where the proposal points.</t>
         </is>
@@ -3372,12 +3488,12 @@
           <t>After a bar takes effect, no relative of a president or a member holds a White House, envoy or ambassadorial post.</t>
         </is>
       </c>
-      <c r="F83" s="4" t="inlineStr">
+      <c r="G83" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="V83" s="4" t="inlineStr">
+      <c r="W83" s="4" t="inlineStr">
         <is>
           <t>Easy to measure and easy to satisfy without changing anything, which is the objection in one line.</t>
         </is>
@@ -3402,12 +3518,12 @@
           <t>Documented contacts in which a foreign government routes business through a presidential relative fall relative to the preceding decade.</t>
         </is>
       </c>
-      <c r="F84" s="4" t="inlineStr">
+      <c r="G84" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="V84" s="4" t="inlineStr">
+      <c r="W84" s="4" t="inlineStr">
         <is>
           <t>The right thing to measure, measured by a proxy that moves for other reasons.</t>
         </is>
@@ -3432,12 +3548,12 @@
           <t>Relatives continue to shape policy as private citizens and unpaid informal advisers, and the number of documented family-channel contacts is unchanged.</t>
         </is>
       </c>
-      <c r="F85" s="4" t="inlineStr">
+      <c r="G85" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="V85" s="4" t="inlineStr">
+      <c r="W85" s="4" t="inlineStr">
         <is>
           <t>The way this belief most plausibly fails.</t>
         </is>
@@ -3462,7 +3578,7 @@
           <t>Official decisions stop being made by people the president cannot supervise or remove in the ordinary way.</t>
         </is>
       </c>
-      <c r="F86" s="4" t="inlineStr">
+      <c r="G86" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
@@ -3487,7 +3603,7 @@
           <t>Foreign governments lose a contact point that carries private family interests with it.</t>
         </is>
       </c>
-      <c r="F87" s="4" t="inlineStr">
+      <c r="G87" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
@@ -3512,7 +3628,7 @@
           <t>Career staff can raise objections to a senior adviser without raising them to the president about his own family.</t>
         </is>
       </c>
-      <c r="F88" s="4" t="inlineStr">
+      <c r="G88" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
@@ -3537,7 +3653,7 @@
           <t>A president loses advisers he trusts most, at some cost to the quality of advice he acts on.</t>
         </is>
       </c>
-      <c r="F89" s="4" t="inlineStr">
+      <c r="G89" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
@@ -3562,7 +3678,7 @@
           <t>Qualified people are excluded from public service for a family relationship they did not choose.</t>
         </is>
       </c>
-      <c r="F90" s="4" t="inlineStr">
+      <c r="G90" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
@@ -3587,7 +3703,7 @@
           <t>Influence moves to informal channels that file nothing and leave no record.</t>
         </is>
       </c>
-      <c r="F91" s="4" t="inlineStr">
+      <c r="G91" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
@@ -3612,12 +3728,12 @@
           <t>A relative in an official role creates conflicts that ordinary supervision and ethics rules cannot check.</t>
         </is>
       </c>
-      <c r="F92" s="4" t="inlineStr">
+      <c r="G92" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="V92" s="4" t="inlineStr">
+      <c r="W92" s="4" t="inlineStr">
         <is>
           <t>Contested, and the disagreement is the mirror image of the "inside the rules" argument.</t>
         </is>
@@ -3642,12 +3758,12 @@
           <t>A bar removes the influence rather than pushing it into informal channels.</t>
         </is>
       </c>
-      <c r="F93" s="4" t="inlineStr">
+      <c r="G93" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="V93" s="4" t="inlineStr">
+      <c r="W93" s="4" t="inlineStr">
         <is>
           <t>Tied for weakest load-bearing component on this page, which is why the cap bites.</t>
         </is>
@@ -3672,12 +3788,12 @@
           <t>Congress can impose the bar on White House appointments.</t>
         </is>
       </c>
-      <c r="F94" s="4" t="inlineStr">
+      <c r="G94" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="V94" s="4" t="inlineStr">
+      <c r="W94" s="4" t="inlineStr">
         <is>
           <t>More defensible than the pardon case and less settled than the stock case.</t>
         </is>
@@ -3702,7 +3818,7 @@
           <t>Both sides want relatives' financial interests visible rather than hidden.</t>
         </is>
       </c>
-      <c r="F95" s="4" t="inlineStr">
+      <c r="G95" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
@@ -3727,7 +3843,7 @@
           <t>Bar relatives from Senate-confirmed and envoy positions, and require anyone performing official functions, whatever their title, to file the same disclosures and follow the same conflict rules as an employee.</t>
         </is>
       </c>
-      <c r="F96" s="4" t="inlineStr">
+      <c r="G96" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
@@ -3752,7 +3868,7 @@
           <t>Relatives of the president should be barred from Senate-confirmed positions but permitted to serve as unpaid advisers subject to full disclosure.</t>
         </is>
       </c>
-      <c r="F97" s="4" t="inlineStr">
+      <c r="G97" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
@@ -3782,12 +3898,12 @@
           <t>A published tax return shows what the federal financial disclosure form does not: exact income and its character, foreign income and foreign tax credits, business losses carried forward, charitable giving, and the rate actually paid.</t>
         </is>
       </c>
-      <c r="F98" s="4" t="inlineStr">
+      <c r="G98" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="V98" s="4" t="inlineStr">
+      <c r="W98" s="4" t="inlineStr">
         <is>
           <t>The factual claim about what each document contains is correct; whether the extra content is what screens conflicts is the argument.</t>
         </is>
@@ -3817,12 +3933,12 @@
           <t>The internal check on a president’s tax compliance failed in the one case that tested it: the mandatory presidential audit was dormant, and the audit of the first two years opened the day Congress asked for the returns.</t>
         </is>
       </c>
-      <c r="F99" s="4" t="inlineStr">
+      <c r="G99" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="V99" s="4" t="inlineStr">
+      <c r="W99" s="4" t="inlineStr">
         <is>
           <t>The strongest evidence on the page, and it is about the audit rather than about publication.</t>
         </is>
@@ -3852,12 +3968,12 @@
           <t>Every president from Carter through Obama released tax returns voluntarily, so a publication requirement restores a forty-year norm rather than inventing an obligation.</t>
         </is>
       </c>
-      <c r="F100" s="4" t="inlineStr">
+      <c r="G100" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="V100" s="4" t="inlineStr">
+      <c r="W100" s="4" t="inlineStr">
         <is>
           <t>Accurate history; the step from norm to statute is the contested part.</t>
         </is>
@@ -3887,12 +4003,12 @@
           <t>A published tax return can be checked by anyone, which is the only enforcement of an officeholder’s tax compliance that does not depend on an agency the officeholder appoints.</t>
         </is>
       </c>
-      <c r="F101" s="4" t="inlineStr">
+      <c r="G101" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="V101" s="4" t="inlineStr">
+      <c r="W101" s="4" t="inlineStr">
         <is>
           <t>The structural argument, and the one least dependent on any particular administration.</t>
         </is>
@@ -3922,12 +4038,12 @@
           <t>A tax return shows tax positions, not conflicts, and the federal financial disclosure form already lists assets, income sources, liabilities and positions in categories built for conflict screening.</t>
         </is>
       </c>
-      <c r="F102" s="4" t="inlineStr">
+      <c r="G102" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="V102" s="4" t="inlineStr">
+      <c r="W102" s="4" t="inlineStr">
         <is>
           <t>The best argument against, and the rebuttal is specific enough to test.</t>
         </is>
@@ -3957,12 +4073,12 @@
           <t>Requiring the president and members of Congress to publish their tax returns would publish the finances of spouses, children and business partners who never ran for office.</t>
         </is>
       </c>
-      <c r="F103" s="4" t="inlineStr">
+      <c r="G103" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="V103" s="4" t="inlineStr">
+      <c r="W103" s="4" t="inlineStr">
         <is>
           <t>A real privacy cost with a partial drafting answer.</t>
         </is>
@@ -3992,12 +4108,12 @@
           <t>The constitutional route to a tax-return publication requirement is narrow: a disclosure condition on ballot access was already struck down once, and a badly drafted rule would be litigated rather than obeyed.</t>
         </is>
       </c>
-      <c r="F104" s="4" t="inlineStr">
+      <c r="G104" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="V104" s="4" t="inlineStr">
+      <c r="W104" s="4" t="inlineStr">
         <is>
           <t>The precedent is real and much narrower than the argument treats it.</t>
         </is>
@@ -4022,12 +4138,12 @@
           <t>Sophisticated wealth sits in pass-through entities and trusts that file their own returns, so a personal return can be published and show very little.</t>
         </is>
       </c>
-      <c r="F105" s="4" t="inlineStr">
+      <c r="G105" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="V105" s="4" t="inlineStr">
+      <c r="W105" s="4" t="inlineStr">
         <is>
           <t>The most technically substantive objection on the page.</t>
         </is>
@@ -4052,17 +4168,17 @@
           <t>The mandatory IRS audit of presidential returns was "dormant, at best," and the audit of the 2015 and 2016 returns opened on April 3, 2019, the day the committee requested them; only 2016 was completed in office.</t>
         </is>
       </c>
-      <c r="F106" s="4" t="inlineStr">
+      <c r="G106" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="O106" s="5" t="inlineStr">
+      <c r="P106" s="5" t="inlineStr">
         <is>
           <t>record</t>
         </is>
       </c>
-      <c r="V106" s="4" t="inlineStr">
+      <c r="W106" s="4" t="inlineStr">
         <is>
           <t>The dates are documentary and the characterization is the committee's.</t>
         </is>
@@ -4087,17 +4203,17 @@
           <t>Nixon released his returns in December 1973 and asked the Joint Committee on Taxation to review them; the review found roughly $465,000 in back taxes owed.</t>
         </is>
       </c>
-      <c r="F107" s="4" t="inlineStr">
+      <c r="G107" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="O107" s="5" t="inlineStr">
+      <c r="P107" s="5" t="inlineStr">
         <is>
           <t>record</t>
         </is>
       </c>
-      <c r="V107" s="4" t="inlineStr">
+      <c r="W107" s="4" t="inlineStr">
         <is>
           <t>The founding case of the norm, and it cuts slightly against compulsion.</t>
         </is>
@@ -4122,17 +4238,17 @@
           <t>The public financial disclosure form already requires assets, income sources, liabilities, positions, agreements and gifts, reported in value ranges.</t>
         </is>
       </c>
-      <c r="F108" s="4" t="inlineStr">
+      <c r="G108" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="O108" s="5" t="inlineStr">
+      <c r="P108" s="5" t="inlineStr">
         <is>
           <t>record</t>
         </is>
       </c>
-      <c r="V108" s="4" t="inlineStr">
+      <c r="W108" s="4" t="inlineStr">
         <is>
           <t>Accurate, and the range structure is exactly what the other side points at.</t>
         </is>
@@ -4157,17 +4273,17 @@
           <t>A state law requiring five years of returns from presidential primary candidates was struck down unanimously on state constitutional grounds.</t>
         </is>
       </c>
-      <c r="F109" s="4" t="inlineStr">
+      <c r="G109" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="O109" s="5" t="inlineStr">
+      <c r="P109" s="5" t="inlineStr">
         <is>
           <t>record</t>
         </is>
       </c>
-      <c r="V109" s="4" t="inlineStr">
+      <c r="W109" s="4" t="inlineStr">
         <is>
           <t>Frequently cited for more than it holds, which is what its linkage page is for.</t>
         </is>
@@ -4192,12 +4308,12 @@
           <t>Within two election cycles of a publication requirement, at least one significant undisclosed foreign income source or lender relationship is found in a published return.</t>
         </is>
       </c>
-      <c r="F110" s="4" t="inlineStr">
+      <c r="G110" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="V110" s="4" t="inlineStr">
+      <c r="W110" s="4" t="inlineStr">
         <is>
           <t>Diagnostic, and its failure would be ambiguous between deterrence and nothing to find.</t>
         </is>
@@ -4222,12 +4338,12 @@
           <t>Published returns add nothing to what the disclosure form already showed, and no conflict is identified from a return that the form had not already flagged.</t>
         </is>
       </c>
-      <c r="F111" s="4" t="inlineStr">
+      <c r="G111" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="V111" s="4" t="inlineStr">
+      <c r="W111" s="4" t="inlineStr">
         <is>
           <t>Directly testable against the one case where both documents exist.</t>
         </is>
@@ -4257,7 +4373,7 @@
           <t>If the president and members of Congress published their tax returns, foreign income and lender relationships would become visible without a subpoena.</t>
         </is>
       </c>
-      <c r="F112" s="4" t="inlineStr">
+      <c r="G112" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
@@ -4287,7 +4403,7 @@
           <t>If the president and members of Congress published their tax returns, voters could judge an official’s financial entanglements before voting rather than after an investigation.</t>
         </is>
       </c>
-      <c r="F113" s="4" t="inlineStr">
+      <c r="G113" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
@@ -4317,7 +4433,7 @@
           <t>If the president published their tax returns, the audit of the president would stop depending on an agency the president appoints.</t>
         </is>
       </c>
-      <c r="F114" s="4" t="inlineStr">
+      <c r="G114" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
@@ -4347,7 +4463,7 @@
           <t>Under a tax-return publication requirement, spouses, children and business partners have their finances published without holding office.</t>
         </is>
       </c>
-      <c r="F115" s="4" t="inlineStr">
+      <c r="G115" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
@@ -4377,7 +4493,7 @@
           <t>Under a tax-return publication requirement, officials structure their finances to look unremarkable rather than to be efficient.</t>
         </is>
       </c>
-      <c r="F116" s="4" t="inlineStr">
+      <c r="G116" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
@@ -4407,7 +4523,7 @@
           <t>Published tax returns are read as scandal rather than as data, and complex but lawful items are litigated in public.</t>
         </is>
       </c>
-      <c r="F117" s="4" t="inlineStr">
+      <c r="G117" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
@@ -4432,12 +4548,12 @@
           <t>Tax returns contain conflict-relevant information that the financial disclosure form does not.</t>
         </is>
       </c>
-      <c r="F118" s="4" t="inlineStr">
+      <c r="G118" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="V118" s="4" t="inlineStr">
+      <c r="W118" s="4" t="inlineStr">
         <is>
           <t>The most checkable component on any of these four pages.</t>
         </is>
@@ -4467,12 +4583,12 @@
           <t>Publishing the tax returns of the president and members of Congress changes what officials do, or lets someone act on what it shows.</t>
         </is>
       </c>
-      <c r="F119" s="4" t="inlineStr">
+      <c r="G119" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="V119" s="4" t="inlineStr">
+      <c r="W119" s="4" t="inlineStr">
         <is>
           <t>The weak link in substance, and it scores level with the other two rather than below them.</t>
         </is>
@@ -4497,12 +4613,12 @@
           <t>A federal publication requirement for officeholders can be enacted and would survive review.</t>
         </is>
       </c>
-      <c r="F120" s="4" t="inlineStr">
+      <c r="G120" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="V120" s="4" t="inlineStr">
+      <c r="W120" s="4" t="inlineStr">
         <is>
           <t>Stronger than the pardon case: the disclosure precedent is well established.</t>
         </is>
@@ -4527,7 +4643,7 @@
           <t>Both sides want conflicts visible; they disagree about which document shows them.</t>
         </is>
       </c>
-      <c r="F121" s="4" t="inlineStr">
+      <c r="G121" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
@@ -4552,7 +4668,7 @@
           <t>Require exact values rather than ranges on the disclosure form, add foreign income and lender identity, and require the president to publish returns while leaving members under the enhanced form.</t>
         </is>
       </c>
-      <c r="F122" s="4" t="inlineStr">
+      <c r="G122" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
@@ -4577,7 +4693,7 @@
           <t>All senior federal officials, including agency heads and judges, should publish their tax returns annually.</t>
         </is>
       </c>
-      <c r="F123" s="4" t="inlineStr">
+      <c r="G123" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
@@ -4602,12 +4718,12 @@
           <t>Clemency is the only executive power with no check at all: impeachment reaches the officer, not the act, and the act is final the moment it is signed.</t>
         </is>
       </c>
-      <c r="F124" s="4" t="inlineStr">
+      <c r="G124" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="V124" s="4" t="inlineStr">
+      <c r="W124" s="4" t="inlineStr">
         <is>
           <t>Structurally accurate. Whether the absence of a check is a defect or the point is the whole argument.</t>
         </is>
@@ -4632,12 +4748,12 @@
           <t>Pardons granted to the president's relatives, donors, business partners and co-defendants are the clearest case of office used for private benefit, and nothing reviews them.</t>
         </is>
       </c>
-      <c r="F125" s="4" t="inlineStr">
+      <c r="G125" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="V125" s="4" t="inlineStr">
+      <c r="W125" s="4" t="inlineStr">
         <is>
           <t>The pattern is documented across parties, which is what makes it a structural argument rather than a partisan one.</t>
         </is>
@@ -4662,12 +4778,12 @@
           <t>A two-thirds threshold means only the pardons that both parties find indefensible would ever be reversed.</t>
         </is>
       </c>
-      <c r="F126" s="4" t="inlineStr">
+      <c r="G126" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="V126" s="4" t="inlineStr">
+      <c r="W126" s="4" t="inlineStr">
         <is>
           <t>The threshold argument cuts both ways, and the page should show that rather than resolve it.</t>
         </is>
@@ -4692,12 +4808,12 @@
           <t>Most states already put a structural check on clemency and those systems function.</t>
         </is>
       </c>
-      <c r="F127" s="4" t="inlineStr">
+      <c r="G127" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="V127" s="4" t="inlineStr">
+      <c r="W127" s="4" t="inlineStr">
         <is>
           <t>The best evidence that a check is workable, and the rebuttal correctly identifies that it is not this check.</t>
         </is>
@@ -4722,12 +4838,12 @@
           <t>Article II grants the power without a congressional role, and the Supreme Court has held it is not subject to legislative control, so this requires a constitutional amendment rather than a statute.</t>
         </is>
       </c>
-      <c r="F128" s="4" t="inlineStr">
+      <c r="G128" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="V128" s="4" t="inlineStr">
+      <c r="W128" s="4" t="inlineStr">
         <is>
           <t>Decisive against a statute and not against the belief as written, which is why it is a component question rather than a refutation.</t>
         </is>
@@ -4752,12 +4868,12 @@
           <t>Clemency exists to correct injustices the political branches will not, so a legislative veto would remove precisely the unpopular mercy the power is for.</t>
         </is>
       </c>
-      <c r="F129" s="4" t="inlineStr">
+      <c r="G129" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="V129" s="4" t="inlineStr">
+      <c r="W129" s="4" t="inlineStr">
         <is>
           <t>The strongest argument on the page in principle, and the two-thirds threshold is a real answer to it.</t>
         </is>
@@ -4782,12 +4898,12 @@
           <t>A reversible pardon is not a pardon: nobody could rely on it, and the power to settle whole classes of cases through amnesties would end.</t>
         </is>
       </c>
-      <c r="F130" s="4" t="inlineStr">
+      <c r="G130" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="V130" s="4" t="inlineStr">
+      <c r="W130" s="4" t="inlineStr">
         <is>
           <t>A serious design objection with an obvious drafting answer that no proposal has adopted.</t>
         </is>
@@ -4812,12 +4928,12 @@
           <t>A narrower fix reaches the actual abuse without touching the power: prosecute bribes paid for pardons, and require the review file to be published.</t>
         </is>
       </c>
-      <c r="F131" s="4" t="inlineStr">
+      <c r="G131" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="V131" s="4" t="inlineStr">
+      <c r="W131" s="4" t="inlineStr">
         <is>
           <t>The most practical alternative, and the response is that it has never actually been used.</t>
         </is>
@@ -4842,17 +4958,17 @@
           <t>58 percent of Americans said the president grants too many pardons and 56 percent supported a constitutional amendment limiting the power, with Democrats at 76 percent and Republicans at 34 percent.</t>
         </is>
       </c>
-      <c r="F132" s="4" t="inlineStr">
+      <c r="G132" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="O132" s="5" t="inlineStr">
+      <c r="P132" s="5" t="inlineStr">
         <is>
           <t>statistics</t>
         </is>
       </c>
-      <c r="V132" s="4" t="inlineStr">
+      <c r="W132" s="4" t="inlineStr">
         <is>
           <t>Real support, and the crosstabs are the reason to doubt the amendment path.</t>
         </is>
@@ -4877,17 +4993,17 @@
           <t>A federal judge unsealed a redacted opinion describing a Justice Department investigation into an alleged bribery-for-pardon scheme; no names were released and nobody was charged.</t>
         </is>
       </c>
-      <c r="F133" s="4" t="inlineStr">
+      <c r="G133" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="O133" s="5" t="inlineStr">
+      <c r="P133" s="5" t="inlineStr">
         <is>
           <t>record</t>
         </is>
       </c>
-      <c r="V133" s="4" t="inlineStr">
+      <c r="W133" s="4" t="inlineStr">
         <is>
           <t>Enough to show the risk is not hypothetical; not enough to show it materialized.</t>
         </is>
@@ -4912,17 +5028,17 @@
           <t>Independent boards hold or gate the clemency power in more than a dozen states, and those systems operate continuously.</t>
         </is>
       </c>
-      <c r="F134" s="4" t="inlineStr">
+      <c r="G134" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="O134" s="5" t="inlineStr">
+      <c r="P134" s="5" t="inlineStr">
         <is>
           <t>statistics</t>
         </is>
       </c>
-      <c r="V134" s="4" t="inlineStr">
+      <c r="W134" s="4" t="inlineStr">
         <is>
           <t>Strong precedent for a check; weak precedent for this particular check.</t>
         </is>
@@ -4947,17 +5063,17 @@
           <t>The Supreme Court held that the pardon power is not subject to legislative control and that Congress can neither limit the effect of a pardon nor exclude any class of offenders from it.</t>
         </is>
       </c>
-      <c r="F135" s="4" t="inlineStr">
+      <c r="G135" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="O135" s="5" t="inlineStr">
+      <c r="P135" s="5" t="inlineStr">
         <is>
           <t>record</t>
         </is>
       </c>
-      <c r="V135" s="4" t="inlineStr">
+      <c r="W135" s="4" t="inlineStr">
         <is>
           <t>Decisive on the mechanism and silent on the belief as stated.</t>
         </is>
@@ -4982,17 +5098,17 @@
           <t>Proposals to let Congress nullify pardons by two-thirds vote have been introduced with bipartisan sponsorship and have not moved out of committee.</t>
         </is>
       </c>
-      <c r="F136" s="4" t="inlineStr">
+      <c r="G136" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="O136" s="5" t="inlineStr">
+      <c r="P136" s="5" t="inlineStr">
         <is>
           <t>record</t>
         </is>
       </c>
-      <c r="V136" s="4" t="inlineStr">
+      <c r="W136" s="4" t="inlineStr">
         <is>
           <t>Listed on the weakening side because it is argued that way, and its linkage page is where the relevance fails.</t>
         </is>
@@ -5017,12 +5133,12 @@
           <t>In the decade after an override mechanism exists, the share of clemency grants that bypass the Justice Department review process falls.</t>
         </is>
       </c>
-      <c r="F137" s="4" t="inlineStr">
+      <c r="G137" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="V137" s="4" t="inlineStr">
+      <c r="W137" s="4" t="inlineStr">
         <is>
           <t>The best-measured prediction on the page.</t>
         </is>
@@ -5047,12 +5163,12 @@
           <t>The override is never used, because two thirds of both chambers cannot be assembled against a president whose party holds a third of either one.</t>
         </is>
       </c>
-      <c r="F138" s="4" t="inlineStr">
+      <c r="G138" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="V138" s="4" t="inlineStr">
+      <c r="W138" s="4" t="inlineStr">
         <is>
           <t>The most likely outcome, and the deterrence rebuttal is real but unmeasurable.</t>
         </is>
@@ -5077,12 +5193,12 @@
           <t>Presidents shift to pre-emptive and blanket pardons issued on the last day, where an override vote arrives after the recipients have scattered.</t>
         </is>
       </c>
-      <c r="F139" s="4" t="inlineStr">
+      <c r="G139" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="V139" s="4" t="inlineStr">
+      <c r="W139" s="4" t="inlineStr">
         <is>
           <t>Predicts the adaptation, and names the drafting fix in its own rebuttal.</t>
         </is>
@@ -5107,7 +5223,7 @@
           <t>Pardons granted to the president's own circle become reviewable rather than final.</t>
         </is>
       </c>
-      <c r="F140" s="4" t="inlineStr">
+      <c r="G140" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
@@ -5132,7 +5248,7 @@
           <t>The prospect of a vote deters the grants that could not survive one.</t>
         </is>
       </c>
-      <c r="F141" s="4" t="inlineStr">
+      <c r="G141" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
@@ -5157,7 +5273,7 @@
           <t>Clemency decisions return to the Justice Department review process that screens petitions on the merits.</t>
         </is>
       </c>
-      <c r="F142" s="4" t="inlineStr">
+      <c r="G142" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
@@ -5182,7 +5298,7 @@
           <t>Unpopular but just clemency becomes harder, which is the case the power exists for.</t>
         </is>
       </c>
-      <c r="F143" s="4" t="inlineStr">
+      <c r="G143" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
@@ -5207,7 +5323,7 @@
           <t>Recipients cannot rely on a pardon, so it settles nothing until the override window closes.</t>
         </is>
       </c>
-      <c r="F144" s="4" t="inlineStr">
+      <c r="G144" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
@@ -5232,7 +5348,7 @@
           <t>Every controversial clemency decision becomes another partisan floor fight.</t>
         </is>
       </c>
-      <c r="F145" s="4" t="inlineStr">
+      <c r="G145" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
@@ -5257,12 +5373,12 @@
           <t>Some pardons are granted for the president's private benefit.</t>
         </is>
       </c>
-      <c r="F146" s="4" t="inlineStr">
+      <c r="G146" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="V146" s="4" t="inlineStr">
+      <c r="W146" s="4" t="inlineStr">
         <is>
           <t>The pattern is documented and the characterization is inference. It is the firmest of the three components.</t>
         </is>
@@ -5287,12 +5403,12 @@
           <t>A congressional override would deter or reverse the grants at issue.</t>
         </is>
       </c>
-      <c r="F147" s="4" t="inlineStr">
+      <c r="G147" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="V147" s="4" t="inlineStr">
+      <c r="W147" s="4" t="inlineStr">
         <is>
           <t>The weakest load-bearing component on this page, and the one that caps it. The prediction table says why.</t>
         </is>
@@ -5317,12 +5433,12 @@
           <t>An override mechanism can be enacted.</t>
         </is>
       </c>
-      <c r="F148" s="4" t="inlineStr">
+      <c r="G148" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="V148" s="4" t="inlineStr">
+      <c r="W148" s="4" t="inlineStr">
         <is>
           <t>Argued down more effectively than the constitutional objection is usually argued, and not the component that caps this page.</t>
         </is>
@@ -5347,7 +5463,7 @@
           <t>Both sides agree that selling a pardon is a crime and that nobody currently checks whether one was sold.</t>
         </is>
       </c>
-      <c r="F149" s="4" t="inlineStr">
+      <c r="G149" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
@@ -5372,7 +5488,7 @@
           <t>Require the Pardon Attorney's file and the president's stated reasons to be published for every grant, and let Congress reverse a grant within sixty days by two-thirds vote, adopted as a constitutional amendment.</t>
         </is>
       </c>
-      <c r="F150" s="4" t="inlineStr">
+      <c r="G150" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
@@ -5397,7 +5513,7 @@
           <t>The pardon power should be abolished and replaced with a clemency commission whose decisions the president may only ratify.</t>
         </is>
       </c>
-      <c r="F151" s="4" t="inlineStr">
+      <c r="G151" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
@@ -5422,7 +5538,7 @@
           <t>A president should be barred from pardoning relatives, donors and co-defendants, with no general override.</t>
         </is>
       </c>
-      <c r="F152" s="4" t="inlineStr">
+      <c r="G152" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
@@ -5447,42 +5563,42 @@
           <t>Citizens need government decisions made on the merits rather than on what enriches the decider.</t>
         </is>
       </c>
-      <c r="F153" s="4" t="inlineStr">
+      <c r="G153" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="H153" s="4" t="inlineStr">
+      <c r="I153" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="L153" s="5" t="inlineStr">
+      <c r="M153" s="5" t="inlineStr">
         <is>
           <t>Fairness</t>
         </is>
       </c>
-      <c r="M153" s="4" t="inlineStr">
+      <c r="N153" s="4" t="inlineStr">
         <is>
           <t>Share of official decisions made by an official holding a personal financial stake in the outcome</t>
         </is>
       </c>
-      <c r="R153" s="4" t="inlineStr">
+      <c r="S153" s="4" t="inlineStr">
         <is>
           <t>Falls after the rule takes effect</t>
         </is>
       </c>
-      <c r="S153" s="4" t="inlineStr">
+      <c r="T153" s="4" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="T153" s="4" t="inlineStr">
+      <c r="U153" s="4" t="inlineStr">
         <is>
           <t>Not measured systematically; 78 members of one Congress filed late transaction reports (Insider, 2023)</t>
         </is>
       </c>
-      <c r="V153" s="4" t="inlineStr">
+      <c r="W153" s="4" t="inlineStr">
         <is>
           <t>Near the top of any hierarchy of public needs, and contested only at the edges of its application.</t>
         </is>
@@ -5507,42 +5623,42 @@
           <t>Investors need markets where nobody trades on information the government has not released.</t>
         </is>
       </c>
-      <c r="F154" s="4" t="inlineStr">
+      <c r="G154" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="H154" s="4" t="inlineStr">
+      <c r="I154" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="L154" s="5" t="inlineStr">
+      <c r="M154" s="5" t="inlineStr">
         <is>
           <t>Free enterprise</t>
         </is>
       </c>
-      <c r="M154" s="4" t="inlineStr">
+      <c r="N154" s="4" t="inlineStr">
         <is>
           <t>Abnormal returns on officials' trades placed before government announcements</t>
         </is>
       </c>
-      <c r="R154" s="4" t="inlineStr">
+      <c r="S154" s="4" t="inlineStr">
         <is>
           <t>Fall to zero</t>
         </is>
       </c>
-      <c r="S154" s="4" t="inlineStr">
+      <c r="T154" s="4" t="inlineStr">
         <is>
           <t>Persist at their current level</t>
         </is>
       </c>
-      <c r="T154" s="4" t="inlineStr">
+      <c r="U154" s="4" t="inlineStr">
         <is>
           <t>Mixed: 85 basis points a month for senators over 1993 to 1998 (Ziobrowski 2004); no advantage found over 2012 to 2020 (Belmont 2022); 3 to 5 percent before legislative events over 2014 to 2021 (Zhou 2025)</t>
         </is>
       </c>
-      <c r="V154" s="4" t="inlineStr">
+      <c r="W154" s="4" t="inlineStr">
         <is>
           <t>Valid and recognized; the disputed part is how much is actually at stake.</t>
         </is>
@@ -5567,42 +5683,42 @@
           <t>Voters need enough information to judge whether an official is compromised.</t>
         </is>
       </c>
-      <c r="F155" s="4" t="inlineStr">
+      <c r="G155" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="H155" s="4" t="inlineStr">
+      <c r="I155" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="L155" s="5" t="inlineStr">
+      <c r="M155" s="5" t="inlineStr">
         <is>
           <t>Accountability</t>
         </is>
       </c>
-      <c r="M155" s="4" t="inlineStr">
+      <c r="N155" s="4" t="inlineStr">
         <is>
           <t>Share of an official's income sources, debts and foreign ties visible in public filings</t>
         </is>
       </c>
-      <c r="R155" s="4" t="inlineStr">
+      <c r="S155" s="4" t="inlineStr">
         <is>
           <t>Rises to near complete</t>
         </is>
       </c>
-      <c r="S155" s="4" t="inlineStr">
+      <c r="T155" s="4" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="T155" s="4" t="inlineStr">
+      <c r="U155" s="4" t="inlineStr">
         <is>
           <t>Assets and income are disclosed in broad ranges; foreign income, lender identity and effective tax rate are not (OGE Public Financial Disclosure Guide, 2024)</t>
         </is>
       </c>
-      <c r="V155" s="4" t="inlineStr">
+      <c r="W155" s="4" t="inlineStr">
         <is>
           <t>Strong as a need, contested in how far into a family it reaches.</t>
         </is>
@@ -5627,42 +5743,42 @@
           <t>Crime victims and the public need clemency decisions that can be reviewed rather than traded.</t>
         </is>
       </c>
-      <c r="F156" s="4" t="inlineStr">
+      <c r="G156" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="H156" s="4" t="inlineStr">
+      <c r="I156" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="L156" s="5" t="inlineStr">
+      <c r="M156" s="5" t="inlineStr">
         <is>
           <t>Rule of law</t>
         </is>
       </c>
-      <c r="M156" s="4" t="inlineStr">
+      <c r="N156" s="4" t="inlineStr">
         <is>
           <t>Share of clemency grants that went through the Justice Department review process</t>
         </is>
       </c>
-      <c r="R156" s="4" t="inlineStr">
+      <c r="S156" s="4" t="inlineStr">
         <is>
           <t>Rises toward the historical norm</t>
         </is>
       </c>
-      <c r="S156" s="4" t="inlineStr">
+      <c r="T156" s="4" t="inlineStr">
         <is>
           <t>Stays at recent lows</t>
         </is>
       </c>
-      <c r="T156" s="4" t="inlineStr">
+      <c r="U156" s="4" t="inlineStr">
         <is>
           <t>About 93 percent of one administration's first-term grants bypassed the Pardon Attorney (Goldsmith and Gluck, 2020)</t>
         </is>
       </c>
-      <c r="V156" s="4" t="inlineStr">
+      <c r="W156" s="4" t="inlineStr">
         <is>
           <t>A real need with an unusually direct constitutional obstacle, which is argued on the belief page rather than here.</t>
         </is>
@@ -5687,42 +5803,42 @@
           <t>Officials need rules they can follow without a lawyer and without violating them by accident.</t>
         </is>
       </c>
-      <c r="F157" s="4" t="inlineStr">
+      <c r="G157" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="H157" s="4" t="inlineStr">
+      <c r="I157" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="L157" s="5" t="inlineStr">
+      <c r="M157" s="5" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="M157" s="4" t="inlineStr">
+      <c r="N157" s="4" t="inlineStr">
         <is>
           <t>Number of inadvertent reporting violations per year</t>
         </is>
       </c>
-      <c r="R157" s="4" t="inlineStr">
+      <c r="S157" s="4" t="inlineStr">
         <is>
           <t>Falls toward zero</t>
         </is>
       </c>
-      <c r="S157" s="4" t="inlineStr">
+      <c r="T157" s="4" t="inlineStr">
         <is>
           <t>Stays at current levels</t>
         </is>
       </c>
-      <c r="T157" s="4" t="inlineStr">
+      <c r="U157" s="4" t="inlineStr">
         <is>
           <t>78 members of the 117th Congress filed late under the STOCK Act (Insider, 2023)</t>
         </is>
       </c>
-      <c r="V157" s="4" t="inlineStr">
+      <c r="W157" s="4" t="inlineStr">
         <is>
           <t>Valid and usually ignored, and it is the interest a bright-line ban serves best.</t>
         </is>
@@ -5747,42 +5863,42 @@
           <t>Officials and their families need the same property rights and privacy as other citizens.</t>
         </is>
       </c>
-      <c r="F158" s="4" t="inlineStr">
+      <c r="G158" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="H158" s="4" t="inlineStr">
+      <c r="I158" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="L158" s="5" t="inlineStr">
+      <c r="M158" s="5" t="inlineStr">
         <is>
           <t>Liberty</t>
         </is>
       </c>
-      <c r="M158" s="4" t="inlineStr">
+      <c r="N158" s="4" t="inlineStr">
         <is>
           <t>Whether a restriction reaches only the official or also family members who hold no office</t>
         </is>
       </c>
-      <c r="R158" s="4" t="inlineStr">
+      <c r="S158" s="4" t="inlineStr">
         <is>
           <t>Restrictions stay narrow and are compensated</t>
         </is>
       </c>
-      <c r="S158" s="4" t="inlineStr">
+      <c r="T158" s="4" t="inlineStr">
         <is>
           <t>Restrictions extend to family and are not</t>
         </is>
       </c>
-      <c r="T158" s="4" t="inlineStr">
+      <c r="U158" s="4" t="inlineStr">
         <is>
           <t>Proposals vary: most reach the spouse and dependent children, and the Federal Reserve rule reaches immediate family</t>
         </is>
       </c>
-      <c r="V158" s="4" t="inlineStr">
+      <c r="W158" s="4" t="inlineStr">
         <is>
           <t>Valid in general, weakest exactly where it is invoked most: a voluntary office with known conditions.</t>
         </is>
@@ -5807,42 +5923,42 @@
           <t>The country needs capable people of ordinary means willing to serve, not only the wealthy and the indifferent.</t>
         </is>
       </c>
-      <c r="F159" s="4" t="inlineStr">
+      <c r="G159" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="H159" s="4" t="inlineStr">
+      <c r="I159" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="L159" s="5" t="inlineStr">
+      <c r="M159" s="5" t="inlineStr">
         <is>
           <t>Opportunity</t>
         </is>
       </c>
-      <c r="M159" s="4" t="inlineStr">
+      <c r="N159" s="4" t="inlineStr">
         <is>
           <t>Net worth distribution of candidates and of incoming members</t>
         </is>
       </c>
-      <c r="R159" s="4" t="inlineStr">
+      <c r="S159" s="4" t="inlineStr">
         <is>
           <t>Unchanged or more representative after the rule</t>
         </is>
       </c>
-      <c r="S159" s="4" t="inlineStr">
+      <c r="T159" s="4" t="inlineStr">
         <is>
           <t>Shifts toward the already-wealthy</t>
         </is>
       </c>
-      <c r="T159" s="4" t="inlineStr">
+      <c r="U159" s="4" t="inlineStr">
         <is>
           <t>Congress is already far wealthier than the population it represents</t>
         </is>
       </c>
-      <c r="V159" s="4" t="inlineStr">
+      <c r="W159" s="4" t="inlineStr">
         <is>
           <t>A real need, and the evidence runs against the version of it used in this debate.</t>
         </is>
@@ -5867,42 +5983,42 @@
           <t>The president needs a clemency power the legislature cannot veto.</t>
         </is>
       </c>
-      <c r="F160" s="4" t="inlineStr">
+      <c r="G160" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="H160" s="4" t="inlineStr">
+      <c r="I160" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="L160" s="5" t="inlineStr">
+      <c r="M160" s="5" t="inlineStr">
         <is>
           <t>Rule of law</t>
         </is>
       </c>
-      <c r="M160" s="4" t="inlineStr">
+      <c r="N160" s="4" t="inlineStr">
         <is>
           <t>Whether unpopular but just clemency grants continue to be made</t>
         </is>
       </c>
-      <c r="R160" s="4" t="inlineStr">
+      <c r="S160" s="4" t="inlineStr">
         <is>
           <t>They continue</t>
         </is>
       </c>
-      <c r="S160" s="4" t="inlineStr">
+      <c r="T160" s="4" t="inlineStr">
         <is>
           <t>They stop</t>
         </is>
       </c>
-      <c r="T160" s="4" t="inlineStr">
+      <c r="U160" s="4" t="inlineStr">
         <is>
           <t>Mass commutations of drug sentences were unpopular when granted and are now widely defended</t>
         </is>
       </c>
-      <c r="V160" s="4" t="inlineStr">
+      <c r="W160" s="4" t="inlineStr">
         <is>
           <t>Strong on the constitutional text, weaker as a claim that the current design is working.</t>
         </is>
@@ -5927,42 +6043,42 @@
           <t>Some officeholders want to keep using their position and their families to make money.</t>
         </is>
       </c>
-      <c r="F161" s="4" t="inlineStr">
+      <c r="G161" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="H161" s="4" t="inlineStr">
+      <c r="I161" s="4" t="inlineStr">
         <is>
           <t>public-office-usable-private</t>
         </is>
       </c>
-      <c r="L161" s="5" t="inlineStr">
+      <c r="M161" s="5" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="M161" s="4" t="inlineStr">
+      <c r="N161" s="4" t="inlineStr">
         <is>
           <t>Income officials and their relatives earn from activities that depend on the office</t>
         </is>
       </c>
-      <c r="R161" s="4" t="inlineStr">
+      <c r="S161" s="4" t="inlineStr">
         <is>
           <t>Falls</t>
         </is>
       </c>
-      <c r="S161" s="4" t="inlineStr">
+      <c r="T161" s="4" t="inlineStr">
         <is>
           <t>Continues</t>
         </is>
       </c>
-      <c r="T161" s="4" t="inlineStr">
+      <c r="U161" s="4" t="inlineStr">
         <is>
           <t>Not measured directly; campaign committees paid $1.3 million in wages to candidates' relatives in one cycle (OpenSecrets, 2020)</t>
         </is>
       </c>
-      <c r="V161" s="4" t="inlineStr">
+      <c r="W161" s="4" t="inlineStr">
         <is>
           <t>Held by some and valid by almost no standard. It is on the page so that the scoring of a bad interest is visible rather than assumed.</t>
         </is>
@@ -5982,32 +6098,32 @@
           <t>driver</t>
         </is>
       </c>
-      <c r="F162" s="4" t="inlineStr">
+      <c r="G162" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G162" s="4" t="inlineStr">
+      <c r="H162" s="4" t="inlineStr">
         <is>
           <t>citizens-need-government-decisions</t>
         </is>
       </c>
-      <c r="H162" s="4" t="inlineStr">
+      <c r="I162" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J162" s="5" t="inlineStr">
+      <c r="K162" s="5" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="U162" s="4" t="inlineStr">
+      <c r="V162" s="4" t="inlineStr">
         <is>
           <t>Support that tracked partisan control rather than institutional distrust would point to a different driver.</t>
         </is>
       </c>
-      <c r="V162" s="4" t="inlineStr">
+      <c r="W162" s="4" t="inlineStr">
         <is>
           <t>Drives the position as strongly as any interest on the page, and the alternative explanation is hard to separate from it.</t>
         </is>
@@ -6027,32 +6143,32 @@
           <t>driver</t>
         </is>
       </c>
-      <c r="F163" s="4" t="inlineStr">
+      <c r="G163" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G163" s="4" t="inlineStr">
+      <c r="H163" s="4" t="inlineStr">
         <is>
           <t>investors-need-markets-where</t>
         </is>
       </c>
-      <c r="H163" s="4" t="inlineStr">
+      <c r="I163" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J163" s="5" t="inlineStr">
+      <c r="K163" s="5" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="U163" s="4" t="inlineStr">
+      <c r="V163" s="4" t="inlineStr">
         <is>
           <t>A coalition that kept its size with the market-integrity argument removed would show this interest is decorative.</t>
         </is>
       </c>
-      <c r="V163" s="4" t="inlineStr">
+      <c r="W163" s="4" t="inlineStr">
         <is>
           <t>Valid but largely decorative here: real interest, small share of what drives the position.</t>
         </is>
@@ -6072,32 +6188,32 @@
           <t>driver</t>
         </is>
       </c>
-      <c r="F164" s="4" t="inlineStr">
+      <c r="G164" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G164" s="4" t="inlineStr">
+      <c r="H164" s="4" t="inlineStr">
         <is>
           <t>voters-need-enough-information</t>
         </is>
       </c>
-      <c r="H164" s="4" t="inlineStr">
+      <c r="I164" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J164" s="5" t="inlineStr">
+      <c r="K164" s="5" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="U164" s="4" t="inlineStr">
+      <c r="V164" s="4" t="inlineStr">
         <is>
           <t>Whether transparency advocates would accept enforced disclosure instead of a ban is the test, and most say they would not.</t>
         </is>
       </c>
-      <c r="V164" s="4" t="inlineStr">
+      <c r="W164" s="4" t="inlineStr">
         <is>
           <t>A strong driver, and partly the same driver as the first interest on the page.</t>
         </is>
@@ -6117,32 +6233,32 @@
           <t>driver</t>
         </is>
       </c>
-      <c r="F165" s="4" t="inlineStr">
+      <c r="G165" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G165" s="4" t="inlineStr">
+      <c r="H165" s="4" t="inlineStr">
         <is>
           <t>officials-need-rules-can</t>
         </is>
       </c>
-      <c r="H165" s="4" t="inlineStr">
+      <c r="I165" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J165" s="5" t="inlineStr">
+      <c r="K165" s="5" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="U165" s="4" t="inlineStr">
+      <c r="V165" s="4" t="inlineStr">
         <is>
           <t>If officials who support a ban stopped doing so when preclearance was added, this interest would be shown to drive them.</t>
         </is>
       </c>
-      <c r="V165" s="4" t="inlineStr">
+      <c r="W165" s="4" t="inlineStr">
         <is>
           <t>A minor driver of the public position and a major one inside the institution.</t>
         </is>
@@ -6162,32 +6278,32 @@
           <t>driver</t>
         </is>
       </c>
-      <c r="F166" s="4" t="inlineStr">
+      <c r="G166" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G166" s="4" t="inlineStr">
+      <c r="H166" s="4" t="inlineStr">
         <is>
           <t>officials-families-need-same</t>
         </is>
       </c>
-      <c r="H166" s="4" t="inlineStr">
+      <c r="I166" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J166" s="5" t="inlineStr">
+      <c r="K166" s="5" t="inlineStr">
         <is>
           <t>Opposition</t>
         </is>
       </c>
-      <c r="U166" s="4" t="inlineStr">
+      <c r="V166" s="4" t="inlineStr">
         <is>
           <t>Opposition as strong among members with no individual holdings would point to principle rather than interest.</t>
         </is>
       </c>
-      <c r="V166" s="4" t="inlineStr">
+      <c r="W166" s="4" t="inlineStr">
         <is>
           <t>Stated first and predicts the position well, which is what a real driver looks like even when the stated principle is inconsistently applied.</t>
         </is>
@@ -6207,32 +6323,32 @@
           <t>driver</t>
         </is>
       </c>
-      <c r="F167" s="4" t="inlineStr">
+      <c r="G167" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G167" s="4" t="inlineStr">
+      <c r="H167" s="4" t="inlineStr">
         <is>
           <t>country-needs-capable-people</t>
         </is>
       </c>
-      <c r="H167" s="4" t="inlineStr">
+      <c r="I167" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J167" s="5" t="inlineStr">
+      <c r="K167" s="5" t="inlineStr">
         <is>
           <t>Opposition</t>
         </is>
       </c>
-      <c r="U167" s="4" t="inlineStr">
+      <c r="V167" s="4" t="inlineStr">
         <is>
           <t>Evidence that candidate recruitment fell in a jurisdiction after a holdings rule would show this interest drives the position.</t>
         </is>
       </c>
-      <c r="V167" s="4" t="inlineStr">
+      <c r="W167" s="4" t="inlineStr">
         <is>
           <t>Weak as a driver: asserted often, never demonstrated.</t>
         </is>
@@ -6252,32 +6368,32 @@
           <t>driver</t>
         </is>
       </c>
-      <c r="F168" s="4" t="inlineStr">
+      <c r="G168" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G168" s="4" t="inlineStr">
+      <c r="H168" s="4" t="inlineStr">
         <is>
           <t>some-officeholders-want-keep</t>
         </is>
       </c>
-      <c r="H168" s="4" t="inlineStr">
+      <c r="I168" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="J168" s="5" t="inlineStr">
+      <c r="K168" s="5" t="inlineStr">
         <is>
           <t>Opposition</t>
         </is>
       </c>
-      <c r="U168" s="4" t="inlineStr">
+      <c r="V168" s="4" t="inlineStr">
         <is>
           <t>Opposition that was uncorrelated with trading volume would show this interest is not the driver.</t>
         </is>
       </c>
-      <c r="V168" s="4" t="inlineStr">
+      <c r="W168" s="4" t="inlineStr">
         <is>
           <t>Drives a small number of positions strongly, which is the shape the evidence supports and no more than that.</t>
         </is>
@@ -6297,32 +6413,32 @@
           <t>driver</t>
         </is>
       </c>
-      <c r="F169" s="4" t="inlineStr">
+      <c r="G169" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="G169" s="4" t="inlineStr">
+      <c r="H169" s="4" t="inlineStr">
         <is>
           <t>crime-victims-public-need</t>
         </is>
       </c>
-      <c r="H169" s="4" t="inlineStr">
+      <c r="I169" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="J169" s="5" t="inlineStr">
+      <c r="K169" s="5" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="U169" s="4" t="inlineStr">
+      <c r="V169" s="4" t="inlineStr">
         <is>
           <t>Support that stayed constant across changes of administration would show a stable interest rather than a partisan one.</t>
         </is>
       </c>
-      <c r="V169" s="4" t="inlineStr">
+      <c r="W169" s="4" t="inlineStr">
         <is>
           <t>Real, and the partisan tracking is strong enough that the driver page scores lower than the interest page does.</t>
         </is>
@@ -6342,32 +6458,32 @@
           <t>driver</t>
         </is>
       </c>
-      <c r="F170" s="4" t="inlineStr">
+      <c r="G170" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="G170" s="4" t="inlineStr">
+      <c r="H170" s="4" t="inlineStr">
         <is>
           <t>president-needs-clemency-power</t>
         </is>
       </c>
-      <c r="H170" s="4" t="inlineStr">
+      <c r="I170" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="J170" s="5" t="inlineStr">
+      <c r="K170" s="5" t="inlineStr">
         <is>
           <t>Opposition</t>
         </is>
       </c>
-      <c r="U170" s="4" t="inlineStr">
+      <c r="V170" s="4" t="inlineStr">
         <is>
           <t>Whether the same officials took this position under the other party's president is the test, and mostly they did not.</t>
         </is>
       </c>
-      <c r="V170" s="4" t="inlineStr">
+      <c r="W170" s="4" t="inlineStr">
         <is>
           <t>Genuinely principled among scholars and almost perfectly partisan among officials, which is why it scores where it does.</t>
         </is>
@@ -6387,37 +6503,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F171" s="4" t="inlineStr">
+      <c r="G171" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G171" s="4" t="inlineStr">
+      <c r="H171" s="4" t="inlineStr">
         <is>
           <t>members-regularly-trade-industries</t>
         </is>
       </c>
-      <c r="H171" s="4" t="inlineStr">
+      <c r="I171" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I171" s="5" t="inlineStr">
+      <c r="J171" s="5" t="inlineStr">
         <is>
           <t>Argument</t>
         </is>
       </c>
-      <c r="J171" s="5" t="inlineStr">
+      <c r="K171" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="U171" s="4" t="inlineStr">
+      <c r="V171" s="4" t="inlineStr">
         <is>
           <t>The overlap is the conflict the ban targets, so if it exists the ban has something to remove.</t>
         </is>
       </c>
-      <c r="V171" s="4" t="inlineStr">
+      <c r="W171" s="4" t="inlineStr">
         <is>
           <t>High linkage: the row and the belief are about the same thing.</t>
         </is>
@@ -6437,37 +6553,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F172" s="4" t="inlineStr">
+      <c r="G172" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G172" s="4" t="inlineStr">
+      <c r="H172" s="4" t="inlineStr">
         <is>
           <t>disclosure-has-failed-check</t>
         </is>
       </c>
-      <c r="H172" s="4" t="inlineStr">
+      <c r="I172" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I172" s="5" t="inlineStr">
+      <c r="J172" s="5" t="inlineStr">
         <is>
           <t>Argument</t>
         </is>
       </c>
-      <c r="J172" s="5" t="inlineStr">
+      <c r="K172" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="U172" s="4" t="inlineStr">
+      <c r="V172" s="4" t="inlineStr">
         <is>
           <t>A ban is only better than disclosure if disclosure is failing, which this row establishes and the rest of the tree has to complete.</t>
         </is>
       </c>
-      <c r="V172" s="4" t="inlineStr">
+      <c r="W172" s="4" t="inlineStr">
         <is>
           <t>Good linkage with a real gap: it rules out the alternative without establishing the proposal.</t>
         </is>
@@ -6487,37 +6603,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F173" s="4" t="inlineStr">
+      <c r="G173" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G173" s="4" t="inlineStr">
+      <c r="H173" s="4" t="inlineStr">
         <is>
           <t>holdings-ban-removes-conflict</t>
         </is>
       </c>
-      <c r="H173" s="4" t="inlineStr">
+      <c r="I173" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I173" s="5" t="inlineStr">
+      <c r="J173" s="5" t="inlineStr">
         <is>
           <t>Argument</t>
         </is>
       </c>
-      <c r="J173" s="5" t="inlineStr">
+      <c r="K173" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="U173" s="4" t="inlineStr">
+      <c r="V173" s="4" t="inlineStr">
         <is>
           <t>If the conflict is structural, a structural remedy reaches it and an intent-based one does not.</t>
         </is>
       </c>
-      <c r="V173" s="4" t="inlineStr">
+      <c r="W173" s="4" t="inlineStr">
         <is>
           <t>The most direct linkage on the page.</t>
         </is>
@@ -6537,37 +6653,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F174" s="4" t="inlineStr">
+      <c r="G174" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G174" s="4" t="inlineStr">
+      <c r="H174" s="4" t="inlineStr">
         <is>
           <t>federal-reserve-barred-its</t>
         </is>
       </c>
-      <c r="H174" s="4" t="inlineStr">
+      <c r="I174" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I174" s="5" t="inlineStr">
+      <c r="J174" s="5" t="inlineStr">
         <is>
           <t>Argument</t>
         </is>
       </c>
-      <c r="J174" s="5" t="inlineStr">
+      <c r="K174" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="U174" s="4" t="inlineStr">
+      <c r="V174" s="4" t="inlineStr">
         <is>
           <t>A comparable institution operating under the rule shows the rule is administrable, which is one of the belief's components.</t>
         </is>
       </c>
-      <c r="V174" s="4" t="inlineStr">
+      <c r="W174" s="4" t="inlineStr">
         <is>
           <t>Bears on feasibility rather than on effect, which is a real but narrower contribution.</t>
         </is>
@@ -6587,37 +6703,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F175" s="4" t="inlineStr">
+      <c r="G175" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G175" s="4" t="inlineStr">
+      <c r="H175" s="4" t="inlineStr">
         <is>
           <t>trading-closed-briefing-almost</t>
         </is>
       </c>
-      <c r="H175" s="4" t="inlineStr">
+      <c r="I175" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I175" s="5" t="inlineStr">
+      <c r="J175" s="5" t="inlineStr">
         <is>
           <t>Argument</t>
         </is>
       </c>
-      <c r="J175" s="5" t="inlineStr">
+      <c r="K175" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="U175" s="4" t="inlineStr">
+      <c r="V175" s="4" t="inlineStr">
         <is>
           <t>If the conduct cannot be prosecuted even when it occurs, the choice is between a status rule and nothing.</t>
         </is>
       </c>
-      <c r="V175" s="4" t="inlineStr">
+      <c r="W175" s="4" t="inlineStr">
         <is>
           <t>Strong linkage, and the rebuttal is the most important sentence on this page.</t>
         </is>
@@ -6637,37 +6753,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F176" s="4" t="inlineStr">
+      <c r="G176" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G176" s="4" t="inlineStr">
+      <c r="H176" s="4" t="inlineStr">
         <is>
           <t>best-identified-studies-actual</t>
         </is>
       </c>
-      <c r="H176" s="4" t="inlineStr">
+      <c r="I176" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I176" s="5" t="inlineStr">
+      <c r="J176" s="5" t="inlineStr">
         <is>
           <t>Argument</t>
         </is>
       </c>
-      <c r="J176" s="5" t="inlineStr">
+      <c r="K176" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="U176" s="4" t="inlineStr">
+      <c r="V176" s="4" t="inlineStr">
         <is>
           <t>Underperformance would weaken the trading-advantage branch of the tree and leave the voting-conflict branch untouched.</t>
         </is>
       </c>
-      <c r="V176" s="4" t="inlineStr">
+      <c r="W176" s="4" t="inlineStr">
         <is>
           <t>This is the page where the belief's two branches come apart, and the linkage score should show it.</t>
         </is>
@@ -6687,37 +6803,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F177" s="4" t="inlineStr">
+      <c r="G177" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G177" s="4" t="inlineStr">
+      <c r="H177" s="4" t="inlineStr">
         <is>
           <t>ban-official-leaves-conflict</t>
         </is>
       </c>
-      <c r="H177" s="4" t="inlineStr">
+      <c r="I177" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I177" s="5" t="inlineStr">
+      <c r="J177" s="5" t="inlineStr">
         <is>
           <t>Argument</t>
         </is>
       </c>
-      <c r="J177" s="5" t="inlineStr">
+      <c r="K177" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="U177" s="4" t="inlineStr">
+      <c r="V177" s="4" t="inlineStr">
         <is>
           <t>A ban only reduces conflicts if what it covers is not simply replaced by what it does not.</t>
         </is>
       </c>
-      <c r="V177" s="4" t="inlineStr">
+      <c r="W177" s="4" t="inlineStr">
         <is>
           <t>The highest-linkage argument on the disagree side: it strikes the load-bearing component directly.</t>
         </is>
@@ -6737,37 +6853,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F178" s="4" t="inlineStr">
+      <c r="G178" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G178" s="4" t="inlineStr">
+      <c r="H178" s="4" t="inlineStr">
         <is>
           <t>forced-divestiture-imposes-real</t>
         </is>
       </c>
-      <c r="H178" s="4" t="inlineStr">
+      <c r="I178" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I178" s="5" t="inlineStr">
+      <c r="J178" s="5" t="inlineStr">
         <is>
           <t>Argument</t>
         </is>
       </c>
-      <c r="J178" s="5" t="inlineStr">
+      <c r="K178" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="U178" s="4" t="inlineStr">
+      <c r="V178" s="4" t="inlineStr">
         <is>
           <t>Divestiture costs would weaken the belief only if they defeated the rule politically or changed who holds office.</t>
         </is>
       </c>
-      <c r="V178" s="4" t="inlineStr">
+      <c r="W178" s="4" t="inlineStr">
         <is>
           <t>Low linkage: a real cost aimed at the wrong question, and it counts fully in the cost-benefit table instead.</t>
         </is>
@@ -6787,37 +6903,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F179" s="4" t="inlineStr">
+      <c r="G179" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G179" s="4" t="inlineStr">
+      <c r="H179" s="4" t="inlineStr">
         <is>
           <t>congress-will-enforce-ban</t>
         </is>
       </c>
-      <c r="H179" s="4" t="inlineStr">
+      <c r="I179" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I179" s="5" t="inlineStr">
+      <c r="J179" s="5" t="inlineStr">
         <is>
           <t>Argument</t>
         </is>
       </c>
-      <c r="J179" s="5" t="inlineStr">
+      <c r="K179" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="U179" s="4" t="inlineStr">
+      <c r="V179" s="4" t="inlineStr">
         <is>
           <t>If Congress will not enforce it, the rule changes filings rather than conduct.</t>
         </is>
       </c>
-      <c r="V179" s="4" t="inlineStr">
+      <c r="W179" s="4" t="inlineStr">
         <is>
           <t>High linkage and the rebuttal is specific: the enforcement mechanism is not the same one that failed.</t>
         </is>
@@ -6837,37 +6953,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F180" s="4" t="inlineStr">
+      <c r="G180" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G180" s="4" t="inlineStr">
+      <c r="H180" s="4" t="inlineStr">
         <is>
           <t>senators-stock-purchases-beat</t>
         </is>
       </c>
-      <c r="H180" s="4" t="inlineStr">
+      <c r="I180" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I180" s="5" t="inlineStr">
+      <c r="J180" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="J180" s="5" t="inlineStr">
+      <c r="K180" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="U180" s="4" t="inlineStr">
+      <c r="V180" s="4" t="inlineStr">
         <is>
           <t>If senators earned abnormal returns, there was an advantage for a rule to remove, at least then.</t>
         </is>
       </c>
-      <c r="V180" s="4" t="inlineStr">
+      <c r="W180" s="4" t="inlineStr">
         <is>
           <t>Moderate linkage: right quantity, wrong era.</t>
         </is>
@@ -6887,37 +7003,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F181" s="4" t="inlineStr">
+      <c r="G181" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G181" s="4" t="inlineStr">
+      <c r="H181" s="4" t="inlineStr">
         <is>
           <t>trades-placed-before-legislative</t>
         </is>
       </c>
-      <c r="H181" s="4" t="inlineStr">
+      <c r="I181" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I181" s="5" t="inlineStr">
+      <c r="J181" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="J181" s="5" t="inlineStr">
+      <c r="K181" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="U181" s="4" t="inlineStr">
+      <c r="V181" s="4" t="inlineStr">
         <is>
           <t>Abnormal returns around legislative events is the conflict operating, measured in the current regime.</t>
         </is>
       </c>
-      <c r="V181" s="4" t="inlineStr">
+      <c r="W181" s="4" t="inlineStr">
         <is>
           <t>The highest-linkage evidence on the page, and the least replicated.</t>
         </is>
@@ -6937,37 +7053,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F182" s="4" t="inlineStr">
+      <c r="G182" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G182" s="4" t="inlineStr">
+      <c r="H182" s="4" t="inlineStr">
         <is>
           <t>78-members-117th-congress</t>
         </is>
       </c>
-      <c r="H182" s="4" t="inlineStr">
+      <c r="I182" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I182" s="5" t="inlineStr">
+      <c r="J182" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="J182" s="5" t="inlineStr">
+      <c r="K182" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="U182" s="4" t="inlineStr">
+      <c r="V182" s="4" t="inlineStr">
         <is>
           <t>Non-compliance bears on the belief only through the comparison between a ban and the disclosure regime it would replace.</t>
         </is>
       </c>
-      <c r="V182" s="4" t="inlineStr">
+      <c r="W182" s="4" t="inlineStr">
         <is>
           <t>Low linkage, cited constantly, and this page is where that gets priced.</t>
         </is>
@@ -6987,37 +7103,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F183" s="4" t="inlineStr">
+      <c r="G183" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G183" s="4" t="inlineStr">
+      <c r="H183" s="4" t="inlineStr">
         <is>
           <t>131-federal-judges-heard</t>
         </is>
       </c>
-      <c r="H183" s="4" t="inlineStr">
+      <c r="I183" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I183" s="5" t="inlineStr">
+      <c r="J183" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="J183" s="5" t="inlineStr">
+      <c r="K183" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="U183" s="4" t="inlineStr">
+      <c r="V183" s="4" t="inlineStr">
         <is>
           <t>If disclosure fails where a recusal duty backs it, it is unlikely to succeed where nothing does.</t>
         </is>
       </c>
-      <c r="V183" s="4" t="inlineStr">
+      <c r="W183" s="4" t="inlineStr">
         <is>
           <t>Moderate linkage through an analogy that has to carry real weight.</t>
         </is>
@@ -7037,37 +7153,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F184" s="4" t="inlineStr">
+      <c r="G184" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G184" s="4" t="inlineStr">
+      <c r="H184" s="4" t="inlineStr">
         <is>
           <t>federal-reserve-officials-have</t>
         </is>
       </c>
-      <c r="H184" s="4" t="inlineStr">
+      <c r="I184" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I184" s="5" t="inlineStr">
+      <c r="J184" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="J184" s="5" t="inlineStr">
+      <c r="K184" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="U184" s="4" t="inlineStr">
+      <c r="V184" s="4" t="inlineStr">
         <is>
           <t>A working example of the rule bears on whether the rule is workable, which is one component of the belief.</t>
         </is>
       </c>
-      <c r="V184" s="4" t="inlineStr">
+      <c r="W184" s="4" t="inlineStr">
         <is>
           <t>Bears on feasibility, and it substantially repeats the Fed argument above, which is what its uniqueness page is about.</t>
         </is>
@@ -7087,37 +7203,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F185" s="4" t="inlineStr">
+      <c r="G185" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G185" s="4" t="inlineStr">
+      <c r="H185" s="4" t="inlineStr">
         <is>
           <t>congressional-portfolios-underperformed-market</t>
         </is>
       </c>
-      <c r="H185" s="4" t="inlineStr">
+      <c r="I185" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I185" s="5" t="inlineStr">
+      <c r="J185" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="J185" s="5" t="inlineStr">
+      <c r="K185" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="U185" s="4" t="inlineStr">
+      <c r="V185" s="4" t="inlineStr">
         <is>
           <t>Underperformance weakens the trading branch of the belief and is silent on the voting branch.</t>
         </is>
       </c>
-      <c r="V185" s="4" t="inlineStr">
+      <c r="W185" s="4" t="inlineStr">
         <is>
           <t>Strong on its own branch, and the tree has two.</t>
         </is>
@@ -7137,37 +7253,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F186" s="4" t="inlineStr">
+      <c r="G186" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G186" s="4" t="inlineStr">
+      <c r="H186" s="4" t="inlineStr">
         <is>
           <t>no-evidence-members-congress</t>
         </is>
       </c>
-      <c r="H186" s="4" t="inlineStr">
+      <c r="I186" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I186" s="5" t="inlineStr">
+      <c r="J186" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="J186" s="5" t="inlineStr">
+      <c r="K186" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="U186" s="4" t="inlineStr">
+      <c r="V186" s="4" t="inlineStr">
         <is>
           <t>No post-reform advantage would mean the trading channel is already closed by the current rule.</t>
         </is>
       </c>
-      <c r="V186" s="4" t="inlineStr">
+      <c r="W186" s="4" t="inlineStr">
         <is>
           <t>The most relevant weakening evidence, and it reaches only one of the two branches.</t>
         </is>
@@ -7187,37 +7303,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F187" s="4" t="inlineStr">
+      <c r="G187" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G187" s="4" t="inlineStr">
+      <c r="H187" s="4" t="inlineStr">
         <is>
           <t>five-years-after-ban</t>
         </is>
       </c>
-      <c r="H187" s="4" t="inlineStr">
+      <c r="I187" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I187" s="5" t="inlineStr">
+      <c r="J187" s="5" t="inlineStr">
         <is>
           <t>Prediction</t>
         </is>
       </c>
-      <c r="J187" s="5" t="inlineStr">
+      <c r="K187" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="U187" s="4" t="inlineStr">
+      <c r="V187" s="4" t="inlineStr">
         <is>
           <t>Would this observation tell the two sides apart, or do both expect it?</t>
         </is>
       </c>
-      <c r="V187" s="4" t="inlineStr">
+      <c r="W187" s="4" t="inlineStr">
         <is>
           <t>Half diagnostic: the compliance half is expected by everyone, the scandal half is not.</t>
         </is>
@@ -7237,37 +7353,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F188" s="4" t="inlineStr">
+      <c r="G188" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G188" s="4" t="inlineStr">
+      <c r="H188" s="4" t="inlineStr">
         <is>
           <t>public-trust-congress-five</t>
         </is>
       </c>
-      <c r="H188" s="4" t="inlineStr">
+      <c r="I188" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I188" s="5" t="inlineStr">
+      <c r="J188" s="5" t="inlineStr">
         <is>
           <t>Prediction</t>
         </is>
       </c>
-      <c r="J188" s="5" t="inlineStr">
+      <c r="K188" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="U188" s="4" t="inlineStr">
+      <c r="V188" s="4" t="inlineStr">
         <is>
           <t>Would this observation tell the two sides apart, or do both expect it?</t>
         </is>
       </c>
-      <c r="V188" s="4" t="inlineStr">
+      <c r="W188" s="4" t="inlineStr">
         <is>
           <t>Weakly diagnostic, and this page is why its contribution to the belief is small.</t>
         </is>
@@ -7287,37 +7403,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F189" s="4" t="inlineStr">
+      <c r="G189" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G189" s="4" t="inlineStr">
+      <c r="H189" s="4" t="inlineStr">
         <is>
           <t>jurisdiction-adopts-holdings-ban</t>
         </is>
       </c>
-      <c r="H189" s="4" t="inlineStr">
+      <c r="I189" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I189" s="5" t="inlineStr">
+      <c r="J189" s="5" t="inlineStr">
         <is>
           <t>Prediction</t>
         </is>
       </c>
-      <c r="J189" s="5" t="inlineStr">
+      <c r="K189" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="U189" s="4" t="inlineStr">
+      <c r="V189" s="4" t="inlineStr">
         <is>
           <t>Would this observation tell the two sides apart, or do both expect it?</t>
         </is>
       </c>
-      <c r="V189" s="4" t="inlineStr">
+      <c r="W189" s="4" t="inlineStr">
         <is>
           <t>The most diagnostic prediction on the page and the only one nobody has attempted.</t>
         </is>
@@ -7337,37 +7453,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F190" s="4" t="inlineStr">
+      <c r="G190" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G190" s="4" t="inlineStr">
+      <c r="H190" s="4" t="inlineStr">
         <is>
           <t>reported-conflicts-migrate-spouse</t>
         </is>
       </c>
-      <c r="H190" s="4" t="inlineStr">
+      <c r="I190" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I190" s="5" t="inlineStr">
+      <c r="J190" s="5" t="inlineStr">
         <is>
           <t>Prediction</t>
         </is>
       </c>
-      <c r="J190" s="5" t="inlineStr">
+      <c r="K190" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="U190" s="4" t="inlineStr">
+      <c r="V190" s="4" t="inlineStr">
         <is>
           <t>Would this observation tell the two sides apart, or do both expect it?</t>
         </is>
       </c>
-      <c r="V190" s="4" t="inlineStr">
+      <c r="W190" s="4" t="inlineStr">
         <is>
           <t>High diagnosticity through a noisy instrument.</t>
         </is>
@@ -7387,37 +7503,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F191" s="4" t="inlineStr">
+      <c r="G191" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G191" s="4" t="inlineStr">
+      <c r="H191" s="4" t="inlineStr">
         <is>
           <t>share-incoming-members-whose</t>
         </is>
       </c>
-      <c r="H191" s="4" t="inlineStr">
+      <c r="I191" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I191" s="5" t="inlineStr">
+      <c r="J191" s="5" t="inlineStr">
         <is>
           <t>Prediction</t>
         </is>
       </c>
-      <c r="J191" s="5" t="inlineStr">
+      <c r="K191" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="U191" s="4" t="inlineStr">
+      <c r="V191" s="4" t="inlineStr">
         <is>
           <t>Would this observation tell the two sides apart, or do both expect it?</t>
         </is>
       </c>
-      <c r="V191" s="4" t="inlineStr">
+      <c r="W191" s="4" t="inlineStr">
         <is>
           <t>Low linkage to the belief and high relevance to the cost-benefit table, which is where it belongs.</t>
         </is>
@@ -7437,37 +7553,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F192" s="4" t="inlineStr">
+      <c r="G192" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G192" s="4" t="inlineStr">
+      <c r="H192" s="4" t="inlineStr">
         <is>
           <t>post-reform-studies-continue</t>
         </is>
       </c>
-      <c r="H192" s="4" t="inlineStr">
+      <c r="I192" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I192" s="5" t="inlineStr">
+      <c r="J192" s="5" t="inlineStr">
         <is>
           <t>Prediction</t>
         </is>
       </c>
-      <c r="J192" s="5" t="inlineStr">
+      <c r="K192" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="U192" s="4" t="inlineStr">
+      <c r="V192" s="4" t="inlineStr">
         <is>
           <t>Would this observation tell the two sides apart, or do both expect it?</t>
         </is>
       </c>
-      <c r="V192" s="4" t="inlineStr">
+      <c r="W192" s="4" t="inlineStr">
         <is>
           <t>Diagnostic for half the belief, which is what its score should reflect.</t>
         </is>
@@ -7487,37 +7603,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F193" s="4" t="inlineStr">
+      <c r="G193" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="G193" s="4" t="inlineStr">
+      <c r="H193" s="4" t="inlineStr">
         <is>
           <t>formal-appointment-what-brings</t>
         </is>
       </c>
-      <c r="H193" s="4" t="inlineStr">
+      <c r="I193" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="I193" s="5" t="inlineStr">
+      <c r="J193" s="5" t="inlineStr">
         <is>
           <t>Argument</t>
         </is>
       </c>
-      <c r="J193" s="5" t="inlineStr">
+      <c r="K193" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="U193" s="4" t="inlineStr">
+      <c r="V193" s="4" t="inlineStr">
         <is>
           <t>A bar that converts a disclosed adviser into an undisclosed one would make things worse rather than better.</t>
         </is>
       </c>
-      <c r="V193" s="4" t="inlineStr">
+      <c r="W193" s="4" t="inlineStr">
         <is>
           <t>The highest-linkage argument on that page.</t>
         </is>
@@ -7537,37 +7653,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F194" s="4" t="inlineStr">
+      <c r="G194" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="G194" s="4" t="inlineStr">
+      <c r="H194" s="4" t="inlineStr">
         <is>
           <t>problem-people-actually-point</t>
         </is>
       </c>
-      <c r="H194" s="4" t="inlineStr">
+      <c r="I194" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="I194" s="5" t="inlineStr">
+      <c r="J194" s="5" t="inlineStr">
         <is>
           <t>Argument</t>
         </is>
       </c>
-      <c r="J194" s="5" t="inlineStr">
+      <c r="K194" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="U194" s="4" t="inlineStr">
+      <c r="V194" s="4" t="inlineStr">
         <is>
           <t>A gap in coverage bears on the size of the effect, not on its direction.</t>
         </is>
       </c>
-      <c r="V194" s="4" t="inlineStr">
+      <c r="W194" s="4" t="inlineStr">
         <is>
           <t>Moderate linkage: a scope argument doing duty as a refutation.</t>
         </is>
@@ -7587,37 +7703,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F195" s="4" t="inlineStr">
+      <c r="G195" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="G195" s="4" t="inlineStr">
+      <c r="H195" s="4" t="inlineStr">
         <is>
           <t>return-shows-tax-positions</t>
         </is>
       </c>
-      <c r="H195" s="4" t="inlineStr">
+      <c r="I195" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="I195" s="5" t="inlineStr">
+      <c r="J195" s="5" t="inlineStr">
         <is>
           <t>Argument</t>
         </is>
       </c>
-      <c r="J195" s="5" t="inlineStr">
+      <c r="K195" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="U195" s="4" t="inlineStr">
+      <c r="V195" s="4" t="inlineStr">
         <is>
           <t>If the existing form shows what a return would show, publication adds nothing.</t>
         </is>
       </c>
-      <c r="V195" s="4" t="inlineStr">
+      <c r="W195" s="4" t="inlineStr">
         <is>
           <t>High linkage and directly checkable, which is unusual and good.</t>
         </is>
@@ -7637,37 +7753,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F196" s="4" t="inlineStr">
+      <c r="G196" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="G196" s="4" t="inlineStr">
+      <c r="H196" s="4" t="inlineStr">
         <is>
           <t>route-constitutionally-narrow-disclosure</t>
         </is>
       </c>
-      <c r="H196" s="4" t="inlineStr">
+      <c r="I196" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="I196" s="5" t="inlineStr">
+      <c r="J196" s="5" t="inlineStr">
         <is>
           <t>Argument</t>
         </is>
       </c>
-      <c r="J196" s="5" t="inlineStr">
+      <c r="K196" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="U196" s="4" t="inlineStr">
+      <c r="V196" s="4" t="inlineStr">
         <is>
           <t>A precedent about ballot access bears on a disclosure duty only if the two are the same kind of rule, and they are not.</t>
         </is>
       </c>
-      <c r="V196" s="4" t="inlineStr">
+      <c r="W196" s="4" t="inlineStr">
         <is>
           <t>Low linkage: the precedent is cited far beyond what it holds, and this page is where that is priced.</t>
         </is>
@@ -7687,37 +7803,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F197" s="4" t="inlineStr">
+      <c r="G197" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="G197" s="4" t="inlineStr">
+      <c r="H197" s="4" t="inlineStr">
         <is>
           <t>article-ii-grants-power</t>
         </is>
       </c>
-      <c r="H197" s="4" t="inlineStr">
+      <c r="I197" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="I197" s="5" t="inlineStr">
+      <c r="J197" s="5" t="inlineStr">
         <is>
           <t>Argument</t>
         </is>
       </c>
-      <c r="J197" s="5" t="inlineStr">
+      <c r="K197" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="U197" s="4" t="inlineStr">
+      <c r="V197" s="4" t="inlineStr">
         <is>
           <t>The cases foreclose a statute; the belief as written does not require one.</t>
         </is>
       </c>
-      <c r="V197" s="4" t="inlineStr">
+      <c r="W197" s="4" t="inlineStr">
         <is>
           <t>The most-cited argument on that page, and nobody has opened this linkage page to argue it either way, so it still reads the presumption that a reason placed under a conclusion is relevant.</t>
         </is>
@@ -7737,37 +7853,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F198" s="4" t="inlineStr">
+      <c r="G198" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="G198" s="4" t="inlineStr">
+      <c r="H198" s="4" t="inlineStr">
         <is>
           <t>proposals-let-congress-nullify</t>
         </is>
       </c>
-      <c r="H198" s="4" t="inlineStr">
+      <c r="I198" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="I198" s="5" t="inlineStr">
+      <c r="J198" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="J198" s="5" t="inlineStr">
+      <c r="K198" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="U198" s="4" t="inlineStr">
+      <c r="V198" s="4" t="inlineStr">
         <is>
           <t>Failure to advance bears on feasibility, and the belief is about effect.</t>
         </is>
       </c>
-      <c r="V198" s="4" t="inlineStr">
+      <c r="W198" s="4" t="inlineStr">
         <is>
           <t>Very low linkage, and it is the clearest example in this workbook of a true fact aimed at the wrong claim.</t>
         </is>
@@ -7787,37 +7903,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F199" s="4" t="inlineStr">
+      <c r="G199" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="G199" s="4" t="inlineStr">
+      <c r="H199" s="4" t="inlineStr">
         <is>
           <t>most-states-already-put</t>
         </is>
       </c>
-      <c r="H199" s="4" t="inlineStr">
+      <c r="I199" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="I199" s="5" t="inlineStr">
+      <c r="J199" s="5" t="inlineStr">
         <is>
           <t>Argument</t>
         </is>
       </c>
-      <c r="J199" s="5" t="inlineStr">
+      <c r="K199" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="U199" s="4" t="inlineStr">
+      <c r="V199" s="4" t="inlineStr">
         <is>
           <t>State practice shows a check is compatible with a functioning clemency power, but not this check.</t>
         </is>
       </c>
-      <c r="V199" s="4" t="inlineStr">
+      <c r="W199" s="4" t="inlineStr">
         <is>
           <t>Real evidence for the general proposition and weak evidence for the specific proposal.</t>
         </is>
@@ -7837,37 +7953,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F200" s="4" t="inlineStr">
+      <c r="G200" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G200" s="4" t="inlineStr">
+      <c r="H200" s="4" t="inlineStr">
         <is>
           <t>78-members-117th-congress</t>
         </is>
       </c>
-      <c r="H200" s="4" t="inlineStr">
+      <c r="I200" s="4" t="inlineStr">
         <is>
           <t>investors-need-markets-where</t>
         </is>
       </c>
-      <c r="I200" s="5" t="inlineStr">
+      <c r="J200" s="5" t="inlineStr">
         <is>
           <t>Interest</t>
         </is>
       </c>
-      <c r="J200" s="5" t="inlineStr">
+      <c r="K200" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="U200" s="4" t="inlineStr">
+      <c r="V200" s="4" t="inlineStr">
         <is>
           <t>The filing deadline exists for the market-integrity interest, but a violation of it does not show that interest was harmed.</t>
         </is>
       </c>
-      <c r="V200" s="4" t="inlineStr">
+      <c r="W200" s="4" t="inlineStr">
         <is>
           <t>Bearing: how far the row is really about this interest.</t>
         </is>
@@ -7887,37 +8003,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F201" s="4" t="inlineStr">
+      <c r="G201" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G201" s="4" t="inlineStr">
+      <c r="H201" s="4" t="inlineStr">
         <is>
           <t>forced-divestiture-imposes-real</t>
         </is>
       </c>
-      <c r="H201" s="4" t="inlineStr">
+      <c r="I201" s="4" t="inlineStr">
         <is>
           <t>country-needs-capable-people</t>
         </is>
       </c>
-      <c r="I201" s="5" t="inlineStr">
+      <c r="J201" s="5" t="inlineStr">
         <is>
           <t>Interest</t>
         </is>
       </c>
-      <c r="J201" s="5" t="inlineStr">
+      <c r="K201" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="U201" s="4" t="inlineStr">
+      <c r="V201" s="4" t="inlineStr">
         <is>
           <t>Cost to sitting officials and deterrence of future candidates are related but not the same quantity.</t>
         </is>
       </c>
-      <c r="V201" s="4" t="inlineStr">
+      <c r="W201" s="4" t="inlineStr">
         <is>
           <t>Bearing: how far the row is really about this interest.</t>
         </is>
@@ -7937,27 +8053,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F202" s="4" t="inlineStr">
+      <c r="G202" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G202" s="4" t="inlineStr">
+      <c r="H202" s="4" t="inlineStr">
         <is>
           <t>members-regularly-trade-industries</t>
         </is>
       </c>
-      <c r="H202" s="4" t="inlineStr">
+      <c r="I202" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="K202" s="4" t="inlineStr">
+      <c r="L202" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="U202" s="4" t="inlineStr">
+      <c r="V202" s="4" t="inlineStr">
         <is>
           <t>Citizens whose decisions are made by someone holding a stake, and investors on the other side of the trades.</t>
         </is>
@@ -7977,27 +8093,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F203" s="4" t="inlineStr">
+      <c r="G203" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G203" s="4" t="inlineStr">
+      <c r="H203" s="4" t="inlineStr">
         <is>
           <t>disclosure-has-failed-check</t>
         </is>
       </c>
-      <c r="H203" s="4" t="inlineStr">
+      <c r="I203" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="K203" s="4" t="inlineStr">
+      <c r="L203" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="U203" s="4" t="inlineStr">
+      <c r="V203" s="4" t="inlineStr">
         <is>
           <t>Voters, who cannot tell a compromised official from a clean one, and officials living under a rule nobody enforces.</t>
         </is>
@@ -8017,27 +8133,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F204" s="4" t="inlineStr">
+      <c r="G204" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G204" s="4" t="inlineStr">
+      <c r="H204" s="4" t="inlineStr">
         <is>
           <t>holdings-ban-removes-conflict</t>
         </is>
       </c>
-      <c r="H204" s="4" t="inlineStr">
+      <c r="I204" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="K204" s="4" t="inlineStr">
+      <c r="L204" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="U204" s="4" t="inlineStr">
+      <c r="V204" s="4" t="inlineStr">
         <is>
           <t>Everyone who needs decisions made on the merits, and officials who want a rule they can actually follow.</t>
         </is>
@@ -8057,27 +8173,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F205" s="4" t="inlineStr">
+      <c r="G205" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G205" s="4" t="inlineStr">
+      <c r="H205" s="4" t="inlineStr">
         <is>
           <t>federal-reserve-barred-its</t>
         </is>
       </c>
-      <c r="H205" s="4" t="inlineStr">
+      <c r="I205" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="K205" s="4" t="inlineStr">
+      <c r="L205" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="U205" s="4" t="inlineStr">
+      <c r="V205" s="4" t="inlineStr">
         <is>
           <t>Officials, who would live under the rule, and anyone worried it makes service impossible.</t>
         </is>
@@ -8097,27 +8213,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F206" s="4" t="inlineStr">
+      <c r="G206" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G206" s="4" t="inlineStr">
+      <c r="H206" s="4" t="inlineStr">
         <is>
           <t>trading-closed-briefing-almost</t>
         </is>
       </c>
-      <c r="H206" s="4" t="inlineStr">
+      <c r="I206" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="K206" s="4" t="inlineStr">
+      <c r="L206" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="U206" s="4" t="inlineStr">
+      <c r="V206" s="4" t="inlineStr">
         <is>
           <t>Citizens and investors, who currently rely on a rule that cannot be enforced.</t>
         </is>
@@ -8137,27 +8253,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F207" s="4" t="inlineStr">
+      <c r="G207" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G207" s="4" t="inlineStr">
+      <c r="H207" s="4" t="inlineStr">
         <is>
           <t>best-identified-studies-actual</t>
         </is>
       </c>
-      <c r="H207" s="4" t="inlineStr">
+      <c r="I207" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="K207" s="4" t="inlineStr">
+      <c r="L207" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="U207" s="4" t="inlineStr">
+      <c r="V207" s="4" t="inlineStr">
         <is>
           <t>Investors, if there turns out to be no advantage being taken.</t>
         </is>
@@ -8177,27 +8293,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F208" s="4" t="inlineStr">
+      <c r="G208" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G208" s="4" t="inlineStr">
+      <c r="H208" s="4" t="inlineStr">
         <is>
           <t>ban-official-leaves-conflict</t>
         </is>
       </c>
-      <c r="H208" s="4" t="inlineStr">
+      <c r="I208" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="K208" s="4" t="inlineStr">
+      <c r="L208" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="U208" s="4" t="inlineStr">
+      <c r="V208" s="4" t="inlineStr">
         <is>
           <t>Citizens, if the conflict moves instead of ending, and voters, who would see less of it.</t>
         </is>
@@ -8217,27 +8333,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F209" s="4" t="inlineStr">
+      <c r="G209" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G209" s="4" t="inlineStr">
+      <c r="H209" s="4" t="inlineStr">
         <is>
           <t>forced-divestiture-imposes-real</t>
         </is>
       </c>
-      <c r="H209" s="4" t="inlineStr">
+      <c r="I209" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="K209" s="4" t="inlineStr">
+      <c r="L209" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="U209" s="4" t="inlineStr">
+      <c r="V209" s="4" t="inlineStr">
         <is>
           <t>People of ordinary means considering office, and officials asked to sell on someone else's schedule.</t>
         </is>
@@ -8257,27 +8373,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F210" s="4" t="inlineStr">
+      <c r="G210" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G210" s="4" t="inlineStr">
+      <c r="H210" s="4" t="inlineStr">
         <is>
           <t>members-keep-property-rights</t>
         </is>
       </c>
-      <c r="H210" s="4" t="inlineStr">
+      <c r="I210" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="K210" s="4" t="inlineStr">
+      <c r="L210" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="U210" s="4" t="inlineStr">
+      <c r="V210" s="4" t="inlineStr">
         <is>
           <t>Officials and their families, whose ordinary rights the rule restricts.</t>
         </is>
@@ -8297,27 +8413,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F211" s="4" t="inlineStr">
+      <c r="G211" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G211" s="4" t="inlineStr">
+      <c r="H211" s="4" t="inlineStr">
         <is>
           <t>congress-will-enforce-ban</t>
         </is>
       </c>
-      <c r="H211" s="4" t="inlineStr">
+      <c r="I211" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="K211" s="4" t="inlineStr">
+      <c r="L211" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="U211" s="4" t="inlineStr">
+      <c r="V211" s="4" t="inlineStr">
         <is>
           <t>Citizens, if the rule is a symbol, and officials, who would carry its burden for nothing.</t>
         </is>
@@ -8337,27 +8453,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F212" s="4" t="inlineStr">
+      <c r="G212" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G212" s="4" t="inlineStr">
+      <c r="H212" s="4" t="inlineStr">
         <is>
           <t>senators-stock-purchases-beat</t>
         </is>
       </c>
-      <c r="H212" s="4" t="inlineStr">
+      <c r="I212" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="K212" s="4" t="inlineStr">
+      <c r="L212" s="4" t="inlineStr">
         <is>
           <t>supporting finding</t>
         </is>
       </c>
-      <c r="U212" s="4" t="inlineStr">
+      <c r="V212" s="4" t="inlineStr">
         <is>
           <t>Investors trading against officials during the period studied.</t>
         </is>
@@ -8377,27 +8493,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F213" s="4" t="inlineStr">
+      <c r="G213" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G213" s="4" t="inlineStr">
+      <c r="H213" s="4" t="inlineStr">
         <is>
           <t>trades-placed-before-legislative</t>
         </is>
       </c>
-      <c r="H213" s="4" t="inlineStr">
+      <c r="I213" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="K213" s="4" t="inlineStr">
+      <c r="L213" s="4" t="inlineStr">
         <is>
           <t>supporting finding</t>
         </is>
       </c>
-      <c r="U213" s="4" t="inlineStr">
+      <c r="V213" s="4" t="inlineStr">
         <is>
           <t>Investors on the other side of trades placed before legislative events.</t>
         </is>
@@ -8417,27 +8533,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F214" s="4" t="inlineStr">
+      <c r="G214" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G214" s="4" t="inlineStr">
+      <c r="H214" s="4" t="inlineStr">
         <is>
           <t>78-members-117th-congress</t>
         </is>
       </c>
-      <c r="H214" s="4" t="inlineStr">
+      <c r="I214" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="K214" s="4" t="inlineStr">
+      <c r="L214" s="4" t="inlineStr">
         <is>
           <t>supporting finding</t>
         </is>
       </c>
-      <c r="U214" s="4" t="inlineStr">
+      <c r="V214" s="4" t="inlineStr">
         <is>
           <t>Investors relying on a disclosure regime, and officials living under a rule that is widely missed.</t>
         </is>
@@ -8457,27 +8573,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F215" s="4" t="inlineStr">
+      <c r="G215" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G215" s="4" t="inlineStr">
+      <c r="H215" s="4" t="inlineStr">
         <is>
           <t>131-federal-judges-heard</t>
         </is>
       </c>
-      <c r="H215" s="4" t="inlineStr">
+      <c r="I215" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="K215" s="4" t="inlineStr">
+      <c r="L215" s="4" t="inlineStr">
         <is>
           <t>supporting finding</t>
         </is>
       </c>
-      <c r="U215" s="4" t="inlineStr">
+      <c r="V215" s="4" t="inlineStr">
         <is>
           <t>Litigants and voters relying on disclosure to reveal a decision-maker's stake.</t>
         </is>
@@ -8497,27 +8613,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F216" s="4" t="inlineStr">
+      <c r="G216" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G216" s="4" t="inlineStr">
+      <c r="H216" s="4" t="inlineStr">
         <is>
           <t>federal-reserve-officials-have</t>
         </is>
       </c>
-      <c r="H216" s="4" t="inlineStr">
+      <c r="I216" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="K216" s="4" t="inlineStr">
+      <c r="L216" s="4" t="inlineStr">
         <is>
           <t>supporting finding</t>
         </is>
       </c>
-      <c r="U216" s="4" t="inlineStr">
+      <c r="V216" s="4" t="inlineStr">
         <is>
           <t>Officials under the rule, and anyone concerned it deters qualified people.</t>
         </is>
@@ -8537,27 +8653,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F217" s="4" t="inlineStr">
+      <c r="G217" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G217" s="4" t="inlineStr">
+      <c r="H217" s="4" t="inlineStr">
         <is>
           <t>congressional-portfolios-underperformed-market</t>
         </is>
       </c>
-      <c r="H217" s="4" t="inlineStr">
+      <c r="I217" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="K217" s="4" t="inlineStr">
+      <c r="L217" s="4" t="inlineStr">
         <is>
           <t>weakening finding</t>
         </is>
       </c>
-      <c r="U217" s="4" t="inlineStr">
+      <c r="V217" s="4" t="inlineStr">
         <is>
           <t>Investors, if there is no advantage to remove.</t>
         </is>
@@ -8577,27 +8693,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F218" s="4" t="inlineStr">
+      <c r="G218" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G218" s="4" t="inlineStr">
+      <c r="H218" s="4" t="inlineStr">
         <is>
           <t>no-evidence-members-congress</t>
         </is>
       </c>
-      <c r="H218" s="4" t="inlineStr">
+      <c r="I218" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="K218" s="4" t="inlineStr">
+      <c r="L218" s="4" t="inlineStr">
         <is>
           <t>weakening finding</t>
         </is>
       </c>
-      <c r="U218" s="4" t="inlineStr">
+      <c r="V218" s="4" t="inlineStr">
         <is>
           <t>Investors in the post-reform period.</t>
         </is>
@@ -8617,27 +8733,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F219" s="4" t="inlineStr">
+      <c r="G219" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G219" s="4" t="inlineStr">
+      <c r="H219" s="4" t="inlineStr">
         <is>
           <t>five-years-after-ban</t>
         </is>
       </c>
-      <c r="H219" s="4" t="inlineStr">
+      <c r="I219" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="K219" s="4" t="inlineStr">
+      <c r="L219" s="4" t="inlineStr">
         <is>
           <t>prediction if the belief is true</t>
         </is>
       </c>
-      <c r="U219" s="4" t="inlineStr">
+      <c r="V219" s="4" t="inlineStr">
         <is>
           <t>Citizens, whose officials would no longer hold the stakes.</t>
         </is>
@@ -8657,27 +8773,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F220" s="4" t="inlineStr">
+      <c r="G220" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G220" s="4" t="inlineStr">
+      <c r="H220" s="4" t="inlineStr">
         <is>
           <t>public-trust-congress-five</t>
         </is>
       </c>
-      <c r="H220" s="4" t="inlineStr">
+      <c r="I220" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="K220" s="4" t="inlineStr">
+      <c r="L220" s="4" t="inlineStr">
         <is>
           <t>prediction if the belief is true</t>
         </is>
       </c>
-      <c r="U220" s="4" t="inlineStr">
+      <c r="V220" s="4" t="inlineStr">
         <is>
           <t>Voters, whose confidence is the thing being measured.</t>
         </is>
@@ -8697,27 +8813,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F221" s="4" t="inlineStr">
+      <c r="G221" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G221" s="4" t="inlineStr">
+      <c r="H221" s="4" t="inlineStr">
         <is>
           <t>jurisdiction-adopts-holdings-ban</t>
         </is>
       </c>
-      <c r="H221" s="4" t="inlineStr">
+      <c r="I221" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="K221" s="4" t="inlineStr">
+      <c r="L221" s="4" t="inlineStr">
         <is>
           <t>prediction if the belief is true</t>
         </is>
       </c>
-      <c r="U221" s="4" t="inlineStr">
+      <c r="V221" s="4" t="inlineStr">
         <is>
           <t>Citizens, whose votes would be cast without the stake.</t>
         </is>
@@ -8737,27 +8853,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F222" s="4" t="inlineStr">
+      <c r="G222" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G222" s="4" t="inlineStr">
+      <c r="H222" s="4" t="inlineStr">
         <is>
           <t>reported-conflicts-migrate-spouse</t>
         </is>
       </c>
-      <c r="H222" s="4" t="inlineStr">
+      <c r="I222" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="K222" s="4" t="inlineStr">
+      <c r="L222" s="4" t="inlineStr">
         <is>
           <t>prediction if the belief is false</t>
         </is>
       </c>
-      <c r="U222" s="4" t="inlineStr">
+      <c r="V222" s="4" t="inlineStr">
         <is>
           <t>Citizens, if the conflict persists out of view.</t>
         </is>
@@ -8777,27 +8893,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F223" s="4" t="inlineStr">
+      <c r="G223" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G223" s="4" t="inlineStr">
+      <c r="H223" s="4" t="inlineStr">
         <is>
           <t>share-incoming-members-whose</t>
         </is>
       </c>
-      <c r="H223" s="4" t="inlineStr">
+      <c r="I223" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="K223" s="4" t="inlineStr">
+      <c r="L223" s="4" t="inlineStr">
         <is>
           <t>prediction if the belief is false</t>
         </is>
       </c>
-      <c r="U223" s="4" t="inlineStr">
+      <c r="V223" s="4" t="inlineStr">
         <is>
           <t>People of ordinary means who might otherwise run.</t>
         </is>
@@ -8817,27 +8933,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F224" s="4" t="inlineStr">
+      <c r="G224" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G224" s="4" t="inlineStr">
+      <c r="H224" s="4" t="inlineStr">
         <is>
           <t>post-reform-studies-continue</t>
         </is>
       </c>
-      <c r="H224" s="4" t="inlineStr">
+      <c r="I224" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="K224" s="4" t="inlineStr">
+      <c r="L224" s="4" t="inlineStr">
         <is>
           <t>prediction if the belief is false</t>
         </is>
       </c>
-      <c r="U224" s="4" t="inlineStr">
+      <c r="V224" s="4" t="inlineStr">
         <is>
           <t>Investors, if the advantage was already gone.</t>
         </is>
@@ -8857,27 +8973,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F225" s="4" t="inlineStr">
+      <c r="G225" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="G225" s="4" t="inlineStr">
+      <c r="H225" s="4" t="inlineStr">
         <is>
           <t>anti-nepotism-statute-stops</t>
         </is>
       </c>
-      <c r="H225" s="4" t="inlineStr">
+      <c r="I225" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="K225" s="4" t="inlineStr">
+      <c r="L225" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="U225" s="4" t="inlineStr">
+      <c r="V225" s="4" t="inlineStr">
         <is>
           <t>Citizens, whose decisions are made by someone outside the rule that covers everyone else.</t>
         </is>
@@ -8897,27 +9013,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F226" s="4" t="inlineStr">
+      <c r="G226" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="G226" s="4" t="inlineStr">
+      <c r="H226" s="4" t="inlineStr">
         <is>
           <t>relative-cannot-supervised-disciplined</t>
         </is>
       </c>
-      <c r="H226" s="4" t="inlineStr">
+      <c r="I226" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="K226" s="4" t="inlineStr">
+      <c r="L226" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="U226" s="4" t="inlineStr">
+      <c r="V226" s="4" t="inlineStr">
         <is>
           <t>Citizens relying on an ordinary chain of command to check official conduct.</t>
         </is>
@@ -8937,27 +9053,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F227" s="4" t="inlineStr">
+      <c r="G227" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="G227" s="4" t="inlineStr">
+      <c r="H227" s="4" t="inlineStr">
         <is>
           <t>official-role-gives-family</t>
         </is>
       </c>
-      <c r="H227" s="4" t="inlineStr">
+      <c r="I227" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="K227" s="4" t="inlineStr">
+      <c r="L227" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="U227" s="4" t="inlineStr">
+      <c r="V227" s="4" t="inlineStr">
         <is>
           <t>Citizens, and voters who cannot see what the channel carries.</t>
         </is>
@@ -8977,27 +9093,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F228" s="4" t="inlineStr">
+      <c r="G228" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="G228" s="4" t="inlineStr">
+      <c r="H228" s="4" t="inlineStr">
         <is>
           <t>rule-already-applies-every</t>
         </is>
       </c>
-      <c r="H228" s="4" t="inlineStr">
+      <c r="I228" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="K228" s="4" t="inlineStr">
+      <c r="L228" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="U228" s="4" t="inlineStr">
+      <c r="V228" s="4" t="inlineStr">
         <is>
           <t>Officials, who would face one rule instead of two.</t>
         </is>
@@ -9017,27 +9133,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F229" s="4" t="inlineStr">
+      <c r="G229" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="G229" s="4" t="inlineStr">
+      <c r="H229" s="4" t="inlineStr">
         <is>
           <t>formal-appointment-what-brings</t>
         </is>
       </c>
-      <c r="H229" s="4" t="inlineStr">
+      <c r="I229" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="K229" s="4" t="inlineStr">
+      <c r="L229" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="U229" s="4" t="inlineStr">
+      <c r="V229" s="4" t="inlineStr">
         <is>
           <t>Voters, who would lose the disclosure that appointment triggers.</t>
         </is>
@@ -9057,27 +9173,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F230" s="4" t="inlineStr">
+      <c r="G230" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="G230" s="4" t="inlineStr">
+      <c r="H230" s="4" t="inlineStr">
         <is>
           <t>problem-people-actually-point</t>
         </is>
       </c>
-      <c r="H230" s="4" t="inlineStr">
+      <c r="I230" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="K230" s="4" t="inlineStr">
+      <c r="L230" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="U230" s="4" t="inlineStr">
+      <c r="V230" s="4" t="inlineStr">
         <is>
           <t>Relatives making money from the name, which the rule does not reach.</t>
         </is>
@@ -9097,27 +9213,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F231" s="4" t="inlineStr">
+      <c r="G231" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="G231" s="4" t="inlineStr">
+      <c r="H231" s="4" t="inlineStr">
         <is>
           <t>president-entitled-advisers-he</t>
         </is>
       </c>
-      <c r="H231" s="4" t="inlineStr">
+      <c r="I231" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="K231" s="4" t="inlineStr">
+      <c r="L231" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="U231" s="4" t="inlineStr">
+      <c r="V231" s="4" t="inlineStr">
         <is>
           <t>A president restricted in whom he may consult.</t>
         </is>
@@ -9137,27 +9253,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F232" s="4" t="inlineStr">
+      <c r="G232" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="G232" s="4" t="inlineStr">
+      <c r="H232" s="4" t="inlineStr">
         <is>
           <t>competence-neither-inherited-nor</t>
         </is>
       </c>
-      <c r="H232" s="4" t="inlineStr">
+      <c r="I232" s="4" t="inlineStr">
         <is>
           <t>barring-president-members-congress</t>
         </is>
       </c>
-      <c r="K232" s="4" t="inlineStr">
+      <c r="L232" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="U232" s="4" t="inlineStr">
+      <c r="V232" s="4" t="inlineStr">
         <is>
           <t>Qualified people excluded for a relationship.</t>
         </is>
@@ -9177,27 +9293,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F233" s="4" t="inlineStr">
+      <c r="G233" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="G233" s="4" t="inlineStr">
+      <c r="H233" s="4" t="inlineStr">
         <is>
           <t>return-shows-what-financial</t>
         </is>
       </c>
-      <c r="H233" s="4" t="inlineStr">
+      <c r="I233" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="K233" s="4" t="inlineStr">
+      <c r="L233" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="U233" s="4" t="inlineStr">
+      <c r="V233" s="4" t="inlineStr">
         <is>
           <t>Voters, who currently see ranges instead of figures.</t>
         </is>
@@ -9217,27 +9333,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F234" s="4" t="inlineStr">
+      <c r="G234" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="G234" s="4" t="inlineStr">
+      <c r="H234" s="4" t="inlineStr">
         <is>
           <t>internal-check-failed-one</t>
         </is>
       </c>
-      <c r="H234" s="4" t="inlineStr">
+      <c r="I234" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="K234" s="4" t="inlineStr">
+      <c r="L234" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="U234" s="4" t="inlineStr">
+      <c r="V234" s="4" t="inlineStr">
         <is>
           <t>Citizens relying on an audit that did not happen.</t>
         </is>
@@ -9257,27 +9373,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F235" s="4" t="inlineStr">
+      <c r="G235" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="G235" s="4" t="inlineStr">
+      <c r="H235" s="4" t="inlineStr">
         <is>
           <t>every-president-carter-through</t>
         </is>
       </c>
-      <c r="H235" s="4" t="inlineStr">
+      <c r="I235" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="K235" s="4" t="inlineStr">
+      <c r="L235" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="U235" s="4" t="inlineStr">
+      <c r="V235" s="4" t="inlineStr">
         <is>
           <t>Voters, who had the information for forty years and then did not.</t>
         </is>
@@ -9297,27 +9413,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F236" s="4" t="inlineStr">
+      <c r="G236" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="G236" s="4" t="inlineStr">
+      <c r="H236" s="4" t="inlineStr">
         <is>
           <t>published-return-can-checked</t>
         </is>
       </c>
-      <c r="H236" s="4" t="inlineStr">
+      <c r="I236" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="K236" s="4" t="inlineStr">
+      <c r="L236" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="U236" s="4" t="inlineStr">
+      <c r="V236" s="4" t="inlineStr">
         <is>
           <t>Voters, who can check a published document without waiting for an agency.</t>
         </is>
@@ -9337,27 +9453,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F237" s="4" t="inlineStr">
+      <c r="G237" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="G237" s="4" t="inlineStr">
+      <c r="H237" s="4" t="inlineStr">
         <is>
           <t>return-shows-tax-positions</t>
         </is>
       </c>
-      <c r="H237" s="4" t="inlineStr">
+      <c r="I237" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="K237" s="4" t="inlineStr">
+      <c r="L237" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="U237" s="4" t="inlineStr">
+      <c r="V237" s="4" t="inlineStr">
         <is>
           <t>Voters, if the existing form already tells them what they need.</t>
         </is>
@@ -9377,27 +9493,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F238" s="4" t="inlineStr">
+      <c r="G238" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="G238" s="4" t="inlineStr">
+      <c r="H238" s="4" t="inlineStr">
         <is>
           <t>publication-exposes-spouses-children</t>
         </is>
       </c>
-      <c r="H238" s="4" t="inlineStr">
+      <c r="I238" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="K238" s="4" t="inlineStr">
+      <c r="L238" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="U238" s="4" t="inlineStr">
+      <c r="V238" s="4" t="inlineStr">
         <is>
           <t>Spouses, children and partners who hold no office.</t>
         </is>
@@ -9417,27 +9533,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F239" s="4" t="inlineStr">
+      <c r="G239" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="G239" s="4" t="inlineStr">
+      <c r="H239" s="4" t="inlineStr">
         <is>
           <t>route-constitutionally-narrow-disclosure</t>
         </is>
       </c>
-      <c r="H239" s="4" t="inlineStr">
+      <c r="I239" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="K239" s="4" t="inlineStr">
+      <c r="L239" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="U239" s="4" t="inlineStr">
+      <c r="V239" s="4" t="inlineStr">
         <is>
           <t>Officials facing a rule that would be litigated rather than obeyed.</t>
         </is>
@@ -9457,27 +9573,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F240" s="4" t="inlineStr">
+      <c r="G240" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="G240" s="4" t="inlineStr">
+      <c r="H240" s="4" t="inlineStr">
         <is>
           <t>sophisticated-wealth-sits-pass</t>
         </is>
       </c>
-      <c r="H240" s="4" t="inlineStr">
+      <c r="I240" s="4" t="inlineStr">
         <is>
           <t>requiring-president-members-congress</t>
         </is>
       </c>
-      <c r="K240" s="4" t="inlineStr">
+      <c r="L240" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="U240" s="4" t="inlineStr">
+      <c r="V240" s="4" t="inlineStr">
         <is>
           <t>Voters, who would see a document that shows little.</t>
         </is>
@@ -9497,27 +9613,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F241" s="4" t="inlineStr">
+      <c r="G241" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="G241" s="4" t="inlineStr">
+      <c r="H241" s="4" t="inlineStr">
         <is>
           <t>clemency-only-executive-power</t>
         </is>
       </c>
-      <c r="H241" s="4" t="inlineStr">
+      <c r="I241" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="K241" s="4" t="inlineStr">
+      <c r="L241" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="U241" s="4" t="inlineStr">
+      <c r="V241" s="4" t="inlineStr">
         <is>
           <t>Victims and the public, for whom nothing reviews a grant.</t>
         </is>
@@ -9537,27 +9653,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F242" s="4" t="inlineStr">
+      <c r="G242" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="G242" s="4" t="inlineStr">
+      <c r="H242" s="4" t="inlineStr">
         <is>
           <t>pardons-granted-president-s</t>
         </is>
       </c>
-      <c r="H242" s="4" t="inlineStr">
+      <c r="I242" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="K242" s="4" t="inlineStr">
+      <c r="L242" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="U242" s="4" t="inlineStr">
+      <c r="V242" s="4" t="inlineStr">
         <is>
           <t>Victims of the underlying offenses, and citizens watching the power used on the president's circle.</t>
         </is>
@@ -9577,27 +9693,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F243" s="4" t="inlineStr">
+      <c r="G243" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="G243" s="4" t="inlineStr">
+      <c r="H243" s="4" t="inlineStr">
         <is>
           <t>two-thirds-threshold-means</t>
         </is>
       </c>
-      <c r="H243" s="4" t="inlineStr">
+      <c r="I243" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="K243" s="4" t="inlineStr">
+      <c r="L243" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="U243" s="4" t="inlineStr">
+      <c r="V243" s="4" t="inlineStr">
         <is>
           <t>A president whose unpopular but just grants would survive a two-thirds test.</t>
         </is>
@@ -9617,27 +9733,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F244" s="4" t="inlineStr">
+      <c r="G244" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="G244" s="4" t="inlineStr">
+      <c r="H244" s="4" t="inlineStr">
         <is>
           <t>most-states-already-put</t>
         </is>
       </c>
-      <c r="H244" s="4" t="inlineStr">
+      <c r="I244" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="K244" s="4" t="inlineStr">
+      <c r="L244" s="4" t="inlineStr">
         <is>
           <t>reason to agree</t>
         </is>
       </c>
-      <c r="U244" s="4" t="inlineStr">
+      <c r="V244" s="4" t="inlineStr">
         <is>
           <t>The public in states where clemency already carries a check.</t>
         </is>
@@ -9657,27 +9773,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F245" s="4" t="inlineStr">
+      <c r="G245" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="G245" s="4" t="inlineStr">
+      <c r="H245" s="4" t="inlineStr">
         <is>
           <t>article-ii-grants-power</t>
         </is>
       </c>
-      <c r="H245" s="4" t="inlineStr">
+      <c r="I245" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="K245" s="4" t="inlineStr">
+      <c r="L245" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="U245" s="4" t="inlineStr">
+      <c r="V245" s="4" t="inlineStr">
         <is>
           <t>A president whose constitutional power would be narrowed.</t>
         </is>
@@ -9697,27 +9813,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F246" s="4" t="inlineStr">
+      <c r="G246" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="G246" s="4" t="inlineStr">
+      <c r="H246" s="4" t="inlineStr">
         <is>
           <t>clemency-exists-correct-injustices</t>
         </is>
       </c>
-      <c r="H246" s="4" t="inlineStr">
+      <c r="I246" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="K246" s="4" t="inlineStr">
+      <c r="L246" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="U246" s="4" t="inlineStr">
+      <c r="V246" s="4" t="inlineStr">
         <is>
           <t>People whom only an unpopular act of mercy can reach.</t>
         </is>
@@ -9737,27 +9853,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F247" s="4" t="inlineStr">
+      <c r="G247" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="G247" s="4" t="inlineStr">
+      <c r="H247" s="4" t="inlineStr">
         <is>
           <t>reversible-pardon-pardon-nobody</t>
         </is>
       </c>
-      <c r="H247" s="4" t="inlineStr">
+      <c r="I247" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="K247" s="4" t="inlineStr">
+      <c r="L247" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="U247" s="4" t="inlineStr">
+      <c r="V247" s="4" t="inlineStr">
         <is>
           <t>Recipients who could not rely on a grant.</t>
         </is>
@@ -9777,27 +9893,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F248" s="4" t="inlineStr">
+      <c r="G248" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="G248" s="4" t="inlineStr">
+      <c r="H248" s="4" t="inlineStr">
         <is>
           <t>narrower-fix-reaches-actual</t>
         </is>
       </c>
-      <c r="H248" s="4" t="inlineStr">
+      <c r="I248" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="K248" s="4" t="inlineStr">
+      <c r="L248" s="4" t="inlineStr">
         <is>
           <t>reason to disagree</t>
         </is>
       </c>
-      <c r="U248" s="4" t="inlineStr">
+      <c r="V248" s="4" t="inlineStr">
         <is>
           <t>The same public interest, served by a smaller change.</t>
         </is>
@@ -9817,27 +9933,27 @@
           <t>uniqueness</t>
         </is>
       </c>
-      <c r="F249" s="4" t="inlineStr">
+      <c r="G249" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G249" s="4" t="inlineStr">
+      <c r="H249" s="4" t="inlineStr">
         <is>
           <t>federal-reserve-officials-have</t>
         </is>
       </c>
-      <c r="H249" s="4" t="inlineStr">
+      <c r="I249" s="4" t="inlineStr">
         <is>
           <t>federal-reserve-barred-its</t>
         </is>
       </c>
-      <c r="U249" s="4" t="inlineStr">
+      <c r="V249" s="4" t="inlineStr">
         <is>
           <t>The finding adds the rule's scope and dates; the argument adds the claim that the institution kept working.</t>
         </is>
       </c>
-      <c r="V249" s="4" t="inlineStr">
+      <c r="W249" s="4" t="inlineStr">
         <is>
           <t>Largely redundant: the finding keeps a minority of its weight, which is the discount working as intended.</t>
         </is>
@@ -9857,27 +9973,27 @@
           <t>uniqueness</t>
         </is>
       </c>
-      <c r="F250" s="4" t="inlineStr">
+      <c r="G250" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G250" s="4" t="inlineStr">
+      <c r="H250" s="4" t="inlineStr">
         <is>
           <t>congress-will-enforce-ban</t>
         </is>
       </c>
-      <c r="H250" s="4" t="inlineStr">
+      <c r="I250" s="4" t="inlineStr">
         <is>
           <t>ban-official-leaves-conflict</t>
         </is>
       </c>
-      <c r="U250" s="4" t="inlineStr">
+      <c r="V250" s="4" t="inlineStr">
         <is>
           <t>Substitution is about what the rule covers; non-enforcement is about whether what it covers is policed.</t>
         </is>
       </c>
-      <c r="V250" s="4" t="inlineStr">
+      <c r="W250" s="4" t="inlineStr">
         <is>
           <t>Distinct: they fail in different ways and would be refuted by different evidence.</t>
         </is>
@@ -9897,27 +10013,27 @@
           <t>equivalence</t>
         </is>
       </c>
-      <c r="F251" s="4" t="inlineStr">
+      <c r="G251" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G251" s="4" t="inlineStr">
+      <c r="H251" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H251" s="4" t="inlineStr">
+      <c r="I251" s="4" t="inlineStr">
         <is>
           <t>members-congress-barred-owning</t>
         </is>
       </c>
-      <c r="U251" s="4" t="inlineStr">
+      <c r="V251" s="4" t="inlineStr">
         <is>
           <t>The broader version reaches every asset class rather than publicly traded shares.</t>
         </is>
       </c>
-      <c r="V251" s="4" t="inlineStr">
+      <c r="W251" s="4" t="inlineStr">
         <is>
           <t>Same direction, different policy. Keep both pages and cross-link them.</t>
         </is>
@@ -9937,27 +10053,27 @@
           <t>equivalence</t>
         </is>
       </c>
-      <c r="F252" s="4" t="inlineStr">
+      <c r="G252" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G252" s="4" t="inlineStr">
+      <c r="H252" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H252" s="4" t="inlineStr">
+      <c r="I252" s="4" t="inlineStr">
         <is>
           <t>members-congress-required-place</t>
         </is>
       </c>
-      <c r="U252" s="4" t="inlineStr">
+      <c r="V252" s="4" t="inlineStr">
         <is>
           <t>A blind trust removes control and keeps ownership; a ban removes ownership.</t>
         </is>
       </c>
-      <c r="V252" s="4" t="inlineStr">
+      <c r="W252" s="4" t="inlineStr">
         <is>
           <t>Overlapping rather than equivalent: keep both pages and name the difference on each.</t>
         </is>
@@ -9977,27 +10093,27 @@
           <t>equivalence</t>
         </is>
       </c>
-      <c r="F253" s="4" t="inlineStr">
+      <c r="G253" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="G253" s="4" t="inlineStr">
+      <c r="H253" s="4" t="inlineStr">
         <is>
           <t>letting-congress-overturn-presidential</t>
         </is>
       </c>
-      <c r="H253" s="4" t="inlineStr">
+      <c r="I253" s="4" t="inlineStr">
         <is>
           <t>president-barred-pardoning-relatives</t>
         </is>
       </c>
-      <c r="U253" s="4" t="inlineStr">
+      <c r="V253" s="4" t="inlineStr">
         <is>
           <t>One restricts who may be pardoned; the other lets Congress undo any grant.</t>
         </is>
       </c>
-      <c r="V253" s="4" t="inlineStr">
+      <c r="W253" s="4" t="inlineStr">
         <is>
           <t>Distinct mechanisms aimed at overlapping cases. Both need an amendment.</t>
         </is>
@@ -10022,32 +10138,32 @@
           <t>Ziobrowski, Cheng, Boyd and Ziobrowski, Abnormal Returns from the Common Stock Investments of the U.S. Senate (2004)</t>
         </is>
       </c>
-      <c r="F254" s="4" t="inlineStr">
+      <c r="G254" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H254" s="4" t="inlineStr">
+      <c r="I254" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I254" s="5" t="inlineStr">
+      <c r="J254" s="5" t="inlineStr">
         <is>
           <t>Study</t>
         </is>
       </c>
-      <c r="N254" s="4" t="inlineStr">
+      <c r="O254" s="4" t="inlineStr">
         <is>
           <t>Journal of Financial and Quantitative Analysis 39(4), 661 to 676</t>
         </is>
       </c>
-      <c r="U254" s="4" t="inlineStr">
+      <c r="V254" s="4" t="inlineStr">
         <is>
           <t>Senators earned abnormal returns on their stock purchases in the 1990s.</t>
         </is>
       </c>
-      <c r="V254" s="4" t="inlineStr">
+      <c r="W254" s="4" t="inlineStr">
         <is>
           <t>The foundational study for the trading-advantage argument, and its period is now a generation old.</t>
         </is>
@@ -10072,32 +10188,32 @@
           <t>Insider, Conflicted Congress (2021 to 2023)</t>
         </is>
       </c>
-      <c r="F255" s="4" t="inlineStr">
+      <c r="G255" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H255" s="4" t="inlineStr">
+      <c r="I255" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I255" s="5" t="inlineStr">
+      <c r="J255" s="5" t="inlineStr">
         <is>
           <t>Report</t>
         </is>
       </c>
-      <c r="N255" s="4" t="inlineStr">
+      <c r="O255" s="4" t="inlineStr">
         <is>
           <t>Insider investigative series, tally updated January 2023</t>
         </is>
       </c>
-      <c r="U255" s="4" t="inlineStr">
+      <c r="V255" s="4" t="inlineStr">
         <is>
           <t>Members of Congress violate the existing disclosure rule routinely and without consequence.</t>
         </is>
       </c>
-      <c r="V255" s="4" t="inlineStr">
+      <c r="W255" s="4" t="inlineStr">
         <is>
           <t>Accurate as a count and routinely oversold as a measure of misconduct.</t>
         </is>
@@ -10122,32 +10238,32 @@
           <t>Eggers and Hainmueller, Capitol Losses: The Mediocre Performance of Congressional Stock Portfolios (2013)</t>
         </is>
       </c>
-      <c r="F256" s="4" t="inlineStr">
+      <c r="G256" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="H256" s="4" t="inlineStr">
+      <c r="I256" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I256" s="5" t="inlineStr">
+      <c r="J256" s="5" t="inlineStr">
         <is>
           <t>Study</t>
         </is>
       </c>
-      <c r="N256" s="4" t="inlineStr">
+      <c r="O256" s="4" t="inlineStr">
         <is>
           <t>Journal of Politics 75(2)</t>
         </is>
       </c>
-      <c r="U256" s="4" t="inlineStr">
+      <c r="V256" s="4" t="inlineStr">
         <is>
           <t>Congressional portfolios did not beat the market.</t>
         </is>
       </c>
-      <c r="V256" s="4" t="inlineStr">
+      <c r="W256" s="4" t="inlineStr">
         <is>
           <t>The most careful study on the skeptical side, and the tail-versus-average objection is unresolved.</t>
         </is>
@@ -10167,37 +10283,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F257" s="4" t="inlineStr">
+      <c r="G257" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G257" s="4" t="inlineStr">
+      <c r="H257" s="4" t="inlineStr">
         <is>
           <t>ziobrowski-cheng-boyd-ziobrowski</t>
         </is>
       </c>
-      <c r="H257" s="4" t="inlineStr">
+      <c r="I257" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I257" s="5" t="inlineStr">
+      <c r="J257" s="5" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="J257" s="5" t="inlineStr">
+      <c r="K257" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="U257" s="4" t="inlineStr">
+      <c r="V257" s="4" t="inlineStr">
         <is>
           <t>The work speaks to the trading branch of the belief and not to the voting branch.</t>
         </is>
       </c>
-      <c r="V257" s="4" t="inlineStr">
+      <c r="W257" s="4" t="inlineStr">
         <is>
           <t>Bears on one of the belief's two branches.</t>
         </is>
@@ -10217,37 +10333,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F258" s="4" t="inlineStr">
+      <c r="G258" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G258" s="4" t="inlineStr">
+      <c r="H258" s="4" t="inlineStr">
         <is>
           <t>insider-conflicted-congress-2021</t>
         </is>
       </c>
-      <c r="H258" s="4" t="inlineStr">
+      <c r="I258" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I258" s="5" t="inlineStr">
+      <c r="J258" s="5" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="J258" s="5" t="inlineStr">
+      <c r="K258" s="5" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="U258" s="4" t="inlineStr">
+      <c r="V258" s="4" t="inlineStr">
         <is>
           <t>The work speaks to the trading branch of the belief and not to the voting branch.</t>
         </is>
       </c>
-      <c r="V258" s="4" t="inlineStr">
+      <c r="W258" s="4" t="inlineStr">
         <is>
           <t>Bears on one of the belief's two branches.</t>
         </is>
@@ -10267,37 +10383,37 @@
           <t>linkage</t>
         </is>
       </c>
-      <c r="F259" s="4" t="inlineStr">
+      <c r="G259" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G259" s="4" t="inlineStr">
+      <c r="H259" s="4" t="inlineStr">
         <is>
           <t>eggers-hainmueller-capitol-losses</t>
         </is>
       </c>
-      <c r="H259" s="4" t="inlineStr">
+      <c r="I259" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="I259" s="5" t="inlineStr">
+      <c r="J259" s="5" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="J259" s="5" t="inlineStr">
+      <c r="K259" s="5" t="inlineStr">
         <is>
           <t>Weakens</t>
         </is>
       </c>
-      <c r="U259" s="4" t="inlineStr">
+      <c r="V259" s="4" t="inlineStr">
         <is>
           <t>The work speaks to the trading branch of the belief and not to the voting branch.</t>
         </is>
       </c>
-      <c r="V259" s="4" t="inlineStr">
+      <c r="W259" s="4" t="inlineStr">
         <is>
           <t>Bears on one of the belief's two branches.</t>
         </is>
@@ -10317,27 +10433,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F260" s="4" t="inlineStr">
+      <c r="G260" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G260" s="4" t="inlineStr">
+      <c r="H260" s="4" t="inlineStr">
         <is>
           <t>ziobrowski-cheng-boyd-ziobrowski</t>
         </is>
       </c>
-      <c r="H260" s="4" t="inlineStr">
+      <c r="I260" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="K260" s="4" t="inlineStr">
+      <c r="L260" s="4" t="inlineStr">
         <is>
           <t>work</t>
         </is>
       </c>
-      <c r="U260" s="4" t="inlineStr">
+      <c r="V260" s="4" t="inlineStr">
         <is>
           <t>Investors on the other side of the trades the study measures.</t>
         </is>
@@ -10357,27 +10473,27 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F261" s="4" t="inlineStr">
+      <c r="G261" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G261" s="4" t="inlineStr">
+      <c r="H261" s="4" t="inlineStr">
         <is>
           <t>insider-conflicted-congress-2021</t>
         </is>
       </c>
-      <c r="H261" s="4" t="inlineStr">
+      <c r="I261" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="K261" s="4" t="inlineStr">
+      <c r="L261" s="4" t="inlineStr">
         <is>
           <t>work</t>
         </is>
       </c>
-      <c r="U261" s="4" t="inlineStr">
+      <c r="V261" s="4" t="inlineStr">
         <is>
           <t>Voters relying on disclosure, and officials living under the rule being violated.</t>
         </is>
@@ -10397,46 +10513,49 @@
           <t>importance</t>
         </is>
       </c>
-      <c r="F262" s="4" t="inlineStr">
+      <c r="G262" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="G262" s="4" t="inlineStr">
+      <c r="H262" s="4" t="inlineStr">
         <is>
           <t>eggers-hainmueller-capitol-losses</t>
         </is>
       </c>
-      <c r="H262" s="4" t="inlineStr">
+      <c r="I262" s="4" t="inlineStr">
         <is>
           <t>barring-members-congress-president</t>
         </is>
       </c>
-      <c r="K262" s="4" t="inlineStr">
+      <c r="L262" s="4" t="inlineStr">
         <is>
           <t>work</t>
         </is>
       </c>
-      <c r="U262" s="4" t="inlineStr">
+      <c r="V262" s="4" t="inlineStr">
         <is>
           <t>Investors, if the advantage the belief assumes is not there.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X262"/>
-  <dataValidations count="4">
+  <autoFilter ref="A1:Z262"/>
+  <dataValidations count="5">
     <dataValidation sqref="C2:C5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"belief,claim,linkage,importance,interest,uniqueness,equivalence,driver,media"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Argument,Evidence,Prediction,Interest,Media,Book,Study,Article,Report,Film,Podcast,Video"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Supports,Weakens,Support,Opposition"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"analogy,anecdote,artifact,expert_claim,expert_data,eyewitness,historical,intuition,logic,meta,news,norm,observational,rct,record,statistics,survey,visual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="Y2:Y5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Modest,Moderate,Strong,Total"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -31420,4 +31539,103 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>parent</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>definition</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>government-ethics</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Government ethics</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Rules and norms about how people who hold public power may use it, and who checks them.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Conflicts of interest, disclosure, clemency, appointments and the limits on each. Electoral rules and campaign finance have their own topics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Public office and private gain</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>government-ethics</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Whether, and how, the law should stop officeholders and their families from using an office to make money.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Holdings and trading rules, family appointments, published tax returns and the reversal of pardons. Bribery statutes and lobbying rules belong to neighbouring topics.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
 </file>
--- a/tools/static-site/ISE_Data_Entry.xlsx
+++ b/tools/static-site/ISE_Data_Entry.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'pages'!$A$1:$Z$262</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'edges'!$A$1:$T$885</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'edges'!$A$1:$T$897</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'topics'!$A$1:$E$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10569,7 +10569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T885"/>
+  <dimension ref="A1:T897"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -31526,11 +31526,285 @@
         </is>
       </c>
     </row>
+    <row r="886">
+      <c r="A886" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B886" s="5" t="inlineStr">
+        <is>
+          <t>direction</t>
+        </is>
+      </c>
+      <c r="E886" s="4" t="inlineStr">
+        <is>
+          <t>Existing disclosure rules and conflict-of-interest statutes already catch what matters; new bans mostly deter capable people of ordinary means from serving.</t>
+        </is>
+      </c>
+      <c r="O886" s="4" t="inlineStr">
+        <is>
+          <t>-50</t>
+        </is>
+      </c>
+      <c r="T886" s="4" t="inlineStr">
+        <is>
+          <t>argument: A holdings ban or a publication rule reaches the honest official and the family who never ran, while the determined one restructures around it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B887" s="5" t="inlineStr">
+        <is>
+          <t>direction</t>
+        </is>
+      </c>
+      <c r="E887" s="4" t="inlineStr">
+        <is>
+          <t>Whether a rule helps depends on the mechanism: strengthen the disclosure form and the audits first, and ban only where disclosure has been shown to fail.</t>
+        </is>
+      </c>
+      <c r="O887" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T887" s="4" t="inlineStr">
+        <is>
+          <t>argument: Both sides want conflicts visible; they disagree about which document shows them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B888" s="5" t="inlineStr">
+        <is>
+          <t>stack</t>
+        </is>
+      </c>
+      <c r="O888" s="4" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="T888" s="4" t="inlineStr">
+        <is>
+          <t>worldview: Public power is held in trust, and a trustee may not profit from the trust | political: Rules that bind officials must bind them equally, whichever party holds office | causal: Where an official holds a private stake in a decision, the decision moves toward the stake | specific: Disclosure alone has not stopped members trading in the industries their committees oversee</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B889" s="5" t="inlineStr">
+        <is>
+          <t>stack</t>
+        </is>
+      </c>
+      <c r="O889" s="4" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="T889" s="4" t="inlineStr">
+        <is>
+          <t>worldview: Officials keep the ordinary rights of citizens unless a rule earns its exception | political: The burden is on a new restriction to show the old one failed | causal: Most conflicts are already visible on the disclosure form; the question is who acts on them | specific: Strengthen the form and the audits before reaching for a ban</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B890" s="5" t="inlineStr">
+        <is>
+          <t>stack</t>
+        </is>
+      </c>
+      <c r="O890" s="4" t="inlineStr">
+        <is>
+          <t>oppose</t>
+        </is>
+      </c>
+      <c r="T890" s="4" t="inlineStr">
+        <is>
+          <t>worldview: A capable person of ordinary means must be able to serve without a lawyer and without a pay cut | political: Ethics rules written after a scandal punish the next honest officeholder, not the last dishonest one | causal: Sophisticated wealth sits in entities a personal rule never reaches | specific: Each new rule deters more candidates than it catches conflicts</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B891" s="5" t="inlineStr">
+        <is>
+          <t>topic_values</t>
+        </is>
+      </c>
+      <c r="C891" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="T891" s="4" t="inlineStr">
+        <is>
+          <t>advertised: Honest government; Accountability; Transparency | critics: Punishing wealth as such; A scandal-driven urge to be seen doing something</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B892" s="5" t="inlineStr">
+        <is>
+          <t>topic_values</t>
+        </is>
+      </c>
+      <c r="C892" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="T892" s="4" t="inlineStr">
+        <is>
+          <t>advertised: Property rights; Privacy for families who hold no office; Open service to people of ordinary means | critics: Keeping a lucrative arrangement; Treating complexity as a reason nobody should look</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B893" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E893" s="4" t="inlineStr">
+        <is>
+          <t>Both sides want conflicts visible; they disagree about which document shows them.</t>
+        </is>
+      </c>
+      <c r="O893" s="4" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B894" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E894" s="4" t="inlineStr">
+        <is>
+          <t>Neither side wants rules an honest official cannot follow without a lawyer.</t>
+        </is>
+      </c>
+      <c r="O894" s="4" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B895" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E895" s="4" t="inlineStr">
+        <is>
+          <t>An officeholder’s family’s privacy against the public’s need to see entanglements before voting: no likelihood shift dissolves the trade-off.</t>
+        </is>
+      </c>
+      <c r="O895" s="4" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B896" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E896" s="4" t="inlineStr">
+        <is>
+          <t>Require exact values rather than ranges on the disclosure form, add foreign income and lender identity, and require the president alone to publish returns.</t>
+        </is>
+      </c>
+      <c r="O896" s="4" t="inlineStr">
+        <is>
+          <t>compromise</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B897" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E897" s="4" t="inlineStr">
+        <is>
+          <t>Blind trusts or index funds for members, with a holdings ban only where a committee oversees the industry.</t>
+        </is>
+      </c>
+      <c r="O897" s="4" t="inlineStr">
+        <is>
+          <t>compromise</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T885"/>
+  <autoFilter ref="A1:T897"/>
   <dataValidations count="2">
     <dataValidation sqref="B2:B5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"argument,assumption,bias,category,cba,component,compromise,definition,dispute,downstream,evidence,impact,interest,interest_listing,law,long_term,media,motive,obstacle,person,prediction,related,shared_interest,short_term,similar,upstream,value"</formula1>
+      <formula1>"argument,assumption,bias,category,cba,common,component,compromise,criteria,definition,direction,dispute,downstream,engagement,evidence,impact,interest,interest_listing,law,long_term,media,motive,obstacle,person,prediction,related,rung,shared_interest,short_term,similar,stack,strength,topic_media,topic_values,upstream,value"</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"agree,disagree,extreme,moderate,x,y"</formula1>

--- a/tools/static-site/ISE_Data_Entry.xlsx
+++ b/tools/static-site/ISE_Data_Entry.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'pages'!$A$1:$Z$262</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'edges'!$A$1:$T$897</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'topics'!$A$1:$E$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'topics'!$A$1:$E$79</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -31821,7 +31821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -31869,6 +31869,11 @@
           <t>Government ethics</t>
         </is>
       </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>government</t>
+        </is>
+      </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Rules and norms about how people who hold public power may use it, and who checks them.</t>
@@ -31907,8 +31912,1300 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>business-and-economy</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Business &amp; Economy</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Beliefs about how people trade, work, invest and are paid, and what the law should do about it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>business</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>business-and-economy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>business-and-economy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>trade</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Trade</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>business-and-economy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Jobs</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>business-and-economy</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>consumer-protection</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Protection</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>business-and-economy</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>computers-and-internet</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Computers &amp; Internet</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Beliefs about software, networks and the rules that govern them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>internet</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>computers-and-internet</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>software</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>computers-and-internet</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>privacy-and-data</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Privacy and Data</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>computers-and-internet</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>computers-and-internet</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>artificial-intelligence</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>computers-and-internet</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>news-and-media</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>News &amp; Media</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Beliefs about how news is made, paid for and trusted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>newspapers</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Newspapers</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>news-and-media</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>television</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Television</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>news-and-media</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>radio</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Radio</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>news-and-media</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>social-media</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Social Media</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>news-and-media</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>press-freedom</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Press Freedom</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>news-and-media</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>entertainment</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Beliefs about film, music, humor and the industries behind them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>movies</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Movies</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>entertainment</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>music</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>entertainment</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>humor</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Humor</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>entertainment</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>publishing</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Publishing</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>entertainment</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>recreation-and-sports</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Recreation &amp; Sports</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Beliefs about sport, travel, cars and the outdoors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>sports</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>recreation-and-sports</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>travel</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>recreation-and-sports</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>autos</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Autos</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>recreation-and-sports</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>outdoors</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Outdoors</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>recreation-and-sports</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Beliefs about disease, treatment, fitness and the systems that deliver care.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>diseases</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Diseases</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>drugs</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Drugs</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>fitness</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Fitness</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>medicine</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Medicine</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>health-insurance</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Health Insurance</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>government</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Beliefs about how public power is won, held, used and checked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>elections</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Elections</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>government</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>military</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Military</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>government</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>law</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Law</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>government</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>government</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>regional</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Beliefs that belong to one place: a country, a region, a state or a city.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>countries</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>regions</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Regions</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>u-s-states</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>U.S. States</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>cities</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Cities</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>society-and-culture</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Society &amp; Culture</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Beliefs about people, communities, the environment and belief itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>society-and-culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>environment</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>society-and-culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>religion</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Religion</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>society-and-culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>society-and-culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>crime-and-justice</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Crime and Justice</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>society-and-culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Beliefs about schools, universities and how people learn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>college-and-university</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>College and University</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>k-12</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>K-12</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>teaching</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Teaching</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>student-debt</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Student Debt</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>arts-and-humanities</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Arts &amp; Humanities</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Beliefs about art, history, literature and philosophy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>photography</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>arts-and-humanities</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>history</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>arts-and-humanities</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>literature</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Literature</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>arts-and-humanities</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>philosophy</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Philosophy</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>arts-and-humanities</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>science</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Beliefs about what is known about the natural world and how.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>animals</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Animals</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>science</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>astronomy</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Astronomy</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>science</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>engineering</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>science</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>climate</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>Climate</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>science</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>physics</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>science</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>social-science</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>Social Science</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>Beliefs about how people behave, alone and together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>languages</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Languages</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>social-science</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>archaeology</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Archaeology</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>social-science</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>psychology</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Psychology</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>social-science</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>economics</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>social-science</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>sociology</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Sociology</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>social-science</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Definitions, statistics and quotations the other topics rest on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>dictionaries</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Dictionaries</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>statistics</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>Statistics</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>quotations</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Quotations</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E3"/>
+  <autoFilter ref="A1:E79"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>

--- a/tools/static-site/ISE_Data_Entry.xlsx
+++ b/tools/static-site/ISE_Data_Entry.xlsx
@@ -13,7 +13,7 @@
     <sheet name="topics" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'pages'!$A$1:$Z$262</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'pages'!$A$1:$AC$262</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'edges'!$A$1:$T$897</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'topics'!$A$1:$E$79</definedName>
   </definedNames>
@@ -282,15 +282,30 @@
     </comment>
     <comment ref="X1" authorId="0" shapeId="0">
       <text>
-        <t>belief: -100 to +100 on the topic page.</t>
+        <t>belief: one or two sentences naming an itch the reader already feels. Concrete, not abstract. Shown in the box under the heading.</t>
       </text>
     </comment>
     <comment ref="Y1" authorId="0" shapeId="0">
       <text>
+        <t>belief: one sentence ending in a question mark, stating exactly what the page dissects. Answerable, not rhetorical.</t>
+      </text>
+    </comment>
+    <comment ref="Z1" authorId="0" shapeId="0">
+      <text>
+        <t>belief: one specific slot a newcomer can fill in five minutes. Leave blank and the page names its own emptiest slot.</t>
+      </text>
+    </comment>
+    <comment ref="AA1" authorId="0" shapeId="0">
+      <text>
+        <t>belief: -100 to +100 on the topic page.</t>
+      </text>
+    </comment>
+    <comment ref="AB1" authorId="0" shapeId="0">
+      <text>
         <t>belief: how absolute the claim is, as a label. Modest (hedged), Moderate (definite but bounded), Strong (near-universal) or Total (no exceptions). Typed, never scored: it places the belief on the topic page and nothing reads it as a number.</t>
       </text>
     </comment>
-    <comment ref="Z1" authorId="0" shapeId="0">
+    <comment ref="AC1" authorId="0" shapeId="0">
       <text>
         <t>belief: the logical form of the claim.</t>
       </text>
@@ -839,7 +854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z262"/>
+  <dimension ref="A1:AC262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -867,7 +882,10 @@
     <col width="60" customWidth="1" min="23" max="23"/>
     <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="60" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="60" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -988,15 +1006,30 @@
       </c>
       <c r="X1" s="3" t="inlineStr">
         <is>
+          <t>hook</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="Z1" s="3" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AA1" s="3" t="inlineStr">
+        <is>
           <t>positivity</t>
         </is>
       </c>
-      <c r="Y1" s="3" t="inlineStr">
+      <c r="AB1" s="3" t="inlineStr">
         <is>
           <t>strength</t>
         </is>
       </c>
-      <c r="Z1" s="3" t="inlineStr">
+      <c r="AC1" s="3" t="inlineStr">
         <is>
           <t>form</t>
         </is>
@@ -1036,15 +1069,25 @@
           <t>The conflict is documented and the disclosure regime demonstrably fails. Whether a ban removes the conflict or relocates it into spouses, partnerships and the revolving door is the open question. It is one of three load-bearing components all sitting at the neutral start, and while they sit there any one of them caps what this page can read, however far the evidence carries the argument.</t>
         </is>
       </c>
-      <c r="X2" s="5" t="n">
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Members of Congress trade in the industries their own committees oversee, and the penalty for filing late is a $200 fee that is routinely waived.</t>
+        </is>
+      </c>
+      <c r="Y2" s="5" t="inlineStr">
+        <is>
+          <t>Would barring members of Congress and the president from holding individual stocks reduce the use of office for private gain, or move the money somewhere the rule cannot see?</t>
+        </is>
+      </c>
+      <c r="AA2" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="Y2" s="5" t="inlineStr">
+      <c r="AB2" s="5" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="Z2" s="4" t="inlineStr">
+      <c r="AC2" s="4" t="inlineStr">
         <is>
           <t>(Officials' holdings currently influence official decisions) AND (removing the holdings removes the influence rather than relocating it) AND (a ban can be enacted and enforced). The normative component, that reducing conflicts is worth a narrower candidate pool, is separable.</t>
         </is>
@@ -1084,15 +1127,25 @@
           <t>The legal gap is documented and the supervision problem is real. The page turns on whether a bar removes the conflict or converts a disclosed adviser into an undisclosed one. All three load-bearing components sit at the neutral start, so nothing has been established here yet and nothing is capping anything: the work is to argue them.</t>
         </is>
       </c>
-      <c r="X3" s="5" t="n">
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>The anti-nepotism statute stops at the White House door.</t>
+        </is>
+      </c>
+      <c r="Y3" s="5" t="inlineStr">
+        <is>
+          <t>Would barring the president and members of Congress from handing official functions to relatives reduce the use of office for private gain?</t>
+        </is>
+      </c>
+      <c r="AA3" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="Y3" s="5" t="inlineStr">
+      <c r="AB3" s="5" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="Z3" s="4" t="inlineStr">
+      <c r="AC3" s="4" t="inlineStr">
         <is>
           <t>(Relatives in official roles produce conflicts that ordinary supervision cannot check) AND (a bar removes those conflicts rather than driving them out of view) AND (Congress can impose the bar on the White House). The third component is where the legal fight is.</t>
         </is>
@@ -1132,15 +1185,25 @@
           <t>The documentary claim is the strongest part: returns do carry conflict-relevant facts the disclosure form omits. What nobody can show is that publishing them changes anything. All three load-bearing components sit at the neutral start, so what this page needs is not more evidence for the conclusion but an argument for each of its parts.</t>
         </is>
       </c>
-      <c r="X4" s="5" t="n">
+      <c r="X4" s="5" t="inlineStr">
+        <is>
+          <t>Every president from Carter through Obama published tax returns without a law requiring it.</t>
+        </is>
+      </c>
+      <c r="Y4" s="5" t="inlineStr">
+        <is>
+          <t>Would requiring the president and members of Congress to publish their tax returns reduce the use of office for private gain, or expose spouses and partners for little in return?</t>
+        </is>
+      </c>
+      <c r="AA4" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="Y4" s="5" t="inlineStr">
+      <c r="AB4" s="5" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="AC4" s="4" t="inlineStr">
         <is>
           <t>(Returns contain conflict-relevant information the disclosure form lacks) AND (publishing it changes behavior or enables a check) AND (a publication requirement can be imposed). The first is documentary, the second is contested, the third is narrower than the usual objection assumes.</t>
         </is>
@@ -1180,15 +1243,25 @@
           <t>The gap is real: clemency is the only federal power with no check, and grants to the president's own circle are documented in both parties. All three load-bearing components sit at the neutral start, so any one of them caps the page. The one to argue first is not the constitutional objection but whether an override could ever be exercised at a two-thirds threshold against a president whose own party holds a third of either chamber.</t>
         </is>
       </c>
-      <c r="X5" s="5" t="n">
+      <c r="X5" s="5" t="inlineStr">
+        <is>
+          <t>A pardon is final the moment it is signed, and no other executive power has so little standing over it.</t>
+        </is>
+      </c>
+      <c r="Y5" s="5" t="inlineStr">
+        <is>
+          <t>Would letting Congress overturn a pardon by a two-thirds vote of both chambers reduce the use of the pardon power for private gain?</t>
+        </is>
+      </c>
+      <c r="AA5" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="Y5" s="5" t="inlineStr">
+      <c r="AB5" s="5" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="Z5" s="4" t="inlineStr">
+      <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>(Some pardons are granted for the president's private benefit) AND (a congressional override would deter or reverse those grants) AND (an override can be enacted). The third component is legal rather than empirical, and it is the one most likely to hold this page down once all three have been argued.</t>
         </is>
@@ -1223,10 +1296,20 @@
           <t>Held nearly universally at this level of generality, which is why the argument always moves to the specific rules below it.</t>
         </is>
       </c>
-      <c r="X6" s="5" t="n">
+      <c r="X6" s="5" t="inlineStr">
+        <is>
+          <t>Every federal ethics statute since the 1962 reforms rests on one sentence, and the sentence itself is rarely argued.</t>
+        </is>
+      </c>
+      <c r="Y6" s="5" t="inlineStr">
+        <is>
+          <t>Should public office be unusable for private gain, without exception, or are there gains an officeholder may keep?</t>
+        </is>
+      </c>
+      <c r="AA6" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="Y6" s="5" t="inlineStr">
+      <c r="AB6" s="5" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
@@ -10540,7 +10623,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z262"/>
+  <autoFilter ref="A1:AC262"/>
   <dataValidations count="5">
     <dataValidation sqref="C2:C5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"belief,claim,linkage,importance,interest,uniqueness,equivalence,driver,media"</formula1>
@@ -10554,7 +10637,7 @@
     <dataValidation sqref="P2:P5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"analogy,anecdote,artifact,expert_claim,expert_data,eyewitness,historical,intuition,logic,meta,news,norm,observational,rct,record,statistics,survey,visual"</formula1>
     </dataValidation>
-    <dataValidation sqref="Y2:Y5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AB2:AB5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Modest,Moderate,Strong,Total"</formula1>
     </dataValidation>
   </dataValidations>
@@ -31804,7 +31887,7 @@
   <autoFilter ref="A1:T897"/>
   <dataValidations count="2">
     <dataValidation sqref="B2:B5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"argument,assumption,bias,category,cba,common,component,compromise,criteria,definition,direction,dispute,downstream,engagement,evidence,impact,interest,interest_listing,law,long_term,media,motive,obstacle,person,prediction,related,rung,shared_interest,short_term,similar,stack,strength,topic_media,topic_values,upstream,value"</formula1>
+      <formula1>"argument,assumption,bias,category,cba,common,component,compromise,criteria,criterion,definition,direction,dispute,downstream,engagement,evidence,falsify,impact,interest,interest_listing,law,long_term,media,motive,obstacle,person,prediction,related,rung,shared_interest,short_term,similar,stack,strength,topic_media,topic_values,upstream,value"</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"agree,disagree,extreme,moderate,x,y"</formula1>

--- a/tools/static-site/ISE_Data_Entry.xlsx
+++ b/tools/static-site/ISE_Data_Entry.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'pages'!$A$1:$AC$262</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'edges'!$A$1:$T$897</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'edges'!$A$1:$T$898</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'topics'!$A$1:$E$79</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10652,7 +10652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T897"/>
+  <dimension ref="A1:T898"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -31883,8 +31883,30 @@
         </is>
       </c>
     </row>
+    <row r="898">
+      <c r="A898" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B898" s="5" t="inlineStr">
+        <is>
+          <t>topic_media</t>
+        </is>
+      </c>
+      <c r="D898" s="4" t="inlineStr">
+        <is>
+          <t>insider-conflicted-congress-2021</t>
+        </is>
+      </c>
+      <c r="T898" s="4" t="inlineStr">
+        <is>
+          <t>medium: Report | tone: Journalistic</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T897"/>
+  <autoFilter ref="A1:T898"/>
   <dataValidations count="2">
     <dataValidation sqref="B2:B5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"argument,assumption,bias,category,cba,common,component,compromise,criteria,criterion,definition,direction,dispute,downstream,engagement,evidence,falsify,impact,interest,interest_listing,law,long_term,media,motive,obstacle,person,prediction,related,rung,shared_interest,short_term,similar,stack,strength,topic_media,topic_values,upstream,value"</formula1>

--- a/tools/static-site/ISE_Data_Entry.xlsx
+++ b/tools/static-site/ISE_Data_Entry.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'pages'!$A$1:$AC$262</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'edges'!$A$1:$T$898</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'topics'!$A$1:$E$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'topics'!$A$1:$F$79</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -455,6 +455,11 @@
         <t>topic: what sits inside this page and what belongs to a neighbouring topic with its own page.</t>
       </text>
     </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>topic: what a positive position means on this topic and what a negative one means, so a reader can place a belief on Continuum 1 without guessing. Blank means the site says only Oppose and Support.</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -31926,7 +31931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -31934,6 +31939,7 @@
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31962,6 +31968,11 @@
           <t>scope</t>
         </is>
       </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>axis</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -33310,7 +33321,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E79"/>
+  <autoFilter ref="A1:F79"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>

--- a/tools/static-site/ISE_Data_Entry.xlsx
+++ b/tools/static-site/ISE_Data_Entry.xlsx
@@ -13,8 +13,8 @@
     <sheet name="topics" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'pages'!$A$1:$AC$262</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'edges'!$A$1:$T$898</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'pages'!$A$1:$AC$402</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'edges'!$A$1:$T$1058</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'topics'!$A$1:$F$79</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -859,7 +859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC262"/>
+  <dimension ref="A1:AC402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -10627,8 +10627,3348 @@
         </is>
       </c>
     </row>
+    <row r="263">
+      <c r="A263" s="4" t="inlineStr">
+        <is>
+          <t>large-companies-required-law</t>
+        </is>
+      </c>
+      <c r="C263" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D263" s="4" t="inlineStr">
+        <is>
+          <t>Large companies should be required by law to give their workers seats on their boards.</t>
+        </is>
+      </c>
+      <c r="F263" s="5" t="inlineStr">
+        <is>
+          <t>business</t>
+        </is>
+      </c>
+      <c r="W263" s="4" t="inlineStr">
+        <is>
+          <t>Whether the people whose jobs depend on a company have a stronger claim to steer it than the people whose money does.</t>
+        </is>
+      </c>
+      <c r="AA263" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB263" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="4" t="inlineStr">
+        <is>
+          <t>workers-bear-costs-bad</t>
+        </is>
+      </c>
+      <c r="C264" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D264" s="4" t="inlineStr">
+        <is>
+          <t>Workers bear the costs of bad decisions such as layoffs and plant closures, so they deserve a voice in making them.</t>
+        </is>
+      </c>
+      <c r="G264" s="4" t="inlineStr">
+        <is>
+          <t>large-companies-required-law</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="4" t="inlineStr">
+        <is>
+          <t>workers-know-how-company</t>
+        </is>
+      </c>
+      <c r="C265" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D265" s="4" t="inlineStr">
+        <is>
+          <t>Workers know how the company actually runs day to day, and boards make better decisions with that knowledge in the room.</t>
+        </is>
+      </c>
+      <c r="G265" s="4" t="inlineStr">
+        <is>
+          <t>large-companies-required-law</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="4" t="inlineStr">
+        <is>
+          <t>board-answers-only-shareholders</t>
+        </is>
+      </c>
+      <c r="C266" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D266" s="4" t="inlineStr">
+        <is>
+          <t>A board that answers only to shareholders tends to chase short-term stock gains at the expense of the company's long-term health.</t>
+        </is>
+      </c>
+      <c r="G266" s="4" t="inlineStr">
+        <is>
+          <t>large-companies-required-law</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="4" t="inlineStr">
+        <is>
+          <t>owners-put-money-risk</t>
+        </is>
+      </c>
+      <c r="C267" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D267" s="4" t="inlineStr">
+        <is>
+          <t>Owners put their money at risk, and the people who bear the financial risk should be the ones who control the company.</t>
+        </is>
+      </c>
+      <c r="G267" s="4" t="inlineStr">
+        <is>
+          <t>large-companies-required-law</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="4" t="inlineStr">
+        <is>
+          <t>worker-directors-face-conflict</t>
+        </is>
+      </c>
+      <c r="C268" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D268" s="4" t="inlineStr">
+        <is>
+          <t>Worker directors face a conflict of interest whenever the board must cut jobs or close a site to keep the company alive.</t>
+        </is>
+      </c>
+      <c r="G268" s="4" t="inlineStr">
+        <is>
+          <t>large-companies-required-law</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="4" t="inlineStr">
+        <is>
+          <t>boards-two-sets-loyalties</t>
+        </is>
+      </c>
+      <c r="C269" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D269" s="4" t="inlineStr">
+        <is>
+          <t>Boards with two sets of loyalties reach decisions more slowly, and slow companies lose to faster rivals.</t>
+        </is>
+      </c>
+      <c r="G269" s="4" t="inlineStr">
+        <is>
+          <t>large-companies-required-law</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="4" t="inlineStr">
+        <is>
+          <t>company-generally-serves-public</t>
+        </is>
+      </c>
+      <c r="C270" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D270" s="4" t="inlineStr">
+        <is>
+          <t>A company generally serves the public best when it focuses on making a profit for its owners within the law.</t>
+        </is>
+      </c>
+      <c r="F270" s="5" t="inlineStr">
+        <is>
+          <t>business</t>
+        </is>
+      </c>
+      <c r="W270" s="4" t="inlineStr">
+        <is>
+          <t>Whether profit within the law is a good enough stand-in for public benefit or leaves too much harm uncounted.</t>
+        </is>
+      </c>
+      <c r="AA270" s="5" t="n">
+        <v>-50</v>
+      </c>
+      <c r="AB270" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="4" t="inlineStr">
+        <is>
+          <t>profit-signal-company-making</t>
+        </is>
+      </c>
+      <c r="C271" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D271" s="4" t="inlineStr">
+        <is>
+          <t>Profit is a signal that a company is making something people want at a price they will pay, which is itself a public service.</t>
+        </is>
+      </c>
+      <c r="G271" s="4" t="inlineStr">
+        <is>
+          <t>company-generally-serves-public</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="4" t="inlineStr">
+        <is>
+          <t>managers-who-told-serve</t>
+        </is>
+      </c>
+      <c r="C272" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D272" s="4" t="inlineStr">
+        <is>
+          <t>Managers who are told to serve everyone end up answering to no one and can excuse poor results as serving some other goal.</t>
+        </is>
+      </c>
+      <c r="G272" s="4" t="inlineStr">
+        <is>
+          <t>company-generally-serves-public</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="4" t="inlineStr">
+        <is>
+          <t>broad-social-problems-job</t>
+        </is>
+      </c>
+      <c r="C273" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D273" s="4" t="inlineStr">
+        <is>
+          <t>Broad social problems are the job of elected governments, which answer to voters, not of managers who answer to no voter.</t>
+        </is>
+      </c>
+      <c r="G273" s="4" t="inlineStr">
+        <is>
+          <t>company-generally-serves-public</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="4" t="inlineStr">
+        <is>
+          <t>many-company-s-costs</t>
+        </is>
+      </c>
+      <c r="C274" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D274" s="4" t="inlineStr">
+        <is>
+          <t>Many of a company's costs, like pollution or worker burnout, fall on people who never agreed to bear them and never show up in the profit figure.</t>
+        </is>
+      </c>
+      <c r="G274" s="4" t="inlineStr">
+        <is>
+          <t>company-generally-serves-public</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="4" t="inlineStr">
+        <is>
+          <t>law-always-lags-behind</t>
+        </is>
+      </c>
+      <c r="C275" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D275" s="4" t="inlineStr">
+        <is>
+          <t>The law always lags behind business practice, so a company that does only what the law requires will harm people the law has not yet caught up with.</t>
+        </is>
+      </c>
+      <c r="G275" s="4" t="inlineStr">
+        <is>
+          <t>company-generally-serves-public</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="4" t="inlineStr">
+        <is>
+          <t>companies-treat-workers-suppliers</t>
+        </is>
+      </c>
+      <c r="C276" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D276" s="4" t="inlineStr">
+        <is>
+          <t>Companies that treat workers, suppliers and towns well tend to earn trust that pays off over decades, which a narrow focus on profit misses.</t>
+        </is>
+      </c>
+      <c r="G276" s="4" t="inlineStr">
+        <is>
+          <t>company-generally-serves-public</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="4" t="inlineStr">
+        <is>
+          <t>streaming-services-generally-pay</t>
+        </is>
+      </c>
+      <c r="C277" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D277" s="4" t="inlineStr">
+        <is>
+          <t>Streaming services generally pay working musicians too little to make a living from recorded music.</t>
+        </is>
+      </c>
+      <c r="F277" s="5" t="inlineStr">
+        <is>
+          <t>music</t>
+        </is>
+      </c>
+      <c r="W277" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether the right comparison is with the old record business or with the obscurity most musicians faced before it.</t>
+        </is>
+      </c>
+      <c r="AA277" s="5" t="n">
+        <v>-60</v>
+      </c>
+      <c r="AB277" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="4" t="inlineStr">
+        <is>
+          <t>single-play-earns-almost</t>
+        </is>
+      </c>
+      <c r="C278" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D278" s="4" t="inlineStr">
+        <is>
+          <t>A single play earns almost nothing, so only artists with enormous audiences see meaningful income from their recordings.</t>
+        </is>
+      </c>
+      <c r="G278" s="4" t="inlineStr">
+        <is>
+          <t>streaming-services-generally-pay</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="4" t="inlineStr">
+        <is>
+          <t>money-split-so-most</t>
+        </is>
+      </c>
+      <c r="C279" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D279" s="4" t="inlineStr">
+        <is>
+          <t>The money is split so that most of it flows to labels, publishers and the platforms before any reaches the person who wrote or performed the song.</t>
+        </is>
+      </c>
+      <c r="G279" s="4" t="inlineStr">
+        <is>
+          <t>streaming-services-generally-pay</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="4" t="inlineStr">
+        <is>
+          <t>musicians-now-depend-touring</t>
+        </is>
+      </c>
+      <c r="C280" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D280" s="4" t="inlineStr">
+        <is>
+          <t>Musicians now depend on touring and merchandise to survive, which favors the young and healthy and pushes out those who cannot live on the road.</t>
+        </is>
+      </c>
+      <c r="G280" s="4" t="inlineStr">
+        <is>
+          <t>streaming-services-generally-pay</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="4" t="inlineStr">
+        <is>
+          <t>streaming-brought-paying-listeners</t>
+        </is>
+      </c>
+      <c r="C281" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D281" s="4" t="inlineStr">
+        <is>
+          <t>Streaming brought paying listeners back after years of free downloading, and total music income has grown again as a result, spread across far more artists.</t>
+        </is>
+      </c>
+      <c r="G281" s="4" t="inlineStr">
+        <is>
+          <t>streaming-services-generally-pay</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="4" t="inlineStr">
+        <is>
+          <t>before-streaming-most-musicians</t>
+        </is>
+      </c>
+      <c r="C282" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D282" s="4" t="inlineStr">
+        <is>
+          <t>Before streaming, most musicians earned nothing from recordings because they never got a record deal at all, so the comparison is with obscurity, not with a golden age.</t>
+        </is>
+      </c>
+      <c r="G282" s="4" t="inlineStr">
+        <is>
+          <t>streaming-services-generally-pay</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="4" t="inlineStr">
+        <is>
+          <t>low-per-play-rates</t>
+        </is>
+      </c>
+      <c r="C283" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D283" s="4" t="inlineStr">
+        <is>
+          <t>Low per-play rates reflect what listeners will pay for unlimited music, and forcing rates higher would shrink the audience rather than raise incomes.</t>
+        </is>
+      </c>
+      <c r="G283" s="4" t="inlineStr">
+        <is>
+          <t>streaming-services-generally-pay</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="4" t="inlineStr">
+        <is>
+          <t>streaming-has-clearly-done</t>
+        </is>
+      </c>
+      <c r="C284" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D284" s="4" t="inlineStr">
+        <is>
+          <t>Streaming has clearly done more good than harm for musicians by letting anyone reach a worldwide audience without a record label.</t>
+        </is>
+      </c>
+      <c r="F284" s="5" t="inlineStr">
+        <is>
+          <t>music</t>
+        </is>
+      </c>
+      <c r="W284" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether being able to publish anywhere is worth much when so many others can too.</t>
+        </is>
+      </c>
+      <c r="AA284" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB284" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="4" t="inlineStr">
+        <is>
+          <t>any-musician-can-upload</t>
+        </is>
+      </c>
+      <c r="C285" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D285" s="4" t="inlineStr">
+        <is>
+          <t>Any musician can upload a song and be heard anywhere in the world the same day, which was impossible when labels controlled distribution.</t>
+        </is>
+      </c>
+      <c r="G285" s="4" t="inlineStr">
+        <is>
+          <t>streaming-has-clearly-done</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="4" t="inlineStr">
+        <is>
+          <t>listeners-discover-artists-other</t>
+        </is>
+      </c>
+      <c r="C286" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D286" s="4" t="inlineStr">
+        <is>
+          <t>Listeners discover artists from other countries and small scenes, so careers can start from anywhere instead of a few music-industry cities.</t>
+        </is>
+      </c>
+      <c r="G286" s="4" t="inlineStr">
+        <is>
+          <t>streaming-has-clearly-done</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="4" t="inlineStr">
+        <is>
+          <t>artists-keep-rights-own</t>
+        </is>
+      </c>
+      <c r="C287" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D287" s="4" t="inlineStr">
+        <is>
+          <t>Artists keep the rights to their own work more often, because they no longer need a label's money to press records and ship them to stores.</t>
+        </is>
+      </c>
+      <c r="G287" s="4" t="inlineStr">
+        <is>
+          <t>streaming-has-clearly-done</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="4" t="inlineStr">
+        <is>
+          <t>when-everyone-can-publish</t>
+        </is>
+      </c>
+      <c r="C288" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D288" s="4" t="inlineStr">
+        <is>
+          <t>When everyone can publish, the flood of new songs makes it harder than ever for any one artist to be noticed, and reach without attention is worth little.</t>
+        </is>
+      </c>
+      <c r="G288" s="4" t="inlineStr">
+        <is>
+          <t>streaming-has-clearly-done</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="4" t="inlineStr">
+        <is>
+          <t>playlists-chosen-platform-staff</t>
+        </is>
+      </c>
+      <c r="C289" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D289" s="4" t="inlineStr">
+        <is>
+          <t>Playlists chosen by platform staff and software have replaced record labels as gatekeepers, so artists still depend on a few decision-makers they cannot reach.</t>
+        </is>
+      </c>
+      <c r="G289" s="4" t="inlineStr">
+        <is>
+          <t>streaming-has-clearly-done</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="4" t="inlineStr">
+        <is>
+          <t>making-music-available-almost</t>
+        </is>
+      </c>
+      <c r="C290" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D290" s="4" t="inlineStr">
+        <is>
+          <t>Making music available for almost nothing worldwide has taught listeners that music should cost nothing, and that expectation follows artists into every other part of their business.</t>
+        </is>
+      </c>
+      <c r="G290" s="4" t="inlineStr">
+        <is>
+          <t>streaming-has-clearly-done</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="4" t="inlineStr">
+        <is>
+          <t>comedians-generally-able-joke</t>
+        </is>
+      </c>
+      <c r="C291" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D291" s="4" t="inlineStr">
+        <is>
+          <t>Comedians should generally be able to joke about any subject without losing work over the offense a joke causes.</t>
+        </is>
+      </c>
+      <c r="F291" s="5" t="inlineStr">
+        <is>
+          <t>humor</t>
+        </is>
+      </c>
+      <c r="W291" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether losing bookings over a joke is censorship or simply the market answering back.</t>
+        </is>
+      </c>
+      <c r="AA291" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB291" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="4" t="inlineStr">
+        <is>
+          <t>comedy-works-saying-what</t>
+        </is>
+      </c>
+      <c r="C292" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D292" s="4" t="inlineStr">
+        <is>
+          <t>Comedy works by saying what people are not supposed to say, and a comedian who must avoid every touchy subject cannot do the job.</t>
+        </is>
+      </c>
+      <c r="G292" s="4" t="inlineStr">
+        <is>
+          <t>comedians-generally-able-joke</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="4" t="inlineStr">
+        <is>
+          <t>audiences-already-control-comedy</t>
+        </is>
+      </c>
+      <c r="C293" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D293" s="4" t="inlineStr">
+        <is>
+          <t>Audiences already control comedy by laughing or not, and a joke that lands badly punishes itself without anyone needing to end a career.</t>
+        </is>
+      </c>
+      <c r="G293" s="4" t="inlineStr">
+        <is>
+          <t>comedians-generally-able-joke</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="4" t="inlineStr">
+        <is>
+          <t>when-comedians-punished-offense</t>
+        </is>
+      </c>
+      <c r="C294" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D294" s="4" t="inlineStr">
+        <is>
+          <t>When comedians are punished for offense, the safest response is blandness, and the loss falls on every audience, not just the people who were offended.</t>
+        </is>
+      </c>
+      <c r="G294" s="4" t="inlineStr">
+        <is>
+          <t>comedians-generally-able-joke</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="4" t="inlineStr">
+        <is>
+          <t>losing-booking-censorship-venues</t>
+        </is>
+      </c>
+      <c r="C295" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D295" s="4" t="inlineStr">
+        <is>
+          <t>Losing a booking is not censorship; venues and networks are free to decide who they pay, just as comedians are free to speak.</t>
+        </is>
+      </c>
+      <c r="G295" s="4" t="inlineStr">
+        <is>
+          <t>comedians-generally-able-joke</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="4" t="inlineStr">
+        <is>
+          <t>joke-spreads-contempt-group</t>
+        </is>
+      </c>
+      <c r="C296" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D296" s="4" t="inlineStr">
+        <is>
+          <t>A joke that spreads contempt for a group is a public act with public consequences, and the person who makes it should answer for it like anyone else.</t>
+        </is>
+      </c>
+      <c r="G296" s="4" t="inlineStr">
+        <is>
+          <t>comedians-generally-able-joke</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="4" t="inlineStr">
+        <is>
+          <t>great-comedians-have-always</t>
+        </is>
+      </c>
+      <c r="C297" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D297" s="4" t="inlineStr">
+        <is>
+          <t>Great comedians have always worked within limits set by their audience and era, and doing so pushed them toward sharper and more original material.</t>
+        </is>
+      </c>
+      <c r="G297" s="4" t="inlineStr">
+        <is>
+          <t>comedians-generally-able-joke</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="4" t="inlineStr">
+        <is>
+          <t>jokes-mock-people-race</t>
+        </is>
+      </c>
+      <c r="C298" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D298" s="4" t="inlineStr">
+        <is>
+          <t>Jokes that mock people for their race, religion, disability or sex do real harm and deserve public pushback.</t>
+        </is>
+      </c>
+      <c r="F298" s="5" t="inlineStr">
+        <is>
+          <t>humor</t>
+        </is>
+      </c>
+      <c r="W298" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether a joke about a group targets the stereotype or the people, and on who gets to say which.</t>
+        </is>
+      </c>
+      <c r="AA298" s="5" t="n">
+        <v>-50</v>
+      </c>
+      <c r="AB298" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="4" t="inlineStr">
+        <is>
+          <t>laughter-makes-contempt-feel</t>
+        </is>
+      </c>
+      <c r="C299" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D299" s="4" t="inlineStr">
+        <is>
+          <t>Laughter makes contempt feel normal, so a joke can spread an ugly attitude further than a plain insult ever could.</t>
+        </is>
+      </c>
+      <c r="G299" s="4" t="inlineStr">
+        <is>
+          <t>jokes-mock-people-race</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="4" t="inlineStr">
+        <is>
+          <t>people-mocked-group-hear</t>
+        </is>
+      </c>
+      <c r="C300" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D300" s="4" t="inlineStr">
+        <is>
+          <t>People in the mocked group hear the joke too, and being the punchline in a room full of laughter teaches them they do not belong.</t>
+        </is>
+      </c>
+      <c r="G300" s="4" t="inlineStr">
+        <is>
+          <t>jokes-mock-people-race</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="4" t="inlineStr">
+        <is>
+          <t>pushback-itself-free-speech</t>
+        </is>
+      </c>
+      <c r="C301" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D301" s="4" t="inlineStr">
+        <is>
+          <t>Pushback is itself free speech; a comedian who claims the right to offend cannot deny others the right to answer.</t>
+        </is>
+      </c>
+      <c r="G301" s="4" t="inlineStr">
+        <is>
+          <t>jokes-mock-people-race</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="4" t="inlineStr">
+        <is>
+          <t>most-jokes-about-groups</t>
+        </is>
+      </c>
+      <c r="C302" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D302" s="4" t="inlineStr">
+        <is>
+          <t>Most jokes about groups poke at the stereotype rather than the people, and audiences understand the difference better than critics assume.</t>
+        </is>
+      </c>
+      <c r="G302" s="4" t="inlineStr">
+        <is>
+          <t>jokes-mock-people-race</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="4" t="inlineStr">
+        <is>
+          <t>comedians-within-group-often</t>
+        </is>
+      </c>
+      <c r="C303" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D303" s="4" t="inlineStr">
+        <is>
+          <t>Comedians from within a group often tell the sharpest jokes about it, and a blanket rule against such jokes silences them first.</t>
+        </is>
+      </c>
+      <c r="G303" s="4" t="inlineStr">
+        <is>
+          <t>jokes-mock-people-race</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="4" t="inlineStr">
+        <is>
+          <t>organized-pushback-rarely-stays</t>
+        </is>
+      </c>
+      <c r="C304" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D304" s="4" t="inlineStr">
+        <is>
+          <t>Organized pushback rarely stays with the worst offenders; it quickly reaches mild jokes and creates a fear that shrinks comedy for everyone.</t>
+        </is>
+      </c>
+      <c r="G304" s="4" t="inlineStr">
+        <is>
+          <t>jokes-mock-people-race</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="4" t="inlineStr">
+        <is>
+          <t>traditional-publishers-still-generally</t>
+        </is>
+      </c>
+      <c r="C305" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D305" s="4" t="inlineStr">
+        <is>
+          <t>Traditional publishers still generally produce better books for readers than self-publishing does.</t>
+        </is>
+      </c>
+      <c r="F305" s="5" t="inlineStr">
+        <is>
+          <t>publishing</t>
+        </is>
+      </c>
+      <c r="W305" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether a publisher's filter selects for quality or merely for what it expects to sell.</t>
+        </is>
+      </c>
+      <c r="AA305" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB305" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="4" t="inlineStr">
+        <is>
+          <t>publisher-s-editors-designers</t>
+        </is>
+      </c>
+      <c r="C306" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D306" s="4" t="inlineStr">
+        <is>
+          <t>A publisher's editors, designers and fact-checkers catch problems an author working alone cannot see, and readers get a cleaner book as a result.</t>
+        </is>
+      </c>
+      <c r="G306" s="4" t="inlineStr">
+        <is>
+          <t>traditional-publishers-still-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="4" t="inlineStr">
+        <is>
+          <t>publishers-pay-authors-advance</t>
+        </is>
+      </c>
+      <c r="C307" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D307" s="4" t="inlineStr">
+        <is>
+          <t>Publishers pay authors in advance, which lets writers spend a year or more on a book instead of rushing out whatever sells fastest.</t>
+        </is>
+      </c>
+      <c r="G307" s="4" t="inlineStr">
+        <is>
+          <t>traditional-publishers-still-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="4" t="inlineStr">
+        <is>
+          <t>when-publisher-has-invest</t>
+        </is>
+      </c>
+      <c r="C308" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D308" s="4" t="inlineStr">
+        <is>
+          <t>When a publisher has to invest its own money in a book, it must judge whether the book is worth a reader's time, and that judgment filters out a great deal of weak work.</t>
+        </is>
+      </c>
+      <c r="G308" s="4" t="inlineStr">
+        <is>
+          <t>traditional-publishers-still-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="4" t="inlineStr">
+        <is>
+          <t>publishers-pick-books-think</t>
+        </is>
+      </c>
+      <c r="C309" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D309" s="4" t="inlineStr">
+        <is>
+          <t>Publishers pick books they think will sell, not books that are good, so their filter favors the familiar and rejects much that readers would love.</t>
+        </is>
+      </c>
+      <c r="G309" s="4" t="inlineStr">
+        <is>
+          <t>traditional-publishers-still-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="4" t="inlineStr">
+        <is>
+          <t>online-reviews-recommendations-now</t>
+        </is>
+      </c>
+      <c r="C310" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D310" s="4" t="inlineStr">
+        <is>
+          <t>Online reviews and recommendations now do the sorting that publishers once did, and they do it with far more readers weighing in.</t>
+        </is>
+      </c>
+      <c r="G310" s="4" t="inlineStr">
+        <is>
+          <t>traditional-publishers-still-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="4" t="inlineStr">
+        <is>
+          <t>self-published-authors-can</t>
+        </is>
+      </c>
+      <c r="C311" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D311" s="4" t="inlineStr">
+        <is>
+          <t>Self-published authors can hire the same editors and designers publishers use, so the quality gap comes down to money, not to who owns the imprint.</t>
+        </is>
+      </c>
+      <c r="G311" s="4" t="inlineStr">
+        <is>
+          <t>traditional-publishers-still-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="4" t="inlineStr">
+        <is>
+          <t>most-working-authors-better</t>
+        </is>
+      </c>
+      <c r="C312" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D312" s="4" t="inlineStr">
+        <is>
+          <t>Most working authors are better off self-publishing than signing with a traditional publisher.</t>
+        </is>
+      </c>
+      <c r="F312" s="5" t="inlineStr">
+        <is>
+          <t>publishing</t>
+        </is>
+      </c>
+      <c r="W312" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether keeping most of each sale outweighs losing guaranteed money and access to stores, libraries and reviewers.</t>
+        </is>
+      </c>
+      <c r="AA312" s="5" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AB312" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="4" t="inlineStr">
+        <is>
+          <t>self-published-author-keeps</t>
+        </is>
+      </c>
+      <c r="C313" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D313" s="4" t="inlineStr">
+        <is>
+          <t>A self-published author keeps most of each sale, while a traditional contract hands the publisher the larger share for the life of the book.</t>
+        </is>
+      </c>
+      <c r="G313" s="4" t="inlineStr">
+        <is>
+          <t>most-working-authors-better</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="4" t="inlineStr">
+        <is>
+          <t>authors-who-self-publish</t>
+        </is>
+      </c>
+      <c r="C314" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D314" s="4" t="inlineStr">
+        <is>
+          <t>Authors who self-publish keep control of their rights, pricing and cover, and can fix mistakes or change course without asking permission.</t>
+        </is>
+      </c>
+      <c r="G314" s="4" t="inlineStr">
+        <is>
+          <t>most-working-authors-better</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="4" t="inlineStr">
+        <is>
+          <t>publishers-put-marketing-behind</t>
+        </is>
+      </c>
+      <c r="C315" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D315" s="4" t="inlineStr">
+        <is>
+          <t>Publishers put their marketing behind a few lead titles each season, and most authors on their lists get little more than a listing in a catalog.</t>
+        </is>
+      </c>
+      <c r="G315" s="4" t="inlineStr">
+        <is>
+          <t>most-working-authors-better</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="4" t="inlineStr">
+        <is>
+          <t>self-publishing-turns-writer</t>
+        </is>
+      </c>
+      <c r="C316" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D316" s="4" t="inlineStr">
+        <is>
+          <t>Self-publishing turns a writer into a small business owner who must handle editing, design, marketing and taxes, and most writers are neither good at that nor want to be.</t>
+        </is>
+      </c>
+      <c r="G316" s="4" t="inlineStr">
+        <is>
+          <t>most-working-authors-better</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="4" t="inlineStr">
+        <is>
+          <t>bookstores-libraries-prizes-review</t>
+        </is>
+      </c>
+      <c r="C317" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D317" s="4" t="inlineStr">
+        <is>
+          <t>Bookstores, libraries, prizes and review pages still mostly deal with traditional publishers, so self-published books are shut out of the places where readers browse.</t>
+        </is>
+      </c>
+      <c r="G317" s="4" t="inlineStr">
+        <is>
+          <t>most-working-authors-better</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="4" t="inlineStr">
+        <is>
+          <t>advance-guaranteed-money-field</t>
+        </is>
+      </c>
+      <c r="C318" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D318" s="4" t="inlineStr">
+        <is>
+          <t>An advance is guaranteed money in a field where most books lose money, and a self-published author carries every cost and every risk alone.</t>
+        </is>
+      </c>
+      <c r="G318" s="4" t="inlineStr">
+        <is>
+          <t>most-working-authors-better</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="4" t="inlineStr">
+        <is>
+          <t>governments-generally-require-proven</t>
+        </is>
+      </c>
+      <c r="C319" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D319" s="4" t="inlineStr">
+        <is>
+          <t>Governments should generally require proven childhood vaccines for school attendance.</t>
+        </is>
+      </c>
+      <c r="F319" s="5" t="inlineStr">
+        <is>
+          <t>diseases</t>
+        </is>
+      </c>
+      <c r="W319" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether protecting the classmates who cannot be vaccinated outweighs a parent's right to decide for their own child.</t>
+        </is>
+      </c>
+      <c r="AA319" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB319" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="4" t="inlineStr">
+        <is>
+          <t>some-children-cannot-vaccinated</t>
+        </is>
+      </c>
+      <c r="C320" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D320" s="4" t="inlineStr">
+        <is>
+          <t>Some children cannot be vaccinated for medical reasons, and they are only protected when nearly everyone around them is.</t>
+        </is>
+      </c>
+      <c r="G320" s="4" t="inlineStr">
+        <is>
+          <t>governments-generally-require-proven</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="4" t="inlineStr">
+        <is>
+          <t>schools-gather-many-children</t>
+        </is>
+      </c>
+      <c r="C321" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D321" s="4" t="inlineStr">
+        <is>
+          <t>Schools gather many children in close quarters every day, which is exactly the setting where an outbreak spreads fastest.</t>
+        </is>
+      </c>
+      <c r="G321" s="4" t="inlineStr">
+        <is>
+          <t>governments-generally-require-proven</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="4" t="inlineStr">
+        <is>
+          <t>requirement-tied-school-attendance</t>
+        </is>
+      </c>
+      <c r="C322" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D322" s="4" t="inlineStr">
+        <is>
+          <t>A requirement tied to school attendance reaches almost every family, while a purely voluntary approach leaves gaps that a disease can find.</t>
+        </is>
+      </c>
+      <c r="G322" s="4" t="inlineStr">
+        <is>
+          <t>governments-generally-require-proven</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="4" t="inlineStr">
+        <is>
+          <t>parents-school-administrators-responsible</t>
+        </is>
+      </c>
+      <c r="C323" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D323" s="4" t="inlineStr">
+        <is>
+          <t>Parents, not school administrators, are responsible for a child's body and should make medical decisions for that child.</t>
+        </is>
+      </c>
+      <c r="G323" s="4" t="inlineStr">
+        <is>
+          <t>governments-generally-require-proven</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="4" t="inlineStr">
+        <is>
+          <t>mandates-breed-resentment-distrust</t>
+        </is>
+      </c>
+      <c r="C324" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D324" s="4" t="inlineStr">
+        <is>
+          <t>Mandates breed resentment and distrust of public health, which can lower vaccination rates over time more than persuasion would.</t>
+        </is>
+      </c>
+      <c r="G324" s="4" t="inlineStr">
+        <is>
+          <t>governments-generally-require-proven</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="4" t="inlineStr">
+        <is>
+          <t>most-vaccine-preventable-diseases</t>
+        </is>
+      </c>
+      <c r="C325" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D325" s="4" t="inlineStr">
+        <is>
+          <t>Most vaccine-preventable diseases are already rare, so the added benefit of forcing the last holdouts is small compared with the cost to liberty.</t>
+        </is>
+      </c>
+      <c r="G325" s="4" t="inlineStr">
+        <is>
+          <t>governments-generally-require-proven</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="4" t="inlineStr">
+        <is>
+          <t>routine-cancer-screening-healthy</t>
+        </is>
+      </c>
+      <c r="C326" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D326" s="4" t="inlineStr">
+        <is>
+          <t>Routine cancer screening of healthy adults with no symptoms generally does more harm than good.</t>
+        </is>
+      </c>
+      <c r="F326" s="5" t="inlineStr">
+        <is>
+          <t>diseases</t>
+        </is>
+      </c>
+      <c r="W326" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether the lives saved by catching a few cancers early outweigh the worry, tests, and treatment inflicted on the many who were never going to be hurt by what was found.</t>
+        </is>
+      </c>
+      <c r="AA326" s="5" t="n">
+        <v>-40</v>
+      </c>
+      <c r="AB326" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="4" t="inlineStr">
+        <is>
+          <t>screening-finds-many-slow</t>
+        </is>
+      </c>
+      <c r="C327" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D327" s="4" t="inlineStr">
+        <is>
+          <t>Screening finds many slow-growing abnormalities that would never have caused harm, and treating them exposes healthy people to surgery and drugs they did not need.</t>
+        </is>
+      </c>
+      <c r="G327" s="4" t="inlineStr">
+        <is>
+          <t>routine-cancer-screening-healthy</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="4" t="inlineStr">
+        <is>
+          <t>false-alarm-sets-off</t>
+        </is>
+      </c>
+      <c r="C328" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D328" s="4" t="inlineStr">
+        <is>
+          <t>A false alarm sets off follow-up tests and weeks of fear, and false alarms are common when large numbers of people who feel fine are tested.</t>
+        </is>
+      </c>
+      <c r="G328" s="4" t="inlineStr">
+        <is>
+          <t>routine-cancer-screening-healthy</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="4" t="inlineStr">
+        <is>
+          <t>finding-cancer-earlier-often</t>
+        </is>
+      </c>
+      <c r="C329" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D329" s="4" t="inlineStr">
+        <is>
+          <t>Finding a cancer earlier often just means a person lives longer knowing they have it, without changing when or whether they die from it.</t>
+        </is>
+      </c>
+      <c r="G329" s="4" t="inlineStr">
+        <is>
+          <t>routine-cancer-screening-healthy</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="4" t="inlineStr">
+        <is>
+          <t>many-cancers-far-easier</t>
+        </is>
+      </c>
+      <c r="C330" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D330" s="4" t="inlineStr">
+        <is>
+          <t>Many cancers are far easier to treat before they spread, and screening is the only way to catch them in people who feel fine.</t>
+        </is>
+      </c>
+      <c r="G330" s="4" t="inlineStr">
+        <is>
+          <t>routine-cancer-screening-healthy</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="4" t="inlineStr">
+        <is>
+          <t>patients-can-told-risks</t>
+        </is>
+      </c>
+      <c r="C331" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D331" s="4" t="inlineStr">
+        <is>
+          <t>Patients can be told the risks of overdiagnosis and choose for themselves; the answer to false alarms is better counseling, not fewer tests.</t>
+        </is>
+      </c>
+      <c r="G331" s="4" t="inlineStr">
+        <is>
+          <t>routine-cancer-screening-healthy</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="4" t="inlineStr">
+        <is>
+          <t>harms-screening-mostly-temporary</t>
+        </is>
+      </c>
+      <c r="C332" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D332" s="4" t="inlineStr">
+        <is>
+          <t>The harms of screening are mostly temporary anxiety and minor procedures, while the harm of a missed cancer is death.</t>
+        </is>
+      </c>
+      <c r="G332" s="4" t="inlineStr">
+        <is>
+          <t>routine-cancer-screening-healthy</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="4" t="inlineStr">
+        <is>
+          <t>adults-generally-allowed-buy</t>
+        </is>
+      </c>
+      <c r="C333" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D333" s="4" t="inlineStr">
+        <is>
+          <t>Adults should generally be allowed to buy common prescription drugs from a pharmacist without a doctor's visit.</t>
+        </is>
+      </c>
+      <c r="F333" s="5" t="inlineStr">
+        <is>
+          <t>drugs</t>
+        </is>
+      </c>
+      <c r="W333" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether the doctor's visit before a routine prescription is a safeguard worth its cost or a toll booth.</t>
+        </is>
+      </c>
+      <c r="AA333" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB333" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="4" t="inlineStr">
+        <is>
+          <t>many-prescriptions-refills-medicines</t>
+        </is>
+      </c>
+      <c r="C334" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D334" s="4" t="inlineStr">
+        <is>
+          <t>Many prescriptions are refills of medicines a person has taken for years, and requiring an appointment to renew them adds cost and delay without adding safety.</t>
+        </is>
+      </c>
+      <c r="G334" s="4" t="inlineStr">
+        <is>
+          <t>adults-generally-allowed-buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="4" t="inlineStr">
+        <is>
+          <t>pharmacists-trained-drugs-interactions</t>
+        </is>
+      </c>
+      <c r="C335" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D335" s="4" t="inlineStr">
+        <is>
+          <t>Pharmacists are trained in drugs and their interactions, often more thoroughly than the doctors who prescribe them.</t>
+        </is>
+      </c>
+      <c r="G335" s="4" t="inlineStr">
+        <is>
+          <t>adults-generally-allowed-buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="4" t="inlineStr">
+        <is>
+          <t>people-who-cannot-easily</t>
+        </is>
+      </c>
+      <c r="C336" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D336" s="4" t="inlineStr">
+        <is>
+          <t>People who cannot easily get to a doctor, because of cost, distance, or work hours, often go without medicine they need rather than jump through the hoops.</t>
+        </is>
+      </c>
+      <c r="G336" s="4" t="inlineStr">
+        <is>
+          <t>adults-generally-allowed-buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="4" t="inlineStr">
+        <is>
+          <t>doctor-s-visit-catches</t>
+        </is>
+      </c>
+      <c r="C337" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D337" s="4" t="inlineStr">
+        <is>
+          <t>A doctor's visit catches problems the patient did not come in for; the refill is often the excuse that gets a person examined at all.</t>
+        </is>
+      </c>
+      <c r="G337" s="4" t="inlineStr">
+        <is>
+          <t>adults-generally-allowed-buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="4" t="inlineStr">
+        <is>
+          <t>pharmacists-work-stores-profit</t>
+        </is>
+      </c>
+      <c r="C338" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D338" s="4" t="inlineStr">
+        <is>
+          <t>Pharmacists work for stores that profit from selling drugs, which puts them in a poor position to tell a customer not to buy one.</t>
+        </is>
+      </c>
+      <c r="G338" s="4" t="inlineStr">
+        <is>
+          <t>adults-generally-allowed-buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="4" t="inlineStr">
+        <is>
+          <t>antibiotic-resistance-dependence-some</t>
+        </is>
+      </c>
+      <c r="C339" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D339" s="4" t="inlineStr">
+        <is>
+          <t>Antibiotic resistance and dependence on some medicines grow when access loosens, and those harms fall on everyone, not just the buyer.</t>
+        </is>
+      </c>
+      <c r="G339" s="4" t="inlineStr">
+        <is>
+          <t>adults-generally-allowed-buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="4" t="inlineStr">
+        <is>
+          <t>governments-generally-set-maximum</t>
+        </is>
+      </c>
+      <c r="C340" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D340" s="4" t="inlineStr">
+        <is>
+          <t>Governments should generally set a maximum price for medicines that are still under patent.</t>
+        </is>
+      </c>
+      <c r="F340" s="5" t="inlineStr">
+        <is>
+          <t>drugs</t>
+        </is>
+      </c>
+      <c r="W340" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether the money saved today is worth the medicines that might not be invented tomorrow.</t>
+        </is>
+      </c>
+      <c r="AA340" s="5" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AB340" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="4" t="inlineStr">
+        <is>
+          <t>patent-already-gives-company</t>
+        </is>
+      </c>
+      <c r="C341" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D341" s="4" t="inlineStr">
+        <is>
+          <t>A patent already gives a company a monopoly, and a monopoly seller with sick customers will charge whatever the desperate will pay unless someone stops it.</t>
+        </is>
+      </c>
+      <c r="G341" s="4" t="inlineStr">
+        <is>
+          <t>governments-generally-set-maximum</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="4" t="inlineStr">
+        <is>
+          <t>much-basic-research-behind</t>
+        </is>
+      </c>
+      <c r="C342" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D342" s="4" t="inlineStr">
+        <is>
+          <t>Much of the basic research behind new drugs is paid for by taxpayers, so the public has already bought a share of the result.</t>
+        </is>
+      </c>
+      <c r="G342" s="4" t="inlineStr">
+        <is>
+          <t>governments-generally-set-maximum</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="4" t="inlineStr">
+        <is>
+          <t>patients-who-skip-doses</t>
+        </is>
+      </c>
+      <c r="C343" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D343" s="4" t="inlineStr">
+        <is>
+          <t>Patients who skip doses or split pills because of cost end up sicker and in hospitals, and that bill lands on everyone.</t>
+        </is>
+      </c>
+      <c r="G343" s="4" t="inlineStr">
+        <is>
+          <t>governments-generally-set-maximum</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="4" t="inlineStr">
+        <is>
+          <t>companies-invest-research-because</t>
+        </is>
+      </c>
+      <c r="C344" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D344" s="4" t="inlineStr">
+        <is>
+          <t>Companies invest in research because a successful drug earns a large return; cap the return and the riskiest, most valuable research is the first to be cut.</t>
+        </is>
+      </c>
+      <c r="G344" s="4" t="inlineStr">
+        <is>
+          <t>governments-generally-set-maximum</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="4" t="inlineStr">
+        <is>
+          <t>cap-set-officials-will</t>
+        </is>
+      </c>
+      <c r="C345" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D345" s="4" t="inlineStr">
+        <is>
+          <t>A cap set by officials will be wrong in both directions, too high for cheap-to-make drugs and too low for hard ones, because no committee knows the true cost of discovery.</t>
+        </is>
+      </c>
+      <c r="G345" s="4" t="inlineStr">
+        <is>
+          <t>governments-generally-set-maximum</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="4" t="inlineStr">
+        <is>
+          <t>prices-already-bargained-down</t>
+        </is>
+      </c>
+      <c r="C346" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D346" s="4" t="inlineStr">
+        <is>
+          <t>Prices are already bargained down by insurers and public programs; a legal cap adds a blunt tool where negotiation is already doing the work.</t>
+        </is>
+      </c>
+      <c r="G346" s="4" t="inlineStr">
+        <is>
+          <t>governments-generally-set-maximum</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="4" t="inlineStr">
+        <is>
+          <t>california-generally-override-local</t>
+        </is>
+      </c>
+      <c r="C347" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D347" s="4" t="inlineStr">
+        <is>
+          <t>California should generally override local zoning rules to force far more housing to be built.</t>
+        </is>
+      </c>
+      <c r="F347" s="5" t="inlineStr">
+        <is>
+          <t>u-s-states</t>
+        </is>
+      </c>
+      <c r="W347" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether the housing shortage is caused by local vetoes that only the state can break, or whether state mandates fail to deliver homes on their own.</t>
+        </is>
+      </c>
+      <c r="AA347" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB347" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="4" t="inlineStr">
+        <is>
+          <t>local-governments-have-blocked</t>
+        </is>
+      </c>
+      <c r="C348" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D348" s="4" t="inlineStr">
+        <is>
+          <t>Local governments have blocked new homes for decades because existing residents vote and future residents cannot, and only the state answers to both.</t>
+        </is>
+      </c>
+      <c r="G348" s="4" t="inlineStr">
+        <is>
+          <t>california-generally-override-local</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="4" t="inlineStr">
+        <is>
+          <t>teachers-nurses-service-workers</t>
+        </is>
+      </c>
+      <c r="C349" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D349" s="4" t="inlineStr">
+        <is>
+          <t>Teachers, nurses, and service workers commute for hours because they cannot afford to live near their jobs, and that cost falls on the whole state.</t>
+        </is>
+      </c>
+      <c r="G349" s="4" t="inlineStr">
+        <is>
+          <t>california-generally-override-local</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="4" t="inlineStr">
+        <is>
+          <t>people-businesses-leaving-state</t>
+        </is>
+      </c>
+      <c r="C350" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D350" s="4" t="inlineStr">
+        <is>
+          <t>People and businesses are leaving the state mainly because of housing costs, which shrinks the tax base that pays for everything else.</t>
+        </is>
+      </c>
+      <c r="G350" s="4" t="inlineStr">
+        <is>
+          <t>california-generally-override-local</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="4" t="inlineStr">
+        <is>
+          <t>local-communities-understand-own</t>
+        </is>
+      </c>
+      <c r="C351" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D351" s="4" t="inlineStr">
+        <is>
+          <t>Local communities understand their own roads, schools, water supplies, and fire risks, and homes added without regard to those limits create new problems.</t>
+        </is>
+      </c>
+      <c r="G351" s="4" t="inlineStr">
+        <is>
+          <t>california-generally-override-local</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="4" t="inlineStr">
+        <is>
+          <t>state-mandates-have-mostly</t>
+        </is>
+      </c>
+      <c r="C352" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D352" s="4" t="inlineStr">
+        <is>
+          <t>State mandates have mostly produced lawsuits, paperwork, and resentment rather than finished homes, because building still depends on local approval in practice.</t>
+        </is>
+      </c>
+      <c r="G352" s="4" t="inlineStr">
+        <is>
+          <t>california-generally-override-local</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="4" t="inlineStr">
+        <is>
+          <t>market-rate-construction-alone</t>
+        </is>
+      </c>
+      <c r="C353" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D353" s="4" t="inlineStr">
+        <is>
+          <t>Market-rate construction alone does not produce housing that low-income families can afford, so the state's effort would be better spent on direct subsidy.</t>
+        </is>
+      </c>
+      <c r="G353" s="4" t="inlineStr">
+        <is>
+          <t>california-generally-override-local</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="4" t="inlineStr">
+        <is>
+          <t>texas-connect-its-separate</t>
+        </is>
+      </c>
+      <c r="C354" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D354" s="4" t="inlineStr">
+        <is>
+          <t>Texas should connect its separate electric grid to the national grids rather than keeping it apart.</t>
+        </is>
+      </c>
+      <c r="F354" s="5" t="inlineStr">
+        <is>
+          <t>u-s-states</t>
+        </is>
+      </c>
+      <c r="W354" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether the reliability gained from sharing power across regions is worth giving up state control over how the grid is run.</t>
+        </is>
+      </c>
+      <c r="AA354" s="5" t="n">
+        <v>-65</v>
+      </c>
+      <c r="AB354" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="4" t="inlineStr">
+        <is>
+          <t>when-extreme-weather-hits</t>
+        </is>
+      </c>
+      <c r="C355" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D355" s="4" t="inlineStr">
+        <is>
+          <t>When extreme weather hits, a connected grid can import power from regions that are not suffering the same storm, which is exactly when a closed grid fails.</t>
+        </is>
+      </c>
+      <c r="G355" s="4" t="inlineStr">
+        <is>
+          <t>texas-connect-its-separate</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="4" t="inlineStr">
+        <is>
+          <t>texas-produces-more-wind</t>
+        </is>
+      </c>
+      <c r="C356" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D356" s="4" t="inlineStr">
+        <is>
+          <t>Texas produces more wind and solar power than it can always use, and connection would let it sell that surplus instead of wasting it.</t>
+        </is>
+      </c>
+      <c r="G356" s="4" t="inlineStr">
+        <is>
+          <t>texas-connect-its-separate</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="4" t="inlineStr">
+        <is>
+          <t>investors-more-willing-build</t>
+        </is>
+      </c>
+      <c r="C357" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D357" s="4" t="inlineStr">
+        <is>
+          <t>Investors are more willing to build power plants and transmission lines where they can reach a bigger market.</t>
+        </is>
+      </c>
+      <c r="G357" s="4" t="inlineStr">
+        <is>
+          <t>texas-connect-its-separate</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="4" t="inlineStr">
+        <is>
+          <t>connecting-national-grids-brings</t>
+        </is>
+      </c>
+      <c r="C358" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D358" s="4" t="inlineStr">
+        <is>
+          <t>Connecting to the national grids brings federal oversight of prices and rules, and the state's freedom to run its own market is the reason it has been able to build so much new generation so quickly.</t>
+        </is>
+      </c>
+      <c r="G358" s="4" t="inlineStr">
+        <is>
+          <t>texas-connect-its-separate</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="4" t="inlineStr">
+        <is>
+          <t>lines-needed-connect-grids</t>
+        </is>
+      </c>
+      <c r="C359" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D359" s="4" t="inlineStr">
+        <is>
+          <t>The lines needed to connect the grids would cost an enormous amount and take many years, and the state can harden its own system faster and cheaper.</t>
+        </is>
+      </c>
+      <c r="G359" s="4" t="inlineStr">
+        <is>
+          <t>texas-connect-its-separate</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="4" t="inlineStr">
+        <is>
+          <t>neighboring-regions-have-had</t>
+        </is>
+      </c>
+      <c r="C360" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D360" s="4" t="inlineStr">
+        <is>
+          <t>Neighboring regions have had their own blackouts and shortages, so connection would not guarantee help in a crisis and could import their problems.</t>
+        </is>
+      </c>
+      <c r="G360" s="4" t="inlineStr">
+        <is>
+          <t>texas-connect-its-separate</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="4" t="inlineStr">
+        <is>
+          <t>judging-teachers-partly-students</t>
+        </is>
+      </c>
+      <c r="C361" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D361" s="4" t="inlineStr">
+        <is>
+          <t>Judging teachers partly by their students' test results generally makes schools better.</t>
+        </is>
+      </c>
+      <c r="F361" s="5" t="inlineStr">
+        <is>
+          <t>teaching</t>
+        </is>
+      </c>
+      <c r="W361" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether test results measure what a teacher actually adds or mostly reflect which students walked in the door.</t>
+        </is>
+      </c>
+      <c r="AA361" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB361" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="4" t="inlineStr">
+        <is>
+          <t>without-measure-results-teacher</t>
+        </is>
+      </c>
+      <c r="C362" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D362" s="4" t="inlineStr">
+        <is>
+          <t>Without a measure of results, teacher ratings rest on a principal's impression, and nearly everyone ends up rated the same.</t>
+        </is>
+      </c>
+      <c r="G362" s="4" t="inlineStr">
+        <is>
+          <t>judging-teachers-partly-students</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="4" t="inlineStr">
+        <is>
+          <t>parents-deserve-know-whether</t>
+        </is>
+      </c>
+      <c r="C363" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D363" s="4" t="inlineStr">
+        <is>
+          <t>Parents deserve to know whether their child's teacher is helping students learn, and test growth is the one measure that can be compared across classrooms.</t>
+        </is>
+      </c>
+      <c r="G363" s="4" t="inlineStr">
+        <is>
+          <t>judging-teachers-partly-students</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="4" t="inlineStr">
+        <is>
+          <t>teachers-who-consistently-help</t>
+        </is>
+      </c>
+      <c r="C364" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D364" s="4" t="inlineStr">
+        <is>
+          <t>Teachers who consistently help students grow deserve recognition and pay that a system without measurement cannot give them.</t>
+        </is>
+      </c>
+      <c r="G364" s="4" t="inlineStr">
+        <is>
+          <t>judging-teachers-partly-students</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="4" t="inlineStr">
+        <is>
+          <t>students-arrive-wildly-different</t>
+        </is>
+      </c>
+      <c r="C365" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D365" s="4" t="inlineStr">
+        <is>
+          <t>Students arrive with wildly different home lives and prior learning, and a single year's scores cannot cleanly separate the teacher's effect from everything else.</t>
+        </is>
+      </c>
+      <c r="G365" s="4" t="inlineStr">
+        <is>
+          <t>judging-teachers-partly-students</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="4" t="inlineStr">
+        <is>
+          <t>when-jobs-depend-scores</t>
+        </is>
+      </c>
+      <c r="C366" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D366" s="4" t="inlineStr">
+        <is>
+          <t>When jobs depend on scores, teaching narrows to what is tested, and subjects, projects and habits that are not tested get pushed aside.</t>
+        </is>
+      </c>
+      <c r="G366" s="4" t="inlineStr">
+        <is>
+          <t>judging-teachers-partly-students</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="4" t="inlineStr">
+        <is>
+          <t>strong-teachers-avoid-hardest</t>
+        </is>
+      </c>
+      <c r="C367" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D367" s="4" t="inlineStr">
+        <is>
+          <t>Strong teachers avoid the hardest schools and classes when a low score can cost them their job, which hurts exactly the students who need them most.</t>
+        </is>
+      </c>
+      <c r="G367" s="4" t="inlineStr">
+        <is>
+          <t>judging-teachers-partly-students</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="4" t="inlineStr">
+        <is>
+          <t>teachers-generally-do-best</t>
+        </is>
+      </c>
+      <c r="C368" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D368" s="4" t="inlineStr">
+        <is>
+          <t>Teachers generally do their best work when they control what and how they teach rather than following a set script.</t>
+        </is>
+      </c>
+      <c r="F368" s="5" t="inlineStr">
+        <is>
+          <t>teaching</t>
+        </is>
+      </c>
+      <c r="W368" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether the average classroom is better served by an expert's plan applied faithfully or by a teacher's on-the-spot judgment about the children in front of them.</t>
+        </is>
+      </c>
+      <c r="AA368" s="5" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AB368" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="4" t="inlineStr">
+        <is>
+          <t>teacher-sees-each-child</t>
+        </is>
+      </c>
+      <c r="C369" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D369" s="4" t="inlineStr">
+        <is>
+          <t>A teacher sees each child's confusion in real time and can change course, while a script written far away cannot.</t>
+        </is>
+      </c>
+      <c r="G369" s="4" t="inlineStr">
+        <is>
+          <t>teachers-generally-do-best</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="4" t="inlineStr">
+        <is>
+          <t>professionals-who-trusted-stay</t>
+        </is>
+      </c>
+      <c r="C370" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D370" s="4" t="inlineStr">
+        <is>
+          <t>Professionals who are trusted stay in the job longer, and turnover harms students more than any curriculum choice.</t>
+        </is>
+      </c>
+      <c r="G370" s="4" t="inlineStr">
+        <is>
+          <t>teachers-generally-do-best</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="4" t="inlineStr">
+        <is>
+          <t>lessons-teacher-believes-taught</t>
+        </is>
+      </c>
+      <c r="C371" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D371" s="4" t="inlineStr">
+        <is>
+          <t>Lessons a teacher believes in are taught with an energy that students notice, and scripted lessons rarely earn that belief.</t>
+        </is>
+      </c>
+      <c r="G371" s="4" t="inlineStr">
+        <is>
+          <t>teachers-generally-do-best</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="4" t="inlineStr">
+        <is>
+          <t>most-teachers-were-never</t>
+        </is>
+      </c>
+      <c r="C372" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D372" s="4" t="inlineStr">
+        <is>
+          <t>Most teachers were never trained to design a curriculum, and asking each one to build their own means many students get an untested plan.</t>
+        </is>
+      </c>
+      <c r="G372" s="4" t="inlineStr">
+        <is>
+          <t>teachers-generally-do-best</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="4" t="inlineStr">
+        <is>
+          <t>well-designed-materials-carry</t>
+        </is>
+      </c>
+      <c r="C373" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D373" s="4" t="inlineStr">
+        <is>
+          <t>Well-designed materials carry the judgment of many experts, and a teacher who follows them gives students a better lesson than most could write alone.</t>
+        </is>
+      </c>
+      <c r="G373" s="4" t="inlineStr">
+        <is>
+          <t>teachers-generally-do-best</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="4" t="inlineStr">
+        <is>
+          <t>children-who-move-between</t>
+        </is>
+      </c>
+      <c r="C374" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D374" s="4" t="inlineStr">
+        <is>
+          <t>Children who move between classrooms and schools need continuity, and full teacher control means what a child learns depends on luck.</t>
+        </is>
+      </c>
+      <c r="G374" s="4" t="inlineStr">
+        <is>
+          <t>teachers-generally-do-best</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="4" t="inlineStr">
+        <is>
+          <t>statues-honoring-historical-figures</t>
+        </is>
+      </c>
+      <c r="C375" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D375" s="4" t="inlineStr">
+        <is>
+          <t>Statues honoring historical figures who did serious wrongs should generally be removed from public squares.</t>
+        </is>
+      </c>
+      <c r="F375" s="5" t="inlineStr">
+        <is>
+          <t>history</t>
+        </is>
+      </c>
+      <c r="W375" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether a public statue is an honor that the living may withdraw or a record that the living have a duty to keep.</t>
+        </is>
+      </c>
+      <c r="AA375" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB375" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="4" t="inlineStr">
+        <is>
+          <t>statue-public-square-honor</t>
+        </is>
+      </c>
+      <c r="C376" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D376" s="4" t="inlineStr">
+        <is>
+          <t>A statue in a public square is an honor paid by the community, not a history lesson, and a community is entitled to stop honoring someone whose deeds it now finds shameful.</t>
+        </is>
+      </c>
+      <c r="G376" s="4" t="inlineStr">
+        <is>
+          <t>statues-honoring-historical-figures</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="4" t="inlineStr">
+        <is>
+          <t>public-spaces-belong-people</t>
+        </is>
+      </c>
+      <c r="C377" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D377" s="4" t="inlineStr">
+        <is>
+          <t>Public spaces belong to the people who use them now, and asking them to walk past a tribute to someone who harmed their ancestors is a daily insult they never agreed to.</t>
+        </is>
+      </c>
+      <c r="G377" s="4" t="inlineStr">
+        <is>
+          <t>statues-honoring-historical-figures</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="4" t="inlineStr">
+        <is>
+          <t>moving-statue-museum-explanation</t>
+        </is>
+      </c>
+      <c r="C378" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D378" s="4" t="inlineStr">
+        <is>
+          <t>Moving a statue to a museum with an explanation preserves the history better than leaving it on a pedestal with no context at all.</t>
+        </is>
+      </c>
+      <c r="G378" s="4" t="inlineStr">
+        <is>
+          <t>statues-honoring-historical-figures</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="4" t="inlineStr">
+        <is>
+          <t>removing-monuments-makes-uncomfortable</t>
+        </is>
+      </c>
+      <c r="C379" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D379" s="4" t="inlineStr">
+        <is>
+          <t>Removing monuments makes the uncomfortable parts of the past easier to forget, and a society that cannot see its old heroes clearly cannot learn from its old mistakes.</t>
+        </is>
+      </c>
+      <c r="G379" s="4" t="inlineStr">
+        <is>
+          <t>statues-honoring-historical-figures</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="4" t="inlineStr">
+        <is>
+          <t>nearly-everyone-honored-past</t>
+        </is>
+      </c>
+      <c r="C380" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D380" s="4" t="inlineStr">
+        <is>
+          <t>Nearly everyone honored in the past fails some test of the present, so a rule of removal has no natural stopping point and ends up emptying the squares.</t>
+        </is>
+      </c>
+      <c r="G380" s="4" t="inlineStr">
+        <is>
+          <t>statues-honoring-historical-figures</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="4" t="inlineStr">
+        <is>
+          <t>decisions-about-which-statues</t>
+        </is>
+      </c>
+      <c r="C381" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D381" s="4" t="inlineStr">
+        <is>
+          <t>Decisions about which statues fall become contests of political power rather than judgments about history, and each side then tears down what the other side put up.</t>
+        </is>
+      </c>
+      <c r="G381" s="4" t="inlineStr">
+        <is>
+          <t>statues-honoring-historical-figures</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="4" t="inlineStr">
+        <is>
+          <t>historians-generally-judge-people</t>
+        </is>
+      </c>
+      <c r="C382" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D382" s="4" t="inlineStr">
+        <is>
+          <t>Historians generally should not judge people of the past by today's moral standards.</t>
+        </is>
+      </c>
+      <c r="F382" s="5" t="inlineStr">
+        <is>
+          <t>history</t>
+        </is>
+      </c>
+      <c r="W382" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether understanding a past era requires setting aside our moral views or whether refusing to judge is itself a moral choice.</t>
+        </is>
+      </c>
+      <c r="AA382" s="5" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AB382" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="4" t="inlineStr">
+        <is>
+          <t>people-past-could-know</t>
+        </is>
+      </c>
+      <c r="C383" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D383" s="4" t="inlineStr">
+        <is>
+          <t>People in the past could not know what later generations would learn, and blaming them for not seeing it is like blaming a doctor of an earlier century for not using medicine that had not been invented.</t>
+        </is>
+      </c>
+      <c r="G383" s="4" t="inlineStr">
+        <is>
+          <t>historians-generally-judge-people</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="4" t="inlineStr">
+        <is>
+          <t>historian-s-job-explain</t>
+        </is>
+      </c>
+      <c r="C384" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D384" s="4" t="inlineStr">
+        <is>
+          <t>The historian's job is to explain why people acted as they did, and moral condemnation tends to replace that explanation with a verdict that teaches nothing.</t>
+        </is>
+      </c>
+      <c r="G384" s="4" t="inlineStr">
+        <is>
+          <t>historians-generally-judge-people</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="4" t="inlineStr">
+        <is>
+          <t>our-own-standards-will</t>
+        </is>
+      </c>
+      <c r="C385" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D385" s="4" t="inlineStr">
+        <is>
+          <t>Our own standards will look wrong to our descendants in ways we cannot predict, so the humility we would want from them is the humility we owe the past.</t>
+        </is>
+      </c>
+      <c r="G385" s="4" t="inlineStr">
+        <is>
+          <t>historians-generally-judge-people</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="4" t="inlineStr">
+        <is>
+          <t>nearly-every-era-there</t>
+        </is>
+      </c>
+      <c r="C386" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D386" s="4" t="inlineStr">
+        <is>
+          <t>In nearly every era there were people who objected to the cruelties of their time, which shows the alternatives were visible and the choice to ignore them was a real choice.</t>
+        </is>
+      </c>
+      <c r="G386" s="4" t="inlineStr">
+        <is>
+          <t>historians-generally-judge-people</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="4" t="inlineStr">
+        <is>
+          <t>declining-judge-neutral-because</t>
+        </is>
+      </c>
+      <c r="C387" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D387" s="4" t="inlineStr">
+        <is>
+          <t>Declining to judge is not neutral, because a history told without moral weight quietly tells readers that the suffering of the victims did not much matter.</t>
+        </is>
+      </c>
+      <c r="G387" s="4" t="inlineStr">
+        <is>
+          <t>historians-generally-judge-people</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="4" t="inlineStr">
+        <is>
+          <t>history-written-living-readers</t>
+        </is>
+      </c>
+      <c r="C388" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D388" s="4" t="inlineStr">
+        <is>
+          <t>History is written for the living, and readers need to know not only what happened but whether it was right, or the past cannot guide anything they do next.</t>
+        </is>
+      </c>
+      <c r="G388" s="4" t="inlineStr">
+        <is>
+          <t>historians-generally-judge-people</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="4" t="inlineStr">
+        <is>
+          <t>fish-clearly-feel-pain</t>
+        </is>
+      </c>
+      <c r="C389" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D389" s="4" t="inlineStr">
+        <is>
+          <t>Fish clearly feel pain in a way that matters, not just a reflex to avoid harm.</t>
+        </is>
+      </c>
+      <c r="F389" s="5" t="inlineStr">
+        <is>
+          <t>animals</t>
+        </is>
+      </c>
+      <c r="W389" s="4" t="inlineStr">
+        <is>
+          <t>It comes down to whether behaving as if hurt is enough to conclude that something is felt, or whether a mammal-like brain is required.</t>
+        </is>
+      </c>
+      <c r="AA389" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB389" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="4" t="inlineStr">
+        <is>
+          <t>fish-have-nerve-structures</t>
+        </is>
+      </c>
+      <c r="C390" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D390" s="4" t="inlineStr">
+        <is>
+          <t>Fish have the nerve structures and chemical messengers that carry pain signals in mammals, so the machinery for feeling pain is present.</t>
+        </is>
+      </c>
+      <c r="G390" s="4" t="inlineStr">
+        <is>
+          <t>fish-clearly-feel-pain</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="4" t="inlineStr">
+        <is>
+          <t>fish-change-behavior-long</t>
+        </is>
+      </c>
+      <c r="C391" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D391" s="4" t="inlineStr">
+        <is>
+          <t>Fish change their behavior for a long time after an injury, including avoiding places where they were hurt, which a simple reflex would not produce.</t>
+        </is>
+      </c>
+      <c r="G391" s="4" t="inlineStr">
+        <is>
+          <t>fish-clearly-feel-pain</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="4" t="inlineStr">
+        <is>
+          <t>pain-relief-drugs-return</t>
+        </is>
+      </c>
+      <c r="C392" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D392" s="4" t="inlineStr">
+        <is>
+          <t>Pain relief drugs return injured fish to normal behavior, which is what you would expect if the injury was being felt rather than just detected.</t>
+        </is>
+      </c>
+      <c r="G392" s="4" t="inlineStr">
+        <is>
+          <t>fish-clearly-feel-pain</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="4" t="inlineStr">
+        <is>
+          <t>fish-lack-outer-brain</t>
+        </is>
+      </c>
+      <c r="C393" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D393" s="4" t="inlineStr">
+        <is>
+          <t>Fish lack the outer brain layer that in mammals turns damage signals into conscious suffering, so the signals may never become an experience.</t>
+        </is>
+      </c>
+      <c r="G393" s="4" t="inlineStr">
+        <is>
+          <t>fish-clearly-feel-pain</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="4" t="inlineStr">
+        <is>
+          <t>avoiding-place-where-you</t>
+        </is>
+      </c>
+      <c r="C394" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D394" s="4" t="inlineStr">
+        <is>
+          <t>Avoiding a place where you were hurt can be learned without any feeling, as simple machines and insects already show.</t>
+        </is>
+      </c>
+      <c r="G394" s="4" t="inlineStr">
+        <is>
+          <t>fish-clearly-feel-pain</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="4" t="inlineStr">
+        <is>
+          <t>judging-animal-s-inner</t>
+        </is>
+      </c>
+      <c r="C395" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D395" s="4" t="inlineStr">
+        <is>
+          <t>Judging an animal's inner life from behavior that looks like ours projects human experience onto a creature built very differently.</t>
+        </is>
+      </c>
+      <c r="G395" s="4" t="inlineStr">
+        <is>
+          <t>fish-clearly-feel-pain</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="4" t="inlineStr">
+        <is>
+          <t>claims-apes-parrots-understand</t>
+        </is>
+      </c>
+      <c r="C396" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D396" s="4" t="inlineStr">
+        <is>
+          <t>Claims that apes and parrots understand language generally reflect human wishful thinking rather than real ability.</t>
+        </is>
+      </c>
+      <c r="F396" s="5" t="inlineStr">
+        <is>
+          <t>animals</t>
+        </is>
+      </c>
+      <c r="W396" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement is about where understanding begins: at using a sign for something absent, or only at building new sentences.</t>
+        </is>
+      </c>
+      <c r="AA396" s="5" t="n">
+        <v>-50</v>
+      </c>
+      <c r="AB396" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="4" t="inlineStr">
+        <is>
+          <t>trained-animals-mostly-produce</t>
+        </is>
+      </c>
+      <c r="C397" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D397" s="4" t="inlineStr">
+        <is>
+          <t>Trained animals mostly produce signs or words when a reward follows, which is what you would expect from learned tricks rather than from meaning.</t>
+        </is>
+      </c>
+      <c r="G397" s="4" t="inlineStr">
+        <is>
+          <t>claims-apes-parrots-understand</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="4" t="inlineStr">
+        <is>
+          <t>people-reporting-animal-s</t>
+        </is>
+      </c>
+      <c r="C398" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D398" s="4" t="inlineStr">
+        <is>
+          <t>The people reporting an animal's language use are usually the ones who raised and love it, and they read intention into ambiguous signs.</t>
+        </is>
+      </c>
+      <c r="G398" s="4" t="inlineStr">
+        <is>
+          <t>claims-apes-parrots-understand</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="4" t="inlineStr">
+        <is>
+          <t>no-animal-has-been</t>
+        </is>
+      </c>
+      <c r="C399" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D399" s="4" t="inlineStr">
+        <is>
+          <t>No animal has been shown to combine signs into new sentences with grammar, which is the part of language that separates it from a vocabulary of signals.</t>
+        </is>
+      </c>
+      <c r="G399" s="4" t="inlineStr">
+        <is>
+          <t>claims-apes-parrots-understand</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="4" t="inlineStr">
+        <is>
+          <t>some-animals-use-learned</t>
+        </is>
+      </c>
+      <c r="C400" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D400" s="4" t="inlineStr">
+        <is>
+          <t>Some animals use learned signs to ask for things that are not present, which shows the sign stands for an idea and not just a trained response.</t>
+        </is>
+      </c>
+      <c r="G400" s="4" t="inlineStr">
+        <is>
+          <t>claims-apes-parrots-understand</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="4" t="inlineStr">
+        <is>
+          <t>wild-animals-already-use</t>
+        </is>
+      </c>
+      <c r="C401" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D401" s="4" t="inlineStr">
+        <is>
+          <t>Wild animals already use different calls for different dangers and answer accordingly, so a foundation for meaningful communication exists without any human trainer.</t>
+        </is>
+      </c>
+      <c r="G401" s="4" t="inlineStr">
+        <is>
+          <t>claims-apes-parrots-understand</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="4" t="inlineStr">
+        <is>
+          <t>demanding-full-human-grammar</t>
+        </is>
+      </c>
+      <c r="C402" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D402" s="4" t="inlineStr">
+        <is>
+          <t>Demanding full human grammar before counting anything as understanding sets a bar designed so that only humans can clear it.</t>
+        </is>
+      </c>
+      <c r="G402" s="4" t="inlineStr">
+        <is>
+          <t>claims-apes-parrots-understand</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC262"/>
+  <autoFilter ref="A1:AC402"/>
   <dataValidations count="5">
     <dataValidation sqref="C2:C5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"belief,claim,linkage,importance,interest,uniqueness,equivalence,driver,media"</formula1>
@@ -10657,7 +13997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T898"/>
+  <dimension ref="A1:T1058"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -31910,8 +35250,3768 @@
         </is>
       </c>
     </row>
+    <row r="899">
+      <c r="A899" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B899" s="5" t="inlineStr">
+        <is>
+          <t>direction</t>
+        </is>
+      </c>
+      <c r="E899" s="4" t="inlineStr">
+        <is>
+          <t>Taking public office should cost an official and their family none of the ordinary rights of citizens: they should be free to own and trade what any private citizen may own, to work in any role they are qualified for, and to keep their finances private, with the law punishing proven corruption rather than lawful activity.</t>
+        </is>
+      </c>
+      <c r="O899" s="4" t="inlineStr">
+        <is>
+          <t>-100</t>
+        </is>
+      </c>
+      <c r="T899" s="4" t="inlineStr">
+        <is>
+          <t>argument: Public office is a job, not a surrender of citizenship, so a rule that takes away property or privacy because of the job reaches the honest official and the family who never ran, while sophisticated wealth moves into entities the rule never touches and Congress declines to enforce it on itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B900" s="5" t="inlineStr">
+        <is>
+          <t>strength</t>
+        </is>
+      </c>
+      <c r="C900" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="E900" s="4" t="inlineStr">
+        <is>
+          <t>In certain cases, a rule that limits what officeholders and their families may own or earn from their position tends to reduce the use of public office for private gain.</t>
+        </is>
+      </c>
+      <c r="O900" s="4" t="inlineStr">
+        <is>
+          <t>Modest</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B901" s="5" t="inlineStr">
+        <is>
+          <t>strength</t>
+        </is>
+      </c>
+      <c r="C901" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="E901" s="4" t="inlineStr">
+        <is>
+          <t>An officeholder should never be permitted to hold a personal financial stake in a decision the office controls, whoever the officeholder is and whatever form the stake takes.</t>
+        </is>
+      </c>
+      <c r="O901" s="4" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B902" s="5" t="inlineStr">
+        <is>
+          <t>strength</t>
+        </is>
+      </c>
+      <c r="C902" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="E902" s="4" t="inlineStr">
+        <is>
+          <t>Rules restricting what an officeholder or a relative may lawfully own or earn fundamentally punish lawful activity because of a job, and across the board they reach families who never ran for office while sophisticated wealth routes around them.</t>
+        </is>
+      </c>
+      <c r="O902" s="4" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B903" s="5" t="inlineStr">
+        <is>
+          <t>strength</t>
+        </is>
+      </c>
+      <c r="C903" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="E903" s="4" t="inlineStr">
+        <is>
+          <t>Congress will never enforce a financial rule on its own members, so a new restriction on officeholders' private gain always ends as a symbol in place of the enforcement that could work.</t>
+        </is>
+      </c>
+      <c r="O903" s="4" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B904" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C904" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D904" s="4" t="inlineStr">
+        <is>
+          <t>public-office-usable-private</t>
+        </is>
+      </c>
+      <c r="O904" s="4" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B905" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C905" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D905" s="4" t="inlineStr">
+        <is>
+          <t>citizens-keep-ordinary-rights</t>
+        </is>
+      </c>
+      <c r="O905" s="4" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B906" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C906" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D906" s="4" t="inlineStr">
+        <is>
+          <t>barring-members-congress-president</t>
+        </is>
+      </c>
+      <c r="O906" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T906" s="4" t="inlineStr">
+        <is>
+          <t>branch: Holdings and trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B907" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C907" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="E907" s="4" t="inlineStr">
+        <is>
+          <t>Officials should be free to hold and trade any asset a private citizen may hold, with disclosure and insider trading law as the only check.</t>
+        </is>
+      </c>
+      <c r="O907" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T907" s="4" t="inlineStr">
+        <is>
+          <t>branch: Holdings and trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B908" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C908" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D908" s="4" t="inlineStr">
+        <is>
+          <t>barring-president-members-congress</t>
+        </is>
+      </c>
+      <c r="O908" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T908" s="4" t="inlineStr">
+        <is>
+          <t>branch: Family appointments</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B909" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C909" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="E909" s="4" t="inlineStr">
+        <is>
+          <t>A president should be free to choose any adviser, including a relative, without congressional permission.</t>
+        </is>
+      </c>
+      <c r="O909" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T909" s="4" t="inlineStr">
+        <is>
+          <t>branch: Family appointments</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B910" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C910" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D910" s="4" t="inlineStr">
+        <is>
+          <t>requiring-president-members-congress</t>
+        </is>
+      </c>
+      <c r="O910" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T910" s="4" t="inlineStr">
+        <is>
+          <t>branch: Published tax returns</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B911" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C911" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="E911" s="4" t="inlineStr">
+        <is>
+          <t>Officeholders should not be required to publish their tax returns, because the public financial disclosure form already screens for conflicts and a return exposes families who never ran.</t>
+        </is>
+      </c>
+      <c r="O911" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T911" s="4" t="inlineStr">
+        <is>
+          <t>branch: Published tax returns</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B912" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C912" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D912" s="4" t="inlineStr">
+        <is>
+          <t>letting-congress-overturn-presidential</t>
+        </is>
+      </c>
+      <c r="O912" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T912" s="4" t="inlineStr">
+        <is>
+          <t>branch: Reversing pardons</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B913" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C913" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="E913" s="4" t="inlineStr">
+        <is>
+          <t>The pardon power should remain final and beyond congressional review, with prosecution of pardon bribery and publication of the review file as the check on its abuse.</t>
+        </is>
+      </c>
+      <c r="O913" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T913" s="4" t="inlineStr">
+        <is>
+          <t>branch: Reversing pardons</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B914" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C914" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D914" s="4" t="inlineStr">
+        <is>
+          <t>members-regularly-trade-industries</t>
+        </is>
+      </c>
+      <c r="O914" s="4" t="inlineStr">
+        <is>
+          <t>A.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B915" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C915" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D915" s="4" t="inlineStr">
+        <is>
+          <t>holdings-ban-removes-conflict</t>
+        </is>
+      </c>
+      <c r="O915" s="4" t="inlineStr">
+        <is>
+          <t>A.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B916" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C916" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D916" s="4" t="inlineStr">
+        <is>
+          <t>ban-official-leaves-conflict</t>
+        </is>
+      </c>
+      <c r="O916" s="4" t="inlineStr">
+        <is>
+          <t>A.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B917" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C917" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D917" s="4" t="inlineStr">
+        <is>
+          <t>disclosure-has-failed-check</t>
+        </is>
+      </c>
+      <c r="O917" s="4" t="inlineStr">
+        <is>
+          <t>A.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B918" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C918" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D918" s="4" t="inlineStr">
+        <is>
+          <t>congress-will-enforce-ban</t>
+        </is>
+      </c>
+      <c r="O918" s="4" t="inlineStr">
+        <is>
+          <t>A.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B919" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C919" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D919" s="4" t="inlineStr">
+        <is>
+          <t>federal-reserve-barred-its</t>
+        </is>
+      </c>
+      <c r="O919" s="4" t="inlineStr">
+        <is>
+          <t>A.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B920" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C920" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D920" s="4" t="inlineStr">
+        <is>
+          <t>forced-divestiture-imposes-real</t>
+        </is>
+      </c>
+      <c r="O920" s="4" t="inlineStr">
+        <is>
+          <t>A.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B921" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C921" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D921" s="4" t="inlineStr">
+        <is>
+          <t>trading-closed-briefing-almost</t>
+        </is>
+      </c>
+      <c r="O921" s="4" t="inlineStr">
+        <is>
+          <t>A.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B922" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C922" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D922" s="4" t="inlineStr">
+        <is>
+          <t>members-keep-property-rights</t>
+        </is>
+      </c>
+      <c r="O922" s="4" t="inlineStr">
+        <is>
+          <t>A.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B923" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C923" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D923" s="4" t="inlineStr">
+        <is>
+          <t>anti-nepotism-statute-stops</t>
+        </is>
+      </c>
+      <c r="O923" s="4" t="inlineStr">
+        <is>
+          <t>B.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B924" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C924" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D924" s="4" t="inlineStr">
+        <is>
+          <t>president-entitled-advisers-he</t>
+        </is>
+      </c>
+      <c r="O924" s="4" t="inlineStr">
+        <is>
+          <t>B.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B925" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C925" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D925" s="4" t="inlineStr">
+        <is>
+          <t>relative-cannot-supervised-disciplined</t>
+        </is>
+      </c>
+      <c r="O925" s="4" t="inlineStr">
+        <is>
+          <t>B.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B926" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C926" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D926" s="4" t="inlineStr">
+        <is>
+          <t>formal-appointment-what-brings</t>
+        </is>
+      </c>
+      <c r="O926" s="4" t="inlineStr">
+        <is>
+          <t>B.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B927" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C927" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D927" s="4" t="inlineStr">
+        <is>
+          <t>official-role-gives-family</t>
+        </is>
+      </c>
+      <c r="O927" s="4" t="inlineStr">
+        <is>
+          <t>B.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B928" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C928" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D928" s="4" t="inlineStr">
+        <is>
+          <t>problem-people-actually-point</t>
+        </is>
+      </c>
+      <c r="O928" s="4" t="inlineStr">
+        <is>
+          <t>B.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B929" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C929" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D929" s="4" t="inlineStr">
+        <is>
+          <t>rule-already-applies-every</t>
+        </is>
+      </c>
+      <c r="O929" s="4" t="inlineStr">
+        <is>
+          <t>B.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B930" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C930" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D930" s="4" t="inlineStr">
+        <is>
+          <t>competence-neither-inherited-nor</t>
+        </is>
+      </c>
+      <c r="O930" s="4" t="inlineStr">
+        <is>
+          <t>B.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B931" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C931" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D931" s="4" t="inlineStr">
+        <is>
+          <t>return-shows-what-financial</t>
+        </is>
+      </c>
+      <c r="O931" s="4" t="inlineStr">
+        <is>
+          <t>C.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B932" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C932" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D932" s="4" t="inlineStr">
+        <is>
+          <t>return-shows-tax-positions</t>
+        </is>
+      </c>
+      <c r="O932" s="4" t="inlineStr">
+        <is>
+          <t>C.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B933" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C933" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D933" s="4" t="inlineStr">
+        <is>
+          <t>internal-check-failed-one</t>
+        </is>
+      </c>
+      <c r="O933" s="4" t="inlineStr">
+        <is>
+          <t>C.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B934" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C934" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D934" s="4" t="inlineStr">
+        <is>
+          <t>every-president-carter-through</t>
+        </is>
+      </c>
+      <c r="O934" s="4" t="inlineStr">
+        <is>
+          <t>C.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B935" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C935" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D935" s="4" t="inlineStr">
+        <is>
+          <t>route-constitutionally-narrow-disclosure</t>
+        </is>
+      </c>
+      <c r="O935" s="4" t="inlineStr">
+        <is>
+          <t>C.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B936" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C936" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D936" s="4" t="inlineStr">
+        <is>
+          <t>published-return-can-checked</t>
+        </is>
+      </c>
+      <c r="O936" s="4" t="inlineStr">
+        <is>
+          <t>C.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B937" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C937" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D937" s="4" t="inlineStr">
+        <is>
+          <t>sophisticated-wealth-sits-pass</t>
+        </is>
+      </c>
+      <c r="O937" s="4" t="inlineStr">
+        <is>
+          <t>C.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B938" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C938" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D938" s="4" t="inlineStr">
+        <is>
+          <t>publication-exposes-spouses-children</t>
+        </is>
+      </c>
+      <c r="O938" s="4" t="inlineStr">
+        <is>
+          <t>C.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="4" t="inlineStr">
+        <is>
+          <t>large-companies-required-law</t>
+        </is>
+      </c>
+      <c r="B939" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C939" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D939" s="4" t="inlineStr">
+        <is>
+          <t>workers-bear-costs-bad</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="4" t="inlineStr">
+        <is>
+          <t>large-companies-required-law</t>
+        </is>
+      </c>
+      <c r="B940" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C940" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D940" s="4" t="inlineStr">
+        <is>
+          <t>workers-know-how-company</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="4" t="inlineStr">
+        <is>
+          <t>large-companies-required-law</t>
+        </is>
+      </c>
+      <c r="B941" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C941" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D941" s="4" t="inlineStr">
+        <is>
+          <t>board-answers-only-shareholders</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="4" t="inlineStr">
+        <is>
+          <t>large-companies-required-law</t>
+        </is>
+      </c>
+      <c r="B942" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C942" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D942" s="4" t="inlineStr">
+        <is>
+          <t>owners-put-money-risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="4" t="inlineStr">
+        <is>
+          <t>large-companies-required-law</t>
+        </is>
+      </c>
+      <c r="B943" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C943" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D943" s="4" t="inlineStr">
+        <is>
+          <t>worker-directors-face-conflict</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="4" t="inlineStr">
+        <is>
+          <t>large-companies-required-law</t>
+        </is>
+      </c>
+      <c r="B944" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C944" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D944" s="4" t="inlineStr">
+        <is>
+          <t>boards-two-sets-loyalties</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="4" t="inlineStr">
+        <is>
+          <t>company-generally-serves-public</t>
+        </is>
+      </c>
+      <c r="B945" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C945" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D945" s="4" t="inlineStr">
+        <is>
+          <t>profit-signal-company-making</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="4" t="inlineStr">
+        <is>
+          <t>company-generally-serves-public</t>
+        </is>
+      </c>
+      <c r="B946" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C946" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D946" s="4" t="inlineStr">
+        <is>
+          <t>managers-who-told-serve</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" s="4" t="inlineStr">
+        <is>
+          <t>company-generally-serves-public</t>
+        </is>
+      </c>
+      <c r="B947" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C947" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D947" s="4" t="inlineStr">
+        <is>
+          <t>broad-social-problems-job</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="4" t="inlineStr">
+        <is>
+          <t>company-generally-serves-public</t>
+        </is>
+      </c>
+      <c r="B948" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C948" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D948" s="4" t="inlineStr">
+        <is>
+          <t>many-company-s-costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="4" t="inlineStr">
+        <is>
+          <t>company-generally-serves-public</t>
+        </is>
+      </c>
+      <c r="B949" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C949" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D949" s="4" t="inlineStr">
+        <is>
+          <t>law-always-lags-behind</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="4" t="inlineStr">
+        <is>
+          <t>company-generally-serves-public</t>
+        </is>
+      </c>
+      <c r="B950" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C950" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D950" s="4" t="inlineStr">
+        <is>
+          <t>companies-treat-workers-suppliers</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="4" t="inlineStr">
+        <is>
+          <t>streaming-services-generally-pay</t>
+        </is>
+      </c>
+      <c r="B951" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C951" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D951" s="4" t="inlineStr">
+        <is>
+          <t>single-play-earns-almost</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="4" t="inlineStr">
+        <is>
+          <t>streaming-services-generally-pay</t>
+        </is>
+      </c>
+      <c r="B952" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C952" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D952" s="4" t="inlineStr">
+        <is>
+          <t>money-split-so-most</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="4" t="inlineStr">
+        <is>
+          <t>streaming-services-generally-pay</t>
+        </is>
+      </c>
+      <c r="B953" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C953" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D953" s="4" t="inlineStr">
+        <is>
+          <t>musicians-now-depend-touring</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="4" t="inlineStr">
+        <is>
+          <t>streaming-services-generally-pay</t>
+        </is>
+      </c>
+      <c r="B954" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C954" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D954" s="4" t="inlineStr">
+        <is>
+          <t>streaming-brought-paying-listeners</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="4" t="inlineStr">
+        <is>
+          <t>streaming-services-generally-pay</t>
+        </is>
+      </c>
+      <c r="B955" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C955" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D955" s="4" t="inlineStr">
+        <is>
+          <t>before-streaming-most-musicians</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="4" t="inlineStr">
+        <is>
+          <t>streaming-services-generally-pay</t>
+        </is>
+      </c>
+      <c r="B956" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C956" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D956" s="4" t="inlineStr">
+        <is>
+          <t>low-per-play-rates</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="4" t="inlineStr">
+        <is>
+          <t>streaming-has-clearly-done</t>
+        </is>
+      </c>
+      <c r="B957" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C957" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D957" s="4" t="inlineStr">
+        <is>
+          <t>any-musician-can-upload</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="4" t="inlineStr">
+        <is>
+          <t>streaming-has-clearly-done</t>
+        </is>
+      </c>
+      <c r="B958" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C958" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D958" s="4" t="inlineStr">
+        <is>
+          <t>listeners-discover-artists-other</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="4" t="inlineStr">
+        <is>
+          <t>streaming-has-clearly-done</t>
+        </is>
+      </c>
+      <c r="B959" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C959" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D959" s="4" t="inlineStr">
+        <is>
+          <t>artists-keep-rights-own</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="4" t="inlineStr">
+        <is>
+          <t>streaming-has-clearly-done</t>
+        </is>
+      </c>
+      <c r="B960" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C960" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D960" s="4" t="inlineStr">
+        <is>
+          <t>when-everyone-can-publish</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="4" t="inlineStr">
+        <is>
+          <t>streaming-has-clearly-done</t>
+        </is>
+      </c>
+      <c r="B961" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C961" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D961" s="4" t="inlineStr">
+        <is>
+          <t>playlists-chosen-platform-staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="4" t="inlineStr">
+        <is>
+          <t>streaming-has-clearly-done</t>
+        </is>
+      </c>
+      <c r="B962" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C962" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D962" s="4" t="inlineStr">
+        <is>
+          <t>making-music-available-almost</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="4" t="inlineStr">
+        <is>
+          <t>comedians-generally-able-joke</t>
+        </is>
+      </c>
+      <c r="B963" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C963" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D963" s="4" t="inlineStr">
+        <is>
+          <t>comedy-works-saying-what</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="4" t="inlineStr">
+        <is>
+          <t>comedians-generally-able-joke</t>
+        </is>
+      </c>
+      <c r="B964" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C964" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D964" s="4" t="inlineStr">
+        <is>
+          <t>audiences-already-control-comedy</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="4" t="inlineStr">
+        <is>
+          <t>comedians-generally-able-joke</t>
+        </is>
+      </c>
+      <c r="B965" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C965" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D965" s="4" t="inlineStr">
+        <is>
+          <t>when-comedians-punished-offense</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="4" t="inlineStr">
+        <is>
+          <t>comedians-generally-able-joke</t>
+        </is>
+      </c>
+      <c r="B966" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C966" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D966" s="4" t="inlineStr">
+        <is>
+          <t>losing-booking-censorship-venues</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="4" t="inlineStr">
+        <is>
+          <t>comedians-generally-able-joke</t>
+        </is>
+      </c>
+      <c r="B967" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C967" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D967" s="4" t="inlineStr">
+        <is>
+          <t>joke-spreads-contempt-group</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="4" t="inlineStr">
+        <is>
+          <t>comedians-generally-able-joke</t>
+        </is>
+      </c>
+      <c r="B968" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C968" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D968" s="4" t="inlineStr">
+        <is>
+          <t>great-comedians-have-always</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="4" t="inlineStr">
+        <is>
+          <t>jokes-mock-people-race</t>
+        </is>
+      </c>
+      <c r="B969" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C969" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D969" s="4" t="inlineStr">
+        <is>
+          <t>laughter-makes-contempt-feel</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="4" t="inlineStr">
+        <is>
+          <t>jokes-mock-people-race</t>
+        </is>
+      </c>
+      <c r="B970" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C970" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D970" s="4" t="inlineStr">
+        <is>
+          <t>people-mocked-group-hear</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" s="4" t="inlineStr">
+        <is>
+          <t>jokes-mock-people-race</t>
+        </is>
+      </c>
+      <c r="B971" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C971" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D971" s="4" t="inlineStr">
+        <is>
+          <t>pushback-itself-free-speech</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="4" t="inlineStr">
+        <is>
+          <t>jokes-mock-people-race</t>
+        </is>
+      </c>
+      <c r="B972" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C972" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D972" s="4" t="inlineStr">
+        <is>
+          <t>most-jokes-about-groups</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="4" t="inlineStr">
+        <is>
+          <t>jokes-mock-people-race</t>
+        </is>
+      </c>
+      <c r="B973" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C973" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D973" s="4" t="inlineStr">
+        <is>
+          <t>comedians-within-group-often</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="4" t="inlineStr">
+        <is>
+          <t>jokes-mock-people-race</t>
+        </is>
+      </c>
+      <c r="B974" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C974" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D974" s="4" t="inlineStr">
+        <is>
+          <t>organized-pushback-rarely-stays</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="4" t="inlineStr">
+        <is>
+          <t>traditional-publishers-still-generally</t>
+        </is>
+      </c>
+      <c r="B975" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C975" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D975" s="4" t="inlineStr">
+        <is>
+          <t>publisher-s-editors-designers</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="4" t="inlineStr">
+        <is>
+          <t>traditional-publishers-still-generally</t>
+        </is>
+      </c>
+      <c r="B976" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C976" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D976" s="4" t="inlineStr">
+        <is>
+          <t>publishers-pay-authors-advance</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="4" t="inlineStr">
+        <is>
+          <t>traditional-publishers-still-generally</t>
+        </is>
+      </c>
+      <c r="B977" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C977" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D977" s="4" t="inlineStr">
+        <is>
+          <t>when-publisher-has-invest</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="4" t="inlineStr">
+        <is>
+          <t>traditional-publishers-still-generally</t>
+        </is>
+      </c>
+      <c r="B978" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C978" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D978" s="4" t="inlineStr">
+        <is>
+          <t>publishers-pick-books-think</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" s="4" t="inlineStr">
+        <is>
+          <t>traditional-publishers-still-generally</t>
+        </is>
+      </c>
+      <c r="B979" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C979" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D979" s="4" t="inlineStr">
+        <is>
+          <t>online-reviews-recommendations-now</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="4" t="inlineStr">
+        <is>
+          <t>traditional-publishers-still-generally</t>
+        </is>
+      </c>
+      <c r="B980" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C980" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D980" s="4" t="inlineStr">
+        <is>
+          <t>self-published-authors-can</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" s="4" t="inlineStr">
+        <is>
+          <t>most-working-authors-better</t>
+        </is>
+      </c>
+      <c r="B981" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C981" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D981" s="4" t="inlineStr">
+        <is>
+          <t>self-published-author-keeps</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="4" t="inlineStr">
+        <is>
+          <t>most-working-authors-better</t>
+        </is>
+      </c>
+      <c r="B982" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C982" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D982" s="4" t="inlineStr">
+        <is>
+          <t>authors-who-self-publish</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" s="4" t="inlineStr">
+        <is>
+          <t>most-working-authors-better</t>
+        </is>
+      </c>
+      <c r="B983" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C983" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D983" s="4" t="inlineStr">
+        <is>
+          <t>publishers-put-marketing-behind</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" s="4" t="inlineStr">
+        <is>
+          <t>most-working-authors-better</t>
+        </is>
+      </c>
+      <c r="B984" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C984" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D984" s="4" t="inlineStr">
+        <is>
+          <t>self-publishing-turns-writer</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" s="4" t="inlineStr">
+        <is>
+          <t>most-working-authors-better</t>
+        </is>
+      </c>
+      <c r="B985" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C985" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D985" s="4" t="inlineStr">
+        <is>
+          <t>bookstores-libraries-prizes-review</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="4" t="inlineStr">
+        <is>
+          <t>most-working-authors-better</t>
+        </is>
+      </c>
+      <c r="B986" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C986" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D986" s="4" t="inlineStr">
+        <is>
+          <t>advance-guaranteed-money-field</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="4" t="inlineStr">
+        <is>
+          <t>governments-generally-require-proven</t>
+        </is>
+      </c>
+      <c r="B987" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C987" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D987" s="4" t="inlineStr">
+        <is>
+          <t>some-children-cannot-vaccinated</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="4" t="inlineStr">
+        <is>
+          <t>governments-generally-require-proven</t>
+        </is>
+      </c>
+      <c r="B988" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C988" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D988" s="4" t="inlineStr">
+        <is>
+          <t>schools-gather-many-children</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" s="4" t="inlineStr">
+        <is>
+          <t>governments-generally-require-proven</t>
+        </is>
+      </c>
+      <c r="B989" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C989" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D989" s="4" t="inlineStr">
+        <is>
+          <t>requirement-tied-school-attendance</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" s="4" t="inlineStr">
+        <is>
+          <t>governments-generally-require-proven</t>
+        </is>
+      </c>
+      <c r="B990" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C990" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D990" s="4" t="inlineStr">
+        <is>
+          <t>parents-school-administrators-responsible</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" s="4" t="inlineStr">
+        <is>
+          <t>governments-generally-require-proven</t>
+        </is>
+      </c>
+      <c r="B991" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C991" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D991" s="4" t="inlineStr">
+        <is>
+          <t>mandates-breed-resentment-distrust</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" s="4" t="inlineStr">
+        <is>
+          <t>governments-generally-require-proven</t>
+        </is>
+      </c>
+      <c r="B992" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C992" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D992" s="4" t="inlineStr">
+        <is>
+          <t>most-vaccine-preventable-diseases</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" s="4" t="inlineStr">
+        <is>
+          <t>routine-cancer-screening-healthy</t>
+        </is>
+      </c>
+      <c r="B993" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C993" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D993" s="4" t="inlineStr">
+        <is>
+          <t>screening-finds-many-slow</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" s="4" t="inlineStr">
+        <is>
+          <t>routine-cancer-screening-healthy</t>
+        </is>
+      </c>
+      <c r="B994" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C994" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D994" s="4" t="inlineStr">
+        <is>
+          <t>false-alarm-sets-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" s="4" t="inlineStr">
+        <is>
+          <t>routine-cancer-screening-healthy</t>
+        </is>
+      </c>
+      <c r="B995" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C995" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D995" s="4" t="inlineStr">
+        <is>
+          <t>finding-cancer-earlier-often</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" s="4" t="inlineStr">
+        <is>
+          <t>routine-cancer-screening-healthy</t>
+        </is>
+      </c>
+      <c r="B996" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C996" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D996" s="4" t="inlineStr">
+        <is>
+          <t>many-cancers-far-easier</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" s="4" t="inlineStr">
+        <is>
+          <t>routine-cancer-screening-healthy</t>
+        </is>
+      </c>
+      <c r="B997" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C997" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D997" s="4" t="inlineStr">
+        <is>
+          <t>patients-can-told-risks</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" s="4" t="inlineStr">
+        <is>
+          <t>routine-cancer-screening-healthy</t>
+        </is>
+      </c>
+      <c r="B998" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C998" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D998" s="4" t="inlineStr">
+        <is>
+          <t>harms-screening-mostly-temporary</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" s="4" t="inlineStr">
+        <is>
+          <t>adults-generally-allowed-buy</t>
+        </is>
+      </c>
+      <c r="B999" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C999" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D999" s="4" t="inlineStr">
+        <is>
+          <t>many-prescriptions-refills-medicines</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="4" t="inlineStr">
+        <is>
+          <t>adults-generally-allowed-buy</t>
+        </is>
+      </c>
+      <c r="B1000" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1000" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1000" s="4" t="inlineStr">
+        <is>
+          <t>pharmacists-trained-drugs-interactions</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="4" t="inlineStr">
+        <is>
+          <t>adults-generally-allowed-buy</t>
+        </is>
+      </c>
+      <c r="B1001" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1001" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1001" s="4" t="inlineStr">
+        <is>
+          <t>people-who-cannot-easily</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="4" t="inlineStr">
+        <is>
+          <t>adults-generally-allowed-buy</t>
+        </is>
+      </c>
+      <c r="B1002" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1002" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1002" s="4" t="inlineStr">
+        <is>
+          <t>doctor-s-visit-catches</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="4" t="inlineStr">
+        <is>
+          <t>adults-generally-allowed-buy</t>
+        </is>
+      </c>
+      <c r="B1003" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1003" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1003" s="4" t="inlineStr">
+        <is>
+          <t>pharmacists-work-stores-profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="4" t="inlineStr">
+        <is>
+          <t>adults-generally-allowed-buy</t>
+        </is>
+      </c>
+      <c r="B1004" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1004" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1004" s="4" t="inlineStr">
+        <is>
+          <t>antibiotic-resistance-dependence-some</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="4" t="inlineStr">
+        <is>
+          <t>governments-generally-set-maximum</t>
+        </is>
+      </c>
+      <c r="B1005" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1005" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1005" s="4" t="inlineStr">
+        <is>
+          <t>patent-already-gives-company</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="4" t="inlineStr">
+        <is>
+          <t>governments-generally-set-maximum</t>
+        </is>
+      </c>
+      <c r="B1006" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1006" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1006" s="4" t="inlineStr">
+        <is>
+          <t>much-basic-research-behind</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="4" t="inlineStr">
+        <is>
+          <t>governments-generally-set-maximum</t>
+        </is>
+      </c>
+      <c r="B1007" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1007" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1007" s="4" t="inlineStr">
+        <is>
+          <t>patients-who-skip-doses</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="4" t="inlineStr">
+        <is>
+          <t>governments-generally-set-maximum</t>
+        </is>
+      </c>
+      <c r="B1008" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1008" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1008" s="4" t="inlineStr">
+        <is>
+          <t>companies-invest-research-because</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="4" t="inlineStr">
+        <is>
+          <t>governments-generally-set-maximum</t>
+        </is>
+      </c>
+      <c r="B1009" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1009" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1009" s="4" t="inlineStr">
+        <is>
+          <t>cap-set-officials-will</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="4" t="inlineStr">
+        <is>
+          <t>governments-generally-set-maximum</t>
+        </is>
+      </c>
+      <c r="B1010" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1010" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1010" s="4" t="inlineStr">
+        <is>
+          <t>prices-already-bargained-down</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="4" t="inlineStr">
+        <is>
+          <t>california-generally-override-local</t>
+        </is>
+      </c>
+      <c r="B1011" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1011" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1011" s="4" t="inlineStr">
+        <is>
+          <t>local-governments-have-blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="4" t="inlineStr">
+        <is>
+          <t>california-generally-override-local</t>
+        </is>
+      </c>
+      <c r="B1012" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1012" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1012" s="4" t="inlineStr">
+        <is>
+          <t>teachers-nurses-service-workers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="4" t="inlineStr">
+        <is>
+          <t>california-generally-override-local</t>
+        </is>
+      </c>
+      <c r="B1013" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1013" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1013" s="4" t="inlineStr">
+        <is>
+          <t>people-businesses-leaving-state</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="4" t="inlineStr">
+        <is>
+          <t>california-generally-override-local</t>
+        </is>
+      </c>
+      <c r="B1014" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1014" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1014" s="4" t="inlineStr">
+        <is>
+          <t>local-communities-understand-own</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="4" t="inlineStr">
+        <is>
+          <t>california-generally-override-local</t>
+        </is>
+      </c>
+      <c r="B1015" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1015" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1015" s="4" t="inlineStr">
+        <is>
+          <t>state-mandates-have-mostly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="4" t="inlineStr">
+        <is>
+          <t>california-generally-override-local</t>
+        </is>
+      </c>
+      <c r="B1016" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1016" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1016" s="4" t="inlineStr">
+        <is>
+          <t>market-rate-construction-alone</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="4" t="inlineStr">
+        <is>
+          <t>texas-connect-its-separate</t>
+        </is>
+      </c>
+      <c r="B1017" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1017" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1017" s="4" t="inlineStr">
+        <is>
+          <t>when-extreme-weather-hits</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="4" t="inlineStr">
+        <is>
+          <t>texas-connect-its-separate</t>
+        </is>
+      </c>
+      <c r="B1018" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1018" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1018" s="4" t="inlineStr">
+        <is>
+          <t>texas-produces-more-wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="4" t="inlineStr">
+        <is>
+          <t>texas-connect-its-separate</t>
+        </is>
+      </c>
+      <c r="B1019" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1019" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1019" s="4" t="inlineStr">
+        <is>
+          <t>investors-more-willing-build</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="4" t="inlineStr">
+        <is>
+          <t>texas-connect-its-separate</t>
+        </is>
+      </c>
+      <c r="B1020" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1020" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1020" s="4" t="inlineStr">
+        <is>
+          <t>connecting-national-grids-brings</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="4" t="inlineStr">
+        <is>
+          <t>texas-connect-its-separate</t>
+        </is>
+      </c>
+      <c r="B1021" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1021" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1021" s="4" t="inlineStr">
+        <is>
+          <t>lines-needed-connect-grids</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="4" t="inlineStr">
+        <is>
+          <t>texas-connect-its-separate</t>
+        </is>
+      </c>
+      <c r="B1022" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1022" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1022" s="4" t="inlineStr">
+        <is>
+          <t>neighboring-regions-have-had</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="4" t="inlineStr">
+        <is>
+          <t>judging-teachers-partly-students</t>
+        </is>
+      </c>
+      <c r="B1023" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1023" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1023" s="4" t="inlineStr">
+        <is>
+          <t>without-measure-results-teacher</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="4" t="inlineStr">
+        <is>
+          <t>judging-teachers-partly-students</t>
+        </is>
+      </c>
+      <c r="B1024" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1024" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1024" s="4" t="inlineStr">
+        <is>
+          <t>parents-deserve-know-whether</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="4" t="inlineStr">
+        <is>
+          <t>judging-teachers-partly-students</t>
+        </is>
+      </c>
+      <c r="B1025" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1025" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1025" s="4" t="inlineStr">
+        <is>
+          <t>teachers-who-consistently-help</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="4" t="inlineStr">
+        <is>
+          <t>judging-teachers-partly-students</t>
+        </is>
+      </c>
+      <c r="B1026" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1026" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1026" s="4" t="inlineStr">
+        <is>
+          <t>students-arrive-wildly-different</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="4" t="inlineStr">
+        <is>
+          <t>judging-teachers-partly-students</t>
+        </is>
+      </c>
+      <c r="B1027" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1027" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1027" s="4" t="inlineStr">
+        <is>
+          <t>when-jobs-depend-scores</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="4" t="inlineStr">
+        <is>
+          <t>judging-teachers-partly-students</t>
+        </is>
+      </c>
+      <c r="B1028" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1028" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1028" s="4" t="inlineStr">
+        <is>
+          <t>strong-teachers-avoid-hardest</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="4" t="inlineStr">
+        <is>
+          <t>teachers-generally-do-best</t>
+        </is>
+      </c>
+      <c r="B1029" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1029" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1029" s="4" t="inlineStr">
+        <is>
+          <t>teacher-sees-each-child</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="4" t="inlineStr">
+        <is>
+          <t>teachers-generally-do-best</t>
+        </is>
+      </c>
+      <c r="B1030" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1030" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1030" s="4" t="inlineStr">
+        <is>
+          <t>professionals-who-trusted-stay</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="4" t="inlineStr">
+        <is>
+          <t>teachers-generally-do-best</t>
+        </is>
+      </c>
+      <c r="B1031" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1031" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1031" s="4" t="inlineStr">
+        <is>
+          <t>lessons-teacher-believes-taught</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="4" t="inlineStr">
+        <is>
+          <t>teachers-generally-do-best</t>
+        </is>
+      </c>
+      <c r="B1032" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1032" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1032" s="4" t="inlineStr">
+        <is>
+          <t>most-teachers-were-never</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="4" t="inlineStr">
+        <is>
+          <t>teachers-generally-do-best</t>
+        </is>
+      </c>
+      <c r="B1033" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1033" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1033" s="4" t="inlineStr">
+        <is>
+          <t>well-designed-materials-carry</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="4" t="inlineStr">
+        <is>
+          <t>teachers-generally-do-best</t>
+        </is>
+      </c>
+      <c r="B1034" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1034" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1034" s="4" t="inlineStr">
+        <is>
+          <t>children-who-move-between</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="4" t="inlineStr">
+        <is>
+          <t>statues-honoring-historical-figures</t>
+        </is>
+      </c>
+      <c r="B1035" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1035" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1035" s="4" t="inlineStr">
+        <is>
+          <t>statue-public-square-honor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="4" t="inlineStr">
+        <is>
+          <t>statues-honoring-historical-figures</t>
+        </is>
+      </c>
+      <c r="B1036" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1036" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1036" s="4" t="inlineStr">
+        <is>
+          <t>public-spaces-belong-people</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="4" t="inlineStr">
+        <is>
+          <t>statues-honoring-historical-figures</t>
+        </is>
+      </c>
+      <c r="B1037" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1037" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1037" s="4" t="inlineStr">
+        <is>
+          <t>moving-statue-museum-explanation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="4" t="inlineStr">
+        <is>
+          <t>statues-honoring-historical-figures</t>
+        </is>
+      </c>
+      <c r="B1038" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1038" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1038" s="4" t="inlineStr">
+        <is>
+          <t>removing-monuments-makes-uncomfortable</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="4" t="inlineStr">
+        <is>
+          <t>statues-honoring-historical-figures</t>
+        </is>
+      </c>
+      <c r="B1039" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1039" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1039" s="4" t="inlineStr">
+        <is>
+          <t>nearly-everyone-honored-past</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="4" t="inlineStr">
+        <is>
+          <t>statues-honoring-historical-figures</t>
+        </is>
+      </c>
+      <c r="B1040" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1040" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1040" s="4" t="inlineStr">
+        <is>
+          <t>decisions-about-which-statues</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="4" t="inlineStr">
+        <is>
+          <t>historians-generally-judge-people</t>
+        </is>
+      </c>
+      <c r="B1041" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1041" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1041" s="4" t="inlineStr">
+        <is>
+          <t>people-past-could-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="4" t="inlineStr">
+        <is>
+          <t>historians-generally-judge-people</t>
+        </is>
+      </c>
+      <c r="B1042" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1042" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1042" s="4" t="inlineStr">
+        <is>
+          <t>historian-s-job-explain</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="4" t="inlineStr">
+        <is>
+          <t>historians-generally-judge-people</t>
+        </is>
+      </c>
+      <c r="B1043" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1043" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1043" s="4" t="inlineStr">
+        <is>
+          <t>our-own-standards-will</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="4" t="inlineStr">
+        <is>
+          <t>historians-generally-judge-people</t>
+        </is>
+      </c>
+      <c r="B1044" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1044" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1044" s="4" t="inlineStr">
+        <is>
+          <t>nearly-every-era-there</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="4" t="inlineStr">
+        <is>
+          <t>historians-generally-judge-people</t>
+        </is>
+      </c>
+      <c r="B1045" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1045" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1045" s="4" t="inlineStr">
+        <is>
+          <t>declining-judge-neutral-because</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="4" t="inlineStr">
+        <is>
+          <t>historians-generally-judge-people</t>
+        </is>
+      </c>
+      <c r="B1046" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1046" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1046" s="4" t="inlineStr">
+        <is>
+          <t>history-written-living-readers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="4" t="inlineStr">
+        <is>
+          <t>fish-clearly-feel-pain</t>
+        </is>
+      </c>
+      <c r="B1047" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1047" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1047" s="4" t="inlineStr">
+        <is>
+          <t>fish-have-nerve-structures</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="4" t="inlineStr">
+        <is>
+          <t>fish-clearly-feel-pain</t>
+        </is>
+      </c>
+      <c r="B1048" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1048" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1048" s="4" t="inlineStr">
+        <is>
+          <t>fish-change-behavior-long</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="4" t="inlineStr">
+        <is>
+          <t>fish-clearly-feel-pain</t>
+        </is>
+      </c>
+      <c r="B1049" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1049" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1049" s="4" t="inlineStr">
+        <is>
+          <t>pain-relief-drugs-return</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="4" t="inlineStr">
+        <is>
+          <t>fish-clearly-feel-pain</t>
+        </is>
+      </c>
+      <c r="B1050" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1050" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1050" s="4" t="inlineStr">
+        <is>
+          <t>fish-lack-outer-brain</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="4" t="inlineStr">
+        <is>
+          <t>fish-clearly-feel-pain</t>
+        </is>
+      </c>
+      <c r="B1051" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1051" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1051" s="4" t="inlineStr">
+        <is>
+          <t>avoiding-place-where-you</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="4" t="inlineStr">
+        <is>
+          <t>fish-clearly-feel-pain</t>
+        </is>
+      </c>
+      <c r="B1052" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1052" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1052" s="4" t="inlineStr">
+        <is>
+          <t>judging-animal-s-inner</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" s="4" t="inlineStr">
+        <is>
+          <t>claims-apes-parrots-understand</t>
+        </is>
+      </c>
+      <c r="B1053" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1053" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1053" s="4" t="inlineStr">
+        <is>
+          <t>trained-animals-mostly-produce</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="4" t="inlineStr">
+        <is>
+          <t>claims-apes-parrots-understand</t>
+        </is>
+      </c>
+      <c r="B1054" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1054" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1054" s="4" t="inlineStr">
+        <is>
+          <t>people-reporting-animal-s</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="4" t="inlineStr">
+        <is>
+          <t>claims-apes-parrots-understand</t>
+        </is>
+      </c>
+      <c r="B1055" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1055" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1055" s="4" t="inlineStr">
+        <is>
+          <t>no-animal-has-been</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="4" t="inlineStr">
+        <is>
+          <t>claims-apes-parrots-understand</t>
+        </is>
+      </c>
+      <c r="B1056" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1056" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1056" s="4" t="inlineStr">
+        <is>
+          <t>some-animals-use-learned</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="4" t="inlineStr">
+        <is>
+          <t>claims-apes-parrots-understand</t>
+        </is>
+      </c>
+      <c r="B1057" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1057" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1057" s="4" t="inlineStr">
+        <is>
+          <t>wild-animals-already-use</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="4" t="inlineStr">
+        <is>
+          <t>claims-apes-parrots-understand</t>
+        </is>
+      </c>
+      <c r="B1058" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1058" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1058" s="4" t="inlineStr">
+        <is>
+          <t>demanding-full-human-grammar</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T898"/>
+  <autoFilter ref="A1:T1058"/>
   <dataValidations count="2">
     <dataValidation sqref="B2:B5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"argument,assumption,bias,category,cba,common,component,compromise,criteria,criterion,definition,direction,dispute,downstream,engagement,evidence,falsify,impact,interest,interest_listing,law,long_term,media,motive,obstacle,person,prediction,related,rung,shared_interest,short_term,similar,stack,strength,topic_media,topic_values,upstream,value"</formula1>
@@ -32061,6 +39161,16 @@
           <t>business-and-economy</t>
         </is>
       </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Business covers how companies are owned, governed and run, and whom they must answer to.</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>favors tighter public rules on how companies are run and who they answer to, negative favors leaving companies free to run themselves and answer mainly to their owners.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -32384,6 +39494,16 @@
           <t>entertainment</t>
         </is>
       </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Recorded and live music, the people who make it, and the labels, streaming services and platforms that carry it to listeners.</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>holds that music streaming has been good for musicians overall; negative holds that it has shortchanged them.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -32401,6 +39521,16 @@
           <t>entertainment</t>
         </is>
       </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Comedy in stand-up, film, television and online, and the arguments over what jokes are acceptable and who decides.</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>favors wide freedom for comedians to joke about any subject with few social consequences; negative favors holding comedians to social limits on jokes that offend or demean.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -32418,6 +39548,16 @@
           <t>entertainment</t>
         </is>
       </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>The business of producing and selling books, from traditional publishing houses to self-publishing and ebooks.</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>favors traditional publishers as the best path for books, readers and authors; negative favors self-publishing and open platforms.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -32537,6 +39677,16 @@
           <t>health</t>
         </is>
       </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>How societies prevent, detect, and respond to illness, from infectious outbreaks to chronic conditions like cancer and diabetes.</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>favors aggressive public action to prevent and control disease (mandates, screening, surveillance); negative favors leaving disease prevention mainly to individual choice and treating illness as it appears.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -32554,6 +39704,16 @@
           <t>health</t>
         </is>
       </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Prescription medicines, over-the-counter products, and recreational substances, including how they are approved, priced, sold, and regulated.</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>favors treating drugs as a market good with lighter rules on access and pricing; negative favors stronger government control over drug approval, sale, and price.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -32758,6 +39918,16 @@
           <t>regional</t>
         </is>
       </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Beliefs about policies and choices made at the level of an individual American state.</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>favors a state government taking a bigger and more active role; negative favors a smaller state role, leaving matters to local governments, the market, or the federal system.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -32945,6 +40115,16 @@
           <t>education</t>
         </is>
       </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Covers how teachers are trained, paid, evaluated and supported, and how much control they have over what happens in their classrooms.</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>favors more outside structure and accountability for teachers, such as testing, set curricula and formal evaluation; negative favors more trust in teachers' own professional judgment.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -33013,6 +40193,16 @@
           <t>arts-and-humanities</t>
         </is>
       </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>History covers how the past is studied, written, taught and remembered in public, including monuments, textbooks and popular retellings.</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>favors judging and reshaping how the past is presented by today's moral standards and priorities; negative favors presenting the past on its own terms with as little present-day judgment as possible.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -33079,6 +40269,16 @@
       <c r="C65" s="4" t="inlineStr">
         <is>
           <t>science</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Animals covers what is known about how other animals think, feel and behave, and how much their inner lives resemble ours.</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>holds that animals have minds and feelings close to our own; negative holds that the gap between humans and other animals is wide and often exaggerated by wishful thinking.</t>
         </is>
       </c>
     </row>

--- a/tools/static-site/ISE_Data_Entry.xlsx
+++ b/tools/static-site/ISE_Data_Entry.xlsx
@@ -13,8 +13,8 @@
     <sheet name="topics" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'pages'!$A$1:$AC$402</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'edges'!$A$1:$T$1058</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'pages'!$A$1:$AC$416</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'edges'!$A$1:$T$1085</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'topics'!$A$1:$F$79</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -859,7 +859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC402"/>
+  <dimension ref="A1:AC416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -13967,8 +13967,342 @@
         </is>
       </c>
     </row>
+    <row r="403">
+      <c r="A403" s="4" t="inlineStr">
+        <is>
+          <t>most-people-depression-anxiety</t>
+        </is>
+      </c>
+      <c r="C403" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D403" s="4" t="inlineStr">
+        <is>
+          <t>Most people with depression or anxiety would clearly benefit from professional treatment rather than handling it on their own.</t>
+        </is>
+      </c>
+      <c r="F403" s="5" t="inlineStr">
+        <is>
+          <t>psychology</t>
+        </is>
+      </c>
+      <c r="W403" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether common sadness and worry are illnesses that need expert care or ordinary struggles that most people can and should work through themselves.</t>
+        </is>
+      </c>
+      <c r="AA403" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB403" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="4" t="inlineStr">
+        <is>
+          <t>trained-therapists-doctors-have</t>
+        </is>
+      </c>
+      <c r="C404" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D404" s="4" t="inlineStr">
+        <is>
+          <t>Trained therapists and doctors have methods that work and that a person cannot easily apply to themselves, just as a person cannot set their own broken bone well.</t>
+        </is>
+      </c>
+      <c r="G404" s="4" t="inlineStr">
+        <is>
+          <t>most-people-depression-anxiety</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="4" t="inlineStr">
+        <is>
+          <t>very-symptoms-depression-low</t>
+        </is>
+      </c>
+      <c r="C405" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D405" s="4" t="inlineStr">
+        <is>
+          <t>The very symptoms of depression, low energy and hopelessness, make self-help unlikely to succeed, because the illness attacks the will needed to fight it.</t>
+        </is>
+      </c>
+      <c r="G405" s="4" t="inlineStr">
+        <is>
+          <t>most-people-depression-anxiety</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="4" t="inlineStr">
+        <is>
+          <t>untreated-problems-tend-grow</t>
+        </is>
+      </c>
+      <c r="C406" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D406" s="4" t="inlineStr">
+        <is>
+          <t>Untreated problems tend to grow, affecting work, family, and physical health, so early professional care prevents larger costs later.</t>
+        </is>
+      </c>
+      <c r="G406" s="4" t="inlineStr">
+        <is>
+          <t>most-people-depression-anxiety</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="4" t="inlineStr">
+        <is>
+          <t>sadness-worry-normal-responses</t>
+        </is>
+      </c>
+      <c r="C407" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D407" s="4" t="inlineStr">
+        <is>
+          <t>Sadness and worry are normal responses to hard lives, and calling them illnesses teaches people they are broken when they are simply struggling.</t>
+        </is>
+      </c>
+      <c r="G407" s="4" t="inlineStr">
+        <is>
+          <t>most-people-depression-anxiety</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="4" t="inlineStr">
+        <is>
+          <t>many-people-recover-fully</t>
+        </is>
+      </c>
+      <c r="C408" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D408" s="4" t="inlineStr">
+        <is>
+          <t>Many people recover fully through exercise, sleep, friendship, and time, and steering them all toward clinics uses up limited care that the severely ill need.</t>
+        </is>
+      </c>
+      <c r="G408" s="4" t="inlineStr">
+        <is>
+          <t>most-people-depression-anxiety</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="4" t="inlineStr">
+        <is>
+          <t>treatment-carries-its-own</t>
+        </is>
+      </c>
+      <c r="C409" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D409" s="4" t="inlineStr">
+        <is>
+          <t>Treatment carries its own risks, including medication side effects and dependence on a therapist, that are worth accepting only when the problem is serious.</t>
+        </is>
+      </c>
+      <c r="G409" s="4" t="inlineStr">
+        <is>
+          <t>most-people-depression-anxiety</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="4" t="inlineStr">
+        <is>
+          <t>teaching-children-build-toughness</t>
+        </is>
+      </c>
+      <c r="C410" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D410" s="4" t="inlineStr">
+        <is>
+          <t>Teaching children to build toughness and tolerate discomfort does more for their mental health than teaching them to monitor and talk about their feelings.</t>
+        </is>
+      </c>
+      <c r="F410" s="5" t="inlineStr">
+        <is>
+          <t>psychology</t>
+        </is>
+      </c>
+      <c r="W410" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether paying close attention to feelings makes children stronger by helping them ask for help or weaker by making small worries loom large.</t>
+        </is>
+      </c>
+      <c r="AA410" s="5" t="n">
+        <v>-45</v>
+      </c>
+      <c r="AB410" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="4" t="inlineStr">
+        <is>
+          <t>constant-attention-feelings-can</t>
+        </is>
+      </c>
+      <c r="C411" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D411" s="4" t="inlineStr">
+        <is>
+          <t>Constant attention to feelings can make small worries seem large, and children who learn to push through discomfort discover they can handle more than they feared.</t>
+        </is>
+      </c>
+      <c r="G411" s="4" t="inlineStr">
+        <is>
+          <t>teaching-children-build-toughness</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="4" t="inlineStr">
+        <is>
+          <t>life-will-bring-hardship</t>
+        </is>
+      </c>
+      <c r="C412" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D412" s="4" t="inlineStr">
+        <is>
+          <t>Life will bring hardship that no amount of talking can prevent, so the skill that lasts is the ability to keep going through it.</t>
+        </is>
+      </c>
+      <c r="G412" s="4" t="inlineStr">
+        <is>
+          <t>teaching-children-build-toughness</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="4" t="inlineStr">
+        <is>
+          <t>children-who-treated-fragile</t>
+        </is>
+      </c>
+      <c r="C413" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D413" s="4" t="inlineStr">
+        <is>
+          <t>Children who are treated as fragile tend to act fragile, while children expected to cope generally rise to the expectation.</t>
+        </is>
+      </c>
+      <c r="G413" s="4" t="inlineStr">
+        <is>
+          <t>teaching-children-build-toughness</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="4" t="inlineStr">
+        <is>
+          <t>children-who-cannot-name</t>
+        </is>
+      </c>
+      <c r="C414" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D414" s="4" t="inlineStr">
+        <is>
+          <t>Children who cannot name what they feel cannot ask for help, and telling them to tough it out teaches them to hide problems until they become crises.</t>
+        </is>
+      </c>
+      <c r="G414" s="4" t="inlineStr">
+        <is>
+          <t>teaching-children-build-toughness</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="4" t="inlineStr">
+        <is>
+          <t>toughness-training-works-children</t>
+        </is>
+      </c>
+      <c r="C415" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D415" s="4" t="inlineStr">
+        <is>
+          <t>Toughness training works for children who are already secure, but for a child who is being bullied or abused it means suffering in silence.</t>
+        </is>
+      </c>
+      <c r="G415" s="4" t="inlineStr">
+        <is>
+          <t>teaching-children-build-toughness</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="4" t="inlineStr">
+        <is>
+          <t>talking-about-feelings-building</t>
+        </is>
+      </c>
+      <c r="C416" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D416" s="4" t="inlineStr">
+        <is>
+          <t>Talking about feelings and building toughness are not opposites; naming a fear is often the first step to facing it.</t>
+        </is>
+      </c>
+      <c r="G416" s="4" t="inlineStr">
+        <is>
+          <t>teaching-children-build-toughness</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC402"/>
+  <autoFilter ref="A1:AC416"/>
   <dataValidations count="5">
     <dataValidation sqref="C2:C5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"belief,claim,linkage,importance,interest,uniqueness,equivalence,driver,media"</formula1>
@@ -13997,7 +14331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1058"/>
+  <dimension ref="A1:T1085"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -39010,8 +39344,712 @@
         </is>
       </c>
     </row>
+    <row r="1059">
+      <c r="A1059" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1059" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C1059" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1059" s="4" t="inlineStr">
+        <is>
+          <t>clemency-only-executive-power</t>
+        </is>
+      </c>
+      <c r="O1059" s="4" t="inlineStr">
+        <is>
+          <t>D.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1060" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C1060" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1060" s="4" t="inlineStr">
+        <is>
+          <t>article-ii-grants-power</t>
+        </is>
+      </c>
+      <c r="O1060" s="4" t="inlineStr">
+        <is>
+          <t>D.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1061" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C1061" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1061" s="4" t="inlineStr">
+        <is>
+          <t>pardons-granted-president-s</t>
+        </is>
+      </c>
+      <c r="O1061" s="4" t="inlineStr">
+        <is>
+          <t>D.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1062" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C1062" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1062" s="4" t="inlineStr">
+        <is>
+          <t>narrower-fix-reaches-actual</t>
+        </is>
+      </c>
+      <c r="O1062" s="4" t="inlineStr">
+        <is>
+          <t>D.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1063" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C1063" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1063" s="4" t="inlineStr">
+        <is>
+          <t>two-thirds-threshold-means</t>
+        </is>
+      </c>
+      <c r="O1063" s="4" t="inlineStr">
+        <is>
+          <t>D.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1064" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C1064" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1064" s="4" t="inlineStr">
+        <is>
+          <t>clemency-exists-correct-injustices</t>
+        </is>
+      </c>
+      <c r="O1064" s="4" t="inlineStr">
+        <is>
+          <t>D.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1065" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C1065" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1065" s="4" t="inlineStr">
+        <is>
+          <t>most-states-already-put</t>
+        </is>
+      </c>
+      <c r="O1065" s="4" t="inlineStr">
+        <is>
+          <t>D.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1066" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C1066" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1066" s="4" t="inlineStr">
+        <is>
+          <t>reversible-pardon-pardon-nobody</t>
+        </is>
+      </c>
+      <c r="O1066" s="4" t="inlineStr">
+        <is>
+          <t>D.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1067" s="5" t="inlineStr">
+        <is>
+          <t>engagement</t>
+        </is>
+      </c>
+      <c r="C1067" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="E1067" s="4" t="inlineStr">
+        <is>
+          <t>A voter who thinks members of Congress should not trade the stocks of industries their committees oversee, votes for candidates who say so when the choice is easy, and otherwise leaves the matter alone.</t>
+        </is>
+      </c>
+      <c r="O1067" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T1067" s="4" t="inlineStr">
+        <is>
+          <t>example: sympathetic voter</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1068" s="5" t="inlineStr">
+        <is>
+          <t>engagement</t>
+        </is>
+      </c>
+      <c r="C1068" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="E1068" s="4" t="inlineStr">
+        <is>
+          <t>A voter who believes the disclosure form and the existing conflict-of-interest statutes already catch what matters, doubts a new ban would deter anyone but honest people of ordinary means, and says so only when asked.</t>
+        </is>
+      </c>
+      <c r="O1068" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T1068" s="4" t="inlineStr">
+        <is>
+          <t>example: skeptical voter</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1069" s="5" t="inlineStr">
+        <is>
+          <t>engagement</t>
+        </is>
+      </c>
+      <c r="C1069" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="E1069" s="4" t="inlineStr">
+        <is>
+          <t>A citizen who writes to their representative to demand a vote on the drafted holdings ban, signs and circulates petitions, backs candidates who pledge not to trade individual stocks, and asks publicly why the Senate has not scheduled the vote.</t>
+        </is>
+      </c>
+      <c r="O1069" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T1069" s="4" t="inlineStr">
+        <is>
+          <t>example: reform campaigner</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1070" s="5" t="inlineStr">
+        <is>
+          <t>engagement</t>
+        </is>
+      </c>
+      <c r="C1070" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="E1070" s="4" t="inlineStr">
+        <is>
+          <t>A citizen or former official who testifies, writes and organizes against new bans, argues that forced divestiture narrows who can afford to serve and reaches spouses and children who never ran, and pushes instead to strengthen the disclosure form and the audits.</t>
+        </is>
+      </c>
+      <c r="O1070" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T1070" s="4" t="inlineStr">
+        <is>
+          <t>example: disclosure-first advocate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1071" s="5" t="inlineStr">
+        <is>
+          <t>engagement</t>
+        </is>
+      </c>
+      <c r="C1071" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="E1071" s="4" t="inlineStr">
+        <is>
+          <t>An officeholder who sells their individual stocks or moves them into a blind trust, publishes their own tax returns, and declines to give any official role to a relative, all without a rule requiring it, while leaving colleagues to make their own choice.</t>
+        </is>
+      </c>
+      <c r="O1071" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T1071" s="4" t="inlineStr">
+        <is>
+          <t>example: self-divesting officeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1072" s="5" t="inlineStr">
+        <is>
+          <t>engagement</t>
+        </is>
+      </c>
+      <c r="C1072" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="E1072" s="4" t="inlineStr">
+        <is>
+          <t>An officeholder who keeps lawful individual holdings, refuses to sign a voluntary pledge to divest or to publish returns, states plainly that the law does not require it and that officials keep the ordinary rights of citizens, and does not try to stop others from pledging.</t>
+        </is>
+      </c>
+      <c r="O1072" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T1072" s="4" t="inlineStr">
+        <is>
+          <t>example: pledge-declining officeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1073" s="5" t="inlineStr">
+        <is>
+          <t>engagement</t>
+        </is>
+      </c>
+      <c r="C1073" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="E1073" s="4" t="inlineStr">
+        <is>
+          <t>A person with lawful access to an official's confidential tax return who publishes it under their own name to show what the disclosure form leaves out, knowing the law attaches criminal penalties to unauthorized disclosure, and accepts prosecution as the price of forcing the question.</t>
+        </is>
+      </c>
+      <c r="O1073" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T1073" s="4" t="inlineStr">
+        <is>
+          <t>example: open-disclosure lawbreaker</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" s="4" t="inlineStr">
+        <is>
+          <t>most-people-depression-anxiety</t>
+        </is>
+      </c>
+      <c r="B1074" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1074" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1074" s="4" t="inlineStr">
+        <is>
+          <t>trained-therapists-doctors-have</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="4" t="inlineStr">
+        <is>
+          <t>most-people-depression-anxiety</t>
+        </is>
+      </c>
+      <c r="B1075" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1075" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1075" s="4" t="inlineStr">
+        <is>
+          <t>very-symptoms-depression-low</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="4" t="inlineStr">
+        <is>
+          <t>most-people-depression-anxiety</t>
+        </is>
+      </c>
+      <c r="B1076" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1076" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1076" s="4" t="inlineStr">
+        <is>
+          <t>untreated-problems-tend-grow</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" s="4" t="inlineStr">
+        <is>
+          <t>most-people-depression-anxiety</t>
+        </is>
+      </c>
+      <c r="B1077" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1077" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1077" s="4" t="inlineStr">
+        <is>
+          <t>sadness-worry-normal-responses</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="4" t="inlineStr">
+        <is>
+          <t>most-people-depression-anxiety</t>
+        </is>
+      </c>
+      <c r="B1078" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1078" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1078" s="4" t="inlineStr">
+        <is>
+          <t>many-people-recover-fully</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="4" t="inlineStr">
+        <is>
+          <t>most-people-depression-anxiety</t>
+        </is>
+      </c>
+      <c r="B1079" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1079" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1079" s="4" t="inlineStr">
+        <is>
+          <t>treatment-carries-its-own</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="4" t="inlineStr">
+        <is>
+          <t>teaching-children-build-toughness</t>
+        </is>
+      </c>
+      <c r="B1080" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1080" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1080" s="4" t="inlineStr">
+        <is>
+          <t>constant-attention-feelings-can</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" s="4" t="inlineStr">
+        <is>
+          <t>teaching-children-build-toughness</t>
+        </is>
+      </c>
+      <c r="B1081" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1081" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1081" s="4" t="inlineStr">
+        <is>
+          <t>life-will-bring-hardship</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" s="4" t="inlineStr">
+        <is>
+          <t>teaching-children-build-toughness</t>
+        </is>
+      </c>
+      <c r="B1082" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1082" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1082" s="4" t="inlineStr">
+        <is>
+          <t>children-who-treated-fragile</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" s="4" t="inlineStr">
+        <is>
+          <t>teaching-children-build-toughness</t>
+        </is>
+      </c>
+      <c r="B1083" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1083" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1083" s="4" t="inlineStr">
+        <is>
+          <t>children-who-cannot-name</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" s="4" t="inlineStr">
+        <is>
+          <t>teaching-children-build-toughness</t>
+        </is>
+      </c>
+      <c r="B1084" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1084" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1084" s="4" t="inlineStr">
+        <is>
+          <t>toughness-training-works-children</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" s="4" t="inlineStr">
+        <is>
+          <t>teaching-children-build-toughness</t>
+        </is>
+      </c>
+      <c r="B1085" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1085" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1085" s="4" t="inlineStr">
+        <is>
+          <t>talking-about-feelings-building</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T1058"/>
+  <autoFilter ref="A1:T1085"/>
   <dataValidations count="2">
     <dataValidation sqref="B2:B5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"argument,assumption,bias,category,cba,common,component,compromise,criteria,criterion,definition,direction,dispute,downstream,engagement,evidence,falsify,impact,interest,interest_listing,law,long_term,media,motive,obstacle,person,prediction,related,rung,shared_interest,short_term,similar,stack,strength,topic_media,topic_values,upstream,value"</formula1>
@@ -40417,6 +41455,16 @@
           <t>social-science</t>
         </is>
       </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>How the mind works, why people feel and act as they do, and how mental health problems are understood and treated.</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>favors treating mental struggles as medical conditions best handled by professionals and treatment; negative favors seeing them as ordinary parts of life best handled through relationships, habits, and personal effort.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">

--- a/tools/static-site/ISE_Data_Entry.xlsx
+++ b/tools/static-site/ISE_Data_Entry.xlsx
@@ -13,9 +13,9 @@
     <sheet name="topics" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'pages'!$A$1:$AC$416</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'edges'!$A$1:$T$1085</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'topics'!$A$1:$F$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'pages'!$A$1:$AC$490</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'edges'!$A$1:$T$1166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'topics'!$A$1:$F$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -859,7 +859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC416"/>
+  <dimension ref="A1:AC490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -14301,8 +14301,1717 @@
         </is>
       </c>
     </row>
+    <row r="417">
+      <c r="A417" s="4" t="inlineStr">
+        <is>
+          <t>tariffs-imported-goods-generally</t>
+        </is>
+      </c>
+      <c r="C417" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D417" s="4" t="inlineStr">
+        <is>
+          <t>Tariffs on imported goods generally cost a country's consumers more than they save its workers.</t>
+        </is>
+      </c>
+      <c r="F417" s="5" t="inlineStr">
+        <is>
+          <t>trade</t>
+        </is>
+      </c>
+      <c r="W417" s="4" t="inlineStr">
+        <is>
+          <t>Whether a small cost spread across everyone is worse than a large cost concentrated on the towns and workers who lose.</t>
+        </is>
+      </c>
+      <c r="AA417" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB417" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="4" t="inlineStr">
+        <is>
+          <t>tariff-raises-price-good</t>
+        </is>
+      </c>
+      <c r="C418" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D418" s="4" t="inlineStr">
+        <is>
+          <t>A tariff raises the price of the good for every buyer in the country, while it protects only the workers in one industry.</t>
+        </is>
+      </c>
+      <c r="G418" s="4" t="inlineStr">
+        <is>
+          <t>tariffs-imported-goods-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="4" t="inlineStr">
+        <is>
+          <t>other-countries-answer-tariffs</t>
+        </is>
+      </c>
+      <c r="C419" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D419" s="4" t="inlineStr">
+        <is>
+          <t>Other countries answer tariffs with their own, so exporters in industries that were never in trouble lose their foreign customers.</t>
+        </is>
+      </c>
+      <c r="G419" s="4" t="inlineStr">
+        <is>
+          <t>tariffs-imported-goods-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="4" t="inlineStr">
+        <is>
+          <t>industries-shielded-foreign-competition</t>
+        </is>
+      </c>
+      <c r="C420" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D420" s="4" t="inlineStr">
+        <is>
+          <t>Industries shielded from foreign competition tend to stop improving, so the country ends up paying more for worse products.</t>
+        </is>
+      </c>
+      <c r="G420" s="4" t="inlineStr">
+        <is>
+          <t>tariffs-imported-goods-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="4" t="inlineStr">
+        <is>
+          <t>when-factory-closes-whole</t>
+        </is>
+      </c>
+      <c r="C421" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D421" s="4" t="inlineStr">
+        <is>
+          <t>When a factory closes, a whole town can lose its tax base, its shops and its future, and that damage is far larger than a small price increase spread across everyone.</t>
+        </is>
+      </c>
+      <c r="G421" s="4" t="inlineStr">
+        <is>
+          <t>tariffs-imported-goods-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="4" t="inlineStr">
+        <is>
+          <t>when-tariff-removed-importers</t>
+        </is>
+      </c>
+      <c r="C422" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D422" s="4" t="inlineStr">
+        <is>
+          <t>When a tariff is removed, importers and retailers often keep much of the price difference for themselves rather than passing it on, so the saving that reaches shoppers is smaller than the wages that were lost.</t>
+        </is>
+      </c>
+      <c r="G422" s="4" t="inlineStr">
+        <is>
+          <t>tariffs-imported-goods-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="4" t="inlineStr">
+        <is>
+          <t>country-lets-its-factories</t>
+        </is>
+      </c>
+      <c r="C423" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D423" s="4" t="inlineStr">
+        <is>
+          <t>A country that lets its factories die loses the skills and supply chains it would need in a war or a crisis, and no price saving is worth that.</t>
+        </is>
+      </c>
+      <c r="G423" s="4" t="inlineStr">
+        <is>
+          <t>tariffs-imported-goods-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="4" t="inlineStr">
+        <is>
+          <t>country-protect-its-key</t>
+        </is>
+      </c>
+      <c r="C424" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D424" s="4" t="inlineStr">
+        <is>
+          <t>A country should protect its key manufacturing industries with tariffs even when imports are cheaper.</t>
+        </is>
+      </c>
+      <c r="F424" s="5" t="inlineStr">
+        <is>
+          <t>trade</t>
+        </is>
+      </c>
+      <c r="W424" s="4" t="inlineStr">
+        <is>
+          <t>Whether the goods a country cannot afford to lose can be identified honestly and protected more cheaply than with a tariff.</t>
+        </is>
+      </c>
+      <c r="AA424" s="5" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AB424" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="4" t="inlineStr">
+        <is>
+          <t>country-cannot-make-its</t>
+        </is>
+      </c>
+      <c r="C425" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D425" s="4" t="inlineStr">
+        <is>
+          <t>A country that cannot make its own steel, chips or medicine is at the mercy of whoever does, and that is a matter of security rather than price.</t>
+        </is>
+      </c>
+      <c r="G425" s="4" t="inlineStr">
+        <is>
+          <t>country-protect-its-key</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="4" t="inlineStr">
+        <is>
+          <t>manufacturing-jobs-offer-steady</t>
+        </is>
+      </c>
+      <c r="C426" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D426" s="4" t="inlineStr">
+        <is>
+          <t>Manufacturing jobs offer steady middle-class pay to people without college degrees in a way that few service jobs do.</t>
+        </is>
+      </c>
+      <c r="G426" s="4" t="inlineStr">
+        <is>
+          <t>country-protect-its-key</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="4" t="inlineStr">
+        <is>
+          <t>new-industries-need-time</t>
+        </is>
+      </c>
+      <c r="C427" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D427" s="4" t="inlineStr">
+        <is>
+          <t>New industries need time to grow before they can compete with established foreign rivals, and a tariff buys that time.</t>
+        </is>
+      </c>
+      <c r="G427" s="4" t="inlineStr">
+        <is>
+          <t>country-protect-its-key</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="4" t="inlineStr">
+        <is>
+          <t>every-industry-calls-itself</t>
+        </is>
+      </c>
+      <c r="C428" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D428" s="4" t="inlineStr">
+        <is>
+          <t>Every industry calls itself key when a tariff is on offer, so protection ends up going to whoever lobbies hardest rather than to what a country truly needs.</t>
+        </is>
+      </c>
+      <c r="G428" s="4" t="inlineStr">
+        <is>
+          <t>country-protect-its-key</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="4" t="inlineStr">
+        <is>
+          <t>manufacturers-who-use-protected</t>
+        </is>
+      </c>
+      <c r="C429" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D429" s="4" t="inlineStr">
+        <is>
+          <t>Manufacturers who use the protected good as an input pay more, so protecting one industry weakens the ones that depend on it.</t>
+        </is>
+      </c>
+      <c r="G429" s="4" t="inlineStr">
+        <is>
+          <t>country-protect-its-key</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="4" t="inlineStr">
+        <is>
+          <t>country-wants-secure-supply</t>
+        </is>
+      </c>
+      <c r="C430" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D430" s="4" t="inlineStr">
+        <is>
+          <t>A country that wants secure supply can stockpile goods or fund a few plants directly, which costs far less than taxing every buyer.</t>
+        </is>
+      </c>
+      <c r="G430" s="4" t="inlineStr">
+        <is>
+          <t>country-protect-its-key</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="4" t="inlineStr">
+        <is>
+          <t>raising-minimum-wage-generally</t>
+        </is>
+      </c>
+      <c r="C431" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D431" s="4" t="inlineStr">
+        <is>
+          <t>Raising the minimum wage generally helps low-paid workers more than it hurts them.</t>
+        </is>
+      </c>
+      <c r="F431" s="5" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="W431" s="4" t="inlineStr">
+        <is>
+          <t>Whether employers respond to a higher wage floor mostly by paying more or mostly by hiring less.</t>
+        </is>
+      </c>
+      <c r="AA431" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB431" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="4" t="inlineStr">
+        <is>
+          <t>single-worker-has-almost</t>
+        </is>
+      </c>
+      <c r="C432" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D432" s="4" t="inlineStr">
+        <is>
+          <t>A single worker has almost no power to bargain with a large employer, and a wage floor gives them the bargaining position they lack.</t>
+        </is>
+      </c>
+      <c r="G432" s="4" t="inlineStr">
+        <is>
+          <t>raising-minimum-wage-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="4" t="inlineStr">
+        <is>
+          <t>low-paid-workers-spend</t>
+        </is>
+      </c>
+      <c r="C433" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D433" s="4" t="inlineStr">
+        <is>
+          <t>Low-paid workers spend nearly everything they earn, so higher wages flow straight back into local businesses.</t>
+        </is>
+      </c>
+      <c r="G433" s="4" t="inlineStr">
+        <is>
+          <t>raising-minimum-wage-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="4" t="inlineStr">
+        <is>
+          <t>when-wages-too-low</t>
+        </is>
+      </c>
+      <c r="C434" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D434" s="4" t="inlineStr">
+        <is>
+          <t>When wages are too low to live on, taxpayers end up topping them up through public benefits, which is a subsidy to low-paying employers.</t>
+        </is>
+      </c>
+      <c r="G434" s="4" t="inlineStr">
+        <is>
+          <t>raising-minimum-wage-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="4" t="inlineStr">
+        <is>
+          <t>when-labor-costs-more</t>
+        </is>
+      </c>
+      <c r="C435" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D435" s="4" t="inlineStr">
+        <is>
+          <t>When labor costs more, employers hire fewer people, cut hours or turn to machines, and the workers who lose out are the least skilled.</t>
+        </is>
+      </c>
+      <c r="G435" s="4" t="inlineStr">
+        <is>
+          <t>raising-minimum-wage-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="4" t="inlineStr">
+        <is>
+          <t>small-businesses-poorer-regions</t>
+        </is>
+      </c>
+      <c r="C436" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D436" s="4" t="inlineStr">
+        <is>
+          <t>Small businesses in poorer regions cannot pay what a big-city employer can, so one national floor destroys jobs where they are most needed.</t>
+        </is>
+      </c>
+      <c r="G436" s="4" t="inlineStr">
+        <is>
+          <t>raising-minimum-wage-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="4" t="inlineStr">
+        <is>
+          <t>many-minimum-wage-earners</t>
+        </is>
+      </c>
+      <c r="C437" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D437" s="4" t="inlineStr">
+        <is>
+          <t>Many minimum-wage earners are young people or second earners in comfortable households, so a higher minimum wage misses the poorest families it is meant to help.</t>
+        </is>
+      </c>
+      <c r="G437" s="4" t="inlineStr">
+        <is>
+          <t>raising-minimum-wage-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="4" t="inlineStr">
+        <is>
+          <t>employers-generally-free-fire</t>
+        </is>
+      </c>
+      <c r="C438" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D438" s="4" t="inlineStr">
+        <is>
+          <t>Employers should generally be free to fire workers without having to show a reason, as long as the firing is not discriminatory.</t>
+        </is>
+      </c>
+      <c r="F438" s="5" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="W438" s="4" t="inlineStr">
+        <is>
+          <t>Whether making firing easy creates more jobs than it makes worse.</t>
+        </is>
+      </c>
+      <c r="AA438" s="5" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AB438" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="4" t="inlineStr">
+        <is>
+          <t>employer-who-knows-firing</t>
+        </is>
+      </c>
+      <c r="C439" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D439" s="4" t="inlineStr">
+        <is>
+          <t>An employer who knows firing will be hard is slower to hire in the first place, so strict rules protect people who have jobs at the expense of people who want them.</t>
+        </is>
+      </c>
+      <c r="G439" s="4" t="inlineStr">
+        <is>
+          <t>employers-generally-free-fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="4" t="inlineStr">
+        <is>
+          <t>small-businesses-cannot-afford</t>
+        </is>
+      </c>
+      <c r="C440" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D440" s="4" t="inlineStr">
+        <is>
+          <t>Small businesses cannot afford the lawyers and paperwork needed to build a case for every dismissal.</t>
+        </is>
+      </c>
+      <c r="G440" s="4" t="inlineStr">
+        <is>
+          <t>employers-generally-free-fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="4" t="inlineStr">
+        <is>
+          <t>workers-can-quit-job</t>
+        </is>
+      </c>
+      <c r="C441" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D441" s="4" t="inlineStr">
+        <is>
+          <t>Workers can quit a job without giving a reason, so fairness requires that employers be able to end the same working relationship without giving one.</t>
+        </is>
+      </c>
+      <c r="G441" s="4" t="inlineStr">
+        <is>
+          <t>employers-generally-free-fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="4" t="inlineStr">
+        <is>
+          <t>losing-job-can-mean</t>
+        </is>
+      </c>
+      <c r="C442" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D442" s="4" t="inlineStr">
+        <is>
+          <t>Losing a job can mean losing a home, health coverage and a family's stability, and something that serious should require a reason.</t>
+        </is>
+      </c>
+      <c r="G442" s="4" t="inlineStr">
+        <is>
+          <t>employers-generally-free-fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="4" t="inlineStr">
+        <is>
+          <t>workers-who-can-fired</t>
+        </is>
+      </c>
+      <c r="C443" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D443" s="4" t="inlineStr">
+        <is>
+          <t>Workers who can be fired at any moment are afraid to report safety problems, harassment or fraud.</t>
+        </is>
+      </c>
+      <c r="G443" s="4" t="inlineStr">
+        <is>
+          <t>employers-generally-free-fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="4" t="inlineStr">
+        <is>
+          <t>rules-against-unfair-dismissal</t>
+        </is>
+      </c>
+      <c r="C444" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D444" s="4" t="inlineStr">
+        <is>
+          <t>Rules against unfair dismissal push employers to hire more carefully and manage better, which improves the workplace for everyone.</t>
+        </is>
+      </c>
+      <c r="G444" s="4" t="inlineStr">
+        <is>
+          <t>employers-generally-free-fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="4" t="inlineStr">
+        <is>
+          <t>internet-providers-generally-barred</t>
+        </is>
+      </c>
+      <c r="C445" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D445" s="4" t="inlineStr">
+        <is>
+          <t>Internet providers should generally be barred by law from speeding up, slowing down or charging extra for particular websites and services.</t>
+        </is>
+      </c>
+      <c r="F445" s="5" t="inlineStr">
+        <is>
+          <t>internet</t>
+        </is>
+      </c>
+      <c r="W445" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether competition and public attention are enough to keep providers honest, or whether the lack of choice in home internet makes a legal rule necessary.</t>
+        </is>
+      </c>
+      <c r="AA445" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB445" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="4" t="inlineStr">
+        <is>
+          <t>provider-can-slow-down</t>
+        </is>
+      </c>
+      <c r="C446" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D446" s="4" t="inlineStr">
+        <is>
+          <t>A provider that can slow down or charge extra for certain traffic gains a veto over which websites and services succeed, and that power belongs with users, not with the company selling the connection.</t>
+        </is>
+      </c>
+      <c r="G446" s="4" t="inlineStr">
+        <is>
+          <t>internet-providers-generally-barred</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="4" t="inlineStr">
+        <is>
+          <t>many-households-have-little</t>
+        </is>
+      </c>
+      <c r="C447" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D447" s="4" t="inlineStr">
+        <is>
+          <t>Many households have little real choice of home internet provider, so competition alone cannot punish one that plays favorites.</t>
+        </is>
+      </c>
+      <c r="G447" s="4" t="inlineStr">
+        <is>
+          <t>internet-providers-generally-barred</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="4" t="inlineStr">
+        <is>
+          <t>new-services-start-small</t>
+        </is>
+      </c>
+      <c r="C448" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D448" s="4" t="inlineStr">
+        <is>
+          <t>New services start small and cannot pay for fast lanes, so a rule of equal treatment keeps the door open for the next useful idea.</t>
+        </is>
+      </c>
+      <c r="G448" s="4" t="inlineStr">
+        <is>
+          <t>internet-providers-generally-barred</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="4" t="inlineStr">
+        <is>
+          <t>all-traffic-alike-live</t>
+        </is>
+      </c>
+      <c r="C449" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D449" s="4" t="inlineStr">
+        <is>
+          <t>Not all traffic is alike; a live video call suffers far more from delay than a file download does, and a legal ban on favoring traffic turns sensible prioritizing into a legal risk.</t>
+        </is>
+      </c>
+      <c r="G449" s="4" t="inlineStr">
+        <is>
+          <t>internet-providers-generally-barred</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="4" t="inlineStr">
+        <is>
+          <t>building-faster-networks-costs</t>
+        </is>
+      </c>
+      <c r="C450" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D450" s="4" t="inlineStr">
+        <is>
+          <t>Building faster networks costs a great deal, and letting providers charge the services that send the most traffic for faster delivery helps pay for upgrades that all users share.</t>
+        </is>
+      </c>
+      <c r="G450" s="4" t="inlineStr">
+        <is>
+          <t>internet-providers-generally-barred</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="4" t="inlineStr">
+        <is>
+          <t>providers-rarely-block-throttle</t>
+        </is>
+      </c>
+      <c r="C451" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D451" s="4" t="inlineStr">
+        <is>
+          <t>Providers rarely block or throttle in practice because customers and the press notice quickly, so the rule solves a problem that mostly does not occur.</t>
+        </is>
+      </c>
+      <c r="G451" s="4" t="inlineStr">
+        <is>
+          <t>internet-providers-generally-barred</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="4" t="inlineStr">
+        <is>
+          <t>laws-require-people-prove</t>
+        </is>
+      </c>
+      <c r="C452" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D452" s="4" t="inlineStr">
+        <is>
+          <t>Laws that require people to prove their age before using social media do more harm than good.</t>
+        </is>
+      </c>
+      <c r="F452" s="5" t="inlineStr">
+        <is>
+          <t>internet</t>
+        </is>
+      </c>
+      <c r="W452" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether the privacy and access costs of checking everyone's age outweigh the harm to children the checks are meant to prevent.</t>
+        </is>
+      </c>
+      <c r="AA452" s="5" t="n">
+        <v>-50</v>
+      </c>
+      <c r="AB452" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="4" t="inlineStr">
+        <is>
+          <t>proving-age-means-handing</t>
+        </is>
+      </c>
+      <c r="C453" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D453" s="4" t="inlineStr">
+        <is>
+          <t>Proving age means handing an ID or a face scan to a company or a middleman, which creates a new store of sensitive data that can leak or be misused.</t>
+        </is>
+      </c>
+      <c r="G453" s="4" t="inlineStr">
+        <is>
+          <t>laws-require-people-prove</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="4" t="inlineStr">
+        <is>
+          <t>teenagers-who-blocked-mainstream</t>
+        </is>
+      </c>
+      <c r="C454" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D454" s="4" t="inlineStr">
+        <is>
+          <t>Teenagers who are blocked from mainstream sites do not stop going online; they move to smaller, less moderated places where the risks are greater.</t>
+        </is>
+      </c>
+      <c r="G454" s="4" t="inlineStr">
+        <is>
+          <t>laws-require-people-prove</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="4" t="inlineStr">
+        <is>
+          <t>age-rules-set-law</t>
+        </is>
+      </c>
+      <c r="C455" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D455" s="4" t="inlineStr">
+        <is>
+          <t>Age rules set by law sweep in adults too, since everyone has to pass the same check, so a protection for minors becomes a barrier for all.</t>
+        </is>
+      </c>
+      <c r="G455" s="4" t="inlineStr">
+        <is>
+          <t>laws-require-people-prove</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="4" t="inlineStr">
+        <is>
+          <t>society-already-requires-proof</t>
+        </is>
+      </c>
+      <c r="C456" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D456" s="4" t="inlineStr">
+        <is>
+          <t>Society already requires proof of age for alcohol, gambling and driving, and there is no principled reason that products children use heavily and that are built to hold their attention should be exempt.</t>
+        </is>
+      </c>
+      <c r="G456" s="4" t="inlineStr">
+        <is>
+          <t>laws-require-people-prove</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="4" t="inlineStr">
+        <is>
+          <t>leaving-choice-parents-has</t>
+        </is>
+      </c>
+      <c r="C457" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D457" s="4" t="inlineStr">
+        <is>
+          <t>Leaving the choice to parents has not worked, because a child needs only one friend with an account to feel left out, and parents cannot supervise every hour.</t>
+        </is>
+      </c>
+      <c r="G457" s="4" t="inlineStr">
+        <is>
+          <t>laws-require-people-prove</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="4" t="inlineStr">
+        <is>
+          <t>companies-can-verify-age</t>
+        </is>
+      </c>
+      <c r="C458" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D458" s="4" t="inlineStr">
+        <is>
+          <t>Companies can verify age without keeping the underlying documents, but voluntary adoption has been patchy and inconsistent, which is why a uniform legal requirement is needed.</t>
+        </is>
+      </c>
+      <c r="G458" s="4" t="inlineStr">
+        <is>
+          <t>laws-require-people-prove</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="C459" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D459" s="4" t="inlineStr">
+        <is>
+          <t>We should support and strengthen democracy to restore the voter's voice.</t>
+        </is>
+      </c>
+      <c r="F459" s="5" t="inlineStr">
+        <is>
+          <t>democracy-and-rule-of-law</t>
+        </is>
+      </c>
+      <c r="W459" s="4" t="inlineStr">
+        <is>
+          <t>The problem diagnosis is strong: current electoral rules let unrepresentative primary electorates pick the choices, let mapmakers pick their voters, and make candidates depend on a narrow donor class. The reform mechanisms are less certain, since each specific fix (ranked-choice voting, nonpartisan primaries, commissions, donor matching) has real supporting evidence and real implementation risks, so this belief is strongest as "fix the structures, state by state, and measure" and weakest as a blanket endorsement of any one mechanism.</t>
+        </is>
+      </c>
+      <c r="AA459" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB459" s="5" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="4" t="inlineStr">
+        <is>
+          <t>partisan-primaries-let-small</t>
+        </is>
+      </c>
+      <c r="C460" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D460" s="4" t="inlineStr">
+        <is>
+          <t>Partisan primaries let a small and unrepresentative group of voters pick the choices everyone else gets in the general election.</t>
+        </is>
+      </c>
+      <c r="G460" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="4" t="inlineStr">
+        <is>
+          <t>gerrymandering-lets-legislators-choose</t>
+        </is>
+      </c>
+      <c r="C461" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D461" s="4" t="inlineStr">
+        <is>
+          <t>Gerrymandering lets legislators choose their voters instead of voters choosing their legislators.</t>
+        </is>
+      </c>
+      <c r="G461" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces</t>
+        </is>
+      </c>
+      <c r="C462" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D462" s="4" t="inlineStr">
+        <is>
+          <t>Ranked-choice voting produces winners with broader support and reduces negative campaigning.</t>
+        </is>
+      </c>
+      <c r="G462" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="4" t="inlineStr">
+        <is>
+          <t>campaign-finance-structures-make</t>
+        </is>
+      </c>
+      <c r="C463" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D463" s="4" t="inlineStr">
+        <is>
+          <t>Campaign finance structures make candidates dependent on a donor class whose interests differ from those of their constituents.</t>
+        </is>
+      </c>
+      <c r="G463" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="4" t="inlineStr">
+        <is>
+          <t>third-parties-independents-kept</t>
+        </is>
+      </c>
+      <c r="C464" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D464" s="4" t="inlineStr">
+        <is>
+          <t>Third parties and independents are kept out by structural election rules, not because they are unpopular.</t>
+        </is>
+      </c>
+      <c r="G464" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="4" t="inlineStr">
+        <is>
+          <t>specific-electoral-reforms-have</t>
+        </is>
+      </c>
+      <c r="C465" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D465" s="4" t="inlineStr">
+        <is>
+          <t>Specific electoral reforms have real implementation problems and unintended consequences.</t>
+        </is>
+      </c>
+      <c r="G465" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="4" t="inlineStr">
+        <is>
+          <t>two-party-system-has</t>
+        </is>
+      </c>
+      <c r="C466" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D466" s="4" t="inlineStr">
+        <is>
+          <t>The two-party system has stabilizing effects that alternative systems may not replicate.</t>
+        </is>
+      </c>
+      <c r="G466" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="4" t="inlineStr">
+        <is>
+          <t>restoring-voter-s-voice</t>
+        </is>
+      </c>
+      <c r="C467" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D467" s="4" t="inlineStr">
+        <is>
+          <t>Restoring the voter's voice assumes there is a single coherent will of the voters to restore, but on many issues public opinion contradicts itself.</t>
+        </is>
+      </c>
+      <c r="G467" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="4" t="inlineStr">
+        <is>
+          <t>campaign-finance-restrictions-collide</t>
+        </is>
+      </c>
+      <c r="C468" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D468" s="4" t="inlineStr">
+        <is>
+          <t>Campaign finance restrictions collide with the First Amendment's protection of political spending as speech.</t>
+        </is>
+      </c>
+      <c r="G468" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="4" t="inlineStr">
+        <is>
+          <t>nonpartisan-primaries-may-weaken</t>
+        </is>
+      </c>
+      <c r="C469" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D469" s="4" t="inlineStr">
+        <is>
+          <t>Nonpartisan primaries may weaken party accountability rather than strengthen the voter's voice.</t>
+        </is>
+      </c>
+      <c r="G469" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="4" t="inlineStr">
+        <is>
+          <t>congress-polls-15-25</t>
+        </is>
+      </c>
+      <c r="C470" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D470" s="4" t="inlineStr">
+        <is>
+          <t>Congress polls at 15 to 25 percent approval while incumbent reelection rates exceed 90 percent.</t>
+        </is>
+      </c>
+      <c r="G470" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="4" t="inlineStr">
+        <is>
+          <t>primary-voters-measure-significantly</t>
+        </is>
+      </c>
+      <c r="C471" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D471" s="4" t="inlineStr">
+        <is>
+          <t>Primary voters measure significantly more ideologically extreme than each party's general-election supporters.</t>
+        </is>
+      </c>
+      <c r="G471" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="4" t="inlineStr">
+        <is>
+          <t>americans-identifying-independents-reached</t>
+        </is>
+      </c>
+      <c r="C472" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D472" s="4" t="inlineStr">
+        <is>
+          <t>Americans identifying as independents reached 43 percent, more than either party, while remaining excluded from most primaries.</t>
+        </is>
+      </c>
+      <c r="G472" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="4" t="inlineStr">
+        <is>
+          <t>alaska-s-first-federal</t>
+        </is>
+      </c>
+      <c r="C473" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D473" s="4" t="inlineStr">
+        <is>
+          <t>Alaska's first federal ranked-choice election showed none of the predicted voter confusion and had normal ballot-completion rates.</t>
+        </is>
+      </c>
+      <c r="G473" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="4" t="inlineStr">
+        <is>
+          <t>independent-redistricting-commissions-arizona</t>
+        </is>
+      </c>
+      <c r="C474" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D474" s="4" t="inlineStr">
+        <is>
+          <t>Independent redistricting commissions in Arizona and California reduced safe seats by 15 to 20 percent compared with maps drawn by legislatures.</t>
+        </is>
+      </c>
+      <c r="G474" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="4" t="inlineStr">
+        <is>
+          <t>policy-outcomes-correlate-preferences</t>
+        </is>
+      </c>
+      <c r="C475" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D475" s="4" t="inlineStr">
+        <is>
+          <t>Policy outcomes correlate with the preferences of economic elites at far higher rates than with the preferences of the median voter.</t>
+        </is>
+      </c>
+      <c r="G475" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="4" t="inlineStr">
+        <is>
+          <t>burlington-vermont-adopted-ranked</t>
+        </is>
+      </c>
+      <c r="C476" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D476" s="4" t="inlineStr">
+        <is>
+          <t>Burlington, Vermont adopted ranked-choice voting and then repealed it after the candidate with the most first-choice votes lost, though scholars dispute whether the result was actually unfair under the rules.</t>
+        </is>
+      </c>
+      <c r="G476" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="4" t="inlineStr">
+        <is>
+          <t>evidence-whether-nonpartisan-primaries</t>
+        </is>
+      </c>
+      <c r="C477" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D477" s="4" t="inlineStr">
+        <is>
+          <t>The evidence on whether nonpartisan primaries actually moderate candidates is mixed.</t>
+        </is>
+      </c>
+      <c r="G477" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="4" t="inlineStr">
+        <is>
+          <t>independent-voters-about-43</t>
+        </is>
+      </c>
+      <c r="C478" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D478" s="4" t="inlineStr">
+        <is>
+          <t>Independent voters, about 43 percent of Americans, need a meaningful vote because they are locked out of primaries.</t>
+        </is>
+      </c>
+      <c r="M478" s="5" t="inlineStr">
+        <is>
+          <t>Political equality</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="4" t="inlineStr">
+        <is>
+          <t>voters-need-representatives-who</t>
+        </is>
+      </c>
+      <c r="C479" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D479" s="4" t="inlineStr">
+        <is>
+          <t>Voters need representatives who solve problems rather than perform for their base audiences.</t>
+        </is>
+      </c>
+      <c r="M479" s="5" t="inlineStr">
+        <is>
+          <t>Accountability</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="4" t="inlineStr">
+        <is>
+          <t>forward-party-other-third</t>
+        </is>
+      </c>
+      <c r="C480" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D480" s="4" t="inlineStr">
+        <is>
+          <t>The Forward Party and other third parties need open primaries and ranked-choice rules because they benefit directly from them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="4" t="inlineStr">
+        <is>
+          <t>opponents-need-governmental-stability</t>
+        </is>
+      </c>
+      <c r="C481" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D481" s="4" t="inlineStr">
+        <is>
+          <t>Opponents need governmental stability and coherent governing coalitions.</t>
+        </is>
+      </c>
+      <c r="M481" s="5" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="4" t="inlineStr">
+        <is>
+          <t>voters-need-simple-ballots</t>
+        </is>
+      </c>
+      <c r="C482" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D482" s="4" t="inlineStr">
+        <is>
+          <t>Voters need simple ballots and elections they can understand.</t>
+        </is>
+      </c>
+      <c r="M482" s="5" t="inlineStr">
+        <is>
+          <t>Participation</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="4" t="inlineStr">
+        <is>
+          <t>incumbents-major-party-organizations</t>
+        </is>
+      </c>
+      <c r="C483" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D483" s="4" t="inlineStr">
+        <is>
+          <t>Incumbents and major-party organizations need to protect the rules that protect them, and donors need to protect their channel of influence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="4" t="inlineStr">
+        <is>
+          <t>decade-data-alaska-maine</t>
+        </is>
+      </c>
+      <c r="C484" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D484" s="4" t="inlineStr">
+        <is>
+          <t>A decade of data from Alaska and Maine will show that reformed states elect measurably more median-aligned representatives and that their approval-to-reelection gap narrows compared with matched unreformed states.</t>
+        </is>
+      </c>
+      <c r="G484" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="4" t="inlineStr">
+        <is>
+          <t>legislators-jurisdictions-small-donor</t>
+        </is>
+      </c>
+      <c r="C485" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D485" s="4" t="inlineStr">
+        <is>
+          <t>Legislators in jurisdictions with small-donor matching will track constituent preferences better than legislators in jurisdictions without it.</t>
+        </is>
+      </c>
+      <c r="G485" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="4" t="inlineStr">
+        <is>
+          <t>commission-drawn-maps-will</t>
+        </is>
+      </c>
+      <c r="C486" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D486" s="4" t="inlineStr">
+        <is>
+          <t>Commission-drawn maps will keep producing 15 to 20 percent fewer safe seats than maps drawn by legislatures, cycle after cycle.</t>
+        </is>
+      </c>
+      <c r="G486" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="4" t="inlineStr">
+        <is>
+          <t>jurisdictions-use-ranked-choice</t>
+        </is>
+      </c>
+      <c r="C487" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D487" s="4" t="inlineStr">
+        <is>
+          <t>Jurisdictions that use ranked-choice voting will show persistently lower rates of negative advertising.</t>
+        </is>
+      </c>
+      <c r="G487" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="4" t="inlineStr">
+        <is>
+          <t>reformed-states-will-show</t>
+        </is>
+      </c>
+      <c r="C488" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D488" s="4" t="inlineStr">
+        <is>
+          <t>Reformed states will show no movement on any objective criterion after two full election cycles, or repeal waves will spread beyond single incidents like Burlington.</t>
+        </is>
+      </c>
+      <c r="G488" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="4" t="inlineStr">
+        <is>
+          <t>center-squeeze-other-pathological</t>
+        </is>
+      </c>
+      <c r="C489" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D489" s="4" t="inlineStr">
+        <is>
+          <t>Center-squeeze or other pathological outcomes will recur in ranked-choice elections at rates that measurably erode public trust in results.</t>
+        </is>
+      </c>
+      <c r="G489" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="4" t="inlineStr">
+        <is>
+          <t>representatives-reformed-states-will</t>
+        </is>
+      </c>
+      <c r="C490" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D490" s="4" t="inlineStr">
+        <is>
+          <t>Representatives in reformed states will move toward their district medians no faster than representatives in unreformed states.</t>
+        </is>
+      </c>
+      <c r="G490" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC416"/>
+  <autoFilter ref="A1:AC490"/>
   <dataValidations count="5">
     <dataValidation sqref="C2:C5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"belief,claim,linkage,importance,interest,uniqueness,equivalence,driver,media"</formula1>
@@ -14331,7 +16040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1085"/>
+  <dimension ref="A1:T1166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -40048,8 +41757,1825 @@
         </is>
       </c>
     </row>
+    <row r="1086">
+      <c r="A1086" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1086" s="5" t="inlineStr">
+        <is>
+          <t>criteria</t>
+        </is>
+      </c>
+      <c r="E1086" s="4" t="inlineStr">
+        <is>
+          <t>Abnormal returns on officials' trades placed before government announcements</t>
+        </is>
+      </c>
+      <c r="T1086" s="4" t="inlineStr">
+        <is>
+          <t>reading: percentage points per year by which officials' portfolios beat or trail a market benchmark, with a separate figure for trades placed shortly before a legislative or regulatory event | validity: Med | reliability: High | linkage: Med | importance: Med | why: Returns are computed from public filings and market prices, so different researchers can reproduce the figure, but the brief's own findings point in opposite directions over different decades, and the linkage dispute asks whether portfolio performance bears on whether ownership creates a voting conflict at all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1087" s="5" t="inlineStr">
+        <is>
+          <t>criteria</t>
+        </is>
+      </c>
+      <c r="E1087" s="4" t="inlineStr">
+        <is>
+          <t>Share of an official's income sources, debts and foreign ties visible in public filings</t>
+        </is>
+      </c>
+      <c r="T1087" s="4" t="inlineStr">
+        <is>
+          <t>reading: percent of an official's income streams, lenders and foreign income lines that appear in the public record, found by comparing a published tax return against the same official's disclosure form | validity: High | reliability: Med | linkage: High | importance: High | why: It captures exactly what the disclosure-versus-publication argument is about, and the brief says the 2022 release makes a line-by-line comparison possible, but counting what is visible depends on how finely an observer splits income sources and how they treat value ranges against exact figures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1088" s="5" t="inlineStr">
+        <is>
+          <t>criteria</t>
+        </is>
+      </c>
+      <c r="E1088" s="4" t="inlineStr">
+        <is>
+          <t>Whether a restriction reaches only the official or also family members who hold no office</t>
+        </is>
+      </c>
+      <c r="T1088" s="4" t="inlineStr">
+        <is>
+          <t>reading: count of people bound by a rule who hold no office (spouses, dependent children, business partners), per rule, and whether the rule reaches them by name or leaves them uncovered | validity: High | reliability: High | linkage: High | importance: High | why: Both sides accept this as the honest test of the anti side's central complaint and of the agree side's substitution worry, since a rule that stops at the official leaves the conflict in spouse accounts and partnerships while a rule that reaches the family binds people who never ran, and reading it requires only the text of the rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1089" s="5" t="inlineStr">
+        <is>
+          <t>criteria</t>
+        </is>
+      </c>
+      <c r="E1089" s="4" t="inlineStr">
+        <is>
+          <t>Net worth distribution of candidates and of incoming members before and after a rule takes effect</t>
+        </is>
+      </c>
+      <c r="T1089" s="4" t="inlineStr">
+        <is>
+          <t>reading: median net worth of incoming members and the share whose wealth is in the top 1 percent, from disclosure filings, compared across the cohorts before and after a rule takes effect | validity: Med | reliability: High | linkage: Med | importance: High | why: Disclosure filings give a reproducible figure and it is the yardstick behind the anti side's strongest interest, but candidate wealth moves for many reasons besides ethics rules, so a shift after a rule is suggestive rather than proof that the rule deterred people of ordinary means.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1090" s="5" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="E1090" s="4" t="inlineStr">
+        <is>
+          <t>Official Stock Holdings and Trading Rules</t>
+        </is>
+      </c>
+      <c r="O1090" s="4" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1091" s="5" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="E1091" s="4" t="inlineStr">
+        <is>
+          <t>Family Appointments to Official Roles</t>
+        </is>
+      </c>
+      <c r="O1091" s="4" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1092" s="5" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="E1092" s="4" t="inlineStr">
+        <is>
+          <t>Publication of Officeholders' Tax Returns</t>
+        </is>
+      </c>
+      <c r="O1092" s="4" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" s="4" t="inlineStr">
+        <is>
+          <t>tariffs-imported-goods-generally</t>
+        </is>
+      </c>
+      <c r="B1093" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1093" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1093" s="4" t="inlineStr">
+        <is>
+          <t>tariff-raises-price-good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" s="4" t="inlineStr">
+        <is>
+          <t>tariffs-imported-goods-generally</t>
+        </is>
+      </c>
+      <c r="B1094" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1094" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1094" s="4" t="inlineStr">
+        <is>
+          <t>other-countries-answer-tariffs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" s="4" t="inlineStr">
+        <is>
+          <t>tariffs-imported-goods-generally</t>
+        </is>
+      </c>
+      <c r="B1095" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1095" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1095" s="4" t="inlineStr">
+        <is>
+          <t>industries-shielded-foreign-competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" s="4" t="inlineStr">
+        <is>
+          <t>tariffs-imported-goods-generally</t>
+        </is>
+      </c>
+      <c r="B1096" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1096" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1096" s="4" t="inlineStr">
+        <is>
+          <t>when-factory-closes-whole</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" s="4" t="inlineStr">
+        <is>
+          <t>tariffs-imported-goods-generally</t>
+        </is>
+      </c>
+      <c r="B1097" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1097" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1097" s="4" t="inlineStr">
+        <is>
+          <t>when-tariff-removed-importers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" s="4" t="inlineStr">
+        <is>
+          <t>tariffs-imported-goods-generally</t>
+        </is>
+      </c>
+      <c r="B1098" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1098" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1098" s="4" t="inlineStr">
+        <is>
+          <t>country-lets-its-factories</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" s="4" t="inlineStr">
+        <is>
+          <t>country-protect-its-key</t>
+        </is>
+      </c>
+      <c r="B1099" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1099" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1099" s="4" t="inlineStr">
+        <is>
+          <t>country-cannot-make-its</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" s="4" t="inlineStr">
+        <is>
+          <t>country-protect-its-key</t>
+        </is>
+      </c>
+      <c r="B1100" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1100" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1100" s="4" t="inlineStr">
+        <is>
+          <t>manufacturing-jobs-offer-steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" s="4" t="inlineStr">
+        <is>
+          <t>country-protect-its-key</t>
+        </is>
+      </c>
+      <c r="B1101" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1101" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1101" s="4" t="inlineStr">
+        <is>
+          <t>new-industries-need-time</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" s="4" t="inlineStr">
+        <is>
+          <t>country-protect-its-key</t>
+        </is>
+      </c>
+      <c r="B1102" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1102" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1102" s="4" t="inlineStr">
+        <is>
+          <t>every-industry-calls-itself</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" s="4" t="inlineStr">
+        <is>
+          <t>country-protect-its-key</t>
+        </is>
+      </c>
+      <c r="B1103" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1103" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1103" s="4" t="inlineStr">
+        <is>
+          <t>manufacturers-who-use-protected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" s="4" t="inlineStr">
+        <is>
+          <t>country-protect-its-key</t>
+        </is>
+      </c>
+      <c r="B1104" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1104" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1104" s="4" t="inlineStr">
+        <is>
+          <t>country-wants-secure-supply</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" s="4" t="inlineStr">
+        <is>
+          <t>raising-minimum-wage-generally</t>
+        </is>
+      </c>
+      <c r="B1105" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1105" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1105" s="4" t="inlineStr">
+        <is>
+          <t>single-worker-has-almost</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" s="4" t="inlineStr">
+        <is>
+          <t>raising-minimum-wage-generally</t>
+        </is>
+      </c>
+      <c r="B1106" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1106" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1106" s="4" t="inlineStr">
+        <is>
+          <t>low-paid-workers-spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" s="4" t="inlineStr">
+        <is>
+          <t>raising-minimum-wage-generally</t>
+        </is>
+      </c>
+      <c r="B1107" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1107" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1107" s="4" t="inlineStr">
+        <is>
+          <t>when-wages-too-low</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" s="4" t="inlineStr">
+        <is>
+          <t>raising-minimum-wage-generally</t>
+        </is>
+      </c>
+      <c r="B1108" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1108" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1108" s="4" t="inlineStr">
+        <is>
+          <t>when-labor-costs-more</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" s="4" t="inlineStr">
+        <is>
+          <t>raising-minimum-wage-generally</t>
+        </is>
+      </c>
+      <c r="B1109" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1109" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1109" s="4" t="inlineStr">
+        <is>
+          <t>small-businesses-poorer-regions</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" s="4" t="inlineStr">
+        <is>
+          <t>raising-minimum-wage-generally</t>
+        </is>
+      </c>
+      <c r="B1110" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1110" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1110" s="4" t="inlineStr">
+        <is>
+          <t>many-minimum-wage-earners</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" s="4" t="inlineStr">
+        <is>
+          <t>employers-generally-free-fire</t>
+        </is>
+      </c>
+      <c r="B1111" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1111" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1111" s="4" t="inlineStr">
+        <is>
+          <t>employer-who-knows-firing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" s="4" t="inlineStr">
+        <is>
+          <t>employers-generally-free-fire</t>
+        </is>
+      </c>
+      <c r="B1112" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1112" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1112" s="4" t="inlineStr">
+        <is>
+          <t>small-businesses-cannot-afford</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" s="4" t="inlineStr">
+        <is>
+          <t>employers-generally-free-fire</t>
+        </is>
+      </c>
+      <c r="B1113" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1113" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1113" s="4" t="inlineStr">
+        <is>
+          <t>workers-can-quit-job</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" s="4" t="inlineStr">
+        <is>
+          <t>employers-generally-free-fire</t>
+        </is>
+      </c>
+      <c r="B1114" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1114" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1114" s="4" t="inlineStr">
+        <is>
+          <t>losing-job-can-mean</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" s="4" t="inlineStr">
+        <is>
+          <t>employers-generally-free-fire</t>
+        </is>
+      </c>
+      <c r="B1115" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1115" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1115" s="4" t="inlineStr">
+        <is>
+          <t>workers-who-can-fired</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" s="4" t="inlineStr">
+        <is>
+          <t>employers-generally-free-fire</t>
+        </is>
+      </c>
+      <c r="B1116" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1116" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1116" s="4" t="inlineStr">
+        <is>
+          <t>rules-against-unfair-dismissal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" s="4" t="inlineStr">
+        <is>
+          <t>internet-providers-generally-barred</t>
+        </is>
+      </c>
+      <c r="B1117" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1117" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1117" s="4" t="inlineStr">
+        <is>
+          <t>provider-can-slow-down</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" s="4" t="inlineStr">
+        <is>
+          <t>internet-providers-generally-barred</t>
+        </is>
+      </c>
+      <c r="B1118" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1118" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1118" s="4" t="inlineStr">
+        <is>
+          <t>many-households-have-little</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" s="4" t="inlineStr">
+        <is>
+          <t>internet-providers-generally-barred</t>
+        </is>
+      </c>
+      <c r="B1119" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1119" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1119" s="4" t="inlineStr">
+        <is>
+          <t>new-services-start-small</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" s="4" t="inlineStr">
+        <is>
+          <t>internet-providers-generally-barred</t>
+        </is>
+      </c>
+      <c r="B1120" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1120" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1120" s="4" t="inlineStr">
+        <is>
+          <t>all-traffic-alike-live</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" s="4" t="inlineStr">
+        <is>
+          <t>internet-providers-generally-barred</t>
+        </is>
+      </c>
+      <c r="B1121" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1121" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1121" s="4" t="inlineStr">
+        <is>
+          <t>building-faster-networks-costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" s="4" t="inlineStr">
+        <is>
+          <t>internet-providers-generally-barred</t>
+        </is>
+      </c>
+      <c r="B1122" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1122" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1122" s="4" t="inlineStr">
+        <is>
+          <t>providers-rarely-block-throttle</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" s="4" t="inlineStr">
+        <is>
+          <t>laws-require-people-prove</t>
+        </is>
+      </c>
+      <c r="B1123" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1123" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1123" s="4" t="inlineStr">
+        <is>
+          <t>proving-age-means-handing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" s="4" t="inlineStr">
+        <is>
+          <t>laws-require-people-prove</t>
+        </is>
+      </c>
+      <c r="B1124" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1124" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1124" s="4" t="inlineStr">
+        <is>
+          <t>teenagers-who-blocked-mainstream</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" s="4" t="inlineStr">
+        <is>
+          <t>laws-require-people-prove</t>
+        </is>
+      </c>
+      <c r="B1125" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1125" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1125" s="4" t="inlineStr">
+        <is>
+          <t>age-rules-set-law</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" s="4" t="inlineStr">
+        <is>
+          <t>laws-require-people-prove</t>
+        </is>
+      </c>
+      <c r="B1126" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1126" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1126" s="4" t="inlineStr">
+        <is>
+          <t>society-already-requires-proof</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" s="4" t="inlineStr">
+        <is>
+          <t>laws-require-people-prove</t>
+        </is>
+      </c>
+      <c r="B1127" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1127" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1127" s="4" t="inlineStr">
+        <is>
+          <t>leaving-choice-parents-has</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" s="4" t="inlineStr">
+        <is>
+          <t>laws-require-people-prove</t>
+        </is>
+      </c>
+      <c r="B1128" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1128" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1128" s="4" t="inlineStr">
+        <is>
+          <t>companies-can-verify-age</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1129" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1129" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1129" s="4" t="inlineStr">
+        <is>
+          <t>partisan-primaries-let-small</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1130" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1130" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1130" s="4" t="inlineStr">
+        <is>
+          <t>gerrymandering-lets-legislators-choose</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1131" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1131" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1131" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1132" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1132" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1132" s="4" t="inlineStr">
+        <is>
+          <t>campaign-finance-structures-make</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1133" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1133" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1133" s="4" t="inlineStr">
+        <is>
+          <t>third-parties-independents-kept</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1134" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1134" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1134" s="4" t="inlineStr">
+        <is>
+          <t>specific-electoral-reforms-have</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1135" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1135" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1135" s="4" t="inlineStr">
+        <is>
+          <t>two-party-system-has</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1136" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1136" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1136" s="4" t="inlineStr">
+        <is>
+          <t>restoring-voter-s-voice</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1137" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1137" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1137" s="4" t="inlineStr">
+        <is>
+          <t>campaign-finance-restrictions-collide</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1138" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1138" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1138" s="4" t="inlineStr">
+        <is>
+          <t>nonpartisan-primaries-may-weaken</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1139" s="5" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="C1139" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1139" s="4" t="inlineStr">
+        <is>
+          <t>congress-polls-15-25</t>
+        </is>
+      </c>
+      <c r="F1139" s="4" t="inlineStr">
+        <is>
+          <t>Gallup; OpenSecrets, ongoing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1140" s="5" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="C1140" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1140" s="4" t="inlineStr">
+        <is>
+          <t>primary-voters-measure-significantly</t>
+        </is>
+      </c>
+      <c r="F1140" s="4" t="inlineStr">
+        <is>
+          <t>Pew Research, 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1141" s="5" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="C1141" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1141" s="4" t="inlineStr">
+        <is>
+          <t>americans-identifying-independents-reached</t>
+        </is>
+      </c>
+      <c r="F1141" s="4" t="inlineStr">
+        <is>
+          <t>Gallup, 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1142" s="5" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="C1142" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1142" s="4" t="inlineStr">
+        <is>
+          <t>alaska-s-first-federal</t>
+        </is>
+      </c>
+      <c r="F1142" s="4" t="inlineStr">
+        <is>
+          <t>MIT Election Lab, 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1143" s="5" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="C1143" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1143" s="4" t="inlineStr">
+        <is>
+          <t>independent-redistricting-commissions-arizona</t>
+        </is>
+      </c>
+      <c r="F1143" s="4" t="inlineStr">
+        <is>
+          <t>NCSL, 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1144" s="5" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="C1144" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1144" s="4" t="inlineStr">
+        <is>
+          <t>policy-outcomes-correlate-preferences</t>
+        </is>
+      </c>
+      <c r="F1144" s="4" t="inlineStr">
+        <is>
+          <t>Gilens &amp; Page, Princeton, 2014</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1145" s="5" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="C1145" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1145" s="4" t="inlineStr">
+        <is>
+          <t>burlington-vermont-adopted-ranked</t>
+        </is>
+      </c>
+      <c r="F1145" s="4" t="inlineStr">
+        <is>
+          <t>Burlington city records, 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1146" s="5" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="C1146" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1146" s="4" t="inlineStr">
+        <is>
+          <t>evidence-whether-nonpartisan-primaries</t>
+        </is>
+      </c>
+      <c r="F1146" s="4" t="inlineStr">
+        <is>
+          <t>NBER working paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1147" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1147" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1147" s="4" t="inlineStr">
+        <is>
+          <t>independent-voters-about-43</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1148" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1148" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1148" s="4" t="inlineStr">
+        <is>
+          <t>voters-need-representatives-who</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1149" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1149" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1149" s="4" t="inlineStr">
+        <is>
+          <t>forward-party-other-third</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1150" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1150" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1150" s="4" t="inlineStr">
+        <is>
+          <t>opponents-need-governmental-stability</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1151" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1151" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1151" s="4" t="inlineStr">
+        <is>
+          <t>voters-need-simple-ballots</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1152" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1152" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1152" s="4" t="inlineStr">
+        <is>
+          <t>incumbents-major-party-organizations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1153" s="5" t="inlineStr">
+        <is>
+          <t>shared_interest</t>
+        </is>
+      </c>
+      <c r="E1153" s="4" t="inlineStr">
+        <is>
+          <t>Both sides want elections that produce winners most voters can accept as legitimate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1154" s="5" t="inlineStr">
+        <is>
+          <t>shared_interest</t>
+        </is>
+      </c>
+      <c r="E1154" s="4" t="inlineStr">
+        <is>
+          <t>Both sides want less political violence and less democratic backsliding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1155" s="5" t="inlineStr">
+        <is>
+          <t>shared_interest</t>
+        </is>
+      </c>
+      <c r="E1155" s="4" t="inlineStr">
+        <is>
+          <t>Both sides want a political system the next generation wants to join.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1156" s="5" t="inlineStr">
+        <is>
+          <t>compromise</t>
+        </is>
+      </c>
+      <c r="E1156" s="4" t="inlineStr">
+        <is>
+          <t>Try reforms at the state level first, and evaluate the Alaska and Maine experiments against the objective criteria before any federal mandate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1157" s="5" t="inlineStr">
+        <is>
+          <t>compromise</t>
+        </is>
+      </c>
+      <c r="E1157" s="4" t="inlineStr">
+        <is>
+          <t>Adopt open primaries without full ranked-choice voting as the first step, so independents can vote while the ballot format stays familiar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1158" s="5" t="inlineStr">
+        <is>
+          <t>compromise</t>
+        </is>
+      </c>
+      <c r="E1158" s="4" t="inlineStr">
+        <is>
+          <t>Use bipartisan redistricting commissions with neutral tiebreakers, on the Colorado model, which both parties have accepted as legitimate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1159" s="5" t="inlineStr">
+        <is>
+          <t>compromise</t>
+        </is>
+      </c>
+      <c r="E1159" s="4" t="inlineStr">
+        <is>
+          <t>Use small-donor matching, like New York City's 8-to-1 model, which amplifies constituent speech rather than restricting anyone's and so avoids the Citizens United problem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1160" s="5" t="inlineStr">
+        <is>
+          <t>prediction</t>
+        </is>
+      </c>
+      <c r="C1160" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1160" s="4" t="inlineStr">
+        <is>
+          <t>decade-data-alaska-maine</t>
+        </is>
+      </c>
+      <c r="S1160" s="4" t="inlineStr">
+        <is>
+          <t>A decade of Alaska and Maine data</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1161" s="5" t="inlineStr">
+        <is>
+          <t>prediction</t>
+        </is>
+      </c>
+      <c r="C1161" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1161" s="4" t="inlineStr">
+        <is>
+          <t>legislators-jurisdictions-small-donor</t>
+        </is>
+      </c>
+      <c r="S1161" s="4" t="inlineStr">
+        <is>
+          <t>Roll-call alignment studies</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1162" s="5" t="inlineStr">
+        <is>
+          <t>prediction</t>
+        </is>
+      </c>
+      <c r="C1162" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1162" s="4" t="inlineStr">
+        <is>
+          <t>commission-drawn-maps-will</t>
+        </is>
+      </c>
+      <c r="S1162" s="4" t="inlineStr">
+        <is>
+          <t>Each redistricting cycle; Cook ratings, NCSL tracking</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1163" s="5" t="inlineStr">
+        <is>
+          <t>prediction</t>
+        </is>
+      </c>
+      <c r="C1163" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1163" s="4" t="inlineStr">
+        <is>
+          <t>jurisdictions-use-ranked-choice</t>
+        </is>
+      </c>
+      <c r="S1163" s="4" t="inlineStr">
+        <is>
+          <t>Ongoing; ad-tone tracking, FairVote and independent replication</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1164" s="5" t="inlineStr">
+        <is>
+          <t>prediction</t>
+        </is>
+      </c>
+      <c r="C1164" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1164" s="4" t="inlineStr">
+        <is>
+          <t>reformed-states-will-show</t>
+        </is>
+      </c>
+      <c r="S1164" s="4" t="inlineStr">
+        <is>
+          <t>Two full election cycles</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1165" s="5" t="inlineStr">
+        <is>
+          <t>prediction</t>
+        </is>
+      </c>
+      <c r="C1165" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1165" s="4" t="inlineStr">
+        <is>
+          <t>center-squeeze-other-pathological</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" s="4" t="inlineStr">
+        <is>
+          <t>we-support-strengthen-democracy</t>
+        </is>
+      </c>
+      <c r="B1166" s="5" t="inlineStr">
+        <is>
+          <t>prediction</t>
+        </is>
+      </c>
+      <c r="C1166" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1166" s="4" t="inlineStr">
+        <is>
+          <t>representatives-reformed-states-will</t>
+        </is>
+      </c>
+      <c r="S1166" s="4" t="inlineStr">
+        <is>
+          <t>5-10 years; roll-call ideal-point estimates by state cohort</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T1085"/>
+  <autoFilter ref="A1:T1166"/>
   <dataValidations count="2">
     <dataValidation sqref="B2:B5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"argument,assumption,bias,category,cba,common,component,compromise,criteria,criterion,definition,direction,dispute,downstream,engagement,evidence,falsify,impact,interest,interest_listing,law,long_term,media,motive,obstacle,person,prediction,related,rung,shared_interest,short_term,similar,stack,strength,topic_media,topic_values,upstream,value"</formula1>
@@ -40069,7 +43595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -40243,6 +43769,16 @@
           <t>business-and-economy</t>
         </is>
       </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Trade covers the buying and selling of goods and services across national borders and the barriers governments place on it.</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>favors open trade with few barriers, negative favors tariffs and protection for home industries.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -40260,6 +43796,16 @@
           <t>business-and-economy</t>
         </is>
       </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Jobs covers pay, hiring, firing and working conditions, and how much of that the law should set.</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>favors stronger legal protections and pay floors for workers, negative favors leaving pay and conditions to employers and the market.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -40311,6 +43857,16 @@
           <t>computers-and-internet</t>
         </is>
       </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>How the internet is run and who sets its rules, from the companies that carry traffic to the laws that govern access, speech and content.</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>favors more government rules for how the internet and online platforms operate; negative favors leaving those choices to companies and users.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -41568,8 +45124,140 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>core-principles</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>Core Principles</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>society-and-culture</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>The principles the other positions on this site are argued from.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>democracy-and-rule-of-law</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Democracy &amp; Rule of Law</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>government</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>How elections, courts and the constitution keep power answerable, and how to strengthen them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>rights-and-liberty</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>Rights &amp; Liberty</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>government</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>The freedoms the law protects and the responsibilities that come with them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>evidence-and-process</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>Evidence &amp; Process</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>government</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>How public decisions should be made: on evidence, with scorecards, and with a view to the wider world.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>energy</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>business-and-economy</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>How energy is produced, priced and researched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>immigration</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>Immigration</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>government</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>Who may come to the country, on what terms, and how the rules are enforced.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F79"/>
+  <autoFilter ref="A1:F85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>

--- a/tools/static-site/ISE_Data_Entry.xlsx
+++ b/tools/static-site/ISE_Data_Entry.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'pages'!$A$1:$AC$490</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'edges'!$A$1:$T$1166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'edges'!$A$1:$T$1182</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'topics'!$A$1:$F$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16040,7 +16040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1166"/>
+  <dimension ref="A1:T1182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -43574,8 +43574,395 @@
         </is>
       </c>
     </row>
+    <row r="1167">
+      <c r="A1167" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1167" s="5" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="E1167" s="4" t="inlineStr">
+        <is>
+          <t>Congressional Reversal of Pardons</t>
+        </is>
+      </c>
+      <c r="O1167" s="4" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1168" s="5" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="E1168" s="4" t="inlineStr">
+        <is>
+          <t>Bribery Statutes</t>
+        </is>
+      </c>
+      <c r="O1168" s="4" t="inlineStr">
+        <is>
+          <t>sibling</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1169" s="5" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="E1169" s="4" t="inlineStr">
+        <is>
+          <t>Lobbying Rules</t>
+        </is>
+      </c>
+      <c r="O1169" s="4" t="inlineStr">
+        <is>
+          <t>sibling</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1170" s="5" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="E1170" s="4" t="inlineStr">
+        <is>
+          <t>Financial Disclosure Rules</t>
+        </is>
+      </c>
+      <c r="O1170" s="4" t="inlineStr">
+        <is>
+          <t>sibling</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1171" s="5" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="E1171" s="4" t="inlineStr">
+        <is>
+          <t>Revolving Door Restrictions</t>
+        </is>
+      </c>
+      <c r="O1171" s="4" t="inlineStr">
+        <is>
+          <t>sibling</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1172" s="5" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="E1172" s="4" t="inlineStr">
+        <is>
+          <t>Ethics Rules as a Deterrent to Public Service</t>
+        </is>
+      </c>
+      <c r="O1172" s="4" t="inlineStr">
+        <is>
+          <t>opposing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1173" s="5" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="E1173" s="4" t="inlineStr">
+        <is>
+          <t>Disclosure Rather Than Prohibition</t>
+        </is>
+      </c>
+      <c r="O1173" s="4" t="inlineStr">
+        <is>
+          <t>opposing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1174" s="5" t="inlineStr">
+        <is>
+          <t>topic_media</t>
+        </is>
+      </c>
+      <c r="D1174" s="4" t="inlineStr">
+        <is>
+          <t>ziobrowski-cheng-boyd-ziobrowski</t>
+        </is>
+      </c>
+      <c r="T1174" s="4" t="inlineStr">
+        <is>
+          <t>medium: Study | tone: Academic | positivity: +60 | strength: 80 | insight: Senators earned abnormal returns on their stock purchases in the 1990s, which points to a trading advantage tied to the office.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1175" s="5" t="inlineStr">
+        <is>
+          <t>topic_media</t>
+        </is>
+      </c>
+      <c r="D1175" s="4" t="inlineStr">
+        <is>
+          <t>eggers-hainmueller-capitol-losses</t>
+        </is>
+      </c>
+      <c r="T1175" s="4" t="inlineStr">
+        <is>
+          <t>medium: Study | tone: Academic | positivity: -50 | strength: 80 | insight: Congressional portfolios did not beat the market, which is hard to square with a systematic insider advantage for a ban to remove.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1176" s="5" t="inlineStr">
+        <is>
+          <t>strength</t>
+        </is>
+      </c>
+      <c r="C1176" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="E1176" s="4" t="inlineStr">
+        <is>
+          <t>Some new rules on what officeholders may own or trade tend to deter capable people of ordinary means from serving while catching few conflicts the disclosure form did not already show.</t>
+        </is>
+      </c>
+      <c r="O1176" s="4" t="inlineStr">
+        <is>
+          <t>Modest</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1177" s="5" t="inlineStr">
+        <is>
+          <t>strength</t>
+        </is>
+      </c>
+      <c r="C1177" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1177" s="4" t="inlineStr">
+        <is>
+          <t>forced-divestiture-imposes-real</t>
+        </is>
+      </c>
+      <c r="O1177" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1178" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C1178" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1178" s="4" t="inlineStr">
+        <is>
+          <t>members-keep-property-rights</t>
+        </is>
+      </c>
+      <c r="O1178" s="4" t="inlineStr">
+        <is>
+          <t>A.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1179" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C1179" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="E1179" s="4" t="inlineStr">
+        <is>
+          <t>When the mandatory audit of a president's returns goes dormant, the fix is to hold the IRS to that audit on a deadline and report when it is completed, not to publish the president's tax return.</t>
+        </is>
+      </c>
+      <c r="O1179" s="4" t="inlineStr">
+        <is>
+          <t>C.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1180" s="5" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="C1180" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="E1180" s="4" t="inlineStr">
+        <is>
+          <t>When a spouse's or business partner's money appears on an officeholder's tax return, it is part of the financial entanglement voters need to see, so publishing it is a privacy cost worth paying rather than a reason to keep the return private.</t>
+        </is>
+      </c>
+      <c r="O1180" s="4" t="inlineStr">
+        <is>
+          <t>C.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1181" s="5" t="inlineStr">
+        <is>
+          <t>engagement</t>
+        </is>
+      </c>
+      <c r="C1181" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="E1181" s="4" t="inlineStr">
+        <is>
+          <t>An officeholder who, after a holdings ban or a publication requirement is enacted, openly announces that they will keep their holdings or withhold their returns because the rule reaches lawful property and a family that never ran, and accepts whatever penalty or sanction follows rather than comply quietly.</t>
+        </is>
+      </c>
+      <c r="O1181" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T1181" s="4" t="inlineStr">
+        <is>
+          <t>example: defiant officeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="4" t="inlineStr">
+        <is>
+          <t>public-office-private-gain</t>
+        </is>
+      </c>
+      <c r="B1182" s="5" t="inlineStr">
+        <is>
+          <t>criteria</t>
+        </is>
+      </c>
+      <c r="E1182" s="4" t="inlineStr">
+        <is>
+          <t>Share of official decisions made by an official holding a personal financial stake in the outcome</t>
+        </is>
+      </c>
+      <c r="T1182" s="4" t="inlineStr">
+        <is>
+          <t>reading: percent of committee votes, rulings or clemency grants in a year where the deciding official or a family member held a stake in the outcome, from disclosure filings matched against the decisions | validity: High | reliability: Med | linkage: High | importance: High | why: It measures the conflict itself rather than a proxy for it, and it is the yardstick behind an interest cited on every belief page in the topic, but building the reading requires matching holdings against decisions, and no matched study of members' holdings against their roll-call votes yet exists, so observers will draw the line between stake and no stake differently.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T1166"/>
+  <autoFilter ref="A1:T1182"/>
   <dataValidations count="2">
     <dataValidation sqref="B2:B5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"argument,assumption,bias,category,cba,common,component,compromise,criteria,criterion,definition,direction,dispute,downstream,engagement,evidence,falsify,impact,interest,interest_listing,law,long_term,media,motive,obstacle,person,prediction,related,rung,shared_interest,short_term,similar,stack,strength,topic_media,topic_values,upstream,value"</formula1>

--- a/tools/static-site/ISE_Data_Entry.xlsx
+++ b/tools/static-site/ISE_Data_Entry.xlsx
@@ -13,8 +13,8 @@
     <sheet name="topics" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'pages'!$A$1:$AC$490</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'edges'!$A$1:$T$1182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'pages'!$A$1:$AC$637</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'edges'!$A$1:$T$1308</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'topics'!$A$1:$F$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -859,7 +859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC490"/>
+  <dimension ref="A1:AC637"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -16010,8 +16010,3515 @@
         </is>
       </c>
     </row>
+    <row r="491">
+      <c r="A491" s="4" t="inlineStr">
+        <is>
+          <t>companies-need-person-s</t>
+        </is>
+      </c>
+      <c r="C491" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D491" s="4" t="inlineStr">
+        <is>
+          <t>Companies should need a person's clear permission before collecting their data for advertising.</t>
+        </is>
+      </c>
+      <c r="F491" s="5" t="inlineStr">
+        <is>
+          <t>privacy-and-data</t>
+        </is>
+      </c>
+      <c r="W491" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether people can give meaningful consent to data collection at all, and on who should pay for the free services that collection now funds.</t>
+        </is>
+      </c>
+      <c r="AA491" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB491" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="4" t="inlineStr">
+        <is>
+          <t>information-about-person-belongs</t>
+        </is>
+      </c>
+      <c r="C492" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D492" s="4" t="inlineStr">
+        <is>
+          <t>Information about a person belongs to that person first, and taking it without asking treats people as a resource rather than as customers.</t>
+        </is>
+      </c>
+      <c r="G492" s="4" t="inlineStr">
+        <is>
+          <t>companies-need-person-s</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="4" t="inlineStr">
+        <is>
+          <t>most-people-do-know</t>
+        </is>
+      </c>
+      <c r="C493" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D493" s="4" t="inlineStr">
+        <is>
+          <t>Most people do not know how much is gathered about them or where it goes, so silent collection cannot be called consent in any real sense.</t>
+        </is>
+      </c>
+      <c r="G493" s="4" t="inlineStr">
+        <is>
+          <t>companies-need-person-s</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="4" t="inlineStr">
+        <is>
+          <t>requiring-permission-before-collecting</t>
+        </is>
+      </c>
+      <c r="C494" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D494" s="4" t="inlineStr">
+        <is>
+          <t>Requiring permission before collecting personal data forces companies to explain what they want and why, which by itself makes them collect less than they otherwise would.</t>
+        </is>
+      </c>
+      <c r="G494" s="4" t="inlineStr">
+        <is>
+          <t>companies-need-person-s</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="4" t="inlineStr">
+        <is>
+          <t>advertising-pays-most-free</t>
+        </is>
+      </c>
+      <c r="C495" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D495" s="4" t="inlineStr">
+        <is>
+          <t>Advertising pays for most free online services, and when fewer people opt in to data collection for ads, those services either start charging money or disappear.</t>
+        </is>
+      </c>
+      <c r="G495" s="4" t="inlineStr">
+        <is>
+          <t>companies-need-person-s</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="4" t="inlineStr">
+        <is>
+          <t>permission-screens-quickly-become</t>
+        </is>
+      </c>
+      <c r="C496" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D496" s="4" t="inlineStr">
+        <is>
+          <t>Permission screens quickly become a wall of clicks that people wave through without reading, so requiring consent before data collection adds friction without adding understanding.</t>
+        </is>
+      </c>
+      <c r="G496" s="4" t="inlineStr">
+        <is>
+          <t>companies-need-person-s</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="4" t="inlineStr">
+        <is>
+          <t>ads-matched-person-s</t>
+        </is>
+      </c>
+      <c r="C497" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D497" s="4" t="inlineStr">
+        <is>
+          <t>Ads matched to a person's interests are less annoying and more useful than random ones, and many people prefer them once they see the difference.</t>
+        </is>
+      </c>
+      <c r="G497" s="4" t="inlineStr">
+        <is>
+          <t>companies-need-person-s</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="4" t="inlineStr">
+        <is>
+          <t>law-enforcement-able-read</t>
+        </is>
+      </c>
+      <c r="C498" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D498" s="4" t="inlineStr">
+        <is>
+          <t>Law enforcement should be able to read encrypted messages when it has a warrant.</t>
+        </is>
+      </c>
+      <c r="F498" s="5" t="inlineStr">
+        <is>
+          <t>privacy-and-data</t>
+        </is>
+      </c>
+      <c r="W498" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether a way in for lawful searches can exist without becoming a way in for everyone else.</t>
+        </is>
+      </c>
+      <c r="AA498" s="5" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AB498" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="4" t="inlineStr">
+        <is>
+          <t>warrant-already-lets-police</t>
+        </is>
+      </c>
+      <c r="C499" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D499" s="4" t="inlineStr">
+        <is>
+          <t>A warrant already lets police search a home or open a safe, and a message on a phone should not be more protected than a letter in a drawer.</t>
+        </is>
+      </c>
+      <c r="G499" s="4" t="inlineStr">
+        <is>
+          <t>law-enforcement-able-read</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="4" t="inlineStr">
+        <is>
+          <t>people-who-plan-serious</t>
+        </is>
+      </c>
+      <c r="C500" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D500" s="4" t="inlineStr">
+        <is>
+          <t>People who plan serious harm use encrypted apps precisely because they know no one can look, and society should not build them a guaranteed hiding place.</t>
+        </is>
+      </c>
+      <c r="G500" s="4" t="inlineStr">
+        <is>
+          <t>law-enforcement-able-read</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="4" t="inlineStr">
+        <is>
+          <t>letting-police-read-encrypted</t>
+        </is>
+      </c>
+      <c r="C501" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D501" s="4" t="inlineStr">
+        <is>
+          <t>Letting police read an encrypted message only after a judge finds there is cause keeps the decision to look with a court rather than with the officers who want to look.</t>
+        </is>
+      </c>
+      <c r="G501" s="4" t="inlineStr">
+        <is>
+          <t>law-enforcement-able-read</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="4" t="inlineStr">
+        <is>
+          <t>there-no-way-build</t>
+        </is>
+      </c>
+      <c r="C502" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D502" s="4" t="inlineStr">
+        <is>
+          <t>There is no way to build a way into encrypted messages that only the police can use; any built-in opening can be found and used by criminals and hostile governments.</t>
+        </is>
+      </c>
+      <c r="G502" s="4" t="inlineStr">
+        <is>
+          <t>law-enforcement-able-read</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="4" t="inlineStr">
+        <is>
+          <t>warrants-issued-one-country</t>
+        </is>
+      </c>
+      <c r="C503" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D503" s="4" t="inlineStr">
+        <is>
+          <t>Warrants are issued in one country, but the same software runs everywhere, so a way in created for one government becomes available to all of them.</t>
+        </is>
+      </c>
+      <c r="G503" s="4" t="inlineStr">
+        <is>
+          <t>law-enforcement-able-read</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="4" t="inlineStr">
+        <is>
+          <t>ordinary-people-businesses-journalists</t>
+        </is>
+      </c>
+      <c r="C504" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D504" s="4" t="inlineStr">
+        <is>
+          <t>Ordinary people, businesses and journalists rely on encryption for their safety, and weakening it for everyone in order to catch a few makes the whole population less secure.</t>
+        </is>
+      </c>
+      <c r="G504" s="4" t="inlineStr">
+        <is>
+          <t>law-enforcement-able-read</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="4" t="inlineStr">
+        <is>
+          <t>new-movies-generally-open</t>
+        </is>
+      </c>
+      <c r="C505" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D505" s="4" t="inlineStr">
+        <is>
+          <t>New movies should generally open in theaters for a period before they reach streaming services.</t>
+        </is>
+      </c>
+      <c r="F505" s="5" t="inlineStr">
+        <is>
+          <t>movies</t>
+        </is>
+      </c>
+      <c r="W505" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether the shared theater experience is worth making everyone wait for it.</t>
+        </is>
+      </c>
+      <c r="AA505" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB505" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="4" t="inlineStr">
+        <is>
+          <t>theater-run-gives-movie</t>
+        </is>
+      </c>
+      <c r="C506" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D506" s="4" t="inlineStr">
+        <is>
+          <t>A theater run gives a movie a single shared moment when people talk about it, which builds interest that a quiet streaming release rarely matches.</t>
+        </is>
+      </c>
+      <c r="G506" s="4" t="inlineStr">
+        <is>
+          <t>new-movies-generally-open</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="4" t="inlineStr">
+        <is>
+          <t>seeing-film-big-screen</t>
+        </is>
+      </c>
+      <c r="C507" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D507" s="4" t="inlineStr">
+        <is>
+          <t>Seeing a film on a big screen with a crowd is a different and richer experience, and a period when a new film is only in theaters is the only way to keep that as the default way to see a movie.</t>
+        </is>
+      </c>
+      <c r="G507" s="4" t="inlineStr">
+        <is>
+          <t>new-movies-generally-open</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="4" t="inlineStr">
+        <is>
+          <t>theaters-local-businesses-employ</t>
+        </is>
+      </c>
+      <c r="C508" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D508" s="4" t="inlineStr">
+        <is>
+          <t>Theaters are local businesses that employ people and anchor downtowns, and they cannot survive if every film is available at home on the day it opens.</t>
+        </is>
+      </c>
+      <c r="G508" s="4" t="inlineStr">
+        <is>
+          <t>new-movies-generally-open</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="4" t="inlineStr">
+        <is>
+          <t>families-rural-viewers-people</t>
+        </is>
+      </c>
+      <c r="C509" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D509" s="4" t="inlineStr">
+        <is>
+          <t>Families, rural viewers and people with disabilities find theaters costly or hard to reach, and a forced wait before new films reach home screens treats them as second-class audiences.</t>
+        </is>
+      </c>
+      <c r="G509" s="4" t="inlineStr">
+        <is>
+          <t>new-movies-generally-open</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="4" t="inlineStr">
+        <is>
+          <t>piracy-fills-any-gap</t>
+        </is>
+      </c>
+      <c r="C510" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D510" s="4" t="inlineStr">
+        <is>
+          <t>Piracy fills any gap between a movie's release and its availability at home, so delays mostly push viewers toward illegal copies.</t>
+        </is>
+      </c>
+      <c r="G510" s="4" t="inlineStr">
+        <is>
+          <t>new-movies-generally-open</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="4" t="inlineStr">
+        <is>
+          <t>streaming-lets-small-unusual</t>
+        </is>
+      </c>
+      <c r="C511" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D511" s="4" t="inlineStr">
+        <is>
+          <t>Streaming lets small and unusual films find their audience without fighting for a limited number of screens, so a theater-first rule protects blockbusters more than it protects film as a whole.</t>
+        </is>
+      </c>
+      <c r="G511" s="4" t="inlineStr">
+        <is>
+          <t>new-movies-generally-open</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="4" t="inlineStr">
+        <is>
+          <t>studios-let-viewers-choose</t>
+        </is>
+      </c>
+      <c r="C512" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D512" s="4" t="inlineStr">
+        <is>
+          <t>Studios should let viewers choose to watch new movies at home on the same day they open in theaters.</t>
+        </is>
+      </c>
+      <c r="F512" s="5" t="inlineStr">
+        <is>
+          <t>movies</t>
+        </is>
+      </c>
+      <c r="W512" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether viewer convenience or the health of the theater business should decide where a new movie can be seen.</t>
+        </is>
+      </c>
+      <c r="AA512" s="5" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AB512" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="4" t="inlineStr">
+        <is>
+          <t>viewers-studios-decide-where</t>
+        </is>
+      </c>
+      <c r="C513" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D513" s="4" t="inlineStr">
+        <is>
+          <t>Viewers, not studios, should decide where they watch a film they are paying for.</t>
+        </is>
+      </c>
+      <c r="G513" s="4" t="inlineStr">
+        <is>
+          <t>studios-let-viewers-choose</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="4" t="inlineStr">
+        <is>
+          <t>tickets-parking-babysitting-make</t>
+        </is>
+      </c>
+      <c r="C514" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D514" s="4" t="inlineStr">
+        <is>
+          <t>Tickets, parking and babysitting make a night out expensive, and a home option puts new films within reach of people on tight budgets.</t>
+        </is>
+      </c>
+      <c r="G514" s="4" t="inlineStr">
+        <is>
+          <t>studios-let-viewers-choose</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="4" t="inlineStr">
+        <is>
+          <t>same-day-home-release</t>
+        </is>
+      </c>
+      <c r="C515" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D515" s="4" t="inlineStr">
+        <is>
+          <t>A same-day home release lets a film reach people who live far from any theater, so its audience grows instead of shrinking.</t>
+        </is>
+      </c>
+      <c r="G515" s="4" t="inlineStr">
+        <is>
+          <t>studios-let-viewers-choose</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="4" t="inlineStr">
+        <is>
+          <t>same-day-home-release-2</t>
+        </is>
+      </c>
+      <c r="C516" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D516" s="4" t="inlineStr">
+        <is>
+          <t>A same-day home release cuts theater attendance in the very weeks a film needs it most, and the lost ticket income is not replaced by streaming fees.</t>
+        </is>
+      </c>
+      <c r="G516" s="4" t="inlineStr">
+        <is>
+          <t>studios-let-viewers-choose</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="4" t="inlineStr">
+        <is>
+          <t>movies-watched-home-compete</t>
+        </is>
+      </c>
+      <c r="C517" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D517" s="4" t="inlineStr">
+        <is>
+          <t>Movies watched at home compete with phones and interruptions, so filmmakers lose the focused attention their work was made for.</t>
+        </is>
+      </c>
+      <c r="G517" s="4" t="inlineStr">
+        <is>
+          <t>studios-let-viewers-choose</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="4" t="inlineStr">
+        <is>
+          <t>once-viewers-expect-every</t>
+        </is>
+      </c>
+      <c r="C518" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D518" s="4" t="inlineStr">
+        <is>
+          <t>Once viewers expect every film at home on opening day, studios have less reason to spend on the large-scale pictures that only make sense on a big screen.</t>
+        </is>
+      </c>
+      <c r="G518" s="4" t="inlineStr">
+        <is>
+          <t>studios-let-viewers-choose</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="4" t="inlineStr">
+        <is>
+          <t>cities-generally-redesign-streets</t>
+        </is>
+      </c>
+      <c r="C519" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D519" s="4" t="inlineStr">
+        <is>
+          <t>Cities should generally redesign streets to slow cars down, even when that lengthens drive times.</t>
+        </is>
+      </c>
+      <c r="F519" s="5" t="inlineStr">
+        <is>
+          <t>autos</t>
+        </is>
+      </c>
+      <c r="W519" s="4" t="inlineStr">
+        <is>
+          <t>It turns on how many minutes of driving time a community will trade for fewer deaths and more people able to walk and bike.</t>
+        </is>
+      </c>
+      <c r="AA519" s="5" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AB519" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="4" t="inlineStr">
+        <is>
+          <t>whether-crash-kills-someone</t>
+        </is>
+      </c>
+      <c r="C520" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D520" s="4" t="inlineStr">
+        <is>
+          <t>Whether a crash kills someone depends mostly on speed, so a street built for slower driving saves lives without relying on drivers choosing to behave better.</t>
+        </is>
+      </c>
+      <c r="G520" s="4" t="inlineStr">
+        <is>
+          <t>cities-generally-redesign-streets</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="4" t="inlineStr">
+        <is>
+          <t>streets-where-cars-move</t>
+        </is>
+      </c>
+      <c r="C521" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D521" s="4" t="inlineStr">
+        <is>
+          <t>Streets where cars move slowly are streets where children, old people and cyclists can safely be, which gives everyone a choice besides driving.</t>
+        </is>
+      </c>
+      <c r="G521" s="4" t="inlineStr">
+        <is>
+          <t>cities-generally-redesign-streets</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="4" t="inlineStr">
+        <is>
+          <t>redesigning-street-slow-cars</t>
+        </is>
+      </c>
+      <c r="C522" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D522" s="4" t="inlineStr">
+        <is>
+          <t>Redesigning a street to slow cars costs each driver a small amount of time on each trip, while the safety gained is shared by every person who uses the street.</t>
+        </is>
+      </c>
+      <c r="G522" s="4" t="inlineStr">
+        <is>
+          <t>cities-generally-redesign-streets</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="4" t="inlineStr">
+        <is>
+          <t>longer-trips-cost-workers</t>
+        </is>
+      </c>
+      <c r="C523" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D523" s="4" t="inlineStr">
+        <is>
+          <t>Longer trips cost workers, deliveries and emergency vehicles real time every single day, and those costs add up across a whole city.</t>
+        </is>
+      </c>
+      <c r="G523" s="4" t="inlineStr">
+        <is>
+          <t>cities-generally-redesign-streets</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="4" t="inlineStr">
+        <is>
+          <t>slowing-main-road-pushes</t>
+        </is>
+      </c>
+      <c r="C524" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D524" s="4" t="inlineStr">
+        <is>
+          <t>Slowing a main road pushes drivers onto neighborhood side streets, moving the danger to places that were quiet before.</t>
+        </is>
+      </c>
+      <c r="G524" s="4" t="inlineStr">
+        <is>
+          <t>cities-generally-redesign-streets</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="4" t="inlineStr">
+        <is>
+          <t>most-places-most-people</t>
+        </is>
+      </c>
+      <c r="C525" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D525" s="4" t="inlineStr">
+        <is>
+          <t>In most places most people have no practical alternative to driving, so making driving worse punishes them without giving them a better option.</t>
+        </is>
+      </c>
+      <c r="G525" s="4" t="inlineStr">
+        <is>
+          <t>cities-generally-redesign-streets</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="4" t="inlineStr">
+        <is>
+          <t>banning-sale-new-gasoline</t>
+        </is>
+      </c>
+      <c r="C526" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D526" s="4" t="inlineStr">
+        <is>
+          <t>Banning the sale of new gasoline cars by a fixed date is generally a mistake.</t>
+        </is>
+      </c>
+      <c r="F526" s="5" t="inlineStr">
+        <is>
+          <t>autos</t>
+        </is>
+      </c>
+      <c r="W526" s="4" t="inlineStr">
+        <is>
+          <t>It turns on whether a firm deadline speeds the industry up or outruns what buyers and the charging network can absorb.</t>
+        </is>
+      </c>
+      <c r="AA526" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB526" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="4" t="inlineStr">
+        <is>
+          <t>electric-cars-still-out</t>
+        </is>
+      </c>
+      <c r="C527" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D527" s="4" t="inlineStr">
+        <is>
+          <t>Electric cars are still out of reach for many buyers, and people in apartments and rural areas often have nowhere to charge one.</t>
+        </is>
+      </c>
+      <c r="G527" s="4" t="inlineStr">
+        <is>
+          <t>banning-sale-new-gasoline</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="4" t="inlineStr">
+        <is>
+          <t>ban-new-gasoline-cars</t>
+        </is>
+      </c>
+      <c r="C528" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D528" s="4" t="inlineStr">
+        <is>
+          <t>A ban on new gasoline cars locks in one technology when hybrids, cleaner fuels or something not yet invented might turn out to be a better path.</t>
+        </is>
+      </c>
+      <c r="G528" s="4" t="inlineStr">
+        <is>
+          <t>banning-sale-new-gasoline</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="4" t="inlineStr">
+        <is>
+          <t>mandates-get-ahead-what</t>
+        </is>
+      </c>
+      <c r="C529" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D529" s="4" t="inlineStr">
+        <is>
+          <t>Mandates that get ahead of what people are ready to buy provoke a political backlash that can set the shift to electric cars back.</t>
+        </is>
+      </c>
+      <c r="G529" s="4" t="inlineStr">
+        <is>
+          <t>banning-sale-new-gasoline</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="4" t="inlineStr">
+        <is>
+          <t>automakers-charging-companies-only</t>
+        </is>
+      </c>
+      <c r="C530" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D530" s="4" t="inlineStr">
+        <is>
+          <t>Automakers and charging companies only invest at full scale when the end date for gasoline car sales is certain, so a firm deadline is what makes the switch to electric cars happen.</t>
+        </is>
+      </c>
+      <c r="G530" s="4" t="inlineStr">
+        <is>
+          <t>banning-sale-new-gasoline</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="4" t="inlineStr">
+        <is>
+          <t>every-gasoline-car-sold</t>
+        </is>
+      </c>
+      <c r="C531" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D531" s="4" t="inlineStr">
+        <is>
+          <t>Every gasoline car sold today will be on the road for many years, so the cheapest way to cut future emissions is to stop adding new ones.</t>
+        </is>
+      </c>
+      <c r="G531" s="4" t="inlineStr">
+        <is>
+          <t>banning-sale-new-gasoline</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="4" t="inlineStr">
+        <is>
+          <t>past-safety-emissions-standards</t>
+        </is>
+      </c>
+      <c r="C532" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D532" s="4" t="inlineStr">
+        <is>
+          <t>Past safety and emissions standards were routinely called impossible when announced, and the industry usually found a way once the deadline was firm.</t>
+        </is>
+      </c>
+      <c r="G532" s="4" t="inlineStr">
+        <is>
+          <t>banning-sale-new-gasoline</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="4" t="inlineStr">
+        <is>
+          <t>long-prison-sentences-generally</t>
+        </is>
+      </c>
+      <c r="C533" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D533" s="4" t="inlineStr">
+        <is>
+          <t>Long prison sentences generally do little to reduce crime compared with raising the odds of being caught.</t>
+        </is>
+      </c>
+      <c r="F533" s="5" t="inlineStr">
+        <is>
+          <t>law</t>
+        </is>
+      </c>
+      <c r="W533" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether crime is prevented more by keeping known offenders locked away for longer or by making arrest more likely in the first place.</t>
+        </is>
+      </c>
+      <c r="AA533" s="5" t="n">
+        <v>-60</v>
+      </c>
+      <c r="AB533" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="4" t="inlineStr">
+        <is>
+          <t>most-people-who-commit</t>
+        </is>
+      </c>
+      <c r="C534" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D534" s="4" t="inlineStr">
+        <is>
+          <t>Most people who commit crimes do not expect to be caught, so the length of a sentence they never expect to serve does not enter their thinking.</t>
+        </is>
+      </c>
+      <c r="G534" s="4" t="inlineStr">
+        <is>
+          <t>long-prison-sentences-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="4" t="inlineStr">
+        <is>
+          <t>young-men-commit-most</t>
+        </is>
+      </c>
+      <c r="C535" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D535" s="4" t="inlineStr">
+        <is>
+          <t>Young men commit most crimes and stop on their own as they get older, so years added to the end of a sentence hold people who would have quit anyway.</t>
+        </is>
+      </c>
+      <c r="G535" s="4" t="inlineStr">
+        <is>
+          <t>long-prison-sentences-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="4" t="inlineStr">
+        <is>
+          <t>money-spent-extra-years</t>
+        </is>
+      </c>
+      <c r="C536" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D536" s="4" t="inlineStr">
+        <is>
+          <t>Money spent on extra years in prison could instead hire investigators and patrol officers, which raises the chance of being caught and does change behavior.</t>
+        </is>
+      </c>
+      <c r="G536" s="4" t="inlineStr">
+        <is>
+          <t>long-prison-sentences-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="4" t="inlineStr">
+        <is>
+          <t>person-prison-cannot-commit</t>
+        </is>
+      </c>
+      <c r="C537" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D537" s="4" t="inlineStr">
+        <is>
+          <t>A person in prison cannot commit crimes against the public, so every added year prevents whatever that person would have done outside.</t>
+        </is>
+      </c>
+      <c r="G537" s="4" t="inlineStr">
+        <is>
+          <t>long-prison-sentences-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="4" t="inlineStr">
+        <is>
+          <t>small-number-repeat-offenders</t>
+        </is>
+      </c>
+      <c r="C538" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D538" s="4" t="inlineStr">
+        <is>
+          <t>A small number of repeat offenders commit a large share of all serious crime and keep at it well into middle age, so long sentences hold exactly the people who would not have quit on their own.</t>
+        </is>
+      </c>
+      <c r="G538" s="4" t="inlineStr">
+        <is>
+          <t>long-prison-sentences-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="4" t="inlineStr">
+        <is>
+          <t>being-caught-only-deters</t>
+        </is>
+      </c>
+      <c r="C539" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D539" s="4" t="inlineStr">
+        <is>
+          <t>Being caught only deters people if what follows is serious, so more arrests paired with short sentences give offenders little to fear.</t>
+        </is>
+      </c>
+      <c r="G539" s="4" t="inlineStr">
+        <is>
+          <t>long-prison-sentences-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="4" t="inlineStr">
+        <is>
+          <t>judges-allowed-keep-suspects</t>
+        </is>
+      </c>
+      <c r="C540" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D540" s="4" t="inlineStr">
+        <is>
+          <t>Judges should be allowed to keep suspects they consider dangerous in jail before trial, even when those suspects could afford bail.</t>
+        </is>
+      </c>
+      <c r="F540" s="5" t="inlineStr">
+        <is>
+          <t>law</t>
+        </is>
+      </c>
+      <c r="W540" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether a judge's guess about future danger can justify locking up someone not yet convicted.</t>
+        </is>
+      </c>
+      <c r="AA540" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB540" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="4" t="inlineStr">
+        <is>
+          <t>someone-arrested-violent-act</t>
+        </is>
+      </c>
+      <c r="C541" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D541" s="4" t="inlineStr">
+        <is>
+          <t>Someone arrested for a violent act and released the same day can go after the same victim or witness before the trial ever happens.</t>
+        </is>
+      </c>
+      <c r="G541" s="4" t="inlineStr">
+        <is>
+          <t>judges-allowed-keep-suspects</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="4" t="inlineStr">
+        <is>
+          <t>bail-based-money-frees</t>
+        </is>
+      </c>
+      <c r="C542" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D542" s="4" t="inlineStr">
+        <is>
+          <t>Bail based on money frees the wealthy and holds the poor, so a judgment about danger is fairer than a judgment about cash.</t>
+        </is>
+      </c>
+      <c r="G542" s="4" t="inlineStr">
+        <is>
+          <t>judges-allowed-keep-suspects</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="4" t="inlineStr">
+        <is>
+          <t>public-confidence-courts-falls</t>
+        </is>
+      </c>
+      <c r="C543" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D543" s="4" t="inlineStr">
+        <is>
+          <t>Public confidence in the courts falls when people see a suspect walk out hours after a serious arrest.</t>
+        </is>
+      </c>
+      <c r="G543" s="4" t="inlineStr">
+        <is>
+          <t>judges-allowed-keep-suspects</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="4" t="inlineStr">
+        <is>
+          <t>person-who-has-been</t>
+        </is>
+      </c>
+      <c r="C544" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D544" s="4" t="inlineStr">
+        <is>
+          <t>A person who has not been convicted is presumed innocent, and jailing that person is punishment before any trial.</t>
+        </is>
+      </c>
+      <c r="G544" s="4" t="inlineStr">
+        <is>
+          <t>judges-allowed-keep-suspects</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="4" t="inlineStr">
+        <is>
+          <t>predicting-who-dangerous-guesswork</t>
+        </is>
+      </c>
+      <c r="C545" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D545" s="4" t="inlineStr">
+        <is>
+          <t>Predicting who is dangerous is guesswork, and a judge facing public pressure will err toward holding people who would have caused no harm.</t>
+        </is>
+      </c>
+      <c r="G545" s="4" t="inlineStr">
+        <is>
+          <t>judges-allowed-keep-suspects</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="4" t="inlineStr">
+        <is>
+          <t>even-few-weeks-jail</t>
+        </is>
+      </c>
+      <c r="C546" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D546" s="4" t="inlineStr">
+        <is>
+          <t>Even a few weeks in jail can cost a person their job, housing, and custody of their children, so detention harms whole families whether or not the charge holds up.</t>
+        </is>
+      </c>
+      <c r="G546" s="4" t="inlineStr">
+        <is>
+          <t>judges-allowed-keep-suspects</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="4" t="inlineStr">
+        <is>
+          <t>governments-put-protecting-environment</t>
+        </is>
+      </c>
+      <c r="C547" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D547" s="4" t="inlineStr">
+        <is>
+          <t>Governments should put protecting the environment ahead of economic growth when the two conflict.</t>
+        </is>
+      </c>
+      <c r="F547" s="5" t="inlineStr">
+        <is>
+          <t>environment</t>
+        </is>
+      </c>
+      <c r="W547" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether growth is the thing that damages the environment or the thing that eventually pays to repair it.</t>
+        </is>
+      </c>
+      <c r="AA547" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB547" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="4" t="inlineStr">
+        <is>
+          <t>damage-nature-often-cannot</t>
+        </is>
+      </c>
+      <c r="C548" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D548" s="4" t="inlineStr">
+        <is>
+          <t>Damage to nature often cannot be undone, while lost growth can be made up later, so the cautious choice is to protect what cannot be replaced.</t>
+        </is>
+      </c>
+      <c r="G548" s="4" t="inlineStr">
+        <is>
+          <t>governments-put-protecting-environment</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="4" t="inlineStr">
+        <is>
+          <t>growth-uses-up-resources</t>
+        </is>
+      </c>
+      <c r="C549" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D549" s="4" t="inlineStr">
+        <is>
+          <t>Growth that uses up resources is borrowed from future generations who never agreed to the loan.</t>
+        </is>
+      </c>
+      <c r="G549" s="4" t="inlineStr">
+        <is>
+          <t>governments-put-protecting-environment</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="4" t="inlineStr">
+        <is>
+          <t>markets-reward-growth-but</t>
+        </is>
+      </c>
+      <c r="C550" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D550" s="4" t="inlineStr">
+        <is>
+          <t>Markets reward growth but give nobody a reason to pay for clean air, so when growth and clean air collide only a government rule keeps the air clean.</t>
+        </is>
+      </c>
+      <c r="G550" s="4" t="inlineStr">
+        <is>
+          <t>governments-put-protecting-environment</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="4" t="inlineStr">
+        <is>
+          <t>countries-clean-today-mostly</t>
+        </is>
+      </c>
+      <c r="C551" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D551" s="4" t="inlineStr">
+        <is>
+          <t>Countries that are clean today mostly got rich first and then paid for cleanup, so growth is the path to protection rather than its enemy.</t>
+        </is>
+      </c>
+      <c r="G551" s="4" t="inlineStr">
+        <is>
+          <t>governments-put-protecting-environment</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="4" t="inlineStr">
+        <is>
+          <t>strict-environmental-limits-one</t>
+        </is>
+      </c>
+      <c r="C552" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D552" s="4" t="inlineStr">
+        <is>
+          <t>Strict environmental limits in one country push dirty production to places with weaker rules, so the harm moves instead of shrinking.</t>
+        </is>
+      </c>
+      <c r="G552" s="4" t="inlineStr">
+        <is>
+          <t>governments-put-protecting-environment</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="4" t="inlineStr">
+        <is>
+          <t>rules-put-environment-ahead</t>
+        </is>
+      </c>
+      <c r="C553" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D553" s="4" t="inlineStr">
+        <is>
+          <t>Rules that put the environment ahead of growth raise prices and cut jobs for the people least able to absorb either.</t>
+        </is>
+      </c>
+      <c r="G553" s="4" t="inlineStr">
+        <is>
+          <t>governments-put-protecting-environment</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="4" t="inlineStr">
+        <is>
+          <t>technology-tends-solve-environmental</t>
+        </is>
+      </c>
+      <c r="C554" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D554" s="4" t="inlineStr">
+        <is>
+          <t>Technology tends to solve environmental problems better than restrictions on how people live.</t>
+        </is>
+      </c>
+      <c r="F554" s="5" t="inlineStr">
+        <is>
+          <t>environment</t>
+        </is>
+      </c>
+      <c r="W554" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether clean technology arrives on its own or only because rules created a reason to build it.</t>
+        </is>
+      </c>
+      <c r="AA554" s="5" t="n">
+        <v>-35</v>
+      </c>
+      <c r="AB554" s="5" t="inlineStr">
+        <is>
+          <t>Modest</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="4" t="inlineStr">
+        <is>
+          <t>past-resource-scares-tended</t>
+        </is>
+      </c>
+      <c r="C555" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D555" s="4" t="inlineStr">
+        <is>
+          <t>Past resource scares tended to end with a new method or a new material, not with rationing, and there is no reason to expect the pattern to stop.</t>
+        </is>
+      </c>
+      <c r="G555" s="4" t="inlineStr">
+        <is>
+          <t>technology-tends-solve-environmental</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="4" t="inlineStr">
+        <is>
+          <t>restrictions-daily-life-unpopular</t>
+        </is>
+      </c>
+      <c r="C556" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D556" s="4" t="inlineStr">
+        <is>
+          <t>Restrictions on daily life are unpopular and get rolled back, while a cleaner option that is also cheaper stays adopted for good.</t>
+        </is>
+      </c>
+      <c r="G556" s="4" t="inlineStr">
+        <is>
+          <t>technology-tends-solve-environmental</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="4" t="inlineStr">
+        <is>
+          <t>rule-freezes-today-s</t>
+        </is>
+      </c>
+      <c r="C557" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D557" s="4" t="inlineStr">
+        <is>
+          <t>A rule freezes today's best answer in place, while innovation keeps finding better answers that the rule would have blocked.</t>
+        </is>
+      </c>
+      <c r="G557" s="4" t="inlineStr">
+        <is>
+          <t>technology-tends-solve-environmental</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="4" t="inlineStr">
+        <is>
+          <t>new-technology-arrives-its</t>
+        </is>
+      </c>
+      <c r="C558" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D558" s="4" t="inlineStr">
+        <is>
+          <t>New technology arrives on its own schedule while environmental damage is happening now, so waiting for a technical fix is a decision to accept that damage in the meantime.</t>
+        </is>
+      </c>
+      <c r="G558" s="4" t="inlineStr">
+        <is>
+          <t>technology-tends-solve-environmental</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="4" t="inlineStr">
+        <is>
+          <t>new-technology-often-used</t>
+        </is>
+      </c>
+      <c r="C559" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D559" s="4" t="inlineStr">
+        <is>
+          <t>New technology is often used to consume more rather than less, so efficiency gains get eaten by growth unless something limits the total.</t>
+        </is>
+      </c>
+      <c r="G559" s="4" t="inlineStr">
+        <is>
+          <t>technology-tends-solve-environmental</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="4" t="inlineStr">
+        <is>
+          <t>clean-technologies-did-succeed</t>
+        </is>
+      </c>
+      <c r="C560" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D560" s="4" t="inlineStr">
+        <is>
+          <t>The clean technologies that did succeed usually appeared because rules and targets made someone pay for them, so the restriction is what produces the invention.</t>
+        </is>
+      </c>
+      <c r="G560" s="4" t="inlineStr">
+        <is>
+          <t>technology-tends-solve-environmental</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="4" t="inlineStr">
+        <is>
+          <t>longer-prison-sentences-generally</t>
+        </is>
+      </c>
+      <c r="C561" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D561" s="4" t="inlineStr">
+        <is>
+          <t>Longer prison sentences generally make communities safer.</t>
+        </is>
+      </c>
+      <c r="F561" s="5" t="inlineStr">
+        <is>
+          <t>crime-and-justice</t>
+        </is>
+      </c>
+      <c r="W561" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether the extra years are served by people who would have kept offending or by people who would have stopped anyway.</t>
+        </is>
+      </c>
+      <c r="AA561" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB561" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="4" t="inlineStr">
+        <is>
+          <t>person-who-prison-cannot</t>
+        </is>
+      </c>
+      <c r="C562" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D562" s="4" t="inlineStr">
+        <is>
+          <t>A person who is in prison cannot commit crimes on the street, and every year added is a year the community is protected from that person.</t>
+        </is>
+      </c>
+      <c r="G562" s="4" t="inlineStr">
+        <is>
+          <t>longer-prison-sentences-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="4" t="inlineStr">
+        <is>
+          <t>adding-years-sentence-raises</t>
+        </is>
+      </c>
+      <c r="C563" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D563" s="4" t="inlineStr">
+        <is>
+          <t>Adding years to a sentence raises the price of getting caught, and a higher price makes some people decide the crime is not worth it.</t>
+        </is>
+      </c>
+      <c r="G563" s="4" t="inlineStr">
+        <is>
+          <t>longer-prison-sentences-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="4" t="inlineStr">
+        <is>
+          <t>few-repeat-offenders-account</t>
+        </is>
+      </c>
+      <c r="C564" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D564" s="4" t="inlineStr">
+        <is>
+          <t>A few repeat offenders account for a large share of crime, so holding those people longer removes a large share of harm.</t>
+        </is>
+      </c>
+      <c r="G564" s="4" t="inlineStr">
+        <is>
+          <t>longer-prison-sentences-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="4" t="inlineStr">
+        <is>
+          <t>most-people-age-out</t>
+        </is>
+      </c>
+      <c r="C565" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D565" s="4" t="inlineStr">
+        <is>
+          <t>Most people age out of crime on their own, so extra years are mostly served by people who would have stopped anyway, at great cost and for no safety gain.</t>
+        </is>
+      </c>
+      <c r="G565" s="4" t="inlineStr">
+        <is>
+          <t>longer-prison-sentences-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="4" t="inlineStr">
+        <is>
+          <t>prison-teaches-criminal-skills</t>
+        </is>
+      </c>
+      <c r="C566" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D566" s="4" t="inlineStr">
+        <is>
+          <t>Prison teaches criminal skills and cuts jobs and family ties, so people released after long terms often come out more dangerous than they went in.</t>
+        </is>
+      </c>
+      <c r="G566" s="4" t="inlineStr">
+        <is>
+          <t>longer-prison-sentences-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="4" t="inlineStr">
+        <is>
+          <t>money-spent-extra-years-2</t>
+        </is>
+      </c>
+      <c r="C567" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D567" s="4" t="inlineStr">
+        <is>
+          <t>The money spent on extra years of prison could pay for more officers on the street, and being likely to get caught deters more than the length of the sentence.</t>
+        </is>
+      </c>
+      <c r="G567" s="4" t="inlineStr">
+        <is>
+          <t>longer-prison-sentences-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="4" t="inlineStr">
+        <is>
+          <t>police-departments-spend-more</t>
+        </is>
+      </c>
+      <c r="C568" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D568" s="4" t="inlineStr">
+        <is>
+          <t>Police departments should spend more of their effort preventing crime than making arrests.</t>
+        </is>
+      </c>
+      <c r="F568" s="5" t="inlineStr">
+        <is>
+          <t>crime-and-justice</t>
+        </is>
+      </c>
+      <c r="W568" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether harm that was prevented can be counted and answered for the way harm that was punished can.</t>
+        </is>
+      </c>
+      <c r="AA568" s="5" t="n">
+        <v>-45</v>
+      </c>
+      <c r="AB568" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="4" t="inlineStr">
+        <is>
+          <t>arrest-happens-after-someone</t>
+        </is>
+      </c>
+      <c r="C569" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D569" s="4" t="inlineStr">
+        <is>
+          <t>An arrest happens after someone has already been hurt, while a visible patrol, better lighting, or a mediated dispute stops the harm before it occurs.</t>
+        </is>
+      </c>
+      <c r="G569" s="4" t="inlineStr">
+        <is>
+          <t>police-departments-spend-more</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="4" t="inlineStr">
+        <is>
+          <t>arrests-minor-offenses-leave</t>
+        </is>
+      </c>
+      <c r="C570" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D570" s="4" t="inlineStr">
+        <is>
+          <t>Arrests for minor offenses leave young people with a record that narrows their lawful paths and makes crime the easier one.</t>
+        </is>
+      </c>
+      <c r="G570" s="4" t="inlineStr">
+        <is>
+          <t>police-departments-spend-more</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="4" t="inlineStr">
+        <is>
+          <t>communities-share-information-police</t>
+        </is>
+      </c>
+      <c r="C571" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D571" s="4" t="inlineStr">
+        <is>
+          <t>Communities share information with police who help them and hide it from police who mostly punish them, and that information is what solves serious crimes.</t>
+        </is>
+      </c>
+      <c r="G571" s="4" t="inlineStr">
+        <is>
+          <t>police-departments-spend-more</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="4" t="inlineStr">
+        <is>
+          <t>prevention-hard-measure-easy</t>
+        </is>
+      </c>
+      <c r="C572" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D572" s="4" t="inlineStr">
+        <is>
+          <t>Prevention is hard to measure and easy to claim, while an arrest is a public act that can be checked, so shifting effort to prevention makes police less accountable.</t>
+        </is>
+      </c>
+      <c r="G572" s="4" t="inlineStr">
+        <is>
+          <t>police-departments-spend-more</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="4" t="inlineStr">
+        <is>
+          <t>people-who-have-already</t>
+        </is>
+      </c>
+      <c r="C573" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D573" s="4" t="inlineStr">
+        <is>
+          <t>People who have already been harmed are owed a response now, and putting arrests second means the department serves the person who might be hurt tomorrow ahead of the person who was hurt yesterday.</t>
+        </is>
+      </c>
+      <c r="G573" s="4" t="inlineStr">
+        <is>
+          <t>police-departments-spend-more</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="4" t="inlineStr">
+        <is>
+          <t>surest-form-prevention-certainty</t>
+        </is>
+      </c>
+      <c r="C574" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D574" s="4" t="inlineStr">
+        <is>
+          <t>The surest form of prevention is the certainty that offenders get caught, and that certainty is built one arrest at a time.</t>
+        </is>
+      </c>
+      <c r="G574" s="4" t="inlineStr">
+        <is>
+          <t>police-departments-spend-more</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="4" t="inlineStr">
+        <is>
+          <t>heavy-digital-editing-generally</t>
+        </is>
+      </c>
+      <c r="C575" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D575" s="4" t="inlineStr">
+        <is>
+          <t>Heavy digital editing generally does not make a photograph any less of a photograph.</t>
+        </is>
+      </c>
+      <c r="F575" s="5" t="inlineStr">
+        <is>
+          <t>photography</t>
+        </is>
+      </c>
+      <c r="W575" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether a photograph is defined by the camera's capture or by the finished picture the photographer chooses to show.</t>
+        </is>
+      </c>
+      <c r="AA575" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB575" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="4" t="inlineStr">
+        <is>
+          <t>every-photograph-already-involves</t>
+        </is>
+      </c>
+      <c r="C576" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D576" s="4" t="inlineStr">
+        <is>
+          <t>Every photograph already involves choices about framing, timing, lens and light, so editing afterward is one more choice among many rather than a break from the craft.</t>
+        </is>
+      </c>
+      <c r="G576" s="4" t="inlineStr">
+        <is>
+          <t>heavy-digital-editing-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="4" t="inlineStr">
+        <is>
+          <t>printing-developing-have-always</t>
+        </is>
+      </c>
+      <c r="C577" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D577" s="4" t="inlineStr">
+        <is>
+          <t>Printing and developing have always allowed the maker to lighten, darken, crop and combine, and nobody stopped calling those results photographs.</t>
+        </is>
+      </c>
+      <c r="G577" s="4" t="inlineStr">
+        <is>
+          <t>heavy-digital-editing-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="4" t="inlineStr">
+        <is>
+          <t>what-viewers-respond-finished</t>
+        </is>
+      </c>
+      <c r="C578" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D578" s="4" t="inlineStr">
+        <is>
+          <t>What viewers respond to is the finished image on the wall or the screen, and the tools used to reach it matter no more than the brand of brush matters for a painting.</t>
+        </is>
+      </c>
+      <c r="G578" s="4" t="inlineStr">
+        <is>
+          <t>heavy-digital-editing-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="4" t="inlineStr">
+        <is>
+          <t>ordinary-people-trust-photograph</t>
+        </is>
+      </c>
+      <c r="C579" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D579" s="4" t="inlineStr">
+        <is>
+          <t>Ordinary people trust a photograph because they assume it shows something that actually happened, and heavy editing quietly spends that trust without telling them.</t>
+        </is>
+      </c>
+      <c r="G579" s="4" t="inlineStr">
+        <is>
+          <t>heavy-digital-editing-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="4" t="inlineStr">
+        <is>
+          <t>photograph-s-one-special</t>
+        </is>
+      </c>
+      <c r="C580" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D580" s="4" t="inlineStr">
+        <is>
+          <t>A photograph's one special power over painting is its claim to have been there, so an image that no longer makes that claim has given up the thing that made it a photograph.</t>
+        </is>
+      </c>
+      <c r="G580" s="4" t="inlineStr">
+        <is>
+          <t>heavy-digital-editing-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="4" t="inlineStr">
+        <is>
+          <t>when-any-part-picture</t>
+        </is>
+      </c>
+      <c r="C581" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D581" s="4" t="inlineStr">
+        <is>
+          <t>When any part of a picture can be changed after the camera has done its work, being in the right place at the right moment matters less than skill at software, and a photograph made that way is closer to an illustration than to a record.</t>
+        </is>
+      </c>
+      <c r="G581" s="4" t="inlineStr">
+        <is>
+          <t>heavy-digital-editing-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="4" t="inlineStr">
+        <is>
+          <t>photograph-s-worth-clearly</t>
+        </is>
+      </c>
+      <c r="C582" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D582" s="4" t="inlineStr">
+        <is>
+          <t>A photograph's worth clearly rests more on what it truthfully shows than on the photographer's artistry.</t>
+        </is>
+      </c>
+      <c r="F582" s="5" t="inlineStr">
+        <is>
+          <t>photography</t>
+        </is>
+      </c>
+      <c r="W582" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether the camera's link to a real moment or the maker's eye is the source of a photograph's value.</t>
+        </is>
+      </c>
+      <c r="AA582" s="5" t="n">
+        <v>-40</v>
+      </c>
+      <c r="AB582" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="4" t="inlineStr">
+        <is>
+          <t>photographs-people-return-across</t>
+        </is>
+      </c>
+      <c r="C583" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D583" s="4" t="inlineStr">
+        <is>
+          <t>The photographs people return to across generations are the ones that show something real, from a family's kitchen to a war, and their power comes from that reality rather than from technique.</t>
+        </is>
+      </c>
+      <c r="G583" s="4" t="inlineStr">
+        <is>
+          <t>photograph-s-worth-clearly</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="4" t="inlineStr">
+        <is>
+          <t>artistry-can-produced-demand</t>
+        </is>
+      </c>
+      <c r="C584" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D584" s="4" t="inlineStr">
+        <is>
+          <t>Artistry can be produced on demand by anyone with training, but a true and telling moment cannot be staged without becoming something else.</t>
+        </is>
+      </c>
+      <c r="G584" s="4" t="inlineStr">
+        <is>
+          <t>photograph-s-worth-clearly</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="4" t="inlineStr">
+        <is>
+          <t>when-striking-image-turns</t>
+        </is>
+      </c>
+      <c r="C585" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D585" s="4" t="inlineStr">
+        <is>
+          <t>When a striking image turns out to have been posed or altered, most people feel cheated, which shows that truth was what they valued all along.</t>
+        </is>
+      </c>
+      <c r="G585" s="4" t="inlineStr">
+        <is>
+          <t>photograph-s-worth-clearly</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="4" t="inlineStr">
+        <is>
+          <t>millions-truthful-snapshots-taken</t>
+        </is>
+      </c>
+      <c r="C586" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D586" s="4" t="inlineStr">
+        <is>
+          <t>Millions of truthful snapshots are taken every day and nearly all are forgettable, so truth alone plainly is not what separates a memorable image from a dull one.</t>
+        </is>
+      </c>
+      <c r="G586" s="4" t="inlineStr">
+        <is>
+          <t>photograph-s-worth-clearly</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="4" t="inlineStr">
+        <is>
+          <t>choosing-where-stand-what</t>
+        </is>
+      </c>
+      <c r="C587" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D587" s="4" t="inlineStr">
+        <is>
+          <t>Choosing where to stand, what to leave out and when to press the shutter is artistry, and it is what turns a scene anyone could see into a picture worth looking at.</t>
+        </is>
+      </c>
+      <c r="G587" s="4" t="inlineStr">
+        <is>
+          <t>photograph-s-worth-clearly</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="4" t="inlineStr">
+        <is>
+          <t>portraits-still-lifes-fashion</t>
+        </is>
+      </c>
+      <c r="C588" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D588" s="4" t="inlineStr">
+        <is>
+          <t>Portraits, still lifes and fashion pictures are openly arranged, and they are among the most admired photographs ever made, which a truth-first view cannot explain.</t>
+        </is>
+      </c>
+      <c r="G588" s="4" t="inlineStr">
+        <is>
+          <t>photograph-s-worth-clearly</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="4" t="inlineStr">
+        <is>
+          <t>self-driving-cars-can</t>
+        </is>
+      </c>
+      <c r="C589" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D589" s="4" t="inlineStr">
+        <is>
+          <t>Self-driving cars can clearly be made safer than human drivers on ordinary roads.</t>
+        </is>
+      </c>
+      <c r="F589" s="5" t="inlineStr">
+        <is>
+          <t>engineering</t>
+        </is>
+      </c>
+      <c r="W589" s="4" t="inlineStr">
+        <is>
+          <t>It comes down to whether the rare, strange situations a machine handles badly outweigh the common human failures it removes.</t>
+        </is>
+      </c>
+      <c r="AA589" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB589" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="4" t="inlineStr">
+        <is>
+          <t>most-crashes-come-distraction</t>
+        </is>
+      </c>
+      <c r="C590" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D590" s="4" t="inlineStr">
+        <is>
+          <t>Most crashes come from distraction, tiredness, drunkenness and speeding, and a machine suffers from none of them.</t>
+        </is>
+      </c>
+      <c r="G590" s="4" t="inlineStr">
+        <is>
+          <t>self-driving-cars-can</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="4" t="inlineStr">
+        <is>
+          <t>machine-driver-watches-every</t>
+        </is>
+      </c>
+      <c r="C591" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D591" s="4" t="inlineStr">
+        <is>
+          <t>A machine driver watches every direction at once and reacts faster than any person, so it can start braking or steering while a human is still noticing the danger.</t>
+        </is>
+      </c>
+      <c r="G591" s="4" t="inlineStr">
+        <is>
+          <t>self-driving-cars-can</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="4" t="inlineStr">
+        <is>
+          <t>when-one-automated-car</t>
+        </is>
+      </c>
+      <c r="C592" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D592" s="4" t="inlineStr">
+        <is>
+          <t>When one automated car learns from a mistake, the fix goes to every car in the fleet, while every human driver has to learn each lesson alone.</t>
+        </is>
+      </c>
+      <c r="G592" s="4" t="inlineStr">
+        <is>
+          <t>self-driving-cars-can</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="4" t="inlineStr">
+        <is>
+          <t>roads-full-unusual-situations</t>
+        </is>
+      </c>
+      <c r="C593" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D593" s="4" t="inlineStr">
+        <is>
+          <t>Roads are full of unusual situations, from hand signals to fallen debris, and a system trained on typical cases fails exactly where judgment matters most.</t>
+        </is>
+      </c>
+      <c r="G593" s="4" t="inlineStr">
+        <is>
+          <t>self-driving-cars-can</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="4" t="inlineStr">
+        <is>
+          <t>ordinary-roads-self-driving</t>
+        </is>
+      </c>
+      <c r="C594" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D594" s="4" t="inlineStr">
+        <is>
+          <t>On ordinary roads a self-driving car will need a human ready to take over for a long time, and a person told to supervise a machine stops paying attention, so the car plus its bored supervisor is more dangerous than a driver who knows the job is theirs.</t>
+        </is>
+      </c>
+      <c r="G594" s="4" t="inlineStr">
+        <is>
+          <t>self-driving-cars-can</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="4" t="inlineStr">
+        <is>
+          <t>sensors-fail-rain-snow</t>
+        </is>
+      </c>
+      <c r="C595" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D595" s="4" t="inlineStr">
+        <is>
+          <t>Sensors fail in rain, snow, glare and dirt, and a driver who cannot see in bad weather is not safer than one who can.</t>
+        </is>
+      </c>
+      <c r="G595" s="4" t="inlineStr">
+        <is>
+          <t>self-driving-cars-can</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="4" t="inlineStr">
+        <is>
+          <t>adding-automation-critical-systems</t>
+        </is>
+      </c>
+      <c r="C596" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D596" s="4" t="inlineStr">
+        <is>
+          <t>Adding automation to critical systems tends to create new kinds of failure that are harder to catch than the ones it removes.</t>
+        </is>
+      </c>
+      <c r="F596" s="5" t="inlineStr">
+        <is>
+          <t>engineering</t>
+        </is>
+      </c>
+      <c r="W596" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement is whether the surprising failures of automation are a permanent cost or a design problem that gets solved.</t>
+        </is>
+      </c>
+      <c r="AA596" s="5" t="n">
+        <v>-40</v>
+      </c>
+      <c r="AB596" s="5" t="inlineStr">
+        <is>
+          <t>Modest</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="4" t="inlineStr">
+        <is>
+          <t>automation-hides-what-system</t>
+        </is>
+      </c>
+      <c r="C597" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D597" s="4" t="inlineStr">
+        <is>
+          <t>Automation hides what the system is doing, so when it fails the operators are surprised and have no time to understand what went wrong.</t>
+        </is>
+      </c>
+      <c r="G597" s="4" t="inlineStr">
+        <is>
+          <t>adding-automation-critical-systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="4" t="inlineStr">
+        <is>
+          <t>operators-who-rarely-act</t>
+        </is>
+      </c>
+      <c r="C598" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D598" s="4" t="inlineStr">
+        <is>
+          <t>Operators who rarely act lose the skills they need in the moment the machine hands control back to them.</t>
+        </is>
+      </c>
+      <c r="G598" s="4" t="inlineStr">
+        <is>
+          <t>adding-automation-critical-systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="4" t="inlineStr">
+        <is>
+          <t>automated-parts-copied-everywhere</t>
+        </is>
+      </c>
+      <c r="C599" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D599" s="4" t="inlineStr">
+        <is>
+          <t>Automated parts are copied everywhere, so one hidden bug can fail in many places at once instead of one crew making one mistake.</t>
+        </is>
+      </c>
+      <c r="G599" s="4" t="inlineStr">
+        <is>
+          <t>adding-automation-critical-systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="4" t="inlineStr">
+        <is>
+          <t>machine-s-possible-failures</t>
+        </is>
+      </c>
+      <c r="C600" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D600" s="4" t="inlineStr">
+        <is>
+          <t>A machine's possible failures are written into its rules and can be inspected and tested before it ever runs, while a person's failures come from mood, fatigue and distraction that nobody can inspect in advance, so the new failures are easier to catch, not harder.</t>
+        </is>
+      </c>
+      <c r="G600" s="4" t="inlineStr">
+        <is>
+          <t>adding-automation-critical-systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="4" t="inlineStr">
+        <is>
+          <t>automated-failures-logged-repeatable</t>
+        </is>
+      </c>
+      <c r="C601" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D601" s="4" t="inlineStr">
+        <is>
+          <t>Automated failures are logged and repeatable, so once they happen they can be found and fixed for good, while human lapses repeat forever.</t>
+        </is>
+      </c>
+      <c r="G601" s="4" t="inlineStr">
+        <is>
+          <t>adding-automation-critical-systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="4" t="inlineStr">
+        <is>
+          <t>new-failures-automation-creates</t>
+        </is>
+      </c>
+      <c r="C602" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D602" s="4" t="inlineStr">
+        <is>
+          <t>The new failures automation creates can be designed against with alarms and backups, and every safety-critical industry has done so.</t>
+        </is>
+      </c>
+      <c r="G602" s="4" t="inlineStr">
+        <is>
+          <t>adding-automation-critical-systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="4" t="inlineStr">
+        <is>
+          <t>free-trade-other-countries</t>
+        </is>
+      </c>
+      <c r="C603" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D603" s="4" t="inlineStr">
+        <is>
+          <t>Free trade with other countries makes ordinary people in a country better off overall, even when some industries lose.</t>
+        </is>
+      </c>
+      <c r="F603" s="5" t="inlineStr">
+        <is>
+          <t>economics</t>
+        </is>
+      </c>
+      <c r="W603" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether small savings spread across every shopper outweigh heavy losses concentrated on particular towns and workers.</t>
+        </is>
+      </c>
+      <c r="AA603" s="5" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AB603" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="4" t="inlineStr">
+        <is>
+          <t>buying-goods-wherever-made</t>
+        </is>
+      </c>
+      <c r="C604" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D604" s="4" t="inlineStr">
+        <is>
+          <t>Buying goods from wherever they are made cheapest lowers prices for everyone, and lower prices raise living standards as surely as higher wages do.</t>
+        </is>
+      </c>
+      <c r="G604" s="4" t="inlineStr">
+        <is>
+          <t>free-trade-other-countries</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="4" t="inlineStr">
+        <is>
+          <t>competition-abroad-pushes-home</t>
+        </is>
+      </c>
+      <c r="C605" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D605" s="4" t="inlineStr">
+        <is>
+          <t>Competition from abroad pushes home companies to improve and to focus on what they do best, which raises productivity across the economy.</t>
+        </is>
+      </c>
+      <c r="G605" s="4" t="inlineStr">
+        <is>
+          <t>free-trade-other-countries</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="4" t="inlineStr">
+        <is>
+          <t>countries-trade-heavily-each</t>
+        </is>
+      </c>
+      <c r="C606" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D606" s="4" t="inlineStr">
+        <is>
+          <t>Countries that trade heavily with each other have strong reasons to keep the peace, so trade buys security as well as cheaper goods.</t>
+        </is>
+      </c>
+      <c r="G606" s="4" t="inlineStr">
+        <is>
+          <t>free-trade-other-countries</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="4" t="inlineStr">
+        <is>
+          <t>gains-trade-spread-thinly</t>
+        </is>
+      </c>
+      <c r="C607" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D607" s="4" t="inlineStr">
+        <is>
+          <t>The gains from trade are spread thinly across all consumers, while the losses land hard on particular towns and workers who rarely recover.</t>
+        </is>
+      </c>
+      <c r="G607" s="4" t="inlineStr">
+        <is>
+          <t>free-trade-other-countries</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="4" t="inlineStr">
+        <is>
+          <t>depending-other-countries-essential</t>
+        </is>
+      </c>
+      <c r="C608" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D608" s="4" t="inlineStr">
+        <is>
+          <t>Depending on other countries for essential goods leaves a nation exposed when supply chains break or a trading partner turns hostile.</t>
+        </is>
+      </c>
+      <c r="G608" s="4" t="inlineStr">
+        <is>
+          <t>free-trade-other-countries</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="4" t="inlineStr">
+        <is>
+          <t>trade-deals-let-companies</t>
+        </is>
+      </c>
+      <c r="C609" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D609" s="4" t="inlineStr">
+        <is>
+          <t>Trade deals let companies move production to places with weak labor and environmental rules, undercutting the protections workers at home fought for.</t>
+        </is>
+      </c>
+      <c r="G609" s="4" t="inlineStr">
+        <is>
+          <t>free-trade-other-countries</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="4" t="inlineStr">
+        <is>
+          <t>public-decisions-generally-rest</t>
+        </is>
+      </c>
+      <c r="C610" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D610" s="4" t="inlineStr">
+        <is>
+          <t>Public decisions should generally rest on measured statistics rather than on personal experience and anecdote.</t>
+        </is>
+      </c>
+      <c r="F610" s="5" t="inlineStr">
+        <is>
+          <t>statistics</t>
+        </is>
+      </c>
+      <c r="W610" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether counting captures enough of what matters to be trusted over what people have lived through.</t>
+        </is>
+      </c>
+      <c r="AA610" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB610" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="4" t="inlineStr">
+        <is>
+          <t>one-person-s-experience</t>
+        </is>
+      </c>
+      <c r="C611" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D611" s="4" t="inlineStr">
+        <is>
+          <t>One person's experience covers a tiny slice of the world, and a count across many people is the only way to see the whole of it.</t>
+        </is>
+      </c>
+      <c r="G611" s="4" t="inlineStr">
+        <is>
+          <t>public-decisions-generally-rest</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="4" t="inlineStr">
+        <is>
+          <t>anecdotes-remembered-repeated-because</t>
+        </is>
+      </c>
+      <c r="C612" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D612" s="4" t="inlineStr">
+        <is>
+          <t>Anecdotes are remembered and repeated because they are striking, and striking cases are by definition unusual.</t>
+        </is>
+      </c>
+      <c r="G612" s="4" t="inlineStr">
+        <is>
+          <t>public-decisions-generally-rest</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="4" t="inlineStr">
+        <is>
+          <t>number-can-checked-repeated</t>
+        </is>
+      </c>
+      <c r="C613" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D613" s="4" t="inlineStr">
+        <is>
+          <t>A number can be checked, repeated and argued about in the open, while a story cannot.</t>
+        </is>
+      </c>
+      <c r="G613" s="4" t="inlineStr">
+        <is>
+          <t>public-decisions-generally-rest</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="4" t="inlineStr">
+        <is>
+          <t>statistics-measure-only-what</t>
+        </is>
+      </c>
+      <c r="C614" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D614" s="4" t="inlineStr">
+        <is>
+          <t>Statistics measure only what is easy to count, so relying on them pushes decisions toward whatever fits in a spreadsheet.</t>
+        </is>
+      </c>
+      <c r="G614" s="4" t="inlineStr">
+        <is>
+          <t>public-decisions-generally-rest</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="4" t="inlineStr">
+        <is>
+          <t>averages-hide-people-edges</t>
+        </is>
+      </c>
+      <c r="C615" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D615" s="4" t="inlineStr">
+        <is>
+          <t>Averages hide the people at the edges, and the people at the edges are often the ones a decision hurts most.</t>
+        </is>
+      </c>
+      <c r="G615" s="4" t="inlineStr">
+        <is>
+          <t>public-decisions-generally-rest</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="4" t="inlineStr">
+        <is>
+          <t>whoever-chooses-what-gets</t>
+        </is>
+      </c>
+      <c r="C616" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D616" s="4" t="inlineStr">
+        <is>
+          <t>Whoever chooses what gets counted and how shapes the answer before anyone sees the number, so a statistic carries the choices of its maker.</t>
+        </is>
+      </c>
+      <c r="G616" s="4" t="inlineStr">
+        <is>
+          <t>public-decisions-generally-rest</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="4" t="inlineStr">
+        <is>
+          <t>statistics-quoted-public-debate</t>
+        </is>
+      </c>
+      <c r="C617" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D617" s="4" t="inlineStr">
+        <is>
+          <t>Statistics quoted in public debate tend to mislead more often than they inform.</t>
+        </is>
+      </c>
+      <c r="F617" s="5" t="inlineStr">
+        <is>
+          <t>statistics</t>
+        </is>
+      </c>
+      <c r="W617" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether the misuse of numbers in debate outweighs the corrections that only numbers make possible.</t>
+        </is>
+      </c>
+      <c r="AA617" s="5" t="n">
+        <v>-40</v>
+      </c>
+      <c r="AB617" s="5" t="inlineStr">
+        <is>
+          <t>Modest</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="4" t="inlineStr">
+        <is>
+          <t>figure-quoted-without-its</t>
+        </is>
+      </c>
+      <c r="C618" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D618" s="4" t="inlineStr">
+        <is>
+          <t>A figure quoted without its definition, its source and its margin of error sounds precise while saying almost nothing.</t>
+        </is>
+      </c>
+      <c r="G618" s="4" t="inlineStr">
+        <is>
+          <t>statistics-quoted-public-debate</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="4" t="inlineStr">
+        <is>
+          <t>advocates-pick-figure-helps</t>
+        </is>
+      </c>
+      <c r="C619" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D619" s="4" t="inlineStr">
+        <is>
+          <t>Advocates pick the figure that helps their case from the many measures available, so the number the public hears is selected rather than representative.</t>
+        </is>
+      </c>
+      <c r="G619" s="4" t="inlineStr">
+        <is>
+          <t>statistics-quoted-public-debate</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="4" t="inlineStr">
+        <is>
+          <t>most-readers-cannot-tell</t>
+        </is>
+      </c>
+      <c r="C620" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D620" s="4" t="inlineStr">
+        <is>
+          <t>Most readers cannot tell a sound statistic from a shaky one, so a shaky one carries the same authority as a sound one.</t>
+        </is>
+      </c>
+      <c r="G620" s="4" t="inlineStr">
+        <is>
+          <t>statistics-quoted-public-debate</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="4" t="inlineStr">
+        <is>
+          <t>most-figures-quoted-debate</t>
+        </is>
+      </c>
+      <c r="C621" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D621" s="4" t="inlineStr">
+        <is>
+          <t>Most figures quoted in debate are roughly right, and the misleading ones stand out in memory precisely because they are the exception rather than the rule.</t>
+        </is>
+      </c>
+      <c r="G621" s="4" t="inlineStr">
+        <is>
+          <t>statistics-quoted-public-debate</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="4" t="inlineStr">
+        <is>
+          <t>misuse-statistics-gets-exposed</t>
+        </is>
+      </c>
+      <c r="C622" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D622" s="4" t="inlineStr">
+        <is>
+          <t>Misuse of statistics gets exposed by other statistics, which is exactly how public claims get corrected over time.</t>
+        </is>
+      </c>
+      <c r="G622" s="4" t="inlineStr">
+        <is>
+          <t>statistics-quoted-public-debate</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="4" t="inlineStr">
+        <is>
+          <t>people-better-spotting-cherry</t>
+        </is>
+      </c>
+      <c r="C623" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D623" s="4" t="inlineStr">
+        <is>
+          <t>People are better at spotting a cherry-picked figure than critics assume, and the habit of asking where a number came from has spread.</t>
+        </is>
+      </c>
+      <c r="G623" s="4" t="inlineStr">
+        <is>
+          <t>statistics-quoted-public-debate</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="4" t="inlineStr">
+        <is>
+          <t>quoting-famous-person-generally</t>
+        </is>
+      </c>
+      <c r="C624" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D624" s="4" t="inlineStr">
+        <is>
+          <t>Quoting a famous person generally adds little to whether a claim is true.</t>
+        </is>
+      </c>
+      <c r="F624" s="5" t="inlineStr">
+        <is>
+          <t>quotations</t>
+        </is>
+      </c>
+      <c r="W624" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether the person behind a sentence is evidence for it or only an ornament on it.</t>
+        </is>
+      </c>
+      <c r="AA624" s="5" t="n">
+        <v>-60</v>
+      </c>
+      <c r="AB624" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="4" t="inlineStr">
+        <is>
+          <t>claim-true-false-because</t>
+        </is>
+      </c>
+      <c r="C625" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D625" s="4" t="inlineStr">
+        <is>
+          <t>A claim is true or false because of the reasons for it, and a name attached to it changes none of those reasons.</t>
+        </is>
+      </c>
+      <c r="G625" s="4" t="inlineStr">
+        <is>
+          <t>quoting-famous-person-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="4" t="inlineStr">
+        <is>
+          <t>famous-people-quoted-saying</t>
+        </is>
+      </c>
+      <c r="C626" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D626" s="4" t="inlineStr">
+        <is>
+          <t>Famous people are quoted for saying things well, not for being right, and fine wording is not evidence.</t>
+        </is>
+      </c>
+      <c r="G626" s="4" t="inlineStr">
+        <is>
+          <t>quoting-famous-person-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="4" t="inlineStr">
+        <is>
+          <t>nearly-any-position-can</t>
+        </is>
+      </c>
+      <c r="C627" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D627" s="4" t="inlineStr">
+        <is>
+          <t>Nearly any position can be backed by a quotation from someone famous, so quotations on opposite sides cancel each other out.</t>
+        </is>
+      </c>
+      <c r="G627" s="4" t="inlineStr">
+        <is>
+          <t>quoting-famous-person-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="4" t="inlineStr">
+        <is>
+          <t>quotation-person-deep-experience</t>
+        </is>
+      </c>
+      <c r="C628" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D628" s="4" t="inlineStr">
+        <is>
+          <t>A quotation from a person with deep experience in a field is a compressed report of that experience, and experience is a kind of evidence.</t>
+        </is>
+      </c>
+      <c r="G628" s="4" t="inlineStr">
+        <is>
+          <t>quoting-famous-person-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="4" t="inlineStr">
+        <is>
+          <t>person-whose-judgment-has</t>
+        </is>
+      </c>
+      <c r="C629" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D629" s="4" t="inlineStr">
+        <is>
+          <t>A person whose judgment has proven sound on many past questions is more likely to be right on the next one, so a view held by such a person is more likely to be true, not merely more respectable.</t>
+        </is>
+      </c>
+      <c r="G629" s="4" t="inlineStr">
+        <is>
+          <t>quoting-famous-person-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="4" t="inlineStr">
+        <is>
+          <t>saying-usually-becomes-famous</t>
+        </is>
+      </c>
+      <c r="C630" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D630" s="4" t="inlineStr">
+        <is>
+          <t>A saying usually becomes famous by surviving years of public criticism from people who wanted it to be wrong, so a widely quoted claim has been tested in a way an anonymous claim has not.</t>
+        </is>
+      </c>
+      <c r="G630" s="4" t="inlineStr">
+        <is>
+          <t>quoting-famous-person-generally</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="4" t="inlineStr">
+        <is>
+          <t>reference-works-generally-refuse</t>
+        </is>
+      </c>
+      <c r="C631" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D631" s="4" t="inlineStr">
+        <is>
+          <t>Reference works should generally refuse to print a quotation whose original source cannot be found.</t>
+        </is>
+      </c>
+      <c r="F631" s="5" t="inlineStr">
+        <is>
+          <t>quotations</t>
+        </is>
+      </c>
+      <c r="W631" s="4" t="inlineStr">
+        <is>
+          <t>The disagreement turns on whether an unverified saying is better printed with a label or left out altogether.</t>
+        </is>
+      </c>
+      <c r="AA631" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB631" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="4" t="inlineStr">
+        <is>
+          <t>saying-passed-wrong-name</t>
+        </is>
+      </c>
+      <c r="C632" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D632" s="4" t="inlineStr">
+        <is>
+          <t>A saying passed on with the wrong name attached rewrites who thought what, and a reference work exists to prevent exactly that.</t>
+        </is>
+      </c>
+      <c r="G632" s="4" t="inlineStr">
+        <is>
+          <t>reference-works-generally-refuse</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="4" t="inlineStr">
+        <is>
+          <t>misattributed-quotations-spread-fastest</t>
+        </is>
+      </c>
+      <c r="C633" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D633" s="4" t="inlineStr">
+        <is>
+          <t>Misattributed quotations spread fastest once a respected reference repeats them, so the reference is the point where the chain can be broken.</t>
+        </is>
+      </c>
+      <c r="G633" s="4" t="inlineStr">
+        <is>
+          <t>reference-works-generally-refuse</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="4" t="inlineStr">
+        <is>
+          <t>requiring-source-forces-editors</t>
+        </is>
+      </c>
+      <c r="C634" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D634" s="4" t="inlineStr">
+        <is>
+          <t>Requiring a source forces editors to check the wording as well, and many well-known quotations turn out to have been reworded along the way.</t>
+        </is>
+      </c>
+      <c r="G634" s="4" t="inlineStr">
+        <is>
+          <t>reference-works-generally-refuse</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="4" t="inlineStr">
+        <is>
+          <t>many-sayings-shaped-public</t>
+        </is>
+      </c>
+      <c r="C635" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D635" s="4" t="inlineStr">
+        <is>
+          <t>Many sayings that shaped public life survive only in memory or in secondhand reports, and dropping them makes the reference less useful without making it more honest.</t>
+        </is>
+      </c>
+      <c r="G635" s="4" t="inlineStr">
+        <is>
+          <t>reference-works-generally-refuse</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="4" t="inlineStr">
+        <is>
+          <t>quotation-can-clearly-labeled</t>
+        </is>
+      </c>
+      <c r="C636" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D636" s="4" t="inlineStr">
+        <is>
+          <t>A quotation can be clearly labeled as attributed rather than confirmed, which gives readers the truth without throwing the entry away.</t>
+        </is>
+      </c>
+      <c r="G636" s="4" t="inlineStr">
+        <is>
+          <t>reference-works-generally-refuse</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="4" t="inlineStr">
+        <is>
+          <t>insisting-written-original-favors</t>
+        </is>
+      </c>
+      <c r="C637" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D637" s="4" t="inlineStr">
+        <is>
+          <t>Insisting on a written original favors people whose words were recorded over those whose words were only spoken, which skews the record toward the already powerful.</t>
+        </is>
+      </c>
+      <c r="G637" s="4" t="inlineStr">
+        <is>
+          <t>reference-works-generally-refuse</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC490"/>
+  <autoFilter ref="A1:AC637"/>
   <dataValidations count="5">
     <dataValidation sqref="C2:C5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"belief,claim,linkage,importance,interest,uniqueness,equivalence,driver,media"</formula1>
@@ -16040,7 +19547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1182"/>
+  <dimension ref="A1:T1308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -43961,8 +47468,2780 @@
         </is>
       </c>
     </row>
+    <row r="1183">
+      <c r="A1183" s="4" t="inlineStr">
+        <is>
+          <t>companies-need-person-s</t>
+        </is>
+      </c>
+      <c r="B1183" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1183" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1183" s="4" t="inlineStr">
+        <is>
+          <t>information-about-person-belongs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" s="4" t="inlineStr">
+        <is>
+          <t>companies-need-person-s</t>
+        </is>
+      </c>
+      <c r="B1184" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1184" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1184" s="4" t="inlineStr">
+        <is>
+          <t>most-people-do-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" s="4" t="inlineStr">
+        <is>
+          <t>companies-need-person-s</t>
+        </is>
+      </c>
+      <c r="B1185" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1185" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1185" s="4" t="inlineStr">
+        <is>
+          <t>requiring-permission-before-collecting</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" s="4" t="inlineStr">
+        <is>
+          <t>companies-need-person-s</t>
+        </is>
+      </c>
+      <c r="B1186" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1186" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1186" s="4" t="inlineStr">
+        <is>
+          <t>advertising-pays-most-free</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="4" t="inlineStr">
+        <is>
+          <t>companies-need-person-s</t>
+        </is>
+      </c>
+      <c r="B1187" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1187" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1187" s="4" t="inlineStr">
+        <is>
+          <t>permission-screens-quickly-become</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" s="4" t="inlineStr">
+        <is>
+          <t>companies-need-person-s</t>
+        </is>
+      </c>
+      <c r="B1188" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1188" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1188" s="4" t="inlineStr">
+        <is>
+          <t>ads-matched-person-s</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="4" t="inlineStr">
+        <is>
+          <t>law-enforcement-able-read</t>
+        </is>
+      </c>
+      <c r="B1189" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1189" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1189" s="4" t="inlineStr">
+        <is>
+          <t>warrant-already-lets-police</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="4" t="inlineStr">
+        <is>
+          <t>law-enforcement-able-read</t>
+        </is>
+      </c>
+      <c r="B1190" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1190" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1190" s="4" t="inlineStr">
+        <is>
+          <t>people-who-plan-serious</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="4" t="inlineStr">
+        <is>
+          <t>law-enforcement-able-read</t>
+        </is>
+      </c>
+      <c r="B1191" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1191" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1191" s="4" t="inlineStr">
+        <is>
+          <t>letting-police-read-encrypted</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="4" t="inlineStr">
+        <is>
+          <t>law-enforcement-able-read</t>
+        </is>
+      </c>
+      <c r="B1192" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1192" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1192" s="4" t="inlineStr">
+        <is>
+          <t>there-no-way-build</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="4" t="inlineStr">
+        <is>
+          <t>law-enforcement-able-read</t>
+        </is>
+      </c>
+      <c r="B1193" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1193" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1193" s="4" t="inlineStr">
+        <is>
+          <t>warrants-issued-one-country</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" s="4" t="inlineStr">
+        <is>
+          <t>law-enforcement-able-read</t>
+        </is>
+      </c>
+      <c r="B1194" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1194" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1194" s="4" t="inlineStr">
+        <is>
+          <t>ordinary-people-businesses-journalists</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" s="4" t="inlineStr">
+        <is>
+          <t>new-movies-generally-open</t>
+        </is>
+      </c>
+      <c r="B1195" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1195" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1195" s="4" t="inlineStr">
+        <is>
+          <t>theater-run-gives-movie</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" s="4" t="inlineStr">
+        <is>
+          <t>new-movies-generally-open</t>
+        </is>
+      </c>
+      <c r="B1196" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1196" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1196" s="4" t="inlineStr">
+        <is>
+          <t>seeing-film-big-screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" s="4" t="inlineStr">
+        <is>
+          <t>new-movies-generally-open</t>
+        </is>
+      </c>
+      <c r="B1197" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1197" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1197" s="4" t="inlineStr">
+        <is>
+          <t>theaters-local-businesses-employ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" s="4" t="inlineStr">
+        <is>
+          <t>new-movies-generally-open</t>
+        </is>
+      </c>
+      <c r="B1198" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1198" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1198" s="4" t="inlineStr">
+        <is>
+          <t>families-rural-viewers-people</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" s="4" t="inlineStr">
+        <is>
+          <t>new-movies-generally-open</t>
+        </is>
+      </c>
+      <c r="B1199" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1199" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1199" s="4" t="inlineStr">
+        <is>
+          <t>piracy-fills-any-gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" s="4" t="inlineStr">
+        <is>
+          <t>new-movies-generally-open</t>
+        </is>
+      </c>
+      <c r="B1200" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1200" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1200" s="4" t="inlineStr">
+        <is>
+          <t>streaming-lets-small-unusual</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" s="4" t="inlineStr">
+        <is>
+          <t>studios-let-viewers-choose</t>
+        </is>
+      </c>
+      <c r="B1201" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1201" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1201" s="4" t="inlineStr">
+        <is>
+          <t>viewers-studios-decide-where</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" s="4" t="inlineStr">
+        <is>
+          <t>studios-let-viewers-choose</t>
+        </is>
+      </c>
+      <c r="B1202" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1202" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1202" s="4" t="inlineStr">
+        <is>
+          <t>tickets-parking-babysitting-make</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="4" t="inlineStr">
+        <is>
+          <t>studios-let-viewers-choose</t>
+        </is>
+      </c>
+      <c r="B1203" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1203" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1203" s="4" t="inlineStr">
+        <is>
+          <t>same-day-home-release</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="4" t="inlineStr">
+        <is>
+          <t>studios-let-viewers-choose</t>
+        </is>
+      </c>
+      <c r="B1204" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1204" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1204" s="4" t="inlineStr">
+        <is>
+          <t>same-day-home-release-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="4" t="inlineStr">
+        <is>
+          <t>studios-let-viewers-choose</t>
+        </is>
+      </c>
+      <c r="B1205" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1205" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1205" s="4" t="inlineStr">
+        <is>
+          <t>movies-watched-home-compete</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="4" t="inlineStr">
+        <is>
+          <t>studios-let-viewers-choose</t>
+        </is>
+      </c>
+      <c r="B1206" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1206" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1206" s="4" t="inlineStr">
+        <is>
+          <t>once-viewers-expect-every</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="4" t="inlineStr">
+        <is>
+          <t>cities-generally-redesign-streets</t>
+        </is>
+      </c>
+      <c r="B1207" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1207" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1207" s="4" t="inlineStr">
+        <is>
+          <t>whether-crash-kills-someone</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="4" t="inlineStr">
+        <is>
+          <t>cities-generally-redesign-streets</t>
+        </is>
+      </c>
+      <c r="B1208" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1208" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1208" s="4" t="inlineStr">
+        <is>
+          <t>streets-where-cars-move</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" s="4" t="inlineStr">
+        <is>
+          <t>cities-generally-redesign-streets</t>
+        </is>
+      </c>
+      <c r="B1209" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1209" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1209" s="4" t="inlineStr">
+        <is>
+          <t>redesigning-street-slow-cars</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" s="4" t="inlineStr">
+        <is>
+          <t>cities-generally-redesign-streets</t>
+        </is>
+      </c>
+      <c r="B1210" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1210" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1210" s="4" t="inlineStr">
+        <is>
+          <t>longer-trips-cost-workers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" s="4" t="inlineStr">
+        <is>
+          <t>cities-generally-redesign-streets</t>
+        </is>
+      </c>
+      <c r="B1211" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1211" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1211" s="4" t="inlineStr">
+        <is>
+          <t>slowing-main-road-pushes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" s="4" t="inlineStr">
+        <is>
+          <t>cities-generally-redesign-streets</t>
+        </is>
+      </c>
+      <c r="B1212" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1212" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1212" s="4" t="inlineStr">
+        <is>
+          <t>most-places-most-people</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" s="4" t="inlineStr">
+        <is>
+          <t>banning-sale-new-gasoline</t>
+        </is>
+      </c>
+      <c r="B1213" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1213" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1213" s="4" t="inlineStr">
+        <is>
+          <t>electric-cars-still-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" s="4" t="inlineStr">
+        <is>
+          <t>banning-sale-new-gasoline</t>
+        </is>
+      </c>
+      <c r="B1214" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1214" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1214" s="4" t="inlineStr">
+        <is>
+          <t>ban-new-gasoline-cars</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" s="4" t="inlineStr">
+        <is>
+          <t>banning-sale-new-gasoline</t>
+        </is>
+      </c>
+      <c r="B1215" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1215" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1215" s="4" t="inlineStr">
+        <is>
+          <t>mandates-get-ahead-what</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" s="4" t="inlineStr">
+        <is>
+          <t>banning-sale-new-gasoline</t>
+        </is>
+      </c>
+      <c r="B1216" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1216" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1216" s="4" t="inlineStr">
+        <is>
+          <t>automakers-charging-companies-only</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" s="4" t="inlineStr">
+        <is>
+          <t>banning-sale-new-gasoline</t>
+        </is>
+      </c>
+      <c r="B1217" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1217" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1217" s="4" t="inlineStr">
+        <is>
+          <t>every-gasoline-car-sold</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" s="4" t="inlineStr">
+        <is>
+          <t>banning-sale-new-gasoline</t>
+        </is>
+      </c>
+      <c r="B1218" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1218" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1218" s="4" t="inlineStr">
+        <is>
+          <t>past-safety-emissions-standards</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" s="4" t="inlineStr">
+        <is>
+          <t>long-prison-sentences-generally</t>
+        </is>
+      </c>
+      <c r="B1219" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1219" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1219" s="4" t="inlineStr">
+        <is>
+          <t>most-people-who-commit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" s="4" t="inlineStr">
+        <is>
+          <t>long-prison-sentences-generally</t>
+        </is>
+      </c>
+      <c r="B1220" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1220" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1220" s="4" t="inlineStr">
+        <is>
+          <t>young-men-commit-most</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" s="4" t="inlineStr">
+        <is>
+          <t>long-prison-sentences-generally</t>
+        </is>
+      </c>
+      <c r="B1221" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1221" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1221" s="4" t="inlineStr">
+        <is>
+          <t>money-spent-extra-years</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" s="4" t="inlineStr">
+        <is>
+          <t>long-prison-sentences-generally</t>
+        </is>
+      </c>
+      <c r="B1222" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1222" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1222" s="4" t="inlineStr">
+        <is>
+          <t>person-prison-cannot-commit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" s="4" t="inlineStr">
+        <is>
+          <t>long-prison-sentences-generally</t>
+        </is>
+      </c>
+      <c r="B1223" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1223" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1223" s="4" t="inlineStr">
+        <is>
+          <t>small-number-repeat-offenders</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" s="4" t="inlineStr">
+        <is>
+          <t>long-prison-sentences-generally</t>
+        </is>
+      </c>
+      <c r="B1224" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1224" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1224" s="4" t="inlineStr">
+        <is>
+          <t>being-caught-only-deters</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" s="4" t="inlineStr">
+        <is>
+          <t>judges-allowed-keep-suspects</t>
+        </is>
+      </c>
+      <c r="B1225" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1225" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1225" s="4" t="inlineStr">
+        <is>
+          <t>someone-arrested-violent-act</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" s="4" t="inlineStr">
+        <is>
+          <t>judges-allowed-keep-suspects</t>
+        </is>
+      </c>
+      <c r="B1226" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1226" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1226" s="4" t="inlineStr">
+        <is>
+          <t>bail-based-money-frees</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" s="4" t="inlineStr">
+        <is>
+          <t>judges-allowed-keep-suspects</t>
+        </is>
+      </c>
+      <c r="B1227" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1227" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1227" s="4" t="inlineStr">
+        <is>
+          <t>public-confidence-courts-falls</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" s="4" t="inlineStr">
+        <is>
+          <t>judges-allowed-keep-suspects</t>
+        </is>
+      </c>
+      <c r="B1228" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1228" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1228" s="4" t="inlineStr">
+        <is>
+          <t>person-who-has-been</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" s="4" t="inlineStr">
+        <is>
+          <t>judges-allowed-keep-suspects</t>
+        </is>
+      </c>
+      <c r="B1229" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1229" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1229" s="4" t="inlineStr">
+        <is>
+          <t>predicting-who-dangerous-guesswork</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" s="4" t="inlineStr">
+        <is>
+          <t>judges-allowed-keep-suspects</t>
+        </is>
+      </c>
+      <c r="B1230" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1230" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1230" s="4" t="inlineStr">
+        <is>
+          <t>even-few-weeks-jail</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" s="4" t="inlineStr">
+        <is>
+          <t>governments-put-protecting-environment</t>
+        </is>
+      </c>
+      <c r="B1231" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1231" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1231" s="4" t="inlineStr">
+        <is>
+          <t>damage-nature-often-cannot</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" s="4" t="inlineStr">
+        <is>
+          <t>governments-put-protecting-environment</t>
+        </is>
+      </c>
+      <c r="B1232" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1232" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1232" s="4" t="inlineStr">
+        <is>
+          <t>growth-uses-up-resources</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" s="4" t="inlineStr">
+        <is>
+          <t>governments-put-protecting-environment</t>
+        </is>
+      </c>
+      <c r="B1233" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1233" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1233" s="4" t="inlineStr">
+        <is>
+          <t>markets-reward-growth-but</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" s="4" t="inlineStr">
+        <is>
+          <t>governments-put-protecting-environment</t>
+        </is>
+      </c>
+      <c r="B1234" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1234" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1234" s="4" t="inlineStr">
+        <is>
+          <t>countries-clean-today-mostly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" s="4" t="inlineStr">
+        <is>
+          <t>governments-put-protecting-environment</t>
+        </is>
+      </c>
+      <c r="B1235" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1235" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1235" s="4" t="inlineStr">
+        <is>
+          <t>strict-environmental-limits-one</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" s="4" t="inlineStr">
+        <is>
+          <t>governments-put-protecting-environment</t>
+        </is>
+      </c>
+      <c r="B1236" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1236" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1236" s="4" t="inlineStr">
+        <is>
+          <t>rules-put-environment-ahead</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" s="4" t="inlineStr">
+        <is>
+          <t>technology-tends-solve-environmental</t>
+        </is>
+      </c>
+      <c r="B1237" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1237" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1237" s="4" t="inlineStr">
+        <is>
+          <t>past-resource-scares-tended</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" s="4" t="inlineStr">
+        <is>
+          <t>technology-tends-solve-environmental</t>
+        </is>
+      </c>
+      <c r="B1238" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1238" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1238" s="4" t="inlineStr">
+        <is>
+          <t>restrictions-daily-life-unpopular</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" s="4" t="inlineStr">
+        <is>
+          <t>technology-tends-solve-environmental</t>
+        </is>
+      </c>
+      <c r="B1239" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1239" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1239" s="4" t="inlineStr">
+        <is>
+          <t>rule-freezes-today-s</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" s="4" t="inlineStr">
+        <is>
+          <t>technology-tends-solve-environmental</t>
+        </is>
+      </c>
+      <c r="B1240" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1240" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1240" s="4" t="inlineStr">
+        <is>
+          <t>new-technology-arrives-its</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" s="4" t="inlineStr">
+        <is>
+          <t>technology-tends-solve-environmental</t>
+        </is>
+      </c>
+      <c r="B1241" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1241" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1241" s="4" t="inlineStr">
+        <is>
+          <t>new-technology-often-used</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" s="4" t="inlineStr">
+        <is>
+          <t>technology-tends-solve-environmental</t>
+        </is>
+      </c>
+      <c r="B1242" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1242" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1242" s="4" t="inlineStr">
+        <is>
+          <t>clean-technologies-did-succeed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" s="4" t="inlineStr">
+        <is>
+          <t>longer-prison-sentences-generally</t>
+        </is>
+      </c>
+      <c r="B1243" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1243" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1243" s="4" t="inlineStr">
+        <is>
+          <t>person-who-prison-cannot</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" s="4" t="inlineStr">
+        <is>
+          <t>longer-prison-sentences-generally</t>
+        </is>
+      </c>
+      <c r="B1244" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1244" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1244" s="4" t="inlineStr">
+        <is>
+          <t>adding-years-sentence-raises</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" s="4" t="inlineStr">
+        <is>
+          <t>longer-prison-sentences-generally</t>
+        </is>
+      </c>
+      <c r="B1245" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1245" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1245" s="4" t="inlineStr">
+        <is>
+          <t>few-repeat-offenders-account</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" s="4" t="inlineStr">
+        <is>
+          <t>longer-prison-sentences-generally</t>
+        </is>
+      </c>
+      <c r="B1246" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1246" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1246" s="4" t="inlineStr">
+        <is>
+          <t>most-people-age-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" s="4" t="inlineStr">
+        <is>
+          <t>longer-prison-sentences-generally</t>
+        </is>
+      </c>
+      <c r="B1247" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1247" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1247" s="4" t="inlineStr">
+        <is>
+          <t>prison-teaches-criminal-skills</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" s="4" t="inlineStr">
+        <is>
+          <t>longer-prison-sentences-generally</t>
+        </is>
+      </c>
+      <c r="B1248" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1248" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1248" s="4" t="inlineStr">
+        <is>
+          <t>money-spent-extra-years-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" s="4" t="inlineStr">
+        <is>
+          <t>police-departments-spend-more</t>
+        </is>
+      </c>
+      <c r="B1249" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1249" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1249" s="4" t="inlineStr">
+        <is>
+          <t>arrest-happens-after-someone</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" s="4" t="inlineStr">
+        <is>
+          <t>police-departments-spend-more</t>
+        </is>
+      </c>
+      <c r="B1250" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1250" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1250" s="4" t="inlineStr">
+        <is>
+          <t>arrests-minor-offenses-leave</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" s="4" t="inlineStr">
+        <is>
+          <t>police-departments-spend-more</t>
+        </is>
+      </c>
+      <c r="B1251" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1251" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1251" s="4" t="inlineStr">
+        <is>
+          <t>communities-share-information-police</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" s="4" t="inlineStr">
+        <is>
+          <t>police-departments-spend-more</t>
+        </is>
+      </c>
+      <c r="B1252" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1252" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1252" s="4" t="inlineStr">
+        <is>
+          <t>prevention-hard-measure-easy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" s="4" t="inlineStr">
+        <is>
+          <t>police-departments-spend-more</t>
+        </is>
+      </c>
+      <c r="B1253" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1253" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1253" s="4" t="inlineStr">
+        <is>
+          <t>people-who-have-already</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" s="4" t="inlineStr">
+        <is>
+          <t>police-departments-spend-more</t>
+        </is>
+      </c>
+      <c r="B1254" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1254" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1254" s="4" t="inlineStr">
+        <is>
+          <t>surest-form-prevention-certainty</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" s="4" t="inlineStr">
+        <is>
+          <t>heavy-digital-editing-generally</t>
+        </is>
+      </c>
+      <c r="B1255" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1255" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1255" s="4" t="inlineStr">
+        <is>
+          <t>every-photograph-already-involves</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" s="4" t="inlineStr">
+        <is>
+          <t>heavy-digital-editing-generally</t>
+        </is>
+      </c>
+      <c r="B1256" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1256" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1256" s="4" t="inlineStr">
+        <is>
+          <t>printing-developing-have-always</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" s="4" t="inlineStr">
+        <is>
+          <t>heavy-digital-editing-generally</t>
+        </is>
+      </c>
+      <c r="B1257" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1257" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1257" s="4" t="inlineStr">
+        <is>
+          <t>what-viewers-respond-finished</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" s="4" t="inlineStr">
+        <is>
+          <t>heavy-digital-editing-generally</t>
+        </is>
+      </c>
+      <c r="B1258" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1258" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1258" s="4" t="inlineStr">
+        <is>
+          <t>ordinary-people-trust-photograph</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" s="4" t="inlineStr">
+        <is>
+          <t>heavy-digital-editing-generally</t>
+        </is>
+      </c>
+      <c r="B1259" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1259" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1259" s="4" t="inlineStr">
+        <is>
+          <t>photograph-s-one-special</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" s="4" t="inlineStr">
+        <is>
+          <t>heavy-digital-editing-generally</t>
+        </is>
+      </c>
+      <c r="B1260" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1260" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1260" s="4" t="inlineStr">
+        <is>
+          <t>when-any-part-picture</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" s="4" t="inlineStr">
+        <is>
+          <t>photograph-s-worth-clearly</t>
+        </is>
+      </c>
+      <c r="B1261" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1261" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1261" s="4" t="inlineStr">
+        <is>
+          <t>photographs-people-return-across</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" s="4" t="inlineStr">
+        <is>
+          <t>photograph-s-worth-clearly</t>
+        </is>
+      </c>
+      <c r="B1262" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1262" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1262" s="4" t="inlineStr">
+        <is>
+          <t>artistry-can-produced-demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" s="4" t="inlineStr">
+        <is>
+          <t>photograph-s-worth-clearly</t>
+        </is>
+      </c>
+      <c r="B1263" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1263" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1263" s="4" t="inlineStr">
+        <is>
+          <t>when-striking-image-turns</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" s="4" t="inlineStr">
+        <is>
+          <t>photograph-s-worth-clearly</t>
+        </is>
+      </c>
+      <c r="B1264" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1264" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1264" s="4" t="inlineStr">
+        <is>
+          <t>millions-truthful-snapshots-taken</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" s="4" t="inlineStr">
+        <is>
+          <t>photograph-s-worth-clearly</t>
+        </is>
+      </c>
+      <c r="B1265" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1265" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1265" s="4" t="inlineStr">
+        <is>
+          <t>choosing-where-stand-what</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" s="4" t="inlineStr">
+        <is>
+          <t>photograph-s-worth-clearly</t>
+        </is>
+      </c>
+      <c r="B1266" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1266" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1266" s="4" t="inlineStr">
+        <is>
+          <t>portraits-still-lifes-fashion</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" s="4" t="inlineStr">
+        <is>
+          <t>self-driving-cars-can</t>
+        </is>
+      </c>
+      <c r="B1267" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1267" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1267" s="4" t="inlineStr">
+        <is>
+          <t>most-crashes-come-distraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" s="4" t="inlineStr">
+        <is>
+          <t>self-driving-cars-can</t>
+        </is>
+      </c>
+      <c r="B1268" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1268" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1268" s="4" t="inlineStr">
+        <is>
+          <t>machine-driver-watches-every</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" s="4" t="inlineStr">
+        <is>
+          <t>self-driving-cars-can</t>
+        </is>
+      </c>
+      <c r="B1269" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1269" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1269" s="4" t="inlineStr">
+        <is>
+          <t>when-one-automated-car</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" s="4" t="inlineStr">
+        <is>
+          <t>self-driving-cars-can</t>
+        </is>
+      </c>
+      <c r="B1270" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1270" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1270" s="4" t="inlineStr">
+        <is>
+          <t>roads-full-unusual-situations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" s="4" t="inlineStr">
+        <is>
+          <t>self-driving-cars-can</t>
+        </is>
+      </c>
+      <c r="B1271" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1271" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1271" s="4" t="inlineStr">
+        <is>
+          <t>ordinary-roads-self-driving</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" s="4" t="inlineStr">
+        <is>
+          <t>self-driving-cars-can</t>
+        </is>
+      </c>
+      <c r="B1272" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1272" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1272" s="4" t="inlineStr">
+        <is>
+          <t>sensors-fail-rain-snow</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" s="4" t="inlineStr">
+        <is>
+          <t>adding-automation-critical-systems</t>
+        </is>
+      </c>
+      <c r="B1273" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1273" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1273" s="4" t="inlineStr">
+        <is>
+          <t>automation-hides-what-system</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" s="4" t="inlineStr">
+        <is>
+          <t>adding-automation-critical-systems</t>
+        </is>
+      </c>
+      <c r="B1274" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1274" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1274" s="4" t="inlineStr">
+        <is>
+          <t>operators-who-rarely-act</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" s="4" t="inlineStr">
+        <is>
+          <t>adding-automation-critical-systems</t>
+        </is>
+      </c>
+      <c r="B1275" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1275" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1275" s="4" t="inlineStr">
+        <is>
+          <t>automated-parts-copied-everywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" s="4" t="inlineStr">
+        <is>
+          <t>adding-automation-critical-systems</t>
+        </is>
+      </c>
+      <c r="B1276" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1276" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1276" s="4" t="inlineStr">
+        <is>
+          <t>machine-s-possible-failures</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" s="4" t="inlineStr">
+        <is>
+          <t>adding-automation-critical-systems</t>
+        </is>
+      </c>
+      <c r="B1277" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1277" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1277" s="4" t="inlineStr">
+        <is>
+          <t>automated-failures-logged-repeatable</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" s="4" t="inlineStr">
+        <is>
+          <t>adding-automation-critical-systems</t>
+        </is>
+      </c>
+      <c r="B1278" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1278" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1278" s="4" t="inlineStr">
+        <is>
+          <t>new-failures-automation-creates</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" s="4" t="inlineStr">
+        <is>
+          <t>free-trade-other-countries</t>
+        </is>
+      </c>
+      <c r="B1279" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1279" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1279" s="4" t="inlineStr">
+        <is>
+          <t>buying-goods-wherever-made</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" s="4" t="inlineStr">
+        <is>
+          <t>free-trade-other-countries</t>
+        </is>
+      </c>
+      <c r="B1280" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1280" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1280" s="4" t="inlineStr">
+        <is>
+          <t>competition-abroad-pushes-home</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" s="4" t="inlineStr">
+        <is>
+          <t>free-trade-other-countries</t>
+        </is>
+      </c>
+      <c r="B1281" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1281" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1281" s="4" t="inlineStr">
+        <is>
+          <t>countries-trade-heavily-each</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" s="4" t="inlineStr">
+        <is>
+          <t>free-trade-other-countries</t>
+        </is>
+      </c>
+      <c r="B1282" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1282" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1282" s="4" t="inlineStr">
+        <is>
+          <t>gains-trade-spread-thinly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" s="4" t="inlineStr">
+        <is>
+          <t>free-trade-other-countries</t>
+        </is>
+      </c>
+      <c r="B1283" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1283" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1283" s="4" t="inlineStr">
+        <is>
+          <t>depending-other-countries-essential</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" s="4" t="inlineStr">
+        <is>
+          <t>free-trade-other-countries</t>
+        </is>
+      </c>
+      <c r="B1284" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1284" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1284" s="4" t="inlineStr">
+        <is>
+          <t>trade-deals-let-companies</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" s="4" t="inlineStr">
+        <is>
+          <t>public-decisions-generally-rest</t>
+        </is>
+      </c>
+      <c r="B1285" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1285" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1285" s="4" t="inlineStr">
+        <is>
+          <t>one-person-s-experience</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" s="4" t="inlineStr">
+        <is>
+          <t>public-decisions-generally-rest</t>
+        </is>
+      </c>
+      <c r="B1286" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1286" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1286" s="4" t="inlineStr">
+        <is>
+          <t>anecdotes-remembered-repeated-because</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" s="4" t="inlineStr">
+        <is>
+          <t>public-decisions-generally-rest</t>
+        </is>
+      </c>
+      <c r="B1287" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1287" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1287" s="4" t="inlineStr">
+        <is>
+          <t>number-can-checked-repeated</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" s="4" t="inlineStr">
+        <is>
+          <t>public-decisions-generally-rest</t>
+        </is>
+      </c>
+      <c r="B1288" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1288" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1288" s="4" t="inlineStr">
+        <is>
+          <t>statistics-measure-only-what</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" s="4" t="inlineStr">
+        <is>
+          <t>public-decisions-generally-rest</t>
+        </is>
+      </c>
+      <c r="B1289" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1289" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1289" s="4" t="inlineStr">
+        <is>
+          <t>averages-hide-people-edges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" s="4" t="inlineStr">
+        <is>
+          <t>public-decisions-generally-rest</t>
+        </is>
+      </c>
+      <c r="B1290" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1290" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1290" s="4" t="inlineStr">
+        <is>
+          <t>whoever-chooses-what-gets</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" s="4" t="inlineStr">
+        <is>
+          <t>statistics-quoted-public-debate</t>
+        </is>
+      </c>
+      <c r="B1291" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1291" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1291" s="4" t="inlineStr">
+        <is>
+          <t>figure-quoted-without-its</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" s="4" t="inlineStr">
+        <is>
+          <t>statistics-quoted-public-debate</t>
+        </is>
+      </c>
+      <c r="B1292" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1292" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1292" s="4" t="inlineStr">
+        <is>
+          <t>advocates-pick-figure-helps</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" s="4" t="inlineStr">
+        <is>
+          <t>statistics-quoted-public-debate</t>
+        </is>
+      </c>
+      <c r="B1293" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1293" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1293" s="4" t="inlineStr">
+        <is>
+          <t>most-readers-cannot-tell</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" s="4" t="inlineStr">
+        <is>
+          <t>statistics-quoted-public-debate</t>
+        </is>
+      </c>
+      <c r="B1294" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1294" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1294" s="4" t="inlineStr">
+        <is>
+          <t>most-figures-quoted-debate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" s="4" t="inlineStr">
+        <is>
+          <t>statistics-quoted-public-debate</t>
+        </is>
+      </c>
+      <c r="B1295" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1295" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1295" s="4" t="inlineStr">
+        <is>
+          <t>misuse-statistics-gets-exposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" s="4" t="inlineStr">
+        <is>
+          <t>statistics-quoted-public-debate</t>
+        </is>
+      </c>
+      <c r="B1296" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1296" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1296" s="4" t="inlineStr">
+        <is>
+          <t>people-better-spotting-cherry</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" s="4" t="inlineStr">
+        <is>
+          <t>quoting-famous-person-generally</t>
+        </is>
+      </c>
+      <c r="B1297" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1297" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1297" s="4" t="inlineStr">
+        <is>
+          <t>claim-true-false-because</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" s="4" t="inlineStr">
+        <is>
+          <t>quoting-famous-person-generally</t>
+        </is>
+      </c>
+      <c r="B1298" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1298" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1298" s="4" t="inlineStr">
+        <is>
+          <t>famous-people-quoted-saying</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" s="4" t="inlineStr">
+        <is>
+          <t>quoting-famous-person-generally</t>
+        </is>
+      </c>
+      <c r="B1299" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1299" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1299" s="4" t="inlineStr">
+        <is>
+          <t>nearly-any-position-can</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" s="4" t="inlineStr">
+        <is>
+          <t>quoting-famous-person-generally</t>
+        </is>
+      </c>
+      <c r="B1300" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1300" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1300" s="4" t="inlineStr">
+        <is>
+          <t>quotation-person-deep-experience</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" s="4" t="inlineStr">
+        <is>
+          <t>quoting-famous-person-generally</t>
+        </is>
+      </c>
+      <c r="B1301" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1301" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1301" s="4" t="inlineStr">
+        <is>
+          <t>person-whose-judgment-has</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" s="4" t="inlineStr">
+        <is>
+          <t>quoting-famous-person-generally</t>
+        </is>
+      </c>
+      <c r="B1302" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1302" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1302" s="4" t="inlineStr">
+        <is>
+          <t>saying-usually-becomes-famous</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" s="4" t="inlineStr">
+        <is>
+          <t>reference-works-generally-refuse</t>
+        </is>
+      </c>
+      <c r="B1303" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1303" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1303" s="4" t="inlineStr">
+        <is>
+          <t>saying-passed-wrong-name</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" s="4" t="inlineStr">
+        <is>
+          <t>reference-works-generally-refuse</t>
+        </is>
+      </c>
+      <c r="B1304" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1304" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1304" s="4" t="inlineStr">
+        <is>
+          <t>misattributed-quotations-spread-fastest</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" s="4" t="inlineStr">
+        <is>
+          <t>reference-works-generally-refuse</t>
+        </is>
+      </c>
+      <c r="B1305" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1305" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1305" s="4" t="inlineStr">
+        <is>
+          <t>requiring-source-forces-editors</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" s="4" t="inlineStr">
+        <is>
+          <t>reference-works-generally-refuse</t>
+        </is>
+      </c>
+      <c r="B1306" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1306" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1306" s="4" t="inlineStr">
+        <is>
+          <t>many-sayings-shaped-public</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" s="4" t="inlineStr">
+        <is>
+          <t>reference-works-generally-refuse</t>
+        </is>
+      </c>
+      <c r="B1307" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1307" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1307" s="4" t="inlineStr">
+        <is>
+          <t>quotation-can-clearly-labeled</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" s="4" t="inlineStr">
+        <is>
+          <t>reference-works-generally-refuse</t>
+        </is>
+      </c>
+      <c r="B1308" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1308" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1308" s="4" t="inlineStr">
+        <is>
+          <t>insisting-written-original-favors</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T1182"/>
+  <autoFilter ref="A1:T1308"/>
   <dataValidations count="2">
     <dataValidation sqref="B2:B5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"argument,assumption,bias,category,cba,common,component,compromise,criteria,criterion,definition,direction,dispute,downstream,engagement,evidence,falsify,impact,interest,interest_listing,law,long_term,media,motive,obstacle,person,prediction,related,rung,shared_interest,short_term,similar,stack,strength,topic_media,topic_values,upstream,value"</formula1>
@@ -44288,6 +50567,16 @@
           <t>computers-and-internet</t>
         </is>
       </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>How personal information is collected, stored, shared and protected by companies and governments, and what people can do about it.</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>favors stronger limits on collecting and using personal data; negative favors freer collection and access.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -44458,6 +50747,16 @@
           <t>entertainment</t>
         </is>
       </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Feature films and the business that makes, releases and shows them, from theaters to streaming services.</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>favors keeping movies theater-first, with a period on the big screen before they reach homes; negative favors releasing new movies to homes and streaming services right away.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -44607,6 +50906,16 @@
           <t>recreation-and-sports</t>
         </is>
       </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Autos covers cars and driving: how vehicles are built, powered and regulated, and how much of daily life should depend on them.</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>favors fewer restrictions on cars and drivers and a larger role for driving; negative favors more regulation of cars and a shift toward other ways of getting around.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -44814,6 +51123,16 @@
           <t>government</t>
         </is>
       </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>How laws are enforced and judged, including policing, courts, bail, and punishment.</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>favors tougher enforcement and harsher punishment; negative favors restraint, leniency, and rehabilitation.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -44977,6 +51296,16 @@
           <t>society-and-culture</t>
         </is>
       </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Environment covers how people should use, protect, and share natural resources such as land, air, water, wildlife, and the climate.</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>favors stronger limits on human activity to protect nature, negative favors fewer limits and more trust in growth and technology to handle environmental problems.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -45028,6 +51357,16 @@
           <t>society-and-culture</t>
         </is>
       </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Crime and Justice covers how society should prevent crime, punish people who commit it, and treat both victims and the accused.</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>favors tougher enforcement and longer punishment, negative favors prevention, rehabilitation, and limits on the power of police and courts.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -45157,6 +51496,16 @@
           <t>arts-and-humanities</t>
         </is>
       </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>Photography covers how pictures are made with a camera, how they are edited and shown, and how they should be judged as art or as records.</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>favors treating photography as an art defined by the photographer's choices and editing; negative favors treating photography as a record valued for showing what was really in front of the lens.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -45296,6 +51645,16 @@
           <t>science</t>
         </is>
       </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Engineering covers what is known about designing and building machines, structures and systems that work reliably in the real world.</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>favors trusting complex engineered systems and automating human tasks; negative favors caution about complexity and keeping humans in control.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -45425,6 +51784,16 @@
           <t>social-science</t>
         </is>
       </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>How people produce, trade, and share goods and money, and what government should do about markets, prices, and wages.</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>favors more government action to steer markets and share income; negative favors leaving more to free markets and private choice.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -45493,6 +51862,16 @@
           <t>reference</t>
         </is>
       </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>How statistics are produced, reported and used in public argument, and how much trust they deserve compared with other ways of knowing.</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>favors treating measured statistics as trustworthy guides to public decisions, negative favors treating them with suspicion and giving more weight to experience, judgment and other kinds of knowledge.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -45508,6 +51887,16 @@
       <c r="C79" s="4" t="inlineStr">
         <is>
           <t>reference</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>How quotations are attributed, checked and used as authority in argument and in reference works.</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>holds that who said something matters, so quotations must be traced and weighed by their source, negative holds that a quotation's origin and speaker matter little compared with the words themselves.</t>
         </is>
       </c>
     </row>

--- a/tools/static-site/ISE_Data_Entry.xlsx
+++ b/tools/static-site/ISE_Data_Entry.xlsx
@@ -13,8 +13,8 @@
     <sheet name="topics" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'pages'!$A$1:$AC$1099</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'edges'!$A$1:$T$1704</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'pages'!$A$1:$AC$1215</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'edges'!$A$1:$T$1816</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'topics'!$A$1:$F$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -859,7 +859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC1099"/>
+  <dimension ref="A1:AC1215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -30539,8 +30539,2523 @@
         </is>
       </c>
     </row>
+    <row r="1100">
+      <c r="A1100" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+      <c r="C1100" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D1100" s="4" t="inlineStr">
+        <is>
+          <t>We should defend our fundamental freedoms, including freedom of speech.</t>
+        </is>
+      </c>
+      <c r="F1100" s="5" t="inlineStr">
+        <is>
+          <t>rights-and-liberty</t>
+        </is>
+      </c>
+      <c r="AB1100" s="5" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" s="4" t="inlineStr">
+        <is>
+          <t>open-dialogue-vital-informed</t>
+        </is>
+      </c>
+      <c r="C1101" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1101" s="4" t="inlineStr">
+        <is>
+          <t>Open dialogue is vital for informed decision-making and for holding power accountable.</t>
+        </is>
+      </c>
+      <c r="G1101" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" s="4" t="inlineStr">
+        <is>
+          <t>free-exchange-ideas-fosters</t>
+        </is>
+      </c>
+      <c r="C1102" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1102" s="4" t="inlineStr">
+        <is>
+          <t>The free exchange of ideas fosters creativity, scientific discovery, and cultural growth.</t>
+        </is>
+      </c>
+      <c r="G1102" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" s="4" t="inlineStr">
+        <is>
+          <t>free-speech-lets-people</t>
+        </is>
+      </c>
+      <c r="C1103" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1103" s="4" t="inlineStr">
+        <is>
+          <t>Free speech lets people express themselves without fear, which preserves personal dignity and self-expression.</t>
+        </is>
+      </c>
+      <c r="G1103" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" s="4" t="inlineStr">
+        <is>
+          <t>societies-strong-protections-speech</t>
+        </is>
+      </c>
+      <c r="C1104" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1104" s="4" t="inlineStr">
+        <is>
+          <t>Societies with strong protections for speech have historically thrived in liberty and innovation.</t>
+        </is>
+      </c>
+      <c r="G1104" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" s="4" t="inlineStr">
+        <is>
+          <t>defending-free-speech-upholds</t>
+        </is>
+      </c>
+      <c r="C1105" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1105" s="4" t="inlineStr">
+        <is>
+          <t>Defending free speech upholds universal principles of liberty and individual dignity.</t>
+        </is>
+      </c>
+      <c r="G1105" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" s="4" t="inlineStr">
+        <is>
+          <t>defending-free-speech-encourages</t>
+        </is>
+      </c>
+      <c r="C1106" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1106" s="4" t="inlineStr">
+        <is>
+          <t>Defending free speech encourages accountability and resistance to authoritarianism.</t>
+        </is>
+      </c>
+      <c r="G1106" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" s="4" t="inlineStr">
+        <is>
+          <t>defending-free-speech-promotes</t>
+        </is>
+      </c>
+      <c r="C1107" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1107" s="4" t="inlineStr">
+        <is>
+          <t>Defending free speech promotes a vibrant, informed society where ideas can flourish.</t>
+        </is>
+      </c>
+      <c r="G1107" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" s="4" t="inlineStr">
+        <is>
+          <t>defending-free-speech-ensures</t>
+        </is>
+      </c>
+      <c r="C1108" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1108" s="4" t="inlineStr">
+        <is>
+          <t>Defending free speech ensures long-term progress for society through dialogue and debate.</t>
+        </is>
+      </c>
+      <c r="G1108" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" s="4" t="inlineStr">
+        <is>
+          <t>unchecked-speech-can-spread</t>
+        </is>
+      </c>
+      <c r="C1109" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1109" s="4" t="inlineStr">
+        <is>
+          <t>Unchecked speech can spread misinformation, incite violence, and perpetuate hate.</t>
+        </is>
+      </c>
+      <c r="G1109" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" s="4" t="inlineStr">
+        <is>
+          <t>free-speech-protections-can</t>
+        </is>
+      </c>
+      <c r="C1110" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1110" s="4" t="inlineStr">
+        <is>
+          <t>Free speech protections can be exploited by those in power to drown out marginalized voices.</t>
+        </is>
+      </c>
+      <c r="G1110" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" s="4" t="inlineStr">
+        <is>
+          <t>defending-free-speech-may</t>
+        </is>
+      </c>
+      <c r="C1111" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1111" s="4" t="inlineStr">
+        <is>
+          <t>Defending free speech may allow harmful or false narratives to go unchecked.</t>
+        </is>
+      </c>
+      <c r="G1111" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" s="4" t="inlineStr">
+        <is>
+          <t>defending-free-speech-risks</t>
+        </is>
+      </c>
+      <c r="C1112" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1112" s="4" t="inlineStr">
+        <is>
+          <t>Defending free speech risks perpetuating systemic inequalities by empowering harmful speech.</t>
+        </is>
+      </c>
+      <c r="G1112" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" s="4" t="inlineStr">
+        <is>
+          <t>defending-free-speech-could</t>
+        </is>
+      </c>
+      <c r="C1113" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1113" s="4" t="inlineStr">
+        <is>
+          <t>Defending free speech could foster division or harm vulnerable populations.</t>
+        </is>
+      </c>
+      <c r="G1113" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" s="4" t="inlineStr">
+        <is>
+          <t>defending-free-speech-may-2</t>
+        </is>
+      </c>
+      <c r="C1114" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1114" s="4" t="inlineStr">
+        <is>
+          <t>Defending free speech may undermine trust in public institutions if misinformation spreads unchecked.</t>
+        </is>
+      </c>
+      <c r="G1114" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" s="4" t="inlineStr">
+        <is>
+          <t>supporters-need-individual-liberties</t>
+        </is>
+      </c>
+      <c r="C1115" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D1115" s="4" t="inlineStr">
+        <is>
+          <t>Supporters need individual liberties preserved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" s="4" t="inlineStr">
+        <is>
+          <t>supporters-need-accountability-transparency</t>
+        </is>
+      </c>
+      <c r="C1116" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D1116" s="4" t="inlineStr">
+        <is>
+          <t>Supporters need accountability and transparency in governance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" s="4" t="inlineStr">
+        <is>
+          <t>supporters-need-open-dialogue</t>
+        </is>
+      </c>
+      <c r="C1117" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D1117" s="4" t="inlineStr">
+        <is>
+          <t>Supporters need open dialogue and resistance to authoritarian control, which they believe have the power to transform society.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" s="4" t="inlineStr">
+        <is>
+          <t>opponents-need-public-safety</t>
+        </is>
+      </c>
+      <c r="C1118" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D1118" s="4" t="inlineStr">
+        <is>
+          <t>Opponents need public safety and mental well-being protected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" s="4" t="inlineStr">
+        <is>
+          <t>opponents-need-free-speech</t>
+        </is>
+      </c>
+      <c r="C1119" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D1119" s="4" t="inlineStr">
+        <is>
+          <t>Opponents need free speech kept from being exploited for harmful purposes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" s="4" t="inlineStr">
+        <is>
+          <t>opponents-need-safer-more</t>
+        </is>
+      </c>
+      <c r="C1120" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D1120" s="4" t="inlineStr">
+        <is>
+          <t>Opponents need a safer, more inclusive society where speech does not endanger others.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+      <c r="C1121" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D1121" s="4" t="inlineStr">
+        <is>
+          <t>We should defend the freedom of religion and the freedom from religion.</t>
+        </is>
+      </c>
+      <c r="F1121" s="5" t="inlineStr">
+        <is>
+          <t>rights-and-liberty</t>
+        </is>
+      </c>
+      <c r="AB1121" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" s="4" t="inlineStr">
+        <is>
+          <t>defending-freedom-religion-protects</t>
+        </is>
+      </c>
+      <c r="C1122" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1122" s="4" t="inlineStr">
+        <is>
+          <t>Defending freedom of and from religion protects personal beliefs and practices from interference by other people or the government.</t>
+        </is>
+      </c>
+      <c r="G1122" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" s="4" t="inlineStr">
+        <is>
+          <t>freedom-religion-allows-diverse</t>
+        </is>
+      </c>
+      <c r="C1123" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1123" s="4" t="inlineStr">
+        <is>
+          <t>Freedom of and from religion allows diverse religions and worldviews to coexist peacefully.</t>
+        </is>
+      </c>
+      <c r="G1123" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" s="4" t="inlineStr">
+        <is>
+          <t>defending-freedom-religion-prevents</t>
+        </is>
+      </c>
+      <c r="C1124" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1124" s="4" t="inlineStr">
+        <is>
+          <t>Defending freedom of and from religion prevents the government from imposing or endorsing religious practices.</t>
+        </is>
+      </c>
+      <c r="G1124" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" s="4" t="inlineStr">
+        <is>
+          <t>defending-both-freedom-religion</t>
+        </is>
+      </c>
+      <c r="C1125" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1125" s="4" t="inlineStr">
+        <is>
+          <t>Defending both freedom of religion and freedom from religion balances the rights of religious and non-religious people.</t>
+        </is>
+      </c>
+      <c r="G1125" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" s="4" t="inlineStr">
+        <is>
+          <t>defending-freedom-religion-respects</t>
+        </is>
+      </c>
+      <c r="C1126" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1126" s="4" t="inlineStr">
+        <is>
+          <t>Defending freedom of and from religion respects individual autonomy and diverse worldviews.</t>
+        </is>
+      </c>
+      <c r="G1126" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" s="4" t="inlineStr">
+        <is>
+          <t>defending-freedom-religion-prevents-2</t>
+        </is>
+      </c>
+      <c r="C1127" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1127" s="4" t="inlineStr">
+        <is>
+          <t>Defending freedom of and from religion prevents coercion and encourages an environment of voluntary belief and expression.</t>
+        </is>
+      </c>
+      <c r="G1127" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" s="4" t="inlineStr">
+        <is>
+          <t>defending-freedom-religion-encourages</t>
+        </is>
+      </c>
+      <c r="C1128" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1128" s="4" t="inlineStr">
+        <is>
+          <t>Defending freedom of and from religion encourages mutual respect and coexistence in diverse societies.</t>
+        </is>
+      </c>
+      <c r="G1128" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" s="4" t="inlineStr">
+        <is>
+          <t>defending-freedom-religion-preserves</t>
+        </is>
+      </c>
+      <c r="C1129" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1129" s="4" t="inlineStr">
+        <is>
+          <t>Defending freedom of and from religion preserves the basic principle that government stays neutral toward religion.</t>
+        </is>
+      </c>
+      <c r="G1129" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" s="4" t="inlineStr">
+        <is>
+          <t>defending-freedom-religion-means</t>
+        </is>
+      </c>
+      <c r="C1130" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1130" s="4" t="inlineStr">
+        <is>
+          <t>Defending freedom of and from religion means balancing religious freedoms against secular interests, which can lead to disagreements and legal battles.</t>
+        </is>
+      </c>
+      <c r="G1130" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" s="4" t="inlineStr">
+        <is>
+          <t>religious-groups-can-exploit</t>
+        </is>
+      </c>
+      <c r="C1131" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1131" s="4" t="inlineStr">
+        <is>
+          <t>Religious groups can exploit religious freedoms to justify harmful practices.</t>
+        </is>
+      </c>
+      <c r="G1131" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" s="4" t="inlineStr">
+        <is>
+          <t>defending-freedom-religion-can</t>
+        </is>
+      </c>
+      <c r="C1132" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1132" s="4" t="inlineStr">
+        <is>
+          <t>Defending freedom of and from religion can blur the line between government neutrality toward religion and government hostility to religion.</t>
+        </is>
+      </c>
+      <c r="G1132" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" s="4" t="inlineStr">
+        <is>
+          <t>complete-freedom-religion-could</t>
+        </is>
+      </c>
+      <c r="C1133" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1133" s="4" t="inlineStr">
+        <is>
+          <t>Complete freedom from religion could marginalize cultural traditions rooted in faith.</t>
+        </is>
+      </c>
+      <c r="G1133" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" s="4" t="inlineStr">
+        <is>
+          <t>defending-freedom-religion-may</t>
+        </is>
+      </c>
+      <c r="C1134" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1134" s="4" t="inlineStr">
+        <is>
+          <t>Defending freedom of and from religion may be seen as sidelining religious expression in public life.</t>
+        </is>
+      </c>
+      <c r="G1134" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" s="4" t="inlineStr">
+        <is>
+          <t>defending-freedom-religion-could</t>
+        </is>
+      </c>
+      <c r="C1135" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1135" s="4" t="inlineStr">
+        <is>
+          <t>Defending freedom of and from religion could let secularism dominate cultural norms and make society less inclusive for religious groups.</t>
+        </is>
+      </c>
+      <c r="G1135" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" s="4" t="inlineStr">
+        <is>
+          <t>defending-freedom-religion-risks</t>
+        </is>
+      </c>
+      <c r="C1136" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1136" s="4" t="inlineStr">
+        <is>
+          <t>Defending freedom of and from religion risks weakening the cultural and moral values historically rooted in religion.</t>
+        </is>
+      </c>
+      <c r="G1136" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" s="4" t="inlineStr">
+        <is>
+          <t>defending-freedom-religion-may-2</t>
+        </is>
+      </c>
+      <c r="C1137" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1137" s="4" t="inlineStr">
+        <is>
+          <t>Defending freedom of and from religion may foster division by putting secularism ahead of religious traditions.</t>
+        </is>
+      </c>
+      <c r="G1137" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" s="4" t="inlineStr">
+        <is>
+          <t>supporters-need-individual-liberties-2</t>
+        </is>
+      </c>
+      <c r="C1138" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D1138" s="4" t="inlineStr">
+        <is>
+          <t>Supporters need individual liberties protected and society kept harmonious.</t>
+        </is>
+      </c>
+      <c r="M1138" s="5" t="inlineStr">
+        <is>
+          <t>Equality, personal autonomy, and democratic principles</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" s="4" t="inlineStr">
+        <is>
+          <t>supporters-need-government-stay</t>
+        </is>
+      </c>
+      <c r="C1139" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D1139" s="4" t="inlineStr">
+        <is>
+          <t>Supporters need the government to stay neutral in matters of faith.</t>
+        </is>
+      </c>
+      <c r="M1139" s="5" t="inlineStr">
+        <is>
+          <t>Equality, personal autonomy, and democratic principles</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" s="4" t="inlineStr">
+        <is>
+          <t>opponents-need-dominant-cultural</t>
+        </is>
+      </c>
+      <c r="C1140" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D1140" s="4" t="inlineStr">
+        <is>
+          <t>Opponents need dominant cultural or religious traditions upheld.</t>
+        </is>
+      </c>
+      <c r="M1140" s="5" t="inlineStr">
+        <is>
+          <t>Societal cohesion, morality, and traditional values</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" s="4" t="inlineStr">
+        <is>
+          <t>opponents-need-religious-freedoms</t>
+        </is>
+      </c>
+      <c r="C1141" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D1141" s="4" t="inlineStr">
+        <is>
+          <t>Opponents need religious freedoms protected from what they see as secular overreach.</t>
+        </is>
+      </c>
+      <c r="M1141" s="5" t="inlineStr">
+        <is>
+          <t>Societal cohesion, morality, and traditional values</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+      <c r="C1142" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D1142" s="4" t="inlineStr">
+        <is>
+          <t>The United States should stop outsourcing and become a manufacturing superpower.</t>
+        </is>
+      </c>
+      <c r="F1142" s="5" t="inlineStr">
+        <is>
+          <t>trade</t>
+        </is>
+      </c>
+      <c r="AB1142" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" s="4" t="inlineStr">
+        <is>
+          <t>making-critical-goods-home</t>
+        </is>
+      </c>
+      <c r="C1143" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1143" s="4" t="inlineStr">
+        <is>
+          <t>Making critical goods at home reduces United States dependence on foreign nations.</t>
+        </is>
+      </c>
+      <c r="G1143" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" s="4" t="inlineStr">
+        <is>
+          <t>bringing-manufacturing-home-creates</t>
+        </is>
+      </c>
+      <c r="C1144" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1144" s="4" t="inlineStr">
+        <is>
+          <t>Bringing manufacturing home creates high-paying jobs and strengthens the middle class.</t>
+        </is>
+      </c>
+      <c r="G1144" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" s="4" t="inlineStr">
+        <is>
+          <t>domestic-production-ensures-secure</t>
+        </is>
+      </c>
+      <c r="C1145" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1145" s="4" t="inlineStr">
+        <is>
+          <t>Domestic production ensures a secure supply of essential items such as medical equipment and defense materials.</t>
+        </is>
+      </c>
+      <c r="G1145" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" s="4" t="inlineStr">
+        <is>
+          <t>producing-more-goods-home</t>
+        </is>
+      </c>
+      <c r="C1146" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1146" s="4" t="inlineStr">
+        <is>
+          <t>Producing more goods at home for export reduces the trade deficit.</t>
+        </is>
+      </c>
+      <c r="G1146" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" s="4" t="inlineStr">
+        <is>
+          <t>bringing-manufacturing-home-encourages</t>
+        </is>
+      </c>
+      <c r="C1147" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1147" s="4" t="inlineStr">
+        <is>
+          <t>Bringing manufacturing home encourages investment in automation and innovation so that American industry can compete globally.</t>
+        </is>
+      </c>
+      <c r="G1147" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" s="4" t="inlineStr">
+        <is>
+          <t>push-bring-manufacturing-home</t>
+        </is>
+      </c>
+      <c r="C1148" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1148" s="4" t="inlineStr">
+        <is>
+          <t>The push to bring manufacturing home focuses on fair wages and better working conditions for American workers.</t>
+        </is>
+      </c>
+      <c r="G1148" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" s="4" t="inlineStr">
+        <is>
+          <t>curbing-outsourcing-reduces-exploitation</t>
+        </is>
+      </c>
+      <c r="C1149" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1149" s="4" t="inlineStr">
+        <is>
+          <t>Curbing outsourcing reduces the exploitation of workers in low-wage countries.</t>
+        </is>
+      </c>
+      <c r="G1149" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" s="4" t="inlineStr">
+        <is>
+          <t>manufacturing-revival-promotes-fair</t>
+        </is>
+      </c>
+      <c r="C1150" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1150" s="4" t="inlineStr">
+        <is>
+          <t>A manufacturing revival promotes fair economic opportunity and reduces wealth gaps.</t>
+        </is>
+      </c>
+      <c r="G1150" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" s="4" t="inlineStr">
+        <is>
+          <t>manufacturing-revival-strengthens-united</t>
+        </is>
+      </c>
+      <c r="C1151" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1151" s="4" t="inlineStr">
+        <is>
+          <t>A manufacturing revival strengthens the United States economy in a way that benefits all citizens.</t>
+        </is>
+      </c>
+      <c r="G1151" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" s="4" t="inlineStr">
+        <is>
+          <t>domestic-production-often-more</t>
+        </is>
+      </c>
+      <c r="C1152" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1152" s="4" t="inlineStr">
+        <is>
+          <t>Domestic production is often more expensive because of higher wages and regulations, which raises consumer prices.</t>
+        </is>
+      </c>
+      <c r="G1152" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" s="4" t="inlineStr">
+        <is>
+          <t>reducing-outsourcing-harms-economies</t>
+        </is>
+      </c>
+      <c r="C1153" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1153" s="4" t="inlineStr">
+        <is>
+          <t>Reducing outsourcing harms economies that depend on United States contracts and could strain international relations.</t>
+        </is>
+      </c>
+      <c r="G1153" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" s="4" t="inlineStr">
+        <is>
+          <t>united-states-lacks-enough</t>
+        </is>
+      </c>
+      <c r="C1154" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1154" s="4" t="inlineStr">
+        <is>
+          <t>The United States lacks enough skilled labor for a large-scale manufacturing revival.</t>
+        </is>
+      </c>
+      <c r="G1154" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" s="4" t="inlineStr">
+        <is>
+          <t>increased-domestic-manufacturing-could</t>
+        </is>
+      </c>
+      <c r="C1155" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1155" s="4" t="inlineStr">
+        <is>
+          <t>Increased domestic manufacturing could lead to higher carbon emissions and resource depletion.</t>
+        </is>
+      </c>
+      <c r="G1155" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" s="4" t="inlineStr">
+        <is>
+          <t>protectionist-policies-end-outsourcing</t>
+        </is>
+      </c>
+      <c r="C1156" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1156" s="4" t="inlineStr">
+        <is>
+          <t>Protectionist policies to end outsourcing may disrupt global trade, harm international partnerships, and provoke retaliation that hurts United States exports.</t>
+        </is>
+      </c>
+      <c r="G1156" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" s="4" t="inlineStr">
+        <is>
+          <t>policies-discourage-outsourcing-may</t>
+        </is>
+      </c>
+      <c r="C1157" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1157" s="4" t="inlineStr">
+        <is>
+          <t>Policies that discourage outsourcing may violate free trade principles.</t>
+        </is>
+      </c>
+      <c r="G1157" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" s="4" t="inlineStr">
+        <is>
+          <t>curbing-outsourcing-could-harm</t>
+        </is>
+      </c>
+      <c r="C1158" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1158" s="4" t="inlineStr">
+        <is>
+          <t>Curbing outsourcing could harm foreign workers who depend on outsourced jobs to survive.</t>
+        </is>
+      </c>
+      <c r="G1158" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" s="4" t="inlineStr">
+        <is>
+          <t>domestic-manufacturing-could-raise</t>
+        </is>
+      </c>
+      <c r="C1159" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1159" s="4" t="inlineStr">
+        <is>
+          <t>Domestic manufacturing could raise consumer costs in a way that falls hardest on low-income families.</t>
+        </is>
+      </c>
+      <c r="G1159" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" s="4" t="inlineStr">
+        <is>
+          <t>pushing-become-manufacturing-superpower</t>
+        </is>
+      </c>
+      <c r="C1160" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1160" s="4" t="inlineStr">
+        <is>
+          <t>Pushing to become a manufacturing superpower risks fostering nationalism at the expense of global cooperation.</t>
+        </is>
+      </c>
+      <c r="G1160" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" s="4" t="inlineStr">
+        <is>
+          <t>supporters-need-economic-growth</t>
+        </is>
+      </c>
+      <c r="C1161" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D1161" s="4" t="inlineStr">
+        <is>
+          <t>Supporters need economic growth through job creation and infrastructure investment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" s="4" t="inlineStr">
+        <is>
+          <t>supporters-need-national-security</t>
+        </is>
+      </c>
+      <c r="C1162" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D1162" s="4" t="inlineStr">
+        <is>
+          <t>Supporters need national security and industrial independence protected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" s="4" t="inlineStr">
+        <is>
+          <t>supporters-need-self-sufficiency</t>
+        </is>
+      </c>
+      <c r="C1163" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D1163" s="4" t="inlineStr">
+        <is>
+          <t>Supporters need self-sufficiency, economic justice, and less reliance on foreign powers such as China.</t>
+        </is>
+      </c>
+      <c r="M1163" s="5" t="inlineStr">
+        <is>
+          <t>Self-sufficiency and economic justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" s="4" t="inlineStr">
+        <is>
+          <t>opponents-need-lower-costs</t>
+        </is>
+      </c>
+      <c r="C1164" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D1164" s="4" t="inlineStr">
+        <is>
+          <t>Opponents need lower costs for goods and services, which globalization provides.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" s="4" t="inlineStr">
+        <is>
+          <t>opponents-need-strong-international</t>
+        </is>
+      </c>
+      <c r="C1165" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D1165" s="4" t="inlineStr">
+        <is>
+          <t>Opponents need strong international trade partnerships maintained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" s="4" t="inlineStr">
+        <is>
+          <t>opponents-need-global-economic</t>
+        </is>
+      </c>
+      <c r="C1166" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D1166" s="4" t="inlineStr">
+        <is>
+          <t>Opponents need global economic interdependence and efficiency.</t>
+        </is>
+      </c>
+      <c r="M1166" s="5" t="inlineStr">
+        <is>
+          <t>Global interdependence and efficiency</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+      <c r="C1167" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D1167" s="4" t="inlineStr">
+        <is>
+          <t>Ranked-choice voting produces better electoral outcomes than plurality voting.</t>
+        </is>
+      </c>
+      <c r="F1167" s="5" t="inlineStr">
+        <is>
+          <t>democracy-and-rule-of-law</t>
+        </is>
+      </c>
+      <c r="W1167" s="4" t="inlineStr">
+        <is>
+          <t>The evidence gives ranked-choice voting a moderate advantage. The case that it removes the spoiler effect is strong and the record in Maine, Alaska and Australia is real; the strongest live objections are ballot exhaustion and the documented non-monotonicity failure in Burlington.</t>
+        </is>
+      </c>
+      <c r="AA1167" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB1167" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-eliminates</t>
+        </is>
+      </c>
+      <c r="C1168" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1168" s="4" t="inlineStr">
+        <is>
+          <t>Ranked-choice voting eliminates the spoiler effect.</t>
+        </is>
+      </c>
+      <c r="G1168" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-3</t>
+        </is>
+      </c>
+      <c r="C1169" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1169" s="4" t="inlineStr">
+        <is>
+          <t>Ranked-choice voting produces winners backed by a majority of voters.</t>
+        </is>
+      </c>
+      <c r="G1169" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-rewards</t>
+        </is>
+      </c>
+      <c r="C1170" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1170" s="4" t="inlineStr">
+        <is>
+          <t>Ranked-choice voting rewards candidates who build coalitions.</t>
+        </is>
+      </c>
+      <c r="G1170" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-makes</t>
+        </is>
+      </c>
+      <c r="C1171" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1171" s="4" t="inlineStr">
+        <is>
+          <t>Ranked-choice voting makes third parties more viable.</t>
+        </is>
+      </c>
+      <c r="G1171" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-causes</t>
+        </is>
+      </c>
+      <c r="C1172" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1172" s="4" t="inlineStr">
+        <is>
+          <t>Ranked-choice voting causes voter confusion and ballot errors.</t>
+        </is>
+      </c>
+      <c r="G1172" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" s="4" t="inlineStr">
+        <is>
+          <t>under-ranked-choice-voting</t>
+        </is>
+      </c>
+      <c r="C1173" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1173" s="4" t="inlineStr">
+        <is>
+          <t>Under ranked-choice voting, ballots become exhausted and stop counting before the final round.</t>
+        </is>
+      </c>
+      <c r="G1173" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-non</t>
+        </is>
+      </c>
+      <c r="C1174" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1174" s="4" t="inlineStr">
+        <is>
+          <t>Ranked-choice voting is non-monotonic, so ranking a candidate higher can cause that candidate to lose.</t>
+        </is>
+      </c>
+      <c r="G1174" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-adds</t>
+        </is>
+      </c>
+      <c r="C1175" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1175" s="4" t="inlineStr">
+        <is>
+          <t>Ranked-choice voting adds cost and complexity to running elections.</t>
+        </is>
+      </c>
+      <c r="G1175" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" s="4" t="inlineStr">
+        <is>
+          <t>maine-has-run-statewide</t>
+        </is>
+      </c>
+      <c r="C1176" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1176" s="4" t="inlineStr">
+        <is>
+          <t>Maine has run statewide ranked-choice voting in federal elections since 2018 with no chaotic or fraudulent outcomes.</t>
+        </is>
+      </c>
+      <c r="G1176" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" s="4" t="inlineStr">
+        <is>
+          <t>australia-has-used-preferential</t>
+        </is>
+      </c>
+      <c r="C1177" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1177" s="4" t="inlineStr">
+        <is>
+          <t>Australia has used preferential voting for its federal House since 1918 with stable majority outcomes.</t>
+        </is>
+      </c>
+      <c r="G1177" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" s="4" t="inlineStr">
+        <is>
+          <t>academic-simulations-find-ranked</t>
+        </is>
+      </c>
+      <c r="C1178" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1178" s="4" t="inlineStr">
+        <is>
+          <t>Academic simulations find that ranked-choice voting picks the candidate who would beat every rival head to head (the Condorcet winner) about 94% of the time, compared with about 70% for plurality voting.</t>
+        </is>
+      </c>
+      <c r="G1178" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" s="4" t="inlineStr">
+        <is>
+          <t>roughly-15-us-congressional</t>
+        </is>
+      </c>
+      <c r="C1179" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1179" s="4" t="inlineStr">
+        <is>
+          <t>Roughly 15 US congressional races from 1992 to 2022 were decided by a spoiler, and ranked-choice voting would have changed several of them.</t>
+        </is>
+      </c>
+      <c r="G1179" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="4" t="inlineStr">
+        <is>
+          <t>2021-new-york-city</t>
+        </is>
+      </c>
+      <c r="C1180" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1180" s="4" t="inlineStr">
+        <is>
+          <t>In the 2021 New York City mayoral primary, 14.9% of ballots were exhausted by the final round.</t>
+        </is>
+      </c>
+      <c r="G1180" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="4" t="inlineStr">
+        <is>
+          <t>burlington-vermont-s-2009</t>
+        </is>
+      </c>
+      <c r="C1181" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1181" s="4" t="inlineStr">
+        <is>
+          <t>In Burlington, Vermont's 2009 election, the candidate who would have beaten every rival head to head (the Condorcet winner) was eliminated early, and voters repealed ranked-choice voting in 2010.</t>
+        </is>
+      </c>
+      <c r="G1181" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="4" t="inlineStr">
+        <is>
+          <t>australian-invalid-ballot-rates</t>
+        </is>
+      </c>
+      <c r="C1182" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1182" s="4" t="inlineStr">
+        <is>
+          <t>Australian invalid-ballot rates run 2 to 5%, which indicates a real learning curve.</t>
+        </is>
+      </c>
+      <c r="G1182" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" s="4" t="inlineStr">
+        <is>
+          <t>jurisdictions-adopt-ranked-choice</t>
+        </is>
+      </c>
+      <c r="C1183" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1183" s="4" t="inlineStr">
+        <is>
+          <t>Jurisdictions that adopt ranked-choice voting document higher up-front equipment, training, and tabulation costs.</t>
+        </is>
+      </c>
+      <c r="G1183" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" s="4" t="inlineStr">
+        <is>
+          <t>supporters-ranked-choice-voting</t>
+        </is>
+      </c>
+      <c r="C1184" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D1184" s="4" t="inlineStr">
+        <is>
+          <t>Supporters of ranked-choice voting need to break the two-party lock on elections.</t>
+        </is>
+      </c>
+      <c r="M1184" s="5" t="inlineStr">
+        <is>
+          <t>Representation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" s="4" t="inlineStr">
+        <is>
+          <t>supporters-ranked-choice-voting-2</t>
+        </is>
+      </c>
+      <c r="C1185" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D1185" s="4" t="inlineStr">
+        <is>
+          <t>Supporters of ranked-choice voting need to vote sincerely without wasting their vote.</t>
+        </is>
+      </c>
+      <c r="M1185" s="5" t="inlineStr">
+        <is>
+          <t>Representation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" s="4" t="inlineStr">
+        <is>
+          <t>opponents-ranked-choice-voting</t>
+        </is>
+      </c>
+      <c r="C1186" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D1186" s="4" t="inlineStr">
+        <is>
+          <t>Opponents of ranked-choice voting need to protect the advantage of incumbents and major parties.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="4" t="inlineStr">
+        <is>
+          <t>opponents-ranked-choice-voting-2</t>
+        </is>
+      </c>
+      <c r="C1187" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D1187" s="4" t="inlineStr">
+        <is>
+          <t>Opponents of ranked-choice voting need to keep elections cheap and simple to administer.</t>
+        </is>
+      </c>
+      <c r="M1187" s="5" t="inlineStr">
+        <is>
+          <t>Simplicity and trust</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" s="4" t="inlineStr">
+        <is>
+          <t>voter-error-rates-fall</t>
+        </is>
+      </c>
+      <c r="C1188" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1188" s="4" t="inlineStr">
+        <is>
+          <t>Voter error rates fall after the first ranked-choice voting cycle in a jurisdiction.</t>
+        </is>
+      </c>
+      <c r="G1188" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="4" t="inlineStr">
+        <is>
+          <t>jurisdictions-using-ranked-choice</t>
+        </is>
+      </c>
+      <c r="C1189" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1189" s="4" t="inlineStr">
+        <is>
+          <t>Jurisdictions using ranked-choice voting show more majority winners and fewer spoiler outcomes than comparable jurisdictions using plurality voting.</t>
+        </is>
+      </c>
+      <c r="G1189" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="4" t="inlineStr">
+        <is>
+          <t>jurisdiction-adopts-ranked-choice</t>
+        </is>
+      </c>
+      <c r="C1190" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1190" s="4" t="inlineStr">
+        <is>
+          <t>In a jurisdiction that adopts ranked-choice voting, the cost of running each election falls after the initial outlay for ranked-choice voting equipment.</t>
+        </is>
+      </c>
+      <c r="G1190" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="4" t="inlineStr">
+        <is>
+          <t>jurisdictions-using-ranked-choice-2</t>
+        </is>
+      </c>
+      <c r="C1191" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1191" s="4" t="inlineStr">
+        <is>
+          <t>Jurisdictions using ranked-choice voting show no rise in majority winners, persistently high ballot exhaustion, or falling turnout that does not recover.</t>
+        </is>
+      </c>
+      <c r="G1191" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="4" t="inlineStr">
+        <is>
+          <t>everyone-treated-respect-dignity</t>
+        </is>
+      </c>
+      <c r="C1192" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D1192" s="4" t="inlineStr">
+        <is>
+          <t>Everyone should be treated with respect and dignity.</t>
+        </is>
+      </c>
+      <c r="F1192" s="5" t="inlineStr">
+        <is>
+          <t>rights-and-liberty</t>
+        </is>
+      </c>
+      <c r="W1192" s="4" t="inlineStr">
+        <is>
+          <t>Treating people with dignity does not mean shielding them from the truth. It means inviting them into it.</t>
+        </is>
+      </c>
+      <c r="AB1192" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+      <c r="C1193" s="5" t="inlineStr">
+        <is>
+          <t>belief</t>
+        </is>
+      </c>
+      <c r="D1193" s="4" t="inlineStr">
+        <is>
+          <t>Workers should get tax cuts, and tips should not be taxed as income.</t>
+        </is>
+      </c>
+      <c r="F1193" s="5" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="AB1193" s="5" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" s="4" t="inlineStr">
+        <is>
+          <t>cutting-taxes-workers-exempting</t>
+        </is>
+      </c>
+      <c r="C1194" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1194" s="4" t="inlineStr">
+        <is>
+          <t>Cutting taxes on workers and exempting tips from tax gives workers immediate financial relief.</t>
+        </is>
+      </c>
+      <c r="G1194" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" s="4" t="inlineStr">
+        <is>
+          <t>tipped-workers-often-earn</t>
+        </is>
+      </c>
+      <c r="C1195" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1195" s="4" t="inlineStr">
+        <is>
+          <t>Tipped workers often earn below minimum wage before tips, so cutting taxes on workers and exempting tips from tax would help level the playing field for them.</t>
+        </is>
+      </c>
+      <c r="G1195" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" s="4" t="inlineStr">
+        <is>
+          <t>cutting-taxes-workers-exempting-2</t>
+        </is>
+      </c>
+      <c r="C1196" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1196" s="4" t="inlineStr">
+        <is>
+          <t>Cutting taxes on workers and exempting tips from tax would leave more money in workers' pockets, which could lead to more consumer spending and economic growth.</t>
+        </is>
+      </c>
+      <c r="G1196" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" s="4" t="inlineStr">
+        <is>
+          <t>removing-tips-taxable-income</t>
+        </is>
+      </c>
+      <c r="C1197" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1197" s="4" t="inlineStr">
+        <is>
+          <t>Removing tips from taxable income makes tax filing simpler for tipped workers.</t>
+        </is>
+      </c>
+      <c r="G1197" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" s="4" t="inlineStr">
+        <is>
+          <t>cutting-taxes-workers-exempting-3</t>
+        </is>
+      </c>
+      <c r="C1198" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1198" s="4" t="inlineStr">
+        <is>
+          <t>Cutting taxes on workers and exempting tips from tax reduces financial stress for workers whose income is already precarious.</t>
+        </is>
+      </c>
+      <c r="G1198" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" s="4" t="inlineStr">
+        <is>
+          <t>cutting-taxes-workers-exempting-4</t>
+        </is>
+      </c>
+      <c r="C1199" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1199" s="4" t="inlineStr">
+        <is>
+          <t>Cutting taxes on workers and exempting tips from tax is consistent with the values of fairness and economic equity.</t>
+        </is>
+      </c>
+      <c r="G1199" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" s="4" t="inlineStr">
+        <is>
+          <t>cutting-taxes-workers-exempting-5</t>
+        </is>
+      </c>
+      <c r="C1200" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1200" s="4" t="inlineStr">
+        <is>
+          <t>Cutting taxes on workers and exempting tips from tax helps close the gap between low-income and middle-income earners.</t>
+        </is>
+      </c>
+      <c r="G1200" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" s="4" t="inlineStr">
+        <is>
+          <t>cutting-taxes-workers-exempting-6</t>
+        </is>
+      </c>
+      <c r="C1201" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1201" s="4" t="inlineStr">
+        <is>
+          <t>Cutting taxes on workers and exempting tips from tax strengthens local economies by increasing consumer spending.</t>
+        </is>
+      </c>
+      <c r="G1201" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" s="4" t="inlineStr">
+        <is>
+          <t>cutting-taxes-workers-exempting-7</t>
+        </is>
+      </c>
+      <c r="C1202" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1202" s="4" t="inlineStr">
+        <is>
+          <t>Cutting taxes on workers and exempting tips from tax could create budget deficits for governments that rely on that revenue.</t>
+        </is>
+      </c>
+      <c r="G1202" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="4" t="inlineStr">
+        <is>
+          <t>exempting-tips-tax-may</t>
+        </is>
+      </c>
+      <c r="C1203" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1203" s="4" t="inlineStr">
+        <is>
+          <t>Exempting tips from tax may encourage people to underreport income or make fraudulent claims.</t>
+        </is>
+      </c>
+      <c r="G1203" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="4" t="inlineStr">
+        <is>
+          <t>exempting-tips-tax-could</t>
+        </is>
+      </c>
+      <c r="C1204" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1204" s="4" t="inlineStr">
+        <is>
+          <t>Exempting tips from tax could encourage tax avoidance or fraudulent reporting.</t>
+        </is>
+      </c>
+      <c r="G1204" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="4" t="inlineStr">
+        <is>
+          <t>workers-industries-without-tips</t>
+        </is>
+      </c>
+      <c r="C1205" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1205" s="4" t="inlineStr">
+        <is>
+          <t>Workers in industries without tips may see exempting tips from tax as unfair preferential treatment.</t>
+        </is>
+      </c>
+      <c r="G1205" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="4" t="inlineStr">
+        <is>
+          <t>exempting-tips-tax-could-2</t>
+        </is>
+      </c>
+      <c r="C1206" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1206" s="4" t="inlineStr">
+        <is>
+          <t>Exempting tips from tax could disproportionately favor one group of workers over others.</t>
+        </is>
+      </c>
+      <c r="G1206" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="4" t="inlineStr">
+        <is>
+          <t>exempting-tips-tax-may-2</t>
+        </is>
+      </c>
+      <c r="C1207" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1207" s="4" t="inlineStr">
+        <is>
+          <t>Exempting tips from tax may create perceptions of unfairness among workers who do not receive tips.</t>
+        </is>
+      </c>
+      <c r="G1207" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="4" t="inlineStr">
+        <is>
+          <t>cutting-taxes-workers-exempting-8</t>
+        </is>
+      </c>
+      <c r="C1208" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1208" s="4" t="inlineStr">
+        <is>
+          <t>Cutting taxes on workers and exempting tips from tax may not significantly improve workers' overall financial stability without broader wage reforms.</t>
+        </is>
+      </c>
+      <c r="G1208" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" s="4" t="inlineStr">
+        <is>
+          <t>even-though-financial-relief</t>
+        </is>
+      </c>
+      <c r="C1209" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1209" s="4" t="inlineStr">
+        <is>
+          <t>Even though financial relief for workers is a good goal, cutting taxes on workers and exempting tips from tax is the wrong way to reach it, because it could undermine the tax system's equity and fiscal sustainability and create long-term economic problems.</t>
+        </is>
+      </c>
+      <c r="G1209" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" s="4" t="inlineStr">
+        <is>
+          <t>tax-revenue-lost-cutting</t>
+        </is>
+      </c>
+      <c r="C1210" s="5" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="D1210" s="4" t="inlineStr">
+        <is>
+          <t>The tax revenue lost by cutting taxes on workers and exempting tips may harm public services, and that harm would ultimately fall on the same workers.</t>
+        </is>
+      </c>
+      <c r="G1210" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" s="4" t="inlineStr">
+        <is>
+          <t>low-income-workers-need</t>
+        </is>
+      </c>
+      <c r="C1211" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D1211" s="4" t="inlineStr">
+        <is>
+          <t>Low-income workers need financial relief.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" s="4" t="inlineStr">
+        <is>
+          <t>economy-needs-stimulation-comes</t>
+        </is>
+      </c>
+      <c r="C1212" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D1212" s="4" t="inlineStr">
+        <is>
+          <t>The economy needs the stimulation that comes from increased consumer spending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" s="4" t="inlineStr">
+        <is>
+          <t>tipped-employees-need-fairer</t>
+        </is>
+      </c>
+      <c r="C1213" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D1213" s="4" t="inlineStr">
+        <is>
+          <t>Tipped employees need fairer treatment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" s="4" t="inlineStr">
+        <is>
+          <t>governments-need-preserve-tax</t>
+        </is>
+      </c>
+      <c r="C1214" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D1214" s="4" t="inlineStr">
+        <is>
+          <t>Governments need to preserve tax revenue to fund essential public services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" s="4" t="inlineStr">
+        <is>
+          <t>workers-every-income-category</t>
+        </is>
+      </c>
+      <c r="C1215" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D1215" s="4" t="inlineStr">
+        <is>
+          <t>Workers in every income category need to be treated fairly by the tax system.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC1099"/>
+  <autoFilter ref="A1:AC1215"/>
   <dataValidations count="5">
     <dataValidation sqref="C2:C5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"belief,claim,linkage,importance,interest,uniqueness,equivalence,driver,media"</formula1>
@@ -30569,7 +33084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1704"/>
+  <dimension ref="A1:T1816"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -69974,8 +72489,2482 @@
         </is>
       </c>
     </row>
+    <row r="1705">
+      <c r="A1705" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+      <c r="B1705" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1705" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1705" s="4" t="inlineStr">
+        <is>
+          <t>open-dialogue-vital-informed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+      <c r="B1706" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1706" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1706" s="4" t="inlineStr">
+        <is>
+          <t>free-exchange-ideas-fosters</t>
+        </is>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+      <c r="B1707" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1707" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1707" s="4" t="inlineStr">
+        <is>
+          <t>free-speech-lets-people</t>
+        </is>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+      <c r="B1708" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1708" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1708" s="4" t="inlineStr">
+        <is>
+          <t>societies-strong-protections-speech</t>
+        </is>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+      <c r="B1709" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1709" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1709" s="4" t="inlineStr">
+        <is>
+          <t>defending-free-speech-upholds</t>
+        </is>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+      <c r="B1710" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1710" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1710" s="4" t="inlineStr">
+        <is>
+          <t>defending-free-speech-encourages</t>
+        </is>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+      <c r="B1711" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1711" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1711" s="4" t="inlineStr">
+        <is>
+          <t>defending-free-speech-promotes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+      <c r="B1712" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1712" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1712" s="4" t="inlineStr">
+        <is>
+          <t>defending-free-speech-ensures</t>
+        </is>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+      <c r="B1713" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1713" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1713" s="4" t="inlineStr">
+        <is>
+          <t>unchecked-speech-can-spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+      <c r="B1714" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1714" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1714" s="4" t="inlineStr">
+        <is>
+          <t>free-speech-protections-can</t>
+        </is>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+      <c r="B1715" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1715" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1715" s="4" t="inlineStr">
+        <is>
+          <t>defending-free-speech-may</t>
+        </is>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+      <c r="B1716" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1716" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1716" s="4" t="inlineStr">
+        <is>
+          <t>defending-free-speech-risks</t>
+        </is>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+      <c r="B1717" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1717" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1717" s="4" t="inlineStr">
+        <is>
+          <t>defending-free-speech-could</t>
+        </is>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+      <c r="B1718" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1718" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1718" s="4" t="inlineStr">
+        <is>
+          <t>defending-free-speech-may-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+      <c r="B1719" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1719" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1719" s="4" t="inlineStr">
+        <is>
+          <t>supporters-need-individual-liberties</t>
+        </is>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+      <c r="B1720" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1720" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1720" s="4" t="inlineStr">
+        <is>
+          <t>supporters-need-accountability-transparency</t>
+        </is>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+      <c r="B1721" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1721" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1721" s="4" t="inlineStr">
+        <is>
+          <t>supporters-need-open-dialogue</t>
+        </is>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+      <c r="B1722" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1722" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1722" s="4" t="inlineStr">
+        <is>
+          <t>opponents-need-public-safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+      <c r="B1723" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1723" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1723" s="4" t="inlineStr">
+        <is>
+          <t>opponents-need-free-speech</t>
+        </is>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-our-fundamental</t>
+        </is>
+      </c>
+      <c r="B1724" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1724" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1724" s="4" t="inlineStr">
+        <is>
+          <t>opponents-need-safer-more</t>
+        </is>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+      <c r="B1725" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1725" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1725" s="4" t="inlineStr">
+        <is>
+          <t>defending-freedom-religion-protects</t>
+        </is>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+      <c r="B1726" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1726" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1726" s="4" t="inlineStr">
+        <is>
+          <t>freedom-religion-allows-diverse</t>
+        </is>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+      <c r="B1727" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1727" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1727" s="4" t="inlineStr">
+        <is>
+          <t>defending-freedom-religion-prevents</t>
+        </is>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+      <c r="B1728" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1728" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1728" s="4" t="inlineStr">
+        <is>
+          <t>defending-both-freedom-religion</t>
+        </is>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+      <c r="B1729" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1729" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1729" s="4" t="inlineStr">
+        <is>
+          <t>defending-freedom-religion-respects</t>
+        </is>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+      <c r="B1730" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1730" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1730" s="4" t="inlineStr">
+        <is>
+          <t>defending-freedom-religion-prevents-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+      <c r="B1731" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1731" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1731" s="4" t="inlineStr">
+        <is>
+          <t>defending-freedom-religion-encourages</t>
+        </is>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+      <c r="B1732" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1732" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1732" s="4" t="inlineStr">
+        <is>
+          <t>defending-freedom-religion-preserves</t>
+        </is>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+      <c r="B1733" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1733" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1733" s="4" t="inlineStr">
+        <is>
+          <t>defending-freedom-religion-means</t>
+        </is>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+      <c r="B1734" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1734" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1734" s="4" t="inlineStr">
+        <is>
+          <t>religious-groups-can-exploit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+      <c r="B1735" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1735" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1735" s="4" t="inlineStr">
+        <is>
+          <t>defending-freedom-religion-can</t>
+        </is>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+      <c r="B1736" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1736" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1736" s="4" t="inlineStr">
+        <is>
+          <t>complete-freedom-religion-could</t>
+        </is>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+      <c r="B1737" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1737" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1737" s="4" t="inlineStr">
+        <is>
+          <t>defending-freedom-religion-may</t>
+        </is>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+      <c r="B1738" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1738" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1738" s="4" t="inlineStr">
+        <is>
+          <t>defending-freedom-religion-could</t>
+        </is>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+      <c r="B1739" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1739" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1739" s="4" t="inlineStr">
+        <is>
+          <t>defending-freedom-religion-risks</t>
+        </is>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+      <c r="B1740" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1740" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1740" s="4" t="inlineStr">
+        <is>
+          <t>defending-freedom-religion-may-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+      <c r="B1741" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1741" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1741" s="4" t="inlineStr">
+        <is>
+          <t>supporters-need-individual-liberties-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+      <c r="B1742" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1742" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1742" s="4" t="inlineStr">
+        <is>
+          <t>supporters-need-government-stay</t>
+        </is>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+      <c r="B1743" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1743" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1743" s="4" t="inlineStr">
+        <is>
+          <t>opponents-need-dominant-cultural</t>
+        </is>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" s="4" t="inlineStr">
+        <is>
+          <t>we-defend-freedom-religion</t>
+        </is>
+      </c>
+      <c r="B1744" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1744" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1744" s="4" t="inlineStr">
+        <is>
+          <t>opponents-need-religious-freedoms</t>
+        </is>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+      <c r="B1745" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1745" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1745" s="4" t="inlineStr">
+        <is>
+          <t>making-critical-goods-home</t>
+        </is>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+      <c r="B1746" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1746" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1746" s="4" t="inlineStr">
+        <is>
+          <t>bringing-manufacturing-home-creates</t>
+        </is>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+      <c r="B1747" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1747" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1747" s="4" t="inlineStr">
+        <is>
+          <t>domestic-production-ensures-secure</t>
+        </is>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+      <c r="B1748" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1748" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1748" s="4" t="inlineStr">
+        <is>
+          <t>producing-more-goods-home</t>
+        </is>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+      <c r="B1749" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1749" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1749" s="4" t="inlineStr">
+        <is>
+          <t>bringing-manufacturing-home-encourages</t>
+        </is>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+      <c r="B1750" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1750" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1750" s="4" t="inlineStr">
+        <is>
+          <t>push-bring-manufacturing-home</t>
+        </is>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+      <c r="B1751" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1751" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1751" s="4" t="inlineStr">
+        <is>
+          <t>curbing-outsourcing-reduces-exploitation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+      <c r="B1752" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1752" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1752" s="4" t="inlineStr">
+        <is>
+          <t>manufacturing-revival-promotes-fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+      <c r="B1753" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1753" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1753" s="4" t="inlineStr">
+        <is>
+          <t>manufacturing-revival-strengthens-united</t>
+        </is>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+      <c r="B1754" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1754" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1754" s="4" t="inlineStr">
+        <is>
+          <t>domestic-production-often-more</t>
+        </is>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+      <c r="B1755" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1755" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1755" s="4" t="inlineStr">
+        <is>
+          <t>reducing-outsourcing-harms-economies</t>
+        </is>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+      <c r="B1756" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1756" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1756" s="4" t="inlineStr">
+        <is>
+          <t>united-states-lacks-enough</t>
+        </is>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+      <c r="B1757" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1757" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1757" s="4" t="inlineStr">
+        <is>
+          <t>increased-domestic-manufacturing-could</t>
+        </is>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+      <c r="B1758" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1758" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1758" s="4" t="inlineStr">
+        <is>
+          <t>protectionist-policies-end-outsourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+      <c r="B1759" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1759" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1759" s="4" t="inlineStr">
+        <is>
+          <t>policies-discourage-outsourcing-may</t>
+        </is>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+      <c r="B1760" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1760" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1760" s="4" t="inlineStr">
+        <is>
+          <t>curbing-outsourcing-could-harm</t>
+        </is>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+      <c r="B1761" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1761" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1761" s="4" t="inlineStr">
+        <is>
+          <t>domestic-manufacturing-could-raise</t>
+        </is>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+      <c r="B1762" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1762" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1762" s="4" t="inlineStr">
+        <is>
+          <t>pushing-become-manufacturing-superpower</t>
+        </is>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+      <c r="B1763" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1763" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1763" s="4" t="inlineStr">
+        <is>
+          <t>supporters-need-economic-growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="A1764" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+      <c r="B1764" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1764" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1764" s="4" t="inlineStr">
+        <is>
+          <t>supporters-need-national-security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="A1765" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+      <c r="B1765" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1765" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1765" s="4" t="inlineStr">
+        <is>
+          <t>supporters-need-self-sufficiency</t>
+        </is>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+      <c r="B1766" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1766" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1766" s="4" t="inlineStr">
+        <is>
+          <t>opponents-need-lower-costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+      <c r="B1767" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1767" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1767" s="4" t="inlineStr">
+        <is>
+          <t>opponents-need-strong-international</t>
+        </is>
+      </c>
+    </row>
+    <row r="1768">
+      <c r="A1768" s="4" t="inlineStr">
+        <is>
+          <t>united-states-stop-outsourcing</t>
+        </is>
+      </c>
+      <c r="B1768" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1768" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1768" s="4" t="inlineStr">
+        <is>
+          <t>opponents-need-global-economic</t>
+        </is>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+      <c r="B1769" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1769" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1769" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-eliminates</t>
+        </is>
+      </c>
+    </row>
+    <row r="1770">
+      <c r="A1770" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+      <c r="B1770" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1770" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1770" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+      <c r="B1771" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1771" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1771" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-rewards</t>
+        </is>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+      <c r="B1772" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1772" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1772" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-makes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1773">
+      <c r="A1773" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+      <c r="B1773" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1773" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1773" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-causes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+      <c r="B1774" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1774" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1774" s="4" t="inlineStr">
+        <is>
+          <t>under-ranked-choice-voting</t>
+        </is>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+      <c r="B1775" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1775" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1775" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-non</t>
+        </is>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+      <c r="B1776" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1776" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1776" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-adds</t>
+        </is>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="A1777" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+      <c r="B1777" s="5" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="C1777" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1777" s="4" t="inlineStr">
+        <is>
+          <t>maine-has-run-statewide</t>
+        </is>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+      <c r="B1778" s="5" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="C1778" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1778" s="4" t="inlineStr">
+        <is>
+          <t>australia-has-used-preferential</t>
+        </is>
+      </c>
+    </row>
+    <row r="1779">
+      <c r="A1779" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+      <c r="B1779" s="5" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="C1779" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1779" s="4" t="inlineStr">
+        <is>
+          <t>academic-simulations-find-ranked</t>
+        </is>
+      </c>
+      <c r="F1779" s="4" t="inlineStr">
+        <is>
+          <t>Tideman; Levin and Nalebuff</t>
+        </is>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+      <c r="B1780" s="5" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="C1780" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1780" s="4" t="inlineStr">
+        <is>
+          <t>roughly-15-us-congressional</t>
+        </is>
+      </c>
+      <c r="F1780" s="4" t="inlineStr">
+        <is>
+          <t>FairVote</t>
+        </is>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+      <c r="B1781" s="5" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="C1781" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1781" s="4" t="inlineStr">
+        <is>
+          <t>2021-new-york-city</t>
+        </is>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="A1782" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+      <c r="B1782" s="5" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="C1782" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1782" s="4" t="inlineStr">
+        <is>
+          <t>burlington-vermont-s-2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="1783">
+      <c r="A1783" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+      <c r="B1783" s="5" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="C1783" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1783" s="4" t="inlineStr">
+        <is>
+          <t>australian-invalid-ballot-rates</t>
+        </is>
+      </c>
+    </row>
+    <row r="1784">
+      <c r="A1784" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+      <c r="B1784" s="5" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="C1784" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1784" s="4" t="inlineStr">
+        <is>
+          <t>jurisdictions-adopt-ranked-choice</t>
+        </is>
+      </c>
+    </row>
+    <row r="1785">
+      <c r="A1785" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+      <c r="B1785" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1785" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1785" s="4" t="inlineStr">
+        <is>
+          <t>supporters-ranked-choice-voting</t>
+        </is>
+      </c>
+    </row>
+    <row r="1786">
+      <c r="A1786" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+      <c r="B1786" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1786" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1786" s="4" t="inlineStr">
+        <is>
+          <t>supporters-ranked-choice-voting-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1787">
+      <c r="A1787" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+      <c r="B1787" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1787" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1787" s="4" t="inlineStr">
+        <is>
+          <t>opponents-ranked-choice-voting</t>
+        </is>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="A1788" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+      <c r="B1788" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1788" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1788" s="4" t="inlineStr">
+        <is>
+          <t>opponents-ranked-choice-voting-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1789">
+      <c r="A1789" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+      <c r="B1789" s="5" t="inlineStr">
+        <is>
+          <t>shared_interest</t>
+        </is>
+      </c>
+      <c r="E1789" s="4" t="inlineStr">
+        <is>
+          <t>Both sides need legitimate winners that voters trust.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1790">
+      <c r="A1790" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+      <c r="B1790" s="5" t="inlineStr">
+        <is>
+          <t>compromise</t>
+        </is>
+      </c>
+      <c r="E1790" s="4" t="inlineStr">
+        <is>
+          <t>Ranked-choice voting should be phased in at the local level first, with funded equipment, voter education, and a rule that voters rank enough candidates to cut ballot exhaustion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1791">
+      <c r="A1791" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+      <c r="B1791" s="5" t="inlineStr">
+        <is>
+          <t>prediction</t>
+        </is>
+      </c>
+      <c r="C1791" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1791" s="4" t="inlineStr">
+        <is>
+          <t>voter-error-rates-fall</t>
+        </is>
+      </c>
+      <c r="S1791" s="4" t="inlineStr">
+        <is>
+          <t>2 to 3 cycles; spoiled-ballot rates over time</t>
+        </is>
+      </c>
+    </row>
+    <row r="1792">
+      <c r="A1792" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+      <c r="B1792" s="5" t="inlineStr">
+        <is>
+          <t>prediction</t>
+        </is>
+      </c>
+      <c r="C1792" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1792" s="4" t="inlineStr">
+        <is>
+          <t>jurisdictions-using-ranked-choice</t>
+        </is>
+      </c>
+    </row>
+    <row r="1793">
+      <c r="A1793" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+      <c r="B1793" s="5" t="inlineStr">
+        <is>
+          <t>prediction</t>
+        </is>
+      </c>
+      <c r="C1793" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1793" s="4" t="inlineStr">
+        <is>
+          <t>jurisdiction-adopts-ranked-choice</t>
+        </is>
+      </c>
+      <c r="S1793" s="4" t="inlineStr">
+        <is>
+          <t>5+ years; jurisdiction budget records</t>
+        </is>
+      </c>
+    </row>
+    <row r="1794">
+      <c r="A1794" s="4" t="inlineStr">
+        <is>
+          <t>ranked-choice-voting-produces-2</t>
+        </is>
+      </c>
+      <c r="B1794" s="5" t="inlineStr">
+        <is>
+          <t>prediction</t>
+        </is>
+      </c>
+      <c r="C1794" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1794" s="4" t="inlineStr">
+        <is>
+          <t>jurisdictions-using-ranked-choice-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1795">
+      <c r="A1795" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+      <c r="B1795" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1795" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1795" s="4" t="inlineStr">
+        <is>
+          <t>cutting-taxes-workers-exempting</t>
+        </is>
+      </c>
+    </row>
+    <row r="1796">
+      <c r="A1796" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+      <c r="B1796" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1796" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1796" s="4" t="inlineStr">
+        <is>
+          <t>tipped-workers-often-earn</t>
+        </is>
+      </c>
+    </row>
+    <row r="1797">
+      <c r="A1797" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+      <c r="B1797" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1797" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1797" s="4" t="inlineStr">
+        <is>
+          <t>cutting-taxes-workers-exempting-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1798">
+      <c r="A1798" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+      <c r="B1798" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1798" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1798" s="4" t="inlineStr">
+        <is>
+          <t>removing-tips-taxable-income</t>
+        </is>
+      </c>
+    </row>
+    <row r="1799">
+      <c r="A1799" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+      <c r="B1799" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1799" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1799" s="4" t="inlineStr">
+        <is>
+          <t>cutting-taxes-workers-exempting-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1800">
+      <c r="A1800" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+      <c r="B1800" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1800" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1800" s="4" t="inlineStr">
+        <is>
+          <t>cutting-taxes-workers-exempting-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1801">
+      <c r="A1801" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+      <c r="B1801" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1801" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1801" s="4" t="inlineStr">
+        <is>
+          <t>cutting-taxes-workers-exempting-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1802">
+      <c r="A1802" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+      <c r="B1802" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1802" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1802" s="4" t="inlineStr">
+        <is>
+          <t>cutting-taxes-workers-exempting-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1803">
+      <c r="A1803" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+      <c r="B1803" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1803" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1803" s="4" t="inlineStr">
+        <is>
+          <t>cutting-taxes-workers-exempting-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1804">
+      <c r="A1804" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+      <c r="B1804" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1804" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1804" s="4" t="inlineStr">
+        <is>
+          <t>exempting-tips-tax-may</t>
+        </is>
+      </c>
+    </row>
+    <row r="1805">
+      <c r="A1805" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+      <c r="B1805" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1805" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1805" s="4" t="inlineStr">
+        <is>
+          <t>exempting-tips-tax-could</t>
+        </is>
+      </c>
+    </row>
+    <row r="1806">
+      <c r="A1806" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+      <c r="B1806" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1806" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1806" s="4" t="inlineStr">
+        <is>
+          <t>workers-industries-without-tips</t>
+        </is>
+      </c>
+    </row>
+    <row r="1807">
+      <c r="A1807" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+      <c r="B1807" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1807" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1807" s="4" t="inlineStr">
+        <is>
+          <t>exempting-tips-tax-could-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1808">
+      <c r="A1808" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+      <c r="B1808" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1808" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1808" s="4" t="inlineStr">
+        <is>
+          <t>exempting-tips-tax-may-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1809">
+      <c r="A1809" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+      <c r="B1809" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1809" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1809" s="4" t="inlineStr">
+        <is>
+          <t>cutting-taxes-workers-exempting-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1810">
+      <c r="A1810" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+      <c r="B1810" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1810" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1810" s="4" t="inlineStr">
+        <is>
+          <t>even-though-financial-relief</t>
+        </is>
+      </c>
+    </row>
+    <row r="1811">
+      <c r="A1811" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+      <c r="B1811" s="5" t="inlineStr">
+        <is>
+          <t>argument</t>
+        </is>
+      </c>
+      <c r="C1811" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1811" s="4" t="inlineStr">
+        <is>
+          <t>tax-revenue-lost-cutting</t>
+        </is>
+      </c>
+    </row>
+    <row r="1812">
+      <c r="A1812" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+      <c r="B1812" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1812" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1812" s="4" t="inlineStr">
+        <is>
+          <t>low-income-workers-need</t>
+        </is>
+      </c>
+    </row>
+    <row r="1813">
+      <c r="A1813" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+      <c r="B1813" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1813" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1813" s="4" t="inlineStr">
+        <is>
+          <t>economy-needs-stimulation-comes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1814">
+      <c r="A1814" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+      <c r="B1814" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1814" s="5" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="D1814" s="4" t="inlineStr">
+        <is>
+          <t>tipped-employees-need-fairer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1815">
+      <c r="A1815" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+      <c r="B1815" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1815" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1815" s="4" t="inlineStr">
+        <is>
+          <t>governments-need-preserve-tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="1816">
+      <c r="A1816" s="4" t="inlineStr">
+        <is>
+          <t>workers-get-tax-cuts</t>
+        </is>
+      </c>
+      <c r="B1816" s="5" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="C1816" s="5" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="D1816" s="4" t="inlineStr">
+        <is>
+          <t>workers-every-income-category</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T1704"/>
+  <autoFilter ref="A1:T1816"/>
   <dataValidations count="2">
     <dataValidation sqref="B2:B5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"argument,assumption,bias,category,cba,common,component,compromise,criteria,criterion,definition,direction,dispute,downstream,engagement,evidence,falsify,impact,interest,interest_listing,law,long_term,media,motive,obstacle,person,prediction,related,rung,shared_interest,short_term,similar,stack,strength,topic_media,topic_values,upstream,value"</formula1>
